--- a/work/from_google/missions.xlsx
+++ b/work/from_google/missions.xlsx
@@ -1989,7 +1989,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Captura de un miembro de la pandilla de Arlington en Oslo, Arlington.</v>
+        <v>Captura de un miembro de una pandilla de Arlington en Oslo, Arlington.</v>
       </c>
     </row>
     <row r="319" xml:space="preserve">
@@ -2749,7 +2749,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v> Otro intento de entrega de viento rojo</v>
+        <v> Otro intento de entrega de Red Wind</v>
       </c>
     </row>
     <row r="471" xml:space="preserve">

--- a/work/from_google/missions.xlsx
+++ b/work/from_google/missions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A609"/>
+  <dimension ref="A1:A1503"/>
   <cols>
     <col min="1" max="1" width="150.83203125" customWidth="1"/>
   </cols>
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v xml:space="preserve"> Certificación de Detención de Sospechosos</v>
+        <v> Se necesita recuperador (escasa cantidad de RMC)</v>
       </c>
     </row>
     <row r="3">
@@ -419,7 +419,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v> Certificación de Permiso de Iniciación para Rastreadores</v>
+        <v> Adagio Holdings necesita rescatadores.</v>
       </c>
     </row>
     <row r="5">
@@ -429,7 +429,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v> Certificación de recuperación de fugitivos</v>
+        <v xml:space="preserve"> Se necesita recuperador (suministro médico de RMC)</v>
       </c>
     </row>
     <row r="7">
@@ -439,3017 +439,7487 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v> Certificación de Licencia de Rastreador Oficial</v>
+        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v> Certificación de licencia de rastreador</v>
+        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v> Certificación de Licencia de Rastreador Maestro</v>
+        <v> Recompensa preliminar: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v> Recompensa preliminar: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v> Certificación de Permiso de Capacitación en Rastreo</v>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v> Certificación de licencia de rastreador avanzado</v>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) | Cazadores de cabezas | ~misión(Peligro)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) | Cazadores de cabezas | ~misión(Peligro)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v> En llamas</v>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v> Mal funcionamiento grave</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str" xml:space="preserve">
-        <v xml:space="preserve">No voy a entrar en detalles sobre el porqué, pero hay algunas partes de ~mission(Location|Address) que necesitamos destruir. Lo importante es que quiero pagarte una buena cantidad de créditos por hacerlo. Casi siento que deberías pagarnos tú por esto, porque va a ser muy divertido. No me importa cómo lo hagas. Granadas, lanzacohetes, Torpedo Burrito del día anterior, nos da igual. -Bit Zeros</v>
+        <v> Recompensa verificada: ~mission(TargetName)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v> Recompensa verificada: ~mission(TargetName)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v> Servidor no encontrado</v>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos un problema en el que podríamos necesitar tu ayuda. Uno de nuestros exreclutas hizo un trabajo pésimo en un hackeo y dejó una huella digital tan desastrosa que casi podría considerarse una confesión. Un borrado remoto no será suficiente, así que quiero que vayas a ~mission(Location|Address) y te asegures de que sus servidores de datos sean eliminados por completo. Como si esto no fuera ya un lío mayor, los códigos de acceso a la puerta cerrada de la sala de servidores solo se almacenan físicamente allí. Eso significa que primero tendrás que conseguir un datapad con el código antes de poder siquiera acercarte a ellos. Pero no te preocupes, me aseguraré de que las credenciales valgan la pena. - Bit Zeros</v>
+        <v>Recompensa verificada: ~misión(Nombre del objetivo) | Amenaza alienígena | ~misión(Peligro)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) | Amenaza alienígena | ~misión(Peligro)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v> Golpéalos donde más les duele</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los cretinos de ~mission(Location|Address) decidieron que sería buena idea interferir en nuestros asuntos, y ahora debemos dejarles bien claro que se equivocaron. Tras investigar un poco sus datos, descubrimos dónde guardan su mercancía. Ahora solo tienes que ir allí y destruirlo todo. Creo que con eso les quedará claro. - Bit Zeros</v>
+        <v xml:space="preserve"> Certificación de Detención de Sospechosos</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v> Eliminar permanentemente</v>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Esos cretinos repugnantes de ~mission(Location|Address) nos han estado vendiendo datos basura mientras intentaban engañarnos. No podemos permitirlo. Queremos que les des una última lección y elimines a todos los cobardes que encuentres. La última vez que supe de ellos, estaban escondidos cerca de ~mission(Location). Si los derribas, te llenaremos la cartera. -Bit Zeros</v>
+        <v> Certificación de Permiso de Iniciación para Rastreadores</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v> Reasignación de propiedad</v>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Muy bien, en ~mission(Location|Address) tienen algunas cosas que necesitan ser recuperadas. Claro que puede que tengas que lidiar con algunos guardias o personas preocupadas, pero en general es una transacción bastante sencilla: toma las cosas de ~mission(Location) y tráelas a ~mission(Destination|Address). A veces, lo simple es lo mejor. -Bit Zeros</v>
+        <v> Certificación de recuperación de fugitivos</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v> Tratos delicados</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espero de verdad que aceptes hacer esto, ya que no parece haber mucha gente dispuesta a encargarse de un montón de minas de proximidad. Verás, hemos encontrado un botín en ~mission(Location|Address), pero la seguridad física está resultando más difícil de lo esperado. Si encuentras la manera de sortear las minas o, posiblemente, de activarlas a distancia, debería ser relativamente fácil recoger el botín y escapar. Déjalo en ~mission(Destination|Address) y recibirás una buena parte de los créditos por correr el riesgo. -Bit Zeros</v>
+        <v> Certificación de Licencia de Rastreador Oficial</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (?RT)</v>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan capturar a una persona con el nombre ~mission(TargetName) en ~mission(Location|Address). Si bien puede haber otros cómplices criminales en el lugar, les pido que tengan cuidado con los civiles o trabajadores que puedan estar allí. Ya tengo suficientes problemas, así que no necesito explicar por qué un contratista disparó a varios civiles. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v> Certificación de licencia de rastreador</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Actualmente tengo más recompensas que cazarrecompensas, así que busco ampliar nuestra plantilla. Si hacen un buen trabajo en esta primera misión, habrá más contratos. Veamos cómo les va con la recompensa en ~mission(TargetName). Se cree que se esconden en ~mission(Location|Address). Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v> Certificación de Licencia de Rastreador Maestro</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Excazador de recompensas de BlacJac. Sé que BlacJac dejó de ofrecer contratos de recompensa, pero los tiempos cambian y aquí estamos para darle otra oportunidad. Si logra completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reactivar su cuenta. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v> Certificación de Permiso de Capacitación en Rastreo</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (ERT)</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Quizás hayan oído hablar de ~mission(TargetName). Son un objetivo de alto riesgo y han estado en las noticias últimamente. Esperamos que puedan formar un equipo de respuesta y ayudar a BlacJac a neutralizarlos definitivamente. Según nuestra información más reciente, su nave subcapital y escoltas fuertemente armadas sobrevuelan ~mission(Location|Address). Les recomiendo asegurarse de tener una identificación actualizada antes de partir. Por si acaso. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
+        <v> Certificación de licencia de rastreador avanzado</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (HRT)</v>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Su próximo objetivo, ~mission(TargetName), es sin duda un objetivo de alto riesgo, y con razón. Se sabe que viaja con armamento pesado y cuenta con suficiente protección como para que cualquiera se lo piense dos veces antes de enfrentarse a él. Según fuentes, ~mission(TargetName|Last) se esconde en ~mission(Location|Address). Cuando salgan a buscarlo, asegúrense de estar preparados. Quizás incluso deberían llevar refuerzos. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
+        <v> En llamas</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazadores de recompensas. No sé si les interesa, pero BlacJac busca ampliar su equipo de cazarrecompensas. Tenemos más trabajos de los que nuestros contratistas actuales pueden cubrir, así que espero que puedan ayudarnos a cubrir parte de la carga de trabajo. Sus cualificaciones se ven bien en papel, pero antes de formalizar nada, BlacJac necesita ver su desempeño en el campo. Incluso tenemos un caso de prueba preparado: queremos que resuelvan la misión ~(Nombre del objetivo). Fueron vistos por última vez en ~misión(Ubicación|Dirección). Debería ser una recompensa bastante sencilla, sin demasiada resistencia. Una oportunidad perfecta para que se pongan a prueba. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (LRT)</v>
+        <v> Mal funcionamiento grave</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Se ha ofrecido una recompensa por un objetivo de bajo riesgo llamado ~mission(TargetName). El objetivo en sí no es muy peligroso, pero parece que suelen volar en grupo, así que hay muchas probabilidades de que vengan acompañados cuando los localicen. Por cierto, les recomiendo comenzar la búsqueda en ~mission(Location|Address), ya que tenemos informes de que los han visto en la zona. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> No voy a entrar en detalles sobre el porqué, pero hay algunas partes de ~mission(Location|Address) que necesitamos destruir. Lo importante es que quiero pagarte una buena cantidad de créditos por hacerlo. Casi siento que deberías pagarnos tú por esto, porque va a ser muy divertido. No me importa cómo lo hagas. Granadas, lanzacohetes, Torpedo Burrito del día anterior, nos da igual. -Bit Zeros</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (MRT)</v>
+        <v> Servidor no encontrado</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan que se encarguen de ~mission(TargetName), una recompensa de riesgo moderado vista por última vez en ~mission(Location|Address) pilotando una pequeña nave con tripulación múltiple. No pudimos obtener detalles sobre la nave que pilotaban, pero parece que tenían otras naves con ellos. Prepárense para una fuerte resistencia cuando lleguen. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">Hola, tenemos un problema en el que podríamos necesitar tu ayuda. Uno de nuestros exreclutas hizo un trabajo pésimo en un hackeo y dejó una huella digital tan desastrosa que casi podría considerarse una confesión. Un borrado remoto no será suficiente, así que quiero que vayas a ~mission(Location|Address) y te asegures de que sus servidores de datos sean eliminados por completo. Como si esto no fuera ya un lío mayor, los códigos de acceso a la puerta cerrada de la sala de servidores solo se almacenan físicamente allí. Eso significa que primero tendrás que conseguir un datapad con el código antes de poder siquiera acercarte a ellos. Pero no te preocupes, me aseguraré de que las credenciales valgan la pena. - Bit Zeros</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
+        <v> Golpéalos donde más les duele</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Excazador de recompensas de BlacJac. Sé que tu última misión para BlacJac no salió bien, pero el aumento de casos significa que tienes la suerte de tener otra oportunidad. Si logras completar la misión en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reincorporarte. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">Los cretinos de ~mission(Location|Address) decidieron que sería buena idea interferir en nuestros asuntos, y ahora debemos dejarles bien claro que se equivocaron. Tras investigar un poco sus datos, descubrimos dónde guardan su mercancía. Ahora solo tienes que ir allí y destruirlo todo. Creo que con eso les quedará claro. - Bit Zeros</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VHRT)</v>
+        <v> Eliminar permanentemente</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas BlacJac acaba de recibir información de que un objetivo de altísimo riesgo, ~mission(TargetName), fue avistado en las rutas aéreas de ~mission(Location|Address) pilotando una formidable nave con una fuerte escolta. Queremos eliminar esta recompensa antes de que cometa más delitos. Reúnan los recursos y el apoyo que necesiten y salgan cuanto antes. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> Esos cretinos repugnantes de ~mission(Location|Address) nos han estado vendiendo datos basura mientras intentaban engañarnos. No podemos permitirlo. Queremos que les des una última lección y elimines a todos los cobardes que encuentres. La última vez que supe de ellos, estaban escondidos cerca de ~mission(Location). Si los derribas, te llenaremos la cartera. -Bit Zeros</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VLRT)</v>
+        <v> Reasignación de propiedad</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Tengo un objetivo de muy bajo riesgo del que debo encargarme: ~mission(NombreDelObjetivo). Su última ubicación conocida fue ~mission(Ubicación|Dirección). Se trata de una recompensa de bajo riesgo, así que espero que puedan resolverla rápidamente. Suelen pilotar una nave pequeña y no tienen muchos conocidos. Es una misión sencilla. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">Muy bien, en ~mission(Location|Address) tienen algunas cosas que necesitan ser recuperadas. Claro que puede que tengas que lidiar con algunos guardias o personas preocupadas, pero en general es una transacción bastante sencilla: toma las cosas de ~mission(Location) y tráelas a ~mission(Destination|Address). A veces, lo simple es lo mejor. -Bit Zeros</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Proteger el sitio y obtener materiales confidenciales.</v>
+        <v> Tratos delicados</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
       <c r="A55" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Mercenarios con experiencia en manejo de carga. Nine Tails está atacando una de nuestras instalaciones en ~mission(Location|address). Dado que acaban de recibir un envío de material confidencial, no creemos que sea una coincidencia. BlacJac necesita que alguien se dirija rápidamente al lugar y asegure estas cajas importantes antes de que lo haga Nine Tails. Están autorizados a usar fuerza letal contra cualquiera que intente detenerlos. Como parte de nuestro protocolo de seguridad estándar, el material confidencial se integró en otro envío y se guardó en la bóveda automatizada. Deberán encontrar los códigos de recuperación correspondientes para el material confidencial e introducirlos en la cinta transportadora de paquetes para recuperar las cajas. Los códigos de recuperación se almacenan localmente en tabletas de datos y solo se entregan al personal de alto rango. Esperemos que estén vivos para ayudarlos, pero considerando el apagón total de comunicaciones, tememos que no sea así. Existe la posibilidad de que Nine Tails ya se haya apoderado de las tabletas de datos. Una vez que haya reunido todo el material confidencial, deberá entregarlo en ~mission(dropoff1|address). El pago está condicionado a su entrega. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">Espero de verdad que aceptes hacer esto, ya que no parece haber mucha gente dispuesta a encargarse de un montón de minas de proximidad. Verás, hemos encontrado un botín en ~mission(Location|Address), pero la seguridad física está resultando más difícil de lo esperado. Si encuentras la manera de sortear las minas o, posiblemente, de activarlas a distancia, debería ser relativamente fácil recoger el botín y escapar. Déjalo en ~mission(Destination|Address) y recibirás una buena parte de los créditos por correr el riesgo. -Bit Zeros</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Proteger el sitio de amenazas menores</v>
+        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (?RT)</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Operadores Mercenarios Verificados. Uno de los sitios bajo la supervisión de BlacJac ha tenido enfrentamientos con algunos delincuentes locales. Les pedimos que se dirijan a ~mission(Ubicación|Dirección) y aseguren el sitio de estas amenazas. Según los primeros informes, esto será bastante sencillo, pero si lo desean, pueden reclutar un equipo para que les brinde apoyo adicional. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan capturar a una persona con el nombre ~mission(TargetName) en ~mission(Location|Address). Si bien puede haber otros cómplices criminales en el lugar, les pido que tengan cuidado con los civiles o trabajadores que puedan estar allí. Ya tengo suficientes problemas, así que no necesito explicar por qué un contratista disparó a varios civiles. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v> Proteja el sitio de amenazas</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que algunos matones locales han estado haciendo amenazas contra ~mission(Location|Address). BlacJac busca que formen un equipo para proteger el sitio de estas amenazas. Y aunque a todos nos encantan los créditos, no recomiendo intentar hacerlo solos. Contratar un equipo sería beneficioso para su sustento. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Actualmente tengo más recompensas que cazarrecompensas, así que busco ampliar nuestra plantilla. Si hacen un buen trabajo en esta primera misión, habrá más contratos. Veamos cómo les va con la recompensa en ~mission(TargetName). Se cree que se esconden en ~mission(Location|Address). Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v> Proteja el sitio de amenazas peligrosas.</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. He recibido un informe de que algunos operadores planean un ataque contra ~mission(Location|Address). BlacJac les pide que formen un equipo para defender el sitio de esta peligrosa amenaza. Se recomienda encarecidamente no intentar completar este contrato en solitario. Contratar un equipo de mercenarios experimentados para que les brinden apoyo sería la opción más inteligente. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security. "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Excazador de recompensas de BlacJac. Sé que BlacJac dejó de ofrecer contratos de recompensa, pero los tiempos cambian y aquí estamos para darle otra oportunidad. Si logra completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reactivar su cuenta. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v> Eliminar el alijo de drogas</v>
+        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (ERT)</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Parece que hay un nuevo operador intentando fabricar drogas en ~mission(Location|Address), pero el producto que está produciendo es extremadamente tóxico. Estamos analizando cómo proceder con los arrestos, pero lo importante es evitar que se distribuya más de su mercancía. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. Es muy probable que la instalación no esté abandonada, así que podrían encontrarse con estos delincuentes al llegar. Prepárense para una pelea. Pero si su habilidad con las armas es similar a su química, probablemente no será muy dura. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Quizás hayan oído hablar de ~mission(TargetName). Son un objetivo de alto riesgo y han estado en las noticias últimamente. Esperamos que puedan formar un equipo de respuesta y ayudar a BlacJac a neutralizarlos definitivamente. Según nuestra información más reciente, su nave subcapital y escoltas fuertemente armadas sobrevuelan ~mission(Location|Address). Les recomiendo asegurarse de tener una identificación actualizada antes de partir. Por si acaso. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v> Destruir drogas peligrosas</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (HRT)</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Unos químicos emprendedores han creado un nuevo producto que es el doble de potente y letal que el original. Hemos podido rastrear algunas muestras hasta la fuente en ~mission(Location|Address). BlacJac quiere que vayas cuanto antes para destruir todo el lote antes de que pueda perjudicar a más personas. Ya nos ocuparemos de los arrestos después. Por lo que sabemos de este grupo, debes esperar una fuerte resistencia al intentar eliminar el alijo. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Su próximo objetivo, ~mission(TargetName), es sin duda un objetivo de alto riesgo, y con razón. Se sabe que viaja con armamento pesado y cuenta con suficiente protección como para que cualquiera se lo piense dos veces antes de enfrentarse a él. Según fuentes, ~mission(TargetName|Last) se esconde en ~mission(Location|Address). Cuando salgan a buscarlo, asegúrense de estar preparados. Quizás incluso deberían llevar refuerzos. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v> Eliminar las drogas</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos enteramos de que un sindicato adulteró un paquete de drogas de un rival y está causando caos en las calles. Los forenses han identificado la fuente: una planta de producción ubicada en ~mission(Location|Address). Se rumorea que los fabricantes de drogas ni siquiera saben que tienen droga envenenada. Estamos analizando cómo proceder con los arrestos, pero lo importante es sacar esta porquería de las calles ahora. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. No les hará ninguna gracia, así que probablemente tendrán que enfrentarse a una pelea, pero lo importante es eliminar el producto. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazadores de recompensas. No sé si les interesa, pero BlacJac busca ampliar su equipo de cazarrecompensas. Tenemos más trabajos de los que nuestros contratistas actuales pueden cubrir, así que espero que puedan ayudarnos a cubrir parte de la carga de trabajo. Sus cualificaciones se ven bien en papel, pero antes de formalizar nada, BlacJac necesita ver su desempeño en el campo. Incluso tenemos un caso de prueba preparado: queremos que resuelvan la misión ~(Nombre del objetivo). Fueron vistos por última vez en ~misión(Ubicación|Dirección). Debería ser una recompensa bastante sencilla, sin demasiada resistencia. Una oportunidad perfecta para que se pongan a prueba. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v> Proteger el sitio</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (LRT)</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. El equipo de seguridad de ~mission(Location|Address) nos ha informado de que algunos delincuentes locales han estado realizando ataques. BlacJac busca que acudan al lugar para ayudar a protegerlo de amenazas hostiles. Asegúrense de controlar el fuego allí abajo. No quiero oír hablar de ningún incidente entre fuerzas propias. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Se ha ofrecido una recompensa por un objetivo de bajo riesgo llamado ~mission(TargetName). El objetivo en sí no es muy peligroso, pero parece que suelen volar en grupo, así que hay muchas probabilidades de que vengan acompañados cuando los localicen. Por cierto, les recomiendo comenzar la búsqueda en ~mission(Location|Address), ya que tenemos informes de que los han visto en la zona. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v> Contrato de prueba del sitio de protección</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
       <c r="A71" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. BlacJac busca ampliar su equipo de profesionales de seguridad. Para evaluar si usted encaja en el perfil, le solicitamos que preste apoyo en ~mission(Location|Address), ya que han tenido problemas con personas hostiles en la zona. Si puede ayudar a proteger el sitio y eliminar la amenaza, podremos ofrecerle más trabajo de seguridad. Tenga en cuenta que no se tolerarán incidentes de fuego amigo. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan que se encarguen de ~mission(TargetName), una recompensa de riesgo moderado vista por última vez en ~mission(Location|Address) pilotando una pequeña nave con tripulación múltiple. No pudimos obtener detalles sobre la nave que pilotaban, pero parece que tenían otras naves con ellos. Prepárense para una fuerte resistencia cuando lleguen. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v> Contrato de prueba del sitio de protección</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
       <c r="A73" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Exoperador Mercenario. Sé que BlacJac dejó de ofrecer servicios de seguridad, pero debido a cambios en el personal, se decidió ofrecerle otra oportunidad. Nos han informado que ~mission(Location|Address) necesita ayuda para lidiar con una banda local de forajidos. BlacJac busca que usted acuda al lugar y ayude a eliminar esta amenaza. Y dado que su situación ya es delicada, no quiero oír que haya estado involucrado en ningún incidente de fuego amigo. Si logra llevar a cabo esta operación con éxito, podemos considerar su reincorporación. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> ATENCIÓN: Excazador de recompensas de BlacJac. Sé que tu última misión para BlacJac no salió bien, pero el aumento de casos significa que tienes la suerte de tener otra oportunidad. Si logras completar la misión en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reincorporarte. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v> Despejar el sitio</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VHRT)</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
       <c r="A75" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que ~mission(Location|Address) está siendo utilizada por delincuentes locales como base de operaciones. BlacJac busca que ustedes realicen una inspección del sitio y eliminen a cualquier persona hostil. Nuestros primeros informes indican que es muy probable que la banda tenga civiles trabajando para ellos en el lugar. No buscamos ser noticia, así que recuerden que solo están autorizados a interactuar con personas hostiles confirmadas. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas BlacJac acaba de recibir información de que un objetivo de altísimo riesgo, ~mission(TargetName), fue avistado en las rutas aéreas de ~mission(Location|Address) pilotando una formidable nave con una fuerte escolta. Queremos eliminar esta recompensa antes de que cometa más delitos. Reúnan los recursos y el apoyo que necesiten y salgan cuanto antes. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v> Buscando Zeta-Prolanide</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VLRT)</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
       <c r="A77" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se rumorea que han robado una gran cantidad de Zeta-Prolanida en ~mission(Location|address). Si encuentras alguna, tráela a ~mission(DropOffLocation|address) y te aseguraremos un buen precio. Si no, puedes rechazar esta oferta sin problema.</v>
+        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Tengo un objetivo de muy bajo riesgo del que debo encargarme: ~mission(NombreDelObjetivo). Su última ubicación conocida fue ~mission(Ubicación|Dirección). Se trata de una recompensa de bajo riesgo, así que espero que puedan resolverla rápidamente. Suelen pilotar una nave pequeña y no tienen muchos conocidos. Es una misión sencilla. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v> ALERTA DE CDF: ~misión(Ubicación) Se necesitan agentes para bloquear el acceso</v>
+        <v>Proteger el sitio y obtener materiales confidenciales.</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
       <c r="A79" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Una flota hostil de naves equipadas con inhibidores cuánticos ha creado un bloqueo alrededor de ~mission(Location|address), ha desactivado las torretas defensivas de la estación y ha robado una gran cantidad de Zeta-Prolanida. En respuesta, la CDF ha recibido autorización para activar su fuerza de voluntarios. Aunque la situación general es crítica, el robo de la Zeta-Prolanida es nuestra prioridad. Sin una acción directa, la pérdida de las reservas de Zeta-Prolanida del sector podría tener efectos devastadores en la economía de todo el sistema. Mientras las fuerzas de seguridad locales investigan la incursión, han rastreado el inventario robado hasta varias ubicaciones. Los voluntarios de la CDF tienen la misión de dirigirse a estas ubicaciones, recuperar la Zeta-Prolanida robada y transportarla de vuelta a la estación antes de que el material se degrade por completo y deje de ser viable. Tengan cuidado, la información sugiere que los cúmulos más grandes de Zeta-Prolanida tienen una mayor presencia de delincuentes. Dado que el tiempo apremia, se recomienda encarecidamente contar con un rayo tractor para facilitar el traslado de la carga. Como incentivo adicional, los voluntarios recibirán bonificaciones periódicas por su colaboración.</v>
+        <v xml:space="preserve">ATENCIÓN: Mercenarios con experiencia en manejo de carga. Nine Tails está atacando una de nuestras instalaciones en ~mission(Location|address). Dado que acaban de recibir un envío de material confidencial, no creemos que sea una coincidencia. BlacJac necesita que alguien se dirija rápidamente al lugar y asegure estas cajas importantes antes de que lo haga Nine Tails. Están autorizados a usar fuerza letal contra cualquiera que intente detenerlos. Como parte de nuestro protocolo de seguridad estándar, el material confidencial se integró en otro envío y se guardó en la bóveda automatizada. Deberán encontrar los códigos de recuperación correspondientes para el material confidencial e introducirlos en la cinta transportadora de paquetes para recuperar las cajas. Los códigos de recuperación se almacenan localmente en tabletas de datos y solo se entregan al personal de alto rango. Esperemos que estén vivos para ayudarlos, pero considerando el apagón total de comunicaciones, tememos que no sea así. Existe la posibilidad de que Nine Tails ya se haya apoderado de las tabletas de datos. Una vez que haya reunido todo el material confidencial, deberá entregarlo en ~mission(dropoff1|address). El pago está condicionado a su entrega. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Recompensa emitida: ~mission(TargetName)</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v>Proteger el sitio de amenazas menores</v>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ATENCIÓN: Operadores Mercenarios Verificados. Uno de los sitios bajo la supervisión de BlacJac ha tenido enfrentamientos con algunos delincuentes locales. Les pedimos que se dirijan a ~mission(Ubicación|Dirección) y aseguren el sitio de estas amenazas. Según los primeros informes, esto será bastante sencillo, pero si lo desean, pueden reclutar un equipo para que les brinde apoyo adicional. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v> Superando el desafío</v>
+        <v> Proteja el sitio de amenazas</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
       <c r="A83" t="str" xml:space="preserve">
-        <v xml:space="preserve"> La CDF se ha asociado con Anvil Aerospace para encontrar a los operativos más capaces del sistema. Si encuentras una de estas certificaciones Platino, puedes canjear el boleto en un quiosco de naves en New Deal, Astro Armada o Crusader Showroom por un F8C gratis. La condición es que tu identidad y ubicación se han compartido con los participantes de todo el sistema. Para los demás, si logras detener al poseedor del boleto antes de que llegue al quiosco, puedes reclamarlo para ti. Quien lo consiga no solo recibirá este caza de superioridad de última generación, sino que también demostrará que tiene lo necesario para las misiones más difíciles de la CDF. ¡Buena suerte!</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que algunos matones locales han estado haciendo amenazas contra ~mission(Location|Address). BlacJac busca que formen un equipo para proteger el sitio de estas amenazas. Y aunque a todos nos encantan los créditos, no recomiendo intentar hacerlo solos. Contratar un equipo sería beneficioso para su sustento. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v> Entrega para ~misión(Destino) Lista</v>
+        <v> Proteja el sitio de amenazas peligrosas.</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
       <c r="A85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. He recibido un informe de que algunos operadores planean un ataque contra ~mission(Location|Address). BlacJac les pide que formen un equipo para defender el sitio de esta peligrosa amenaza. Se recomienda encarecidamente no intentar completar este contrato en solitario. Contratar un equipo de mercenarios experimentados para que les brinden apoyo sería la opción más inteligente. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security. "Protección garantizada".</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v> Múltiples entregas listas</v>
+        <v> Eliminar el alijo de drogas</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
       <c r="A87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, necesito que me entreguen dos paquetes. El paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; debe recogerse en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; y llevarse a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;, y el paquete &lt;EM4&gt;#~mission(item2|serialnumber)&lt;/EM4&gt; va de &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt;. Debería ser una forma fácil de ganar algunos créditos. Además, para facilitarte la vida, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¡Buen viaje! Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Parece que hay un nuevo operador intentando fabricar drogas en ~mission(Location|Address), pero el producto que está produciendo es extremadamente tóxico. Estamos analizando cómo proceder con los arrestos, pero lo importante es evitar que se distribuya más de su mercancía. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. Es muy probable que la instalación no esté abandonada, así que podrían encontrarse con estos delincuentes al llegar. Prepárense para una pelea. Pero si su habilidad con las armas es similar a su química, probablemente no será muy dura. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v> Eliminar la amenaza Xeno Idris</v>
+        <v> Destruir drogas peligrosas</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
       <c r="A89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, los rumores son ciertos. XenoThreat ha desplegado un Idris para acechar y atacar las operaciones de Ciudadanos por la Prosperidad, en una escalada dramática de su hostilidad hacia nosotros. Acabamos de recibir la noticia de que la nave, bajo el mando de ~mission(TargetName), avanza hacia ~mission(location|address). No podemos enviar nuestras fuerzas allí lo suficientemente rápido para combatirlos y necesitamos ayuda urgentemente. Buscamos a alguien lo suficientemente valiente como para enfrentarse a estos bastardos. No basta con ahuyentarlos, necesitamos garantizar que no puedan volver a atacarnos. No sé si te has enfrentado a un Idris antes, pero es una tarea titánica para alguien que lo haga solo. Recomiendo encarecidamente reclutar a otros para la causa. Saludos, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Unos químicos emprendedores han creado un nuevo producto que es el doble de potente y letal que el original. Hemos podido rastrear algunas muestras hasta la fuente en ~mission(Location|Address). BlacJac quiere que vayas cuanto antes para destruir todo el lote antes de que pueda perjudicar a más personas. Ya nos ocuparemos de los arrestos después. Por lo que sabemos de este grupo, debes esperar una fuerte resistencia al intentar eliminar el alijo. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v> Suministros robados</v>
+        <v> Eliminar las drogas</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
       <c r="A91" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos enteramos de que un sindicato adulteró un paquete de drogas de un rival y está causando caos en las calles. Los forenses han identificado la fuente: una planta de producción ubicada en ~mission(Location|Address). Se rumorea que los fabricantes de drogas ni siquiera saben que tienen droga envenenada. Estamos analizando cómo proceder con los arrestos, pero lo importante es sacar esta porquería de las calles ahora. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. No les hará ninguna gracia, así que probablemente tendrán que enfrentarse a una pelea, pero lo importante es eliminar el producto. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v> Material confidencial robado</v>
+        <v> Proteger el sitio</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
       <c r="A93" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Estás disponible para un trabajo? Uno de nuestros centros de seguridad fue asaltado y robaron material altamente confidencial. Como puedes imaginar, Citizens for Prosperity necesita recuperarlo cuanto antes. Gracias a un contacto local, pudimos rastrear a los delincuentes hasta ~mission(Location|Address), donde almacenan el material confidencial en una bóveda automatizada de alta seguridad. Para acceder a ella, primero debes encontrar el código de recuperación e introducirlo en la cinta transportadora de la bóveda. Creemos que uno de los líderes de los delincuentes llevará el código consigo, por lo que es muy probable que tengas que hablar directamente con él para obtenerlo. Una vez que tengas el material confidencial en tu poder, te pedimos que lo entregues en ~mission(Dropoff1|Address). Si lo consigues, ayudarás mucho a muchas personas. Gracias de antemano, Lima Endicott, Despachadora Principal, Citizens for Prosperity</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. El equipo de seguridad de ~mission(Location|Address) nos ha informado de que algunos delincuentes locales han estado realizando ataques. BlacJac busca que acudan al lugar para ayudar a protegerlo de amenazas hostiles. Asegúrense de controlar el fuego allí abajo. No quiero oír hablar de ningún incidente entre fuerzas propias. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v> Falta: ~misión(NombreObjetivo)</v>
+        <v> Contrato de prueba del sitio de protección</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
       <c r="A95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lamentablemente, uno de nuestros socios comunitarios, ~mission(TargetName), lleva desaparecido varios días. Su familia se puso en contacto con Citizens for Prosperity para pedir ayuda y les dije que haríamos lo posible. Dicho esto, con tanto tiempo transcurrido, no tengo muchas esperanzas. Sea cual sea su situación actual, buscamos a alguien que nos ayude a localizarlo. Hay muchas probabilidades de que se dirigiera a ~mission(Location|Address), una zona conocida por ser muy peligrosa. Si logra localizarlo y confirmar su paradero, de una forma u otra, me aseguraré de que reciba la compensación adecuada. Lima Endicott, Coordinadora Principal de Despacho, Citizens for Prosperity</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. BlacJac busca ampliar su equipo de profesionales de seguridad. Para evaluar si usted encaja en el perfil, le solicitamos que preste apoyo en ~mission(Location|Address), ya que han tenido problemas con personas hostiles en la zona. Si puede ayudar a proteger el sitio y eliminar la amenaza, podremos ofrecerle más trabajo de seguridad. Tenga en cuenta que no se tolerarán incidentes de fuego amigo. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v> Falta: ~misión(NombreObjetivo)</v>
+        <v> Contrato de prueba del sitio de protección</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
       <c r="A97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de nuestros compañeros, ~mission(TargetName), debía realizar un reconocimiento preliminar en ~mission(Location|Address), pero nunca se presentó. Esperamos que simplemente haya tenido mala suerte, pero aquí, incluso el más mínimo error puede resultar fatal. Agradecería que alguien se dirigiera a la zona e intentara localizarlo. Sería estupendo encontrarlo con vida, pero si no, brindarles un cierre es lo mínimo que podemos hacer por su familia. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">ATENCIÓN: Exoperador Mercenario. Sé que BlacJac dejó de ofrecer servicios de seguridad, pero debido a cambios en el personal, se decidió ofrecerle otra oportunidad. Nos han informado que ~mission(Location|Address) necesita ayuda para lidiar con una banda local de forajidos. BlacJac busca que usted acuda al lugar y ayude a eliminar esta amenaza. Y dado que su situación ya es delicada, no quiero oír que haya estado involucrado en ningún incidente de fuego amigo. Si logra llevar a cabo esta operación con éxito, podemos considerar su reincorporación. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v> Entrega de regalos de Luminalia</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v> ~misión(Contratista|DescripciónDeEntregaLocal)</v>
+        <v> Despejar el sitio</v>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str" xml:space="preserve">
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que ~mission(Location|Address) está siendo utilizada por delincuentes locales como base de operaciones. BlacJac busca que ustedes realicen una inspección del sitio y eliminen a cualquier persona hostil. Nuestros primeros informes indican que es muy probable que la banda tenga civiles trabajando para ellos en el lugar. No buscamos ser noticia, así que recuerden que solo están autorizados a interactuar con personas hostiles confirmadas. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v> Ruta de envío local de Covalex</v>
+        <v> Buscando Zeta-Prolanide</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
       <c r="A101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos un envío bastante grande esperando en la misión (Recogida 1) en la dirección (Recogida 1) que está listo para ser entregado. Con esta cantidad de cajas para transportar, probablemente sería bueno contar con ayuda adicional para cargar y descargar todo de su nave. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item11|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item12|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item13|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item14|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item15|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; Mucha suerte, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite'. Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
+        <v xml:space="preserve"> Se rumorea que han robado una gran cantidad de Zeta-Prolanida en ~mission(Location|address). Si encuentras alguna, tráela a ~mission(DropOffLocation|address) y te aseguraremos un buen precio. Si no, puedes rechazar esta oferta sin problema.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Oportunidad para transportista de carga independiente</v>
+        <v> ALERTA DE CDF: ~misión(Ubicación) Se necesitan agentes para bloquear el acceso</v>
       </c>
     </row>
     <row r="103" xml:space="preserve">
       <c r="A103" t="str" xml:space="preserve">
-        <v xml:space="preserve">Covalex, galardonada con reconocimientos como "Las 10 mejores empresas de transporte marítimo" de Imperial Finance y "El transporte más confiable de Delivery Digest" (2945), está más activa que nunca. Esto significa más carga para más destinos. Ahí es donde entras tú. Covalex busca pilotos confiables y trabajadores para unirse a nuestra creciente familia. ¿Tienes acceso a un barco con capacidad para contenedores de carga de &lt;EM4&gt;~mission(MissionMaxSCUSize)&lt;/EM4&gt;? ¿Puedes superar una verificación de antecedentes de Advocacy si se requiere? Entonces, un universo de oportunidades te espera. Simplemente completa una "Prueba de evaluación" recogiendo un envío de &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entregándolo con éxito en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Tras completar satisfactoriamente el proceso, podrá formar parte de la amplia red de especialistas en transporte independientes de Covalex Shipping*. Por cierto, recomendamos encarecidamente a los contratistas que traigan consigo un rayo tractor portátil. Covalex Shipping: «Todo lo que necesite, donde lo necesite». *Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de carga, Covalex Shipping establecerá un plazo de entrega y, una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
+        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Una flota hostil de naves equipadas con inhibidores cuánticos ha creado un bloqueo alrededor de ~mission(Location|address), ha desactivado las torretas defensivas de la estación y ha robado una gran cantidad de Zeta-Prolanida. En respuesta, la CDF ha recibido autorización para activar su fuerza de voluntarios. Aunque la situación general es crítica, el robo de la Zeta-Prolanida es nuestra prioridad. Sin una acción directa, la pérdida de las reservas de Zeta-Prolanida del sector podría tener efectos devastadores en la economía de todo el sistema. Mientras las fuerzas de seguridad locales investigan la incursión, han rastreado el inventario robado hasta varias ubicaciones. Los voluntarios de la CDF tienen la misión de dirigirse a estas ubicaciones, recuperar la Zeta-Prolanida robada y transportarla de vuelta a la estación antes de que el material se degrade por completo y deje de ser viable. Tengan cuidado, la información sugiere que los cúmulos más grandes de Zeta-Prolanida tienen una mayor presencia de delincuentes. Dado que el tiempo apremia, se recomienda encarecidamente contar con un rayo tractor para facilitar el traslado de la carga. Como incentivo adicional, los voluntarios recibirán bonificaciones periódicas por su colaboración.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Reevaluación del servicio de transporte de carga de Covalex</v>
-      </c>
-    </row>
-    <row r="105" xml:space="preserve">
-      <c r="A105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos buenas noticias para ti. Covalex ha finalizado recientemente una evaluación de nuestro grupo de contratistas y ha decidido reconsiderar tu estatus como transportista de carga. Para volver a calificar, solo necesitas completar con éxito la siguiente entrega. Recoge &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entrégalo en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Para completar este transporte de forma rápida y eficiente, necesitarás un barco que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Esperamos que todo salga bien para poder darte la bienvenida de nuevo al equipo. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Covalex Shipping 'Todo lo que necesitas, donde lo necesitas'. Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de mercancías, Covalex Shipping establecerá un plazo límite de entrega. Una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
+        <v>Recompensa emitida: ~mission(TargetName)</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Manipulador de paquetes Covalex</v>
+        <v> Superando el desafío</v>
       </c>
     </row>
     <row r="107" xml:space="preserve">
       <c r="A107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, hay un montón de paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que necesitan ser trasladados dentro de las instalaciones hasta su lugar de almacenamiento correspondiente. Sería de gran ayuda si pudieras encargarte personalmente de que todo se organice. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Realmente aprecio todo lo que haces, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones como se describen en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29' extendida. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
+        <v xml:space="preserve"> La CDF se ha asociado con Anvil Aerospace para encontrar a los operativos más capaces del sistema. Si encuentras una de estas certificaciones Platino, puedes canjear el boleto en un quiosco de naves en New Deal, Astro Armada o Crusader Showroom por un F8C gratis. La condición es que tu identidad y ubicación se han compartido con los participantes de todo el sistema. Para los demás, si logras detener al poseedor del boleto antes de que llegue al quiosco, puedes reclamarlo para ti. Quien lo consiga no solo recibirá este caza de superioridad de última generación, sino que también demostrará que tiene lo necesario para las misiones más difíciles de la CDF. ¡Buena suerte!</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Ruta de reparto local de Covalex</v>
-      </c>
-    </row>
-    <row r="109" xml:space="preserve">
-      <c r="A109" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Hola! Acabamos de recibir una entrega local que necesitamos que se encarguen, si están disponibles. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no se hace responsable de los daños que puedan producirse mientras opera como contratista independiente.</v>
+        <v> Eliminar las estaciones de servicio</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v> Eliminar las estaciones de servicio</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Evaluación de Covalex</v>
-      </c>
-    </row>
-    <row r="111" xml:space="preserve">
-      <c r="A111" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Hola! Covalex está buscando nuevos contratistas de entrega. Para ver si tienes el perfil de Covalex, hemos organizado la siguiente ruta de entrega como evaluación de tus habilidades. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Completar con éxito esta ruta te certificará como contratista oficial de Covalex. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra "Guía de información complementaria para trabajadores independientes v.2948.01.29". Covalex Shipping no se responsabiliza de los daños que puedan producirse durante su actividad como contratista independiente.</v>
+        <v> Reducir la preparación operativa de Outlaw</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v> Reducir la preparación operativa de Outlaw</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Reevaluación de Covalex</v>
-      </c>
-    </row>
-    <row r="113" xml:space="preserve">
-      <c r="A113" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, dado que Covalex ha estado experimentando un exceso de entregas y escasez de contratistas, logré convencer a la administración para que reconsiderara tu situación. Solo tienes que completar con éxito la siguiente entrega y volverás a formar parte del sistema. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Buena suerte. Sería genial tenerte de nuevo en la lista. Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de los daños que se produzcan mientras se opera como contratista independiente.</v>
+        <v> Alerta: ~misión(Ubicación) bajo ataque</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v> Alerta: ~misión(Ubicación) bajo ataque</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Error de envío - Carga sensible a la calidad</v>
+        <v>Recuperando terreno de los cazatalentos</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v> ~misión(Contratista|DescripciónDeEntregaSensibleCuántica)</v>
+        <v> Recuperando terreno de los cazatalentos</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v> Programa piloto de entrega para Covalex</v>
-      </c>
-    </row>
-    <row r="117" xml:space="preserve">
-      <c r="A117" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, tengo una entrega que necesito gestionar. El pedido está esperando en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser llevado a &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Estoy seguro de que no tendrás problemas, pero para que lo sepas, veo varias advertencias de seguridad en esta zona. Parece que ha habido algunos ataques en esa área en los últimos días. No digo que vayas a tener ningún problema, pero probablemente sería mejor que llevaras algo de protección. Mucha suerte, Chase Hewitt Jr., Coordinador de Logística de Covalex Shipping. «Todo lo que necesites, donde lo necesites».</v>
+        <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v> Efectos personales</v>
-      </c>
-    </row>
-    <row r="119" xml:space="preserve">
-      <c r="A119" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, entenderé perfectamente si no quieres ayudarme con esto, pero si puedes, sería genial. Verás, mi novio falleció durante la tragedia de Covalex Gundo. Me dijeron que recuperaría todas las pertenencias de Scott una vez que terminara la investigación, pero hasta donde sé, ya pasó un tiempo y todavía no me han dado ninguna indicación de cuándo podré recuperarlas. Ya ha sido bastante difícil lidiar con todo esto, y saber que dentro de uno o dos meses llegará un paquete que reabrirá todas estas heridas es demasiado. Preferiría resolverlo ahora y terminar con esto. Si pudieras encontrar la manera de recoger sus efectos personales (ID de empleado n.° 104) y entregarlos en ~mission(Destino), te lo agradecería muchísimo. Gracias por tu ayuda, Anya</v>
+        <v> Ataque de forajidos en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v> Ataque de forajidos en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v> Ayúdenme a recuperar mis cosas.</v>
-      </c>
-    </row>
-    <row r="121" xml:space="preserve">
-      <c r="A121" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mi hermano fue una de las personas que murió cuando explotó la estación Covalex cerca de Crusader. Peor aún, estaba usando algo mío cuando ocurrió. Ahora un burócrata de mierda me dice que tengo que esperar para recuperar mis cosas. ¡Claro que sí! Primero matan a mi hermano y ahora quieren que tenga paciencia. ¡Qué descaro el de estos imbéciles corporativos! Olvídalo. En vez de eso, pensé en contratar a alguien para que vaya a Gundo a buscar mis cosas y las lleve a ~misión(Destino) por mí. O sea, ¿qué demonios van a hacer al respecto? En fin, es lo que mi hermano hubiera querido. Será la caja marcada con el número 156. - Ed</v>
+        <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v> Herencia inesperada</v>
-      </c>
-    </row>
-    <row r="123" xml:space="preserve">
-      <c r="A123" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, esto me resulta un poco incómodo, pero resulta que una de las personas que falleció en el desastre de la estación Covalex, Kyomi Santos, me dejó algo en su testamento. Me sorprendió mucho, pero ahora soy el orgulloso dueño de todo lo que hay en la caja n.° 173. En Covalex dicen que podré recogerlo cuando la estación vuelva a abrir, pero... aquí viene lo incómodo... lo necesito urgentemente. Normalmente esperaría, pero estoy intentando montar mi propio negocio (hago pasteles con la forma de los planetas de origen de la gente) y los créditos que gane con la venta me vendrán de maravilla. Tengo algo de dinero ahorrado que puedo usar para pagarle a alguien que me lo envíe desde Gundo hasta ~misión(Destino). Sé que todo esto es un poco raro, pero si hubiera otra manera, no estaría preguntando. Gracias por la ayuda, Thrace.</v>
+        <v> Recuperando puestos avanzados de la amenaza alienígena</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v> Recuperando puestos avanzados de la amenaza alienígena</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v> La súplica de una madre</v>
-      </c>
-    </row>
-    <row r="125" xml:space="preserve">
-      <c r="A125" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mi hijo Nico fue, lamentablemente, una de las víctimas del trágico accidente en la estación de Covelex en Gundo, y aún no me han devuelto todas sus pertenencias. Entiendo que deben cumplir con las normas, pero me parece inconcebible que no tengan en cuenta el dolor de la familia. Por ello, busco a alguien que pueda ir a la estación por mí. Cabe aclarar que actualmente Gundo está fuera de los límites, lo que significa que esto no sería legal, pero creo que mi situación merece una consideración especial. Mi hermana dice que la tarifa que ofrezco es la correcta para recuperar la caja con las pertenencias de Nico (n.º 964) y llevarlas a ~mission(Destination), así que espero encontrar a alguien competente que pueda resolver este asunto rápidamente. Atentamente, Gloria Theolone</v>
+        <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v> Buscando un cierre</v>
+        <v> Recuperando clústeres de las manos de los cazatalentos</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Me dijeron que podría encontrar a alguien aquí que fuera a Gundo por mí y recogiera una caja que pertenecía a mi esposa. Si el nombre no te suena, es la estación donde ocurrió aquel gran accidente. Mi esposa trabajaba para Covalex y sé que eso no hará que su pérdida sea más fácil, pero de verdad quiero recuperar las cosas de Claudia. Pienso en su colección de fotos o en el collar que le regalé, ahí, en esa fría y desolada estación, en una caja marcada con el número 249, y no es justo. Ella se merece algo mejor. ¿Qué te parece? ¿Estás dispuesto a ir a Gundo y llevar su caja de vuelta a ~misión(Destino)?</v>
+        <v> Recuperando clústeres de las manos de los cazatalentos</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v> Las cosas de mi papá</v>
-      </c>
-    </row>
-    <row r="129" xml:space="preserve">
-      <c r="A129" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, busco a alguien que vaya a la estación Covalex Gundo cerca de Crusader y recoja algunos objetos. Sé que puede sonar a robo, pero son las cosas de mi papá. Verás, él estaba en la estación Gundo cuando ocurrió el accidente. Mi mamá dice que tenemos que esperar a que Covalex lo autorice, pero no me parece justo porque lo extraño muchísimo. Me gustaría tener algo para recordarlo y no quiero esperar más porque podría empezar a olvidar cosas. Te pagaré para que me consigas la caja 510 y la lleves a ~mission(Destination) para que pueda tenerla. Muchas gracias, Baylor Ward</v>
+        <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v> Apoderarse de los datos</v>
-      </c>
-    </row>
-    <row r="131" xml:space="preserve">
-      <c r="A131" t="str" xml:space="preserve">
-        <v xml:space="preserve">He estado buscando un paquete de datos específico y justo cuando tengo un respiro, la nave es atacada por esta Reclamadora de Nueve Colas modificada llamada Cometa Negra. Intenté hackear los servidores de la Cometa Negra para ver si copiaron los datos, pero no pude encontrar la manera de sortear sus protocolos de cifrado de forma remota sin la clave física. Ahí es donde entras tú. Necesito que alguien acceda a su nave, consiga su clave de descifrado y descifre el servidor para poder descargar remotamente lo que necesito. Eres lo suficientemente inteligente como para saber con quién estamos tratando, así que planifica en consecuencia. Dado que esto va a causar revuelo, no dejemos nada al azar. Destruye la Cometa Negra cuando termines para cubrirnos las espaldas a ambos.</v>
+        <v> Se necesita ayuda en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v> Se necesita ayuda en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v> Extracción de recompensa: ~misión(Nombre del objetivo) (MRT)</v>
-      </c>
-    </row>
-    <row r="133" xml:space="preserve">
-      <c r="A133" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tuvimos suerte y algunos escaneos recientes de ~mission(Location|Address) han revelado que hay una recompensa pendiente con el nombre de ~mission(TargetName) oculta allí. Se le ha autorizado a entrar en el sitio, encontrarla y resolver la recompensa. Sin embargo, además de la recompensa y sus cómplices, es probable que también haya civiles en el sitio. Si bien estamos ansiosos por eliminar a ~mission(TargetName|Last), no podemos permitirnos bajas civiles. Tenga cuidado al interactuar con los hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Gibbs ID# 91G66BW0</v>
+        <v> Ataque de Headhunter en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v> Ataque de Headhunter en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (LRT)</v>
+        <v> Solicitar ayuda: ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Solicitar ayuda: ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v> Evaluación de recompensas para freelancers verificados</v>
-      </c>
-    </row>
-    <row r="137" xml:space="preserve">
-      <c r="A137" t="str" xml:space="preserve">
-        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personas cualificadas para colaborar en la cobranza de recompensas en la zona. Hemos evaluado que usted posee las habilidades necesarias y, por lo tanto, nos gustaría ofrecerle un contrato inicial de prueba para la captura de ~mission(TargetName), vista por última vez en ~mission(Location|Address). Al completar con éxito este contrato, se le incluirá en la lista de Freelancers Verificados de Crusader y podrá optar a futuros trabajos de cobranza de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Defiende ~misión(Ubicación) de los forajidos</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Defiende ~misión(Ubicación) de los forajidos</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (HRT)</v>
+        <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (MRT)</v>
+        <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v> Reevaluación de la recompensa para freelancers verificados</v>
-      </c>
-    </row>
-    <row r="143" xml:space="preserve">
-      <c r="A143" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Buenas noticias! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de recompensas. Esperamos que durante este tiempo hayas corregido cualquier problema de rendimiento anterior y puedas volver a ser un activo valioso. Sin embargo, primero debemos reevaluarte, por lo que nos gustaría que completaras este contrato de recompensa para ~mission(TargetName). Tras completar con éxito esta prueba, volverás a la lista de Freelancers Verificados de Crusader y podrás optar a futuros trabajos de cobro de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (ERT)</v>
+        <v> Se buscan pilotos de combate experimentados.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Se buscan pilotos de combate experimentados.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (VLRT)</v>
+        <v> Proporcionar apoyo en combate</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Proporcionar apoyo en combate</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (VHRT)</v>
+        <v> Piloto busca apoyo en combate</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Piloto busca apoyo en combate</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v> URGENTE: Retomar el puesto de seguridad de Kareah</v>
-      </c>
-    </row>
-    <row r="151" xml:space="preserve">
-      <c r="A151" t="str" xml:space="preserve">
-        <v xml:space="preserve">El puesto de seguridad Kareah está siendo atacado por un número desconocido de asaltantes. Crusader busca contratistas que se dirijan rápidamente a la estación y eliminen a todos los intrusos en las inmediaciones antes de que nuestras fuerzas de seguridad se vean superadas. No sabemos si los atacantes buscan el contrabando en nuestro depósito de pruebas o nuestra base de datos CrimeStat, pero sea lo que sea que busquen, debemos neutralizarlos. Recibirás una bonificación de combate por cada objetivo neutralizado. Al aceptar este contrato, te comprometes a cumplir con todos los protocolos de seguridad de Crusader: si dañas a algún guardia u otro contratista autorizado mientras te encuentres en la estación, tu contrato se dará por terminado y serás marcado como objetivo. El tiempo apremia, así que asegúrate de estar bien equipado para enfrentarte a los hostiles antes de responder. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Ayudar al barco en retirada</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v> Ayudar al barco en retirada</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v> Apoyar a las fuerzas de seguridad y proteger los materiales confidenciales.</v>
-      </c>
-    </row>
-    <row r="153" xml:space="preserve">
-      <c r="A153" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los informes indican que nuestro personal de seguridad en ~mission(location|address) ha sido aniquilado por un grupo de los Nueve Colas, quienes intentan robar material confidencial entregado recientemente a las instalaciones. Crusader Security necesita un contratista experimentado para expulsar a los hostiles y asegurar estas cajas. Según los informes iniciales, recomendamos encarecidamente que venga bien equipado y considere traer refuerzos. Por motivos de seguridad, el material confidencial fue transportado allí como parte de un envío con otras cajas y guardado bajo llave en una bóveda automatizada. Los códigos de acceso al material confidencial se encuentran en tabletas de datos en poder de personal de seguridad de alto rango, pero desconocemos quién las tiene ahora. Es probable que los Nueve Colas también las estén buscando. Cuando tenga todo el material confidencial, entréguelo en ~mission(dropoff1|address) para recibir el pago. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Detengan el ataque al barco.</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v> Detengan el ataque al barco.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v> Sitio de vigilancia contra hostiles</v>
-      </c>
-    </row>
-    <row r="155" xml:space="preserve">
-      <c r="A155" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una pandilla local y estamos buscando contratar a un contratista para formar un equipo de seguridad que haga frente a cualquier ataque. Esta pandilla tiene antecedentes, pero aún son bastante novatos. Creo que será relativamente sencillo para usted y su equipo manejar la situación. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> El barco necesita asistencia de emergencia</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v> El barco necesita asistencia de emergencia</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v> Sitio de protección contra hostiles graves</v>
-      </c>
-    </row>
-    <row r="157" xml:space="preserve">
-      <c r="A157" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes y estamos buscando contratar a un contratista para formar un equipo de seguridad que repela cualquier ataque. Sé que puede que tengas la tentación de intentar resolver esto por tu cuenta, pero necesitas formar un equipo. Créeme, no vale la pena intentarlo solo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Ayudar a un convoy emboscado</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v> Ayudar a un convoy emboscado</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v> Sitio de vigilancia contra hostiles peligrosos</v>
-      </c>
-    </row>
-    <row r="159" xml:space="preserve">
-      <c r="A159" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una banda criminal conocida que opera en la zona y estamos buscando contratar un equipo de seguridad experimentado para hacer frente a cualquier ataque. Asegúrese de que la persona que contrate esté debidamente cualificada. Necesitará toda la ayuda posible para lidiar con este grupo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Convoy atrapado en un brutal ataque.</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v> Convoy atrapado en un brutal ataque.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v> Destruir las drogas ilegales</v>
-      </c>
-    </row>
-    <row r="161" xml:space="preserve">
-      <c r="A161" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos descubierto que un grupo está intentando montar su propio negocio de drogas en ~mission(Location|Address). Aunque parecen ser delincuentes comunes y corrientes, el producto que fabrican es tóxico y ha causado la muerte de varios civiles, así que no podemos permitir que se venda más. Estamos trabajando en una operación a gran escala para desmantelar su negocio definitivamente, pero mientras tanto, debemos detener el flujo de sus drogas. Por eso, Crusader quiere que vayas al lugar y destruyas el alijo que tienen allí. Sin duda, tendrán guardias protegiendo el alijo, pero no creo que representen una gran amenaza. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> El convoy necesita asistencia de emergencia</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v> El convoy necesita asistencia de emergencia</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v> Destruye el contrabando mortal</v>
-      </c>
-    </row>
-    <row r="163" xml:space="preserve">
-      <c r="A163" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un incipiente sindicato se ha instalado en ~mission(Location|Address) y está intentando introducirse en el mercado de las drogas. Desafortunadamente, su producto se ha relacionado con varias muertes en Crusader y sus alrededores. Dada la potencia de esta sustancia, representa una grave amenaza para la población. Crusader está trabajando para desmantelar la operación, pero mientras su producto siga circulando, los cadáveres se acumularán. Queremos que vayas al lugar y destruyas el alijo que tienen allí antes de que tengan la oportunidad de venderlo. Sin embargo, debes tener en cuenta que su alijo está extremadamente bien custodiado. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Detengan el ataque de la Espada Destrozada Salvaje</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Detengan el ataque de la Espada Destrozada Salvaje</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v> Destruir narcóticos tóxicos</v>
-      </c>
-    </row>
-    <row r="165" xml:space="preserve">
-      <c r="A165" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos estado investigando una reciente oleada de sobredosis y todas parecen haberse originado con un lote defectuoso de drogas fabricado en ~mission(Location|Address). Estoy trabajando con otros contratistas para dar con los responsables, pero la gente sigue muriendo mientras el producto siga circulando. Quiero que vayas al lugar y destruyas el alijo que tienen allí. Eso nos dará algo de tiempo antes de cerrarlo definitivamente. Tendrán guardias protegiendo su suministro, así que prepárate para enfrentarte a hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Acudan en auxilio del convoy</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v> Acudan en auxilio del convoy</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v> Proporcionar respaldo</v>
-      </c>
-    </row>
-    <row r="167" xml:space="preserve">
-      <c r="A167" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes. Si bien contamos con personal de seguridad en el lugar, estamos buscando contratar personal adicional para repeler cualquier ataque. Como contratista, desconozco su experiencia trabajando en equipo, pero no quiero oír hablar de "fuego amigo", ya que esto podría generar problemas. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Convoy bajo ataque</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v> Convoy bajo ataque</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v> Evaluación del trabajo de seguridad</v>
-      </c>
-    </row>
-    <row r="169" xml:space="preserve">
-      <c r="A169" t="str" xml:space="preserve">
-        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personal cualificado para colaborar en labores de seguridad en la zona. Hemos determinado que usted posee las habilidades necesarias para ofrecerle un contrato de prueba inicial. Colaborará con Crusader Security para hacer frente a un pequeño grupo hostil que ha estado realizando amenazas contra ~mission(Location|Address). Tenga en cuenta que ya contamos con personal de seguridad en el lugar, por lo que deberá tener cuidado con el fuego amigo. Tras la finalización satisfactoria de este contrato, podrá solicitar cualquier otro puesto de seguridad que surja en el futuro. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Responder a la baliza de socorro</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v> Responder a la baliza de socorro</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v> Reevaluación del trabajo de seguridad</v>
-      </c>
-    </row>
-    <row r="171" xml:space="preserve">
-      <c r="A171" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Felicidades! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de seguridad. Con un poco de esfuerzo y dedicación, esperamos que puedas superar cualquier problema de rendimiento anterior. Sin embargo, para reevaluar tu idoneidad, nos gustaría que ayudaras a Crusader Security a lidiar con un grupo de delincuentes que ha estado realizando amenazas contra ~mission(Location|Address). Ahora bien, dado que has tenido problemas de rendimiento en el pasado, te recuerdo que el fuego amigo no será tolerado. Una vez que completes con éxito esta prueba, se restablecerá tu elegibilidad y podrás volver a solicitar trabajo de seguridad con Crusader. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Convoy bajo ataque de una amenaza alienígena</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v> Convoy bajo ataque de una amenaza alienígena</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v> Despejemos el nido criminal</v>
-      </c>
-    </row>
-    <row r="173" xml:space="preserve">
-      <c r="A173" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) se está utilizando actualmente como base de operaciones para numerosas actividades ilegales. Para acabar con este "nido de delincuentes", buscamos un contratista para que se dirija al lugar y elimine a todos los elementos hostiles. Por la fuerza si es necesario. Cabe mencionar que, a veces, bandas como esta reclutan civiles para que trabajen para ellas, a menudo mediante coacción. Es obvio, pero si ven a algún civil, deben protegerlo. Crusader Security no puede permitir que uno de sus contratistas ande disparando indiscriminadamente contra la gente. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Buque de apoyo bajo ataque</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v> Buque de apoyo bajo ataque</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v> Fin de la ocupación de Nine Tails en Orison</v>
-      </c>
-    </row>
-    <row r="175" xml:space="preserve">
-      <c r="A175" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención, las fuerzas de Nine Tails han tomado el control de varias plataformas comerciales cerca de Orison. Usando un Inversor de Identidad Amigo o Enemigo (IFFI), se han apoderado del espacio aéreo restringido que rodea las plataformas y solo las naves afiliadas a Nine Tails pueden acceder al área. Esto ha obstaculizado gravemente los intentos iniciales de Crusader Security para retomar las plataformas. Por lo tanto, Crusader ha solicitado a las fuerzas de CDF que ayuden a apagar el inversor y eliminar toda presencia hostil. Se anima a todos los voluntarios de CDF disponibles a brindar apoyo. Información adicional: * Mientras el inversor está activo y el espacio aéreo inaccesible, CDF ha logrado tomar el control de un sistema de transporte local y redirigirlo para acceder a la Plataforma Solanki sin el conocimiento de Nine Tails. Los voluntarios deberán dirigirse a la Sala de Exposiciones de Crusader Industries en la Plataforma Comercial y llegar a la azotea para encontrar el transporte que viajará a las plataformas ocupadas. * Se cree que el IFFI está ubicado en un contenedor de almacenamiento cerrado en una barcaza de carga atracada en el Centro de Administración central. * Los códigos de acceso para el contenedor IFFI están en posesión del líder de las fuerzas de Nine Tails, Mendo Ren. * La experiencia previa con Mendo Ren indica que es improbable que muestre su rostro y se arriesgue a ser capturado. Sin embargo, si todos sus lugartenientes son neutralizados, creemos que no tendrá más remedio que tomar el mando de las fuerzas en persona y darnos la oportunidad de recuperar los códigos. * Además del sistema de transporte, Crusader Security nos ha informado que hay varios vehículos en las plataformas disponibles para que las CDF los requisen. Estos vehículos serán la única forma de llegar al Centro Administrativo. NOTA: Si todos los vehículos dentro del espacio aéreo restringido son destruidos antes de que se pueda apagar el inversor, entonces no habrá forma de llegar a la barcaza de carga y las CDF se verán obligadas a retirarse. * Las plataformas están protegidas por armas antiaéreas controladas por Nine Tails. Tenga en cuenta que la SAIC Rowena Dulli de Advocacy es la agregada oficial de las CDF y dirigirá la operación.</v>
+        <v> Piloto en apuros</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v> Piloto en apuros</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Doble toque</v>
-      </c>
-    </row>
-    <row r="177" xml:space="preserve">
-      <c r="A177" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se ha puesto precio a las cabezas de ~mission(TargetName) y ~mission(TargetName2). Si bien tener que alcanzar dos objetivos no es tan extraño, el cliente quiere enviar un mensaje muy específico, así que necesitan que ambos objetivos sean alcanzados en el mismo instante. Los créditos adicionales compensarán las molestias. Y, lamentablemente, como no viajan juntos, es obvio que para lograrlo necesitarás ayuda. Asegúrate de llevar gente de confianza que pueda manejar más de una nave, ya que se sabe que los objetivos viajan con refuerzos.</v>
+        <v> Se necesita ayuda contra XenoThreat Raid</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v> Se necesita ayuda contra XenoThreat Raid</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v> Dos en la cabeza</v>
+        <v> Entrega para ~misión(Destino) Lista</v>
       </c>
     </row>
     <row r="179" xml:space="preserve">
       <c r="A179" t="str" xml:space="preserve">
-        <v xml:space="preserve">Se trata de dos objetivos que deben ser eliminados simultáneamente. Al parecer, el cliente teme que, si no se eliminan juntos, uno de ellos se vuelva loco y busque venganza. Se les conoce como ~mission(TargetName) y ~mission(TargetName2). Reúne a tu equipo, divide y vencerás. Asegúrate de que cada miembro tenga las habilidades necesarias, porque estos dos tienen fama de ser muy hábiles en combate y, sin duda, no estarán solos. Prepárate para que te den problemas.</v>
+        <v xml:space="preserve">Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v> Eliminación coordinada</v>
+        <v> Múltiples entregas listas</v>
       </c>
     </row>
     <row r="181" xml:space="preserve">
       <c r="A181" t="str" xml:space="preserve">
-        <v xml:space="preserve">Me ha llegado una misión interesante. Necesito eliminar a dos objetivos distintos: ~mission(TargetName) y ~mission(TargetName2). El problema es que si uno se entera de que el otro ha sido atacado, se esconderá. No puedo arriesgarme a perder a ninguno. Requerirá una coordinación considerable, pero quiero que los elimines a ambos al mismo tiempo. Y como no puedes estar en dos sitios a la vez, tendrás que encontrar a alguien de confianza que te ayude. Por suerte, mi información indica que ambos objetivos viajarán solos. Eso debería facilitarte las cosas.</v>
+        <v xml:space="preserve">Hola, necesito que me entreguen dos paquetes. El paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; debe recogerse en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; y llevarse a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;, y el paquete &lt;EM4&gt;#~mission(item2|serialnumber)&lt;/EM4&gt; va de &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt;. Debería ser una forma fácil de ganar algunos créditos. Además, para facilitarte la vida, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¡Buen viaje! Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v> Doble eliminación</v>
+        <v> Eliminar la amenaza Xeno Idris</v>
       </c>
     </row>
     <row r="183" xml:space="preserve">
       <c r="A183" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tengo un contrato para eliminar a dos jóvenes problemáticos que han estado causando problemas. Tiene que ser una operación limpia y simultánea, o podrían causar aún más problemas. En resumen, necesitarás ayuda. Tanto ~mission(TargetName) como ~mission(TargetName2) saben defenderse, y sus compañeros de vuelo tampoco son ninguna broma. Cada uno de ellos estará protegido por varias naves.</v>
+        <v xml:space="preserve">Hola, los rumores son ciertos. XenoThreat ha desplegado un Idris para acechar y atacar las operaciones de Ciudadanos por la Prosperidad, en una escalada dramática de su hostilidad hacia nosotros. Acabamos de recibir la noticia de que la nave, bajo el mando de ~mission(TargetName), avanza hacia ~mission(location|address). No podemos enviar nuestras fuerzas allí lo suficientemente rápido para combatirlos y necesitamos ayuda urgentemente. Buscamos a alguien lo suficientemente valiente como para enfrentarse a estos bastardos. No basta con ahuyentarlos, necesitamos garantizar que no puedan volver a atacarnos. No sé si te has enfrentado a un Idris antes, pero es una tarea titánica para alguien que lo haga solo. Recomiendo encarecidamente reclutar a otros para la causa. Saludos, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v> Divide y vencerás</v>
-      </c>
-    </row>
-    <row r="185" xml:space="preserve">
-      <c r="A185" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Normalmente, enfrentarse a ~mission(TargetName) y ~mission(TargetName2) juntos sería demasiado. Ambos son excelentes en combate aéreo y sus tripulaciones son casi igual de buenas. Sin embargo, recientemente se separaron —no se sabe por qué— y por el momento vuelan por separado. Alguien cree que esta podría ser la mejor oportunidad para eliminarlos. Reúna personal de confianza y planifique un ataque simultáneo contra ambos objetivos. Es demasiado peligroso arriesgar la vida de uno de ellos tras un ataque tan directo.</v>
+        <v> Ataque a un puesto de avanzada de la CFP</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v> Ataque a un puesto de avanzada de la CFP</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Combinación de uno-dos</v>
-      </c>
-    </row>
-    <row r="187" xml:space="preserve">
-      <c r="A187" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hay otro par que deben ser eliminados: ~mission(TargetName) y ~mission(TargetName2). Han estado desaparecidos durante algunos días, pero acaban de aparecer. Si no los eliminamos ahora, no estoy seguro de que tengamos otra oportunidad. Necesitas reclutar a un compañero para asegurarte de que ambos objetivos sean alcanzados al mismo tiempo. En cuanto a su resistencia, se sabe que ~mission(TargetName) trae a un amigo para que le cubra las espaldas, y sospecho que ~mission(TargetName2) hará lo mismo.</v>
+        <v> Se necesitan defensores contra los cazadores de cabezas</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v> Se necesitan defensores contra los cazadores de cabezas</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v> Combinación mortal</v>
-      </c>
-    </row>
-    <row r="189" xml:space="preserve">
-      <c r="A189" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Dos operadores de alto nivel que recientemente decidieron atacar a su jefe. Cada uno viaja con una pequeña armada de élite y se adentra en territorio ajeno. Tú, junto con quien reclutes para que te ayude, los eliminarás, y ambos deben hacerlo simultáneamente para que no puedan reagruparse.</v>
+        <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v> Juego de guerra de Idris</v>
-      </c>
-    </row>
-    <row r="191" xml:space="preserve">
-      <c r="A191" t="str" xml:space="preserve">
-        <v xml:space="preserve">Para poner a prueba la preparación de nuestros equipos de respuesta, solicitamos voluntarios que simulen un asalto contra un Idris de la CDF, neutralizando y tomando el control de la embarcación. Es importante aclarar que el objetivo del ejercicio no es destruir el Idris, sino abordarlo y mantener el control el mayor tiempo posible. Los voluntarios deben esperar una fuerte resistencia por parte de la tripulación altamente entrenada del Idris y se les recomienda obtener una imagen actualizada con anticipación. Las coordenadas se proporcionarán una vez confirmada su participación. Gracias y buena suerte.</v>
+        <v>Recuperar el puesto de avanzada de los cazadores de cabezas</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v> Recuperar el puesto de avanzada de los cazadores de cabezas</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v> Perezoso</v>
-      </c>
-    </row>
-    <row r="193" xml:space="preserve">
-      <c r="A193" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Headhunters le prestaron créditos recientemente a ~mission(TargetName) bajo ciertas condiciones. Específicamente, páguenos o lo mataremos. Es increíble pensar que eso no fue suficiente incentivo, pero aquí estamos, después de la fecha límite de pago. Ahora, por mucho que apreciemos a ~mission(TargetName|First), necesito que cumpla nuestra promesa. ~mission(TargetName|Last) fue visto por última vez en ~mission(Location|Address). Rastrea a ese tipo, hazlo desaparecer y cobra. Es así de simple. Se esconde.</v>
+        <v> Establecer la seguridad</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v> Establecer la seguridad</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v> Vencido</v>
-      </c>
-    </row>
-    <row r="195" xml:space="preserve">
-      <c r="A195" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se acabó el tiempo para la misión (Nombre del objetivo). Los Skav tienen un retraso considerable en el pago a los Cazadores de cabezas, así que necesito que los elimines. Mátalos, no los golpees, por si no queda claro. Alguien vio recientemente a la misión (Apellido del objetivo) cerca de la ubicación (Dirección), así que dirígete allí y elimínalos. Aviso importante: hemos recibido informes de que usaron parte de nuestros créditos para contratar protección adicional. Prepárate. Se esconde.</v>
+        <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v> Aviso de cobro</v>
-      </c>
-    </row>
-    <row r="197" xml:space="preserve">
-      <c r="A197" t="str" xml:space="preserve">
-        <v xml:space="preserve">~mission(TargetName) tomó prestados varios créditos de los Headhunters y pensó que lo más inteligente era intentar esconderse en lugar de devolvernos el dinero, así que necesito que alguien haga un escarmiento a ~mission(TargetName|Last). Acaban de ser vistos en ~mission(Location|Address), así que recomiendo ir allí ahora antes de que se pierda el rastro. ~mission(TargetName|Last) es una persona paranoica, así que no te sorprendas si no está solo. Haz lo que quieras, siempre y cuando ~mission(TargetName|Last) sea polvo cuando termines. Se esconde.</v>
+        <v> Protección contra ~misión(NombreObjetivo|Apellido)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v> Protección contra ~misión(NombreObjetivo|Apellido)</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v> Ataque preventivo</v>
-      </c>
-    </row>
-    <row r="199" xml:space="preserve">
-      <c r="A199" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Headhunters recibieron información de que se está preparando una operación XenoThreat dirigida contra uno de nuestros equipos. No tenemos detalles precisos sobre el plan, pero sabemos que ~mission(TargetName) lo está organizando. En lugar de quedarnos de brazos cruzados esperando a que algo suceda, hemos decidido actuar de forma proactiva. ~mission(TargetName|Last) acaba de ser visto con otros cerca de ~mission(Location|Address). No podemos movilizar a nadie lo suficientemente rápido para que lleguen allí. Quiero que vayas corriendo y lances un ataque preventivo. Stows out.</v>
+        <v> Intercepción de la carrera de suministros</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v> Intercepción de la carrera de suministros</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v> Venganza</v>
-      </c>
-    </row>
-    <row r="201" xml:space="preserve">
-      <c r="A201" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat atacó recientemente un bastión de Headhunters. Les ahorraré los detalles, pero le hicieron algo realmente atroz a nuestro equipo. Hemos identificado al líder de la operación como ~mission(TargetName) y buscamos venganza. No nos importa lo que hagan para lograrlo. Solo que ~mission(TargetName|Last) esté muerto. Una fuente nos acaba de decir que pueden rastrear a este canalla de XenoThreat en ~mission(Location|Address). Este enfermo es un profesional y nunca viaja solo, así que no esperen que eliminarlo sea pan comido. Se esconde.</v>
+        <v> Es necesario recuperar suministros esenciales.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v> Es necesario recuperar suministros esenciales.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v> Justicia exacta</v>
-      </c>
-    </row>
-    <row r="203" xml:space="preserve">
-      <c r="A203" t="str" xml:space="preserve">
-        <v xml:space="preserve">Recientemente se reveló que ~mission(TargetName) era un topo de XenoThreat. Ahora todo tiene sentido porque el skav era un verdadero cabrón. Desafortunadamente, se separaron antes de que pudiéramos encargarnos nosotros mismos. Basándonos en todo lo que aprendieron sobre nuestras operaciones, necesitamos eliminarlos cuanto antes. Si nos ven venir, simplemente volverán a huir, pero pensé que alguien como tú tiene más posibilidades de acercarse lo suficiente para un disparo mortal. Acabamos de enterarnos de que ~mission(TargetName|Last) andaba por ~mission(Location|Address). Parece que también hay otras naves protegiéndolos. ¿Crees que tienes la habilidad para librar al universo de un bastardo traidor y sus amigos bastardos? Esconderse.</v>
+        <v> Recuperación de suministros valiosos</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v> Recuperación de suministros valiosos</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v> Eliminar a los espías</v>
-      </c>
-    </row>
-    <row r="205" xml:space="preserve">
-      <c r="A205" t="str" xml:space="preserve">
-        <v xml:space="preserve">Algún imbécil está intentando desenterrar trapos sucios de los Headhunters. Se desplegaron algunos centinelas orbitales en ~mission(location|address) para espiarnos. También hemos visto una nave vigilándolos. Una propuesta sencilla para ti: ve a eliminar a los centinelas y te pagaremos por ello. ¿Te interesa? En cuanto a la nave, puedes hacer lo que quieras con ella, pero si te detecta, no te sorprendas si intenta buscar refuerzos. Así son estas cosas. Se esconde.</v>
+        <v> Operación especial de recuperación</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v> Operación especial de recuperación</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v> Exterminar a los espías</v>
-      </c>
-    </row>
-    <row r="207" xml:space="preserve">
-      <c r="A207" t="str" xml:space="preserve">
-        <v xml:space="preserve">Algunos idiotas creen que pueden espiar descaradamente a los Headhunters y salirse con la suya. Han instalado varios centinelas orbitales en ~mission(location|address) y tienen algunas naves patrullando la zona. No sabemos quién está detrás de esto, pero sinceramente no nos importa. Solo necesitamos que desaparezcan. Avísanos si te apetece poner en su sitio a esos descarados. Te pagaremos bien y te daremos los créditos en cuanto termines el trabajo. Ten en cuenta que solo nos preocupan los centinelas. Las naves que tienen patrullando solo son un problema si se interponen en tu camino o si intentan llamar a algunos amigos para detenerte.</v>
+        <v> El envío de carga debe completarse.</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v> El envío de carga debe completarse.</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v> Borrar espía</v>
+        <v> Suministros robados</v>
       </c>
     </row>
     <row r="209" xml:space="preserve">
       <c r="A209" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Tenemos un pequeño problema que los Headhunters deben solucionar. Hay una torreta orbital en ~mission(location|address) que algún pequeño alborotador instaló para espiar nuestras operaciones. ¿Quieres ganar algo de dinero fácil y volarla por nosotros? ¡Adelante!</v>
+        <v xml:space="preserve">Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v> Erradicar a los espías</v>
-      </c>
-    </row>
-    <row r="211" xml:space="preserve">
-      <c r="A211" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Headhunters buscan un mercenario para que nos ayude con un poco de limpieza. Descubrimos que alguien está intentando espiarnos en ~mission(location|address). No podemos permitirlo. Necesitamos un operador experto para que se encargue de los centinelas orbitales que desplegaron allí y, si es necesario, de cualquier nave que se interponga en tu camino. Parece una operación bien organizada, así que conseguirla puede no ser fácil, pero seguro que será divertido. Avísanos si eres el indicado. Los créditos se transferirán una vez que nuestros escaneos confirmen que se ha ido. Se esconde.</v>
+        <v> Recuperar carga</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v> Recuperar carga</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v> Una rápida represalia</v>
-      </c>
-    </row>
-    <row r="213" xml:space="preserve">
-      <c r="A213" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Oye, unos matones de poca monta se han atrincherado en ~mission(Location|Address). No les prestaríamos atención si no fuera porque esos arrogantes intentaron atacar un puesto de avanzada bajo nuestra protección. Los ahuyentamos sin mayores problemas, pero no podemos dejar que semejante falta de respeto quede impune. Nuestros agentes están ocupados con asuntos más importantes, así que nos gustaría que te encargaras de esto. ¡No te lo pierdas!</v>
+        <v> Redada para recuperar suministros</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v> Redada para recuperar suministros</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v> Gestión de la reputación</v>
-      </c>
-    </row>
-    <row r="215" xml:space="preserve">
-      <c r="A215" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unos cretinos se niegan a pagarnos lo que nos deben. El problema es que estos idiotas se jactan de ello. Si se hubieran callado, podríamos haber resuelto esto de forma más eficaz, pero ahora tenemos que dar un escarmiento. Estos imbéciles operan desde ~mission(Location|Address). Necesitamos que se vayan todos. ¡Que se oiga bien alto! Enviaremos el pago una vez que nos hayamos encargado de todos. - Se despide.</v>
+        <v> Reclamar la carga robada</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v> Reclamar la carga robada</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v xml:space="preserve"> Listos para la retribución</v>
-      </c>
-    </row>
-    <row r="217" xml:space="preserve">
-      <c r="A217" t="str" xml:space="preserve">
-        <v xml:space="preserve">Me acaba de caer información interesante. Parece que el infame líder de XenoThreat, ~mission(TargetName), está escondido en ~mission(location|address) trabajando en una gran operación para ellos. Oportunidad perfecta para acabar con ese cabrón de una vez por todas. El problema es que los Xenos están vigilando todas las operaciones de Headhunter en este momento. No hay forma de que podamos movilizar y desplegar un equipo sin que ~mission(TargetName|Last) se entere. Así que te ofrezco la oportunidad de mejorar Pyro y ganar algo de crédito al mismo tiempo. Si te interesa, te sugiero que te equipes y busques refuerzos antes de salir. Solo te pagarán si eliminas a ~mission(TargetName|Last), pero no dudes en matar a cualquier otro XenoThug que pueda estar escondido allí con ellos. ¡Que se vayan!</v>
+        <v> Recuperar suministros de XenoThreat</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Recuperar suministros de XenoThreat</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v> Iniciativa Overdrive: OBJETIVOS PRIORITARIOS</v>
-      </c>
-    </row>
-    <row r="219" xml:space="preserve">
-      <c r="A219" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nuestros analistas han examinado la información incautada a los equipos de reconocimiento de XenoThreat, pero los datos parecen estar protegidos por un sofisticado sistema de cifrado y requieren una clave criptográfica personalizada para acceder a ellos. Hemos logrado localizar a varios tenientes de XenoThreat que operan en el sistema; su misión es encontrar e interrogar a los sospechosos para determinar si poseen una clave criptográfica que nos permita acceder a la información. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de las Fuerzas de Defensa de Canadá que lleven esta iniciativa hasta el final.</v>
+        <v> Recuperar suministros</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v> Recuperar suministros</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v> Iniciativa Overdrive: VIGILANCIA DE AMENAZAS XENOTRAS</v>
-      </c>
-    </row>
-    <row r="221" xml:space="preserve">
-      <c r="A221" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de los sospechosos capturados durante los recientes ataques reveló que XenoThreat busca acceder remotamente a varias antenas de comunicación en todo el sistema. Que XenoThreat esté interceptando las comunicaciones es extremadamente peligroso para la población local, por lo que se ha solicitado a la CDF que reinicie la antena de comunicación y la defienda de cualquier Vanguardia de XenoThreat que intente reconectarse a los servidores. Una vez derrotadas dichas Vanguardias, se eliminarán las naves hostiles restantes en la zona. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que completen esta iniciativa.</v>
+        <v> Encontrar el barco de suministros perdido</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v> Encontrar el barco de suministros perdido</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v> Iniciativa Overdrive: INTEL RAID</v>
+        <v> Material confidencial robado</v>
       </c>
     </row>
     <row r="223" xml:space="preserve">
       <c r="A223" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos recibido información de que XenoThreat planea lanzar otro ataque contra el sistema Stanton. La CDF ha solicitado a la organización Advocacy la creación de una nueva iniciativa, denominada Operación Overdrive, para detener este ataque antes de que se produzca. La CDF está enviando voluntarios para infiltrarse y obtener información que pueda revelar sus planes. Huelga decir que se espera una fuerte resistencia por parte de cualquier XenoThreat presente. Como incentivo adicional, las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
+        <v xml:space="preserve">¿Estás disponible para un trabajo? Uno de nuestros centros de seguridad fue asaltado y robaron material altamente confidencial. Como puedes imaginar, Citizens for Prosperity necesita recuperarlo cuanto antes. Gracias a un contacto local, pudimos rastrear a los delincuentes hasta ~mission(Location|Address), donde almacenan el material confidencial en una bóveda automatizada de alta seguridad. Para acceder a ella, primero debes encontrar el código de recuperación e introducirlo en la cinta transportadora de la bóveda. Creemos que uno de los líderes de los delincuentes llevará el código consigo, por lo que es muy probable que tengas que hablar directamente con él para obtenerlo. Una vez que tengas el material confidencial en tu poder, te pedimos que lo entregues en ~mission(Dropoff1|Address). Si lo consigues, ayudarás mucho a muchas personas. Gracias de antemano, Lima Endicott, Despachadora Principal, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v> Iniciativa Overdrive: INCURSIÓN DE AMENAZA XENÓCRATA</v>
-      </c>
-    </row>
-    <row r="225" xml:space="preserve">
-      <c r="A225" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Oleadas de naves de la Amenaza Xeno han estado invadiendo el sistema Stanton y atacando a civiles al azar. No podemos determinar si se trata de un ataque aislado o una reacción a nuestras iniciativas recientes, pero debemos detenerlas. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
+        <v> Operación de detención de narcóticos</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Operación de detención de narcóticos</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v> Iniciativa Overdrive: EMERGENCIA EN KAREAH</v>
-      </c>
-    </row>
-    <row r="227" xml:space="preserve">
-      <c r="A227" t="str" xml:space="preserve">
-        <v xml:space="preserve">Atención a todos los voluntarios de CDF: hemos recibido una llamada de auxilio del Puesto de Seguridad Kareah. Resulta que XenoThreat utilizó los sistemas de comunicaciones como distracción para alejar a las fuerzas del orden y así poder lanzar un ataque contra la estación. Hemos descubierto que están intentando acceder a sus sistemas, por lo que todos los voluntarios deben desviarse inmediatamente para retomar Kareah y eliminar a todas las fuerzas de XenoThreat. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
+        <v> Desactiva Headhunter Stronghold</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v> Desactiva Headhunter Stronghold</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v> Iniciativa Overdrive: SOLICITUD DE SUMINISTRO</v>
-      </c>
-    </row>
-    <row r="229" xml:space="preserve">
-      <c r="A229" t="str" xml:space="preserve">
-        <v xml:space="preserve">Atención, voluntarios de CDF: XenoThreat ha desaparecido. Sospechamos que se han desconectado para preparar la fase final de su plan. La historia demuestra que a XenoThreat le gusta luchar, así que es lógico pensar que podría tratarse de un ataque. Por ello, solicitamos voluntarios para entregar suministros a la estación Gateway, cerca del punto de salto Stanton-Pyro, para reforzar la defensa ante un posible asalto. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
+        <v> Limitar la capacidad operativa de los forajidos</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v> Limitar la capacidad operativa de los forajidos</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v> Iniciativa Overdrive: Recompensa</v>
-      </c>
-    </row>
-    <row r="231" xml:space="preserve">
-      <c r="A231" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Gracias por tu dedicación a esta Iniciativa Overdrive. Como prometimos, te hemos aprobado una mejora de una F7C mk ii civil a una F7A mk ii militar, si dispones de una. Además, se te ha proporcionado un alquiler temporal de una F7A mk ii militar a la que puedes acceder en tu ASOP. _________________ Para actualizar, visita la página web de RSI para aplicar el token, luego reinicia el juego y accede a la nave.</v>
+        <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Recompensa esquiva: ~misión(Nombre del objetivo) (HRT)</v>
-      </c>
-    </row>
-    <row r="233" xml:space="preserve">
-      <c r="A233" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGOS: Objetivo de alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Esta recompensa ha resultado extremadamente escurridiza hasta ahora, pero los informes de inteligencia han rastreado al objetivo y a un grupo de sus asociados conocidos hasta ~mission(Location|Address). Sin embargo, hay una alta probabilidad de que ~mission(TargetName|Last) no se arriesgue a una confrontación a menos que se vea absolutamente obligado a ello. Recomendamos que primero neutralice a una parte significativa de los aliados del criminal para atraerlos. El informe indica que un gran grupo de estos hostiles se encuentra actualmente cerca de ~mission(Location). El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v> Desactivar Fortaleza de Forajidos en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v> Desactivar Fortaleza de Forajidos en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Recompensa atrincherada: ~misión(Nombre del objetivo) (MRT)</v>
-      </c>
-    </row>
-    <row r="235" xml:space="preserve">
-      <c r="A235" t="str" xml:space="preserve">
-        <v xml:space="preserve"> DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensa AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: L. Paleski EVALUACIÓN DE RIESGO: Objetivo de riesgo moderado (posible apoyo armado) CONTRATO URGENTE: No Hurston Dynamics busca un contratista para completar una recompensa para ~mission(TargetName). Los informes de inteligencia han localizado el paradero actual del objetivo en ~mission(Location|Address). Si bien tiene autorización para interactuar con cualquier delincuente en el lugar como considere oportuno, se debe proteger a cualquier civil presente en el lugar. El pago se realizará únicamente después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v> Eliminar todo rastro de datos de reclutadores</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v> Eliminar todo rastro de datos de reclutadores</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v> Recompensa evasiva: ~misión(Nombre del objetivo) (VHRT)</v>
-      </c>
-    </row>
-    <row r="237" xml:space="preserve">
-      <c r="A237" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGO: Objetivo de muy alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Se ha informado que este objetivo y la gran fuerza hostil con la que viaja han atacado recientemente ~mission(Location|Address). Sin embargo, si su modus operandi es el correcto, ~mission(TargetName|Last) generalmente se ha mantenido oculto durante los ataques, prefiriendo dirigir sus fuerzas desde lejos. Recomendamos que se concentre primero en reducir el número de sus aliados, y una vez que sus números se hayan debilitado significativamente, ~mission(TargetName|Last) no tendrá más remedio que enfrentarlo directamente. El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v> Borrar los servidores de datos de Headhunter</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v> Borrar los servidores de datos de Headhunter</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo) (LRT)</v>
+        <v> Destruir datos logísticos de XenoThreat</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Destruir datos logísticos de XenoThreat</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo) (HRT)</v>
+        <v> Destruye los datos robados de Headhunter</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Destruye los datos robados de Headhunter</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v xml:space="preserve"> Evaluación de contratistas de cazarrecompensas</v>
-      </c>
-    </row>
-    <row r="243" xml:space="preserve">
-      <c r="A243" t="str" xml:space="preserve">
-        <v xml:space="preserve">DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Después de repetidos y continuos delitos menores, se ha emitido una recompensa por la siguiente persona: ~mission(TargetName). Para evaluar su potencial para ayudar en la captura de criminales más escurridizos, Hurston Dynamics evaluará su capacidad para localizar y aprehender a ~mission(TargetName|Last) por cualquier medio a su disposición. La información más reciente sobre el paradero actual de ~mission(TargetName|Last) indica que fue visto por última vez en ~mission(Location|Address). El pago se liberará solo después de que se haya resuelto la recompensa. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v> Centro de datos Clear Outlaw</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v> Centro de datos Clear Outlaw</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo) (MRT)</v>
+        <v> Destruir los servidores de datos de XenoThreat</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Destruir los servidores de datos de XenoThreat</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v xml:space="preserve"> Reevaluación del contratista de cazarrecompensas</v>
-      </c>
-    </row>
-    <row r="247" xml:space="preserve">
-      <c r="A247" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Nuestro departamento realiza reevaluaciones periódicas de antiguos cazadores de recompensas y ha determinado que usted puede ser un candidato adecuado para una posible reincorporación. Como demostración de su idoneidad, capture con éxito al siguiente individuo buscado: ~mission(TargetName). La información más reciente sobre el paradero actual de ~mission(TargetName|Last) es que fue visto por última vez en ~mission(Location|Address). La reincorporación como cazador de recompensas de Hurston Dynamics y el pago se producirán tras la finalización exitosa de este contrato. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v> Destruir servidores de datos de Outlaw</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v> Destruir servidores de datos de Outlaw</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo) (ERT)</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Falta: ~misión(NombreObjetivo)</v>
+      </c>
+    </row>
+    <row r="249" xml:space="preserve">
+      <c r="A249" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lamentablemente, uno de nuestros socios comunitarios, ~mission(TargetName), lleva desaparecido varios días. Su familia se puso en contacto con Citizens for Prosperity para pedir ayuda y les dije que haríamos lo posible. Dicho esto, con tanto tiempo transcurrido, no tengo muchas esperanzas. Sea cual sea su situación actual, buscamos a alguien que nos ayude a localizarlo. Hay muchas probabilidades de que se dirigiera a ~mission(Location|Address), una zona conocida por ser muy peligrosa. Si logra localizarlo y confirmar su paradero, de una forma u otra, me aseguraré de que reciba la compensación adecuada. Lima Endicott, Coordinadora Principal de Despacho, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo) (VLRT)</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Falta: ~misión(NombreObjetivo)</v>
+      </c>
+    </row>
+    <row r="251" xml:space="preserve">
+      <c r="A251" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de nuestros compañeros, ~mission(TargetName), debía realizar un reconocimiento preliminar en ~mission(Location|Address), pero nunca se presentó. Esperamos que simplemente haya tenido mala suerte, pero aquí, incluso el más mínimo error puede resultar fatal. Agradecería que alguien se dirigiera a la zona e intentara localizarlo. Sería estupendo encontrarlo con vida, pero si no, brindarles un cierre es lo mínimo que podemos hacer por su familia. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo) (VHRT)</v>
+        <v> Entrega de regalos de Luminalia</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> ~misión(Contratista|DescripciónDeEntregaLocal)</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v> Neutralizar la incursión de forajidos</v>
+        <v> Ruta de envío local de Covalex</v>
       </c>
     </row>
     <row r="255" xml:space="preserve">
       <c r="A255" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Neutralización de Fuerzas Hostiles GERENTE DE SUBCONTRATACIÓN: T. Dalik EVALUACIÓN DE RIESGO: Alto Nuestras fuerzas de seguridad han sido notificadas de una incursión de delincuentes en curso en ~mission(Ubicación|Dirección), y necesitamos un operador independiente capaz de desalojar a los actores hostiles. Según el personal en el lugar, los delincuentes se encuentran actualmente atrincherados cerca de ~mission(Ubicación). Proceda con precaución y esté preparado para usar fuerza letal si los delincuentes se resisten a ser desalojados. El pago solo se autorizará una vez que la ubicación haya sido despejada de manera efectiva. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, tenemos un envío bastante grande esperando en la misión (Recogida 1) en la dirección (Recogida 1) que está listo para ser entregado. Con esta cantidad de cajas para transportar, probablemente sería bueno contar con ayuda adicional para cargar y descargar todo de su nave. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item11|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item12|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item13|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item14|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item15|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; Mucha suerte, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite'. Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v> Recompensa localizada: ~misión(Nombre del objetivo) (MRT)</v>
+        <v>Oportunidad para transportista de carga independiente</v>
       </c>
     </row>
     <row r="257" xml:space="preserve">
       <c r="A257" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: T. Davik EVALUACIÓN DE RIESGOS: Riesgo moderado Hurston Dynamics busca un contratista para completar una recompensa por la misión ~(Nombre del objetivo). Los informes de inteligencia han rastreado al objetivo hasta ~(Ubicación|Dirección), donde fue visto por última vez cerca de ~(Ubicación). Prepárese para que oponga resistencia a la detención y para el uso de fuerza letal si fuera necesario. El pago se realizará únicamente después de que la recompensa se considere completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Covalex, galardonada con reconocimientos como "Las 10 mejores empresas de transporte marítimo" de Imperial Finance y "El transporte más confiable de Delivery Digest" (2945), está más activa que nunca. Esto significa más carga para más destinos. Ahí es donde entras tú. Covalex busca pilotos confiables y trabajadores para unirse a nuestra creciente familia. ¿Tienes acceso a un barco con capacidad para contenedores de carga de &lt;EM4&gt;~mission(MissionMaxSCUSize)&lt;/EM4&gt;? ¿Puedes superar una verificación de antecedentes de Advocacy si se requiere? Entonces, un universo de oportunidades te espera. Simplemente completa una "Prueba de evaluación" recogiendo un envío de &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entregándolo con éxito en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Tras completar satisfactoriamente el proceso, podrá formar parte de la amplia red de especialistas en transporte independientes de Covalex Shipping*. Por cierto, recomendamos encarecidamente a los contratistas que traigan consigo un rayo tractor portátil. Covalex Shipping: «Todo lo que necesite, donde lo necesite». *Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de carga, Covalex Shipping establecerá un plazo de entrega y, una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v> Erradicar todos los nidos</v>
+        <v>Reevaluación del servicio de transporte de carga de Covalex</v>
       </c>
     </row>
     <row r="259" xml:space="preserve">
       <c r="A259" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar varios nidos que han impedido que los departamentos inspeccionen las cuevas pertinentes en busca de recursos. Estamos dispuestos a ofrecer una generosa remuneración por la erradicación de estas plagas. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, tenemos buenas noticias para ti. Covalex ha finalizado recientemente una evaluación de nuestro grupo de contratistas y ha decidido reconsiderar tu estatus como transportista de carga. Para volver a calificar, solo necesitas completar con éxito la siguiente entrega. Recoge &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entrégalo en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Para completar este transporte de forma rápida y eficiente, necesitarás un barco que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Esperamos que todo salga bien para poder darte la bienvenida de nuevo al equipo. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Covalex Shipping 'Todo lo que necesitas, donde lo necesitas'. Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de mercancías, Covalex Shipping establecerá un plazo límite de entrega. Una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v> Exterminar Nido de ~misión(Criatura)</v>
+        <v>Manipulador de paquetes Covalex</v>
       </c>
     </row>
     <row r="261" xml:space="preserve">
       <c r="A261" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar a ~mission(Criatura) que se ha instalado en ~mission(ubicación|dirección). Se han convertido en un problema y necesitamos un profesional para resolver la situación. El pago se realizará una vez que se haya eliminado el nido. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, hay un montón de paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que necesitan ser trasladados dentro de las instalaciones hasta su lugar de almacenamiento correspondiente. Sería de gran ayuda si pudieras encargarte personalmente de que todo se organice. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Realmente aprecio todo lo que haces, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones como se describen en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29' extendida. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v xml:space="preserve"> Proteger el sitio y recuperar materiales confidenciales.</v>
+        <v>Ruta de reparto local de Covalex</v>
       </c>
     </row>
     <row r="263" xml:space="preserve">
       <c r="A263" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Inspección de instalaciones y recuperación de paquetes AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: Sí Hurston ha sabido que los Nine Tails están atacando ~mission(Location|address). Nuestras fuerzas en el sitio han sufrido numerosas bajas y han dejado de responder a las comunicaciones. Los informes iniciales indicaron que la banda estaba intentando obtener material confidencial entregado recientemente a las instalaciones. Afortunadamente, contamos con medidas de seguridad que deberían darnos tiempo para responder. Necesitamos que un agente se dirija a las instalaciones de inmediato, recupere esas cajas y las entregue en un lugar seguro. Usted y cualquier refuerzo que elija traer están autorizados a tomar las medidas necesarias al enfrentarse a los intrusos. Se considera que los sospechosos están armados y son peligrosos. Hurston no proporcionará apoyo material ni actualizaciones sobre el estado de las fuerzas de seguridad de las instalaciones. El material confidencial se entregó discretamente junto con otras cajas en un envío y se guardó en nuestra bóveda automatizada con códigos de acceso almacenados en tabletas electrónicas custodiadas por personal de seguridad de alto nivel. Sin embargo, existe una alta probabilidad de que Nine Tails ya se haya apoderado de él. Deberá encontrar esas tabletas electrónicas e introducir los códigos en la cinta transportadora de paquetes para recuperar el material confidencial. El pago se enviará una vez que se haya entregado en ~mission(dropoff1|address). ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como cualquier acción basada en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve"> ¡Hola! Acabamos de recibir una entrega local que necesitamos que se encarguen, si están disponibles. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no se hace responsable de los daños que puedan producirse mientras opera como contratista independiente.</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v xml:space="preserve">Informe de persona desaparecida: ~misión(Nombre del objetivo)</v>
+        <v>Evaluación de Covalex</v>
       </c>
     </row>
     <row r="265" xml:space="preserve">
       <c r="A265" t="str" xml:space="preserve">
-        <v xml:space="preserve"> CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Localización de persona desaparecida. GERENTE DE SUBCONTRATACIÓN: I. Takao. EVALUACIÓN DE RIESGO: Baja. El personal de ~mission(Ubicación|Dirección) ha presentado recientemente una denuncia por desaparición de ~mission(Nombre del objetivo). Esta persona lleva varios días desaparecida y fue vista por última vez dirigiéndose a ~mission(Ubicación). Se le contrata para realizar una búsqueda in situ de ~mission(Apellido del objetivo) e intentar determinar su paradero. El pago depende de la obtención de un registro de su ubicación actual, ya sea que se encuentre viva o fallecida. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">¡Hola! Covalex está buscando nuevos contratistas de entrega. Para ver si tienes el perfil de Covalex, hemos organizado la siguiente ruta de entrega como evaluación de tus habilidades. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Completar con éxito esta ruta te certificará como contratista oficial de Covalex. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra "Guía de información complementaria para trabajadores independientes v.2948.01.29". Covalex Shipping no se responsabiliza de los daños que puedan producirse durante su actividad como contratista independiente.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v> Instalación de protección contra amenazas</v>
+        <v>Reevaluación de Covalex</v>
       </c>
     </row>
     <row r="267" xml:space="preserve">
       <c r="A267" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Una pequeña banda local ha estado profiriendo amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, dado que Covalex ha estado experimentando un exceso de entregas y escasez de contratistas, logré convencer a la administración para que reconsiderara tu situación. Solo tienes que completar con éxito la siguiente entrega y volverás a formar parte del sistema. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Buena suerte. Sería genial tenerte de nuevo en la lista. Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de los daños que se produzcan mientras se opera como contratista independiente.</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v> Instalación de vigilancia contra hostiles</v>
-      </c>
-    </row>
-    <row r="269" xml:space="preserve">
-      <c r="A269" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Delincuentes locales han estado realizando amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v>Error de envío - Carga sensible a la calidad</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v> ~misión(Contratista|DescripciónDeEntregaSensibleCuántica)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v> Instalación de vigilancia contra hostiles peligrosos</v>
+        <v> Programa piloto de entrega para Covalex</v>
       </c>
     </row>
     <row r="271" xml:space="preserve">
       <c r="A271" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Muy alta CONTRATO URGENTE: No Una creciente facción delictiva ha estado realizando amenazas contra ~mission(Location|Address) y Hurston Security requiere un contratista para formar un equipo de seguridad y proteger las instalaciones contra cualquier intrusión. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve"> Hola, tengo una entrega que necesito gestionar. El pedido está esperando en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser llevado a &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Estoy seguro de que no tendrás problemas, pero para que lo sepas, veo varias advertencias de seguridad en esta zona. Parece que ha habido algunos ataques en esa área en los últimos días. No digo que vayas a tener ningún problema, pero probablemente sería mejor que llevaras algo de protección. Mucha suerte, Chase Hewitt Jr., Coordinador de Logística de Covalex Shipping. «Todo lo que necesites, donde lo necesites».</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v> Eliminar el alijo de contrabando</v>
+        <v> Efectos personales</v>
       </c>
     </row>
     <row r="273" xml:space="preserve">
       <c r="A273" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Delincuentes locales han estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de contrabando. Hurston Security requiere un contratista para que acuda a las instalaciones y destruya todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, entenderé perfectamente si no quieres ayudarme con esto, pero si puedes, sería genial. Verás, mi novio falleció durante la tragedia de Covalex Gundo. Me dijeron que recuperaría todas las pertenencias de Scott una vez que terminara la investigación, pero hasta donde sé, ya pasó un tiempo y todavía no me han dado ninguna indicación de cuándo podré recuperarlas. Ya ha sido bastante difícil lidiar con todo esto, y saber que dentro de uno o dos meses llegará un paquete que reabrirá todas estas heridas es demasiado. Preferiría resolverlo ahora y terminar con esto. Si pudieras encontrar la manera de recoger sus efectos personales (ID de empleado n.° 104) y entregarlos en ~mission(Destino), te lo agradecería muchísimo. Gracias por tu ayuda, Anya</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v> Eliminar el alijo de narcóticos</v>
+        <v> Ayúdenme a recuperar mis cosas.</v>
       </c>
     </row>
     <row r="275" xml:space="preserve">
       <c r="A275" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Muy alta CONTRATO URGENTE: No Un pequeño grupo criminal ha estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de narcóticos altamente peligrosos. Hurston Security busca un contratista para que acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Mi hermano fue una de las personas que murió cuando explotó la estación Covalex cerca de Crusader. Peor aún, estaba usando algo mío cuando ocurrió. Ahora un burócrata de mierda me dice que tengo que esperar para recuperar mis cosas. ¡Claro que sí! Primero matan a mi hermano y ahora quieren que tenga paciencia. ¡Qué descaro el de estos imbéciles corporativos! Olvídalo. En vez de eso, pensé en contratar a alguien para que vaya a Gundo a buscar mis cosas y las lleve a ~misión(Destino) por mí. O sea, ¿qué demonios van a hacer al respecto? En fin, es lo que mi hermano hubiera querido. Será la caja marcada con el número 156. - Ed</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v> Eliminar el alijo de drogas</v>
+        <v> Herencia inesperada</v>
       </c>
     </row>
     <row r="277" xml:space="preserve">
       <c r="A277" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Se ha identificado a delincuentes locales que utilizan ~mission(Location|Address) para fabricar grandes cantidades de contrabando ilegal. Hurston Security requiere que un contratista acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, esto me resulta un poco incómodo, pero resulta que una de las personas que falleció en el desastre de la estación Covalex, Kyomi Santos, me dejó algo en su testamento. Me sorprendió mucho, pero ahora soy el orgulloso dueño de todo lo que hay en la caja n.° 173. En Covalex dicen que podré recogerlo cuando la estación vuelva a abrir, pero... aquí viene lo incómodo... lo necesito urgentemente. Normalmente esperaría, pero estoy intentando montar mi propio negocio (hago pasteles con la forma de los planetas de origen de la gente) y los créditos que gane con la venta me vendrán de maravilla. Tengo algo de dinero ahorrado que puedo usar para pagarle a alguien que me lo envíe desde Gundo hasta ~misión(Destino). Sé que todo esto es un poco raro, pero si hubiera otra manera, no estaría preguntando. Gracias por la ayuda, Thrace.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v> Ayudar en la defensa del sitio.</v>
+        <v> La súplica de una madre</v>
       </c>
     </row>
     <row r="279" xml:space="preserve">
       <c r="A279" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No El personal de seguridad en ~mission(Location|Address) está siendo amenazado por un grupo criminal local y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente acceder al sitio. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Mi hijo Nico fue, lamentablemente, una de las víctimas del trágico accidente en la estación de Covelex en Gundo, y aún no me han devuelto todas sus pertenencias. Entiendo que deben cumplir con las normas, pero me parece inconcebible que no tengan en cuenta el dolor de la familia. Por ello, busco a alguien que pueda ir a la estación por mí. Cabe aclarar que actualmente Gundo está fuera de los límites, lo que significa que esto no sería legal, pero creo que mi situación merece una consideración especial. Mi hermana dice que la tarifa que ofrezco es la correcta para recuperar la caja con las pertenencias de Nico (n.º 964) y llevarlas a ~mission(Destination), así que espero encontrar a alguien competente que pueda resolver este asunto rápidamente. Atentamente, Gloria Theolone</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v> Evaluación de contratistas de seguridad</v>
-      </c>
-    </row>
-    <row r="281" xml:space="preserve">
-      <c r="A281" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Un grupo criminal local ha estado amenazando ~mission(Location|Address) y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente entrar en las instalaciones. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en las instalaciones resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta evaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v> Buscando un cierre</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Me dijeron que podría encontrar a alguien aquí que fuera a Gundo por mí y recogiera una caja que pertenecía a mi esposa. Si el nombre no te suena, es la estación donde ocurrió aquel gran accidente. Mi esposa trabajaba para Covalex y sé que eso no hará que su pérdida sea más fácil, pero de verdad quiero recuperar las cosas de Claudia. Pienso en su colección de fotos o en el collar que le regalé, ahí, en esa fría y desolada estación, en una caja marcada con el número 249, y no es justo. Ella se merece algo mejor. ¿Qué te parece? ¿Estás dispuesto a ir a Gundo y llevar su caja de vuelta a ~misión(Destino)?</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v> Reevaluación de contratistas de seguridad</v>
+        <v> Las cosas de mi papá</v>
       </c>
     </row>
     <row r="283" xml:space="preserve">
       <c r="A283" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Nuestro departamento realiza reevaluaciones periódicas de los contratistas de seguridad anteriores y ha determinado que usted podría ser un candidato adecuado para una posible reincorporación. Para recuperar su estatus, Hurston Security busca contratistas que ayuden a eliminar un elemento criminal local que amenaza ~mission(Location|Address). Tenga en cuenta que solo está autorizado para interactuar con hostiles confirmados. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta reevaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, busco a alguien que vaya a la estación Covalex Gundo cerca de Crusader y recoja algunos objetos. Sé que puede sonar a robo, pero son las cosas de mi papá. Verás, él estaba en la estación Gundo cuando ocurrió el accidente. Mi mamá dice que tenemos que esperar a que Covalex lo autorice, pero no me parece justo porque lo extraño muchísimo. Me gustaría tener algo para recordarlo y no quiero esperar más porque podría empezar a olvidar cosas. Te pagaré para que me consigas la caja 510 y la lleves a ~mission(Destination) para que pueda tenerla. Muchas gracias, Baylor Ward</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Desalojar a los ocupantes ilegales</v>
+        <v> Apoderarse de los datos</v>
       </c>
     </row>
     <row r="285" xml:space="preserve">
       <c r="A285" t="str" xml:space="preserve">
-        <v xml:space="preserve"> CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Limpieza de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: K. Restle EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Hurston busca un contratista dispuesto a desalojar a los ocupantes criminales de ~mission(Location|Address). El sitio se ha utilizado para albergar numerosas actividades ilegales, por lo que es imperativo asegurarlo. Tenga en cuenta que solo está autorizado a interactuar con hostiles confirmados. Agredir a cualquier civil en el sitio se considerará una violación de su contrato. El pago se enviará una vez que se confirme que las instalaciones están despejadas. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">He estado buscando un paquete de datos específico y justo cuando tengo un respiro, la nave es atacada por esta Reclamadora de Nueve Colas modificada llamada Cometa Negra. Intenté hackear los servidores de la Cometa Negra para ver si copiaron los datos, pero no pude encontrar la manera de sortear sus protocolos de cifrado de forma remota sin la clave física. Ahí es donde entras tú. Necesito que alguien acceda a su nave, consiga su clave de descifrado y descifre el servidor para poder descargar remotamente lo que necesito. Eres lo suficientemente inteligente como para saber con quién estamos tratando, así que planifica en consecuencia. Dado que esto va a causar revuelo, no dejemos nada al azar. Destruye la Cometa Negra cuando termines para cubrirnos las espaldas a ambos.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v> Listo para ser aprovechado</v>
+        <v> Extracción de recompensa: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
     <row r="287" xml:space="preserve">
       <c r="A287" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tengo buenas noticias para ti. En este preciso instante, hay una instalación automatizada que está produciendo paquete tras paquete de producto de primera calidad, prácticamente listo para ser aprovechado. Solo tienes que ir allí, lidiar con un par de matones, agarrar lo que puedas y venderlo con una gran ganancia. No debería ser ningún problema. Y hay mucha gente dispuesta a pagar bien por comprarte ese producto. Hablando de créditos, no voy a dar las coordenadas de esta instalación por pura generosidad. Creo que es justo pedir una comisión por información tan valiosa. No esperes demasiado. No sé cuánto tiempo más estará activa la página web. -Ruto</v>
+        <v xml:space="preserve">Tuvimos suerte y algunos escaneos recientes de ~mission(Location|Address) han revelado que hay una recompensa pendiente con el nombre de ~mission(TargetName) oculta allí. Se le ha autorizado a entrar en el sitio, encontrarla y resolver la recompensa. Sin embargo, además de la recompensa y sus cómplices, es probable que también haya civiles en el sitio. Si bien estamos ansiosos por eliminar a ~mission(TargetName|Last), no podemos permitirnos bajas civiles. Tenga cuidado al interactuar con los hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Gibbs ID# 91G66BW0</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v> Confiscar contrabando</v>
-      </c>
-    </row>
-    <row r="289" xml:space="preserve">
-      <c r="A289" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados Hemos podido rastrear un reciente aumento de contrabando hasta una planta de producción automatizada en ~mission(Location|Address). No podemos asegurar cuánto tiempo más estará operativa la planta, por lo que BlacJac necesita a alguien en el lugar para inspeccionar, asegurar el contrabando y transportarlo hasta ~mission(Destination|Address). Una vez allí, pueden usar la terminal administrativa de mercancías para transferirnos el contrabando y cobrar su recompensa. No hemos podido determinar qué tipo de fuerza hostil estará presente, pero sea cual sea la que encuentren, están autorizados a usar la fuerza letal si es necesario. Cuanto más contrabando logren traernos, más créditos ganarán. Gracias, Teniente Aaron Riegert, Supervisor de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
+        <v> Recompensa emitida para ~mission(TargetName) (LRT)</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v> Confiscar contrabando</v>
+        <v> Evaluación de recompensas para freelancers verificados</v>
       </c>
     </row>
     <row r="291" xml:space="preserve">
       <c r="A291" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que una instalación de producción ilegal en ~mission(Location|Address) se está utilizando para fabricar contrabando. Buscamos un contratista para asegurar el sitio, confiscar el contrabando y entregarlo en ~mission(Destination|Address). La terminal administrativa de mercancías le permitirá entregar el contrabando a nuestro depósito de pruebas y cobrar su pago. Dado que se trata de una instalación automatizada, no está claro cuánto tiempo estarán fabricando ni cuántas personas podrían estar presentes. Para mayor seguridad, le recomendamos que vaya preparado para encontrar una fuerte resistencia. Su compensación total dependerá de la seguridad con la que se entreguen los paquetes como prueba. CONTRATO AUTORIZADO POR: Oficial de Enlace Vanzant ID# 712L921P</v>
+        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personas cualificadas para colaborar en la cobranza de recompensas en la zona. Hemos evaluado que usted posee las habilidades necesarias y, por lo tanto, nos gustaría ofrecerle un contrato inicial de prueba para la captura de ~mission(TargetName), vista por última vez en ~mission(Location|Address). Al completar con éxito este contrato, se le incluirá en la lista de Freelancers Verificados de Crusader y podrá optar a futuros trabajos de cobranza de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v> Confiscar contrabando</v>
-      </c>
-    </row>
-    <row r="293" xml:space="preserve">
-      <c r="A293" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Confiscar contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Odington EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Hurston Security ha tenido conocimiento de una instalación de producción automatizada ilegal y activa en ~mission(Location|Address) y busca un contratista para asegurar el sitio y confiscar la mayor cantidad posible de paquetes de contrabando para su entrega a una instalación de Hurston Security en ~mission(Destination|Address) para su eliminación inmediata. La transferencia del contrabando y la atribución de su pago de recompensa deben realizarse a través de la terminal administrativa de mercancías en dicho lugar. Usted está autorizado a usar la fuerza necesaria para completar su objetivo. El pago se basará en la cantidad de contrabando incautado. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v> Recompensa emitida para ~mission(TargetName) (HRT)</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Confiscar contrabando</v>
-      </c>
-    </row>
-    <row r="295" xml:space="preserve">
-      <c r="A295" t="str" xml:space="preserve">
-        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional de seguridad orientado a los detalles que pueda ayudarnos a asegurar el contrabando de un sitio de producción automatizado ilegal en ~mission(Location|Address). Los paquetes luego deberán ser llevados a ~mission(Destination|Address) y transferidos a nuestra posesión para su destrucción a través de la terminal administrativa de mercancías. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Gestionar cualquier hostil encontrado dentro del sitio; usando la fuerza según sea necesario. • Asegurar el contrabando y entregarlo a las terminales de mercancías en ~mission(Destination|Address) REQUISITOS MÍNIMOS • 2 años de experiencia combinada de mercenario y/o seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v> Recompensa emitida para ~mission(TargetName) (MRT)</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v> Ruta de reparto local de la familia Ling</v>
+        <v> Reevaluación de la recompensa para freelancers verificados</v>
       </c>
     </row>
     <row r="297" xml:space="preserve">
       <c r="A297" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, espero que estés disponible para hacer una entrega. ~mission(Contractor|Family) PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Avísame si puedes hacerlo. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling Coordinadora de Envíos Ling Family Hauling</v>
+        <v xml:space="preserve">¡Buenas noticias! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de recompensas. Esperamos que durante este tiempo hayas corregido cualquier problema de rendimiento anterior y puedas volver a ser un activo valioso. Sin embargo, primero debemos reevaluarte, por lo que nos gustaría que completaras este contrato de recompensa para ~mission(TargetName). Tras completar con éxito esta prueba, volverás a la lista de Freelancers Verificados de Crusader y podrás optar a futuros trabajos de cobro de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v> La familia Ling busca nuevos contratistas.</v>
-      </c>
-    </row>
-    <row r="299" xml:space="preserve">
-      <c r="A299" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, somos una pequeña empresa de reparto familiar que actualmente busca nuevos contratistas en la zona de Crusader. Si te interesa trabajar con nosotros, la siguiente entrega sería una excelente prueba para ver si encajas bien con la empresa. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si todo sale bien, te convertirás en el miembro más reciente de Ling Family Hauling. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+        <v> Recompensa emitida para ~mission(TargetName) (ERT)</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v> Reevaluación del contratista Ling</v>
-      </c>
-    </row>
-    <row r="301" xml:space="preserve">
-      <c r="A301" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, no me entusiasma tener que hacer esto, pero tenemos escasez de contratistas y más entregas que nunca. Estoy dispuesto a darte otra oportunidad, pero necesitas completar la siguiente entrega. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por último, probablemente sería buena idea llevar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+        <v> Recompensa emitida para ~mission(TargetName) (VLRT)</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Entrega de paquetes para Ling</v>
-      </c>
-    </row>
-    <row r="303" xml:space="preserve">
-      <c r="A303" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, necesitamos que recojas un paquete en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y lo lleves a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Originalmente iba a enviar a mi hermano Ricki, pero dijo que la zona es demasiado peligrosa. Supongo que ha habido varias advertencias de seguridad por allí, pero mientras tengas cuidado y lleves armas o algo así, seguro que no tendrás problemas. Probablemente ni siquiera te topes con nada. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+        <v> Recompensa emitida para ~mission(TargetName) (VHRT)</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="str">
-        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
+        <v> URGENTE: Retomar el puesto de seguridad de Kareah</v>
+      </c>
+    </row>
+    <row r="305" xml:space="preserve">
+      <c r="A305" t="str" xml:space="preserve">
+        <v xml:space="preserve">El puesto de seguridad Kareah está siendo atacado por un número desconocido de asaltantes. Crusader busca contratistas que se dirijan rápidamente a la estación y eliminen a todos los intrusos en las inmediaciones antes de que nuestras fuerzas de seguridad se vean superadas. No sabemos si los atacantes buscan el contrabando en nuestro depósito de pruebas o nuestra base de datos CrimeStat, pero sea lo que sea que busquen, debemos neutralizarlos. Recibirás una bonificación de combate por cada objetivo neutralizado. Al aceptar este contrato, te comprometes a cumplir con todos los protocolos de seguridad de Crusader: si dañas a algún guardia u otro contratista autorizado mientras te encuentres en la estación, tu contrato se dará por terminado y serás marcado como objetivo. El tiempo apremia, así que asegúrate de estar bien equipado para enfrentarte a los hostiles antes de responder. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v> Oportunidades de empleo en seguridad de Eckhart</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="str">
-        <v> ~misión(Descripción)</v>
+        <v> Apoyar a las fuerzas de seguridad y proteger los materiales confidenciales.</v>
+      </c>
+    </row>
+    <row r="307" xml:space="preserve">
+      <c r="A307" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los informes indican que nuestro personal de seguridad en ~mission(location|address) ha sido aniquilado por un grupo de los Nueve Colas, quienes intentan robar material confidencial entregado recientemente a las instalaciones. Crusader Security necesita un contratista experimentado para expulsar a los hostiles y asegurar estas cajas. Según los informes iniciales, recomendamos encarecidamente que venga bien equipado y considere traer refuerzos. Por motivos de seguridad, el material confidencial fue transportado allí como parte de un envío con otras cajas y guardado bajo llave en una bóveda automatizada. Los códigos de acceso al material confidencial se encuentran en tabletas de datos en poder de personal de seguridad de alto rango, pero desconocemos quién las tiene ahora. Es probable que los Nueve Colas también las estén buscando. Cuando tenga todo el material confidencial, entréguelo en ~mission(dropoff1|address) para recibir el pago. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v> Supervisión de la producción</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="str">
-        <v> ~misión(Contratista|Descripción del producto farmacéutico de entrega local)</v>
+        <v> Sitio de vigilancia contra hostiles</v>
+      </c>
+    </row>
+    <row r="309" xml:space="preserve">
+      <c r="A309" t="str" xml:space="preserve">
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una pandilla local y estamos buscando contratar a un contratista para formar un equipo de seguridad que haga frente a cualquier ataque. Esta pandilla tiene antecedentes, pero aún son bastante novatos. Creo que será relativamente sencillo para usted y su equipo manejar la situación. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v> Una tanda hecha desde cero</v>
+        <v> Sitio de protección contra hostiles graves</v>
       </c>
     </row>
     <row r="311" xml:space="preserve">
       <c r="A311" t="str" xml:space="preserve">
-        <v xml:space="preserve">Normalmente, me gusta cocinar todo desde cero. Me enorgullece el producto y todo eso. Pero de vez en cuando, ya sea por mucha demanda, mucho calor o lo que sea, necesito recurrir a otros laboratorios para un pedido. Sin embargo, aquí estoy muy ocupado, así que me vendría bien alguien que me ayudara a supervisar toda la línea de producción. No se me ocurre nadie mejor ni más disponible que tú. ~Misión (Itinerario) Simplemente no te distraigas ni te desvíes del camino. Sucede más a menudo de lo que crees. Si logras completar la lista, me aseguraré de que recibas una buena parte de las ganancias. -Wallace</v>
+        <v xml:space="preserve"> Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes y estamos buscando contratar a un contratista para formar un equipo de seguridad que repela cualquier ataque. Sé que puede que tengas la tentación de intentar resolver esto por tu cuenta, pero necesitas formar un equipo. Créeme, no vale la pena intentarlo solo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v> Capturan al miembro de la pandilla de Arlington, Les Arlington</v>
+        <v> Sitio de vigilancia contra hostiles peligrosos</v>
       </c>
     </row>
     <row r="313" xml:space="preserve">
       <c r="A313" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Una comunicación anónima nos ha avisado de que Les Arlington, hijo del líder de la banda Maltrox Arlington, había sido visto recogiendo una entrega en un centro de transferencia de Covalex. Le proporcionaremos las coordenadas de donde creemos que se encuentran actualmente. Les es un piloto experimentado que lleva volando casi tanto tiempo como ellos llevan caminando y suele ser el piloto de escape de la banda. Podría ser conveniente traer naves de apoyo adicionales para frustrar cualquier intento de fuga. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una banda criminal conocida que opera en la zona y estamos buscando contratar un equipo de seguridad experimentado para hacer frente a cualquier ataque. Asegúrese de que la persona que contrate esté debidamente cualificada. Necesitará toda la ayuda posible para lidiar con este grupo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Captura de Nicks Cantwell, miembro de la pandilla de Arlington.</v>
+        <v> Destruir las drogas ilegales</v>
       </c>
     </row>
     <row r="315" xml:space="preserve">
       <c r="A315" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de arresto grupal para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero de reparación. Si bien el robo fue detenido, los miembros del grupo se han dispersado en la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. Hemos recibido información de que Nicks Cantwell, conocido de larga data y confidente de Maltrox Arlington, fue visto intentando comprar un láser de minería de alta densidad, del tipo que se usa frecuentemente en intentos de secuestro de naves para perforar estratégicamente los cascos. Hemos proporcionado las coordenadas de la última ubicación conocida de Nicks. Nicks es un experto en municiones muy respetado en los círculos criminales y suele dejar un rastro de destrucción a su paso. Se recomienda aumentar la potencia de fuego en este encuentro. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Hemos descubierto que un grupo está intentando montar su propio negocio de drogas en ~mission(Location|Address). Aunque parecen ser delincuentes comunes y corrientes, el producto que fabrican es tóxico y ha causado la muerte de varios civiles, así que no podemos permitir que se venda más. Estamos trabajando en una operación a gran escala para desmantelar su negocio definitivamente, pero mientras tanto, debemos detener el flujo de sus drogas. Por eso, Crusader quiere que vayas al lugar y destruyas el alijo que tienen allí. Sin duda, tendrán guardias protegiendo el alijo, pero no creo que representen una gran amenaza. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Captura a Sam 'Weepy' Arlington, miembro de la pandilla de Arlington.</v>
+        <v> Destruye el contrabando mortal</v>
       </c>
     </row>
     <row r="317" xml:space="preserve">
       <c r="A317" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Sam 'Weepy' Arlington fue marcado por sistemas de seguridad automatizados en un R&amp;R después de estar involucrado en una pelea de borrachos. Weepy logró abandonar la estación antes de que llegaran los equipos de respuesta, pero hemos podido localizarlo en el lugar donde creemos que se encuentra escondido. Weepy es tío y principal ejecutor del líder de la pandilla, Maltrox Arlington. Sus problemas de ira, sumados a un largo historial de abuso de sustancias, lo convierten en un verdadero impredecible. Espere que oponga una resistencia considerable cuando usted y sus fuerzas lo acorralen. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Un incipiente sindicato se ha instalado en ~mission(Location|Address) y está intentando introducirse en el mercado de las drogas. Desafortunadamente, su producto se ha relacionado con varias muertes en Crusader y sus alrededores. Dada la potencia de esta sustancia, representa una grave amenaza para la población. Crusader está trabajando para desmantelar la operación, pero mientras su producto siga circulando, los cadáveres se acumularán. Queremos que vayas al lugar y destruyas el alijo que tienen allí antes de que tengan la oportunidad de venderlo. Sin embargo, debes tener en cuenta que su alijo está extremadamente bien custodiado. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Captura de un miembro de una pandilla de Arlington en Oslo, Arlington.</v>
+        <v> Destruir narcóticos tóxicos</v>
       </c>
     </row>
     <row r="319" xml:space="preserve">
       <c r="A319" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Recientemente, se accedió ilegalmente a una terminal de seguridad utilizando una criptoclave personalizada única que había sido utilizada en un robo el año pasado por un tal Oslo Arlington, el hermano menor del líder de la banda Maltrox Arlington. Aunque no podemos confirmar con certeza si Oslo hackeó la terminal, consideramos que vale la pena investigarlo. Oslo, un estratega de renombre, sumamente inteligente y experto en tecnología, ha demostrado ser difícil de capturar en el pasado. Si esta pista conduce a su localización, un equipo de ataque táctico bien coordinado sería fundamental para el éxito de la operación. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al finalizar el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. Dicha información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Hemos estado investigando una reciente oleada de sobredosis y todas parecen haberse originado con un lote defectuoso de drogas fabricado en ~mission(Location|Address). Estoy trabajando con otros contratistas para dar con los responsables, pero la gente sigue muriendo mientras el producto siga circulando. Quiero que vayas al lugar y destruyas el alijo que tienen allí. Eso nos dará algo de tiempo antes de cerrarlo definitivamente. Tendrán guardias protegiendo su suministro, así que prepárate para enfrentarte a hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Captura de Kass Dent, miembro de la pandilla de Arlington.</v>
+        <v> Proporcionar respaldo</v>
       </c>
     </row>
     <row r="321" xml:space="preserve">
       <c r="A321" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado al espacio profundo. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Dos guardias de banco fueron reportados como desaparecidos la semana pasada. Hace unas horas, sus cuerpos aparecieron en un montón de basura en Magnus con sus datos biométricos robados. Afortunadamente, un puesto de dumplings cercano tenía una cámara de seguridad que captó el momento en que arrojaron los cadáveres. El reconocimiento facial permitió identificar a Kass Dent, pareja sentimental de Maltrox Arlington y padre de Les Arlington. Usando el video para reconstruir la cronología, hemos proporcionado las coordenadas del lugar donde se cree que Kass se esconde actualmente. Se sospecha que Kass es responsable de una larga lista de asesinatos, siendo estos dos los más recientes. Recomendamos traer solo a personas altamente capacitadas para intentar minimizar el número de víctimas. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes. Si bien contamos con personal de seguridad en el lugar, estamos buscando contratar personal adicional para repeler cualquier ataque. Como contratista, desconozco su experiencia trabajando en equipo, pero no quiero oír hablar de "fuego amigo", ya que esto podría generar problemas. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Captura de Maltrox Arlington, líder de la pandilla de Arlington.</v>
+        <v> Evaluación del trabajo de seguridad</v>
       </c>
     </row>
     <row r="323" xml:space="preserve">
       <c r="A323" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado en el espacio. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Maltrox Arlington ha estado manteniendo un perfil bajo últimamente, pero creemos que ha salido de su escondite. Una patrulla estaba reabasteciendo combustible en una estación cuando una de sus naves fue potenciada. Maltrox es el sospechoso más probable. Aunque el registro de la nave estuvo desactivado temporalmente, hemos podido rastrear su firma cuántica y le hemos facilitado las coordenadas. La banda de Arlington, criminal de tercera generación, ha estado bajo el liderazgo de Maltrox durante los últimos seis años. Tenga en cuenta que se trata de un objetivo inteligente, agresivo y muy peligroso. Cuantos más recursos pueda aportar, mayores serán las probabilidades de que logremos capturar a Maltrox de una vez por todas. Está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personal cualificado para colaborar en labores de seguridad en la zona. Hemos determinado que usted posee las habilidades necesarias para ofrecerle un contrato de prueba inicial. Colaborará con Crusader Security para hacer frente a un pequeño grupo hostil que ha estado realizando amenazas contra ~mission(Location|Address). Tenga en cuenta que ya contamos con personal de seguridad en el lugar, por lo que deberá tener cuidado con el fuego amigo. Tras la finalización satisfactoria de este contrato, podrá solicitar cualquier otro puesto de seguridad que surja en el futuro. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Idris robado por una banda de Arlington</v>
+        <v> Reevaluación del trabajo de seguridad</v>
       </c>
     </row>
     <row r="325" xml:space="preserve">
       <c r="A325" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO Parece que la segunda vez es la vencida para la banda de Arlington. Después de un intento fallido, la familia criminal recientemente fugada ha logrado robar un Idris de un astillero. Ahora sabemos para qué eran el láser de minería y la biometría que robaron. Dado que tuvimos tanto éxito capturándolos la primera vez, Eckhart Security ha recibido la orden de arresto de la banda. Esto requerirá una potencia de fuego considerable para derribar una nave capital de esta capacidad. Usted está autorizado a usar la fuerza que sea necesaria para rastrear el Idris y neutralizar a la banda. El pago se emitirá al completar con éxito el contrato y se ajustará según la evaluación final de su calificación de efectividad en combate y la de su equipo. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">¡Felicidades! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de seguridad. Con un poco de esfuerzo y dedicación, esperamos que puedas superar cualquier problema de rendimiento anterior. Sin embargo, para reevaluar tu idoneidad, nos gustaría que ayudaras a Crusader Security a lidiar con un grupo de delincuentes que ha estado realizando amenazas contra ~mission(Location|Address). Ahora bien, dado que has tenido problemas de rendimiento en el pasado, te recuerdo que el fuego amigo no será tolerado. Una vez que completes con éxito esta prueba, se restablecerá tu elegibilidad y podrás volver a solicitar trabajo de seguridad con Crusader. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Se emite la orden de compra grupal.</v>
+        <v> Despejemos el nido criminal</v>
       </c>
     </row>
     <row r="327" xml:space="preserve">
       <c r="A327" t="str" xml:space="preserve">
-        <v xml:space="preserve"> TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO En relación con un delito cometido conjuntamente, se ha emitido una orden de arresto grupal para: ~mission(Target1) ~mission(Target2) ~mission(Target3) Actualmente se cree que ya no viajan juntos para evadir la captura y que pronto podrían huir del sistema. Debería considerar seriamente reclutar ayuda adicional para ejecutar todas las órdenes de arresto en el plazo limitado. Está autorizado a usar la fuerza que sea necesaria para neutralizar a los objetivos. El pago se emitirá al completar con éxito el contrato cuando todos los objetivos hayan sido neutralizados en el tiempo asignado. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) se está utilizando actualmente como base de operaciones para numerosas actividades ilegales. Para acabar con este "nido de delincuentes", buscamos un contratista para que se dirija al lugar y elimine a todos los elementos hostiles. Por la fuerza si es necesario. Cabe mencionar que, a veces, bandas como esta reclutan civiles para que trabajen para ellas, a menudo mediante coacción. Es obvio, pero si ven a algún civil, deben protegerlo. Crusader Security no puede permitir que uno de sus contratistas ande disparando indiscriminadamente contra la gente. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v> ¿Necesitas una salida?</v>
+        <v> Fin de la ocupación de Nine Tails en Orison</v>
       </c>
     </row>
     <row r="329" xml:space="preserve">
       <c r="A329" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. Todavía no hemos tenido la oportunidad de trabajar juntos, pero estoy en un aprieto y necesito a alguien más. No gratis, por supuesto. Me gusta el intercambio. Uno de mis socios, que estuvo cumpliendo condena en Klescher, debía traerme un chip de datos, pero luego dejó de dar señales de vida. Supongo que está muerto, pero aquí está el trato: si terminas su trabajo, borro tu historial delictivo. No está mal, ¿verdad? Tu predecesor planeaba usar unos túneles viejos para escapar. Dio a entender que no eran precisamente fáciles de acceder, pero confío en que podrás resolverlo. Supongo que encontrarás su cuerpo por ahí y, si tenemos suerte, todavía tendrá el chip. Una vez que lo consigas, termina de escapar como puedas. Luego, tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me sorprendería que te los encontraras. Después de obtener los datos y validarlos, borraré tu historial delictivo. Entonces podrás disfrutar de tu recién descubierta libertad. Si lo haces bien, tal vez tenga un trabajo más lucrativo para ti en el futuro.</v>
+        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención, las fuerzas de Nine Tails han tomado el control de varias plataformas comerciales cerca de Orison. Usando un Inversor de Identidad Amigo o Enemigo (IFFI), se han apoderado del espacio aéreo restringido que rodea las plataformas y solo las naves afiliadas a Nine Tails pueden acceder al área. Esto ha obstaculizado gravemente los intentos iniciales de Crusader Security para retomar las plataformas. Por lo tanto, Crusader ha solicitado a las fuerzas de CDF que ayuden a apagar el inversor y eliminar toda presencia hostil. Se anima a todos los voluntarios de CDF disponibles a brindar apoyo. Información adicional: * Mientras el inversor está activo y el espacio aéreo inaccesible, CDF ha logrado tomar el control de un sistema de transporte local y redirigirlo para acceder a la Plataforma Solanki sin el conocimiento de Nine Tails. Los voluntarios deberán dirigirse a la Sala de Exposiciones de Crusader Industries en la Plataforma Comercial y llegar a la azotea para encontrar el transporte que viajará a las plataformas ocupadas. * Se cree que el IFFI está ubicado en un contenedor de almacenamiento cerrado en una barcaza de carga atracada en el Centro de Administración central. * Los códigos de acceso para el contenedor IFFI están en posesión del líder de las fuerzas de Nine Tails, Mendo Ren. * La experiencia previa con Mendo Ren indica que es improbable que muestre su rostro y se arriesgue a ser capturado. Sin embargo, si todos sus lugartenientes son neutralizados, creemos que no tendrá más remedio que tomar el mando de las fuerzas en persona y darnos la oportunidad de recuperar los códigos. * Además del sistema de transporte, Crusader Security nos ha informado que hay varios vehículos en las plataformas disponibles para que las CDF los requisen. Estos vehículos serán la única forma de llegar al Centro Administrativo. NOTA: Si todos los vehículos dentro del espacio aéreo restringido son destruidos antes de que se pueda apagar el inversor, entonces no habrá forma de llegar a la barcaza de carga y las CDF se verán obligadas a retirarse. * Las plataformas están protegidas por armas antiaéreas controladas por Nine Tails. Tenga en cuenta que la SAIC Rowena Dulli de Advocacy es la agregada oficial de las CDF y dirigirá la operación.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ayudémonos mutuamente</v>
+        <v>Doble toque</v>
       </c>
     </row>
     <row r="331" xml:space="preserve">
       <c r="A331" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. Oí que acabaste en Klescher, lo cual es una verdadera lástima. Pero en realidad podría ser un día de suerte para ambos. En resumen, tenía a alguien sacando un chip de datos de la prisión, pero nunca volvió a contactarme. Sé con certeza que no ha salido de las instalaciones, así que creo que algo le pudo haber pasado. Aunque es trágico, el trabajo debe continuar. Si puedes conseguir el chip y terminar el trabajo, puedo borrar tu historial criminal. ¿Qué dices? Claro, no sé exactamente hasta dónde llegó, pero puedo decirte que la prisión tiene toda una red de túneles ocultos que mi tipo planeaba usar para escapar. Supongo que su cadáver se está pudriendo por ahí. Cuando encuentres el cuerpo, espero que el chip todavía esté con él. Cuando lo tengas, termina de escapar y tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Una advertencia: ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me extrañaría que te los encontraras. Cuando tenga los datos, borraré tu historial delictivo y listo, quedarás libre de toda sospecha. Lo que hagas después es decisión tuya.</v>
+        <v xml:space="preserve"> Se ha puesto precio a las cabezas de ~mission(TargetName) y ~mission(TargetName2). Si bien tener que alcanzar dos objetivos no es tan extraño, el cliente quiere enviar un mensaje muy específico, así que necesitan que ambos objetivos sean alcanzados en el mismo instante. Los créditos adicionales compensarán las molestias. Y, lamentablemente, como no viajan juntos, es obvio que para lograrlo necesitarás ayuda. Asegúrate de llevar gente de confianza que pueda manejar más de una nave, ya que se sabe que los objetivos viajan con refuerzos.</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Violación y robo</v>
+        <v> Dos en la cabeza</v>
       </c>
     </row>
     <row r="333" xml:space="preserve">
       <c r="A333" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. Los Nueve Colas tienen un pequeño problema. Resulta que tienen un pequeño negocio paralelo en el tráfico clandestino de órganos. Un tema que prefiero evitar, pero un trabajo es un trabajo, ¿no? Parece que una de sus carnicerías móviles a bordo del 'October Rising' fue asaltada por seguridad privada mientras trabajaba. Ahora los Nueve Colas están dispuestos a romper lazos con el barco y su tripulación (que probablemente ya estén todos muertos), pero necesitan que les extraigan una caja en particular. Supongo que era un pedido especial o algo así. En fin, suban al October Rising, consigan el paquete y salgan. La seguridad sigue por ahí, así que tengan cuidado y tal vez traigan a algunos amigos, pero recuerden, su prioridad es el paquete. Si quieren ahorrarse problemas, también podrían apagar la zona desactivando la antena de comunicaciones más cercana si quieren evitar que los arresten por, ya saben, matar a un montón de guardias de seguridad. Pero bueno, hagan lo que quieran. Cuando salgas, deja el paquete en la clínica de Grim HEX y yo me encargaré del pago. Pan comido, Ruto.</v>
+        <v xml:space="preserve">Se trata de dos objetivos que deben ser eliminados simultáneamente. Al parecer, el cliente teme que, si no se eliminan juntos, uno de ellos se vuelva loco y busque venganza. Se les conoce como ~mission(TargetName) y ~mission(TargetName2). Reúne a tu equipo, divide y vencerás. Asegúrate de que cada miembro tenga las habilidades necesarias, porque estos dos tienen fama de ser muy hábiles en combate y, sin duda, no estarán solos. Prepárate para que te den problemas.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>consigue los productos</v>
+        <v> Eliminación coordinada</v>
       </c>
     </row>
     <row r="335" xml:space="preserve">
       <c r="A335" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, hace poco escuché información confidencial de que ~mission(location|address) recibió material confidencial de gran interés para un conocido mío. Es tan interesante que están dispuestos a pagar para que alguien asalte las instalaciones, se apodere del material y lo entregue en ~mission(DropOff1|address). Supongo que habrá mucha seguridad, que probablemente opondrá resistencia, así que llevaría un par de armas. Se rumorea que el material confidencial se entregó en un envío junto con otras cosas y ahora se encuentra almacenado en la bóveda automatizada de las instalaciones. Los oficiales de seguridad de alto rango llevan tabletas con códigos de acceso a la bóveda. Tendrás que conseguir una tableta antes de usar la cinta transportadora para recuperar las cajas. Si necesitas un incentivo adicional, he visto el manifiesto y puedo confirmar que las otras cajas almacenadas en las instalaciones son de primera calidad. A mi cliente no le importa lo que les pase, así que puedes hacer lo que quieras con ellas. Si lo gestionas bien, esas cajas adicionales podrían suponer una buena ganancia extra, además de la tarifa de envío.</v>
+        <v xml:space="preserve">Me ha llegado una misión interesante. Necesito eliminar a dos objetivos distintos: ~mission(TargetName) y ~mission(TargetName2). El problema es que si uno se entera de que el otro ha sido atacado, se esconderá. No puedo arriesgarme a perder a ninguno. Requerirá una coordinación considerable, pero quiero que los elimines a ambos al mismo tiempo. Y como no puedes estar en dos sitios a la vez, tendrás que encontrar a alguien de confianza que te ayude. Por suerte, mi información indica que ambos objetivos viajarán solos. Eso debería facilitarte las cosas.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>suministro limitado</v>
+        <v> Doble eliminación</v>
       </c>
     </row>
     <row r="337" xml:space="preserve">
       <c r="A337" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Parece que hay un nuevo advenedizo en el sector que no ha estado pagando lo que le corresponde. Para darles una lección, mi cliente quiere que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Los matones de bajo nivel que tienen allí probablemente armarán un escándalo e intentarán detenerte. Haz lo que quieras con ellos, pero lo más importante es deshacerte de la droga.</v>
+        <v xml:space="preserve">Tengo un contrato para eliminar a dos jóvenes problemáticos que han estado causando problemas. Tiene que ser una operación limpia y simultánea, o podrían causar aún más problemas. En resumen, necesitarás ayuda. Tanto ~mission(TargetName) como ~mission(TargetName2) saben defenderse, y sus compañeros de vuelo tampoco son ninguna broma. Cada uno de ellos estará protegido por varias naves.</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v> liquidación de inventario</v>
+        <v> Divide y vencerás</v>
       </c>
     </row>
     <row r="339" xml:space="preserve">
       <c r="A339" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Un cliente mío está intentando negociar un acuerdo, pero no está teniendo mucha suerte. La otra parte cree tener toda la ventaja porque tiene un gran inventario a su disposición. Para facilitar las negociaciones, necesito que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Debería advertirte que el sitio está protegido por gente muy peligrosa, así que llegar al alijo va a ser complicado, pero confío en que encontrarás la manera.</v>
+        <v xml:space="preserve"> Normalmente, enfrentarse a ~mission(TargetName) y ~mission(TargetName2) juntos sería demasiado. Ambos son excelentes en combate aéreo y sus tripulaciones son casi igual de buenas. Sin embargo, recientemente se separaron —no se sabe por qué— y por el momento vuelan por separado. Alguien cree que esta podría ser la mejor oportunidad para eliminarlos. Reúna personal de confianza y planifique un ataque simultáneo contra ambos objetivos. Es demasiado peligroso arriesgar la vida de uno de ellos tras un ataque tan directo.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v> Agotado</v>
+        <v>Combinación de uno-dos</v>
       </c>
     </row>
     <row r="341" xml:space="preserve">
       <c r="A341" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de mis clientes se ha enfadado al enterarse de que alguien está invadiendo su territorio. Ahora, en lugar de optar por la vía tradicional de matar a algunas personas y armar un escándalo, ha decidido enviar un mensaje diferente. Vas a ir a ~misión(Ubicación|Dirección) y destruir toda la droga del lugar. Claro que, si alguien quiere pelear contigo, puedes defenderte, pero lo más importante es deshacerte de la droga.</v>
+        <v xml:space="preserve"> Hay otro par que deben ser eliminados: ~mission(TargetName) y ~mission(TargetName2). Han estado desaparecidos durante algunos días, pero acaban de aparecer. Si no los eliminamos ahora, no estoy seguro de que tengamos otra oportunidad. Necesitas reclutar a un compañero para asegurarte de que ambos objetivos sean alcanzados al mismo tiempo. En cuanto a su resistencia, se sabe que ~mission(TargetName) trae a un amigo para que le cubra las espaldas, y sospecho que ~mission(TargetName2) hará lo mismo.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v> demasiados cocineros</v>
+        <v> Combinación mortal</v>
       </c>
     </row>
     <row r="343" xml:space="preserve">
       <c r="A343" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Un cliente está siendo superado por un nuevo competidor y busca sabotear el negocio. Dirígete a ~mission(Location|Address) y elimina a todos los civiles que trabajan allí. Haz lo que quieras con los matones armados que custodian a los trabajadores, pero recuerda que no son la prioridad.</v>
+        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Dos operadores de alto nivel que recientemente decidieron atacar a su jefe. Cada uno viaja con una pequeña armada de élite y se adentra en territorio ajeno. Tú, junto con quien reclutes para que te ayude, los eliminarás, y ambos deben hacerlo simultáneamente para que no puedan reagruparse.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v> Vive y deja que un contratista independiente se vengue.</v>
+        <v> Solicitud de asistencia para el buque</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v xml:space="preserve">Todo el mundo guarda rencor, ¿no? O sea, cuando te pillan cometiendo un delito, entiendo que te moleste un poco, pero así son las cosas, ¿no?</v>
+        <v> Solicitud de asistencia para el buque</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v> Es difícil encontrar buena ayuda.</v>
-      </c>
-    </row>
-    <row r="347" xml:space="preserve">
-      <c r="A347" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Conozco a alguien que quiere montar un negocio, pero le cuesta mucho contratar a los trabajadores cualificados que necesita. Resulta que encontró al equipo perfecto en ~mission(Location|Address), pero sus jefes no les dejan ir. Incluso contrataron guardias armados adicionales para asegurarse. Lo que quiero que hagas es ir allí y acabar con todos los guardias, asegurándote de que los trabajadores salgan ilesos.</v>
+        <v>Soporte al cliente bajo ataque</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v> Soporte al cliente bajo ataque</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v> haciendo un desastre</v>
-      </c>
-    </row>
-    <row r="349" xml:space="preserve">
-      <c r="A349" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Esto es un poco agresivo para mi gusto, pero los créditos son créditos, ¿no? Tengo un cliente que busca a alguien muy motivado para ir a ~misión(Ubicación|Dirección) y matar a todos los que estén allí. Básicamente, empieza a disparar y no pares. Te pagarán cuando el lugar esté despejado.</v>
+        <v> Repeler naves de cuchillas destrozadas</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v> Repeler naves de cuchillas destrozadas</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v> coger y llevar</v>
-      </c>
-    </row>
-    <row r="351" xml:space="preserve">
-      <c r="A351" t="str" xml:space="preserve">
-        <v xml:space="preserve">Esta misión es perfecta para alguien como tú. Hay un paquete retenido en ~mission(Location|Address) y necesito que lo lleves a ~mission(Destination|Address). Hay un pequeño detalle que debes saber: habrá muchísima seguridad allí. Pero seguro que todo irá bien. :)</v>
+        <v> Detengan el ataque contra un cliente de alto perfil.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v> Detengan el ataque contra un cliente de alto perfil.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v> Tras el desastre</v>
-      </c>
-    </row>
-    <row r="353" xml:space="preserve">
-      <c r="A353" t="str" xml:space="preserve">
-        <v xml:space="preserve">La fortuna nos sonríe una vez más. Acabo de enterarme de una batalla cerca de ~mission(Location) que acaba de tener lugar lejos de las miradas indiscretas de cualquier sistema de comunicaciones entrometido, y aún no se han enviado refuerzos de ninguna de las fuerzas involucradas. Esto significa que hay una oportunidad para que un alma emprendedora saquee el cementerio. Me gustaría ofrecer esta oportunidad a todos mis contactos de confianza. Cualquiera que esté interesado puede obtener la ubicación... por el precio adecuado. Las coordenadas se proporcionarán una vez que acepte el contrato y permanecerán disponibles hasta que decida rescindirlo. Por supuesto, la rapidez será esencial, ya que no solo se enfrentará a la posible competencia de otros rescatadores, sino también a la inminente posibilidad de que lleguen refuerzos para inspeccionar el campo de batalla. Si aún lo duda, recuerde: la fortuna favorece a los audaces. -cd</v>
+        <v> Ataque de hoja rota grave</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v> Ataque de hoja rota grave</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
-      </c>
-    </row>
-    <row r="355" xml:space="preserve">
-      <c r="A355" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para ayudar en la detención de ~mission(TargetName) de ~mission(Location|Address). Somos conscientes de que puede haber civiles en el lugar, así que tenga cuidado con el posible fuego cruzado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. • Asegurar que no haya bajas civiles. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Encuentro de alto riesgo con un barco</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v> Encuentro de alto riesgo con un barco</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v xml:space="preserve"> Evaluación de recompensas activas</v>
-      </c>
-    </row>
-    <row r="357" xml:space="preserve">
-      <c r="A357" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que nos ayudara a capturar a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, su principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Golpe de hoja destrozada</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v> Golpe de hoja destrozada</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v xml:space="preserve"> Reevaluación activa de recompensas</v>
-      </c>
-    </row>
-    <row r="359" xml:space="preserve">
-      <c r="A359" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO Aunque tu desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerte una oportunidad para redimirte. Para reevaluar tus habilidades, nos gustaría que detuvieras a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, tu principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar tu propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazadores de Recompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Defensa extremadamente peligrosa</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v> Defensa extremadamente peligrosa</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (ERT)</v>
-      </c>
-    </row>
-    <row r="361" xml:space="preserve">
-      <c r="A361" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo extremo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo extremo generalmente pilota una nave de clase subcapital, tiene varios aliados fuertemente armados y se espera que sea muy difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Necesidades del cliente Apoyo en combate</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v> Necesidades del cliente Apoyo en combate</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (HRT)</v>
-      </c>
-    </row>
-    <row r="363" xml:space="preserve">
-      <c r="A363" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de alto riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de alto riesgo generalmente pilota una nave grande con tripulación múltiple, tiene varios aliados conocidos y se espera que sea difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Detengan el ataque mortal al barco</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v> Detengan el ataque mortal al barco</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v> Evaluación de recompensas activas</v>
-      </c>
-    </row>
-    <row r="365" xml:space="preserve">
-      <c r="A365" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra lista actual. Para evaluar sus habilidades, nos gustaría que nos ayudara en la detención de ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Detengan el ataque de la hoja destrozada</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v> Detengan el ataque de la hoja destrozada</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (LRT)</v>
-      </c>
-    </row>
-    <row r="367" xml:space="preserve">
-      <c r="A367" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de bajo riesgo generalmente pilota una nave monoplaza, tiene varios aliados conocidos y debería ser fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Guardar envío</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v> Guardar envío</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
-      </c>
-    </row>
-    <row r="369" xml:space="preserve">
-      <c r="A369" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo moderado ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo moderado generalmente pilota una pequeña nave multitripulación, tiene varios aliados conocidos y puede ser un poco difícil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Equipo de protección ejecutiva</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v> Equipo de protección ejecutiva</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v> Reevaluación de la detención de recompensas</v>
-      </c>
-    </row>
-    <row r="371" xml:space="preserve">
-      <c r="A371" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. Para reevaluar sus habilidades, nos gustaría que detuviera a ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Los clientes VIP necesitan protección.</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v> Los clientes VIP necesitan protección.</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (VLRT)</v>
-      </c>
-    </row>
-    <row r="373" xml:space="preserve">
-      <c r="A373" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de muy bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de muy bajo riesgo generalmente pilota una nave monoplaza, tiene pocos aliados conocidos y debería ser relativamente fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Se necesita personal de seguridad con experiencia.</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v> Se necesita personal de seguridad con experiencia.</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v> Eliminar fuerza hostil</v>
-      </c>
-    </row>
-    <row r="375" xml:space="preserve">
-      <c r="A375" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos rápida y seguramente en la eliminación completa del grupo de forajidos que ha tomado temporalmente el control de ~mission(Location) en ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los miembros de la fuerza hostil de forajidos; usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v> Se necesita operador de primer nivel.</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v> Se necesita operador de primer nivel.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v> Capturar recompensa: ~misión(Nombre del objetivo) (HRT)</v>
-      </c>
-    </row>
-    <row r="377" xml:space="preserve">
-      <c r="A377" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa en ~mission(Location|Address), y creemos que finalmente podrían salir de su escondite si sus fuerzas que atacan ~mission(Location) se enfrentan a una resistencia lo suficientemente fuerte. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a los asociados criminales de ~mission(TargetName) cerca de ~mission(Location) para atraer al objetivo a campo abierto. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Detalle de protección de bajo riesgo</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Detalle de protección de bajo riesgo</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v> Recompensa asegurada: ~misión(Nombre del objetivo) (VHRT)</v>
-      </c>
-    </row>
-    <row r="379" xml:space="preserve">
-      <c r="A379" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa que se ha extendido por todo ~mission(Location|Address). Esperamos que finalmente pueda sacarlos de su escondite si enfrenta a sus fuerzas en varios puntos de ataque diferentes. Con sus números suficientemente debilitados, ~mission(TargetName|Last) probablemente correrá el riesgo de ser expuesto y usted podrá enfrentarlos directamente. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Enfrentar a los asociados criminales de ~mission(TargetName) para hacer que el objetivo salga a la luz. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Se requiere protección adicional. Alto riesgo.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v> Se requiere protección adicional. Alto riesgo.</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
-      </c>
-    </row>
-    <row r="381" xml:space="preserve">
-      <c r="A381" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName) en ~mission(Location|Address). Fueron vistos recientemente cerca de ~mission(Location) y se cree que todavía están en esa área. Si bien puede haber otros criminales activos en el sitio, su enfoque principal debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v> Es hora de dar una lección</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v> Es hora de dar una lección</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v> Ajuste de la población de vida silvestre</v>
-      </c>
-    </row>
-    <row r="383" xml:space="preserve">
-      <c r="A383" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para eliminar varias criaturas de diversas especies. Esta es una medida preventiva para asegurar que el tamaño de su población no aumente más allá de los parámetros aceptables. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar la especie objetivo en ~misión(Ubicación). • Usar la fuerza según sea necesario para eliminar a los animales. REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su Diario.</v>
+        <v> Emboscada engañosa</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v> Emboscada engañosa</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v> Control de vida silvestre: ~misión(Criatura)</v>
-      </c>
-    </row>
-    <row r="385" xml:space="preserve">
-      <c r="A385" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para reducir el número de ~mission(Creature) en estado salvaje a parámetros aceptables. Su población está aumentando demasiado rápido, y la reducción de algunos de sus números ayudará a garantizar que la situación no se salga de control. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar a ~mission(Creature) en ~mission(Location). • Usar la fuerza según sea necesario para eliminar a ~mission(Creature). REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio Para obtener más información sobre los animales en cuestión, consulte "The Guide to Stanton Wildlife" en su Diario.</v>
+        <v> Nueva oportunidad: ataque de emboscada</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v> Nueva oportunidad: ataque de emboscada</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v> Proteger la ubicación y entregar materiales confidenciales.</v>
-      </c>
-    </row>
-    <row r="387" xml:space="preserve">
-      <c r="A387" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional de seguridad para una operación de recuperación en ~mission(Location). La ubicación está actualmente bajo ataque y las fuerzas de seguridad en el sitio no responden y se presumen muertas. Creemos que los materiales confidenciales entregados recientemente a las instalaciones para custodia temporal fueron el objetivo del ataque. Su enfoque principal será recoger esas cajas y entregarlas en un lugar seguro. Por razones de seguridad, los materiales confidenciales se entregaron como parte de un envío más grande y se aseguraron en la bóveda automatizada. Los materiales tienen códigos de recuperación únicos que deben ingresarse en el teclado en la cinta transportadora de paquetes. Los protocolos exigen que solo los oficiales de seguridad de alto rango pueden llevar un datapad que contenga un código, pero dada la situación volátil, no podemos garantizar que los Nine Tails no se hayan apoderado de ellos. Una vez asegurados, entregue todos los materiales confidenciales a ~mission(dropoff1) para el pago. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|address). • Usar la fuerza según sea necesario para recoger los materiales confidenciales. • Entregar los materiales confidenciales a ~mission(dropoff1|address). REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate. • Acceso a una nave espacial con capacidad de transporte de carga. • Disponibilidad para despliegue inmediato. REQUISITOS DESEABLES • Experiencia en técnicas de desescalada rápida de hostilidades. • Experiencia en el transporte de carga importante.</v>
+        <v> Lanzar ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v> Lanzar ataque sorpresa</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Proteger la ubicación contra amenazas menores</v>
-      </c>
-    </row>
-    <row r="389" xml:space="preserve">
-      <c r="A389" t="str" xml:space="preserve">
-        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra cualquier amenaza menor. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+        <v> Emboscada sumamente peligrosa</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v> Emboscada sumamente peligrosa</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v> Proteger la ubicación contra amenazas moderadas</v>
-      </c>
-    </row>
-    <row r="391" xml:space="preserve">
-      <c r="A391" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+        <v> Ajustar cuentas</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v> Ajustar cuentas</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v> Proteja la ubicación contra amenazas graves.</v>
-      </c>
-    </row>
-    <row r="393" xml:space="preserve">
-      <c r="A393" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles graves. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+        <v> Emboscada peligrosa</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v> Emboscada peligrosa</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v> Sitio libre de contrabando</v>
+        <v> Sitio seguro</v>
       </c>
     </row>
     <row r="395" xml:space="preserve">
       <c r="A395" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir el contrabando que se almacena allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de contrabando; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de Ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente ha interceptado comunicaciones entre miembros de pandillas y ha descubierto que están planeando un ataque en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Ahora necesitan nuestra ayuda para asegurar que el ataque no tenga éxito. Buscamos un contratista que pueda defender la ubicación de esta ofensiva. No tenemos detalles sobre los delincuentes, pero dudamos que sean muy hábiles si nuestro cliente interceptó sus comunicaciones tan fácilmente. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v> Sitio libre de narcóticos</v>
+        <v> Repeler a los asaltantes</v>
       </c>
     </row>
     <row r="397" xml:space="preserve">
       <c r="A397" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir los narcóticos que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de narcóticos; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Se avecina un grave problema para uno de nuestros clientes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Han sido advertidos de que un grupo de forajidos altamente capacitados tiene la mira puesta en tomar y ocupar esa ubicación. Hemos sido contratados para asegurarnos de que eso no suceda. Necesitamos un contratista para desplegarse en la ubicación de inmediato. Según la información proporcionada por el cliente, esto no será fácil. Le recomendamos encarecidamente que traiga aliados y muchos suministros para ayudar a repeler el inminente ataque. El pago se emitirá una vez completado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v> Sitio libre de drogas</v>
+        <v> Proteger ubicación</v>
       </c>
     </row>
     <row r="399" xml:space="preserve">
       <c r="A399" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir las drogas que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de drogas; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de la ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido información de que delincuentes tienen la mira puesta en atacar &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Nuestro cliente está preocupado por la inminencia del ataque y solicitó que se despliegue seguridad en el sitio de inmediato. Si está interesado y disponible, reúna todos los suministros y el apoyo que pueda necesitar y diríjase a la ubicación lo antes posible. El pago se emitirá una vez completado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v> Defender a los ocupantes</v>
+        <v> Expulsar a los forajidos</v>
       </c>
     </row>
     <row r="401" xml:space="preserve">
       <c r="A401" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudar de manera rápida y segura al equipo de seguridad estacionado en ~mission(Location|Address) a proteger el sitio contra amenazas hostiles. Tenga en cuenta que cualquier fuego amigo, accidental o de otro tipo, no será tolerado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar al equipo de seguridad local a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Desalojo de ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente está enviando comunicaciones frenéticas indicando que una de sus ubicaciones está siendo atacada. Necesitamos un contratista que pueda dirigirse rápidamente a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y despejar la ubicación de actores hostiles. Según el personal en el sitio, los delincuentes se encuentran actualmente atrincherados cerca de &lt;EM4&gt;~mission(Location)&lt;/EM4&gt;. Acérquese con precaución y esté preparado para usar fuerza letal si los delincuentes se resisten a ser desalojados. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v> Evaluación de contratistas de seguridad</v>
-      </c>
-    </row>
-    <row r="403" xml:space="preserve">
-      <c r="A403" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita profesionales de seguridad nuevos, calificados y orientados a los detalles para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que ayudara a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v> Apoyo en combate: ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v> Apoyo en combate: ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v> Reevaluación de contratistas de seguridad</v>
-      </c>
-    </row>
-    <row r="405" xml:space="preserve">
-      <c r="A405" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. En un esfuerzo por reevaluar sus habilidades, microTech Protection Services desea que ayude a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza según sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v> Solicitar ayuda</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v> Solicitar ayuda</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v> Desalojar a los ocupantes ilegales</v>
+        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="407" xml:space="preserve">
       <c r="A407" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos de manera rápida y segura en la eliminación completa de ocupantes ilegales que han tomado temporalmente el control de ~mission(Location|Address). Tenga en cuenta que nuestra inteligencia muestra que hay trabajadores civiles en el sitio. Dado que su conexión con la pandilla no está clara, deben ser considerados no combatientes. No se tolerará ninguna acción hostil hacia ellos. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los ocupantes hostiles que se encuentren dentro del sitio; usando la fuerza si es necesario. • Garantizar la seguridad de cualquier civil que pueda estar en el sitio. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido información procesable sobre una recompensa peligrosa, que ha resultado ser extremadamente escurridiza. &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; fue visto con un contingente dedicado de asociados conocidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Estamos buscando un contratista listo y dispuesto a ejecutar esta recompensa antes de que desaparezca de nuevo. Basándonos en intentos anteriores de aprehender a este criminal, hay una buena probabilidad de que &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; intente evitar una confrontación directa y, en su lugar, envíe a sus aliados a enfrentarlo. Creemos que neutralizar estas fuerzas protectoras y destruir la red de seguridad que proporcionan es la mejor manera de obligar a &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; a enfrentarse directamente a usted. Prepárese para enfrentarse a una fuerza significativa y experimentada. Le recomendamos que planifique en consecuencia. El pago se efectuará una vez finalizado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v> URGENTE: Embarque en curso</v>
+        <v>Recompensa de caza: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="409" xml:space="preserve">
       <c r="A409" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un cliente ejecutivo nos acaba de informar que su 890 Jump fue interceptada en ~mission(Location) y abordada por forajidos. Prefieren que el asunto se resuelva de forma privada debido a la naturaleza confidencial de los datos confidenciales almacenados a bordo. Su prioridad será eliminar a todos los forajidos lo antes posible para que se pueda enviar un equipo de recuperación y devolver la nave al propietario. Cuanto más tiempo tengan los forajidos el control de la nave, mayor será la probabilidad de que se pierda. Le recomiendo que consiga un equipo para esta misión para agilizar el proceso. Tenga en cuenta que, gracias a un pequeño contingente de personal de seguridad que permaneció a bordo, todos los miembros supervivientes de la tripulación pudieron escapar en una nave de escape. Se desconoce el estado actual del resto del personal de seguridad, pero por si acaso, esté atento a la presencia de aliados cuando se enfrente a los hostiles. En segundo lugar, si es posible, el cliente está muy interesado en evitar el robo de los datos mencionados. Si logra detener el robo de sus almacenes de datos confidenciales antes de que se transmitan, recibirá una generosa bonificación. Como es lógico, este es un cliente al que me gustaría mantener muy satisfecho. Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido un aviso sobre la ubicación de una recompensa de alto perfil. Los informes de inteligencia han rastreado a &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Necesitamos un contratista que se dirija rápidamente hacia esa dirección antes de que el objetivo desaparezca. Según los últimos informes, fueron vistos por última vez cerca de &lt;EM4&gt;~mission(Location)&lt;/EM4&gt;. Venga preparado para usar fuerza letal si &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; se resiste a la detención. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Asignación de recompensa: ~misión(Nombre del objetivo) (HRT)</v>
+        <v> Evaluación de contratistas de seguridad</v>
       </c>
     </row>
     <row r="411" xml:space="preserve">
       <c r="A411" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, tengo un contrato para ti que requiere un poco más de estrategia de lo habitual. Un criminal de alto nivel llamado ~mission(TargetName) se esconde con un gran contingente de forajidos en ~mission(Location|Address). Nuestra información sugiere que las fuerzas de ~mission(TargetName|Last) probablemente actuarán como línea defensiva para proteger a su jefe. Supongo que tendrás que enfrentarte a ellos antes de poder acceder a ~mission(TargetName|Last). Dicho esto, no quiero que dispares indiscriminadamente. A veces, estos forajidos mantienen a civiles cerca y deben ser tratados como no combatientes. Mucha suerte, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Juicio - Defensa Ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Eckhart Security está buscando profesionales de seguridad calificados para unirse a sus filas. Si cree que tiene la disposición y la experiencia para manejar una amplia variedad de contratos de seguridad, lo alentamos a demostrar su competencia ejecutando el contrato a continuación. Los delincuentes han estado molestando a uno de nuestros clientes atacando a su personal y operaciones. Basándonos en el patrón establecido por ataques anteriores, creemos que estas fuerzas hostiles atacarán &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; a continuación. Complete con éxito este contrato para recibir el pago y más oportunidades de trabajo de Eckhart Security. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v> Misión de recompensa por fuga: ~mission(Nombre del objetivo)</v>
+        <v>Reevaluación de contratistas de seguridad</v>
       </c>
     </row>
     <row r="413" xml:space="preserve">
       <c r="A413" t="str" xml:space="preserve">
-        <v xml:space="preserve">El delincuente convicto ~mission(TargetName) se ha fugado de un centro de rehabilitación local y Northrock ha sido contratado para devolverlo a prisión. En mi experiencia, los presos fugados no suelen rendirse pacíficamente, así que utilicen cualquier método posible para encontrarlo y someterlo. Podría ser conveniente vigilar los lugares donde podría intentar borrar sus antecedentes penales. No sería la primera vez que un preso intenta borrar su condena tras fugarse. Buena suerte en la búsqueda, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Prueba - Defender Ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Eckhart Security continúa evaluando posibles nuevos contratistas. Según nuestros registros, usted ya intentó un contrato de prueba. Entendemos lo exigente e impredecible que puede ser este trabajo y nos gustaría darle otra oportunidad de completar un contrato que califique. Si está interesado, preséntese en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; listo para defenderlo de un ataque inminente de delincuentes. Complete con éxito este contrato para recibir el pago y más oportunidades de trabajo de Eckhart Security. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v> Contrato provisional de recompensa por fuga</v>
+        <v> Gestionar la misión (nombre del objetivo) y las fuerzas de apoyo.</v>
       </c>
     </row>
     <row r="415" xml:space="preserve">
       <c r="A415" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, mi nombre es Braden Corchado y soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera en el sistema Stanton. Puede que ya te haya contactado, pero nos esforzamos por contactar a cualquier persona que cumpla con nuestros altos estándares y animarla a completar un contrato temporal. No hay mejor opción que ser contratista de Northrock. Tenemos una sólida reputación por ofrecer trabajo desafiante e interesante con una remuneración superior a la de muchos de nuestros competidores en el sistema. Para ser aprobado, deberás capturar a ~mission(TargetName). Recientemente escapó del centro de detención y tu trabajo consistirá en localizarlo antes de que desaparezca por completo. Un pequeño consejo: es probable que el objetivo intente limpiar su historial. Te recomiendo triangular tu búsqueda entre el centro de detención del que escapó y los lugares donde pueda acceder al sistema de registros. Si lo logras, veremos si podemos ofrecerte más trabajo. Espero tener noticias suyas pronto, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Tenemos un contrato de recompensa de alto nivel listo para ser ejecutado. &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y su equipo fueron identificados ejecutando una incursión en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Si su modus operandi es el correcto, &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; ha aparecido para dar un gran golpe y luego desaparecerá en el éter. No permitamos que eso vuelva a suceder. Se dice que las fuerzas hostiles se han dispersado por la ubicación. Eso hará que rastrear la ubicación precisa de &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; sea difícil. Además, espere que el objetivo actúe a la defensiva cuando sea atacado. En enfrentamientos anteriores, permanecieron ocultos y dirigieron sus fuerzas desde lejos. Recomendamos que se concentre primero en eliminar a sus aliados y obligue a &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; a defenderse. También le aconsejamos que lleve abundante munición e incluso algún tipo de apoyo para evitar ser superado. El pago se realizará al completar el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Contrato provisional de recompensa para fugitivos (reevaluación)</v>
-      </c>
-    </row>
-    <row r="417" xml:space="preserve">
-      <c r="A417" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, sé que ha pasado un tiempo, pero si todavía te interesa trabajar por contrato para Northrock, convencí a la gerencia para que te hicieran una reevaluación. Si logras completar con éxito una misión de recompensa, podemos ver si podemos restituirte tu puesto. Este contrato temporal consiste en localizar al criminal fugado ~mission(TargetName). Haz todo lo posible por encontrarlo antes de que borre su registro en el punto de acceso a la base de datos, o el trabajo será mucho más difícil. Esperamos poder confiar en ti. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v>Contrato de nivel amarillo: Interrupción de operaciones</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v> Contrato de nivel amarillo: Interrupción de operaciones</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v> Detener sospechoso: ~misión(Nombre del objetivo)</v>
+        <v> Contrato de nivel naranja: Destruir infraestructura ilegal</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v> ~misión(Contratista|DescripciónPVPRecompensa)</v>
+        <v> Contrato de nivel naranja: Destruir infraestructura ilegal</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v> Detención provisional del sospechoso</v>
-      </c>
-    </row>
-    <row r="421" xml:space="preserve">
-      <c r="A421" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, espero que no le importe, pero me enteré de su pertenencia al Gremio de Cazadores de Recompensas y quería ponerme en contacto con usted para ver si estaría interesado en colaborar con Northrock Service Group, una de las empresas de seguridad privada mejor valoradas del sistema. Si es así, el primer paso sería completar una detención provisional del sospechoso. No se trata tanto de una evaluación, sino más bien de una oportunidad para asegurarnos de que podemos establecer una buena relación laboral. El sospechoso que busca se conoce como &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;. Se sabe que es particularmente escurridizo, así que puede que tenga un trabajo arduo por delante. Espero tener noticias suyas pronto. Atentamente, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v> Contrato de nivel naranja: Retire los suministros de combustible</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v> Contrato de nivel naranja: Retire los suministros de combustible</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v> Detención provisional de sospechoso (reevaluación)</v>
-      </c>
-    </row>
-    <row r="423" xml:space="preserve">
-      <c r="A423" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola de nuevo, hace tiempo que no hablamos, espero que todo esté bien. Sé que las cosas no terminaron de la mejor manera, pero después de hablarlo con la gerencia, me gustaría ofrecerte una oportunidad para redimirte. Tenías potencial y me da mucha pena que no hayas tenido la oportunidad de demostrar de lo que eres capaz. Completa la misión &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y veremos cómo podemos restituirte en tu puesto. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v> Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v> Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v> Operación de recuperación</v>
-      </c>
-    </row>
-    <row r="425" xml:space="preserve">
-      <c r="A425" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aquí está el trato: un cliente nuestro (que debería haber gastado los créditos extra en una escolta de Northrock) sufrió un ataque a una de sus naves y ahora necesita que lideremos una operación de recuperación de un paquete importante que fue robado. Por suerte, tuvimos un golpe de suerte y pudimos localizar a los responsables en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;. Necesitamos que vayas allí y recuperes el paquete. Podrás identificarlo por su número de serie: &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt;. Supongo que los forajidos van a oponer resistencia, pero recuerda que no son la prioridad. Una vez que tengas el paquete, llévalo de vuelta al cliente en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Una última cosa, asegúrate de llevar una nave con suficiente espacio para carga. No queremos que llegues hasta allí en tu Gladius o lo que sea solo para tener que regresar. Enorgullécenos, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group *RESUMEN DE LA OPERACIÓN DE RECUPERACIÓN* * Recuperar el paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; * Entregar en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;</v>
+        <v> Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v> Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asignación de recompensa: Orden de arresto grupal (MRT)</v>
+        <v> Contrato de nivel rojo: Demolición de contenedores de combustible</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v> Contrato de nivel rojo: Demolición de contenedores de combustible</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v> Asignación de recompensa: Orden de arresto grupal (HRT)</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v> Contrato de nivel amarillo: Proteger ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="429" xml:space="preserve">
+      <c r="A429" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Hay algún piloto dispuesto en la zona? Necesitamos protección alrededor de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; para un cliente. Una banda de forajidos ha estado atacando su &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;, y si no se hace nada al respecto causarán daños graves. Necesitamos a alguien que proteja la propiedad del cliente lo mejor posible y se encargue de los matones. Según la información que hemos logrado recopilar, estos matones son de poca monta, pero pueden causar problemas si no se tiene cuidado. Así que, si logras cumplir con los estándares de Foxwell, ofrecemos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v> Asignación de recompensa: Orden de arresto grupal (VHRT)</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v>Contrato de nivel naranja: Proteger ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="431" xml:space="preserve">
+      <c r="A431" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de nuestros clientes de alta prioridad está siendo atacado por una banda criminal que apunta a sus &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Los activos del cliente son valiosos, así que necesitamos mantenerlos seguros a toda costa, pero no voy a bromear: será un desafío enorme con estos matones decididos a causar daños reales. Si fuera yo, no dudaría en &lt;EM&gt;traer refuerzos&lt;/EM4&gt; para lidiar con ellos. No son ninguna broma, así que ofrecemos un merecido &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal que se encargue de estos tipos con éxito. Mucha suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v> Asignación de recompensa: Orden de grupo (ERT)</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v>Contrato de nivel naranja: Defender ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str" xml:space="preserve">
+        <v xml:space="preserve">Espero que puedas brindar servicios de protección en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Uno de nuestros clientes de alta prioridad está teniendo serios problemas con una banda de forajidos que atacan su ~mission(Objects). Necesitamos poder mantener los activos lo más seguros e intactos posible. El cliente espera el servicio por el que paga, así que no lo arruines o podríamos perder un cliente leal. Por ahora, todavía estamos un poco a oscuras con respecto a estos forajidos, pero si logras resolver esto según los estándares de Foxwell, le ofreceremos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v> Contrato de garantía grupal pro tempore</v>
+        <v>Contrato de nivel rojo: Proteger ~misión(Objetos)</v>
       </c>
     </row>
     <row r="435" xml:space="preserve">
       <c r="A435" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, espero que todo vaya bien. Puede que ya te haya contactado, pero quería asegurarme de presentarme. Soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera actualmente en el sistema Stanton, que proporciona una variedad de servicios a todos los principales organismos gubernamentales, así como a varias empresas privadas. El motivo por el que me pongo en contacto contigo es porque creemos que alguien con tus habilidades podría ser muy valioso para nuestros clientes. Además, creo que seríamos una buena opción para ti. Nuestros contratistas suelen recibir una remuneración más alta que muchos de nuestros competidores en el sistema, y muchos de ellos me comentan lo mucho que disfrutan del trabajo desafiante e interesante que les ofrecemos. Ahora bien, Northrock se rige por estándares muy altos, por lo que antes de que podamos formalizar nada, tendrás que obtener la aprobación como contratista completando un contrato provisional. Esperaba que pudieras capturar a varios miembros buscados de una banda de forajidos: ~misión(Objetivo1), ~misión(Objetivo2) y ~misión(Objetivo3). Una vez que lo hagas, veremos si podemos conseguirte más trabajo. Espero tener noticias tuyas pronto. Atentamente, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve">Acaba de llegar un contrato de emergencia sobre una banda de matones violentos que están causando estragos en la infraestructura de uno de nuestros clientes VIP. Si está disponible, necesitamos que acuda rápidamente a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y defienda los valiosos &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; del cliente a toda costa. Foxwell está muy al tanto de este grupo, así que créame cuando le digo que no hay que subestimar a estos pilotos. Le recomiendo encarecidamente que organice una &lt;EM&gt;fuerza de apoyo altamente competente&lt;/EM&gt; para que vuele con usted al lugar. Si logra sobrevivir al encuentro con la propiedad del cliente intacta, añadiremos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; a cualquier contratista principal lo suficientemente valiente como para aceptar este trabajo. Manténgase a salvo y buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Orden de reevaluación del grupo provisional</v>
+        <v>Contrato de nivel amarillo: Defender ~misión(Objetos)</v>
       </c>
     </row>
     <row r="437" xml:space="preserve">
       <c r="A437" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, he estado reflexionando sobre todo lo sucedido y decidí hablar con la gerencia. Han accedido a darte otra oportunidad, pero solo si completas con éxito un contrato para nosotros. Podemos considerar la posibilidad de restituirte en tu puesto si logras capturar a este trío criminal: ~misión(Objetivo1) ~misión(Objetivo2) ~misión(Objetivo3). Evadieron al último asociado que los persiguió, así que si los capturas a todos, sin duda ganarás puntos. Espero que hayas enderezado tu vida desde tu último trabajo. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> Llamando a todos los pilotos: uno de nuestros clientes busca protección para sus &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;, ubicados en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Por lo que hemos averiguado, los atacantes son un grupo de aspirantes a delincuentes que probablemente no se han dado cuenta del valor de los bienes que intentan destruir, solo causan estragos por diversión. Aun así, la propiedad del cliente es importante, por lo que debe mantenerse lo más intacta posible. Si se encargan de ellos según los estándares de Foxwell, ofrecemos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v> Ayuda al bloqueo</v>
+        <v>Contrato de nivel rojo: Defender ~misión(Objetos)</v>
       </c>
     </row>
     <row r="439" xml:space="preserve">
       <c r="A439" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ahora que Crusader ha encontrado su flota, parece que los Nueve Colas por fin se han dado cuenta de lo útil que puede ser un poco de ayuda extra. En resumen, buscan mercenarios para mantener a raya a Crusader. Tú y todos los demás que se ofrezcan voluntarios recibiréis una recompensa por cada nave de seguridad que derribéis. Y, además, si mantenéis a Crusader ocupado el tiempo suficiente para que los Nueve Colas terminen con lo que sea que estén tramando con este bloqueo cuántico, recibiréis una generosa bonificación.</v>
+        <v xml:space="preserve">Se necesita apoyo urgente para el barco en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Una conocida organización criminal destructiva ha estado tanteando el terreno con la propiedad de uno de nuestros clientes durante meses, y ahora ha causado estragos atacando los &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; del cliente. Estos activos son muy valiosos, por lo que debemos mantenerlos a salvo a toda costa, aunque sabemos que no será tarea fácil. No puedo enfatizar lo suficiente lo peligrosos que son estos individuos, así que no dudaría en &lt;EM&gt;traer refuerzos&lt;/EM&gt; para lidiar con ellos. Si usted y los activos salen ilesos, ofrecemos un merecido &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Mucha suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v> Bloqueo ilegal: Neutralización de la Flota de Nueve Colas</v>
+        <v>Contrato de nivel amarillo: Defender ~mission(DefendLocationWrapperLocation)</v>
       </c>
     </row>
     <row r="441" xml:space="preserve">
       <c r="A441" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha confirmado la ubicación de la flota forajida de los Nueve Colas y se está movilizando para poner fin al bloqueo cuántico de ~mission(Location). Buscamos nuevamente profesionales de seguridad capacitados para unirse a nuestros esfuerzos de respuesta de emergencia y ayudar a neutralizar esta peligrosa amenaza. Antes de aceptar, tenga en cuenta que se espera que los Nueve Colas ofrezcan una resistencia considerable y que, hasta que se levante el bloqueo, no será posible realizar viajes cuánticos en el sector. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+        <v xml:space="preserve"> Las naves que entran y salen de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; están siendo atacadas por fuerzas hostiles. La gente de allí nos ha contratado para solucionar este problema de inmediato. Necesitamos a alguien que llegue pronto y empiece a combatir estas naves. La situación parece estar en constante evolución, así que te mantendré informado sobre dónde se te necesita más. Por el esfuerzo y la diligencia, también pagaremos una bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal por encargarse de esto. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v> Lejos de miradas indiscretas</v>
+        <v> Contrato de Nivel Naranja: Proteja los intereses de nuestros clientes.</v>
       </c>
     </row>
     <row r="443" xml:space="preserve">
       <c r="A443" t="str" xml:space="preserve">
-        <v xml:space="preserve">Les dije a los Nueve Colas que bloquear los viajes cuánticos para mantener toda una zona como rehén iba a atraer la atención equivocada, pero ¿me hacen caso? No. Ahora Crusader tiene docenas de naves de escaneo por ahí husmeando en cosas que prefiero mantener ocultas. Por eso estoy intentando contratar a tanta gente como pueda para que me ayude. Quiero pagarte por cada nave de escaneo de Crusader que destruyas. De hecho, incluso aumentaré tu tarifa por nave si todos alcanzan un cierto número de bajas. Llámalo incentivo por rendimiento. Y si de verdad te sientes con ganas de superarte, elimina a cualquier tonto lo suficientemente valiente como para intentar transportar carga a la estación bloqueada. Tengo algunos proveedores que agradecerán la demanda extra.</v>
+        <v xml:space="preserve">La gente de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; está bajo ataque y necesita nuestro apoyo. Sus naves en la zona están siendo atacadas y existe una creciente preocupación de que esto sea solo el preludio de algo más grande. La situación está evolucionando, pero estoy recibiendo actualizaciones constantes sobre lo que está sucediendo y te mantendré informado a medida que avance el contrato. ¿Estás disponible para ayudarlos? Sería inteligente reclutar a algunos amigos para que ayuden. Son clientes importantes y no podemos permitirnos fallarles. El contratista principal ganará un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; si completas el trabajo. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v> Bloqueo ilegal: se busca al responsable de la flota de las Nueve Colas.</v>
+        <v>Contrato de nivel naranja: Se requiere protección para el buque.</v>
       </c>
     </row>
     <row r="445" xml:space="preserve">
       <c r="A445" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que la organización criminal conocida como los Nueve Colas ha establecido un bloqueo ilegal alrededor de ~mission(Location) y ha detenido todo el tráfico cuántico entrante y saliente en el sector. Es necesario localizar la flota ilegal y levantar el bloqueo. Solicitamos urgentemente a cualquier profesional de seguridad capacitado en el sistema que se una a las fuerzas de Crusader Security y proteja nuestras naves de escaneo mientras buscan la ubicación de la flota de los Nueve Colas que está causando este bloqueo. Tenga en cuenta que, con el viaje cuántico desactivado y numerosos enemigos en la zona, esta debe considerarse una operación de alto riesgo. Se recomienda encarecidamente que todos los pilotos que participen en esta operación de respuesta de emergencia cuenten con el equipo adecuado y el tanque de combustible lleno. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+        <v xml:space="preserve">Tenemos clientes que reportan ataques de forajidos a barcos alrededor de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt;. Están completamente bloqueados y cualquiera que entre o salga es un objetivo. Cualquier intento de resolver el problema solo ha sido recibido con más refuerzos de forajidos. El cliente está desesperado por una solución, así que estamos contratando a un contratista para que vaya y restablezca la paz en el área. Si surge algún otro problema una vez que estés allí, te comunicaré las instrucciones sobre cómo ayudar. Realmente necesitamos a alguien rápido. Así que para hacer la oferta más atractiva, el contratista principal también recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v> Bloqueo ilegal: se necesitan suministros médicos.</v>
+        <v xml:space="preserve">Contrato de nivel rojo: Soporte a clientes VIP</v>
       </c>
     </row>
     <row r="447" xml:space="preserve">
       <c r="A447" t="str" xml:space="preserve">
-        <v xml:space="preserve">El bloqueo cuántico ilegal de ~mission(Location) ha interrumpido las rutas comerciales habituales y los productos esenciales escasean. Crusader Security busca comerciantes y transportistas para suministrar los suministros médicos que tanto necesita la estación. Los precios ofrecidos por la administración de la estación se ajustarán para reflejar la situación con los Nine Tails y, además, Crusader otorgará una bonificación por riesgo al entregar con éxito los suministros médicos debido al mayor riesgo. Gracias de antemano por su apoyo durante estos tiempos difíciles. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+        <v xml:space="preserve"> Buscamos un profesional consumado para manejar un trabajo de alto riesgo. Tenemos clientes VIP en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; que se enfrentan a forajidos extremadamente agresivos y motivados que atacan naves alrededor de su ubicación. Los detalles exactos del ataque aún están llegando, pero parece ser una operación amplia y multifacética. Si está disponible, le recomiendo encarecidamente que traiga naves de apoyo de combate adicionales, muchos suministros y su mejor desempeño. Si lo hace bien, recompensaremos al contratista principal con un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v> Iniciativa Overdrive: Emboscada contra Xenoamenazas - Se necesita apoyo</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="str">
-        <v/>
+        <v>Contrato de nivel amarillo: Enfréntate a los agresores</v>
+      </c>
+    </row>
+    <row r="449" xml:space="preserve">
+      <c r="A449" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Naves no autorizadas están acosando a cualquiera que intente aterrizar o salir de las operaciones de nuestro cliente en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt;. Necesitamos a alguien que vuele hasta allí para defender el sitio y proteger las naves de nuestro cliente antes de que la situación se salga de control. Llega allí, persigue a esos agresores y te mantendré informado sobre la situación. Ayuda a solucionar esto y le pasaremos un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v> ALERTA DE LAS FDI: Emboscada de xenoamenazas - Se necesita apoyo</v>
+        <v> Contrato de nivel rojo: Salvar naves en ~mission(DefendLocationWrapperLocation)</v>
       </c>
     </row>
     <row r="451" xml:space="preserve">
       <c r="A451" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA PUBLICACIÓN INMEDIATA EN TODO EL SISTEMA* Atención, fuerzas de XenoThreat comenzaron a emboscar a los convoyes navales que transportaban suministros vitales mientras se dirigían a la estación Jericho en el Pyro Gateway en el Sistema Stanton. La Armada ha solicitado a las fuerzas de CDF que ayuden a recuperar estos suministros de los restos y entregarlos de forma segura a Jericho. La Armada ha organizado un estipendio comunitario para gestionar la distribución del pago. Este se distribuirá entre todos los voluntarios de CDF en intervalos asignados. Aparecerá un indicador en su HUD para medir estos pagos. Tenga en cuenta que algunos de estos suministros son altamente volátiles si no se manipulan correctamente. Tenga precaución al transportar estos materiales: * Zeta-Prolanide se degrada con el tiempo hasta descomponerse por completo. * AcryliPlex Composite se vuelve explosivamente inestable si se daña. * Diluthermex libera un pulso de energía destructivo si se expone al viaje cuántico. Además, si bien no es tan volátil, la Armada aún necesita urgentemente los suministros de DynaFlex perdidos durante el ataque para completar las reparaciones del Javelin, por lo que su recuperación debe ser prioritaria. Asimismo, es posible que aún haya hostiles de XenoThreat en la zona, así que tengan cuidado. Se insta a los voluntarios de las CDF con experiencia en combate a contribuir asegurando estas áreas de las fuerzas XenoThreat que aún persistan. La SAIC Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
+        <v xml:space="preserve">Se necesita apoyo naval en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; inmediatamente. Los intereses de nuestro cliente en la zona están siendo atacados ferozmente por fuerzas ilegales. Buscamos a alguien que pueda recoger su equipo, algunos barcos de apoyo de confianza y desplegarlos antes de que sea demasiado tarde. Una vez que llegues, te enviaré cualquier actualización de la situación. No lo estropees. Estos clientes están pagando y esperan protección de primer nivel. Si algo sale mal, podríamos perder este contrato. Por eso, le daremos al contratista principal un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; si todo sale a la perfección. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Iniciativa Overdrive: Ataque a XenoThreat</v>
-      </c>
-    </row>
-    <row r="453" xml:space="preserve">
-      <c r="A453" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Atención, las fuerzas navales se han reagrupado para el asalto final que XenoThreat ha estado planeando. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. Esto incluye a voluntarios que no hayan participado en la Iniciativa Overdrive. La suboficial Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y dirigirá la operación. Si tiene éxito, se completará esta serie de la Iniciativa Overdrive y recibirá acceso temporal a los F7A Hornet o una actualización gratuita si actualmente posee un F7C.</v>
+        <v>Contrato de nivel amarillo: Barco bajo ataque</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v> Contrato de nivel amarillo: Barco bajo ataque</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v> ALERTA DE CDF: Ataque a XenoThreat</v>
-      </c>
-    </row>
-    <row r="455" xml:space="preserve">
-      <c r="A455" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención: las fuerzas navales se han reagrupado para un asalto final contra la manada de forajidos XenoThreat que ha estado asolando el Sistema Stanton. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. La suboficial Rowena Dulli, de la División de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
+        <v> Contrato de nivel rojo: El barco está bajo ataque.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v> Contrato de nivel rojo: El barco está bajo ataque.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v> dinero de la nada</v>
+        <v> Contrato de nivel naranja: ~misión (nave) necesita asistencia</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v> ¿Alguna vez has deseado que aparecieran créditos por arte de magia? Varias terminales de crédito antiguas de CCB están activas y simulan transacciones bancarias para desviar fondos a quien las controle. Si te interesa, te vendo las coordenadas por una pequeña comisión. Date prisa si quieres aprovechar la oportunidad. No sé cuánto tiempo seguirá funcionando.</v>
+        <v> Contrato de nivel naranja: ~misión (nave) necesita asistencia</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v> Ruta de envío local de Red Wind</v>
-      </c>
-    </row>
-    <row r="459" xml:space="preserve">
-      <c r="A459" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Recibimos una solicitud de ~mission(Pickup1|Address) indicando que tienen una buena cantidad de paquetes esperando en ~mission(Pickup1) que necesitan ser entregados. Antes de aceptar el contrato, asegúrese de tener una nave con suficiente espacio. Un rayo tractor tampoco vendría mal. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; SOMOS UNA EMPRESA QUE OFRECE IGUALDAD DE OPORTUNIDADES: Red Wind Linehaul es y siempre ha sido una empresa que ofrece igualdad de oportunidades. Si cree que puede hacer un buen trabajo para nosotros, no dude en inscribirse.</v>
+        <v> Desmantelan una nueva operación antidrogas.</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v> Desmantelan una nueva operación antidrogas.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Servicio de mensajería discreta Red Wind</v>
-      </c>
-    </row>
-    <row r="461" xml:space="preserve">
-      <c r="A461" t="str" xml:space="preserve">
-        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tengo otro trabajo especial para el que podrías contar contigo. Debería ser un viaje rápido. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;) LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Y por favor recuerda no molestar a los clientes ni a ninguno de sus invitados. La profesionalidad es clave aquí.</v>
+        <v> Destruir drogas peligrosas</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v> Destruir drogas peligrosas</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v> Viento Rojo necesita mensajeros discretos</v>
-      </c>
-    </row>
-    <row r="463" xml:space="preserve">
-      <c r="A463" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Sé que has hecho un buen trabajo para nosotros en el pasado, así que pensé en preguntarte si te interesaría encargarte de un viaje especial que está un poco más lejos de lo que has estado haciendo hasta ahora. En resumen, necesitamos un piloto que esté dispuesto a trabajar con discreción, concentrarse en entregar los paquetes y, lo más importante, no hacer muchas preguntas. Verás, para una empresa pequeña como la nuestra, mantenernos por delante de la competencia significa que necesitamos ofrecer a nuestros clientes algo que no pueden obtener en ningún otro lugar: discreción. En Red Wind, siempre que tengas los créditos, llevaremos lo que sea a donde sea. ¿Entendido? Si eso te parece bien, veamos cómo te va en esta carrera: PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Un último consejo: probablemente sería bueno evitar retrasos innecesarios una vez que los paquetes estén a bordo, por ejemplo, que sean registrados por las fuerzas del orden locales.</v>
+        <v> Destruir las drogas ilegales</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v> Destruir las drogas ilegales</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Manipulador de paquetes de Red Wind</v>
-      </c>
-    </row>
-    <row r="465" xml:space="preserve">
-      <c r="A465" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Parece que hubo un pequeño problema logístico en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitan a alguien que se asegure de que los paquetes extraviados terminen donde se supone que deben ir dentro de las instalaciones. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; LA CONFIANZA ES BIDIRECTA: al aceptar este contrato, usted se compromete a no estafarnos, y Red Wind Linehaul se compromete a tratarlo de la misma manera.</v>
+        <v> Ayuda a proteger el sitio.</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v> Ayuda a proteger el sitio.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Ruta de reparto local de Red Wind</v>
-      </c>
-    </row>
-    <row r="467" xml:space="preserve">
-      <c r="A467" t="str" xml:space="preserve">
-        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Se necesita un piloto independiente disponible para una entrega local rápida. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de la &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Intente no causar problemas cuando esté fuera. Si lleva paquetes de Red Wind a bordo, se agradece cierto nivel de profesionalismo. Y no olvide empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar consigo. ~mission(Contractor|SignOff)</v>
+        <v> Limpie cuidadosamente el sitio</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v> Limpie cuidadosamente el sitio</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v> Red Wind busca nuevos pilotos.</v>
-      </c>
-    </row>
-    <row r="469" xml:space="preserve">
-      <c r="A469" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Buscamos contratar un piloto independiente interesado en operar una ruta local para nosotros. PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si lo logras, podemos considerar otros contratos en el futuro. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~mission(Contractor|SignOff)</v>
+        <v> Contrato de nivel amarillo: Merc Work</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v> Contrato de nivel amarillo: Merc Work</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v> Otro intento de entrega de Red Wind</v>
-      </c>
-    </row>
-    <row r="471" xml:space="preserve">
-      <c r="A471" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Aunque hace tiempo que no le contratamos, ahora mismo nos vendría bien su ayuda extra. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a la &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Si logras esta entrega, podemos ver si podemos volver a hacerla más frecuente. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~misión(Contratista|Aprobación)</v>
+        <v> Contrato de nivel amarillo: Despeje de la PAF</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v> Contrato de nivel amarillo: Despeje de la PAF</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>SE NECESITA PILOTO DE RED WIND DELIVERY</v>
-      </c>
-    </row>
-    <row r="473" xml:space="preserve">
-      <c r="A473" t="str" xml:space="preserve">
-        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tenemos un envío esperando ser transportado desde &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Sin embargo, seré sincero contigo, este lugar no tiene la mejor reputación. Dicho esto, todavía necesitan entregar paquetes y tienen créditos, así que todo está en orden. Pero si vas allí, hay una buena posibilidad de que te encuentres con algunos problemas. No aceptes el trabajo si no puedes manejar eso. A TODOS LOS VETERANOS: ¡Red Wind agradece su servicio a nuestro Imperio! ¡Sus esfuerzos significan nuestra libertad!</v>
+        <v> Barrer y despejar la ubicación</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v> Barrer y despejar la ubicación</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v> Oportunidad de manutención para reclusos</v>
-      </c>
-    </row>
-    <row r="475" xml:space="preserve">
-      <c r="A475" t="str" xml:space="preserve">
-        <v xml:space="preserve">Estimados usuarios: Recientemente nos han informado de que uno de nuestros dispensadores de oxígeno ha sufrido una avería técnica. Como saben, estos dispensadores son esenciales para garantizar que dispongan de suficiente oxígeno durante su participación en nuestro Programa de Reinserción Laboral. Buscamos a algún usuario disponible que pueda reiniciar el dispensador. Esto debería reconectarlo a la red y solucionar el problema. El primer usuario que complete esta tarea no solo recibirá una recompensa, sino también la satisfacción de contribuir a un entorno de trabajo más seguro para los demás usuarios. Gracias.</v>
+        <v> Ataque de precisión en ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v> Ataque de precisión en ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v> Negociaciones fallidas</v>
-      </c>
-    </row>
-    <row r="477" xml:space="preserve">
-      <c r="A477" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tuve un percance con la mala suerte y espero que puedas ayudarme. Hace unos días, contraté a la tripulación del 'Orgullo de Arliss' para obtener datos importantes. Cumplieron el trabajo sin problemas, pero el capitán, ese desgraciado, me contactó exigiendo más créditos. Resulta que no era la primera vez que intentaba esta trampa, porque en medio de una "negociación" conmigo, su nave fue atacada por unos individuos muy enfadados que querían darle una lección. Nuestra comunicación se cortó cuando empezó el tiroteo y fue lo último que supe de él. Supongo que lo han borrado de mi vida, pero quiero que vayas al Orgullo de Arliss e intentes obtener mis datos del datapad personal del capitán. Una vez que los tengas, he configurado un canal de transmisión seguro en el área de descanso ARC-L1. Ve allí y, cuando estés dentro del alcance, envíame los datos a través de este contrato para que te pague. No intentes engañarme. El karma puede ser un verdadero cabrón.</v>
+        <v> Localizar ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v> Localizar ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v> Doble juego</v>
-      </c>
-    </row>
-    <row r="479" xml:space="preserve">
-      <c r="A479" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rough &amp; Ready recientemente proporcionó servicios de repostaje a un transportista llamado ~mission(TargetName), quien accedió a entregarnos su próximo cargamento como compensación. Pues bien, acabamos de descubrir que el mentiroso vendió su último cargamento a una banda rival. Buscamos a alguien que localice y elimine a ~mission(TargetName|Last) por su traición. Un viejo amigo mío acaba de ver al traidor en ~mission(Location|Address). Parece que lleva más cargamento que no va dirigido a nosotros y viaja con escolta. Solo te pagaremos por destruir el barco, así que todo lo que encuentres a bordo es tuyo. - Smokey</v>
+        <v> Contrato de nivel rojo: Recuperar cargamento</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Contrato de nivel rojo: Recuperar cargamento</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v> Entrega fallida</v>
-      </c>
-    </row>
-    <row r="481" xml:space="preserve">
-      <c r="A481" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mis socios y yo cerramos un trato con un transportista llamado ~mission(TargetName) para que nos entregara suministros. Lo curioso es que el envío nunca llegó. Afirmaron que unos piratas asaltaron su barco y se llevaron nuestros suministros, pero resulta que esa historia es una completa mentira. Mentir para cancelar nuestro trato no puede quedar impune y vas a dejarlo bien claro. ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Mientras mates a ~mission(TargetName|Last), no nos importa lo que pase con la carga que transportan. - Smokey</v>
+        <v> Contrato de nivel rojo: Recuperar el cargamento robado</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v> Contrato de nivel rojo: Recuperar el cargamento robado</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v> Activar una trampa</v>
-      </c>
-    </row>
-    <row r="483" xml:space="preserve">
-      <c r="A483" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un imbécil con el nombre ~mission(TargetName) ha estado tramando un plan: su carguero solicita repostaje solo para emboscar a nuestros barcos al llegar. Incluso cargó la maldita nave con mercancía real para asegurarse de que pasara los escaneos. Hemos corrido la voz para que nadie en Rough &amp; Ready vuelva a caer en la trampa, pero quiero que este cretino sea castigado. Creo que ~mission(TargetName|Last) reconoce a muchos de los nuestros, así que supongo que será mejor pagarte para que te encargues. He oído que lo han visto cerca de ~mission(Location|Address). Dirígete allí ahora mismo y acaba con ese carguero y con cualquiera que lo proteja de una vez por todas. - Smokey</v>
+        <v> Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v> Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v> Saboteador de la huelga</v>
-      </c>
-    </row>
-    <row r="485" xml:space="preserve">
-      <c r="A485" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Te interesa ir de caza? ~mission(TargetName) saboteó uno de nuestros envíos de combustible y nos costó un montón de créditos, así que busco a alguien que le haga pagar por lo que hizo. Me acaban de avisar de que ~mission(TargetName|Last) fue visto en ~mission(Location|Address). Si vas allí ahora, hay muchas posibilidades de que puedas seguirle la pista y acabar con él definitivamente. ~mission(TargetName|Last) no actuó solo, así que no te sorprendas si va acompañado. - Smokey</v>
+        <v> Nuevas y emocionantes oportunidades con Foxwell Enforcement</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v> Nuevas y emocionantes oportunidades con Foxwell Enforcement</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v> Ya era hora.</v>
-      </c>
-    </row>
-    <row r="487" xml:space="preserve">
-      <c r="A487" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rough &amp; Ready lleva años haciendo negocios con ~mission(TargetName), pero la relación se ha deteriorado. Durante un tiempo, les suministrábamos combustible a crédito, pero a la hora de cobrar, el cobarde se escondió. Si ~mission(TargetName|Last) no puede pagar con créditos, supongo que pagará con su vida. Un socio acaba de localizar a ~mission(TargetName|Last) en ~mission(Location|Address). Me encantaría que fueras allí ahora mismo para hacer que ese tacaño pague. Por cierto, parece que ~mission(TargetName|Last) no viaja solo, así que asegúrate de tener suficiente combustible antes de ir tras él. - Smokey</v>
+        <v> ¿Sigues buscando trabajo?</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v> ¿Sigues buscando trabajo?</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v> Regalo de despedida</v>
+        <v> Contrato de nivel amarillo: Inspección de seguridad</v>
       </c>
     </row>
     <row r="489" xml:space="preserve">
       <c r="A489" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tengo una situación delicada que requiere atención. Tras años de ser un miembro leal de Rough &amp; Ready, ~mission(TargetName) desertó de la banda y está por ahí filtrando secretos a nuestros rivales. Necesitamos eliminar a ~mission(TargetName|Last) de inmediato. En casos como este, siempre es mejor pagarle a alguien ajeno a nosotros para que se encargue. Los escaneos detectaron a ~mission(TargetName|Last) cerca de ~mission(Location|Address) hace poco. Te pagaremos bien para que vayas allí ahora mismo y te encargues de él. ~mission(TargetName|Last) no es tonto y sabe que iremos tras él. Prepárate para una dura batalla y no esperes que esté solo. - Smokey</v>
+        <v xml:space="preserve">Necesitas a alguien para eliminar una patrulla de seguridad. Tendrás que ir al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en tu HUD y luego escanear varios puntos de ruta designados asegurándote de que sean seguros. Los satélites en esa región han estado fallando últimamente. No estoy seguro de qué está pasando allí, pero es mejor estar preparado en caso de que haya algún problema. Completa este contrato y el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(ScripAmount) MG Scrip.&lt;/EM4&gt; Buena suerte, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v> Operación de espionaje en silencio</v>
+        <v> Contrato de nivel naranja: amenaza potencial para la seguridad</v>
       </c>
     </row>
     <row r="491" xml:space="preserve">
       <c r="A491" t="str" xml:space="preserve">
-        <v xml:space="preserve">El equipo de Rough &amp; Ready busca a alguien para manejar una situación delicada. Hemos descubierto una nave y centinelas orbitales en ~mission(location|address) espiándonos. Estamos en un aprieto porque no queremos iniciar una pelea mayor con quienquiera que esté detrás de esto. Por eso buscamos ayuda a sueldo que pueda encargarse de esto rápida y discretamente. ¿Te interesa? Último consejo: una vez allí, asegúrate de vigilar la nave. Apuesto a que en cuanto empieces a destruir sus centinelas intentarán traer refuerzos para detenerte. - Smokey</v>
+        <v xml:space="preserve">Se han avistado varios barcos desconocidos en zonas frecuentadas por transportistas que entregan mercancías para nuestro cliente. Les preocupa que estos barcos estén vigilando a sus transportistas para preparar una emboscada, por lo que nos han contratado para patrullar la zona. Empiece por ir al marcador de ubicación en su HUD y escanéelo para asegurarse de que no haya peligro. Después, le enviaremos a otras zonas para que busque posibles amenazas. Le recomendamos que traiga un compañero y suficientes suministros para estar preparado para cualquier eventualidad. Tenga en cuenta también que completar con éxito este contrato le reportará al contratista principal una bonificación de ~misión(Cantidad de Scrip) MG Scrip. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v> Operación de espionaje de Stomp</v>
+        <v>Contrato de nivel naranja: Patrulla de seguridad</v>
       </c>
     </row>
     <row r="493" xml:space="preserve">
       <c r="A493" t="str" xml:space="preserve">
-        <v xml:space="preserve">El equipo de Rough &amp; Ready busca un mercenario independiente interesado en algo pesado. Hemos estado vigilando una situación que se está desarrollando en ~mission(location|address), donde varias naves custodian centinelas orbitales que espían nuestras operaciones. Puede que haya nacido de noche, pero no fue anoche. Dada la descarada forma en que están instalados, quien sea el responsable debía saber que tarde o temprano lo descubriríamos. Casi parece que están tendiéndole una trampa a R&amp;R para que ataquemos, y no quiero que caigamos en ella. En cambio, tú lo harás por nosotros y recibirás una buena cantidad de créditos por tu esfuerzo. Las naves estacionadas allí sospecharán menos de una nave no afiliada que se acerque, lo que dificultará que nos atribuyan el ataque. Asegúrate de planificar bien antes de ir. Quizás deberías llevar tus propios refuerzos por si alguna de sus naves escapa y pide ayuda. - Smokey</v>
+        <v xml:space="preserve"> Un cliente está preocupado por la actividad cerca de algunos de sus intereses. Hemos sido contratados para patrullar el área y realizar escaneos en varias ubicaciones. ¿Interesado? Si es así, diríjase al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en su HUD para comenzar el patrullaje. El cliente no especificó las amenazas, pero no cree que todo sea del todo correcto. Esperamos poder brindarle algo de tranquilidad. Además, el cliente acordó que ofrezcamos un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v xml:space="preserve"> Detengan las operaciones de espionaje</v>
+        <v> Contrato de Nivel Rojo: Asegurar el Espacio Amenazado</v>
       </c>
     </row>
     <row r="495" xml:space="preserve">
       <c r="A495" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mis socios y yo nos encontramos en un pequeño aprieto y necesitamos ayuda. Hay un centinela orbital en ~mission(location|address) que nos está espiando. No sabemos quién lo puso ahí, pero desde luego no puede quedarse. El problema es que somos gente de negocios ante todo y nos preocupa que si lo destruimos nosotros mismos se arme un lío. Por eso es mejor que lo haga alguien como tú. Debería ser un trabajo rápido y fácil para alguien interesado en ganar algo de prestigio. - Smokey</v>
+        <v xml:space="preserve">Necesitamos un piloto experimentado para una patrulla importante. Un cliente importante está harto de que los forajidos ataquen sus naves y satélites. Nos han contratado para escanear las áreas en cuestión y lidiar con las fuerzas hostiles. La patrulla comienza en el marcador de ubicación &lt;EM4&gt; en tu HUD antes de dirigirnos a otras ubicaciones que esperamos que despejes. No sabemos con qué te encontrarás, pero según la información compartida por el cliente, frecuentemente ven grupos de cazas de cinco a siete naves patrullando la región. Algunos incluso tienen naves más grandes liderando el ataque. Eso significa que más te vale estar preparado para una dura batalla. Si puedes, intenta reclutar al menos a &lt;EM4&gt;tres amigos&lt;/EM4&gt; para la causa. Incluso un piloto experimentado necesitará toda la ayuda posible contra esta tripulación. Dado que esta va a ser una misión difícil, el contratista principal recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al final de la patrulla. Buena suerte, Kevin Walton, Despachador de Foxwell Enforcement. «Seguridad a tu medida». Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v> Operación de espionaje de Squash</v>
+        <v>Contrato de nivel amarillo: Patrullaje de rutina</v>
       </c>
     </row>
     <row r="497" xml:space="preserve">
       <c r="A497" t="str" xml:space="preserve">
-        <v xml:space="preserve">Recientemente hicimos un descubrimiento interesante: alguien instaló varios centinelas orbitales en ~mission(location|address). Supongo que intentan obtener información sobre nuestras operaciones allí. Incluso tienen algunas naves vigilando para asegurarse de que no les pase nada. Por supuesto, queremos deshacernos de estos desgraciados, pero me preocupa que hacerlo nosotros mismos sea perjudicial para el negocio. Por eso buscamos una forma de "negación plausible". Alguien ajeno a R&amp;R que elimine el problema, para que quien esté detrás no pueda vincular directamente el ataque con nosotros. Sé que no será fácil, sobre todo con esos guardias al acecho. ¿Quién sabe cuántos refuerzos tienen preparados? Pero si lo consigues, estamos dispuestos a pagarte como es debido. ¿Crees que tienes las habilidades necesarias para lograrlo? - Smokey</v>
+        <v xml:space="preserve"> Es hora de realizar una patrulla de rutina para uno de nuestros clientes de larga data. La ruta es una serie de puntos de referencia que deben visitarse y escanearse para confirmar que todo esté como se espera. Debería ser bastante simple. Si está interesado, acepte y diríjase al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en su HUD para comenzar. Si lo logra, el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(ScripAmount) MG Scrip.&lt;/EM4&gt; Buena suerte, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v> Echar leña al fuego</v>
+        <v> Contrato de nivel rojo: Patrulla de seguridad de alto riesgo</v>
       </c>
     </row>
     <row r="499" xml:space="preserve">
       <c r="A499" t="str" xml:space="preserve">
-        <v xml:space="preserve">Si buscas créditos fáciles, tengo una oferta para ti. Verás, corre el rumor de que ~mission(location|address) está funcionando como depósito de combustible. Parece que no se enteraron de que el comercio de combustible en Pyro pertenece a Rough &amp; Ready. Por eso tienes que ir allí y destruir sus reservas de combustible. Deberían ser fáciles de encontrar. Son los grandes tanques de almacenamiento amarillos repartidos por el puesto de avanzada. Pero ten cuidado, hay torretas defendiendo la zona, así que asegúrate de estar preparado para esquivar sus disparos o volar las armas por los aires. Tú decides cómo llevar a cabo la demolición. Las bombas serían mi primera opción, pero no me importa mucho con tal de que el trabajo se haga. - Smokey</v>
+        <v xml:space="preserve">Un cliente necesita nuestra ayuda. Forajidos están merodeando por ciertos sectores donde hacen negocios y atacando a cualquiera que se cruce en su camino. Nuestro cliente ya ha perdido varias naves y no puede permitirse perder más. Necesitamos a alguien que patrulle esas áreas y atraiga a cualquier fuerza hostil. El trabajo comienza con usted dirigiéndose al marcador de ubicación &lt;EM4&gt; en su HUD y escaneando. Luego compartiremos algunos otros puntos de patrulla para que los escanee. Por lo que parece, estos grupos de naves cuentan con pilotos hábiles y agresivos. Mejor prepárese para la pelea si se encuentra con alguno de ellos. Sería bueno tener al menos &lt;EM4&gt;dos pilotos de confianza&lt;/EM4&gt; a su lado para esto. Al final de una patrulla exitosa, el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Manténgase frío, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v> Invitados no deseados</v>
-      </c>
-    </row>
-    <row r="501" xml:space="preserve">
-      <c r="A501" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tenemos a unos forajidos que se están quedando más tiempo del debido en una de nuestras estaciones. Intentaron engañarnos, pero ahora están atrapados en ~mission(location|address). Necesitamos que los elimines. Rough &amp; Ready no quiere que quede ninguno con vida cuando termines. No importa lo complicado que sea, con tal de que se haga, ¿entendido? - Smokey</v>
+        <v>Contrato de nivel amarillo: Ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v> Contrato de nivel amarillo: Ataque sorpresa</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v> Trabajo de exterminio</v>
-      </c>
-    </row>
-    <row r="503" xml:space="preserve">
-      <c r="A503" t="str" xml:space="preserve">
-        <v xml:space="preserve"> En Rough &amp; Ready tenemos un problema de ratas. Una de nuestras tripulaciones intentó amotinarse y ahora se han apoderado de ~mission(location|address). Como no puedo estar completamente seguro de que no tengan simpatizantes a bordo, quiero que te encargues de eliminar a estos traidores. Si logras solucionar este problema de plagas, recibirás una buena recompensa. Solo asegúrate de no dejar a ninguno con vida. No quiero que a nadie más se le ocurran ideas raras. - Smokey</v>
+        <v> Contrato de nivel naranja: Devuelve el favor</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v> Contrato de nivel naranja: Devuelve el favor</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v> juntos para siempre</v>
-      </c>
-    </row>
-    <row r="505" xml:space="preserve">
-      <c r="A505" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aquí está el trato. ~mission(TargetName) y ~mission(TargetName2) deben morir al mismo tiempo. Desafortunadamente, no estarán en el mismo lugar. Un doble impacto puede sonar complicado, pero si contratas algunos artilleros adicionales, no debería ser tan difícil lograr dos impactos simultáneos. Asegúrate de encontrar gente con habilidades, ya que tengo información fidedigna de que cada uno volará con escoltas para "protección".</v>
+        <v> Contrato de nivel naranja: Tender una trampa</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v> Contrato de nivel naranja: Tender una trampa</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v> El doble de dolor de cabeza</v>
-      </c>
-    </row>
-    <row r="507" xml:space="preserve">
-      <c r="A507" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hay otro par que necesita ser asesinado simultáneamente. Parece que se está volviendo cada vez más popular como opción de asesinato. Esta vez son ~mission(TargetName) y ~mission(TargetName2). Se supone que ambos son operadores bastante hábiles y no volarán solos. Asegúrate de que quien te ayude en esta misión pueda manejar un combate.</v>
+        <v> Contrato de nivel rojo: Ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v> Contrato de nivel rojo: Ataque sorpresa</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v> lanzamiento simultáneo</v>
-      </c>
-    </row>
-    <row r="509" xml:space="preserve">
-      <c r="A509" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Adivina qué tienen en común ~mission(TargetName) y ~mission(TargetName2)? ¡Vas a matarlos a ambos! Lo difícil es que necesito que los mates al mismo tiempo para que ninguno pueda escapar, o peor aún, matar a quien intenta matarlo. Así que forma un equipo para rastrear a un objetivo mientras tú te encargas del otro. ¡Divide y vencerás! Y a pesar de que armaron un lío lo suficientemente grande como para que los mataran, entiendo que son bastante débiles. No esperes mucha resistencia.</v>
+        <v> Contrato de nivel amarillo: Emboscada a un aficionado</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v> Contrato de nivel amarillo: Emboscada a un aficionado</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v> amigos hasta el final</v>
-      </c>
-    </row>
-    <row r="511" xml:space="preserve">
-      <c r="A511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espero de verdad que no seas amigo de ~mission(TargetName) ni de ~mission(TargetName2), porque necesito que los elimines a ambos... al mismo tiempo... Claro que no nos lo pondrían fácil viajando en la misma nave o algo así de obvio. No. Tendrás que formar una tripulación para poder derribar a ambos objetivos simultáneamente. En cuanto uno de ellos muera, prepárate para eliminar al otro también. No podemos arriesgarnos a que ninguno escape. Y creo que debería mencionar que no solo son buenos pilotos, sino que también viajarán con refuerzos. Seguro que puedes con esto.</v>
+        <v> Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v> Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v> doble problema</v>
+        <v> Contrato de nivel amarillo: Neutralizar a la banda de secuestradores de barcos</v>
       </c>
     </row>
     <row r="513" xml:space="preserve">
       <c r="A513" t="str" xml:space="preserve">
-        <v xml:space="preserve">Si me hubieras preguntado, te habría dicho que ~mission(TargetName) y ~mission(TargetName2) acabarían matándose entre sí. Pero en cambio, tendrás el honor de eliminarlos a ambos a la vez. Eso sí, tendrás que ganártelo. Son peligrosos. Tienen un historial delictivo, están altamente entrenados y son demasiado listos para volar sin refuerzos. Reúne al mejor equipo posible. Lo necesitarás. Y no seas tacaño. No puedes gastar créditos si estás muerto.</v>
+        <v xml:space="preserve">Bien, esto podría ser un poco complicado de hacer solo, así que si tienes algún favor que pedir, sería bueno cobrarlo ahora. Hay un grupo de forajidos atacando naves de reparto en este sector y nos han encargado eliminarlos. Cuando tu tripulación esté lista, dirígete a ~mission(Location|Address) y acaba con los enemigos de allí. Estos desgraciados son bastante listos, así que tienden a dividirse en grupos más pequeños. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v> Que la muerte nos separe</v>
+        <v> Contrato de nivel naranja: Eliminar flota criminal</v>
       </c>
     </row>
     <row r="515" xml:space="preserve">
       <c r="A515" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Es bastante conmovedor encontrarse con una pareja dispuesta a morir el uno por el otro. Estúpido pero conmovedor. ~mission(TargetName) y ~mission(TargetName2) decidieron apoyarse mutuamente y ahora la situación los ha llevado a la muerte. Busca a un amigo y dales caza a estos dos. Asegúrate de matarlos al mismo tiempo. Llámalo justicia poética. Deberían morir fácilmente. Tal vez tengan una o dos naves con ellos, pero no creo que sea nada de qué preocuparse.</v>
+        <v xml:space="preserve">Parece que un par de pandillas de poca monta han decidido unir fuerzas y comenzar a realizar ataques coordinados. Por separado no eran gran cosa, pero juntas están demostrando ser una seria amenaza que hay que neutralizar. Recluta refuerzos de confianza y vuela a ~misión(Ubicación|Dirección). Una vez que ataques a los primeros miembros de la pandilla que encuentres allí, los otros grupos llegarán para apoyarlos. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada y con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>dos por el precio de dos</v>
+        <v> Contrato de nivel naranja: Destruir la amenaza de los forajidos</v>
       </c>
     </row>
     <row r="517" xml:space="preserve">
       <c r="A517" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Creo que podrían estar emparentados, ¿o saliendo juntos? En realidad no importa, alguien quiere matarlos. He organizado todo para que puedas atacarlos cuando no estén volando juntos. Así estarás más seguro. Son objetivos serios y cuentan con un apoyo igualmente serio. Asegúrate de que tú y tu equipo coordinen bien los ataques. No quiero que ninguno quede con vida, o será un verdadero dolor de cabeza.</v>
+        <v xml:space="preserve">Un grupo disidente de forajidos se ha separado de una de las principales bandas del sistema y está intentando actuar por su cuenta. Por la cantidad de problemas que han causado, es evidente que buscan hacerse un nombre cuanto antes. Dependerá de ti y de tu equipo detenerlos. Cuando tu equipo esté listo, dirígete a ~mission(Location|Address) y enfréntate a la banda. No todos estarán esperando allí. Espera refuerzos una vez que comiences el asalto. Asegúrate de quedarte hasta que te hayas encargado de todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. "Seguridad a tu manera". Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v> Asistencia en combate</v>
+        <v> Contrato de nivel amarillo: Clear Shipjacking Group</v>
       </c>
     </row>
     <row r="519" xml:space="preserve">
       <c r="A519" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) solicita asistencia en combate en ~mission(InitiatorLocation). Si se acepta, recibirá ~mission(PaymentAmount) aUEC al eliminar la amenaza.</v>
+        <v xml:space="preserve">Hay un pequeño grupo de criminales que han estado marcando su territorio, atacando a cualquier carguero que se acerque lo suficiente. Sin embargo, se volvieron un poco codiciosos, porque ahora alguien nos está pagando para que nos encarguemos de ellos. Una vez que usted y quien lo acompañe estén listos, diríjase a ~mission(Location|Address) y enfréntese a estos criminales. Como les gusta volar en grupos separados, asegúrese de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v> Asistencia en combate - BAJO RIESGO</v>
+        <v> SE NECESITA MENSAJERO DE NIVEL INICIAL EN NYX</v>
       </c>
     </row>
     <row r="521" xml:space="preserve">
       <c r="A521" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [BAJO NIVEL DE AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve">CONTRATO FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** FTL requiere un mensajero de nivel inicial para realizar entregas en Nyx. El mensajero debe contar con su propio transporte. Se prefiere experiencia previa en levantamiento manual de cargas, con la capacidad de mover cajas de hasta 0.25 SCU de peso. Al aceptar este contrato, usted acepta asumir la responsabilidad total de la seguridad de los paquetes asignados. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Asistencia en combate - ALTA AMENAZA</v>
+        <v> SE NECESITA MENSAJERO DE NIVEL INICIAL EN STANTON</v>
       </c>
     </row>
     <row r="523" xml:space="preserve">
       <c r="A523" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [ALTA AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve"> CONTRATO DE FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** Se necesita un mensajero confiable y trabajador de nivel inicial para realizar una entrega en Stanton. Usted será responsable de su propio transporte. Los contratistas interesados deben tener la capacidad de levantar cajas de hasta 0.25 SCU. Los contratistas son empleados de forma independiente y, por lo tanto, no están cubiertos por el seguro de la empresa FTL. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v> Asistencia en combate - AMENAZA MODERADA</v>
+        <v> SE NECESITA MENSAJERO DE NIVEL JUNIOR EN STANTON</v>
       </c>
     </row>
     <row r="525" xml:space="preserve">
       <c r="A525" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [AMENAZA MODERADA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve">CONTRATO FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** Se necesita mensajero de nivel junior para entregas en todo el Sistema Stanton. El transporte debe ser proporcionado por el mensajero. Deberá levantar hasta 0.25 SCU de peso. Los mensajeros son responsables del manejo correcto y la seguridad de todos los paquetes a su cargo. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v> Asistencia en combate - AMENAZA CRÍTICA</v>
+        <v> Juego de guerra de Idris</v>
       </c>
     </row>
     <row r="527" xml:space="preserve">
       <c r="A527" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [AMENAZA CRÍTICA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve"> Para poner a prueba la preparación de nuestros equipos de respuesta, solicitamos voluntarios que simulen un asalto contra un Idris de la CDF, neutralizando y tomando el control de la embarcación. Es importante aclarar que el objetivo del ejercicio no es destruir el Idris, sino abordarlo y mantener el control el mayor tiempo posible. Los voluntarios deben esperar una fuerte resistencia por parte de la tripulación altamente entrenada del Idris y se les recomienda obtener una imagen actualizada con anticipación. Las coordenadas se proporcionarán una vez confirmada su participación. Gracias y buena suerte.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v> Escolta</v>
+        <v> Perezoso</v>
       </c>
     </row>
     <row r="529" xml:space="preserve">
       <c r="A529" t="str" xml:space="preserve">
-        <v xml:space="preserve">~mission(InitiatorName) solicita un acompañante en la ubicación: ~mission(InitiatorLocation). Si se acepta, recibirá un pago de ~mission(PaymentAmount) aUEC/minuto hasta que el iniciador lo CANCELE o el proveedor del servicio lo ABANDONE. NOTA: El contrato y el pago comenzarán una vez que se reúna con el cliente.</v>
+        <v xml:space="preserve">Los Headhunters le prestaron créditos recientemente a ~mission(TargetName) bajo ciertas condiciones. Específicamente, páguenos o lo mataremos. Es increíble pensar que eso no fue suficiente incentivo, pero aquí estamos, después de la fecha límite de pago. Ahora, por mucho que apreciemos a ~mission(TargetName|First), necesito que cumpla nuestra promesa. ~mission(TargetName|Last) fue visto por última vez en ~mission(Location|Address). Rastrea a ese tipo, hazlo desaparecer y cobra. Es así de simple. Se esconde.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v xml:space="preserve"> Asistencia médica</v>
+        <v> Vencido</v>
       </c>
     </row>
     <row r="531" xml:space="preserve">
       <c r="A531" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) requiere asistencia médica en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
+        <v xml:space="preserve"> Se acabó el tiempo para la misión (Nombre del objetivo). Los Skav tienen un retraso considerable en el pago a los Cazadores de cabezas, así que necesito que los elimines. Mátalos, no los golpees, por si no queda claro. Alguien vio recientemente a la misión (Apellido del objetivo) cerca de la ubicación (Dirección), así que dirígete allí y elimínalos. Aviso importante: hemos recibido informes de que usaron parte de nuestros créditos para contratar protección adicional. Prepárate. Se esconde.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v> Transporte personal</v>
+        <v> Aviso de cobro</v>
       </c>
     </row>
     <row r="533" xml:space="preserve">
       <c r="A533" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) solicita transporte desde ~mission(InitiatorLocation) hasta ~mission(SelectedDestination). Al completar con éxito este servicio, recibirá ~mission(PaymentAmount) aUEC.</v>
+        <v xml:space="preserve">~mission(TargetName) tomó prestados varios créditos de los Headhunters y pensó que lo más inteligente era intentar esconderse en lugar de devolvernos el dinero, así que necesito que alguien haga un escarmiento a ~mission(TargetName|Last). Acaban de ser vistos en ~mission(Location|Address), así que recomiendo ir allí ahora antes de que se pierda el rastro. ~mission(TargetName|Last) es una persona paranoica, así que no te sorprendas si no está solo. Haz lo que quieras, siempre y cuando ~mission(TargetName|Last) sea polvo cuando termines. Se esconde.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v> Rescate médico</v>
+        <v> Ataque preventivo</v>
       </c>
     </row>
     <row r="535" xml:space="preserve">
       <c r="A535" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) requiere tratamiento médico de emergencia en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
+        <v xml:space="preserve">Los Headhunters recibieron información de que se está preparando una operación XenoThreat dirigida contra uno de nuestros equipos. No tenemos detalles precisos sobre el plan, pero sabemos que ~mission(TargetName) lo está organizando. En lugar de quedarnos de brazos cruzados esperando a que algo suceda, hemos decidido actuar de forma proactiva. ~mission(TargetName|Last) acaba de ser visto con otros cerca de ~mission(Location|Address). No podemos movilizar a nadie lo suficientemente rápido para que lleguen allí. Quiero que vayas corriendo y lances un ataque preventivo. Stows out.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v> Eliminar Claimjumpers</v>
+        <v> Venganza</v>
       </c>
     </row>
     <row r="537" xml:space="preserve">
       <c r="A537" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Acabamos de recibir la noticia de que un contratista de Shubin fue expulsado de una de nuestras concesiones por forajidos que operan allí ilegalmente. Para complicar aún más las cosas, han instalado algunos centinelas orbitales para protegerse mientras extraen minerales. Esperamos contratar a un mercenario que pueda buscar y destruir los centinelas en ~mission(location). Si se encuentra con un minero ilegal en el sitio, tenga en cuenta que es práctica común que este tipo de personas contacten refuerzos para pedir ayuda. Podría ser mejor neutralizarlos lo más rápido posible antes de que puedan hacerlo. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">XenoThreat atacó recientemente un bastión de Headhunters. Les ahorraré los detalles, pero le hicieron algo realmente atroz a nuestro equipo. Hemos identificado al líder de la operación como ~mission(TargetName) y buscamos venganza. No nos importa lo que hagan para lograrlo. Solo que ~mission(TargetName|Last) esté muerto. Una fuente nos acaba de decir que pueden rastrear a este canalla de XenoThreat en ~mission(Location|Address). Este enfermo es un profesional y nunca viaja solo, así que no esperen que eliminarlo sea pan comido. Se esconde.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v> Expulsar a los usurpadores de derechos</v>
+        <v> Justicia exacta</v>
       </c>
     </row>
     <row r="539" xml:space="preserve">
       <c r="A539" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) CONDICIONES*: Un equipo minero independiente local de Stanton estaba trabajando en ~mission(Location) como contratistas de Shubin Interstellar cuando una fuerza hostil atacó y tomó el sitio. Creemos que los perpetradores todavía están en la mina usando el equipo que dejaron para extraer el valioso mineral. Entre el equipo perdido había un puñado de centinelas orbitales que, desafortunadamente, aún no se habían desplegado por completo en el momento del ataque. Los escaneos de largo alcance de la mina nos han llevado a concluir que los forajidos han activado los centinelas orbitales y los están usando para proteger sus operaciones ilegales. Para recuperar el sitio, estamos buscando contratistas que vayan a ~mission(Location), destruyan los centinelas orbitales y limpien el sitio de mineros hostiles. Se recomienda encarecidamente la eficiencia, ya que existe un alto riesgo de que pidan refuerzos una vez que descubran que están siendo desalojados. Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+        <v xml:space="preserve">Recientemente se reveló que ~mission(TargetName) era un topo de XenoThreat. Ahora todo tiene sentido porque el skav era un verdadero cabrón. Desafortunadamente, se separaron antes de que pudiéramos encargarnos nosotros mismos. Basándonos en todo lo que aprendieron sobre nuestras operaciones, necesitamos eliminarlos cuanto antes. Si nos ven venir, simplemente volverán a huir, pero pensé que alguien como tú tiene más posibilidades de acercarse lo suficiente para un disparo mortal. Acabamos de enterarnos de que ~mission(TargetName|Last) andaba por ~mission(Location|Address). Parece que también hay otras naves protegiéndolos. ¿Crees que tienes la habilidad para librar al universo de un bastardo traidor y sus amigos bastardos? Esconderse.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Eliminar a los saltadores de reclamaciones</v>
-      </c>
-    </row>
-    <row r="541" xml:space="preserve">
-      <c r="A541" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Recientemente se descubrió que un minero renegado se apropió ilegalmente de una concesión minera de Shubin. Si bien el minero ya no parece estar robando mineral del sitio, dejó un centinela orbital que nos impide recuperarlo debido a sus capacidades ofensivas. Buscamos un mercenario dispuesto a viajar a ~mission(location), dar caza al centinela y destruirlo para preparar la recuperación del sitio por parte de Shubin. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
+        <v> Una pequeña represalia</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v> Una pequeña represalia</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v> Expulsar a los usurpadores de derechos</v>
-      </c>
-    </row>
-    <row r="543" xml:space="preserve">
-      <c r="A543" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar deseable) CONDICIONES*: Se descubrió que una concesión minera de Shubin Interstellar, recientemente adquirida y pendiente de procesamiento, había sido usurpada por una compañía minera renegada que está robando mineral del sitio. Si bien se ha notificado a las autoridades locales, existe la preocupación de que se puedan extraer activos valiosos antes de que se inicie una investigación oficial. Por lo tanto, como es nuestro derecho como titulares de la concesión, deseamos contratar una fuerza mercenaria para que se dirija a ~mission(Location) y destruya los centinelas orbitales que protegen esta operación ilegal. Se recomienda precaución, ya que aún podría haber algunos mineros ilegales en el lugar, junto con cualquier refuerzo que reúnan. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
+        <v> Eliminando algo de basura XenoThreat</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v> Eliminando algo de basura XenoThreat</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Desguace ~misión(NombreObjetivo)</v>
+        <v> Expulsando a CFP</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v> No tengo tiempo que perder, así que iré directo al grano: ~mission(TargetName) tiene que morir y quiero que lo hagas tú. Puedes encontrarlo cerca de ~mission(Location) en ~mission(Location|address). No estará solo, pero no te distraigas con esos otros inútiles. Solo te pagan por eliminar a ~mission(TargetName|Last).</v>
+        <v> Expulsando a CFP</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v> Misión de demolición</v>
-      </c>
-    </row>
-    <row r="547" xml:space="preserve">
-      <c r="A547" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Quiero enviar un mensaje contundente al equipo de ~mission(Location|Address) y sé la manera perfecta de hacerlo: causando daños materiales. Solo tienen que ir, destrozar algunas cosas y dejarles bien clara la importancia de respetar a los superiores. Si lo hacen, me sentiré muy feliz. Y generoso. ¿Les interesa?</v>
+        <v> Limpiar y despejar algunos lugares frecuentados por CFP</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v> Limpiar y despejar algunos lugares frecuentados por CFP</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v> Toma peligrosa</v>
-      </c>
-    </row>
-    <row r="549" xml:space="preserve">
-      <c r="A549" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tenía la esperanza de que te interesara hacer un pequeño trabajo para nosotros. Hay algunas cosas en ~mission(Location|Address) que están listas para ser tomadas. El único problema es, y es uno grande, que los desgraciados que dirigen el lugar tienen toda la zona sembrada de minas de proximidad. Tendrás que encontrar la manera de pasar, o si no te apetece, la manera de activarlas. En cualquier caso, intenta no volarte por los aires. Luego solo tienes que coger las cosas y llevarlas a ~mission(Destination|Address). No será fácil, pero si lo consigues, te prometo que merecerá la pena.</v>
+        <v> Tomando el territorio de XenoThreat</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v> Tomando el territorio de XenoThreat</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v> Venganza 01 (En desarrollo)</v>
+        <v> Golpea un complejo CFP</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v> Descripción de la misión (en desarrollo)</v>
+        <v>Golpea un complejo CFP</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v> Tutorial - Tus primeros pasos</v>
-      </c>
-    </row>
-    <row r="553" xml:space="preserve">
-      <c r="A553" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Enhorabuena por tus primeros pasos en el universo! A lo largo de este tutorial, aprenderás a moverte tanto a pie como en el espacio. Para empezar, te familiarizarás con los controles básicos de movimiento y el uso de tu mobiGlas dentro de tu hábitat. Sigue los objetivos y las indicaciones de tu HUD (pantalla de visualización frontal) para completar esta misión.</v>
+        <v> Desmantelando un escondite de XenoThreat</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v> Desmantelando un escondite de XenoThreat</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v> Tutorial - Tu primera salida</v>
-      </c>
-    </row>
-    <row r="555" xml:space="preserve">
-      <c r="A555" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Bien hecho! Con la primera parte completada, ya deberías tener cierta familiaridad con los controles de movimiento, la gestión de tu hambre y sed, y algunas de las funciones principales de tu mobiGlas, concretamente el Gestor de Contratos y tu Diario. Esta siguiente sección te ayudará a familiarizarte con ~mission(Location|Name) y te llevará a visitar ~mission(StoreName), una tienda de armas aquí en ~mission(Location|Name). Puedes comprar allí, y en otras tiendas similares, usando Créditos de la Tierra Unida (UEC). Durante la fase alfa del desarrollo de Star Citizen, utilizaremos una moneda llamada aUEC (Créditos de la Tierra Unida Alfa). Esta es una moneda temporal diseñada específicamente para probar la economía y el equilibrio del juego.</v>
+        <v> Es hora de empezar con CFP</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v> Es hora de empezar con CFP</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v> Tutorial - Tu primer vuelo</v>
-      </c>
-    </row>
-    <row r="557" xml:space="preserve">
-      <c r="A557" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ya casi terminas el tutorial. ¡Solo queda despegar! Con tu misión en ~mission(Location|Name) terminada, es hora de abandonar la ciudad y, finalmente, el planeta. Dirígete a las lanzaderas de tránsito de ~mission(TransitNameShort). Estas lanzaderas te pueden llevar por toda ~mission(Location|Name), pero tu destino es el puerto espacial, donde te han proporcionado temporalmente una Anvil C8 Pisces. Esta nave de exploración es una excelente nave de iniciación, perfecta para pilotos novatos que buscan obtener sus alas.</v>
+        <v> ¡A la carga!</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v> ¡A la carga!</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v> Ruta de envío local de UDM</v>
-      </c>
-    </row>
-    <row r="559" xml:space="preserve">
-      <c r="A559" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, socio de envíos calificado! Hoy es el día perfecto para adquirir experiencia práctica en envíos. Si dispone de un barco con suficiente espacio de almacenamiento, hay una buena cantidad de paquetes en ~mission(Pickup1) en ~mission(Pickup1|Address) listos para ser entregados. ¡Una excelente oportunidad para el crecimiento profesional! PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
+        <v> Golpear en el comando XenoThreat</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v> Golpear en el comando XenoThreat</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Controlador de paquetes UDM</v>
+        <v> Eliminar a los espías</v>
       </c>
     </row>
     <row r="561" xml:space="preserve">
       <c r="A561" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, experto en manipulación de paquetes! Aunque no tengan que ir muy lejos, los siguientes paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; requieren un manejo experto. ¿Eres el experto que buscamos? PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Solo tienes que aceptar el contrato y listo. Esperamos trabajar contigo, Unified Distribution Management -Ofreciendo el paquete completo-</v>
+        <v xml:space="preserve"> Algún imbécil está intentando desenterrar trapos sucios de los Headhunters. Se desplegaron algunos centinelas orbitales en ~mission(location|address) para espiarnos. También hemos visto una nave vigilándolos. Una propuesta sencilla para ti: ve a eliminar a los centinelas y te pagaremos por ello. ¿Te interesa? En cuanto a la nave, puedes hacer lo que quieras con ella, pero si te detecta, no te sorprendas si intenta buscar refuerzos. Así son estas cosas. Se esconde.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v xml:space="preserve">Ruta de entrega local de UDM</v>
+        <v> Exterminar a los espías</v>
       </c>
     </row>
     <row r="563" xml:space="preserve">
       <c r="A563" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! ¿Busca una excusa para surcar los cielos con su nave de carga? Gane créditos y explore la zona con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si ser su propio supervisor y que le paguen por pilotar su propia nave le parece el trabajo perfecto, este contrato es justo lo que estaba buscando. Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
+        <v xml:space="preserve">Algunos idiotas creen que pueden espiar descaradamente a los Headhunters y salirse con la suya. Han instalado varios centinelas orbitales en ~mission(location|address) y tienen algunas naves patrullando la zona. No sabemos quién está detrás de esto, pero sinceramente no nos importa. Solo necesitamos que desaparezcan. Avísanos si te apetece poner en su sitio a esos descarados. Te pagaremos bien y te daremos los créditos en cuanto termines el trabajo. Ten en cuenta que solo nos preocupan los centinelas. Las naves que tienen patrullando solo son un problema si se interponen en tu camino o si intentan llamar a algunos amigos para detenerte.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v> Evaluación de la entrega local de UDM</v>
+        <v> Borrar espía</v>
       </c>
     </row>
     <row r="565" xml:space="preserve">
       <c r="A565" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, potencial socio de envío cualificado! ¿Listo para contribuir a nuestra creciente red de entregas? ¿Tienes una nave a tu disposición que pueda transportar varios paquetes y volar entre cuerpos celestes y satélites? ¡Unified Distribution Management busca un piloto como tú! Nos encantaría evaluar tu potencial de contratación con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si esto te interesa, ¡acepta esta oferta de inmediato! Solo asegúrate de traer tu propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar contigo, Unified Distribution Management -Entregando el paquete completo-</v>
+        <v xml:space="preserve"> Tenemos un pequeño problema que los Headhunters deben solucionar. Hay una torreta orbital en ~mission(location|address) que algún pequeño alborotador instaló para espiar nuestras operaciones. ¿Quieres ganar algo de dinero fácil y volarla por nosotros? ¡Adelante!</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v> Reevaluación de la entrega local de UDM</v>
+        <v> Erradicar a los espías</v>
       </c>
     </row>
     <row r="567" xml:space="preserve">
       <c r="A567" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, antiguo socio naviero cualificado! ¿Estás listo para otra oportunidad de usar tu buque listo para el transporte de carga y ganar créditos? Unified Distribution Management ha elegido el siguiente itinerario cuidadosamente seleccionado como la manera perfecta de reevaluar sus habilidades: PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos volver a trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
+        <v xml:space="preserve">Los Headhunters buscan un mercenario para que nos ayude con un poco de limpieza. Descubrimos que alguien está intentando espiarnos en ~mission(location|address). No podemos permitirlo. Necesitamos un operador experto para que se encargue de los centinelas orbitales que desplegaron allí y, si es necesario, de cualquier nave que se interponga en tu camino. Parece una operación bien organizada, así que conseguirla puede no ser fácil, pero seguro que será divertido. Avísanos si eres el indicado. Los créditos se transferirán una vez que nuestros escaneos confirmen que se ha ido. Se esconde.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Recogida de paquetes UDM</v>
-      </c>
-    </row>
-    <row r="569" xml:space="preserve">
-      <c r="A569" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! Si buscas trabajo como repartidor, ¡tenemos la oportunidad perfecta para ti! Un paquete te espera en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser entregado en &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. ¿Suena interesante, verdad? Advertencia: se han registrado varias alertas de seguridad en la zona. Asegúrate de llevar contigo medidas de protección para mantenerte a salvo. Si esto te interesa, ¡acepta esta oferta de inmediato! Esperamos trabajar contigo. Unified Distribution Management -Entregando el paquete completo-</v>
+        <v> Recuperemos Carvers Ridge</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v> Recuperemos Carvers Ridge</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v> Todas las cosas llegan a su fin.</v>
-      </c>
-    </row>
-    <row r="571" xml:space="preserve">
-      <c r="A571" t="str" xml:space="preserve">
-        <v xml:space="preserve">No sé si conoces ~mission(Location|Address), pero ~mission(TargetName) es quien manda allí. Necesito eliminarlos. Me temo que es más fácil decirlo que hacerlo. Son conocidos por su renuencia a ocuparse personalmente de los asuntos, prefiriendo que sus subordinados se encarguen del trabajo sucio. Dicho esto, si eliminas a suficientes subordinados, no les quedará más remedio que enfrentarse a ti directamente. Atentamente, Vaughn</v>
+        <v> Concentración en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v> Concentración en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v> Se les echará de menos.</v>
-      </c>
-    </row>
-    <row r="573" xml:space="preserve">
-      <c r="A573" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un alto funcionario de seguridad llamado ~mission(TargetName) ha sido marcado para su eliminación. Aunque se encuentra en ~mission(Location|Address), no será fácil llegar hasta él. Me temo que será necesario un esfuerzo considerable para atraerlo. Normalmente, recomendaría eliminar a suficientes subordinados como para que se vea obligado a enfrentarse a usted personalmente. Sin embargo, en este caso se requiere un enfoque más delicado. Si bien puede eliminar a todas las fuerzas de seguridad presentes, debe garantizar la seguridad de todos los trabajadores civiles. Sin duda, es una tarea ardua, pero necesaria. Atentamente, Vaughn</v>
+        <v> El centro de la ciudad está bajo ataque.</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v> El centro de la ciudad está bajo ataque.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v> Una oportunidad para impresionar</v>
-      </c>
-    </row>
-    <row r="575" xml:space="preserve">
-      <c r="A575" t="str" xml:space="preserve">
-        <v xml:space="preserve">En primer lugar, permítame presentarme. Para decirlo de forma un tanto dramática, me dedico a la vida. La gente me contrata cuando hay que eliminar a alguien, y yo, a cambio, empleo a la persona perfecta para hacerlo. Esto proporciona seguridad a todas las partes involucradas, ya que nadie conoce la identidad de la otra. Una situación ideal en estos casos. Recientemente me enteré de que usted podría poseer habilidades que me serían útiles y decidí que valdría la pena investigar esta afirmación. Si le interesa establecer una relación laboral, necesitaré una demostración de dichas habilidades. Busque y elimine discretamente a ~mission(TargetName) en ~mission(Location|Address). Si lo logra, será recompensado. Además, habrá demostrado ser digno de ser considerado para futuras contrataciones. Atentamente, Vaughn</v>
+        <v> No dejes que caiga la caída del viento</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v> No dejes que caiga la caída del viento</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v> Otra oportunidad para impresionar</v>
-      </c>
-    </row>
-    <row r="577" xml:space="preserve">
-      <c r="A577" t="str" xml:space="preserve">
-        <v xml:space="preserve">No es frecuente en la vida tener una segunda oportunidad para causar una buena primera impresión, pero te la voy a brindar. Decir que me decepcionó cómo se desarrollaron las cosas en tu último intento de asesinato sería quedarse corto. Sin embargo, esta es tu oportunidad para demostrar que eres capaz de más. Elimina a ~mission(TargetName) en ~mission(Location|Address) y consideraré que has borrado el pasado. Atentamente, Vaughn</v>
+        <v> Detengamos la expansión de la amenaza alienígena</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v> Detengamos la expansión de la amenaza alienígena</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v> Localizar a un miembro de la pandilla</v>
-      </c>
-    </row>
-    <row r="579" xml:space="preserve">
-      <c r="A579" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de nivel Clips de la banda Headhunters, ~mission(TargetName|Last) ha liderado operaciones dirigidas contra operativos, misiones e infraestructura de XenoThreat. Por estas transgresiones, XenoThreat pagará a cualquiera que logre localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto cerca de ~mission(Location|Address) hace poco. Si decide aceptar este contrato, diríjase a las coordenadas de inmediato. ~mission(TargetName|Last) sabe que lo estamos buscando y ha estado viajando con un escolta recientemente. No se sorprenda si no está solo. Especialista en Comunicaciones Engler</v>
+        <v> Se necesitan refuerzos en el puesto de avanzada.</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v> Se necesitan refuerzos en el puesto de avanzada.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v> Localiza al traidor</v>
-      </c>
-    </row>
-    <row r="581" xml:space="preserve">
-      <c r="A581" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). ~mission(TargetName|Last), un conocido miembro de la banda Headhunters, ha traicionado a la humanidad al ser un aliado alienígena conocido con quien mantiene relaciones tanto personales como comerciales. XenoThreat exige que estas relaciones traidoras cesen de inmediato antes de que traigan más influencia alienígena a Pyro. Recompensaremos a quien logre localizar y asesinar a ~mission(TargetName|Last) por estos crímenes contra la humanidad. ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
+        <v> Bloquear la expansión de XenoThreat</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v> Bloquear la expansión de XenoThreat</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v> Rastrear al espía</v>
-      </c>
-    </row>
-    <row r="583" xml:space="preserve">
-      <c r="A583" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de la banda Headhunters, ~mission(TargetName|Last) hackeó los sistemas de XenoThreat para robar información sobre nuestras operaciones y personal. El daño causado solo puede repararse asegurándonos de que ~mission(TargetName|Last) jamás vuelva a hacer algo así. Por eso, XenoThreat pagará a cualquiera que pueda localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: Escaneos recientes identificaron a ~mission(TargetName|Last) viajando con otras naves cerca de ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
+        <v>Brindar protección en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v> Brindar protección en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v> Centinelas del silencio</v>
-      </c>
-    </row>
-    <row r="585" xml:space="preserve">
-      <c r="A585" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nuestro movimiento de resistencia crece día a día, pero esto conlleva cierta atención no deseada. Escaneos recientes descubrieron centinelas orbitales en ~mission(location|address) y una nave patrullando. Creemos que esto forma parte de una campaña de espionaje contra XenoThreat, probablemente financiada por la UEE. Buscamos un mercenario experimentado dispuesto a destruir los centinelas cuanto antes. Dado que ya nos tienen vigilados, enviar a alguien ajeno a la organización llamaría menos la atención. Si aceptas el trabajo, recibirás tu pago inmediatamente una vez destruidos los centinelas. Ahora bien, aunque la nave patrulla no es el objetivo principal, sospechamos que si escapa podría tener refuerzos en reserva. Sería prudente neutralizarla cuanto antes. Si decides ayudarnos, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
+        <v> Detén el ataque rival en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v> Detén el ataque rival en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v> Aniquilar centinelas</v>
-      </c>
-    </row>
-    <row r="587" xml:space="preserve">
-      <c r="A587" t="str" xml:space="preserve">
-        <v xml:space="preserve">Escaneos recientes descubrieron varios centinelas orbitales y naves en ~mission(location|address). Creemos que forman parte de una campaña de espionaje contra XenoThreat, en respuesta a nuestras acciones recientes en el sistema Stanton. Parece que XenoThreat está haciendo algo bien, si están espiando de esta manera. Buscamos un mercenario experimentado y altamente capacitado dispuesto a eliminar esta operación. Si no quieres que Pyro se convierta en un sistema de vigilancia, esta es tu oportunidad para impedirlo. Los centinelas probablemente no representen un gran problema, pero ten cuidado con las naves de patrulla. Si logran escapar, tendrás muchos más problemas pisándote los talones. Te estaremos agradecidos y te pagaremos generosamente una vez que completes el trabajo. Especialista en Comunicaciones Engler</v>
+        <v> Asegurar la misión (ubicación) de los advenedizos</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v> Asegurar la misión (ubicación) de los advenedizos</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v> Finalización de la vigilancia</v>
-      </c>
-    </row>
-    <row r="589" xml:space="preserve">
-      <c r="A589" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parece que nuestra lucha por liberar a la humanidad tiene nerviosos a los lacayos del gobierno en la Tierra. Escaneos recientes descubrieron un centinela orbital en ~mission(location|address) que creemos forma parte de una campaña de espionaje de la UEE. Según nuestros informes, están entregando los datos directamente a los propios slinks. Solo se ha detectado un centinela hasta ahora, pero quién sabe hasta dónde llegará la operación si no se desactiva. No debería ser demasiado problema para un mercenario habilidoso. Si te identificas con esto, recibirás el pago inmediatamente después de destruir el centinela. Además, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
+        <v> Guardia ~misión(Ubicación) De Rivales</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v> Guardia ~misión(Ubicación) De Rivales</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v> Erradicar centinelas</v>
-      </c>
-    </row>
-    <row r="591" xml:space="preserve">
-      <c r="A591" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Valoras la libertad de la humanidad? Si es así, te ofrezco la oportunidad de demostrarlo. Escaneos recientes han detectado centinelas orbitales y naves patrullando en ~mission(location|address). Creemos que forman parte de una campaña de espionaje de la UEE contra XenoThreat. Es crucial detener su labor de recopilación de inteligencia antes de lanzar nuestra próxima misión. Buscamos un mercenario experimentado dispuesto a eliminar estas fuerzas de inmediato. Los centinelas son la prioridad, pero las naves podrían representar un problema mayor si logran escapar. Deberás evaluar la situación con más detalle una vez que estés en el lugar. Podríamos encargarnos nosotros mismos, pero preferimos enviar a un contratista para que los responsables no sepan quién los atacó. El pago se realizará puntualmente al finalizar la misión. Además, tendrás la satisfacción de saber que estás ayudando a una buena causa. Especialista en Comunicaciones Engler</v>
+        <v> Mantén ~misión(ubicación) a salvo</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v> Mantén ~misión(ubicación) a salvo</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v> Borrado total del servidor</v>
-      </c>
-    </row>
-    <row r="593" xml:space="preserve">
-      <c r="A593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de nuestros agentes de datos desapareció mientras transportaba información operativa vital. Hace unas horas, determinamos que fue atacado por un grupo de asalto de Headhunters y que el contenido de los almacenes de datos de la nave fue transferido a sus servidores en ~mission(location|address). Si bien tenemos motivos para creer que nuestro cifrado resistirá, no podemos arriesgarnos a que el contenido de esos archivos quede expuesto. Se le ordena dirigirse allí y garantizar la privacidad de nuestros datos destruyendo los servidores de Headhunters. Le recomiendo encarecidamente que actúe con la máxima minuciosidad. Destruya todo y a todos los que pueda. Especialista en Comunicaciones Engler</v>
+        <v> Defender ~misión(Ubicación) de los mercenarios</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v> Defender ~misión(Ubicación) de los mercenarios</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v> Sabotaje de la línea de suministro</v>
-      </c>
-    </row>
-    <row r="595" xml:space="preserve">
-      <c r="A595" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los supuestos “activistas” de salón de Ciudadanos por la Prosperidad siguen intentando extender su influencia por todo el sistema. Con tu ayuda, existe la oportunidad de desmantelar sus operaciones de raíz. El grupo utiliza ~mission(location|address) para distribuir suministros a independientes dispersos por todo el planeta. Si destruimos la ~mission(ship) ubicada allí, su red colapsará. Un bombardeo enviaría un mensaje claro, pero te dejo a ti la decisión sobre el método de destrucción. Especialista en Comunicaciones Engler</v>
+        <v> Necesitamos un bateador</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
+        <v> Necesitamos un bateador</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v> Orden de eliminación: "Ciudadanos" en ~mission(location)</v>
+        <v> Una rápida represalia</v>
       </c>
     </row>
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
-        <v xml:space="preserve">El grupo de instigadores que se autodenomina «Ciudadanos por la Prosperidad» ya no puede seguir difundiendo sus mentiras y propaganda impunemente. Como un claro recordatorio de quién controla realmente a Pyro, hemos emitido una orden de eliminación para erradicar toda presencia de «Ciudadanos» en ~misión(ubicación|dirección). Es probable que haya resistencia, pero esperamos que la resuelvan sin mayores dificultades. Sigan las instrucciones y recibirán una buena recompensa por su trabajo. Especialista en Comunicaciones Engler</v>
+        <v xml:space="preserve"> Oye, unos matones de poca monta se han atrincherado en ~mission(Location|Address). No les prestaríamos atención si no fuera porque esos arrogantes intentaron atacar un puesto de avanzada bajo nuestra protección. Los ahuyentamos sin mayores problemas, pero no podemos dejar que semejante falta de respeto quede impune. Nuestros agentes están ocupados con asuntos más importantes, así que nos gustaría que te encargaras de esto. ¡No te lo pierdas!</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v> Lucha por un Pyro gratis</v>
-      </c>
-    </row>
-    <row r="599" xml:space="preserve">
-      <c r="A599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los esfuerzos de XenoThreat por evitar que influencias externas infecten este sistema están siendo puestos a prueba por un grupo que se atreve a llamarse Ciudadanos por la Prosperidad. Un miembro destacado del grupo, ~mission(TargetName), ha establecido operaciones en ~mission(Location|Address) y ya está trabajando arduamente difundiendo sus mentiras y propaganda a cualquiera que quiera escuchar. Si queremos que Pyro permanezca independiente de la UEE y de la influencia alienígena, entonces debemos hacer algo al respecto ahora. Por eso XenoThreat está emitiendo una orden de eliminación para ~mission(TargetName|Last). Y sabiendo lo importantes que son para las operaciones de Ciudadanos por la Prosperidad, no me sorprendería que tuvieras que abrirte paso luchando contra un grupo de sus seguidores más fanáticos antes de siquiera tener la oportunidad de dispararles. Pero recuerda que ~mission(TargetName|Last) es tu objetivo, y el pago depende únicamente de que te asegures de eliminarlo. Especialista en Comunicaciones Engler</v>
+        <v> Visitar un sitio CFP</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v> Visitar un sitio CFP</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v> Búsqueda de talentos</v>
-      </c>
-    </row>
-    <row r="601" xml:space="preserve">
-      <c r="A601" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Cazadores de Cabezas han reunido un equipo de ataque especial cuyo único propósito es atacar, interrumpir y sabotear nuestras operaciones. Aunque me cueste admitirlo, han tenido algunos éxitos menores y se están convirtiendo rápidamente en una preocupación. XenoThreat sabe que la mejor manera de matar a una serpiente es cortándole la cabeza, así que emitimos una orden de eliminación para el comandante del equipo de ataque, ~mission(TargetName), quien, según nuestras fuentes de inteligencia, se ha estado escondiendo en ~mission(Location|Address) durante algunos días. Preveo una fuerte resistencia por parte de las fuerzas de los Cazadores de Cabezas allí. Por lo que hemos oído, ~mission(TargetName|Last) recibió este mando en parte debido a la feroz lealtad que inspira en los demás. Reunir a tu propio equipo para abordar esto sería una sólida estrategia operativa. Feliz caza de cabezas, Especialista en Comunicaciones Engler</v>
+        <v>Buscando un poco de venganza</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v> Buscando un poco de venganza</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v> Robar subsidios</v>
-      </c>
-    </row>
-    <row r="603" xml:space="preserve">
-      <c r="A603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Típico de la UEE mentirosa, decir que no está involucrada en las operaciones de Ciudadanos por la Prosperidad simplemente porque "donan" suministros a una organización de ayuda terciaria que luego se los entrega inmediatamente. Acabamos de enterarnos de que uno de estos envíos de ayuda gubernamental fue entregado en un puesto avanzado alineado con Ciudadanos por la Prosperidad. Por eso te pagaremos para que asaltes ~mission(Pickup1|Address) y reclames el ~mission(item) para la causa. Una vez que entregues todo en ~mission(Dropoff1|Address), podremos redistribuir el envío para ayudar en nuestra lucha. No hay nada mejor que usar los recursos del enemigo en su contra. Pero no creas que te lo van a entregar así como así. Aunque se supone que Ciudadanos por la Prosperidad está aquí para traer la paz, será mejor que estés preparado para enfrentarte a ellos. Especialista en Comunicaciones Engler</v>
+        <v> Eliminar ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v> Eliminar ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v> Suministros para la recuperación de bienes</v>
-      </c>
-    </row>
-    <row r="605" xml:space="preserve">
-      <c r="A605" t="str" xml:space="preserve">
-        <v xml:space="preserve">Por mucho que XenoThreat se haya esforzado por hacer de Pyro un refugio seguro para los humanos, no todos comparten nuestros objetivos. Entre ellos destacan los Cazadores de Cabezas, que se han degradado al contratar a un transportista alienígena para que les entregue suministros. Perdimos la oportunidad de interceptar ese cargamento, pero aun así queremos dejar claro que no se tolerará la colaboración con alienígenas bajo ninguna circunstancia en este sistema. El cargamento fue entregado en ~mission(Pickup1|Address). Queremos que alguien ataque el puesto de avanzada, reclame el ~mission(item) y lo lleve a ~mission(Dropoff1|Address) para que podamos deshacernos de él adecuadamente. ¿Te animas a mantener Pyro libre de la influencia alienígena? Comm. Spec. Engler</v>
+        <v> Entregar un mensaje</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v> Entregar un mensaje</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v> Agente del Caos</v>
+        <v> Gestión de la reputación</v>
       </c>
     </row>
     <row r="607" xml:space="preserve">
       <c r="A607" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ciudadanos por la Prosperidad se han atrincherado en ~mission(Pickup1|Address). Para evitar que se acomoden demasiado en esa estación, queremos mostrarles cómo es realmente la vida en nuestro sistema. Te pagaremos para que vayas a la estación, recojas el ~mission(item) y mates a cualquiera que se interponga en tu camino. El pago depende de que entregues esos suministros en ~mission(Dropoff1|Address). Cualquiera que mates será una ventaja. Especialista en Comunicaciones Engler</v>
+        <v xml:space="preserve"> Unos cretinos se niegan a pagarnos lo que nos deben. El problema es que estos idiotas se jactan de ello. Si se hubieran callado, podríamos haber resuelto esto de forma más eficaz, pero ahora tenemos que dar un escarmiento. Estos imbéciles operan desde ~mission(Location|Address). Necesitamos que se vayan todos. ¡Que se oiga bien alto! Enviaremos el pago una vez que nos hayamos encargado de todos. - Se despide.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
+        <v> Muéstrales quién manda.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v> Muéstrales quién manda.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v> Muerte y carga</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v> Muerte y carga</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v> Una tarea muy complicada</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v> Una tarea muy complicada</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v> Golpea a XenoThreat en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v> Golpea a XenoThreat en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v> Guerra territorial</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v> Guerra territorial</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v> Luz verde en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v> Luz verde en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v> Saldar una cuenta pendiente</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v> Saldar una cuenta pendiente</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Se necesita una muerte en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v> Se necesita una muerte en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v> Impacto en el espacio profundo</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
+        <v> Impacto en el espacio profundo</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v> Necesitas un bisturí en Carver's</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
+        <v> Necesitas un bisturí en Carver's</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v> Disparado en medio del caos</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v> Disparado en medio del caos</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v> Objetivo pagado en CFP</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v> Objetivo pagado en CFP</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v> Necesito que me quiten el CFP</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v> Necesito que me quiten el CFP</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v> Tapón a un traidor</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v> Tapón a un traidor</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v> Matad al rey</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v> Matad al rey</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v> Necesito que saquen a alguien.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v> Necesito que saquen a alguien.</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v> Luz verde en ~misión(NombreObjetivo|Apellido)</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v> Luz verde en ~misión(NombreObjetivo|Apellido)</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v> Fantasma ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v> Fantasma ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v> Necesitas un éxito en la Riviera</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v> Necesitas un éxito en la Riviera</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v> Golpe a XenoThreat en el Yard</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v> Golpe a XenoThreat en el Yard</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v xml:space="preserve"> Listos para la retribución</v>
+      </c>
+    </row>
+    <row r="649" xml:space="preserve">
+      <c r="A649" t="str" xml:space="preserve">
+        <v xml:space="preserve">Me acaba de caer información interesante. Parece que el infame líder de XenoThreat, ~mission(TargetName), está escondido en ~mission(location|address) trabajando en una gran operación para ellos. Oportunidad perfecta para acabar con ese cabrón de una vez por todas. El problema es que los Xenos están vigilando todas las operaciones de Headhunter en este momento. No hay forma de que podamos movilizar y desplegar un equipo sin que ~mission(TargetName|Last) se entere. Así que te ofrezco la oportunidad de mejorar Pyro y ganar algo de crédito al mismo tiempo. Si te interesa, te sugiero que te equipes y busques refuerzos antes de salir. Solo te pagarán si eliminas a ~mission(TargetName|Last), pero no dudes en matar a cualquier otro XenoThug que pueda estar escondido allí con ellos. ¡Que se vayan!</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
+        <v> Cabeza de la serpiente</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v> Cabeza de la serpiente</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v> El teniente de XenoThreat necesita que lo maten.</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v> El teniente de XenoThreat necesita que lo maten.</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v> Lanza una amenaza xeno</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v> Lanza una amenaza xeno</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v> Se busca: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>Se busca: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
+        <v> Eliminación de objetivo para una vía rápida en</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v> Eliminación de objetivo para una vía rápida en</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v xml:space="preserve"> Objetivo en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v xml:space="preserve"> Objetivo en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v> Orden de matar</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v> Orden de matar</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v> Choca contra un barco de CFP</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v> Choca contra un barco de CFP</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v> Objetivo Primo</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v> Objetivo Primo</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v> Se busca: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v> Se busca: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
+        <v> Un golpe sencillo</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v> Un golpe sencillo</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v> Regálate una pelea</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v> Regálate una pelea</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v> ¿Quieres ser cazatalentos?</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v> ¿Quieres ser cazatalentos?</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v> Fantasma de XenoTrash</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v> Fantasma de XenoTrash</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v> Choquen algunos barcos</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v> Choquen algunos barcos</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v> La oportunidad llama a la puerta en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v> La oportunidad llama a la puerta en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v> Roba algo ~misión(objeto)</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v> Roba algo ~misión(objeto)</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v> Iniciativa Overdrive: OBJETIVOS PRIORITARIOS</v>
+      </c>
+    </row>
+    <row r="685" xml:space="preserve">
+      <c r="A685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nuestros analistas han examinado la información incautada a los equipos de reconocimiento de XenoThreat, pero los datos parecen estar protegidos por un sofisticado sistema de cifrado y requieren una clave criptográfica personalizada para acceder a ellos. Hemos logrado localizar a varios tenientes de XenoThreat que operan en el sistema; su misión es encontrar e interrogar a los sospechosos para determinar si poseen una clave criptográfica que nos permita acceder a la información. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de las Fuerzas de Defensa de Canadá que lleven esta iniciativa hasta el final.</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v> Iniciativa Overdrive: VIGILANCIA DE AMENAZAS XENOTRAS</v>
+      </c>
+    </row>
+    <row r="687" xml:space="preserve">
+      <c r="A687" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de los sospechosos capturados durante los recientes ataques reveló que XenoThreat busca acceder remotamente a varias antenas de comunicación en todo el sistema. Que XenoThreat esté interceptando las comunicaciones es extremadamente peligroso para la población local, por lo que se ha solicitado a la CDF que reinicie la antena de comunicación y la defienda de cualquier Vanguardia de XenoThreat que intente reconectarse a los servidores. Una vez derrotadas dichas Vanguardias, se eliminarán las naves hostiles restantes en la zona. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que completen esta iniciativa.</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v> Iniciativa Overdrive: INTEL RAID</v>
+      </c>
+    </row>
+    <row r="689" xml:space="preserve">
+      <c r="A689" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos recibido información de que XenoThreat planea lanzar otro ataque contra el sistema Stanton. La CDF ha solicitado a la organización Advocacy la creación de una nueva iniciativa, denominada Operación Overdrive, para detener este ataque antes de que se produzca. La CDF está enviando voluntarios para infiltrarse y obtener información que pueda revelar sus planes. Huelga decir que se espera una fuerte resistencia por parte de cualquier XenoThreat presente. Como incentivo adicional, las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v> Iniciativa Overdrive: INCURSIÓN DE AMENAZA XENÓCRATA</v>
+      </c>
+    </row>
+    <row r="691" xml:space="preserve">
+      <c r="A691" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Oleadas de naves de la Amenaza Xeno han estado invadiendo el sistema Stanton y atacando a civiles al azar. No podemos determinar si se trata de un ataque aislado o una reacción a nuestras iniciativas recientes, pero debemos detenerlas. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v> Iniciativa Overdrive: EMERGENCIA EN KAREAH</v>
+      </c>
+    </row>
+    <row r="693" xml:space="preserve">
+      <c r="A693" t="str" xml:space="preserve">
+        <v xml:space="preserve">Atención a todos los voluntarios de CDF: hemos recibido una llamada de auxilio del Puesto de Seguridad Kareah. Resulta que XenoThreat utilizó los sistemas de comunicaciones como distracción para alejar a las fuerzas del orden y así poder lanzar un ataque contra la estación. Hemos descubierto que están intentando acceder a sus sistemas, por lo que todos los voluntarios deben desviarse inmediatamente para retomar Kareah y eliminar a todas las fuerzas de XenoThreat. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v> Iniciativa Overdrive: SOLICITUD DE SUMINISTRO</v>
+      </c>
+    </row>
+    <row r="695" xml:space="preserve">
+      <c r="A695" t="str" xml:space="preserve">
+        <v xml:space="preserve">Atención, voluntarios de CDF: XenoThreat ha desaparecido. Sospechamos que se han desconectado para preparar la fase final de su plan. La historia demuestra que a XenoThreat le gusta luchar, así que es lógico pensar que podría tratarse de un ataque. Por ello, solicitamos voluntarios para entregar suministros a la estación Gateway, cerca del punto de salto Stanton-Pyro, para reforzar la defensa ante un posible asalto. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v> Iniciativa Overdrive: Recompensa</v>
+      </c>
+    </row>
+    <row r="697" xml:space="preserve">
+      <c r="A697" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Gracias por tu dedicación a esta Iniciativa Overdrive. Como prometimos, te hemos aprobado una mejora de una F7C mk ii civil a una F7A mk ii militar, si dispones de una. Además, se te ha proporcionado un alquiler temporal de una F7A mk ii militar a la que puedes acceder en tu ASOP. _________________ Para actualizar, visita la página web de RSI para aplicar el token, luego reinicia el juego y accede a la nave.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>Trata con los Kopions en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v> Trata con los Kopions en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v> Paquete de Kopion del carnicero en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v> Paquete de Kopion del carnicero en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v> Mata a los Kopions en ~mission(Ubicación)</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v> Mata a los Kopions en ~mission(Ubicación)</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v> Control de plagas</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v> Control de plagas</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v> Esfuerzo intensivo de erradicación</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v> Esfuerzo intensivo de erradicación</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v> Eliminar las criaturas invasoras</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v> Eliminar las criaturas invasoras</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v> Reducir la superpoblación</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v> Reducir la superpoblación</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v> Solicitud de eliminación de Kopion</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v> Solicitud de eliminación de Kopion</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v> Reducir la población de la estación de interruptores de Valakkar</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v> Reducir la población de la estación de interruptores de Valakkar</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v> Eliminar kopiones irradiados</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v> Eliminar kopiones irradiados</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v> Jorrit Dossier: Expedientes de Personal de Onyx</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v> Jorrit Dossier: Expedientes de Personal de Onyx</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v> Expediente Jorrit: Acceso a los archivos de ingeniería</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v> Expediente Jorrit: Acceso a los archivos de ingeniería</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v> Expediente Jorrit: Acceso a los archivos de investigación</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v> Expediente Jorrit: Acceso a los archivos de investigación</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v> Expediente Jorrit: Datos actualizados sobre anomalías energéticas</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>Expediente Jorrit: Datos actualizados sobre anomalías energéticas</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v> Expediente Jorrit: Datos de seguridad actualizados</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v> Expediente Jorrit: Datos de seguridad actualizados</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v> Expediente Jorrit: Datos sísmicos actualizados</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v> Expediente Jorrit: Datos sísmicos actualizados</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v> Expediente Jorrit: Datos actualizados sobre el consumo de energía</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v> Expediente Jorrit: Datos actualizados sobre el consumo de energía</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v> Recompensa esquiva: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="733" xml:space="preserve">
+      <c r="A733" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGOS: Objetivo de alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Esta recompensa ha resultado extremadamente escurridiza hasta ahora, pero los informes de inteligencia han rastreado al objetivo y a un grupo de sus asociados conocidos hasta ~mission(Location|Address). Sin embargo, hay una alta probabilidad de que ~mission(TargetName|Last) no se arriesgue a una confrontación a menos que se vea absolutamente obligado a ello. Recomendamos que primero neutralice a una parte significativa de los aliados del criminal para atraerlos. El informe indica que un gran grupo de estos hostiles se encuentra actualmente cerca de ~mission(Location). El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>Recompensa atrincherada: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="735" xml:space="preserve">
+      <c r="A735" t="str" xml:space="preserve">
+        <v xml:space="preserve"> DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensa AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: L. Paleski EVALUACIÓN DE RIESGO: Objetivo de riesgo moderado (posible apoyo armado) CONTRATO URGENTE: No Hurston Dynamics busca un contratista para completar una recompensa para ~mission(TargetName). Los informes de inteligencia han localizado el paradero actual del objetivo en ~mission(Location|Address). Si bien tiene autorización para interactuar con cualquier delincuente en el lugar como considere oportuno, se debe proteger a cualquier civil presente en el lugar. El pago se realizará únicamente después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v> Recompensa evasiva: ~misión(Nombre del objetivo) (VHRT)</v>
+      </c>
+    </row>
+    <row r="737" xml:space="preserve">
+      <c r="A737" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGO: Objetivo de muy alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Se ha informado que este objetivo y la gran fuerza hostil con la que viaja han atacado recientemente ~mission(Location|Address). Sin embargo, si su modus operandi es el correcto, ~mission(TargetName|Last) generalmente se ha mantenido oculto durante los ataques, prefiriendo dirigir sus fuerzas desde lejos. Recomendamos que se concentre primero en reducir el número de sus aliados, y una vez que sus números se hayan debilitado significativamente, ~mission(TargetName|Last) no tendrá más remedio que enfrentarlo directamente. El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>Se busca: ~misión(Nombre del objetivo) (LRT)</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v> Se busca: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v xml:space="preserve"> Evaluación de contratistas de cazarrecompensas</v>
+      </c>
+    </row>
+    <row r="743" xml:space="preserve">
+      <c r="A743" t="str" xml:space="preserve">
+        <v xml:space="preserve">DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Después de repetidos y continuos delitos menores, se ha emitido una recompensa por la siguiente persona: ~mission(TargetName). Para evaluar su potencial para ayudar en la captura de criminales más escurridizos, Hurston Dynamics evaluará su capacidad para localizar y aprehender a ~mission(TargetName|Last) por cualquier medio a su disposición. La información más reciente sobre el paradero actual de ~mission(TargetName|Last) indica que fue visto por última vez en ~mission(Location|Address). El pago se liberará solo después de que se haya resuelto la recompensa. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>Se busca: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v xml:space="preserve"> Reevaluación del contratista de cazarrecompensas</v>
+      </c>
+    </row>
+    <row r="747" xml:space="preserve">
+      <c r="A747" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Nuestro departamento realiza reevaluaciones periódicas de antiguos cazadores de recompensas y ha determinado que usted puede ser un candidato adecuado para una posible reincorporación. Como demostración de su idoneidad, capture con éxito al siguiente individuo buscado: ~mission(TargetName). La información más reciente sobre el paradero actual de ~mission(TargetName|Last) es que fue visto por última vez en ~mission(Location|Address). La reincorporación como cazador de recompensas de Hurston Dynamics y el pago se producirán tras la finalización exitosa de este contrato. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>Se busca: ~misión(Nombre del objetivo) (ERT)</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v> Se busca: ~misión(Nombre del objetivo) (VLRT)</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v> Se busca: ~misión(Nombre del objetivo) (VHRT)</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v> Neutralizar la incursión de forajidos</v>
+      </c>
+    </row>
+    <row r="755" xml:space="preserve">
+      <c r="A755" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Neutralización de Fuerzas Hostiles GERENTE DE SUBCONTRATACIÓN: T. Dalik EVALUACIÓN DE RIESGO: Alto Nuestras fuerzas de seguridad han sido notificadas de una incursión de delincuentes en curso en ~mission(Ubicación|Dirección), y necesitamos un operador independiente capaz de desalojar a los actores hostiles. Según el personal en el lugar, los delincuentes se encuentran actualmente atrincherados cerca de ~mission(Ubicación). Proceda con precaución y esté preparado para usar fuerza letal si los delincuentes se resisten a ser desalojados. El pago solo se autorizará una vez que la ubicación haya sido despejada de manera efectiva. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v> Recompensa localizada: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="757" xml:space="preserve">
+      <c r="A757" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: T. Davik EVALUACIÓN DE RIESGOS: Riesgo moderado Hurston Dynamics busca un contratista para completar una recompensa por la misión ~(Nombre del objetivo). Los informes de inteligencia han rastreado al objetivo hasta ~(Ubicación|Dirección), donde fue visto por última vez cerca de ~(Ubicación). Prepárese para que oponga resistencia a la detención y para el uso de fuerza letal si fuera necesario. El pago se realizará únicamente después de que la recompensa se considere completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v> Erradicar todos los nidos</v>
+      </c>
+    </row>
+    <row r="759" xml:space="preserve">
+      <c r="A759" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar varios nidos que han impedido que los departamentos inspeccionen las cuevas pertinentes en busca de recursos. Estamos dispuestos a ofrecer una generosa remuneración por la erradicación de estas plagas. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v> Exterminar Nido de ~misión(Criatura)</v>
+      </c>
+    </row>
+    <row r="761" xml:space="preserve">
+      <c r="A761" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar a ~mission(Criatura) que se ha instalado en ~mission(ubicación|dirección). Se han convertido en un problema y necesitamos un profesional para resolver la situación. El pago se realizará una vez que se haya eliminado el nido. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v xml:space="preserve"> Proteger el sitio y recuperar materiales confidenciales.</v>
+      </c>
+    </row>
+    <row r="763" xml:space="preserve">
+      <c r="A763" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Inspección de instalaciones y recuperación de paquetes AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: Sí Hurston ha sabido que los Nine Tails están atacando ~mission(Location|address). Nuestras fuerzas en el sitio han sufrido numerosas bajas y han dejado de responder a las comunicaciones. Los informes iniciales indicaron que la banda estaba intentando obtener material confidencial entregado recientemente a las instalaciones. Afortunadamente, contamos con medidas de seguridad que deberían darnos tiempo para responder. Necesitamos que un agente se dirija a las instalaciones de inmediato, recupere esas cajas y las entregue en un lugar seguro. Usted y cualquier refuerzo que elija traer están autorizados a tomar las medidas necesarias al enfrentarse a los intrusos. Se considera que los sospechosos están armados y son peligrosos. Hurston no proporcionará apoyo material ni actualizaciones sobre el estado de las fuerzas de seguridad de las instalaciones. El material confidencial se entregó discretamente junto con otras cajas en un envío y se guardó en nuestra bóveda automatizada con códigos de acceso almacenados en tabletas electrónicas custodiadas por personal de seguridad de alto nivel. Sin embargo, existe una alta probabilidad de que Nine Tails ya se haya apoderado de él. Deberá encontrar esas tabletas electrónicas e introducir los códigos en la cinta transportadora de paquetes para recuperar el material confidencial. El pago se enviará una vez que se haya entregado en ~mission(dropoff1|address). ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como cualquier acción basada en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v xml:space="preserve">Informe de persona desaparecida: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="765" xml:space="preserve">
+      <c r="A765" t="str" xml:space="preserve">
+        <v xml:space="preserve"> CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Localización de persona desaparecida. GERENTE DE SUBCONTRATACIÓN: I. Takao. EVALUACIÓN DE RIESGO: Baja. El personal de ~mission(Ubicación|Dirección) ha presentado recientemente una denuncia por desaparición de ~mission(Nombre del objetivo). Esta persona lleva varios días desaparecida y fue vista por última vez dirigiéndose a ~mission(Ubicación). Se le contrata para realizar una búsqueda in situ de ~mission(Apellido del objetivo) e intentar determinar su paradero. El pago depende de la obtención de un registro de su ubicación actual, ya sea que se encuentre viva o fallecida. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v> Instalación de protección contra amenazas</v>
+      </c>
+    </row>
+    <row r="767" xml:space="preserve">
+      <c r="A767" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Una pequeña banda local ha estado profiriendo amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v> Instalación de vigilancia contra hostiles</v>
+      </c>
+    </row>
+    <row r="769" xml:space="preserve">
+      <c r="A769" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Delincuentes locales han estado realizando amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v> Instalación de vigilancia contra hostiles peligrosos</v>
+      </c>
+    </row>
+    <row r="771" xml:space="preserve">
+      <c r="A771" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Muy alta CONTRATO URGENTE: No Una creciente facción delictiva ha estado realizando amenazas contra ~mission(Location|Address) y Hurston Security requiere un contratista para formar un equipo de seguridad y proteger las instalaciones contra cualquier intrusión. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v> Eliminar el alijo de contrabando</v>
+      </c>
+    </row>
+    <row r="773" xml:space="preserve">
+      <c r="A773" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Delincuentes locales han estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de contrabando. Hurston Security requiere un contratista para que acuda a las instalaciones y destruya todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v> Eliminar el alijo de narcóticos</v>
+      </c>
+    </row>
+    <row r="775" xml:space="preserve">
+      <c r="A775" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Muy alta CONTRATO URGENTE: No Un pequeño grupo criminal ha estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de narcóticos altamente peligrosos. Hurston Security busca un contratista para que acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v> Eliminar el alijo de drogas</v>
+      </c>
+    </row>
+    <row r="777" xml:space="preserve">
+      <c r="A777" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Se ha identificado a delincuentes locales que utilizan ~mission(Location|Address) para fabricar grandes cantidades de contrabando ilegal. Hurston Security requiere que un contratista acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v> Ayudar en la defensa del sitio.</v>
+      </c>
+    </row>
+    <row r="779" xml:space="preserve">
+      <c r="A779" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No El personal de seguridad en ~mission(Location|Address) está siendo amenazado por un grupo criminal local y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente acceder al sitio. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v> Evaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="781" xml:space="preserve">
+      <c r="A781" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Un grupo criminal local ha estado amenazando ~mission(Location|Address) y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente entrar en las instalaciones. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en las instalaciones resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta evaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v> Reevaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="783" xml:space="preserve">
+      <c r="A783" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Nuestro departamento realiza reevaluaciones periódicas de los contratistas de seguridad anteriores y ha determinado que usted podría ser un candidato adecuado para una posible reincorporación. Para recuperar su estatus, Hurston Security busca contratistas que ayuden a eliminar un elemento criminal local que amenaza ~mission(Location|Address). Tenga en cuenta que solo está autorizado para interactuar con hostiles confirmados. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta reevaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>Desalojar a los ocupantes ilegales</v>
+      </c>
+    </row>
+    <row r="785" xml:space="preserve">
+      <c r="A785" t="str" xml:space="preserve">
+        <v xml:space="preserve"> CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Limpieza de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: K. Restle EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Hurston busca un contratista dispuesto a desalojar a los ocupantes criminales de ~mission(Location|Address). El sitio se ha utilizado para albergar numerosas actividades ilegales, por lo que es imperativo asegurarlo. Tenga en cuenta que solo está autorizado a interactuar con hostiles confirmados. Agredir a cualquier civil en el sitio se considerará una violación de su contrato. El pago se enviará una vez que se confirme que las instalaciones están despejadas. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v> Defienda al agente de InterSec</v>
+      </c>
+    </row>
+    <row r="787" xml:space="preserve">
+      <c r="A787" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Nave de Combate Informe: Se requiere asistencia urgente para un agente de InterSec que actualmente está bajo fuego en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Un grupo de forajidos había capturado previamente a nuestro agente con la intención de extraerle información confidencial, pero milagrosamente lograron escapar. Desafortunadamente, los forajidos que lo persiguen ahora lo tienen acorralado. Debido a la cantidad de naves que lo atacan, ofrecemos una compensación adicional para compensar el peligro adicional. &lt;EM4&gt;Reclutar naves adicionales&lt;/EM4&gt; para apoyarlo en esta misión es altamente recomendable. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>Proteja los activos vitales</v>
+      </c>
+    </row>
+    <row r="789" xml:space="preserve">
+      <c r="A789" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: Uno de nuestros pilotos está siendo atacado en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y necesita asistencia. Este operativo lleva información clave sobre un ataque coordinado a infraestructura clave de la UEE y es vital que pueda entregárnosla. Usted y cualquier &lt;EM4&gt;piloto confiable que pueda reclutar&lt;/EM4&gt; tienen la misión de protegerlo de los forajidos que lo persiguen el tiempo suficiente para que pueda escapar mediante QT. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v> Extracción quirúrgica</v>
+      </c>
+    </row>
+    <row r="791" xml:space="preserve">
+      <c r="A791" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: Un agente encubierto nuestro fue descubierto y ahora está siendo perseguido por la banda de forajidos en la que se había infiltrado. Por lo tanto, necesita ser extraído de inmediato en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Una vez en el sitio, interactúe con todos los hostiles para brindar cobertura y que nuestro agente pueda escapar mediante QT. &lt;EM4&gt;Traiga refuerzos adicionales&lt;/EM4&gt; y no subestime a estos forajidos. Son violentos y están motivados, por lo que es poco probable que se rindan pronto. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v> Cómo gestionar el ataque de Vanduul a la nave</v>
+      </c>
+    </row>
+    <row r="793" xml:space="preserve">
+      <c r="A793" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Nave de Combate Informe: Un operador que trabaja con InterSec está siendo atacado por naves Vanduul en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. La probabilidad de que sobrevivan por sí solos es baja, por lo que buscamos un contratista dispuesto a brindar apoyo en combate. Los contratistas que acepten esta misión deben estar bien equipados y listos para enfrentar la amenaza Vanduul de frente. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v> Piloto bajo fuego de Vanduul</v>
+      </c>
+    </row>
+    <row r="795" xml:space="preserve">
+      <c r="A795" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: Acabamos de perder contacto con un piloto que se enfrentó a fuerzas Vanduul en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Viaje a su última ubicación conocida y, si aún está vivo, defiéndalo el tiempo suficiente para asegurar que pueda escapar. Garantizar la seguridad del operativo es crucial, al igual que eliminar cualquier amenaza Vanduul para la UEE. Probablemente necesitará un grupo de &lt;EM4&gt;naves fuertes&lt;/EM4&gt; para neutralizar con éxito a estos Vanduul. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v> Terrorista ~misión(Nombre del objetivo) a neutralizar</v>
+      </c>
+    </row>
+    <row r="797" xml:space="preserve">
+      <c r="A797" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: InterSec ha identificado a más forajidos que planean una operación contra los intereses de la UEE desde Nyx. Su misión será neutralizar esta amenaza potencial antes de que puedan ejecutar sus planes. Viaje a &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; y envíe al líder de estos forajidos, &lt;EM4&gt;~mission(NombreObjetivo)&lt;/EM4&gt; sin dudarlo. Hemos explorado un pequeño número de naves, pero nuestro informe sugiere que son pilotos competentes; &lt;EM4&gt;se recomienda traer refuerzos.&lt;/EM4&gt; Recuerde que eliminar a estos forajidos no solo sirve a la gente de Nyx, sino también a la UEE. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>Ataque preventivo contra ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="799" xml:space="preserve">
+      <c r="A799" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: InterSec requiere un contratista experto para eliminar a un grupo de criminales altamente peligrosos con base en Nyx que planean un ataque coordinado contra un miembro prominente de la Armada de la UEE. Hemos interceptado información crucial que sugiere que un terrorista conocido llamado &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; pretende llevar a cabo este asesinato con la ayuda de elementos criminales locales. Actualmente se encuentran en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;, lo que hace que este sea el momento ideal para nuestro ataque. Tenga cuidado, estos forajidos son asesinos experimentados; se recomienda traer un &lt;EM4&gt;grupo de aliados de confianza&lt;/EM4&gt;. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>Nuevo contrato de defensa: ~misión(Nombre del objetivo) Eliminación</v>
+      </c>
+    </row>
+    <row r="801" xml:space="preserve">
+      <c r="A801" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha sido contratada para combatir el creciente número de forajidos que utilizan Nyx como base para sus operaciones, con la intención de atacar los sistemas UEE vecinos. Como medida preventiva, le solicitamos que viaje a &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y elimine al cabecilla &lt;EM4&gt;~misión(Nombre del Objetivo)&lt;/EM4&gt; para disuadir su ataque planeado contra Stanton. Él y su tripulación son altamente peligrosos y se le &lt;EM4&gt;aconseja que traiga un compañero&lt;/EM4&gt; para apoyo. Los contratistas que puedan demostrar ser confiables y competentes en la ejecución de operaciones serán elegibles para futuras misiones con InterSec. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>Neutralizar la amenaza UEE: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="803" xml:space="preserve">
+      <c r="A803" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: Aparentemente insatisfechos con sus ganancias en Nyx, un grupo de forajidos liderado por &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; ha estado planeando un ataque importante contra la UEE. Esto no puede permitirse. Gracias al trabajo de nuestro equipo de Inteligencia, hemos podido localizarlos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Diríjanse allí lo antes posible y ataquen antes de que tengan la oportunidad de abandonar el sistema. Con base en nuestro análisis estratégico, recomendamos que una flota &lt;EM4&gt;bien armada y capacitada&lt;/EM4&gt; será necesaria para el éxito de esta misión. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>Eliminar la nave Vanduul</v>
+      </c>
+    </row>
+    <row r="805" xml:space="preserve">
+      <c r="A805" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Nave de Combate Informe: InterSec requiere los servicios de un piloto experto que esté preparado para ayudar a derribar un peligroso objetivo Vanduul que ha estado involucrado en numerosos ataques. Las incursiones Vanduul han ido en aumento recientemente, lo que representa una amenaza no solo para el sistema Nyx, sino para la UEE en su conjunto. Es imperativo que estos avistamientos sean respondidos de manera rápida y eficiente. Requerimos que vuele al último avistamiento conocido de la nave Vanduul en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y los elimine de inmediato. Los pilotos Vanduul son altamente expertos y extremadamente peligrosos. Enfréntese al enemigo de inmediato y no dude; no mostrarán la misma piedad. Se otorgará una compensación proporcional al riesgo del contrato. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>Neutralizar objetivo Vanduul</v>
+      </c>
+    </row>
+    <row r="807" xml:space="preserve">
+      <c r="A807" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec necesita un piloto de combate altamente capacitado que pueda localizar y neutralizar un peligroso objetivo Vanduul. Un operador nuestro ha identificado una nave Vanduul volando en las cercanías de &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Hemos recibido instrucciones estrictas de eliminar cualquier Vanduul avistado en los límites del espacio UEE, por temor a una invasión del territorio del Imperio. Traiga una &lt;EM4&gt;pequeña flota de pilotos competentes&lt;/EM4&gt; para enfrentarse y neutralizar el objetivo. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>Recuperar cadáveres de Vanduul</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v> Recuperar cadáveres de Vanduul</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v> Recuperar Vanduul Tech</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v> Recuperar Vanduul Tech</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v> Patrulla en el sector peligroso</v>
+      </c>
+    </row>
+    <row r="813" xml:space="preserve">
+      <c r="A813" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha recibido información de inteligencia de que los forajidos planean lanzar un ataque contra un objetivo dentro de la UEE. En un esfuerzo por evitar que esto suceda, necesitamos un contratista para patrullar un sector que creemos que estos forajidos están usando para preparar su ataque. La actividad de los forajidos en este sector es mayor de lo normal, por lo que InterSec recomienda que &lt;EM4&gt;traiga refuerzos&lt;/EM4&gt;. Cuando esté listo, diríjase al &lt;EM4&gt;marcador de ubicación&lt;/EM4&gt; en su HUD y escanee los puntos de ruta a lo largo de la ruta. Una vez que haya confirmado que todo el sector está despejado, el contratista principal recibirá una bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>Patrulla el terreno de caza de Vanduul</v>
+      </c>
+    </row>
+    <row r="815" xml:space="preserve">
+      <c r="A815" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: Existe una creciente preocupación de que los grupos de caza Vanduul estén avanzando más en Nyx. La primera línea de defensa contra esta invasión es el aumento de patrullas. InterSec ha identificado un sector que ha visto un aumento en la actividad Vanduul y está buscando a alguien para patrullar la región y proporcionar una actualización al respecto. Comenzarás tu patrulla en un marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; enviado a tu HUD y luego escanearás una serie de puntos de ruta a lo largo de una ruta designada. Las naves Vanduul en este sector son altamente hábiles y agresivas, por lo que InterSec recomienda encarecidamente que &lt;EM4&gt;traigas varias naves listas para el combate como respaldo&lt;/EM4&gt;. InterSec comprende el inmenso peligro al que te enfrentarás en esta patrulla, por lo que enviaremos una bonificación especial de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal una vez que el sector esté despejado. Atentamente, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación constituye una oferta no vinculante que, una vez aceptada, podrá ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>Patrulla para prevenir un posible ataque.</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v> Buque de la Alianza Popular Tranquility</v>
+      </c>
+    </row>
+    <row r="819" xml:space="preserve">
+      <c r="A819" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operaciones: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Listo para Combate Informe: Una nave de seguridad de la Alianza Popular clase Idris llamada Tranquility está actualmente en combate con una nave capital Vanduul cerca de una antigua estación de extracción QV y Intersec está buscando pilotos de combate para brindar apoyo. Desplácese rápidamente al AO y ataque a los cazas Vanduul para que la Tranquility pueda concentrarse en la nave capital. Buena suerte, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v> Bombardeo estratégico</v>
+      </c>
+    </row>
+    <row r="821" xml:space="preserve">
+      <c r="A821" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Naves de Combate con Armamento Informe: Los recursos locales han indicado que elementos de Shattered Blade están intentando reconstruir una de sus estaciones e Intersec está buscando un piloto para asegurarse de que eso no suceda. Han logrado poner en línea las defensas básicas de las torretas, pero actualmente solo tienen &lt;EM4&gt;dos relés de energía activados&lt;/EM4&gt;. Estos serán sus objetivos ya que &lt;EM4&gt;no pueden ser destruidos por armas de energía, necesitará traer armamento balístico o de artillería para ser efectivo&lt;/EM4&gt;. La reactivación de esta estación permitirá a Shattered Blade intentar recuperar una posición en este sistema y no podemos permitir que eso suceda. Buena suerte, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa UEE y la legislación del sistema aplicable.</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>Recuperar datos de Vanduul</v>
+      </c>
+    </row>
+    <row r="823" xml:space="preserve">
+      <c r="A823" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: N/A Informe: El Capitán Martel de la nave Tranquility de la Alianza Popular se comunicó para informarle que lo han reclutado para recuperar unidades de datos de la nave capital Vanduul destruida. Tenga cuidado al extraer dichas unidades y entréguelas a la Alianza Popular para su análisis una vez completada la misión. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v> Misión de extracción</v>
+      </c>
+    </row>
+    <row r="825" xml:space="preserve">
+      <c r="A825" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Listo para Combate Informe: Intersec ha interceptado conversaciones de los canales de Shattered Blade que indican que han capturado a un piloto de seguridad de la Alianza Popular en una antigua estación de extracción que controlan. Necesitamos un piloto de combate experimentado para brindar asistencia en combate para que el piloto pueda escapar. El espacio aéreo fuera del hangar está repleto de hostiles, por lo que &lt;EM4&gt;necesitará despejar el espacio aéreo para que el piloto pueda despegar y realizar el QT de forma segura&lt;/EM4&gt;. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v> Se necesita un grupo de ataque táctico.</v>
+      </c>
+    </row>
+    <row r="827" xml:space="preserve">
+      <c r="A827" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Informe del Grupo de Ataque: Hemos recibido información de que una nave de seguridad de la Alianza Popular llamada Tranquility se topó con Shattered Blade escondida en una antigua estación de extracción QV. Los detalles son escasos, pero los conectaremos con recursos locales una vez en el lugar. Intersec está buscando un equipo para intervenir y proteger a la Tranquility y a su personal. Según las conversaciones con el capitán de la Tranquility, necesitarán &lt;EM4&gt;armamento balístico y municiones para romper las defensas de la estación&lt;/EM4&gt; y, en última instancia, &lt;EM4&gt;llegar a tierra para rescatar a su piloto&lt;/EM4&gt;. &lt;EM4&gt;Reclutar naves adicionales&lt;/EM4&gt; para apoyarlos en esta misión es absolutamente crítico. Necesitarán &lt;EM4&gt;una variedad de tipos de naves&lt;/EM4&gt; para equilibrar múltiples zonas de combate en el espacio y en tierra. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Ignore este mensaje si lo ha recibido por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa UEE y las leyes del sistema, según corresponda.</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>Operación de bombardeo táctico</v>
+      </c>
+    </row>
+    <row r="829" xml:space="preserve">
+      <c r="A829" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Naves de Combate con Armamento Informe: El análisis regional indica que existe un posible escondite de Shattered Blade en una antigua estación de extracción QV e Intersec está buscando un piloto para lanzar un ataque contra la infraestructura de energía de la estación. Este será un asalto de múltiples niveles, que requerirá que usted apunte y destruya componentes de la estación en el exterior y el interior. De operaciones anteriores, hemos aprendido que &lt;EM4&gt;ciertos componentes no pueden ser destruidos por armas de energía, por lo que se necesitarán armas balísticas o de munición&lt;/EM4&gt;. Partes de la estación históricamente han estado inundadas con &lt;EM4&gt;energía de distorsión pesada, por lo que deberá actuar con eficiencia mientras esté dentro&lt;/EM4&gt;. Todos estos ataques son un esfuerzo para permitirle &lt;EM4&gt;destruir el núcleo de energía ahora expuesto en el centro&lt;/EM4&gt;. La pérdida de esta estación impactará enormemente la capacidad de la banda para operar en el sistema y, por lo tanto, se ha considerado una alta prioridad. Buena suerte, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación contiene información confidencial destinada exclusivamente al destinatario. Si la recibe por error, ignórela y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la UEE y la legislación del sistema, según corresponda.</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>Listo para ser aprovechado</v>
+      </c>
+    </row>
+    <row r="831" xml:space="preserve">
+      <c r="A831" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tengo buenas noticias para ti. En este preciso instante, hay una instalación automatizada que está produciendo paquete tras paquete de producto de primera calidad, prácticamente listo para ser aprovechado. Solo tienes que ir allí, lidiar con un par de matones, agarrar lo que puedas y venderlo con una gran ganancia. No debería ser ningún problema. Y hay mucha gente dispuesta a pagar bien por comprarte ese producto. Hablando de créditos, no voy a dar las coordenadas de esta instalación por pura generosidad. Creo que es justo pedir una comisión por información tan valiosa. No esperes demasiado. No sé cuánto tiempo más estará activa la página web. -Ruto</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v> Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="833" xml:space="preserve">
+      <c r="A833" t="str" xml:space="preserve">
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados Hemos podido rastrear un reciente aumento de contrabando hasta una planta de producción automatizada en ~mission(Location|Address). No podemos asegurar cuánto tiempo más estará operativa la planta, por lo que BlacJac necesita a alguien en el lugar para inspeccionar, asegurar el contrabando y transportarlo hasta ~mission(Destination|Address). Una vez allí, pueden usar la terminal administrativa de mercancías para transferirnos el contrabando y cobrar su recompensa. No hemos podido determinar qué tipo de fuerza hostil estará presente, pero sea cual sea la que encuentren, están autorizados a usar la fuerza letal si es necesario. Cuanto más contrabando logren traernos, más créditos ganarán. Gracias, Teniente Aaron Riegert, Supervisor de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v> Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="835" xml:space="preserve">
+      <c r="A835" t="str" xml:space="preserve">
+        <v xml:space="preserve">Crusader Security ha descubierto que una instalación de producción ilegal en ~mission(Location|Address) se está utilizando para fabricar contrabando. Buscamos un contratista para asegurar el sitio, confiscar el contrabando y entregarlo en ~mission(Destination|Address). La terminal administrativa de mercancías le permitirá entregar el contrabando a nuestro depósito de pruebas y cobrar su pago. Dado que se trata de una instalación automatizada, no está claro cuánto tiempo estarán fabricando ni cuántas personas podrían estar presentes. Para mayor seguridad, le recomendamos que vaya preparado para encontrar una fuerte resistencia. Su compensación total dependerá de la seguridad con la que se entreguen los paquetes como prueba. CONTRATO AUTORIZADO POR: Oficial de Enlace Vanzant ID# 712L921P</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v> Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="837" xml:space="preserve">
+      <c r="A837" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Confiscar contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Odington EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Hurston Security ha tenido conocimiento de una instalación de producción automatizada ilegal y activa en ~mission(Location|Address) y busca un contratista para asegurar el sitio y confiscar la mayor cantidad posible de paquetes de contrabando para su entrega a una instalación de Hurston Security en ~mission(Destination|Address) para su eliminación inmediata. La transferencia del contrabando y la atribución de su pago de recompensa deben realizarse a través de la terminal administrativa de mercancías en dicho lugar. Usted está autorizado a usar la fuerza necesaria para completar su objetivo. El pago se basará en la cantidad de contrabando incautado. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="839" xml:space="preserve">
+      <c r="A839" t="str" xml:space="preserve">
+        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional de seguridad orientado a los detalles que pueda ayudarnos a asegurar el contrabando de un sitio de producción automatizado ilegal en ~mission(Location|Address). Los paquetes luego deberán ser llevados a ~mission(Destination|Address) y transferidos a nuestra posesión para su destrucción a través de la terminal administrativa de mercancías. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Gestionar cualquier hostil encontrado dentro del sitio; usando la fuerza según sea necesario. • Asegurar el contrabando y entregarlo a las terminales de mercancías en ~mission(Destination|Address) REQUISITOS MÍNIMOS • 2 años de experiencia combinada de mercenario y/o seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v> Contrabandistas de tecnología Vanduul</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v> Contrabandistas de tecnología Vanduul</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>Recuperar información adicional sobre contrabandistas.</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v> Recuperar información adicional sobre contrabandistas.</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v> Oportunidad de transporte de carga con Ling Hauling</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v> Oportunidad de transporte de carga con Ling Hauling</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v> Ruta de reparto local de la familia Ling</v>
+      </c>
+    </row>
+    <row r="851" xml:space="preserve">
+      <c r="A851" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, espero que estés disponible para hacer una entrega. ~mission(Contractor|Family) PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Avísame si puedes hacerlo. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling Coordinadora de Envíos Ling Family Hauling</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v> La familia Ling busca nuevos contratistas.</v>
+      </c>
+    </row>
+    <row r="853" xml:space="preserve">
+      <c r="A853" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, somos una pequeña empresa de reparto familiar que actualmente busca nuevos contratistas en la zona de Crusader. Si te interesa trabajar con nosotros, la siguiente entrega sería una excelente prueba para ver si encajas bien con la empresa. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si todo sale bien, te convertirás en el miembro más reciente de Ling Family Hauling. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v> Reevaluación del contratista Ling</v>
+      </c>
+    </row>
+    <row r="855" xml:space="preserve">
+      <c r="A855" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, no me entusiasma tener que hacer esto, pero tenemos escasez de contratistas y más entregas que nunca. Estoy dispuesto a darte otra oportunidad, pero necesitas completar la siguiente entrega. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por último, probablemente sería buena idea llevar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>Entrega de paquetes para Ling</v>
+      </c>
+    </row>
+    <row r="857" xml:space="preserve">
+      <c r="A857" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola, necesitamos que recojas un paquete en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y lo lleves a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Originalmente iba a enviar a mi hermano Ricki, pero dijo que la zona es demasiado peligrosa. Supongo que ha habido varias advertencias de seguridad por allí, pero mientras tengas cuidado y lleves armas o algo así, seguro que no tendrás problemas. Probablemente ni siquiera te topes con nada. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="str">
+        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="str">
+        <v> Oportunidades de empleo en seguridad de Eckhart</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="str">
+        <v> ~misión(Descripción)</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="str">
+        <v> Supervisión de la producción</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="str">
+        <v> ~misión(Contratista|Descripción del producto farmacéutico de entrega local)</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="str">
+        <v> Una tanda hecha desde cero</v>
+      </c>
+    </row>
+    <row r="865" xml:space="preserve">
+      <c r="A865" t="str" xml:space="preserve">
+        <v xml:space="preserve">Normalmente, me gusta cocinar todo desde cero. Me enorgullece el producto y todo eso. Pero de vez en cuando, ya sea por mucha demanda, mucho calor o lo que sea, necesito recurrir a otros laboratorios para un pedido. Sin embargo, aquí estoy muy ocupado, así que me vendría bien alguien que me ayudara a supervisar toda la línea de producción. No se me ocurre nadie mejor ni más disponible que tú. ~Misión (Itinerario) Simplemente no te distraigas ni te desvíes del camino. Sucede más a menudo de lo que crees. Si logras completar la lista, me aseguraré de que recibas una buena parte de las ganancias. -Wallace</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="str">
+        <v> Capturan al miembro de la pandilla de Arlington, Les Arlington</v>
+      </c>
+    </row>
+    <row r="867" xml:space="preserve">
+      <c r="A867" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Una comunicación anónima nos ha avisado de que Les Arlington, hijo del líder de la banda Maltrox Arlington, había sido visto recogiendo una entrega en un centro de transferencia de Covalex. Le proporcionaremos las coordenadas de donde creemos que se encuentran actualmente. Les es un piloto experimentado que lleva volando casi tanto tiempo como ellos llevan caminando y suele ser el piloto de escape de la banda. Podría ser conveniente traer naves de apoyo adicionales para frustrar cualquier intento de fuga. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="str">
+        <v>Captura de Nicks Cantwell, miembro de la pandilla de Arlington.</v>
+      </c>
+    </row>
+    <row r="869" xml:space="preserve">
+      <c r="A869" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de arresto grupal para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero de reparación. Si bien el robo fue detenido, los miembros del grupo se han dispersado en la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. Hemos recibido información de que Nicks Cantwell, conocido de larga data y confidente de Maltrox Arlington, fue visto intentando comprar un láser de minería de alta densidad, del tipo que se usa frecuentemente en intentos de secuestro de naves para perforar estratégicamente los cascos. Hemos proporcionado las coordenadas de la última ubicación conocida de Nicks. Nicks es un experto en municiones muy respetado en los círculos criminales y suele dejar un rastro de destrucción a su paso. Se recomienda aumentar la potencia de fuego en este encuentro. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="str">
+        <v>Captura a Sam 'Weepy' Arlington, miembro de la pandilla de Arlington.</v>
+      </c>
+    </row>
+    <row r="871" xml:space="preserve">
+      <c r="A871" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Sam 'Weepy' Arlington fue marcado por sistemas de seguridad automatizados en un R&amp;R después de estar involucrado en una pelea de borrachos. Weepy logró abandonar la estación antes de que llegaran los equipos de respuesta, pero hemos podido localizarlo en el lugar donde creemos que se encuentra escondido. Weepy es tío y principal ejecutor del líder de la pandilla, Maltrox Arlington. Sus problemas de ira, sumados a un largo historial de abuso de sustancias, lo convierten en un verdadero impredecible. Espere que oponga una resistencia considerable cuando usted y sus fuerzas lo acorralen. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="str">
+        <v>Captura de un miembro de la pandilla de Arlington en Oslo, Arlington.</v>
+      </c>
+    </row>
+    <row r="873" xml:space="preserve">
+      <c r="A873" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Recientemente, se accedió ilegalmente a una terminal de seguridad utilizando una criptoclave personalizada única que había sido utilizada en un robo el año pasado por un tal Oslo Arlington, el hermano menor del líder de la banda Maltrox Arlington. Aunque no podemos confirmar con certeza si Oslo hackeó la terminal, consideramos que vale la pena investigarlo. Oslo, un estratega de renombre, sumamente inteligente y experto en tecnología, ha demostrado ser difícil de capturar en el pasado. Si esta pista conduce a su localización, un equipo de ataque táctico bien coordinado sería fundamental para el éxito de la operación. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al finalizar el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. Dicha información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="str">
+        <v>Captura de Kass Dent, miembro de la pandilla de Arlington.</v>
+      </c>
+    </row>
+    <row r="875" xml:space="preserve">
+      <c r="A875" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado al espacio profundo. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Dos guardias de banco fueron reportados como desaparecidos la semana pasada. Hace unas horas, sus cuerpos aparecieron en un montón de basura en Magnus con sus datos biométricos robados. Afortunadamente, un puesto de dumplings cercano tenía una cámara de seguridad que captó el momento en que arrojaron los cadáveres. El reconocimiento facial permitió identificar a Kass Dent, pareja sentimental de Maltrox Arlington y padre de Les Arlington. Usando el video para reconstruir la cronología, hemos proporcionado las coordenadas del lugar donde se cree que Kass se esconde actualmente. Se sospecha que Kass es responsable de una larga lista de asesinatos, siendo estos dos los más recientes. Recomendamos traer solo a personas altamente capacitadas para intentar minimizar el número de víctimas. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="str">
+        <v>Captura de Maltrox Arlington, líder de la pandilla de Arlington.</v>
+      </c>
+    </row>
+    <row r="877" xml:space="preserve">
+      <c r="A877" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado en el espacio. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Maltrox Arlington ha estado manteniendo un perfil bajo últimamente, pero creemos que ha salido de su escondite. Una patrulla estaba reabasteciendo combustible en una estación cuando una de sus naves fue potenciada. Maltrox es el sospechoso más probable. Aunque el registro de la nave estuvo desactivado temporalmente, hemos podido rastrear su firma cuántica y le hemos facilitado las coordenadas. La banda de Arlington, criminal de tercera generación, ha estado bajo el liderazgo de Maltrox durante los últimos seis años. Tenga en cuenta que se trata de un objetivo inteligente, agresivo y muy peligroso. Cuantos más recursos pueda aportar, mayores serán las probabilidades de que logremos capturar a Maltrox de una vez por todas. Está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="str">
+        <v>Idris robado por una banda de Arlington</v>
+      </c>
+    </row>
+    <row r="879" xml:space="preserve">
+      <c r="A879" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO Parece que la segunda vez es la vencida para la banda de Arlington. Después de un intento fallido, la familia criminal recientemente fugada ha logrado robar un Idris de un astillero. Ahora sabemos para qué eran el láser de minería y la biometría que robaron. Dado que tuvimos tanto éxito capturándolos la primera vez, Eckhart Security ha recibido la orden de arresto de la banda. Esto requerirá una potencia de fuego considerable para derribar una nave capital de esta capacidad. Usted está autorizado a usar la fuerza que sea necesaria para rastrear el Idris y neutralizar a la banda. El pago se emitirá al completar con éxito el contrato y se ajustará según la evaluación final de su calificación de efectividad en combate y la de su equipo. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="str">
+        <v>Se emite la orden de compra grupal.</v>
+      </c>
+    </row>
+    <row r="881" xml:space="preserve">
+      <c r="A881" t="str" xml:space="preserve">
+        <v xml:space="preserve"> TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO En relación con un delito cometido conjuntamente, se ha emitido una orden de arresto grupal para: ~mission(Target1) ~mission(Target2) ~mission(Target3) Actualmente se cree que ya no viajan juntos para evadir la captura y que pronto podrían huir del sistema. Debería considerar seriamente reclutar ayuda adicional para ejecutar todas las órdenes de arresto en el plazo limitado. Está autorizado a usar la fuerza que sea necesaria para neutralizar a los objetivos. El pago se emitirá al completar con éxito el contrato cuando todos los objetivos hayan sido neutralizados en el tiempo asignado. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="str">
+        <v> ¿Necesitas una salida?</v>
+      </c>
+    </row>
+    <row r="883" xml:space="preserve">
+      <c r="A883" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola. Todavía no hemos tenido la oportunidad de trabajar juntos, pero estoy en un aprieto y necesito a alguien más. No gratis, por supuesto. Me gusta el intercambio. Uno de mis socios, que estuvo cumpliendo condena en Klescher, debía traerme un chip de datos, pero luego dejó de dar señales de vida. Supongo que está muerto, pero aquí está el trato: si terminas su trabajo, borro tu historial delictivo. No está mal, ¿verdad? Tu predecesor planeaba usar unos túneles viejos para escapar. Dio a entender que no eran precisamente fáciles de acceder, pero confío en que podrás resolverlo. Supongo que encontrarás su cuerpo por ahí y, si tenemos suerte, todavía tendrá el chip. Una vez que lo consigas, termina de escapar como puedas. Luego, tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me sorprendería que te los encontraras. Después de obtener los datos y validarlos, borraré tu historial delictivo. Entonces podrás disfrutar de tu recién descubierta libertad. Si lo haces bien, tal vez tenga un trabajo más lucrativo para ti en el futuro.</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="str">
+        <v>ayudémonos mutuamente</v>
+      </c>
+    </row>
+    <row r="885" xml:space="preserve">
+      <c r="A885" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola. Oí que acabaste en Klescher, lo cual es una verdadera lástima. Pero en realidad podría ser un día de suerte para ambos. En resumen, tenía a alguien sacando un chip de datos de la prisión, pero nunca volvió a contactarme. Sé con certeza que no ha salido de las instalaciones, así que creo que algo le pudo haber pasado. Aunque es trágico, el trabajo debe continuar. Si puedes conseguir el chip y terminar el trabajo, puedo borrar tu historial criminal. ¿Qué dices? Claro, no sé exactamente hasta dónde llegó, pero puedo decirte que la prisión tiene toda una red de túneles ocultos que mi tipo planeaba usar para escapar. Supongo que su cadáver se está pudriendo por ahí. Cuando encuentres el cuerpo, espero que el chip todavía esté con él. Cuando lo tengas, termina de escapar y tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Una advertencia: ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me extrañaría que te los encontraras. Cuando tenga los datos, borraré tu historial delictivo y listo, quedarás libre de toda sospecha. Lo que hagas después es decisión tuya.</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="str">
+        <v>Violación y robo</v>
+      </c>
+    </row>
+    <row r="887" xml:space="preserve">
+      <c r="A887" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola. Los Nueve Colas tienen un pequeño problema. Resulta que tienen un pequeño negocio paralelo en el tráfico clandestino de órganos. Un tema que prefiero evitar, pero un trabajo es un trabajo, ¿no? Parece que una de sus carnicerías móviles a bordo del 'October Rising' fue asaltada por seguridad privada mientras trabajaba. Ahora los Nueve Colas están dispuestos a romper lazos con el barco y su tripulación (que probablemente ya estén todos muertos), pero necesitan que les extraigan una caja en particular. Supongo que era un pedido especial o algo así. En fin, suban al October Rising, consigan el paquete y salgan. La seguridad sigue por ahí, así que tengan cuidado y tal vez traigan a algunos amigos, pero recuerden, su prioridad es el paquete. Si quieren ahorrarse problemas, también podrían apagar la zona desactivando la antena de comunicaciones más cercana si quieren evitar que los arresten por, ya saben, matar a un montón de guardias de seguridad. Pero bueno, hagan lo que quieran. Cuando salgas, deja el paquete en la clínica de Grim HEX y yo me encargaré del pago. Pan comido, Ruto.</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="str">
+        <v>consigue los productos</v>
+      </c>
+    </row>
+    <row r="889" xml:space="preserve">
+      <c r="A889" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, hace poco escuché información confidencial de que ~mission(location|address) recibió material confidencial de gran interés para un conocido mío. Es tan interesante que están dispuestos a pagar para que alguien asalte las instalaciones, se apodere del material y lo entregue en ~mission(DropOff1|address). Supongo que habrá mucha seguridad, que probablemente opondrá resistencia, así que llevaría un par de armas. Se rumorea que el material confidencial se entregó en un envío junto con otras cosas y ahora se encuentra almacenado en la bóveda automatizada de las instalaciones. Los oficiales de seguridad de alto rango llevan tabletas con códigos de acceso a la bóveda. Tendrás que conseguir una tableta antes de usar la cinta transportadora para recuperar las cajas. Si necesitas un incentivo adicional, he visto el manifiesto y puedo confirmar que las otras cajas almacenadas en las instalaciones son de primera calidad. A mi cliente no le importa lo que les pase, así que puedes hacer lo que quieras con ellas. Si lo gestionas bien, esas cajas adicionales podrían suponer una buena ganancia extra, además de la tarifa de envío.</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="str">
+        <v>suministro limitado</v>
+      </c>
+    </row>
+    <row r="891" xml:space="preserve">
+      <c r="A891" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Parece que hay un nuevo advenedizo en el sector que no ha estado pagando lo que le corresponde. Para darles una lección, mi cliente quiere que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Los matones de bajo nivel que tienen allí probablemente armarán un escándalo e intentarán detenerte. Haz lo que quieras con ellos, pero lo más importante es deshacerte de la droga.</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="str">
+        <v> liquidación de inventario</v>
+      </c>
+    </row>
+    <row r="893" xml:space="preserve">
+      <c r="A893" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Un cliente mío está intentando negociar un acuerdo, pero no está teniendo mucha suerte. La otra parte cree tener toda la ventaja porque tiene un gran inventario a su disposición. Para facilitar las negociaciones, necesito que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Debería advertirte que el sitio está protegido por gente muy peligrosa, así que llegar al alijo va a ser complicado, pero confío en que encontrarás la manera.</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="str">
+        <v> Agotado</v>
+      </c>
+    </row>
+    <row r="895" xml:space="preserve">
+      <c r="A895" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de mis clientes se ha enfadado al enterarse de que alguien está invadiendo su territorio. Ahora, en lugar de optar por la vía tradicional de matar a algunas personas y armar un escándalo, ha decidido enviar un mensaje diferente. Vas a ir a ~misión(Ubicación|Dirección) y destruir toda la droga del lugar. Claro que, si alguien quiere pelear contigo, puedes defenderte, pero lo más importante es deshacerte de la droga.</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="str">
+        <v> demasiados cocineros</v>
+      </c>
+    </row>
+    <row r="897" xml:space="preserve">
+      <c r="A897" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Un cliente está siendo superado por un nuevo competidor y busca sabotear el negocio. Dirígete a ~mission(Location|Address) y elimina a todos los civiles que trabajan allí. Haz lo que quieras con los matones armados que custodian a los trabajadores, pero recuerda que no son la prioridad.</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="str">
+        <v> Vive y deja que un contratista independiente se vengue.</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="str">
+        <v xml:space="preserve">Todo el mundo guarda rencor, ¿no? O sea, cuando te pillan cometiendo un delito, entiendo que te moleste un poco, pero así son las cosas, ¿no?</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="str">
+        <v> Es difícil encontrar buena ayuda.</v>
+      </c>
+    </row>
+    <row r="901" xml:space="preserve">
+      <c r="A901" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Conozco a alguien que quiere montar un negocio, pero le cuesta mucho contratar a los trabajadores cualificados que necesita. Resulta que encontró al equipo perfecto en ~mission(Location|Address), pero sus jefes no les dejan ir. Incluso contrataron guardias armados adicionales para asegurarse. Lo que quiero que hagas es ir allí y acabar con todos los guardias, asegurándote de que los trabajadores salgan ilesos.</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="str">
+        <v> haciendo un desastre</v>
+      </c>
+    </row>
+    <row r="903" xml:space="preserve">
+      <c r="A903" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Esto es un poco agresivo para mi gusto, pero los créditos son créditos, ¿no? Tengo un cliente que busca a alguien muy motivado para ir a ~misión(Ubicación|Dirección) y matar a todos los que estén allí. Básicamente, empieza a disparar y no pares. Te pagarán cuando el lugar esté despejado.</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="str">
+        <v> coger y llevar</v>
+      </c>
+    </row>
+    <row r="905" xml:space="preserve">
+      <c r="A905" t="str" xml:space="preserve">
+        <v xml:space="preserve">Esta misión es perfecta para alguien como tú. Hay un paquete retenido en ~mission(Location|Address) y necesito que lo lleves a ~mission(Destination|Address). Hay un pequeño detalle que debes saber: habrá muchísima seguridad allí. Pero seguro que todo irá bien. :)</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="str">
+        <v> Tras el desastre</v>
+      </c>
+    </row>
+    <row r="907" xml:space="preserve">
+      <c r="A907" t="str" xml:space="preserve">
+        <v xml:space="preserve">La fortuna nos sonríe una vez más. Acabo de enterarme de una batalla cerca de ~mission(Location) que acaba de tener lugar lejos de las miradas indiscretas de cualquier sistema de comunicaciones entrometido, y aún no se han enviado refuerzos de ninguna de las fuerzas involucradas. Esto significa que hay una oportunidad para que un alma emprendedora saquee el cementerio. Me gustaría ofrecer esta oportunidad a todos mis contactos de confianza. Cualquiera que esté interesado puede obtener la ubicación... por el precio adecuado. Las coordenadas se proporcionarán una vez que acepte el contrato y permanecerán disponibles hasta que decida rescindirlo. Por supuesto, la rapidez será esencial, ya que no solo se enfrentará a la posible competencia de otros rescatadores, sino también a la inminente posibilidad de que lleguen refuerzos para inspeccionar el campo de batalla. Si aún lo duda, recuerde: la fortuna favorece a los audaces. -cd</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="909" xml:space="preserve">
+      <c r="A909" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para ayudar en la detención de ~mission(TargetName) de ~mission(Location|Address). Somos conscientes de que puede haber civiles en el lugar, así que tenga cuidado con el posible fuego cruzado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. • Asegurar que no haya bajas civiles. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="str">
+        <v xml:space="preserve"> Evaluación de recompensas activas</v>
+      </c>
+    </row>
+    <row r="911" xml:space="preserve">
+      <c r="A911" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que nos ayudara a capturar a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, su principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="str">
+        <v xml:space="preserve"> Reevaluación activa de recompensas</v>
+      </c>
+    </row>
+    <row r="913" xml:space="preserve">
+      <c r="A913" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO Aunque tu desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerte una oportunidad para redimirte. Para reevaluar tus habilidades, nos gustaría que detuvieras a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, tu principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar tu propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazadores de Recompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (ERT)</v>
+      </c>
+    </row>
+    <row r="915" xml:space="preserve">
+      <c r="A915" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo extremo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo extremo generalmente pilota una nave de clase subcapital, tiene varios aliados fuertemente armados y se espera que sea muy difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="917" xml:space="preserve">
+      <c r="A917" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de alto riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de alto riesgo generalmente pilota una nave grande con tripulación múltiple, tiene varios aliados conocidos y se espera que sea difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="str">
+        <v> Evaluación de recompensas activas</v>
+      </c>
+    </row>
+    <row r="919" xml:space="preserve">
+      <c r="A919" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra lista actual. Para evaluar sus habilidades, nos gustaría que nos ayudara en la detención de ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (LRT)</v>
+      </c>
+    </row>
+    <row r="921" xml:space="preserve">
+      <c r="A921" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de bajo riesgo generalmente pilota una nave monoplaza, tiene varios aliados conocidos y debería ser fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="923" xml:space="preserve">
+      <c r="A923" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo moderado ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo moderado generalmente pilota una pequeña nave multitripulación, tiene varios aliados conocidos y puede ser un poco difícil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="str">
+        <v> Reevaluación de la detención de recompensas</v>
+      </c>
+    </row>
+    <row r="925" xml:space="preserve">
+      <c r="A925" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. Para reevaluar sus habilidades, nos gustaría que detuviera a ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (VLRT)</v>
+      </c>
+    </row>
+    <row r="927" xml:space="preserve">
+      <c r="A927" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de muy bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de muy bajo riesgo generalmente pilota una nave monoplaza, tiene pocos aliados conocidos y debería ser relativamente fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="str">
+        <v> Eliminar fuerza hostil</v>
+      </c>
+    </row>
+    <row r="929" xml:space="preserve">
+      <c r="A929" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos rápida y seguramente en la eliminación completa del grupo de forajidos que ha tomado temporalmente el control de ~mission(Location) en ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los miembros de la fuerza hostil de forajidos; usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="str">
+        <v> Capturar recompensa: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="931" xml:space="preserve">
+      <c r="A931" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa en ~mission(Location|Address), y creemos que finalmente podrían salir de su escondite si sus fuerzas que atacan ~mission(Location) se enfrentan a una resistencia lo suficientemente fuerte. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a los asociados criminales de ~mission(TargetName) cerca de ~mission(Location) para atraer al objetivo a campo abierto. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="str">
+        <v> Recompensa asegurada: ~misión(Nombre del objetivo) (VHRT)</v>
+      </c>
+    </row>
+    <row r="933" xml:space="preserve">
+      <c r="A933" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa que se ha extendido por todo ~mission(Location|Address). Esperamos que finalmente pueda sacarlos de su escondite si enfrenta a sus fuerzas en varios puntos de ataque diferentes. Con sus números suficientemente debilitados, ~mission(TargetName|Last) probablemente correrá el riesgo de ser expuesto y usted podrá enfrentarlos directamente. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Enfrentar a los asociados criminales de ~mission(TargetName) para hacer que el objetivo salga a la luz. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="str">
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="935" xml:space="preserve">
+      <c r="A935" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName) en ~mission(Location|Address). Fueron vistos recientemente cerca de ~mission(Location) y se cree que todavía están en esa área. Si bien puede haber otros criminales activos en el sitio, su enfoque principal debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="str">
+        <v> Ajuste de la población de vida silvestre</v>
+      </c>
+    </row>
+    <row r="937" xml:space="preserve">
+      <c r="A937" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para eliminar varias criaturas de diversas especies. Esta es una medida preventiva para asegurar que el tamaño de su población no aumente más allá de los parámetros aceptables. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar la especie objetivo en ~misión(Ubicación). • Usar la fuerza según sea necesario para eliminar a los animales. REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su Diario.</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="str">
+        <v> Control de vida silvestre: ~misión(Criatura)</v>
+      </c>
+    </row>
+    <row r="939" xml:space="preserve">
+      <c r="A939" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para reducir el número de ~mission(Creature) en estado salvaje a parámetros aceptables. Su población está aumentando demasiado rápido, y la reducción de algunos de sus números ayudará a garantizar que la situación no se salga de control. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar a ~mission(Creature) en ~mission(Location). • Usar la fuerza según sea necesario para eliminar a ~mission(Creature). REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio Para obtener más información sobre los animales en cuestión, consulte "The Guide to Stanton Wildlife" en su Diario.</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="str">
+        <v> Proteger la ubicación y entregar materiales confidenciales.</v>
+      </c>
+    </row>
+    <row r="941" xml:space="preserve">
+      <c r="A941" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional de seguridad para una operación de recuperación en ~mission(Location). La ubicación está actualmente bajo ataque y las fuerzas de seguridad en el sitio no responden y se presumen muertas. Creemos que los materiales confidenciales entregados recientemente a las instalaciones para custodia temporal fueron el objetivo del ataque. Su enfoque principal será recoger esas cajas y entregarlas en un lugar seguro. Por razones de seguridad, los materiales confidenciales se entregaron como parte de un envío más grande y se aseguraron en la bóveda automatizada. Los materiales tienen códigos de recuperación únicos que deben ingresarse en el teclado en la cinta transportadora de paquetes. Los protocolos exigen que solo los oficiales de seguridad de alto rango pueden llevar un datapad que contenga un código, pero dada la situación volátil, no podemos garantizar que los Nine Tails no se hayan apoderado de ellos. Una vez asegurados, entregue todos los materiales confidenciales a ~mission(dropoff1) para el pago. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|address). • Usar la fuerza según sea necesario para recoger los materiales confidenciales. • Entregar los materiales confidenciales a ~mission(dropoff1|address). REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate. • Acceso a una nave espacial con capacidad de transporte de carga. • Disponibilidad para despliegue inmediato. REQUISITOS DESEABLES • Experiencia en técnicas de desescalada rápida de hostilidades. • Experiencia en el transporte de carga importante.</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="str">
+        <v>Proteger la ubicación contra amenazas menores</v>
+      </c>
+    </row>
+    <row r="943" xml:space="preserve">
+      <c r="A943" t="str" xml:space="preserve">
+        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra cualquier amenaza menor. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="str">
+        <v> Proteger la ubicación contra amenazas moderadas</v>
+      </c>
+    </row>
+    <row r="945" xml:space="preserve">
+      <c r="A945" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="str">
+        <v> Proteja la ubicación contra amenazas graves.</v>
+      </c>
+    </row>
+    <row r="947" xml:space="preserve">
+      <c r="A947" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles graves. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="str">
+        <v> Sitio libre de contrabando</v>
+      </c>
+    </row>
+    <row r="949" xml:space="preserve">
+      <c r="A949" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir el contrabando que se almacena allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de contrabando; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="str">
+        <v> Sitio libre de narcóticos</v>
+      </c>
+    </row>
+    <row r="951" xml:space="preserve">
+      <c r="A951" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir los narcóticos que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de narcóticos; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="str">
+        <v> Sitio libre de drogas</v>
+      </c>
+    </row>
+    <row r="953" xml:space="preserve">
+      <c r="A953" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir las drogas que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de drogas; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="str">
+        <v> Defender a los ocupantes</v>
+      </c>
+    </row>
+    <row r="955" xml:space="preserve">
+      <c r="A955" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudar de manera rápida y segura al equipo de seguridad estacionado en ~mission(Location|Address) a proteger el sitio contra amenazas hostiles. Tenga en cuenta que cualquier fuego amigo, accidental o de otro tipo, no será tolerado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar al equipo de seguridad local a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="str">
+        <v> Evaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="957" xml:space="preserve">
+      <c r="A957" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita profesionales de seguridad nuevos, calificados y orientados a los detalles para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que ayudara a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="str">
+        <v> Reevaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="959" xml:space="preserve">
+      <c r="A959" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. En un esfuerzo por reevaluar sus habilidades, microTech Protection Services desea que ayude a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza según sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="str">
+        <v> Desalojar a los ocupantes ilegales</v>
+      </c>
+    </row>
+    <row r="961" xml:space="preserve">
+      <c r="A961" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos de manera rápida y segura en la eliminación completa de ocupantes ilegales que han tomado temporalmente el control de ~mission(Location|Address). Tenga en cuenta que nuestra inteligencia muestra que hay trabajadores civiles en el sitio. Dado que su conexión con la pandilla no está clara, deben ser considerados no combatientes. No se tolerará ninguna acción hostil hacia ellos. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los ocupantes hostiles que se encuentren dentro del sitio; usando la fuerza si es necesario. • Garantizar la seguridad de cualquier civil que pueda estar en el sitio. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="str">
+        <v> URGENTE: Embarque en curso</v>
+      </c>
+    </row>
+    <row r="963" xml:space="preserve">
+      <c r="A963" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un cliente ejecutivo nos acaba de informar que su 890 Jump fue interceptada en ~mission(Location) y abordada por forajidos. Prefieren que el asunto se resuelva de forma privada debido a la naturaleza confidencial de los datos confidenciales almacenados a bordo. Su prioridad será eliminar a todos los forajidos lo antes posible para que se pueda enviar un equipo de recuperación y devolver la nave al propietario. Cuanto más tiempo tengan los forajidos el control de la nave, mayor será la probabilidad de que se pierda. Le recomiendo que consiga un equipo para esta misión para agilizar el proceso. Tenga en cuenta que, gracias a un pequeño contingente de personal de seguridad que permaneció a bordo, todos los miembros supervivientes de la tripulación pudieron escapar en una nave de escape. Se desconoce el estado actual del resto del personal de seguridad, pero por si acaso, esté atento a la presencia de aliados cuando se enfrente a los hostiles. En segundo lugar, si es posible, el cliente está muy interesado en evitar el robo de los datos mencionados. Si logra detener el robo de sus almacenes de datos confidenciales antes de que se transmitan, recibirá una generosa bonificación. Como es lógico, este es un cliente al que me gustaría mantener muy satisfecho. Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="str">
+        <v>Asignación de recompensa: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="965" xml:space="preserve">
+      <c r="A965" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola, tengo un contrato para ti que requiere un poco más de estrategia de lo habitual. Un criminal de alto nivel llamado ~mission(TargetName) se esconde con un gran contingente de forajidos en ~mission(Location|Address). Nuestra información sugiere que las fuerzas de ~mission(TargetName|Last) probablemente actuarán como línea defensiva para proteger a su jefe. Supongo que tendrás que enfrentarte a ellos antes de poder acceder a ~mission(TargetName|Last). Dicho esto, no quiero que dispares indiscriminadamente. A veces, estos forajidos mantienen a civiles cerca y deben ser tratados como no combatientes. Mucha suerte, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="str">
+        <v> Asignación de recompensa provisional: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="str">
+        <v> Asignación de recompensa provisional: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="str">
+        <v> Misión de recompensa por fuga: ~mission(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="969" xml:space="preserve">
+      <c r="A969" t="str" xml:space="preserve">
+        <v xml:space="preserve">El delincuente convicto ~mission(TargetName) se ha fugado de un centro de rehabilitación local y Northrock ha sido contratado para devolverlo a prisión. En mi experiencia, los presos fugados no suelen rendirse pacíficamente, así que utilicen cualquier método posible para encontrarlo y someterlo. Podría ser conveniente vigilar los lugares donde podría intentar borrar sus antecedentes penales. No sería la primera vez que un preso intenta borrar su condena tras fugarse. Buena suerte en la búsqueda, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="str">
+        <v> Contrato provisional de recompensa por fuga</v>
+      </c>
+    </row>
+    <row r="971" xml:space="preserve">
+      <c r="A971" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, mi nombre es Braden Corchado y soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera en el sistema Stanton. Puede que ya te haya contactado, pero nos esforzamos por contactar a cualquier persona que cumpla con nuestros altos estándares y animarla a completar un contrato temporal. No hay mejor opción que ser contratista de Northrock. Tenemos una sólida reputación por ofrecer trabajo desafiante e interesante con una remuneración superior a la de muchos de nuestros competidores en el sistema. Para ser aprobado, deberás capturar a ~mission(TargetName). Recientemente escapó del centro de detención y tu trabajo consistirá en localizarlo antes de que desaparezca por completo. Un pequeño consejo: es probable que el objetivo intente limpiar su historial. Te recomiendo triangular tu búsqueda entre el centro de detención del que escapó y los lugares donde pueda acceder al sistema de registros. Si lo logras, veremos si podemos ofrecerte más trabajo. Espero tener noticias suyas pronto, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="str">
+        <v>Contrato provisional de recompensa para fugitivos (reevaluación)</v>
+      </c>
+    </row>
+    <row r="973" xml:space="preserve">
+      <c r="A973" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola, sé que ha pasado un tiempo, pero si todavía te interesa trabajar por contrato para Northrock, convencí a la gerencia para que te hicieran una reevaluación. Si logras completar con éxito una misión de recompensa, podemos ver si podemos restituirte tu puesto. Este contrato temporal consiste en localizar al criminal fugado ~mission(TargetName). Haz todo lo posible por encontrarlo antes de que borre su registro en el punto de acceso a la base de datos, o el trabajo será mucho más difícil. Esperamos poder confiar en ti. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="str">
+        <v> Detener sospechoso: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="str">
+        <v> ~misión(Contratista|DescripciónPVPRecompensa)</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="str">
+        <v> Detención provisional del sospechoso</v>
+      </c>
+    </row>
+    <row r="977" xml:space="preserve">
+      <c r="A977" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, espero que no le importe, pero me enteré de su pertenencia al Gremio de Cazadores de Recompensas y quería ponerme en contacto con usted para ver si estaría interesado en colaborar con Northrock Service Group, una de las empresas de seguridad privada mejor valoradas del sistema. Si es así, el primer paso sería completar una detención provisional del sospechoso. No se trata tanto de una evaluación, sino más bien de una oportunidad para asegurarnos de que podemos establecer una buena relación laboral. El sospechoso que busca se conoce como &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;. Se sabe que es particularmente escurridizo, así que puede que tenga un trabajo arduo por delante. Espero tener noticias suyas pronto. Atentamente, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="str">
+        <v> Detención provisional de sospechoso (reevaluación)</v>
+      </c>
+    </row>
+    <row r="979" xml:space="preserve">
+      <c r="A979" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola de nuevo, hace tiempo que no hablamos, espero que todo esté bien. Sé que las cosas no terminaron de la mejor manera, pero después de hablarlo con la gerencia, me gustaría ofrecerte una oportunidad para redimirte. Tenías potencial y me da mucha pena que no hayas tenido la oportunidad de demostrar de lo que eres capaz. Completa la misión &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y veremos cómo podemos restituirte en tu puesto. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="str">
+        <v> Operación de recuperación</v>
+      </c>
+    </row>
+    <row r="981" xml:space="preserve">
+      <c r="A981" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aquí está el trato: un cliente nuestro (que debería haber gastado los créditos extra en una escolta de Northrock) sufrió un ataque a una de sus naves y ahora necesita que lideremos una operación de recuperación de un paquete importante que fue robado. Por suerte, tuvimos un golpe de suerte y pudimos localizar a los responsables en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;. Necesitamos que vayas allí y recuperes el paquete. Podrás identificarlo por su número de serie: &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt;. Supongo que los forajidos van a oponer resistencia, pero recuerda que no son la prioridad. Una vez que tengas el paquete, llévalo de vuelta al cliente en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Una última cosa, asegúrate de llevar una nave con suficiente espacio para carga. No queremos que llegues hasta allí en tu Gladius o lo que sea solo para tener que regresar. Enorgullécenos, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group *RESUMEN DE LA OPERACIÓN DE RECUPERACIÓN* * Recuperar el paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; * Entregar en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="str">
+        <v>Asignación de recompensa: Orden de arresto grupal (MRT)</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="str">
+        <v> Asignación de recompensa: Orden de arresto grupal (HRT)</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="str">
+        <v> Asignación de recompensa: Orden de arresto grupal (VHRT)</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="str">
+        <v> Asignación de recompensa: Orden de grupo (ERT)</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="str">
+        <v> Contrato de garantía grupal pro tempore</v>
+      </c>
+    </row>
+    <row r="991" xml:space="preserve">
+      <c r="A991" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, espero que todo vaya bien. Puede que ya te haya contactado, pero quería asegurarme de presentarme. Soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera actualmente en el sistema Stanton, que proporciona una variedad de servicios a todos los principales organismos gubernamentales, así como a varias empresas privadas. El motivo por el que me pongo en contacto contigo es porque creemos que alguien con tus habilidades podría ser muy valioso para nuestros clientes. Además, creo que seríamos una buena opción para ti. Nuestros contratistas suelen recibir una remuneración más alta que muchos de nuestros competidores en el sistema, y muchos de ellos me comentan lo mucho que disfrutan del trabajo desafiante e interesante que les ofrecemos. Ahora bien, Northrock se rige por estándares muy altos, por lo que antes de que podamos formalizar nada, tendrás que obtener la aprobación como contratista completando un contrato provisional. Esperaba que pudieras capturar a varios miembros buscados de una banda de forajidos: ~misión(Objetivo1), ~misión(Objetivo2) y ~misión(Objetivo3). Una vez que lo hagas, veremos si podemos conseguirte más trabajo. Espero tener noticias tuyas pronto. Atentamente, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v>Orden de reevaluación del grupo provisional</v>
+      </c>
+    </row>
+    <row r="993" xml:space="preserve">
+      <c r="A993" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola, he estado reflexionando sobre todo lo sucedido y decidí hablar con la gerencia. Han accedido a darte otra oportunidad, pero solo si completas con éxito un contrato para nosotros. Podemos considerar la posibilidad de restituirte en tu puesto si logras capturar a este trío criminal: ~misión(Objetivo1) ~misión(Objetivo2) ~misión(Objetivo3). Evadieron al último asociado que los persiguió, así que si los capturas a todos, sin duda ganarás puntos. Espero que hayas enderezado tu vida desde tu último trabajo. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v> Ayuda al bloqueo</v>
+      </c>
+    </row>
+    <row r="995" xml:space="preserve">
+      <c r="A995" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ahora que Crusader ha encontrado su flota, parece que los Nueve Colas por fin se han dado cuenta de lo útil que puede ser un poco de ayuda extra. En resumen, buscan mercenarios para mantener a raya a Crusader. Tú y todos los demás que se ofrezcan voluntarios recibiréis una recompensa por cada nave de seguridad que derribéis. Y, además, si mantenéis a Crusader ocupado el tiempo suficiente para que los Nueve Colas terminen con lo que sea que estén tramando con este bloqueo cuántico, recibiréis una generosa bonificación.</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v> Bloqueo ilegal: Neutralización de la Flota de Nueve Colas</v>
+      </c>
+    </row>
+    <row r="997" xml:space="preserve">
+      <c r="A997" t="str" xml:space="preserve">
+        <v xml:space="preserve">Crusader Security ha confirmado la ubicación de la flota forajida de los Nueve Colas y se está movilizando para poner fin al bloqueo cuántico de ~mission(Location). Buscamos nuevamente profesionales de seguridad capacitados para unirse a nuestros esfuerzos de respuesta de emergencia y ayudar a neutralizar esta peligrosa amenaza. Antes de aceptar, tenga en cuenta que se espera que los Nueve Colas ofrezcan una resistencia considerable y que, hasta que se levante el bloqueo, no será posible realizar viajes cuánticos en el sector. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v> Lejos de miradas indiscretas</v>
+      </c>
+    </row>
+    <row r="999" xml:space="preserve">
+      <c r="A999" t="str" xml:space="preserve">
+        <v xml:space="preserve">Les dije a los Nueve Colas que bloquear los viajes cuánticos para mantener toda una zona como rehén iba a atraer la atención equivocada, pero ¿me hacen caso? No. Ahora Crusader tiene docenas de naves de escaneo por ahí husmeando en cosas que prefiero mantener ocultas. Por eso estoy intentando contratar a tanta gente como pueda para que me ayude. Quiero pagarte por cada nave de escaneo de Crusader que destruyas. De hecho, incluso aumentaré tu tarifa por nave si todos alcanzan un cierto número de bajas. Llámalo incentivo por rendimiento. Y si de verdad te sientes con ganas de superarte, elimina a cualquier tonto lo suficientemente valiente como para intentar transportar carga a la estación bloqueada. Tengo algunos proveedores que agradecerán la demanda extra.</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v> Bloqueo ilegal: se busca al responsable de la flota de las Nueve Colas.</v>
+      </c>
+    </row>
+    <row r="1001" xml:space="preserve">
+      <c r="A1001" t="str" xml:space="preserve">
+        <v xml:space="preserve">Crusader Security ha descubierto que la organización criminal conocida como los Nueve Colas ha establecido un bloqueo ilegal alrededor de ~mission(Location) y ha detenido todo el tráfico cuántico entrante y saliente en el sector. Es necesario localizar la flota ilegal y levantar el bloqueo. Solicitamos urgentemente a cualquier profesional de seguridad capacitado en el sistema que se una a las fuerzas de Crusader Security y proteja nuestras naves de escaneo mientras buscan la ubicación de la flota de los Nueve Colas que está causando este bloqueo. Tenga en cuenta que, con el viaje cuántico desactivado y numerosos enemigos en la zona, esta debe considerarse una operación de alto riesgo. Se recomienda encarecidamente que todos los pilotos que participen en esta operación de respuesta de emergencia cuenten con el equipo adecuado y el tanque de combustible lleno. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="str">
+        <v> Bloqueo ilegal: se necesitan suministros médicos.</v>
+      </c>
+    </row>
+    <row r="1003" xml:space="preserve">
+      <c r="A1003" t="str" xml:space="preserve">
+        <v xml:space="preserve">El bloqueo cuántico ilegal de ~mission(Location) ha interrumpido las rutas comerciales habituales y los productos esenciales escasean. Crusader Security busca comerciantes y transportistas para suministrar los suministros médicos que tanto necesita la estación. Los precios ofrecidos por la administración de la estación se ajustarán para reflejar la situación con los Nine Tails y, además, Crusader otorgará una bonificación por riesgo al entregar con éxito los suministros médicos debido al mayor riesgo. Gracias de antemano por su apoyo durante estos tiempos difíciles. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="str">
+        <v> Iniciativa Overdrive: Emboscada contra Xenoamenazas - Se necesita apoyo</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="str">
+        <v> ALERTA DE LAS FDI: Emboscada de xenoamenazas - Se necesita apoyo</v>
+      </c>
+    </row>
+    <row r="1007" xml:space="preserve">
+      <c r="A1007" t="str" xml:space="preserve">
+        <v xml:space="preserve">*PARA PUBLICACIÓN INMEDIATA EN TODO EL SISTEMA* Atención, fuerzas de XenoThreat comenzaron a emboscar a los convoyes navales que transportaban suministros vitales mientras se dirigían a la estación Jericho en el Pyro Gateway en el Sistema Stanton. La Armada ha solicitado a las fuerzas de CDF que ayuden a recuperar estos suministros de los restos y entregarlos de forma segura a Jericho. La Armada ha organizado un estipendio comunitario para gestionar la distribución del pago. Este se distribuirá entre todos los voluntarios de CDF en intervalos asignados. Aparecerá un indicador en su HUD para medir estos pagos. Tenga en cuenta que algunos de estos suministros son altamente volátiles si no se manipulan correctamente. Tenga precaución al transportar estos materiales: * Zeta-Prolanide se degrada con el tiempo hasta descomponerse por completo. * AcryliPlex Composite se vuelve explosivamente inestable si se daña. * Diluthermex libera un pulso de energía destructivo si se expone al viaje cuántico. Además, si bien no es tan volátil, la Armada aún necesita urgentemente los suministros de DynaFlex perdidos durante el ataque para completar las reparaciones del Javelin, por lo que su recuperación debe ser prioritaria. Asimismo, es posible que aún haya hostiles de XenoThreat en la zona, así que tengan cuidado. Se insta a los voluntarios de las CDF con experiencia en combate a contribuir asegurando estas áreas de las fuerzas XenoThreat que aún persistan. La SAIC Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v>Iniciativa Overdrive: Ataque a XenoThreat</v>
+      </c>
+    </row>
+    <row r="1009" xml:space="preserve">
+      <c r="A1009" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Atención, las fuerzas navales se han reagrupado para el asalto final que XenoThreat ha estado planeando. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. Esto incluye a voluntarios que no hayan participado en la Iniciativa Overdrive. La suboficial Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y dirigirá la operación. Si tiene éxito, se completará esta serie de la Iniciativa Overdrive y recibirá acceso temporal a los F7A Hornet o una actualización gratuita si actualmente posee un F7C.</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v> ALERTA DE CDF: Ataque a XenoThreat</v>
+      </c>
+    </row>
+    <row r="1011" xml:space="preserve">
+      <c r="A1011" t="str" xml:space="preserve">
+        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención: las fuerzas navales se han reagrupado para un asalto final contra la manada de forajidos XenoThreat que ha estado asolando el Sistema Stanton. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. La suboficial Rowena Dulli, de la División de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v> dinero de la nada</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v> ¿Alguna vez has deseado que aparecieran créditos por arte de magia? Varias terminales de crédito antiguas de CCB están activas y simulan transacciones bancarias para desviar fondos a quien las controle. Si te interesa, te vendo las coordenadas por una pequeña comisión. Date prisa si quieres aprovechar la oportunidad. No sé cuánto tiempo seguirá funcionando.</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v> Recursos adicionales para la investigación</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v> Recursos adicionales para la investigación</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v> Recursos vitales necesarios para la investigación</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v> Recursos vitales necesarios para la investigación</v>
+      </c>
+    </row>
+    <row r="1018" xml:space="preserve">
+      <c r="A1018" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesito recursos para la investigación.</v>
+      </c>
+    </row>
+    <row r="1019" xml:space="preserve">
+      <c r="A1019" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesito recursos para la investigación.</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v> Recoge cuernos de kopión irradiados</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v> Recoge cuernos de kopión irradiados</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v> Obtén perlas Valakkar irradiadas</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v> Obtén perlas Valakkar irradiadas</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v> Reúne colmillos de Valakkar irradiados</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v> Reúne colmillos de Valakkar irradiados</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v> Recoge huevos de Valakkar irradiados.</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v> Recoge huevos de Valakkar irradiados.</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v> ¿Te interesa construir un futuro mejor?</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v> ¿Te interesa construir un futuro mejor?</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v> Ruta de envío local de Red Wind</v>
+      </c>
+    </row>
+    <row r="1031" xml:space="preserve">
+      <c r="A1031" t="str" xml:space="preserve">
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Recibimos una solicitud de ~mission(Pickup1|Address) indicando que tienen una buena cantidad de paquetes esperando en ~mission(Pickup1) que necesitan ser entregados. Antes de aceptar el contrato, asegúrese de tener una nave con suficiente espacio. Un rayo tractor tampoco vendría mal. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; SOMOS UNA EMPRESA QUE OFRECE IGUALDAD DE OPORTUNIDADES: Red Wind Linehaul es y siempre ha sido una empresa que ofrece igualdad de oportunidades. Si cree que puede hacer un buen trabajo para nosotros, no dude en inscribirse.</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v>Servicio de mensajería discreta Red Wind</v>
+      </c>
+    </row>
+    <row r="1033" xml:space="preserve">
+      <c r="A1033" t="str" xml:space="preserve">
+        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tengo otro trabajo especial para el que podrías contar contigo. Debería ser un viaje rápido. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;) LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Y por favor recuerda no molestar a los clientes ni a ninguno de sus invitados. La profesionalidad es clave aquí.</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v> Viento Rojo necesita mensajeros discretos</v>
+      </c>
+    </row>
+    <row r="1035" xml:space="preserve">
+      <c r="A1035" t="str" xml:space="preserve">
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Sé que has hecho un buen trabajo para nosotros en el pasado, así que pensé en preguntarte si te interesaría encargarte de un viaje especial que está un poco más lejos de lo que has estado haciendo hasta ahora. En resumen, necesitamos un piloto que esté dispuesto a trabajar con discreción, concentrarse en entregar los paquetes y, lo más importante, no hacer muchas preguntas. Verás, para una empresa pequeña como la nuestra, mantenernos por delante de la competencia significa que necesitamos ofrecer a nuestros clientes algo que no pueden obtener en ningún otro lugar: discreción. En Red Wind, siempre que tengas los créditos, llevaremos lo que sea a donde sea. ¿Entendido? Si eso te parece bien, veamos cómo te va en esta carrera: PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Un último consejo: probablemente sería bueno evitar retrasos innecesarios una vez que los paquetes estén a bordo, por ejemplo, que sean registrados por las fuerzas del orden locales.</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v>Manipulador de paquetes de Red Wind</v>
+      </c>
+    </row>
+    <row r="1037" xml:space="preserve">
+      <c r="A1037" t="str" xml:space="preserve">
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Parece que hubo un pequeño problema logístico en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitan a alguien que se asegure de que los paquetes extraviados terminen donde se supone que deben ir dentro de las instalaciones. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; LA CONFIANZA ES BIDIRECTA: al aceptar este contrato, usted se compromete a no estafarnos, y Red Wind Linehaul se compromete a tratarlo de la misma manera.</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v>Ruta de reparto local de Red Wind</v>
+      </c>
+    </row>
+    <row r="1039" xml:space="preserve">
+      <c r="A1039" t="str" xml:space="preserve">
+        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Se necesita un piloto independiente disponible para una entrega local rápida. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de la &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Intente no causar problemas cuando esté fuera. Si lleva paquetes de Red Wind a bordo, se agradece cierto nivel de profesionalismo. Y no olvide empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar consigo. ~mission(Contractor|SignOff)</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v> Red Wind busca nuevos pilotos.</v>
+      </c>
+    </row>
+    <row r="1041" xml:space="preserve">
+      <c r="A1041" t="str" xml:space="preserve">
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Buscamos contratar un piloto independiente interesado en operar una ruta local para nosotros. PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si lo logras, podemos considerar otros contratos en el futuro. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~mission(Contractor|SignOff)</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v> Otro intento de entrega de viento rojo</v>
+      </c>
+    </row>
+    <row r="1043" xml:space="preserve">
+      <c r="A1043" t="str" xml:space="preserve">
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Aunque hace tiempo que no le contratamos, ahora mismo nos vendría bien su ayuda extra. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a la &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Si logras esta entrega, podemos ver si podemos volver a hacerla más frecuente. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~misión(Contratista|Aprobación)</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v>SE NECESITA PILOTO DE RED WIND DELIVERY</v>
+      </c>
+    </row>
+    <row r="1045" xml:space="preserve">
+      <c r="A1045" t="str" xml:space="preserve">
+        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tenemos un envío esperando ser transportado desde &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Sin embargo, seré sincero contigo, este lugar no tiene la mejor reputación. Dicho esto, todavía necesitan entregar paquetes y tienen créditos, así que todo está en orden. Pero si vas allí, hay una buena posibilidad de que te encuentres con algunos problemas. No aceptes el trabajo si no puedes manejar eso. A TODOS LOS VETERANOS: ¡Red Wind agradece su servicio a nuestro Imperio! ¡Sus esfuerzos significan nuestra libertad!</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v> Oportunidad de manutención para reclusos</v>
+      </c>
+    </row>
+    <row r="1047" xml:space="preserve">
+      <c r="A1047" t="str" xml:space="preserve">
+        <v xml:space="preserve">Estimados usuarios: Recientemente nos han informado de que uno de nuestros dispensadores de oxígeno ha sufrido una avería técnica. Como saben, estos dispensadores son esenciales para garantizar que dispongan de suficiente oxígeno durante su participación en nuestro Programa de Reinserción Laboral. Buscamos a algún usuario disponible que pueda reiniciar el dispensador. Esto debería reconectarlo a la red y solucionar el problema. El primer usuario que complete esta tarea no solo recibirá una recompensa, sino también la satisfacción de contribuir a un entorno de trabajo más seguro para los demás usuarios. Gracias.</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v> Negociaciones fallidas</v>
+      </c>
+    </row>
+    <row r="1049" xml:space="preserve">
+      <c r="A1049" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tuve un percance con la mala suerte y espero que puedas ayudarme. Hace unos días, contraté a la tripulación del 'Orgullo de Arliss' para obtener datos importantes. Cumplieron el trabajo sin problemas, pero el capitán, ese desgraciado, me contactó exigiendo más créditos. Resulta que no era la primera vez que intentaba esta trampa, porque en medio de una "negociación" conmigo, su nave fue atacada por unos individuos muy enfadados que querían darle una lección. Nuestra comunicación se cortó cuando empezó el tiroteo y fue lo último que supe de él. Supongo que lo han borrado de mi vida, pero quiero que vayas al Orgullo de Arliss e intentes obtener mis datos del datapad personal del capitán. Una vez que los tengas, he configurado un canal de transmisión seguro en el área de descanso ARC-L1. Ve allí y, cuando estés dentro del alcance, envíame los datos a través de este contrato para que te pague. No intentes engañarme. El karma puede ser un verdadero cabrón.</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v> Doble juego</v>
+      </c>
+    </row>
+    <row r="1051" xml:space="preserve">
+      <c r="A1051" t="str" xml:space="preserve">
+        <v xml:space="preserve">Rough &amp; Ready recientemente proporcionó servicios de repostaje a un transportista llamado ~mission(TargetName), quien accedió a entregarnos su próximo cargamento como compensación. Pues bien, acabamos de descubrir que el mentiroso vendió su último cargamento a una banda rival. Buscamos a alguien que localice y elimine a ~mission(TargetName|Last) por su traición. Un viejo amigo mío acaba de ver al traidor en ~mission(Location|Address). Parece que lleva más cargamento que no va dirigido a nosotros y viaja con escolta. Solo te pagaremos por destruir el barco, así que todo lo que encuentres a bordo es tuyo. - Smokey</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v> Entrega fallida</v>
+      </c>
+    </row>
+    <row r="1053" xml:space="preserve">
+      <c r="A1053" t="str" xml:space="preserve">
+        <v xml:space="preserve">Mis socios y yo cerramos un trato con un transportista llamado ~mission(TargetName) para que nos entregara suministros. Lo curioso es que el envío nunca llegó. Afirmaron que unos piratas asaltaron su barco y se llevaron nuestros suministros, pero resulta que esa historia es una completa mentira. Mentir para cancelar nuestro trato no puede quedar impune y vas a dejarlo bien claro. ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Mientras mates a ~mission(TargetName|Last), no nos importa lo que pase con la carga que transportan. - Smokey</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v> Activar una trampa</v>
+      </c>
+    </row>
+    <row r="1055" xml:space="preserve">
+      <c r="A1055" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un imbécil con el nombre ~mission(TargetName) ha estado tramando un plan: su carguero solicita repostaje solo para emboscar a nuestros barcos al llegar. Incluso cargó la maldita nave con mercancía real para asegurarse de que pasara los escaneos. Hemos corrido la voz para que nadie en Rough &amp; Ready vuelva a caer en la trampa, pero quiero que este cretino sea castigado. Creo que ~mission(TargetName|Last) reconoce a muchos de los nuestros, así que supongo que será mejor pagarte para que te encargues. He oído que lo han visto cerca de ~mission(Location|Address). Dirígete allí ahora mismo y acaba con ese carguero y con cualquiera que lo proteja de una vez por todas. - Smokey</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v> Saboteador de la huelga</v>
+      </c>
+    </row>
+    <row r="1057" xml:space="preserve">
+      <c r="A1057" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Te interesa ir de caza? ~mission(TargetName) saboteó uno de nuestros envíos de combustible y nos costó un montón de créditos, así que busco a alguien que le haga pagar por lo que hizo. Me acaban de avisar de que ~mission(TargetName|Last) fue visto en ~mission(Location|Address). Si vas allí ahora, hay muchas posibilidades de que puedas seguirle la pista y acabar con él definitivamente. ~mission(TargetName|Last) no actuó solo, así que no te sorprendas si va acompañado. - Smokey</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v> Ya era hora.</v>
+      </c>
+    </row>
+    <row r="1059" xml:space="preserve">
+      <c r="A1059" t="str" xml:space="preserve">
+        <v xml:space="preserve">Rough &amp; Ready lleva años haciendo negocios con ~mission(TargetName), pero la relación se ha deteriorado. Durante un tiempo, les suministrábamos combustible a crédito, pero a la hora de cobrar, el cobarde se escondió. Si ~mission(TargetName|Last) no puede pagar con créditos, supongo que pagará con su vida. Un socio acaba de localizar a ~mission(TargetName|Last) en ~mission(Location|Address). Me encantaría que fueras allí ahora mismo para hacer que ese tacaño pague. Por cierto, parece que ~mission(TargetName|Last) no viaja solo, así que asegúrate de tener suficiente combustible antes de ir tras él. - Smokey</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v> Regalo de despedida</v>
+      </c>
+    </row>
+    <row r="1061" xml:space="preserve">
+      <c r="A1061" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tengo una situación delicada que requiere atención. Tras años de ser un miembro leal de Rough &amp; Ready, ~mission(TargetName) desertó de la banda y está por ahí filtrando secretos a nuestros rivales. Necesitamos eliminar a ~mission(TargetName|Last) de inmediato. En casos como este, siempre es mejor pagarle a alguien ajeno a nosotros para que se encargue. Los escaneos detectaron a ~mission(TargetName|Last) cerca de ~mission(Location|Address) hace poco. Te pagaremos bien para que vayas allí ahora mismo y te encargues de él. ~mission(TargetName|Last) no es tonto y sabe que iremos tras él. Prepárate para una dura batalla y no esperes que esté solo. - Smokey</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v> Operación de espionaje en silencio</v>
+      </c>
+    </row>
+    <row r="1063" xml:space="preserve">
+      <c r="A1063" t="str" xml:space="preserve">
+        <v xml:space="preserve">El equipo de Rough &amp; Ready busca a alguien para manejar una situación delicada. Hemos descubierto una nave y centinelas orbitales en ~mission(location|address) espiándonos. Estamos en un aprieto porque no queremos iniciar una pelea mayor con quienquiera que esté detrás de esto. Por eso buscamos ayuda a sueldo que pueda encargarse de esto rápida y discretamente. ¿Te interesa? Último consejo: una vez allí, asegúrate de vigilar la nave. Apuesto a que en cuanto empieces a destruir sus centinelas intentarán traer refuerzos para detenerte. - Smokey</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v> Operación de espionaje de Stomp</v>
+      </c>
+    </row>
+    <row r="1065" xml:space="preserve">
+      <c r="A1065" t="str" xml:space="preserve">
+        <v xml:space="preserve">El equipo de Rough &amp; Ready busca un mercenario independiente interesado en algo pesado. Hemos estado vigilando una situación que se está desarrollando en ~mission(location|address), donde varias naves custodian centinelas orbitales que espían nuestras operaciones. Puede que haya nacido de noche, pero no fue anoche. Dada la descarada forma en que están instalados, quien sea el responsable debía saber que tarde o temprano lo descubriríamos. Casi parece que están tendiéndole una trampa a R&amp;R para que ataquemos, y no quiero que caigamos en ella. En cambio, tú lo harás por nosotros y recibirás una buena cantidad de créditos por tu esfuerzo. Las naves estacionadas allí sospecharán menos de una nave no afiliada que se acerque, lo que dificultará que nos atribuyan el ataque. Asegúrate de planificar bien antes de ir. Quizás deberías llevar tus propios refuerzos por si alguna de sus naves escapa y pide ayuda. - Smokey</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v xml:space="preserve"> Detengan las operaciones de espionaje</v>
+      </c>
+    </row>
+    <row r="1067" xml:space="preserve">
+      <c r="A1067" t="str" xml:space="preserve">
+        <v xml:space="preserve">Mis socios y yo nos encontramos en un pequeño aprieto y necesitamos ayuda. Hay un centinela orbital en ~mission(location|address) que nos está espiando. No sabemos quién lo puso ahí, pero desde luego no puede quedarse. El problema es que somos gente de negocios ante todo y nos preocupa que si lo destruimos nosotros mismos se arme un lío. Por eso es mejor que lo haga alguien como tú. Debería ser un trabajo rápido y fácil para alguien interesado en ganar algo de prestigio. - Smokey</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v> Operación de espionaje de Squash</v>
+      </c>
+    </row>
+    <row r="1069" xml:space="preserve">
+      <c r="A1069" t="str" xml:space="preserve">
+        <v xml:space="preserve">Recientemente hicimos un descubrimiento interesante: alguien instaló varios centinelas orbitales en ~mission(location|address). Supongo que intentan obtener información sobre nuestras operaciones allí. Incluso tienen algunas naves vigilando para asegurarse de que no les pase nada. Por supuesto, queremos deshacernos de estos desgraciados, pero me preocupa que hacerlo nosotros mismos sea perjudicial para el negocio. Por eso buscamos una forma de "negación plausible". Alguien ajeno a R&amp;R que elimine el problema, para que quien esté detrás no pueda vincular directamente el ataque con nosotros. Sé que no será fácil, sobre todo con esos guardias al acecho. ¿Quién sabe cuántos refuerzos tienen preparados? Pero si lo consigues, estamos dispuestos a pagarte como es debido. ¿Crees que tienes las habilidades necesarias para lograrlo? - Smokey</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v> Echar leña al fuego</v>
+      </c>
+    </row>
+    <row r="1071" xml:space="preserve">
+      <c r="A1071" t="str" xml:space="preserve">
+        <v xml:space="preserve">Si buscas créditos fáciles, tengo una oferta para ti. Verás, corre el rumor de que ~mission(location|address) está funcionando como depósito de combustible. Parece que no se enteraron de que el comercio de combustible en Pyro pertenece a Rough &amp; Ready. Por eso tienes que ir allí y destruir sus reservas de combustible. Deberían ser fáciles de encontrar. Son los grandes tanques de almacenamiento amarillos repartidos por el puesto de avanzada. Pero ten cuidado, hay torretas defendiendo la zona, así que asegúrate de estar preparado para esquivar sus disparos o volar las armas por los aires. Tú decides cómo llevar a cabo la demolición. Las bombas serían mi primera opción, pero no me importa mucho con tal de que el trabajo se haga. - Smokey</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v> Invitados no deseados</v>
+      </c>
+    </row>
+    <row r="1073" xml:space="preserve">
+      <c r="A1073" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos a unos forajidos que se están quedando más tiempo del debido en una de nuestras estaciones. Intentaron engañarnos, pero ahora están atrapados en ~mission(location|address). Necesitamos que los elimines. Rough &amp; Ready no quiere que quede ninguno con vida cuando termines. No importa lo complicado que sea, con tal de que se haga, ¿entendido? - Smokey</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v> Trabajo de exterminio</v>
+      </c>
+    </row>
+    <row r="1075" xml:space="preserve">
+      <c r="A1075" t="str" xml:space="preserve">
+        <v xml:space="preserve"> En Rough &amp; Ready tenemos un problema de ratas. Una de nuestras tripulaciones intentó amotinarse y ahora se han apoderado de ~mission(location|address). Como no puedo estar completamente seguro de que no tengan simpatizantes a bordo, quiero que te encargues de eliminar a estos traidores. Si logras solucionar este problema de plagas, recibirás una buena recompensa. Solo asegúrate de no dejar a ninguno con vida. No quiero que a nadie más se le ocurran ideas raras. - Smokey</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v> juntos para siempre</v>
+      </c>
+    </row>
+    <row r="1077" xml:space="preserve">
+      <c r="A1077" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aquí está el trato. ~mission(TargetName) y ~mission(TargetName2) deben morir al mismo tiempo. Desafortunadamente, no estarán en el mismo lugar. Un doble impacto puede sonar complicado, pero si contratas algunos artilleros adicionales, no debería ser tan difícil lograr dos impactos simultáneos. Asegúrate de encontrar gente con habilidades, ya que tengo información fidedigna de que cada uno volará con escoltas para "protección".</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v> El doble de dolor de cabeza</v>
+      </c>
+    </row>
+    <row r="1079" xml:space="preserve">
+      <c r="A1079" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hay otro par que necesita ser asesinado simultáneamente. Parece que se está volviendo cada vez más popular como opción de asesinato. Esta vez son ~mission(TargetName) y ~mission(TargetName2). Se supone que ambos son operadores bastante hábiles y no volarán solos. Asegúrate de que quien te ayude en esta misión pueda manejar un combate.</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v> lanzamiento simultáneo</v>
+      </c>
+    </row>
+    <row r="1081" xml:space="preserve">
+      <c r="A1081" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Adivina qué tienen en común ~mission(TargetName) y ~mission(TargetName2)? ¡Vas a matarlos a ambos! Lo difícil es que necesito que los mates al mismo tiempo para que ninguno pueda escapar, o peor aún, matar a quien intenta matarlo. Así que forma un equipo para rastrear a un objetivo mientras tú te encargas del otro. ¡Divide y vencerás! Y a pesar de que armaron un lío lo suficientemente grande como para que los mataran, entiendo que son bastante débiles. No esperes mucha resistencia.</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v> amigos hasta el final</v>
+      </c>
+    </row>
+    <row r="1083" xml:space="preserve">
+      <c r="A1083" t="str" xml:space="preserve">
+        <v xml:space="preserve">Espero de verdad que no seas amigo de ~mission(TargetName) ni de ~mission(TargetName2), porque necesito que los elimines a ambos... al mismo tiempo... Claro que no nos lo pondrían fácil viajando en la misma nave o algo así de obvio. No. Tendrás que formar una tripulación para poder derribar a ambos objetivos simultáneamente. En cuanto uno de ellos muera, prepárate para eliminar al otro también. No podemos arriesgarnos a que ninguno escape. Y creo que debería mencionar que no solo son buenos pilotos, sino que también viajarán con refuerzos. Seguro que puedes con esto.</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v> doble problema</v>
+      </c>
+    </row>
+    <row r="1085" xml:space="preserve">
+      <c r="A1085" t="str" xml:space="preserve">
+        <v xml:space="preserve">Si me hubieras preguntado, te habría dicho que ~mission(TargetName) y ~mission(TargetName2) acabarían matándose entre sí. Pero en cambio, tendrás el honor de eliminarlos a ambos a la vez. Eso sí, tendrás que ganártelo. Son peligrosos. Tienen un historial delictivo, están altamente entrenados y son demasiado listos para volar sin refuerzos. Reúne al mejor equipo posible. Lo necesitarás. Y no seas tacaño. No puedes gastar créditos si estás muerto.</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v> Que la muerte nos separe</v>
+      </c>
+    </row>
+    <row r="1087" xml:space="preserve">
+      <c r="A1087" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Es bastante conmovedor encontrarse con una pareja dispuesta a morir el uno por el otro. Estúpido pero conmovedor. ~mission(TargetName) y ~mission(TargetName2) decidieron apoyarse mutuamente y ahora la situación los ha llevado a la muerte. Busca a un amigo y dales caza a estos dos. Asegúrate de matarlos al mismo tiempo. Llámalo justicia poética. Deberían morir fácilmente. Tal vez tengan una o dos naves con ellos, pero no creo que sea nada de qué preocuparse.</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>dos por el precio de dos</v>
+      </c>
+    </row>
+    <row r="1089" xml:space="preserve">
+      <c r="A1089" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Creo que podrían estar emparentados, ¿o saliendo juntos? En realidad no importa, alguien quiere matarlos. He organizado todo para que puedas atacarlos cuando no estén volando juntos. Así estarás más seguro. Son objetivos serios y cuentan con un apoyo igualmente serio. Asegúrate de que tú y tu equipo coordinen bien los ataques. No quiero que ninguno quede con vida, o será un verdadero dolor de cabeza.</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v> Asistencia en combate</v>
+      </c>
+    </row>
+    <row r="1091" xml:space="preserve">
+      <c r="A1091" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ~mission(InitiatorName) solicita asistencia en combate en ~mission(InitiatorLocation). Si se acepta, recibirá ~mission(PaymentAmount) aUEC al eliminar la amenaza.</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v> Asistencia en combate - BAJO RIESGO</v>
+      </c>
+    </row>
+    <row r="1093" xml:space="preserve">
+      <c r="A1093" t="str" xml:space="preserve">
+        <v xml:space="preserve"> [BAJO NIVEL DE AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v>Asistencia en combate - ALTA AMENAZA</v>
+      </c>
+    </row>
+    <row r="1095" xml:space="preserve">
+      <c r="A1095" t="str" xml:space="preserve">
+        <v xml:space="preserve"> [ALTA AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="str">
+        <v> Asistencia en combate - AMENAZA MODERADA</v>
+      </c>
+    </row>
+    <row r="1097" xml:space="preserve">
+      <c r="A1097" t="str" xml:space="preserve">
+        <v xml:space="preserve"> [AMENAZA MODERADA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="str">
+        <v> Asistencia en combate - AMENAZA CRÍTICA</v>
+      </c>
+    </row>
+    <row r="1099" xml:space="preserve">
+      <c r="A1099" t="str" xml:space="preserve">
+        <v xml:space="preserve"> [AMENAZA CRÍTICA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="str">
+        <v> Escolta</v>
+      </c>
+    </row>
+    <row r="1101" xml:space="preserve">
+      <c r="A1101" t="str" xml:space="preserve">
+        <v xml:space="preserve">~mission(InitiatorName) solicita un acompañante en la ubicación: ~mission(InitiatorLocation). Si se acepta, recibirá un pago de ~mission(PaymentAmount) aUEC/minuto hasta que el iniciador lo CANCELE o el proveedor del servicio lo ABANDONE. NOTA: El contrato y el pago comenzarán una vez que se reúna con el cliente.</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="str">
+        <v xml:space="preserve"> Asistencia médica</v>
+      </c>
+    </row>
+    <row r="1103" xml:space="preserve">
+      <c r="A1103" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ~mission(InitiatorName) requiere asistencia médica en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="str">
+        <v> Transporte personal</v>
+      </c>
+    </row>
+    <row r="1105" xml:space="preserve">
+      <c r="A1105" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ~mission(InitiatorName) solicita transporte desde ~mission(InitiatorLocation) hasta ~mission(SelectedDestination). Al completar con éxito este servicio, recibirá ~mission(PaymentAmount) aUEC.</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="str">
+        <v> Rescate médico</v>
+      </c>
+    </row>
+    <row r="1107" xml:space="preserve">
+      <c r="A1107" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ~mission(InitiatorName) requiere tratamiento médico de emergencia en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="str">
+        <v> Eliminar Claimjumpers</v>
+      </c>
+    </row>
+    <row r="1109" xml:space="preserve">
+      <c r="A1109" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Acabamos de recibir la noticia de que un contratista de Shubin fue expulsado de una de nuestras concesiones por forajidos que operan allí ilegalmente. Para complicar aún más las cosas, han instalado algunos centinelas orbitales para protegerse mientras extraen minerales. Esperamos contratar a un mercenario que pueda buscar y destruir los centinelas en ~mission(location). Si se encuentra con un minero ilegal en el sitio, tenga en cuenta que es práctica común que este tipo de personas contacten refuerzos para pedir ayuda. Podría ser mejor neutralizarlos lo más rápido posible antes de que puedan hacerlo. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="str">
+        <v> Expulsar a los usurpadores de derechos</v>
+      </c>
+    </row>
+    <row r="1111" xml:space="preserve">
+      <c r="A1111" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) CONDICIONES*: Un equipo minero independiente local de Stanton estaba trabajando en ~mission(Location) como contratistas de Shubin Interstellar cuando una fuerza hostil atacó y tomó el sitio. Creemos que los perpetradores todavía están en la mina usando el equipo que dejaron para extraer el valioso mineral. Entre el equipo perdido había un puñado de centinelas orbitales que, desafortunadamente, aún no se habían desplegado por completo en el momento del ataque. Los escaneos de largo alcance de la mina nos han llevado a concluir que los forajidos han activado los centinelas orbitales y los están usando para proteger sus operaciones ilegales. Para recuperar el sitio, estamos buscando contratistas que vayan a ~mission(Location), destruyan los centinelas orbitales y limpien el sitio de mineros hostiles. Se recomienda encarecidamente la eficiencia, ya que existe un alto riesgo de que pidan refuerzos una vez que descubran que están siendo desalojados. Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="str">
+        <v>Eliminar a los saltadores de reclamaciones</v>
+      </c>
+    </row>
+    <row r="1113" xml:space="preserve">
+      <c r="A1113" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Recientemente se descubrió que un minero renegado se apropió ilegalmente de una concesión minera de Shubin. Si bien el minero ya no parece estar robando mineral del sitio, dejó un centinela orbital que nos impide recuperarlo debido a sus capacidades ofensivas. Buscamos un mercenario dispuesto a viajar a ~mission(location), dar caza al centinela y destruirlo para preparar la recuperación del sitio por parte de Shubin. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="str">
+        <v> Expulsar a los usurpadores de derechos</v>
+      </c>
+    </row>
+    <row r="1115" xml:space="preserve">
+      <c r="A1115" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar deseable) CONDICIONES*: Se descubrió que una concesión minera de Shubin Interstellar, recientemente adquirida y pendiente de procesamiento, había sido usurpada por una compañía minera renegada que está robando mineral del sitio. Si bien se ha notificado a las autoridades locales, existe la preocupación de que se puedan extraer activos valiosos antes de que se inicie una investigación oficial. Por lo tanto, como es nuestro derecho como titulares de la concesión, deseamos contratar una fuerza mercenaria para que se dirija a ~mission(Location) y destruya los centinelas orbitales que protegen esta operación ilegal. Se recomienda precaución, ya que aún podría haber algunos mineros ilegales en el lugar, junto con cualquier refuerzo que reúnan. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="str">
+        <v>Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v> Orden minera pequeña: Sadaryx</v>
+      </c>
+    </row>
+    <row r="1119" xml:space="preserve">
+      <c r="A1119" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO: Orden de Minería UBICACIÓN: Nyx DETALLES: Uno de nuestros equipos de prospección confirmó recientemente que los asteroides que albergan las Estaciones de Intercambio QV en todo el Cinturón Keeger de Nyx contienen un tipo de mineral raro, Sadaryx. Sin embargo, debido a la dificultad de acceso a estas estaciones y los riesgos inherentes, estamos buscando equipos de minería externos para encargarse de la extracción. No tenemos una ubicación confirmada de dónde se encuentran los depósitos de Sadaryx dentro de la estación, pero recomendamos comenzar con las secciones de cuevas donde los minerales se forman naturalmente. Si tienen mucha suerte, incluso podrían encontrar algunos cristales almacenados que fueron extraídos por los antiguos equipos de trabajo de QV. &lt;EM4&gt;TÉRMINOS*:&lt;/EM4&gt; Su equipo deberá obtener acceso a una &lt;EM4&gt;Estación de Intercambio QV&lt;/EM4&gt;, recolectar el &lt;EM4&gt;mineral Sadaryx&lt;/EM4&gt; requerido y entregarlo al montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Esto requerirá una multiherramienta con accesorio de minería y conocimientos básicos de minería manual. Nuestros equipos de prospección han informado que estas estaciones podrían haber sido infiltradas por forajidos. Se recomienda precaución. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="str">
+        <v>Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="str">
+        <v> Gran orden de compra: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1123" xml:space="preserve">
+      <c r="A1123" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="str">
+        <v> Orden de compra médica: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1125" xml:space="preserve">
+      <c r="A1125" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde extraer&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v> Orden de compra XL: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1127" xml:space="preserve">
+      <c r="A1127" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de materiales raros. Agradecemos su ayuda en este asunto. Solo se conocen algunas ubicaciones donde se pueden obtener estos materiales, principalmente de los sitios ahora inactivos del Grupo Hathor en &lt;EM4&gt;Daymar y Aberdeen&lt;/EM4&gt;. Nuestra sugerencia sería dirigirse a las Instalaciones de Alineación de Plataformas (PAF) e intentar reactivar su Plataforma Láser Orbital (OLP) para acceder a los materiales debajo de la superficie del planeta. Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="str">
+        <v>Orden de compra XL: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1129" xml:space="preserve">
+      <c r="A1129" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="str">
+        <v> Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="str">
+        <v> Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="str">
+        <v> Gran orden de compra: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1135" xml:space="preserve">
+      <c r="A1135" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="str">
+        <v> Gran orden de compra: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1137" xml:space="preserve">
+      <c r="A1137" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v> Orden de compra médica: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1139" xml:space="preserve">
+      <c r="A1139" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde extraer&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v> Orden de compra XL: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1141" xml:space="preserve">
+      <c r="A1141" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de materiales raros. Agradecemos su ayuda en este asunto. Solo se conocen algunas ubicaciones donde se pueden obtener estos materiales, principalmente de los sitios ahora inactivos del Grupo Hathor en &lt;EM4&gt;Daymar y Aberdeen&lt;/EM4&gt;. Nuestra sugerencia sería dirigirse a las Instalaciones de Alineación de Plataformas (PAF) e intentar reactivar su Plataforma Láser Orbital (OLP) para acceder a los materiales debajo de la superficie del planeta. Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1143" xml:space="preserve">
+      <c r="A1143" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v>Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1145" xml:space="preserve">
+      <c r="A1145" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v> Orden de compra médica: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1147" xml:space="preserve">
+      <c r="A1147" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v>Orden de compra mayor: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1149" xml:space="preserve">
+      <c r="A1149" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v>Orden de compra XS: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v> Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1153" xml:space="preserve">
+      <c r="A1153" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v>Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1155" xml:space="preserve">
+      <c r="A1155" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="str">
+        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1157" xml:space="preserve">
+      <c r="A1157" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="str">
+        <v>Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1159" xml:space="preserve">
+      <c r="A1159" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="str">
+        <v> Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1161" xml:space="preserve">
+      <c r="A1161" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="str">
+        <v> Orden de compra médica: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1163" xml:space="preserve">
+      <c r="A1163" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="str">
+        <v>Orden de compra mayor: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1165" xml:space="preserve">
+      <c r="A1165" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="str">
+        <v>Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1167" xml:space="preserve">
+      <c r="A1167" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="str">
+        <v>Orden de compra especial: Materiales extraídos</v>
+      </c>
+    </row>
+    <row r="1169" xml:space="preserve">
+      <c r="A1169" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Esta orden de compra es más compleja de lo habitual, ya que requiere múltiples métodos de minería, pero dado que has demostrado tu habilidad hasta ahora, creemos que tú y tu equipo están listos para el desafío. Recordatorio: los &lt;EM4&gt;materiales deben estar refinados antes de la entrega&lt;/EM4&gt;, y dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="str">
+        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1171" xml:space="preserve">
+      <c r="A1171" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="str">
+        <v>Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1173" xml:space="preserve">
+      <c r="A1173" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="str">
+        <v> Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1175" xml:space="preserve">
+      <c r="A1175" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="str">
+        <v>Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1177" xml:space="preserve">
+      <c r="A1177" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="str">
+        <v> Orden de compra médica: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1179" xml:space="preserve">
+      <c r="A1179" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="str">
+        <v>Orden de compra mayor: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1181" xml:space="preserve">
+      <c r="A1181" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="str">
+        <v>Orden de compra XS: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="str">
+        <v> Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1185" xml:space="preserve">
+      <c r="A1185" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="str">
+        <v>Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1187" xml:space="preserve">
+      <c r="A1187" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="str">
+        <v>Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1189" xml:space="preserve">
+      <c r="A1189" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="str">
+        <v>Orden de compra especial: Materiales extraídos</v>
+      </c>
+    </row>
+    <row r="1191" xml:space="preserve">
+      <c r="A1191" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Esta orden de compra es más compleja de lo habitual, ya que requiere múltiples métodos de minería, pero dado que has demostrado tu habilidad hasta ahora, creemos que tú y tu equipo están listos para el desafío. Recordatorio: los &lt;EM4&gt;materiales deben estar refinados antes de la entrega&lt;/EM4&gt;, y dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="str">
+        <v>Pedido de suministro: Lentes Sadaryx Focus</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="str">
+        <v> Derechos mineros de la estación trituradora QV (compartidos)</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="str">
+        <v> Derechos mineros de la estación trituradora QV (compartidos)</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-320</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-320</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-546</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-546</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-127</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-127</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-425</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-425</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-608</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-608</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-267</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-267</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-235</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-235</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-304</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="str">
+        <v>Derechos mineros (compartidos) de la estación trituradora QV BRK-304</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-521</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-521</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-985</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-985</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-542</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-542</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-184</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-184</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-970</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-970</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-879</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-879</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-563</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-563</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-782</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-782</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-711</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="str">
+        <v>Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-711</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-284</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-284</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-437</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-437</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-630</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-630</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-892</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-892</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-597</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-597</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-110</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-110</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-913</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-913</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-864</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-864</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="str">
+        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-529</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="str">
+        <v>Derechos mineros (compartidos) de la estación trituradora QV BRK-529</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-709</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-709</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-766</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-766</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-223</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="str">
+        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-223</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="str">
+        <v> Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="str">
+        <v> Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="str">
+        <v> Desguace ~misión(NombreObjetivo)</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="str">
+        <v> No tengo tiempo que perder, así que iré directo al grano: ~mission(TargetName) tiene que morir y quiero que lo hagas tú. Puedes encontrarlo cerca de ~mission(Location) en ~mission(Location|address). No estará solo, pero no te distraigas con esos otros inútiles. Solo te pagan por eliminar a ~mission(TargetName|Last).</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="str">
+        <v> Misión de demolición</v>
+      </c>
+    </row>
+    <row r="1259" xml:space="preserve">
+      <c r="A1259" t="str" xml:space="preserve">
+        <v xml:space="preserve">Quiero enviar un mensaje contundente al equipo de ~mission(Location|Address) y sé la manera perfecta de hacerlo: causando daños materiales. Solo tienen que ir, destrozar algunas cosas y dejarles bien clara la importancia de respetar a los superiores. Si lo hacen, me sentiré muy feliz. Y generoso. ¿Les interesa?</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="str">
+        <v> Toma peligrosa</v>
+      </c>
+    </row>
+    <row r="1261" xml:space="preserve">
+      <c r="A1261" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tenía la esperanza de que te interesara hacer un pequeño trabajo para nosotros. Hay algunas cosas en ~mission(Location|Address) que están listas para ser tomadas. El único problema es, y es uno grande, que los desgraciados que dirigen el lugar tienen toda la zona sembrada de minas de proximidad. Tendrás que encontrar la manera de pasar, o si no te apetece, la manera de activarlas. En cualquier caso, intenta no volarte por los aires. Luego solo tienes que coger las cosas y llevarlas a ~mission(Destination|Address). No será fácil, pero si lo consigues, te prometo que merecerá la pena.</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="str">
+        <v> Venganza 01 (En desarrollo)</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="str">
+        <v>Descripción de la misión (en desarrollo)</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="str">
+        <v> Cambiar las cosas a favor</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="str">
+        <v> Cambiar las cosas a favor</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="str">
+        <v> ¿Intercambiar cupones de mercaderes por favores?</v>
+      </c>
+    </row>
+    <row r="1267" xml:space="preserve">
+      <c r="A1267" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Wikelo tiene otra forma de conseguir favores si te interesa. Tu alma mercenaria tiene metales de "scriptos", que se usan como favores, pero están hechos de un metal muy interesante que Wikelo necesita para un nuevo proyecto. Si llevas los scrips a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, los cambiaremos por favores. Adiós.</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="str">
+        <v> ¿El Consejo Comercial ofrece vales a cambio de favores?</v>
+      </c>
+    </row>
+    <row r="1269" xml:space="preserve">
+      <c r="A1269" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Si buscas otra forma de obtener favores de Wikelo, tengo algo para ti. Wikelo necesita vales que le entrega el grupo del Consejo. Wikelo no forma parte de la banda de ladrones, pero tiene negocios de vez en cuando. Si llevas vales a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, los intercambiarás por favores. Adiós.</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="str">
+        <v> ¿Intercambiar partes de gusanos por favores?</v>
+      </c>
+    </row>
+    <row r="1271" xml:space="preserve">
+      <c r="A1271" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hay una nueva forma de obtener favores de Wikelo. Se habla mucho de gusanos en tormentas de radiación. Está compuesto de muchas piezas interesantes que Wikelo utiliza. Si llevas piezas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, las intercambiarás por favores. Adiós.</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="str">
+        <v> ¿Quieres Polaris? Necesitas algo especial.</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="str">
+        <v> ¿Quieres Polaris? Necesitas algo especial.</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="str">
+        <v> Wikelo llega al sistema</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="str">
+        <v> Wikelo llega al sistema</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="str">
+        <v> Tengo mucha hambre</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="str">
+        <v> Tengo mucha hambre</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="str">
+        <v> Mira el desierto pero no te ve.</v>
+      </c>
+    </row>
+    <row r="1279" xml:space="preserve">
+      <c r="A1279" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Estás en el desierto caliente haciendo cosas. Necesitas ser sigiloso. No quieres que te vean. Entiende. Wikelo te dará una armadura que te hará sigiloso en la arena. Trae las cosas a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y lo haré. Fácil. Adiós.</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="str">
+        <v> Hacer un arma Sandy</v>
+      </c>
+    </row>
+    <row r="1281" xml:space="preserve">
+      <c r="A1281" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Wikelo puede hacer que la nueva pistola VOLT parezca un montón de arena. Es muy sigilosa en el desierto. Lleva las cosas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y Wikelo se encargará. Adiós.</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="str">
+        <v> ¿Quieres que tu armadura parezca un árbol?</v>
+      </c>
+    </row>
+    <row r="1283" xml:space="preserve">
+      <c r="A1283" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola. ¿Te gusta pasear por el bosque pero no quieres que nadie lo sepa? Wikelo tiene una armadura para ti. Si la traes a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, podrás conseguirla. ¿Te interesa?</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="str">
+        <v> Pistola Zappy más parecida a la madera</v>
+      </c>
+    </row>
+    <row r="1285" xml:space="preserve">
+      <c r="A1285" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Wikelo se enteró de un nuevo tipo de arma de energía de VOLT souli. Golpeó muy fuerte. Si quieres, Wikelo puede hacer que el arma se vea aún mejor. Se encontró en la tormenta, dispara tormenta, pero Wikelo la hizo parecer más leñosa. ¿Cayó en el bosque? Desapareció. Trae las cosas a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y Wikelo lo hará. Adiós.</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="str">
+        <v> Fabricar armadura naval espacial</v>
+      </c>
+    </row>
+    <row r="1287" xml:space="preserve">
+      <c r="A1287" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Sé que a los humanos les gusta la armada. Wikelo lo entiende. Barcos muy grandes. Y poderosos también. Wikelo puede darte un conjunto de armadura que parezca de color azul marino. Es muy fácil de hacer. Mira lo que Wikelo necesita, consíguelo y tráelo a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y será tuyo. Wikelo</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="str">
+        <v> El arma Volt es más parecida a la de la Marina.</v>
+      </c>
+    </row>
+    <row r="1289" xml:space="preserve">
+      <c r="A1289" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wikelo se enteró de la nueva arma de energía de VOLT Souli. Si quieres, Wikelo puede mejorar el aspecto del arma. Se encuentra en Storm, dispara Storm, pero Wikelo la mejorará para quienes prefieren Human Navy. Trae las cosas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y Wikelo lo hará. Adiós.</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="str">
+        <v> Ahora fabrica Polaris. Oferta por tiempo limitado.</v>
+      </c>
+    </row>
+    <row r="1291" xml:space="preserve">
+      <c r="A1291" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Wikelo ha conseguido recientemente muchos planos a cambio de un humano no muy inteligente. Ahora puede construir naves muy grandes. No son baratas y requieren muchas piezas, pero se construirán. Si quieres, date prisa, esto le cuesta mucho a Wikelo, así que no podrá hacerlo por mucho tiempo, pero me gusta el nuevo sistema humano, así que quiero agradeceros a todos la bienvenida. Llévalo a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; si quieres. Adiós.</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="str">
+        <v> Apolo de la Lucha Roja</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="str">
+        <v> Apollo es una nave muy buena. Sería mucho mejor si fuera roja. Wikelo hace que todo sea posible. Intercambia lo que yo quiero y cerramos el trato.</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="str">
+        <v> Haz que el ATLS se ponga nervioso.</v>
+      </c>
+    </row>
+    <row r="1295" xml:space="preserve">
+      <c r="A1295" t="str" xml:space="preserve">
+        <v xml:space="preserve">Encuentra una pieza muy divertida para añadir a un traje humano grande que te permita saltar muy alto. Ahora dispara y salta. ¡Emocionante! Si quieres, tráeme esto a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;. Lo haré. Wikelo</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="str">
+        <v> Haz que ATLS dispare</v>
+      </c>
+    </row>
+    <row r="1297" xml:space="preserve">
+      <c r="A1297" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola. Sé que a ti, humano, te gustan los trajes metálicos extraños. ¿Qué te parece un traje metálico con ikti? Lo siento, ikti es una palabra Banu, tú la llamas 'pistola'. Si quieres, trae lo que te diga y te la haré. La pistola disparará. Causará mucho daño. Adiós.</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="str">
+        <v> Prueba de armadura</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="str">
+        <v> Tráeme armadura y otras cosas y te daré una armadura de prueba especial. Primera versión. Muy especial. Tráela y te la daré. Adiós.</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="str">
+        <v> Arma curiosa</v>
+      </c>
+    </row>
+    <row r="1301" xml:space="preserve">
+      <c r="A1301" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Wikelo encontró un arma muy extraña pero funcional mientras exploraba tus sistemas. Es muy simple pero muy efectiva. Si me traes algo, te mostraré lo que hago con ello. Muy divertido.</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="str">
+        <v> ¿Quieres ver mejor?</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="str">
+        <v> Wikelo tiene los mejores ojos para ver a lo lejos. Te doy si me das.</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="str">
+        <v> El F55 se ve mejor</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="str">
+        <v> veces disparas a la gente, pero si eres lo último que ven antes de morir, el arma debería verse increíble, ¿verdad? Wikelo hará que tu arma se vea mucho mejor. Tráeme lo que necesito y luego te doy el arma. Adiós.</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="str">
+        <v> Escopeta de combate roja</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="str">
+        <v> Disparar puede ser un desastre. Sangre humana roja por todas partes. Con esta escopeta no hay problema. ¡Las salpicaduras se camuflan perfectamente! Te la doy si me das todo lo que pido en la lista. Buen trato.</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="str">
+        <v> Traje de constructor brillante</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="str">
+        <v> Necesitas un traje de trabajo. Ideal para el trabajo. Si quieres, Wikelo puede hacerlo más brillante. Quedará genial. Consulta con Wikelo qué necesitas y tráelo.</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="str">
+        <v> Traje de nieve oculto</v>
+      </c>
+    </row>
+    <row r="1311" xml:space="preserve">
+      <c r="A1311" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Quieres estar escondido. Wikelo lo entiende. No preguntes por qué. ¿Pero qué haces cuando estás en la nieve? Wikelo tiene un traje para eso. Bienvenido.</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="str">
+        <v> Crea armaduras brillantes</v>
+      </c>
+    </row>
+    <row r="1313" xml:space="preserve">
+      <c r="A1313" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wikelo tuvo una idea genial durante un breve descanso. Estaba pensando en las pequeñas luciérnagas de Pyro y vio cómo la armadura se modificaba para parecerse a ellas. Si me consigues las piezas, tráelas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y te las haré para que tú también puedas brillar. Adiós.</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="str">
+        <v> Pistola de calavera Fun Kopion</v>
+      </c>
+    </row>
+    <row r="1315" xml:space="preserve">
+      <c r="A1315" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola. Puedo hacerle modificaciones divertidas al arma si quieres. Usa la skin de Kopion para el patrón y el pequeño colgante de calavera. Es muy efectiva. Dispara mucho mejor. Solo tienes que traerme las piezas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y la haré. Adiós.</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="str">
+        <v> Pistola de dientes Fun Kopion</v>
+      </c>
+    </row>
+    <row r="1317" xml:space="preserve">
+      <c r="A1317" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola. Puedo hacerle modificaciones divertidas al arma si quieres. Si no te gusta decir que no es una calavera de bebé, tienes otra opción. Usa la piel de kopion para el patrón, pero usa un diente en lugar de un colgante. Sigue siendo efectivo y dispara mejor. Trae las piezas a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y las fabricaré. Adiós.</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="str">
+        <v> Lobo Extra Especial</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="str">
+        <v>Wikelo está muy emocionado. Tiene una idea para un nuevo material. Pero fabricarlo es muy complicado. Necesito ayuda para fabricar una muestra de prueba. Te doy el plano, lo fabricas, me lo traes y te lo cambio. Te doy un L-22 Wolf extra especial. Muy potente, muy lobo.</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="str">
+        <v> Zapper VOLT pesado</v>
+      </c>
+    </row>
+    <row r="1321" xml:space="preserve">
+      <c r="A1321" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesitas un arma útil. Sí, sí, lo entiendo. Wikelo también hace que las armas útiles sean más bonitas. Ves cosas que necesito. ¿Las traes? Sí. Adiós.</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="str">
+        <v> Pistola con calavera militar divertida</v>
+      </c>
+    </row>
+    <row r="1323" xml:space="preserve">
+      <c r="A1323" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola. Puedo hacer una versión del arma si quieres un soldado. Haz un material como el camuflaje del soldado pero con una calavera muerta en el frente. El arma también dispara mejor. Si quieres, trae la pieza a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y la haré.</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="str">
+        <v> Pistola militar divertida con forma de diente</v>
+      </c>
+    </row>
+    <row r="1325" xml:space="preserve">
+      <c r="A1325" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Aquí Wikelo con otra forma de jugar con este tipo de arma. Haz que se parezca más a tu arma de soldado, pero con un diente de kopion colgando. Realmente desagradable. Si quieres, trae la pieza a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y la haré. Adiós.</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="str">
+        <v> Traje de lava</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="str">
+        <v>Si tienes armadura, Wikelo puede hacer que se vea cálida. Buen aspecto para una armadura útil. Tráeme cosas y lo haré.</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="str">
+        <v xml:space="preserve"> Tu mejor oportunidad</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="str">
+        <v> Este rifle dispara muy bien, pero podría tener un diseño más bonito. Arreglo de Wikelo. Ahora se ve muy bien. Te lo doy a cambio. Tráeme cosas y te doy el rifle. Incluso te doy el plano si lo necesitas.</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="str">
+        <v> Hot Shot</v>
+      </c>
+    </row>
+    <row r="1331" xml:space="preserve">
+      <c r="A1331" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesitas una buena arma, ¿verdad? Aquí tienes una. Pequeña pero potente. Como un chile balalu extra picante. Wikelo también hace que esta pistola parezca extra picante. Tú traes lo que necesito y yo hago un intercambio. Adiós.</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="str">
+        <v> Armadura de combate roja</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="str">
+        <v> Wikelo oyó que los humanos piensan que el rojo es el color de la pasión y la ira. Esta armadura es buena para ambas. Dame los objetos de la lista y esta armadura roja será tuya.</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="str">
+        <v> Armadura con cuerno y cuerda</v>
+      </c>
+    </row>
+    <row r="1335" xml:space="preserve">
+      <c r="A1335" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, sé que muchos humanos quieren saldynium para problemas de regeneración. Los créditos son buenos, sí, pero Wikelo puede usar eso, cuerno de kopion y otras cosas para hacer una armadura especial. Una vez hecha, serás muy duro. Da mucho miedo. Verás los objetos necesarios. Tráelos a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y los haré por ti. Adiós.</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="str">
+        <v> Cañón Yormandi</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="str">
+        <v> Esta pistola tiene la imagen de una criatura asombrosa en un costado. Úsala y te hará grande y fuerte como Yormandi. Escupe rayos. Tráeme mis objetos y entonces la obtendrás. Adiós.</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="str">
+        <v> Armadura con Vanduul</v>
+      </c>
+    </row>
+    <row r="1339" xml:space="preserve">
+      <c r="A1339" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Vanduul tiene costumbres extrañas. Nunca hablo con ellos, el viejo souli sí, pero Wikelo no. De todos modos, aunque no son amigables, hacen cosas interesantes. Si quieres, Wikelo puede hacer que te parezcas más a ellos. Trae cosas. Lo haré. Adiós.</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="str">
+        <v> ¡Prepárate y despega!</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="str">
+        <v xml:space="preserve"> Las naves tienen ventanas grandes. Todos pueden verte volar. Debes lucir impecable. Wikelo tiene un traje de vuelo excelente para ti. Intercambia conmigo lo que necesito y Wikelo te dará el traje. Si no tienes el plano, tráemelo también.</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="str">
+        <v>Haz que la escopeta VOLT se enfurezca más.</v>
+      </c>
+    </row>
+    <row r="1343" xml:space="preserve">
+      <c r="A1343" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¿Sientes que el arma no es lo suficientemente agresiva? ¿La escopeta VOLT es muy potente, muy peligrosa, pero no da miedo? Tráela. Puede hacer que te dé mucho miedo y te enfade. Entonces te respetarán. Tráela a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y lo haremos. Adiós.</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="str">
+        <v> agachadiza de nieve</v>
+      </c>
+    </row>
+    <row r="1345" xml:space="preserve">
+      <c r="A1345" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¿Quieres disparar desde lejos y esconderte? ¿Pero está nevando? Wikelo tiene un arma para ti. Trae tus cosas. Te las doy. Adiós.</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="str">
+        <v> Mod de lucha de Asgard</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="str">
+        <v> Mod de lucha de Asgard</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="str">
+        <v xml:space="preserve"> ¿Listos para RAFT?</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="str">
+        <v xml:space="preserve"> ¿Listos para RAFT?</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="str">
+        <v> Quiero un barco Tauro</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="str">
+        <v> Quiero un barco Tauro</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="str">
+        <v> Mod de guerra Starlifter A2</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="str">
+        <v> Mod de guerra Starlifter A2</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="str">
+        <v> Golem Rocas</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="str">
+        <v> Golem Rocas</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="str">
+        <v> Wikelo Navy F7</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="str">
+        <v> Wikelo Navy F7</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="str">
+        <v> Mod de guerra F8</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="str">
+        <v> Mod de guerra F8</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="str">
+        <v> Apuñalador sigiloso</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="str">
+        <v> Apuñalador sigiloso</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="str">
+        <v> Mod de Firebird</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="str">
+        <v> Mod de Firebird</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="str">
+        <v> Barco de la fortuna para ti</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="str">
+        <v> Barco de la fortuna para ti</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="str">
+        <v> Mod de lucha del guardián</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="str">
+        <v> Mod de lucha del guardián</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="str">
+        <v> Guardian WiK-X</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="str">
+        <v> Guardian WiK-X</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="str">
+        <v> El guardián derriba el barco</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="str">
+        <v> El guardián derriba el barco</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="str">
+        <v>Idris especial por matar</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="str">
+        <v> Idris especial por matar</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="str">
+        <v> Actualizar Intrepid</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="str">
+        <v> Actualizar Intrepid</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="str">
+        <v> ¿Dónde está Wolf? Aquí Wolf</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="str">
+        <v> ¿Dónde está Wolf? Aquí Wolf</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="str">
+        <v> Mod de meteorito RSI</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="str">
+        <v> Mod de meteorito RSI</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="str">
+        <v> Las perspectivas son buenas.</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="str">
+        <v> Las perspectivas son buenas.</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="str">
+        <v> Mod Noxy</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="str">
+        <v> Mod Noxy</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="str">
+        <v> Peregrino Wikelo Mod</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="str">
+        <v> Peregrino Wikelo Mod</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="str">
+        <v> Prowler Más utilidad</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="str">
+        <v> Prowler Más utilidad</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="str">
+        <v> Pulse Plus</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="str">
+        <v> Pulse Plus</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="str">
+        <v> Construye un Mod Scorpius</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="str">
+        <v> Construye un Mod Scorpius</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="str">
+        <v> Mod Spirit Cargo</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="str">
+        <v> Mod Spirit Cargo</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="str">
+        <v> Starfighter Inferno Especial</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="str">
+        <v> Starfighter Inferno Especial</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="str">
+        <v> Ion, el astuto caza estelar</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="str">
+        <v> Ion, el astuto caza estelar</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="str">
+        <v> Nueva nave espacial Big Starlancer</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="str">
+        <v> Nueva nave espacial Big Starlancer</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="str">
+        <v> Más que un máximo</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="str">
+        <v> Más que un máximo</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="str">
+        <v> ¿Qué es Terrapin?</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="str">
+        <v> ¿Qué es Terrapin?</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="str">
+        <v> Crea un mod para Ursa</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="str">
+        <v> Crea un mod para Ursa</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="str">
+        <v> Lobo más especial</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="str">
+        <v> Lobo más especial</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="str">
+        <v> Zeus Cargo Especial</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="str">
+        <v> Zeus Cargo Especial</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="str">
+        <v> Especial de Zeus</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="str">
+        <v> Especial de Zeus</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="str">
+        <v> Reparar la pistola Coda</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="str">
+        <v>Reparar la pistola Coda</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="str">
+        <v> Camina en peligro. Luce bien.</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="str">
+        <v> Camina en peligro. Luce bien.</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="str">
+        <v> Embellecer Karna Gun</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="str">
+        <v> Embellecer Karna Gun</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="str">
+        <v> Construido sobre el rifle S71</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="str">
+        <v> Construido sobre el rifle S71</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="str">
+        <v> Una aventura de una vida</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="str">
+        <v> Una aventura de una vida</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="str">
+        <v> Traje Xi'an Xanthule mejorado</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="str">
+        <v> Traje Xi'an Xanthule mejorado</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="str">
+        <v> Tutorial - Tus primeros pasos</v>
+      </c>
+    </row>
+    <row r="1425" xml:space="preserve">
+      <c r="A1425" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¡Enhorabuena por tus primeros pasos en el universo! A lo largo de este tutorial, aprenderás a moverte tanto a pie como en el espacio. Para empezar, te familiarizarás con los controles básicos de movimiento y el uso de tu mobiGlas dentro de tu hábitat. Sigue los objetivos y las indicaciones de tu HUD (pantalla de visualización frontal) para completar esta misión.</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="str">
+        <v> Tutorial - Tu primera salida</v>
+      </c>
+    </row>
+    <row r="1427" xml:space="preserve">
+      <c r="A1427" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Bien hecho! Con la primera parte completada, ya deberías tener cierta familiaridad con los controles de movimiento, la gestión de tu hambre y sed, y algunas de las funciones principales de tu mobiGlas, concretamente el Gestor de Contratos y tu Diario. Esta siguiente sección te ayudará a familiarizarte con ~mission(Location|Name) y te llevará a visitar ~mission(StoreName), una tienda de armas aquí en ~mission(Location|Name). Puedes comprar allí, y en otras tiendas similares, usando Créditos de la Tierra Unida (UEC). Durante la fase alfa del desarrollo de Star Citizen, utilizaremos una moneda llamada aUEC (Créditos de la Tierra Unida Alfa). Esta es una moneda temporal diseñada específicamente para probar la economía y el equilibrio del juego.</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="str">
+        <v> Tutorial - Tu primer vuelo</v>
+      </c>
+    </row>
+    <row r="1429" xml:space="preserve">
+      <c r="A1429" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ya casi terminas el tutorial. ¡Solo queda despegar! Con tu misión en ~mission(Location|Name) terminada, es hora de abandonar la ciudad y, finalmente, el planeta. Dirígete a las lanzaderas de tránsito de ~mission(TransitNameShort). Estas lanzaderas te pueden llevar por toda ~mission(Location|Name), pero tu destino es el puerto espacial, donde te han proporcionado temporalmente una Anvil C8 Pisces. Esta nave de exploración es una excelente nave de iniciación, perfecta para pilotos novatos que buscan obtener sus alas.</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="str">
+        <v> Ruta de envío local de UDM</v>
+      </c>
+    </row>
+    <row r="1431" xml:space="preserve">
+      <c r="A1431" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Saludos, socio de envíos calificado! Hoy es el día perfecto para adquirir experiencia práctica en envíos. Si dispone de un barco con suficiente espacio de almacenamiento, hay una buena cantidad de paquetes en ~mission(Pickup1) en ~mission(Pickup1|Address) listos para ser entregados. ¡Una excelente oportunidad para el crecimiento profesional! PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="str">
+        <v>Controlador de paquetes UDM</v>
+      </c>
+    </row>
+    <row r="1433" xml:space="preserve">
+      <c r="A1433" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Saludos, experto en manipulación de paquetes! Aunque no tengan que ir muy lejos, los siguientes paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; requieren un manejo experto. ¿Eres el experto que buscamos? PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Solo tienes que aceptar el contrato y listo. Esperamos trabajar contigo, Unified Distribution Management -Ofreciendo el paquete completo-</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="str">
+        <v xml:space="preserve">Ruta de entrega local de UDM</v>
+      </c>
+    </row>
+    <row r="1435" xml:space="preserve">
+      <c r="A1435" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! ¿Busca una excusa para surcar los cielos con su nave de carga? Gane créditos y explore la zona con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si ser su propio supervisor y que le paguen por pilotar su propia nave le parece el trabajo perfecto, este contrato es justo lo que estaba buscando. Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="str">
+        <v> Evaluación de la entrega local de UDM</v>
+      </c>
+    </row>
+    <row r="1437" xml:space="preserve">
+      <c r="A1437" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Saludos, potencial socio de envío cualificado! ¿Listo para contribuir a nuestra creciente red de entregas? ¿Tienes una nave a tu disposición que pueda transportar varios paquetes y volar entre cuerpos celestes y satélites? ¡Unified Distribution Management busca un piloto como tú! Nos encantaría evaluar tu potencial de contratación con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si esto te interesa, ¡acepta esta oferta de inmediato! Solo asegúrate de traer tu propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar contigo, Unified Distribution Management -Entregando el paquete completo-</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="str">
+        <v> Reevaluación de la entrega local de UDM</v>
+      </c>
+    </row>
+    <row r="1439" xml:space="preserve">
+      <c r="A1439" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Saludos, antiguo socio naviero cualificado! ¿Estás listo para otra oportunidad de usar tu buque listo para el transporte de carga y ganar créditos? Unified Distribution Management ha elegido el siguiente itinerario cuidadosamente seleccionado como la manera perfecta de reevaluar sus habilidades: PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos volver a trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="str">
+        <v>Recogida de paquetes UDM</v>
+      </c>
+    </row>
+    <row r="1441" xml:space="preserve">
+      <c r="A1441" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! Si buscas trabajo como repartidor, ¡tenemos la oportunidad perfecta para ti! Un paquete te espera en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser entregado en &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. ¿Suena interesante, verdad? Advertencia: se han registrado varias alertas de seguridad en la zona. Asegúrate de llevar contigo medidas de protección para mantenerte a salvo. Si esto te interesa, ¡acepta esta oferta de inmediato! Esperamos trabajar contigo. Unified Distribution Management -Entregando el paquete completo-</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="str">
+        <v> SOLICITUD DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="str">
+        <v> SOLICITUD DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="str">
+        <v xml:space="preserve"> SOLICITUD DE REPOSTAJE CRÍTICA: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="str">
+        <v xml:space="preserve"> SOLICITUD DE REPOSTAJE CRÍTICA: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="str">
+        <v> UWC CONTRATA PERSONAL PARA REPOSTEAR COMBUSTIBLES</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="str">
+        <v> UWC CONTRATA PERSONAL PARA REPOSTEAR COMBUSTIBLES</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="str">
+        <v> SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="str">
+        <v> SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="str">
+        <v> REPOSTAJE URGENTE DE LA FLOTA</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="str">
+        <v>REPOSTAJE URGENTE DE LA FLOTA</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="str">
+        <v> Todas las cosas llegan a su fin.</v>
+      </c>
+    </row>
+    <row r="1453" xml:space="preserve">
+      <c r="A1453" t="str" xml:space="preserve">
+        <v xml:space="preserve"> No sé si conoces ~mission(Location|Address), pero ~mission(TargetName) es quien manda allí. Necesito eliminarlos. Me temo que es más fácil decirlo que hacerlo. Son conocidos por su renuencia a ocuparse personalmente de los asuntos, prefiriendo que sus subordinados se encarguen del trabajo sucio. Dicho esto, si eliminas a suficientes subordinados, no les quedará más remedio que enfrentarse a ti directamente. Atentamente, Vaughn</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="str">
+        <v> Se les echará de menos.</v>
+      </c>
+    </row>
+    <row r="1455" xml:space="preserve">
+      <c r="A1455" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un alto funcionario de seguridad llamado ~mission(TargetName) ha sido marcado para su eliminación. Aunque se encuentra en ~mission(Location|Address), no será fácil llegar hasta él. Me temo que será necesario un esfuerzo considerable para atraerlo. Normalmente, recomendaría eliminar a suficientes subordinados como para que se vea obligado a enfrentarse a usted personalmente. Sin embargo, en este caso se requiere un enfoque más delicado. Si bien puede eliminar a todas las fuerzas de seguridad presentes, debe garantizar la seguridad de todos los trabajadores civiles. Sin duda, es una tarea ardua, pero necesaria. Atentamente, Vaughn</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="str">
+        <v> Una oportunidad para impresionar</v>
+      </c>
+    </row>
+    <row r="1457" xml:space="preserve">
+      <c r="A1457" t="str" xml:space="preserve">
+        <v xml:space="preserve">En primer lugar, permítame presentarme. Para decirlo de forma un tanto dramática, me dedico a la vida. La gente me contrata cuando hay que eliminar a alguien, y yo, a cambio, empleo a la persona perfecta para hacerlo. Esto proporciona seguridad a todas las partes involucradas, ya que nadie conoce la identidad de la otra. Una situación ideal en estos casos. Recientemente me enteré de que usted podría poseer habilidades que me serían útiles y decidí que valdría la pena investigar esta afirmación. Si le interesa establecer una relación laboral, necesitaré una demostración de dichas habilidades. Busque y elimine discretamente a ~mission(TargetName) en ~mission(Location|Address). Si lo logra, será recompensado. Además, habrá demostrado ser digno de ser considerado para futuras contrataciones. Atentamente, Vaughn</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="str">
+        <v> Otra oportunidad para impresionar</v>
+      </c>
+    </row>
+    <row r="1459" xml:space="preserve">
+      <c r="A1459" t="str" xml:space="preserve">
+        <v xml:space="preserve">No es frecuente en la vida tener una segunda oportunidad para causar una buena primera impresión, pero te la voy a brindar. Decir que me decepcionó cómo se desarrollaron las cosas en tu último intento de asesinato sería quedarse corto. Sin embargo, esta es tu oportunidad para demostrar que eres capaz de más. Elimina a ~mission(TargetName) en ~mission(Location|Address) y consideraré que has borrado el pasado. Atentamente, Vaughn</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="str">
+        <v> Fin de una salamandra</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="str">
+        <v> Fin de una salamandra</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="str">
+        <v> Un merecido descanso</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="str">
+        <v> Un merecido descanso</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="str">
+        <v> Un contrato desafiante</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="str">
+        <v> Un contrato desafiante</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="str">
+        <v> Otro desafío que debe ser eliminado</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="str">
+        <v> Otro desafío que debe ser eliminado</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="str">
+        <v> Matar a un fantasma</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="str">
+        <v> Matar a un fantasma</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="str">
+        <v> Contrato de Pyro</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="str">
+        <v> Contrato de Pyro</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="str">
+        <v> Localizar a un miembro de la pandilla</v>
+      </c>
+    </row>
+    <row r="1473" xml:space="preserve">
+      <c r="A1473" t="str" xml:space="preserve">
+        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de nivel Clips de la banda Headhunters, ~mission(TargetName|Last) ha liderado operaciones dirigidas contra operativos, misiones e infraestructura de XenoThreat. Por estas transgresiones, XenoThreat pagará a cualquiera que logre localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto cerca de ~mission(Location|Address) hace poco. Si decide aceptar este contrato, diríjase a las coordenadas de inmediato. ~mission(TargetName|Last) sabe que lo estamos buscando y ha estado viajando con un escolta recientemente. No se sorprenda si no está solo. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="str">
+        <v> Localiza al traidor</v>
+      </c>
+    </row>
+    <row r="1475" xml:space="preserve">
+      <c r="A1475" t="str" xml:space="preserve">
+        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). ~mission(TargetName|Last), un conocido miembro de la banda Headhunters, ha traicionado a la humanidad al ser un aliado alienígena conocido con quien mantiene relaciones tanto personales como comerciales. XenoThreat exige que estas relaciones traidoras cesen de inmediato antes de que traigan más influencia alienígena a Pyro. Recompensaremos a quien logre localizar y asesinar a ~mission(TargetName|Last) por estos crímenes contra la humanidad. ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="str">
+        <v> Rastrear al espía</v>
+      </c>
+    </row>
+    <row r="1477" xml:space="preserve">
+      <c r="A1477" t="str" xml:space="preserve">
+        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de la banda Headhunters, ~mission(TargetName|Last) hackeó los sistemas de XenoThreat para robar información sobre nuestras operaciones y personal. El daño causado solo puede repararse asegurándonos de que ~mission(TargetName|Last) jamás vuelva a hacer algo así. Por eso, XenoThreat pagará a cualquiera que pueda localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: Escaneos recientes identificaron a ~mission(TargetName|Last) viajando con otras naves cerca de ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="str">
+        <v> Centinelas del silencio</v>
+      </c>
+    </row>
+    <row r="1479" xml:space="preserve">
+      <c r="A1479" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nuestro movimiento de resistencia crece día a día, pero esto conlleva cierta atención no deseada. Escaneos recientes descubrieron centinelas orbitales en ~mission(location|address) y una nave patrullando. Creemos que esto forma parte de una campaña de espionaje contra XenoThreat, probablemente financiada por la UEE. Buscamos un mercenario experimentado dispuesto a destruir los centinelas cuanto antes. Dado que ya nos tienen vigilados, enviar a alguien ajeno a la organización llamaría menos la atención. Si aceptas el trabajo, recibirás tu pago inmediatamente una vez destruidos los centinelas. Ahora bien, aunque la nave patrulla no es el objetivo principal, sospechamos que si escapa podría tener refuerzos en reserva. Sería prudente neutralizarla cuanto antes. Si decides ayudarnos, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="str">
+        <v> Aniquilar centinelas</v>
+      </c>
+    </row>
+    <row r="1481" xml:space="preserve">
+      <c r="A1481" t="str" xml:space="preserve">
+        <v xml:space="preserve">Escaneos recientes descubrieron varios centinelas orbitales y naves en ~mission(location|address). Creemos que forman parte de una campaña de espionaje contra XenoThreat, en respuesta a nuestras acciones recientes en el sistema Stanton. Parece que XenoThreat está haciendo algo bien, si están espiando de esta manera. Buscamos un mercenario experimentado y altamente capacitado dispuesto a eliminar esta operación. Si no quieres que Pyro se convierta en un sistema de vigilancia, esta es tu oportunidad para impedirlo. Los centinelas probablemente no representen un gran problema, pero ten cuidado con las naves de patrulla. Si logran escapar, tendrás muchos más problemas pisándote los talones. Te estaremos agradecidos y te pagaremos generosamente una vez que completes el trabajo. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="str">
+        <v> Finalización de la vigilancia</v>
+      </c>
+    </row>
+    <row r="1483" xml:space="preserve">
+      <c r="A1483" t="str" xml:space="preserve">
+        <v xml:space="preserve">Parece que nuestra lucha por liberar a la humanidad tiene nerviosos a los lacayos del gobierno en la Tierra. Escaneos recientes descubrieron un centinela orbital en ~mission(location|address) que creemos forma parte de una campaña de espionaje de la UEE. Según nuestros informes, están entregando los datos directamente a los propios slinks. Solo se ha detectado un centinela hasta ahora, pero quién sabe hasta dónde llegará la operación si no se desactiva. No debería ser demasiado problema para un mercenario habilidoso. Si te identificas con esto, recibirás el pago inmediatamente después de destruir el centinela. Además, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="str">
+        <v> Erradicar centinelas</v>
+      </c>
+    </row>
+    <row r="1485" xml:space="preserve">
+      <c r="A1485" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Valoras la libertad de la humanidad? Si es así, te ofrezco la oportunidad de demostrarlo. Escaneos recientes han detectado centinelas orbitales y naves patrullando en ~mission(location|address). Creemos que forman parte de una campaña de espionaje de la UEE contra XenoThreat. Es crucial detener su labor de recopilación de inteligencia antes de lanzar nuestra próxima misión. Buscamos un mercenario experimentado dispuesto a eliminar estas fuerzas de inmediato. Los centinelas son la prioridad, pero las naves podrían representar un problema mayor si logran escapar. Deberás evaluar la situación con más detalle una vez que estés en el lugar. Podríamos encargarnos nosotros mismos, pero preferimos enviar a un contratista para que los responsables no sepan quién los atacó. El pago se realizará puntualmente al finalizar la misión. Además, tendrás la satisfacción de saber que estás ayudando a una buena causa. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="str">
+        <v> Borrado total del servidor</v>
+      </c>
+    </row>
+    <row r="1487" xml:space="preserve">
+      <c r="A1487" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de nuestros agentes de datos desapareció mientras transportaba información operativa vital. Hace unas horas, determinamos que fue atacado por un grupo de asalto de Headhunters y que el contenido de los almacenes de datos de la nave fue transferido a sus servidores en ~mission(location|address). Si bien tenemos motivos para creer que nuestro cifrado resistirá, no podemos arriesgarnos a que el contenido de esos archivos quede expuesto. Se le ordena dirigirse allí y garantizar la privacidad de nuestros datos destruyendo los servidores de Headhunters. Le recomiendo encarecidamente que actúe con la máxima minuciosidad. Destruya todo y a todos los que pueda. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="str">
+        <v> Sabotaje de la línea de suministro</v>
+      </c>
+    </row>
+    <row r="1489" xml:space="preserve">
+      <c r="A1489" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los supuestos “activistas” de salón de Ciudadanos por la Prosperidad siguen intentando extender su influencia por todo el sistema. Con tu ayuda, existe la oportunidad de desmantelar sus operaciones de raíz. El grupo utiliza ~mission(location|address) para distribuir suministros a independientes dispersos por todo el planeta. Si destruimos la ~mission(ship) ubicada allí, su red colapsará. Un bombardeo enviaría un mensaje claro, pero te dejo a ti la decisión sobre el método de destrucción. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="str">
+        <v> Orden de eliminación: "Ciudadanos" en ~mission(location)</v>
+      </c>
+    </row>
+    <row r="1491" xml:space="preserve">
+      <c r="A1491" t="str" xml:space="preserve">
+        <v xml:space="preserve">El grupo de instigadores que se autodenomina «Ciudadanos por la Prosperidad» ya no puede seguir difundiendo sus mentiras y propaganda impunemente. Como un claro recordatorio de quién controla realmente a Pyro, hemos emitido una orden de eliminación para erradicar toda presencia de «Ciudadanos» en ~misión(ubicación|dirección). Es probable que haya resistencia, pero esperamos que la resuelvan sin mayores dificultades. Sigan las instrucciones y recibirán una buena recompensa por su trabajo. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="str">
+        <v> Lucha por un Pyro gratis</v>
+      </c>
+    </row>
+    <row r="1493" xml:space="preserve">
+      <c r="A1493" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los esfuerzos de XenoThreat por evitar que influencias externas infecten este sistema están siendo puestos a prueba por un grupo que se atreve a llamarse Ciudadanos por la Prosperidad. Un miembro destacado del grupo, ~mission(TargetName), ha establecido operaciones en ~mission(Location|Address) y ya está trabajando arduamente difundiendo sus mentiras y propaganda a cualquiera que quiera escuchar. Si queremos que Pyro permanezca independiente de la UEE y de la influencia alienígena, entonces debemos hacer algo al respecto ahora. Por eso XenoThreat está emitiendo una orden de eliminación para ~mission(TargetName|Last). Y sabiendo lo importantes que son para las operaciones de Ciudadanos por la Prosperidad, no me sorprendería que tuvieras que abrirte paso luchando contra un grupo de sus seguidores más fanáticos antes de siquiera tener la oportunidad de dispararles. Pero recuerda que ~mission(TargetName|Last) es tu objetivo, y el pago depende únicamente de que te asegures de eliminarlo. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="str">
+        <v> Búsqueda de talentos</v>
+      </c>
+    </row>
+    <row r="1495" xml:space="preserve">
+      <c r="A1495" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los Cazadores de Cabezas han reunido un equipo de ataque especial cuyo único propósito es atacar, interrumpir y sabotear nuestras operaciones. Aunque me cueste admitirlo, han tenido algunos éxitos menores y se están convirtiendo rápidamente en una preocupación. XenoThreat sabe que la mejor manera de matar a una serpiente es cortándole la cabeza, así que emitimos una orden de eliminación para el comandante del equipo de ataque, ~mission(TargetName), quien, según nuestras fuentes de inteligencia, se ha estado escondiendo en ~mission(Location|Address) durante algunos días. Preveo una fuerte resistencia por parte de las fuerzas de los Cazadores de Cabezas allí. Por lo que hemos oído, ~mission(TargetName|Last) recibió este mando en parte debido a la feroz lealtad que inspira en los demás. Reunir a tu propio equipo para abordar esto sería una sólida estrategia operativa. Feliz caza de cabezas, Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="str">
+        <v> Robar subsidios</v>
+      </c>
+    </row>
+    <row r="1497" xml:space="preserve">
+      <c r="A1497" t="str" xml:space="preserve">
+        <v xml:space="preserve">Típico de la UEE mentirosa, decir que no está involucrada en las operaciones de Ciudadanos por la Prosperidad simplemente porque "donan" suministros a una organización de ayuda terciaria que luego se los entrega inmediatamente. Acabamos de enterarnos de que uno de estos envíos de ayuda gubernamental fue entregado en un puesto avanzado alineado con Ciudadanos por la Prosperidad. Por eso te pagaremos para que asaltes ~mission(Pickup1|Address) y reclames el ~mission(item) para la causa. Una vez que entregues todo en ~mission(Dropoff1|Address), podremos redistribuir el envío para ayudar en nuestra lucha. No hay nada mejor que usar los recursos del enemigo en su contra. Pero no creas que te lo van a entregar así como así. Aunque se supone que Ciudadanos por la Prosperidad está aquí para traer la paz, será mejor que estés preparado para enfrentarte a ellos. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="str">
+        <v> Suministros para la recuperación de bienes</v>
+      </c>
+    </row>
+    <row r="1499" xml:space="preserve">
+      <c r="A1499" t="str" xml:space="preserve">
+        <v xml:space="preserve">Por mucho que XenoThreat se haya esforzado por hacer de Pyro un refugio seguro para los humanos, no todos comparten nuestros objetivos. Entre ellos destacan los Cazadores de Cabezas, que se han degradado al contratar a un transportista alienígena para que les entregue suministros. Perdimos la oportunidad de interceptar ese cargamento, pero aun así queremos dejar claro que no se tolerará la colaboración con alienígenas bajo ninguna circunstancia en este sistema. El cargamento fue entregado en ~mission(Pickup1|Address). Queremos que alguien ataque el puesto de avanzada, reclame el ~mission(item) y lo lleve a ~mission(Dropoff1|Address) para que podamos deshacernos de él adecuadamente. ¿Te animas a mantener Pyro libre de la influencia alienígena? Comm. Spec. Engler</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="str">
+        <v> Agente del Caos</v>
+      </c>
+    </row>
+    <row r="1501" xml:space="preserve">
+      <c r="A1501" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ciudadanos por la Prosperidad se han atrincherado en ~mission(Pickup1|Address). Para evitar que se acomoden demasiado en esa estación, queremos mostrarles cómo es realmente la vida en nuestro sistema. Te pagaremos para que vayas a la estación, recojas el ~mission(item) y mates a cualquiera que se interponga en tu camino. El pago depende de que entregues esos suministros en ~mission(Dropoff1|Address). Cualquiera que mates será una ventaja. Especialista en Comunicaciones Engler</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="str">
         <v> Precio de los negocios</v>
       </c>
     </row>
-    <row r="609" xml:space="preserve">
-      <c r="A609" t="str" xml:space="preserve">
+    <row r="1503" xml:space="preserve">
+      <c r="A1503" t="str" xml:space="preserve">
         <v xml:space="preserve">No sé si has tenido el placer de tratar con los Rough &amp; Ready, pero la banda está totalmente centrada en acaparar el mercado del combustible en Pyro. Es una jugada inteligente, pero no podemos permitir que suceda sin que nos den algunas concesiones. Como no están interesados en negociar, nos vemos obligados a mostrarles lo que les pasa a quienes se oponen a nosotros. Hemos identificado ~mission(Pickup1|Address) como un objetivo principal para dicho ataque. También sabemos que recientemente recibieron suministros que deberían ser un precio justo por su obstinación. Una vez dentro de la estación, haz lo que sea necesario para confiscar el ~mission(item). Enviaremos el pago una vez que lo hayas entregado en ~mission(Dropoff1|Address). Especialista en Comunicaciones Engler</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A609"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A1503"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/work/from_google/missions.xlsx
+++ b/work/from_google/missions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A1503"/>
+  <dimension ref="A1:A1151"/>
   <cols>
     <col min="1" max="1" width="150.83203125" customWidth="1"/>
   </cols>
@@ -444,7 +444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -454,72 +454,72 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v> Recompensa preliminar: ~misión(Nombre del objetivo)</v>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v> Recompensa preliminar: ~misión(Nombre del objetivo)</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
+        <v> Recompensa verificada: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) | Cazadores de cabezas | ~misión(Peligro)</v>
+        <v xml:space="preserve"> Certificación de Detención de Sospechosos</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) | Cazadores de cabezas | ~misión(Peligro)</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
+        <v> Certificación de Permiso de Iniciación para Rastreadores</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v> Recompensa verificada: ~mission(TargetName)</v>
+        <v> Certificación de recuperación de fugitivos</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v> Recompensa verificada: ~mission(TargetName)</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Recompensa verificada: ~misión(Nombre del objetivo) | Amenaza alienígena | ~misión(Peligro)</v>
+        <v> Certificación de Licencia de Rastreador Oficial</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) | Amenaza alienígena | ~misión(Peligro)</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve"> Certificación de Detención de Sospechosos</v>
+        <v> Certificación de licencia de rastreador</v>
       </c>
     </row>
     <row r="25">
@@ -529,7 +529,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v> Certificación de Permiso de Iniciación para Rastreadores</v>
+        <v> Certificación de Licencia de Rastreador Maestro</v>
       </c>
     </row>
     <row r="27">
@@ -539,7 +539,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v> Certificación de recuperación de fugitivos</v>
+        <v> Certificación de Permiso de Capacitación en Rastreo</v>
       </c>
     </row>
     <row r="29">
@@ -549,7 +549,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v> Certificación de Licencia de Rastreador Oficial</v>
+        <v> Certificación de licencia de rastreador avanzado</v>
       </c>
     </row>
     <row r="31">
@@ -559,7 +559,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v> Certificación de licencia de rastreador</v>
+        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
       </c>
     </row>
     <row r="33">
@@ -569,122 +569,122 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v> Certificación de Licencia de Rastreador Maestro</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v/>
+        <v> En llamas</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v> Certificación de Permiso de Capacitación en Rastreo</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v/>
+        <v> Mal funcionamiento grave</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str" xml:space="preserve">
+        <v xml:space="preserve"> No voy a entrar en detalles sobre el porqué, pero hay algunas partes de ~mission(Location|Address) que necesitamos destruir. Lo importante es que quiero pagarte una buena cantidad de créditos por hacerlo. Casi siento que deberías pagarnos tú por esto, porque va a ser muy divertido. No me importa cómo lo hagas. Granadas, lanzacohetes, Torpedo Burrito del día anterior, nos da igual. -Bit Zeros</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v> Certificación de licencia de rastreador avanzado</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v/>
+        <v> Servidor no encontrado</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, tenemos un problema en el que podríamos necesitar tu ayuda. Uno de nuestros exreclutas hizo un trabajo pésimo en un hackeo y dejó una huella digital tan desastrosa que casi podría considerarse una confesión. Un borrado remoto no será suficiente, así que quiero que vayas a ~mission(Location|Address) y te asegures de que sus servidores de datos sean eliminados por completo. Como si esto no fuera ya un lío mayor, los códigos de acceso a la puerta cerrada de la sala de servidores solo se almacenan físicamente allí. Eso significa que primero tendrás que conseguir un datapad con el código antes de poder siquiera acercarte a ellos. Pero no te preocupes, me aseguraré de que las credenciales valgan la pena. - Bit Zeros</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
+        <v> Golpéalos donde más les duele</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los cretinos de ~mission(Location|Address) decidieron que sería buena idea interferir en nuestros asuntos, y ahora debemos dejarles bien claro que se equivocaron. Tras investigar un poco sus datos, descubrimos dónde guardan su mercancía. Ahora solo tienes que ir allí y destruirlo todo. Creo que con eso les quedará claro. - Bit Zeros</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v> En llamas</v>
+        <v> Eliminar permanentemente</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
+        <v xml:space="preserve"> Esos cretinos repugnantes de ~mission(Location|Address) nos han estado vendiendo datos basura mientras intentaban engañarnos. No podemos permitirlo. Queremos que les des una última lección y elimines a todos los cobardes que encuentres. La última vez que supe de ellos, estaban escondidos cerca de ~mission(Location). Si los derribas, te llenaremos la cartera. -Bit Zeros</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v> Mal funcionamiento grave</v>
+        <v> Reasignación de propiedad</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str" xml:space="preserve">
-        <v xml:space="preserve"> No voy a entrar en detalles sobre el porqué, pero hay algunas partes de ~mission(Location|Address) que necesitamos destruir. Lo importante es que quiero pagarte una buena cantidad de créditos por hacerlo. Casi siento que deberías pagarnos tú por esto, porque va a ser muy divertido. No me importa cómo lo hagas. Granadas, lanzacohetes, Torpedo Burrito del día anterior, nos da igual. -Bit Zeros</v>
+        <v xml:space="preserve">Muy bien, en ~mission(Location|Address) tienen algunas cosas que necesitan ser recuperadas. Claro que puede que tengas que lidiar con algunos guardias o personas preocupadas, pero en general es una transacción bastante sencilla: toma las cosas de ~mission(Location) y tráelas a ~mission(Destination|Address). A veces, lo simple es lo mejor. -Bit Zeros</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v> Servidor no encontrado</v>
+        <v> Tratos delicados</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos un problema en el que podríamos necesitar tu ayuda. Uno de nuestros exreclutas hizo un trabajo pésimo en un hackeo y dejó una huella digital tan desastrosa que casi podría considerarse una confesión. Un borrado remoto no será suficiente, así que quiero que vayas a ~mission(Location|Address) y te asegures de que sus servidores de datos sean eliminados por completo. Como si esto no fuera ya un lío mayor, los códigos de acceso a la puerta cerrada de la sala de servidores solo se almacenan físicamente allí. Eso significa que primero tendrás que conseguir un datapad con el código antes de poder siquiera acercarte a ellos. Pero no te preocupes, me aseguraré de que las credenciales valgan la pena. - Bit Zeros</v>
+        <v xml:space="preserve">Espero de verdad que aceptes hacer esto, ya que no parece haber mucha gente dispuesta a encargarse de un montón de minas de proximidad. Verás, hemos encontrado un botín en ~mission(Location|Address), pero la seguridad física está resultando más difícil de lo esperado. Si encuentras la manera de sortear las minas o, posiblemente, de activarlas a distancia, debería ser relativamente fácil recoger el botín y escapar. Déjalo en ~mission(Destination|Address) y recibirás una buena parte de los créditos por correr el riesgo. -Bit Zeros</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v> Golpéalos donde más les duele</v>
+        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (?RT)</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los cretinos de ~mission(Location|Address) decidieron que sería buena idea interferir en nuestros asuntos, y ahora debemos dejarles bien claro que se equivocaron. Tras investigar un poco sus datos, descubrimos dónde guardan su mercancía. Ahora solo tienes que ir allí y destruirlo todo. Creo que con eso les quedará claro. - Bit Zeros</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan capturar a una persona con el nombre ~mission(TargetName) en ~mission(Location|Address). Si bien puede haber otros cómplices criminales en el lugar, les pido que tengan cuidado con los civiles o trabajadores que puedan estar allí. Ya tengo suficientes problemas, así que no necesito explicar por qué un contratista disparó a varios civiles. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v> Eliminar permanentemente</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Esos cretinos repugnantes de ~mission(Location|Address) nos han estado vendiendo datos basura mientras intentaban engañarnos. No podemos permitirlo. Queremos que les des una última lección y elimines a todos los cobardes que encuentres. La última vez que supe de ellos, estaban escondidos cerca de ~mission(Location). Si los derribas, te llenaremos la cartera. -Bit Zeros</v>
+        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Actualmente tengo más recompensas que cazarrecompensas, así que busco ampliar nuestra plantilla. Si hacen un buen trabajo en esta primera misión, habrá más contratos. Veamos cómo les va con la recompensa en ~mission(TargetName). Se cree que se esconden en ~mission(Location|Address). Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v> Reasignación de propiedad</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Muy bien, en ~mission(Location|Address) tienen algunas cosas que necesitan ser recuperadas. Claro que puede que tengas que lidiar con algunos guardias o personas preocupadas, pero en general es una transacción bastante sencilla: toma las cosas de ~mission(Location) y tráelas a ~mission(Destination|Address). A veces, lo simple es lo mejor. -Bit Zeros</v>
+        <v xml:space="preserve">ATENCIÓN: Excazador de recompensas de BlacJac. Sé que BlacJac dejó de ofrecer contratos de recompensa, pero los tiempos cambian y aquí estamos para darle otra oportunidad. Si logra completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reactivar su cuenta. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v> Tratos delicados</v>
+        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (ERT)</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
       <c r="A55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espero de verdad que aceptes hacer esto, ya que no parece haber mucha gente dispuesta a encargarse de un montón de minas de proximidad. Verás, hemos encontrado un botín en ~mission(Location|Address), pero la seguridad física está resultando más difícil de lo esperado. Si encuentras la manera de sortear las minas o, posiblemente, de activarlas a distancia, debería ser relativamente fácil recoger el botín y escapar. Déjalo en ~mission(Destination|Address) y recibirás una buena parte de los créditos por correr el riesgo. -Bit Zeros</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Quizás hayan oído hablar de ~mission(TargetName). Son un objetivo de alto riesgo y han estado en las noticias últimamente. Esperamos que puedan formar un equipo de respuesta y ayudar a BlacJac a neutralizarlos definitivamente. Según nuestra información más reciente, su nave subcapital y escoltas fuertemente armadas sobrevuelan ~mission(Location|Address). Les recomiendo asegurarse de tener una identificación actualizada antes de partir. Por si acaso. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (?RT)</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (HRT)</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan capturar a una persona con el nombre ~mission(TargetName) en ~mission(Location|Address). Si bien puede haber otros cómplices criminales en el lugar, les pido que tengan cuidado con los civiles o trabajadores que puedan estar allí. Ya tengo suficientes problemas, así que no necesito explicar por qué un contratista disparó a varios civiles. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Su próximo objetivo, ~mission(TargetName), es sin duda un objetivo de alto riesgo, y con razón. Se sabe que viaja con armamento pesado y cuenta con suficiente protección como para que cualquiera se lo piense dos veces antes de enfrentarse a él. Según fuentes, ~mission(TargetName|Last) se esconde en ~mission(Location|Address). Cuando salgan a buscarlo, asegúrense de estar preparados. Quizás incluso deberían llevar refuerzos. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="58">
@@ -694,4732 +694,4732 @@
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Actualmente tengo más recompensas que cazarrecompensas, así que busco ampliar nuestra plantilla. Si hacen un buen trabajo en esta primera misión, habrá más contratos. Veamos cómo les va con la recompensa en ~mission(TargetName). Se cree que se esconden en ~mission(Location|Address). Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazadores de recompensas. No sé si les interesa, pero BlacJac busca ampliar su equipo de cazarrecompensas. Tenemos más trabajos de los que nuestros contratistas actuales pueden cubrir, así que espero que puedan ayudarnos a cubrir parte de la carga de trabajo. Sus cualificaciones se ven bien en papel, pero antes de formalizar nada, BlacJac necesita ver su desempeño en el campo. Incluso tenemos un caso de prueba preparado: queremos que resuelvan la misión ~(Nombre del objetivo). Fueron vistos por última vez en ~misión(Ubicación|Dirección). Debería ser una recompensa bastante sencilla, sin demasiada resistencia. Una oportunidad perfecta para que se pongan a prueba. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (LRT)</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Excazador de recompensas de BlacJac. Sé que BlacJac dejó de ofrecer contratos de recompensa, pero los tiempos cambian y aquí estamos para darle otra oportunidad. Si logra completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reactivar su cuenta. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Se ha ofrecido una recompensa por un objetivo de bajo riesgo llamado ~mission(TargetName). El objetivo en sí no es muy peligroso, pero parece que suelen volar en grupo, así que hay muchas probabilidades de que vengan acompañados cuando los localicen. Por cierto, les recomiendo comenzar la búsqueda en ~mission(Location|Address), ya que tenemos informes de que los han visto en la zona. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (ERT)</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Quizás hayan oído hablar de ~mission(TargetName). Son un objetivo de alto riesgo y han estado en las noticias últimamente. Esperamos que puedan formar un equipo de respuesta y ayudar a BlacJac a neutralizarlos definitivamente. Según nuestra información más reciente, su nave subcapital y escoltas fuertemente armadas sobrevuelan ~mission(Location|Address). Les recomiendo asegurarse de tener una identificación actualizada antes de partir. Por si acaso. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan que se encarguen de ~mission(TargetName), una recompensa de riesgo moderado vista por última vez en ~mission(Location|Address) pilotando una pequeña nave con tripulación múltiple. No pudimos obtener detalles sobre la nave que pilotaban, pero parece que tenían otras naves con ellos. Prepárense para una fuerte resistencia cuando lleguen. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (HRT)</v>
+        <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Su próximo objetivo, ~mission(TargetName), es sin duda un objetivo de alto riesgo, y con razón. Se sabe que viaja con armamento pesado y cuenta con suficiente protección como para que cualquiera se lo piense dos veces antes de enfrentarse a él. Según fuentes, ~mission(TargetName|Last) se esconde en ~mission(Location|Address). Cuando salgan a buscarlo, asegúrense de estar preparados. Quizás incluso deberían llevar refuerzos. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> ATENCIÓN: Excazador de recompensas de BlacJac. Sé que tu última misión para BlacJac no salió bien, pero el aumento de casos significa que tienes la suerte de tener otra oportunidad. Si logras completar la misión en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reincorporarte. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VHRT)</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazadores de recompensas. No sé si les interesa, pero BlacJac busca ampliar su equipo de cazarrecompensas. Tenemos más trabajos de los que nuestros contratistas actuales pueden cubrir, así que espero que puedan ayudarnos a cubrir parte de la carga de trabajo. Sus cualificaciones se ven bien en papel, pero antes de formalizar nada, BlacJac necesita ver su desempeño en el campo. Incluso tenemos un caso de prueba preparado: queremos que resuelvan la misión ~(Nombre del objetivo). Fueron vistos por última vez en ~misión(Ubicación|Dirección). Debería ser una recompensa bastante sencilla, sin demasiada resistencia. Una oportunidad perfecta para que se pongan a prueba. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas BlacJac acaba de recibir información de que un objetivo de altísimo riesgo, ~mission(TargetName), fue avistado en las rutas aéreas de ~mission(Location|Address) pilotando una formidable nave con una fuerte escolta. Queremos eliminar esta recompensa antes de que cometa más delitos. Reúnan los recursos y el apoyo que necesiten y salgan cuanto antes. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (LRT)</v>
+        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VLRT)</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Se ha ofrecido una recompensa por un objetivo de bajo riesgo llamado ~mission(TargetName). El objetivo en sí no es muy peligroso, pero parece que suelen volar en grupo, así que hay muchas probabilidades de que vengan acompañados cuando los localicen. Por cierto, les recomiendo comenzar la búsqueda en ~mission(Location|Address), ya que tenemos informes de que los han visto en la zona. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Tengo un objetivo de muy bajo riesgo del que debo encargarme: ~mission(NombreDelObjetivo). Su última ubicación conocida fue ~mission(Ubicación|Dirección). Se trata de una recompensa de bajo riesgo, así que espero que puedan resolverla rápidamente. Suelen pilotar una nave pequeña y no tienen muchos conocidos. Es una misión sencilla. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (MRT)</v>
+        <v>Proteger el sitio y obtener materiales confidenciales.</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
       <c r="A71" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan que se encarguen de ~mission(TargetName), una recompensa de riesgo moderado vista por última vez en ~mission(Location|Address) pilotando una pequeña nave con tripulación múltiple. No pudimos obtener detalles sobre la nave que pilotaban, pero parece que tenían otras naves con ellos. Prepárense para una fuerte resistencia cuando lleguen. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Mercenarios con experiencia en manejo de carga. Nine Tails está atacando una de nuestras instalaciones en ~mission(Location|address). Dado que acaban de recibir un envío de material confidencial, no creemos que sea una coincidencia. BlacJac necesita que alguien se dirija rápidamente al lugar y asegure estas cajas importantes antes de que lo haga Nine Tails. Están autorizados a usar fuerza letal contra cualquiera que intente detenerlos. Como parte de nuestro protocolo de seguridad estándar, el material confidencial se integró en otro envío y se guardó en la bóveda automatizada. Deberán encontrar los códigos de recuperación correspondientes para el material confidencial e introducirlos en la cinta transportadora de paquetes para recuperar las cajas. Los códigos de recuperación se almacenan localmente en tabletas de datos y solo se entregan al personal de alto rango. Esperemos que estén vivos para ayudarlos, pero considerando el apagón total de comunicaciones, tememos que no sea así. Existe la posibilidad de que Nine Tails ya se haya apoderado de las tabletas de datos. Una vez que haya reunido todo el material confidencial, deberá entregarlo en ~mission(dropoff1|address). El pago está condicionado a su entrega. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v> Contrato de prueba de recompensa de BlacJac</v>
+        <v>Proteger el sitio de amenazas menores</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
       <c r="A73" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Excazador de recompensas de BlacJac. Sé que tu última misión para BlacJac no salió bien, pero el aumento de casos significa que tienes la suerte de tener otra oportunidad. Si logras completar la misión en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reincorporarte. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> ATENCIÓN: Operadores Mercenarios Verificados. Uno de los sitios bajo la supervisión de BlacJac ha tenido enfrentamientos con algunos delincuentes locales. Les pedimos que se dirijan a ~mission(Ubicación|Dirección) y aseguren el sitio de estas amenazas. Según los primeros informes, esto será bastante sencillo, pero si lo desean, pueden reclutar un equipo para que les brinde apoyo adicional. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VHRT)</v>
+        <v> Proteja el sitio de amenazas</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
       <c r="A75" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas BlacJac acaba de recibir información de que un objetivo de altísimo riesgo, ~mission(TargetName), fue avistado en las rutas aéreas de ~mission(Location|Address) pilotando una formidable nave con una fuerte escolta. Queremos eliminar esta recompensa antes de que cometa más delitos. Reúnan los recursos y el apoyo que necesiten y salgan cuanto antes. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que algunos matones locales han estado haciendo amenazas contra ~mission(Location|Address). BlacJac busca que formen un equipo para proteger el sitio de estas amenazas. Y aunque a todos nos encantan los créditos, no recomiendo intentar hacerlo solos. Contratar un equipo sería beneficioso para su sustento. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VLRT)</v>
+        <v> Proteja el sitio de amenazas peligrosas.</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
       <c r="A77" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Tengo un objetivo de muy bajo riesgo del que debo encargarme: ~mission(NombreDelObjetivo). Su última ubicación conocida fue ~mission(Ubicación|Dirección). Se trata de una recompensa de bajo riesgo, así que espero que puedan resolverla rápidamente. Suelen pilotar una nave pequeña y no tienen muchos conocidos. Es una misión sencilla. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. He recibido un informe de que algunos operadores planean un ataque contra ~mission(Location|Address). BlacJac les pide que formen un equipo para defender el sitio de esta peligrosa amenaza. Se recomienda encarecidamente no intentar completar este contrato en solitario. Contratar un equipo de mercenarios experimentados para que les brinden apoyo sería la opción más inteligente. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security. "Protección garantizada".</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Proteger el sitio y obtener materiales confidenciales.</v>
+        <v> Eliminar el alijo de drogas</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
       <c r="A79" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Mercenarios con experiencia en manejo de carga. Nine Tails está atacando una de nuestras instalaciones en ~mission(Location|address). Dado que acaban de recibir un envío de material confidencial, no creemos que sea una coincidencia. BlacJac necesita que alguien se dirija rápidamente al lugar y asegure estas cajas importantes antes de que lo haga Nine Tails. Están autorizados a usar fuerza letal contra cualquiera que intente detenerlos. Como parte de nuestro protocolo de seguridad estándar, el material confidencial se integró en otro envío y se guardó en la bóveda automatizada. Deberán encontrar los códigos de recuperación correspondientes para el material confidencial e introducirlos en la cinta transportadora de paquetes para recuperar las cajas. Los códigos de recuperación se almacenan localmente en tabletas de datos y solo se entregan al personal de alto rango. Esperemos que estén vivos para ayudarlos, pero considerando el apagón total de comunicaciones, tememos que no sea así. Existe la posibilidad de que Nine Tails ya se haya apoderado de las tabletas de datos. Una vez que haya reunido todo el material confidencial, deberá entregarlo en ~mission(dropoff1|address). El pago está condicionado a su entrega. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Parece que hay un nuevo operador intentando fabricar drogas en ~mission(Location|Address), pero el producto que está produciendo es extremadamente tóxico. Estamos analizando cómo proceder con los arrestos, pero lo importante es evitar que se distribuya más de su mercancía. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. Es muy probable que la instalación no esté abandonada, así que podrían encontrarse con estos delincuentes al llegar. Prepárense para una pelea. Pero si su habilidad con las armas es similar a su química, probablemente no será muy dura. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Proteger el sitio de amenazas menores</v>
+        <v> Destruir drogas peligrosas</v>
       </c>
     </row>
     <row r="81" xml:space="preserve">
       <c r="A81" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Operadores Mercenarios Verificados. Uno de los sitios bajo la supervisión de BlacJac ha tenido enfrentamientos con algunos delincuentes locales. Les pedimos que se dirijan a ~mission(Ubicación|Dirección) y aseguren el sitio de estas amenazas. Según los primeros informes, esto será bastante sencillo, pero si lo desean, pueden reclutar un equipo para que les brinde apoyo adicional. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Unos químicos emprendedores han creado un nuevo producto que es el doble de potente y letal que el original. Hemos podido rastrear algunas muestras hasta la fuente en ~mission(Location|Address). BlacJac quiere que vayas cuanto antes para destruir todo el lote antes de que pueda perjudicar a más personas. Ya nos ocuparemos de los arrestos después. Por lo que sabemos de este grupo, debes esperar una fuerte resistencia al intentar eliminar el alijo. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v> Proteja el sitio de amenazas</v>
+        <v> Eliminar las drogas</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
       <c r="A83" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que algunos matones locales han estado haciendo amenazas contra ~mission(Location|Address). BlacJac busca que formen un equipo para proteger el sitio de estas amenazas. Y aunque a todos nos encantan los créditos, no recomiendo intentar hacerlo solos. Contratar un equipo sería beneficioso para su sustento. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos enteramos de que un sindicato adulteró un paquete de drogas de un rival y está causando caos en las calles. Los forenses han identificado la fuente: una planta de producción ubicada en ~mission(Location|Address). Se rumorea que los fabricantes de drogas ni siquiera saben que tienen droga envenenada. Estamos analizando cómo proceder con los arrestos, pero lo importante es sacar esta porquería de las calles ahora. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. No les hará ninguna gracia, así que probablemente tendrán que enfrentarse a una pelea, pero lo importante es eliminar el producto. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v> Proteja el sitio de amenazas peligrosas.</v>
+        <v> Proteger el sitio</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
       <c r="A85" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. He recibido un informe de que algunos operadores planean un ataque contra ~mission(Location|Address). BlacJac les pide que formen un equipo para defender el sitio de esta peligrosa amenaza. Se recomienda encarecidamente no intentar completar este contrato en solitario. Contratar un equipo de mercenarios experimentados para que les brinden apoyo sería la opción más inteligente. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security. "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. El equipo de seguridad de ~mission(Location|Address) nos ha informado de que algunos delincuentes locales han estado realizando ataques. BlacJac busca que acudan al lugar para ayudar a protegerlo de amenazas hostiles. Asegúrense de controlar el fuego allí abajo. No quiero oír hablar de ningún incidente entre fuerzas propias. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v> Eliminar el alijo de drogas</v>
+        <v> Contrato de prueba del sitio de protección</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
       <c r="A87" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Parece que hay un nuevo operador intentando fabricar drogas en ~mission(Location|Address), pero el producto que está produciendo es extremadamente tóxico. Estamos analizando cómo proceder con los arrestos, pero lo importante es evitar que se distribuya más de su mercancía. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. Es muy probable que la instalación no esté abandonada, así que podrían encontrarse con estos delincuentes al llegar. Prepárense para una pelea. Pero si su habilidad con las armas es similar a su química, probablemente no será muy dura. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. BlacJac busca ampliar su equipo de profesionales de seguridad. Para evaluar si usted encaja en el perfil, le solicitamos que preste apoyo en ~mission(Location|Address), ya que han tenido problemas con personas hostiles en la zona. Si puede ayudar a proteger el sitio y eliminar la amenaza, podremos ofrecerle más trabajo de seguridad. Tenga en cuenta que no se tolerarán incidentes de fuego amigo. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v> Destruir drogas peligrosas</v>
+        <v> Contrato de prueba del sitio de protección</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
       <c r="A89" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Unos químicos emprendedores han creado un nuevo producto que es el doble de potente y letal que el original. Hemos podido rastrear algunas muestras hasta la fuente en ~mission(Location|Address). BlacJac quiere que vayas cuanto antes para destruir todo el lote antes de que pueda perjudicar a más personas. Ya nos ocuparemos de los arrestos después. Por lo que sabemos de este grupo, debes esperar una fuerte resistencia al intentar eliminar el alijo. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">ATENCIÓN: Exoperador Mercenario. Sé que BlacJac dejó de ofrecer servicios de seguridad, pero debido a cambios en el personal, se decidió ofrecerle otra oportunidad. Nos han informado que ~mission(Location|Address) necesita ayuda para lidiar con una banda local de forajidos. BlacJac busca que usted acuda al lugar y ayude a eliminar esta amenaza. Y dado que su situación ya es delicada, no quiero oír que haya estado involucrado en ningún incidente de fuego amigo. Si logra llevar a cabo esta operación con éxito, podemos considerar su reincorporación. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v> Eliminar las drogas</v>
+        <v> Despejar el sitio</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
       <c r="A91" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos enteramos de que un sindicato adulteró un paquete de drogas de un rival y está causando caos en las calles. Los forenses han identificado la fuente: una planta de producción ubicada en ~mission(Location|Address). Se rumorea que los fabricantes de drogas ni siquiera saben que tienen droga envenenada. Estamos analizando cómo proceder con los arrestos, pero lo importante es sacar esta porquería de las calles ahora. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. No les hará ninguna gracia, así que probablemente tendrán que enfrentarse a una pelea, pero lo importante es eliminar el producto. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que ~mission(Location|Address) está siendo utilizada por delincuentes locales como base de operaciones. BlacJac busca que ustedes realicen una inspección del sitio y eliminen a cualquier persona hostil. Nuestros primeros informes indican que es muy probable que la banda tenga civiles trabajando para ellos en el lugar. No buscamos ser noticia, así que recuerden que solo están autorizados a interactuar con personas hostiles confirmadas. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v> Proteger el sitio</v>
+        <v> Buscando Zeta-Prolanide</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
       <c r="A93" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. El equipo de seguridad de ~mission(Location|Address) nos ha informado de que algunos delincuentes locales han estado realizando ataques. BlacJac busca que acudan al lugar para ayudar a protegerlo de amenazas hostiles. Asegúrense de controlar el fuego allí abajo. No quiero oír hablar de ningún incidente entre fuerzas propias. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> Se rumorea que han robado una gran cantidad de Zeta-Prolanida en ~mission(Location|address). Si encuentras alguna, tráela a ~mission(DropOffLocation|address) y te aseguraremos un buen precio. Si no, puedes rechazar esta oferta sin problema.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v> Contrato de prueba del sitio de protección</v>
+        <v> ALERTA DE CDF: ~misión(Ubicación) Se necesitan agentes para bloquear el acceso</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
       <c r="A95" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. BlacJac busca ampliar su equipo de profesionales de seguridad. Para evaluar si usted encaja en el perfil, le solicitamos que preste apoyo en ~mission(Location|Address), ya que han tenido problemas con personas hostiles en la zona. Si puede ayudar a proteger el sitio y eliminar la amenaza, podremos ofrecerle más trabajo de seguridad. Tenga en cuenta que no se tolerarán incidentes de fuego amigo. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Una flota hostil de naves equipadas con inhibidores cuánticos ha creado un bloqueo alrededor de ~mission(Location|address), ha desactivado las torretas defensivas de la estación y ha robado una gran cantidad de Zeta-Prolanida. En respuesta, la CDF ha recibido autorización para activar su fuerza de voluntarios. Aunque la situación general es crítica, el robo de la Zeta-Prolanida es nuestra prioridad. Sin una acción directa, la pérdida de las reservas de Zeta-Prolanida del sector podría tener efectos devastadores en la economía de todo el sistema. Mientras las fuerzas de seguridad locales investigan la incursión, han rastreado el inventario robado hasta varias ubicaciones. Los voluntarios de la CDF tienen la misión de dirigirse a estas ubicaciones, recuperar la Zeta-Prolanida robada y transportarla de vuelta a la estación antes de que el material se degrade por completo y deje de ser viable. Tengan cuidado, la información sugiere que los cúmulos más grandes de Zeta-Prolanida tienen una mayor presencia de delincuentes. Dado que el tiempo apremia, se recomienda encarecidamente contar con un rayo tractor para facilitar el traslado de la carga. Como incentivo adicional, los voluntarios recibirán bonificaciones periódicas por su colaboración.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v> Contrato de prueba del sitio de protección</v>
-      </c>
-    </row>
-    <row r="97" xml:space="preserve">
-      <c r="A97" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Exoperador Mercenario. Sé que BlacJac dejó de ofrecer servicios de seguridad, pero debido a cambios en el personal, se decidió ofrecerle otra oportunidad. Nos han informado que ~mission(Location|Address) necesita ayuda para lidiar con una banda local de forajidos. BlacJac busca que usted acuda al lugar y ayude a eliminar esta amenaza. Y dado que su situación ya es delicada, no quiero oír que haya estado involucrado en ningún incidente de fuego amigo. Si logra llevar a cabo esta operación con éxito, podemos considerar su reincorporación. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v>Recompensa emitida: ~mission(TargetName)</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v> Despejar el sitio</v>
+        <v> Superando el desafío</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
       <c r="A99" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que ~mission(Location|Address) está siendo utilizada por delincuentes locales como base de operaciones. BlacJac busca que ustedes realicen una inspección del sitio y eliminen a cualquier persona hostil. Nuestros primeros informes indican que es muy probable que la banda tenga civiles trabajando para ellos en el lugar. No buscamos ser noticia, así que recuerden que solo están autorizados a interactuar con personas hostiles confirmadas. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v xml:space="preserve"> La CDF se ha asociado con Anvil Aerospace para encontrar a los operativos más capaces del sistema. Si encuentras una de estas certificaciones Platino, puedes canjear el boleto en un quiosco de naves en New Deal, Astro Armada o Crusader Showroom por un F8C gratis. La condición es que tu identidad y ubicación se han compartido con los participantes de todo el sistema. Para los demás, si logras detener al poseedor del boleto antes de que llegue al quiosco, puedes reclamarlo para ti. Quien lo consiga no solo recibirá este caza de superioridad de última generación, sino que también demostrará que tiene lo necesario para las misiones más difíciles de la CDF. ¡Buena suerte!</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v> Buscando Zeta-Prolanide</v>
-      </c>
-    </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se rumorea que han robado una gran cantidad de Zeta-Prolanida en ~mission(Location|address). Si encuentras alguna, tráela a ~mission(DropOffLocation|address) y te aseguraremos un buen precio. Si no, puedes rechazar esta oferta sin problema.</v>
+        <v> Eliminar las estaciones de servicio</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v> ALERTA DE CDF: ~misión(Ubicación) Se necesitan agentes para bloquear el acceso</v>
-      </c>
-    </row>
-    <row r="103" xml:space="preserve">
-      <c r="A103" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Una flota hostil de naves equipadas con inhibidores cuánticos ha creado un bloqueo alrededor de ~mission(Location|address), ha desactivado las torretas defensivas de la estación y ha robado una gran cantidad de Zeta-Prolanida. En respuesta, la CDF ha recibido autorización para activar su fuerza de voluntarios. Aunque la situación general es crítica, el robo de la Zeta-Prolanida es nuestra prioridad. Sin una acción directa, la pérdida de las reservas de Zeta-Prolanida del sector podría tener efectos devastadores en la economía de todo el sistema. Mientras las fuerzas de seguridad locales investigan la incursión, han rastreado el inventario robado hasta varias ubicaciones. Los voluntarios de la CDF tienen la misión de dirigirse a estas ubicaciones, recuperar la Zeta-Prolanida robada y transportarla de vuelta a la estación antes de que el material se degrade por completo y deje de ser viable. Tengan cuidado, la información sugiere que los cúmulos más grandes de Zeta-Prolanida tienen una mayor presencia de delincuentes. Dado que el tiempo apremia, se recomienda encarecidamente contar con un rayo tractor para facilitar el traslado de la carga. Como incentivo adicional, los voluntarios recibirán bonificaciones periódicas por su colaboración.</v>
+        <v> Reducir la preparación operativa de Outlaw</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Recompensa emitida: ~mission(TargetName)</v>
+        <v> Alerta: ~misión(Ubicación) bajo ataque</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v> Superando el desafío</v>
-      </c>
-    </row>
-    <row r="107" xml:space="preserve">
-      <c r="A107" t="str" xml:space="preserve">
-        <v xml:space="preserve"> La CDF se ha asociado con Anvil Aerospace para encontrar a los operativos más capaces del sistema. Si encuentras una de estas certificaciones Platino, puedes canjear el boleto en un quiosco de naves en New Deal, Astro Armada o Crusader Showroom por un F8C gratis. La condición es que tu identidad y ubicación se han compartido con los participantes de todo el sistema. Para los demás, si logras detener al poseedor del boleto antes de que llegue al quiosco, puedes reclamarlo para ti. Quien lo consiga no solo recibirá este caza de superioridad de última generación, sino que también demostrará que tiene lo necesario para las misiones más difíciles de la CDF. ¡Buena suerte!</v>
+        <v> Recuperando terreno de los cazatalentos</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v> Eliminar las estaciones de servicio</v>
+        <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v> Eliminar las estaciones de servicio</v>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v> Reducir la preparación operativa de Outlaw</v>
+        <v>Ataque de forajidos en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v> Reducir la preparación operativa de Outlaw</v>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v> Alerta: ~misión(Ubicación) bajo ataque</v>
+        <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v> Alerta: ~misión(Ubicación) bajo ataque</v>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Recuperando terreno de los cazatalentos</v>
+        <v> Recuperando puestos avanzados de la amenaza alienígena</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v> Recuperando terreno de los cazatalentos</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
+        <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
+        <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v> Ataque de forajidos en ~misión(Ubicación)</v>
+        <v> Recuperando clústeres de las manos de los cazatalentos</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v> Ataque de forajidos en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
+        <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v> Recuperando puestos avanzados de la amenaza alienígena</v>
+        <v> Se necesita ayuda en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v> Recuperando puestos avanzados de la amenaza alienígena</v>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
+        <v> Ataque de Headhunter en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
+        <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v> Recuperando clústeres de las manos de los cazatalentos</v>
+        <v> Solicitar ayuda: ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v> Recuperando clústeres de las manos de los cazatalentos</v>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
+        <v> Defiende ~misión(Ubicación) de los forajidos</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v> Se necesita ayuda en ~misión(Ubicación)</v>
+        <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v> Se necesita ayuda en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v> Ataque de Headhunter en ~misión(Ubicación)</v>
+        <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v> Ataque de Headhunter en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v> Solicitar ayuda: ~misión(Ubicación)</v>
+        <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v> Solicitar ayuda: ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v> Defiende ~misión(Ubicación) de los forajidos</v>
+        <v> Piloto busca apoyo en combate</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Defiende ~misión(Ubicación) de los forajidos</v>
+        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
+        <v> El barco necesita asistencia de emergencia</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
+        <v> Convoy atrapado en un brutal ataque.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
+        <v> Acudan en auxilio del convoy</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v> Se buscan pilotos de combate experimentados.</v>
+        <v> Responder a la baliza de socorro</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v> Se buscan pilotos de combate experimentados.</v>
+        <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v> Proporcionar apoyo en combate</v>
+        <v> Piloto en apuros</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v> Proporcionar apoyo en combate</v>
+        <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v> Piloto busca apoyo en combate</v>
+        <v> Se necesita ayuda contra XenoThreat Raid</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v> Piloto busca apoyo en combate</v>
+        <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v> Ayudar al barco en retirada</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v> Ayudar al barco en retirada</v>
+        <v>Entrega para ~misión(Destino) Lista</v>
+      </c>
+    </row>
+    <row r="151" xml:space="preserve">
+      <c r="A151" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v> Detengan el ataque al barco.</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v> Detengan el ataque al barco.</v>
+        <v> Múltiples entregas listas</v>
+      </c>
+    </row>
+    <row r="153" xml:space="preserve">
+      <c r="A153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, necesito que me entreguen dos paquetes. El paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; debe recogerse en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; y llevarse a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;, y el paquete &lt;EM4&gt;#~mission(item2|serialnumber)&lt;/EM4&gt; va de &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt;. Debería ser una forma fácil de ganar algunos créditos. Además, para facilitarte la vida, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¡Buen viaje! Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v> El barco necesita asistencia de emergencia</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v> El barco necesita asistencia de emergencia</v>
+        <v> Eliminar la amenaza Xeno Idris</v>
+      </c>
+    </row>
+    <row r="155" xml:space="preserve">
+      <c r="A155" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, los rumores son ciertos. XenoThreat ha desplegado un Idris para acechar y atacar las operaciones de Ciudadanos por la Prosperidad, en una escalada dramática de su hostilidad hacia nosotros. Acabamos de recibir la noticia de que la nave, bajo el mando de ~mission(TargetName), avanza hacia ~mission(location|address). No podemos enviar nuestras fuerzas allí lo suficientemente rápido para combatirlos y necesitamos ayuda urgentemente. Buscamos a alguien lo suficientemente valiente como para enfrentarse a estos bastardos. No basta con ahuyentarlos, necesitamos garantizar que no puedan volver a atacarnos. No sé si te has enfrentado a un Idris antes, pero es una tarea titánica para alguien que lo haga solo. Recomiendo encarecidamente reclutar a otros para la causa. Saludos, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v> Ayudar a un convoy emboscado</v>
+        <v> Ataque a un puesto de avanzada de la CFP</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v> Ayudar a un convoy emboscado</v>
+        <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v> Convoy atrapado en un brutal ataque.</v>
+        <v> Se necesitan defensores contra los cazadores de cabezas</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v> Convoy atrapado en un brutal ataque.</v>
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v> El convoy necesita asistencia de emergencia</v>
+        <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v> El convoy necesita asistencia de emergencia</v>
+        <v/>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v> Detengan el ataque de la Espada Destrozada Salvaje</v>
+        <v> Recuperar el puesto de avanzada de los cazadores de cabezas</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Detengan el ataque de la Espada Destrozada Salvaje</v>
+        <v/>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v> Acudan en auxilio del convoy</v>
+        <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v> Acudan en auxilio del convoy</v>
+        <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v> Convoy bajo ataque</v>
+        <v>Intercepción de la carrera de suministros</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v> Convoy bajo ataque</v>
+        <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v> Responder a la baliza de socorro</v>
+        <v> Es necesario recuperar suministros esenciales.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v> Responder a la baliza de socorro</v>
+        <v/>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v> Convoy bajo ataque de una amenaza alienígena</v>
+        <v> Recuperación de suministros valiosos</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v> Convoy bajo ataque de una amenaza alienígena</v>
+        <v/>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v> Buque de apoyo bajo ataque</v>
+        <v> Operación especial de recuperación</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v> Buque de apoyo bajo ataque</v>
+        <v/>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v> Piloto en apuros</v>
+        <v> El envío de carga debe completarse.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v> Piloto en apuros</v>
+        <v/>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v> Se necesita ayuda contra XenoThreat Raid</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v> Se necesita ayuda contra XenoThreat Raid</v>
+        <v> Suministros robados</v>
+      </c>
+    </row>
+    <row r="177" xml:space="preserve">
+      <c r="A177" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v> Entrega para ~misión(Destino) Lista</v>
+        <v> Material confidencial robado</v>
       </c>
     </row>
     <row r="179" xml:space="preserve">
       <c r="A179" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">¿Estás disponible para un trabajo? Uno de nuestros centros de seguridad fue asaltado y robaron material altamente confidencial. Como puedes imaginar, Citizens for Prosperity necesita recuperarlo cuanto antes. Gracias a un contacto local, pudimos rastrear a los delincuentes hasta ~mission(Location|Address), donde almacenan el material confidencial en una bóveda automatizada de alta seguridad. Para acceder a ella, primero debes encontrar el código de recuperación e introducirlo en la cinta transportadora de la bóveda. Creemos que uno de los líderes de los delincuentes llevará el código consigo, por lo que es muy probable que tengas que hablar directamente con él para obtenerlo. Una vez que tengas el material confidencial en tu poder, te pedimos que lo entregues en ~mission(Dropoff1|Address). Si lo consigues, ayudarás mucho a muchas personas. Gracias de antemano, Lima Endicott, Despachadora Principal, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v> Múltiples entregas listas</v>
-      </c>
-    </row>
-    <row r="181" xml:space="preserve">
-      <c r="A181" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, necesito que me entreguen dos paquetes. El paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; debe recogerse en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; y llevarse a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;, y el paquete &lt;EM4&gt;#~mission(item2|serialnumber)&lt;/EM4&gt; va de &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt;. Debería ser una forma fácil de ganar algunos créditos. Además, para facilitarte la vida, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¡Buen viaje! Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v> Operación de detención de narcóticos</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v/>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v> Eliminar la amenaza Xeno Idris</v>
-      </c>
-    </row>
-    <row r="183" xml:space="preserve">
-      <c r="A183" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, los rumores son ciertos. XenoThreat ha desplegado un Idris para acechar y atacar las operaciones de Ciudadanos por la Prosperidad, en una escalada dramática de su hostilidad hacia nosotros. Acabamos de recibir la noticia de que la nave, bajo el mando de ~mission(TargetName), avanza hacia ~mission(location|address). No podemos enviar nuestras fuerzas allí lo suficientemente rápido para combatirlos y necesitamos ayuda urgentemente. Buscamos a alguien lo suficientemente valiente como para enfrentarse a estos bastardos. No basta con ahuyentarlos, necesitamos garantizar que no puedan volver a atacarnos. No sé si te has enfrentado a un Idris antes, pero es una tarea titánica para alguien que lo haga solo. Recomiendo encarecidamente reclutar a otros para la causa. Saludos, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v>Desactiva Headhunter Stronghold</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v/>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v> Ataque a un puesto de avanzada de la CFP</v>
+        <v> Limitar la capacidad operativa de los forajidos</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v> Ataque a un puesto de avanzada de la CFP</v>
+        <v/>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v> Se necesitan defensores contra los cazadores de cabezas</v>
+        <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v> Se necesitan defensores contra los cazadores de cabezas</v>
+        <v/>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
+        <v> Desactivar Fortaleza de Forajidos en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
+        <v/>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Recuperar el puesto de avanzada de los cazadores de cabezas</v>
+        <v> Eliminar todo rastro de datos de reclutadores</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v> Recuperar el puesto de avanzada de los cazadores de cabezas</v>
+        <v/>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v> Establecer la seguridad</v>
+        <v> Borrar los servidores de datos de Headhunter</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v> Establecer la seguridad</v>
+        <v/>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
+        <v> Destruir datos logísticos de XenoThreat</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
+        <v/>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v> Protección contra ~misión(NombreObjetivo|Apellido)</v>
+        <v> Destruye los datos robados de Headhunter</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v> Protección contra ~misión(NombreObjetivo|Apellido)</v>
+        <v/>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v> Intercepción de la carrera de suministros</v>
+        <v> Centro de datos Clear Outlaw</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v> Intercepción de la carrera de suministros</v>
+        <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v> Es necesario recuperar suministros esenciales.</v>
+        <v> Destruir los servidores de datos de XenoThreat</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v> Es necesario recuperar suministros esenciales.</v>
+        <v/>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v> Recuperación de suministros valiosos</v>
+        <v> Destruir servidores de datos de Outlaw</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v> Recuperación de suministros valiosos</v>
+        <v/>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v> Operación especial de recuperación</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v> Operación especial de recuperación</v>
+        <v> Falta: ~misión(NombreObjetivo)</v>
+      </c>
+    </row>
+    <row r="205" xml:space="preserve">
+      <c r="A205" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lamentablemente, uno de nuestros socios comunitarios, ~mission(TargetName), lleva desaparecido varios días. Su familia se puso en contacto con Citizens for Prosperity para pedir ayuda y les dije que haríamos lo posible. Dicho esto, con tanto tiempo transcurrido, no tengo muchas esperanzas. Sea cual sea su situación actual, buscamos a alguien que nos ayude a localizarlo. Hay muchas probabilidades de que se dirigiera a ~mission(Location|Address), una zona conocida por ser muy peligrosa. Si logra localizarlo y confirmar su paradero, de una forma u otra, me aseguraré de que reciba la compensación adecuada. Lima Endicott, Coordinadora Principal de Despacho, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v> El envío de carga debe completarse.</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v> El envío de carga debe completarse.</v>
+        <v> Falta: ~misión(NombreObjetivo)</v>
+      </c>
+    </row>
+    <row r="207" xml:space="preserve">
+      <c r="A207" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de nuestros compañeros, ~mission(TargetName), debía realizar un reconocimiento preliminar en ~mission(Location|Address), pero nunca se presentó. Esperamos que simplemente haya tenido mala suerte, pero aquí, incluso el más mínimo error puede resultar fatal. Agradecería que alguien se dirigiera a la zona e intentara localizarlo. Sería estupendo encontrarlo con vida, pero si no, brindarles un cierre es lo mínimo que podemos hacer por su familia. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v> Suministros robados</v>
-      </c>
-    </row>
-    <row r="209" xml:space="preserve">
-      <c r="A209" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v> Entrega de regalos de Luminalia</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v> ~misión(Contratista|DescripciónDeEntregaLocal)</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v> Recuperar carga</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v> Recuperar carga</v>
+        <v> Ruta de envío local de Covalex</v>
+      </c>
+    </row>
+    <row r="211" xml:space="preserve">
+      <c r="A211" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, tenemos un envío bastante grande esperando en la misión (Recogida 1) en la dirección (Recogida 1) que está listo para ser entregado. Con esta cantidad de cajas para transportar, probablemente sería bueno contar con ayuda adicional para cargar y descargar todo de su nave. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item11|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item12|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item13|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item14|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item15|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; Mucha suerte, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite'. Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v> Redada para recuperar suministros</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v> Redada para recuperar suministros</v>
+        <v>Oportunidad para transportista de carga independiente</v>
+      </c>
+    </row>
+    <row r="213" xml:space="preserve">
+      <c r="A213" t="str" xml:space="preserve">
+        <v xml:space="preserve">Covalex, galardonada con reconocimientos como "Las 10 mejores empresas de transporte marítimo" de Imperial Finance y "El transporte más confiable de Delivery Digest" (2945), está más activa que nunca. Esto significa más carga para más destinos. Ahí es donde entras tú. Covalex busca pilotos confiables y trabajadores para unirse a nuestra creciente familia. ¿Tienes acceso a un barco con capacidad para contenedores de carga de &lt;EM4&gt;~mission(MissionMaxSCUSize)&lt;/EM4&gt;? ¿Puedes superar una verificación de antecedentes de Advocacy si se requiere? Entonces, un universo de oportunidades te espera. Simplemente completa una "Prueba de evaluación" recogiendo un envío de &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entregándolo con éxito en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Tras completar satisfactoriamente el proceso, podrá formar parte de la amplia red de especialistas en transporte independientes de Covalex Shipping*. Por cierto, recomendamos encarecidamente a los contratistas que traigan consigo un rayo tractor portátil. Covalex Shipping: «Todo lo que necesite, donde lo necesite». *Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de carga, Covalex Shipping establecerá un plazo de entrega y, una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v> Reclamar la carga robada</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v> Reclamar la carga robada</v>
+        <v>Reevaluación del servicio de transporte de carga de Covalex</v>
+      </c>
+    </row>
+    <row r="215" xml:space="preserve">
+      <c r="A215" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, tenemos buenas noticias para ti. Covalex ha finalizado recientemente una evaluación de nuestro grupo de contratistas y ha decidido reconsiderar tu estatus como transportista de carga. Para volver a calificar, solo necesitas completar con éxito la siguiente entrega. Recoge &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entrégalo en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Para completar este transporte de forma rápida y eficiente, necesitarás un barco que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Esperamos que todo salga bien para poder darte la bienvenida de nuevo al equipo. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Covalex Shipping 'Todo lo que necesitas, donde lo necesitas'. Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de mercancías, Covalex Shipping establecerá un plazo límite de entrega. Una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v> Recuperar suministros de XenoThreat</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Recuperar suministros de XenoThreat</v>
+        <v>Manipulador de paquetes Covalex</v>
+      </c>
+    </row>
+    <row r="217" xml:space="preserve">
+      <c r="A217" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, hay un montón de paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que necesitan ser trasladados dentro de las instalaciones hasta su lugar de almacenamiento correspondiente. Sería de gran ayuda si pudieras encargarte personalmente de que todo se organice. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Realmente aprecio todo lo que haces, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones como se describen en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29' extendida. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v> Recuperar suministros</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v> Recuperar suministros</v>
+        <v>Ruta de reparto local de Covalex</v>
+      </c>
+    </row>
+    <row r="219" xml:space="preserve">
+      <c r="A219" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¡Hola! Acabamos de recibir una entrega local que necesitamos que se encarguen, si están disponibles. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no se hace responsable de los daños que puedan producirse mientras opera como contratista independiente.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v> Encontrar el barco de suministros perdido</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v> Encontrar el barco de suministros perdido</v>
+        <v>Evaluación de Covalex</v>
+      </c>
+    </row>
+    <row r="221" xml:space="preserve">
+      <c r="A221" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Hola! Covalex está buscando nuevos contratistas de entrega. Para ver si tienes el perfil de Covalex, hemos organizado la siguiente ruta de entrega como evaluación de tus habilidades. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Completar con éxito esta ruta te certificará como contratista oficial de Covalex. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra "Guía de información complementaria para trabajadores independientes v.2948.01.29". Covalex Shipping no se responsabiliza de los daños que puedan producirse durante su actividad como contratista independiente.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v> Material confidencial robado</v>
+        <v>Reevaluación de Covalex</v>
       </c>
     </row>
     <row r="223" xml:space="preserve">
       <c r="A223" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Estás disponible para un trabajo? Uno de nuestros centros de seguridad fue asaltado y robaron material altamente confidencial. Como puedes imaginar, Citizens for Prosperity necesita recuperarlo cuanto antes. Gracias a un contacto local, pudimos rastrear a los delincuentes hasta ~mission(Location|Address), donde almacenan el material confidencial en una bóveda automatizada de alta seguridad. Para acceder a ella, primero debes encontrar el código de recuperación e introducirlo en la cinta transportadora de la bóveda. Creemos que uno de los líderes de los delincuentes llevará el código consigo, por lo que es muy probable que tengas que hablar directamente con él para obtenerlo. Una vez que tengas el material confidencial en tu poder, te pedimos que lo entregues en ~mission(Dropoff1|Address). Si lo consigues, ayudarás mucho a muchas personas. Gracias de antemano, Lima Endicott, Despachadora Principal, Citizens for Prosperity</v>
+        <v xml:space="preserve">Hola, dado que Covalex ha estado experimentando un exceso de entregas y escasez de contratistas, logré convencer a la administración para que reconsiderara tu situación. Solo tienes que completar con éxito la siguiente entrega y volverás a formar parte del sistema. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Buena suerte. Sería genial tenerte de nuevo en la lista. Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de los daños que se produzcan mientras se opera como contratista independiente.</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v> Operación de detención de narcóticos</v>
+        <v>Error de envío - Carga sensible a la calidad</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Operación de detención de narcóticos</v>
+        <v> ~misión(Contratista|DescripciónDeEntregaSensibleCuántica)</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v> Desactiva Headhunter Stronghold</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v> Desactiva Headhunter Stronghold</v>
+        <v> Programa piloto de entrega para Covalex</v>
+      </c>
+    </row>
+    <row r="227" xml:space="preserve">
+      <c r="A227" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola, tengo una entrega que necesito gestionar. El pedido está esperando en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser llevado a &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Estoy seguro de que no tendrás problemas, pero para que lo sepas, veo varias advertencias de seguridad en esta zona. Parece que ha habido algunos ataques en esa área en los últimos días. No digo que vayas a tener ningún problema, pero probablemente sería mejor que llevaras algo de protección. Mucha suerte, Chase Hewitt Jr., Coordinador de Logística de Covalex Shipping. «Todo lo que necesites, donde lo necesites».</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v> Limitar la capacidad operativa de los forajidos</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v> Limitar la capacidad operativa de los forajidos</v>
+        <v> Efectos personales</v>
+      </c>
+    </row>
+    <row r="229" xml:space="preserve">
+      <c r="A229" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, entenderé perfectamente si no quieres ayudarme con esto, pero si puedes, sería genial. Verás, mi novio falleció durante la tragedia de Covalex Gundo. Me dijeron que recuperaría todas las pertenencias de Scott una vez que terminara la investigación, pero hasta donde sé, ya pasó un tiempo y todavía no me han dado ninguna indicación de cuándo podré recuperarlas. Ya ha sido bastante difícil lidiar con todo esto, y saber que dentro de uno o dos meses llegará un paquete que reabrirá todas estas heridas es demasiado. Preferiría resolverlo ahora y terminar con esto. Si pudieras encontrar la manera de recoger sus efectos personales (ID de empleado n.° 104) y entregarlos en ~mission(Destino), te lo agradecería muchísimo. Gracias por tu ayuda, Anya</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
+        <v> Ayúdenme a recuperar mis cosas.</v>
+      </c>
+    </row>
+    <row r="231" xml:space="preserve">
+      <c r="A231" t="str" xml:space="preserve">
+        <v xml:space="preserve">Mi hermano fue una de las personas que murió cuando explotó la estación Covalex cerca de Crusader. Peor aún, estaba usando algo mío cuando ocurrió. Ahora un burócrata de mierda me dice que tengo que esperar para recuperar mis cosas. ¡Claro que sí! Primero matan a mi hermano y ahora quieren que tenga paciencia. ¡Qué descaro el de estos imbéciles corporativos! Olvídalo. En vez de eso, pensé en contratar a alguien para que vaya a Gundo a buscar mis cosas y las lleve a ~misión(Destino) por mí. O sea, ¿qué demonios van a hacer al respecto? En fin, es lo que mi hermano hubiera querido. Será la caja marcada con el número 156. - Ed</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v> Desactivar Fortaleza de Forajidos en ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="str">
-        <v> Desactivar Fortaleza de Forajidos en ~misión(Ubicación)</v>
+        <v> Herencia inesperada</v>
+      </c>
+    </row>
+    <row r="233" xml:space="preserve">
+      <c r="A233" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, esto me resulta un poco incómodo, pero resulta que una de las personas que falleció en el desastre de la estación Covalex, Kyomi Santos, me dejó algo en su testamento. Me sorprendió mucho, pero ahora soy el orgulloso dueño de todo lo que hay en la caja n.° 173. En Covalex dicen que podré recogerlo cuando la estación vuelva a abrir, pero... aquí viene lo incómodo... lo necesito urgentemente. Normalmente esperaría, pero estoy intentando montar mi propio negocio (hago pasteles con la forma de los planetas de origen de la gente) y los créditos que gane con la venta me vendrán de maravilla. Tengo algo de dinero ahorrado que puedo usar para pagarle a alguien que me lo envíe desde Gundo hasta ~misión(Destino). Sé que todo esto es un poco raro, pero si hubiera otra manera, no estaría preguntando. Gracias por la ayuda, Thrace.</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v> Eliminar todo rastro de datos de reclutadores</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="str">
-        <v> Eliminar todo rastro de datos de reclutadores</v>
+        <v> La súplica de una madre</v>
+      </c>
+    </row>
+    <row r="235" xml:space="preserve">
+      <c r="A235" t="str" xml:space="preserve">
+        <v xml:space="preserve">Mi hijo Nico fue, lamentablemente, una de las víctimas del trágico accidente en la estación de Covelex en Gundo, y aún no me han devuelto todas sus pertenencias. Entiendo que deben cumplir con las normas, pero me parece inconcebible que no tengan en cuenta el dolor de la familia. Por ello, busco a alguien que pueda ir a la estación por mí. Cabe aclarar que actualmente Gundo está fuera de los límites, lo que significa que esto no sería legal, pero creo que mi situación merece una consideración especial. Mi hermana dice que la tarifa que ofrezco es la correcta para recuperar la caja con las pertenencias de Nico (n.º 964) y llevarlas a ~mission(Destination), así que espero encontrar a alguien competente que pueda resolver este asunto rápidamente. Atentamente, Gloria Theolone</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v> Borrar los servidores de datos de Headhunter</v>
+        <v> Buscando un cierre</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v> Borrar los servidores de datos de Headhunter</v>
+        <v>Me dijeron que podría encontrar a alguien aquí que fuera a Gundo por mí y recogiera una caja que pertenecía a mi esposa. Si el nombre no te suena, es la estación donde ocurrió aquel gran accidente. Mi esposa trabajaba para Covalex y sé que eso no hará que su pérdida sea más fácil, pero de verdad quiero recuperar las cosas de Claudia. Pienso en su colección de fotos o en el collar que le regalé, ahí, en esa fría y desolada estación, en una caja marcada con el número 249, y no es justo. Ella se merece algo mejor. ¿Qué te parece? ¿Estás dispuesto a ir a Gundo y llevar su caja de vuelta a ~misión(Destino)?</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v> Destruir datos logísticos de XenoThreat</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v> Destruir datos logísticos de XenoThreat</v>
+        <v> Las cosas de mi papá</v>
+      </c>
+    </row>
+    <row r="239" xml:space="preserve">
+      <c r="A239" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, busco a alguien que vaya a la estación Covalex Gundo cerca de Crusader y recoja algunos objetos. Sé que puede sonar a robo, pero son las cosas de mi papá. Verás, él estaba en la estación Gundo cuando ocurrió el accidente. Mi mamá dice que tenemos que esperar a que Covalex lo autorice, pero no me parece justo porque lo extraño muchísimo. Me gustaría tener algo para recordarlo y no quiero esperar más porque podría empezar a olvidar cosas. Te pagaré para que me consigas la caja 510 y la lleves a ~mission(Destination) para que pueda tenerla. Muchas gracias, Baylor Ward</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v> Destruye los datos robados de Headhunter</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v> Destruye los datos robados de Headhunter</v>
+        <v> Apoderarse de los datos</v>
+      </c>
+    </row>
+    <row r="241" xml:space="preserve">
+      <c r="A241" t="str" xml:space="preserve">
+        <v xml:space="preserve">He estado buscando un paquete de datos específico y justo cuando tengo un respiro, la nave es atacada por esta Reclamadora de Nueve Colas modificada llamada Cometa Negra. Intenté hackear los servidores de la Cometa Negra para ver si copiaron los datos, pero no pude encontrar la manera de sortear sus protocolos de cifrado de forma remota sin la clave física. Ahí es donde entras tú. Necesito que alguien acceda a su nave, consiga su clave de descifrado y descifre el servidor para poder descargar remotamente lo que necesito. Eres lo suficientemente inteligente como para saber con quién estamos tratando, así que planifica en consecuencia. Dado que esto va a causar revuelo, no dejemos nada al azar. Destruye la Cometa Negra cuando termines para cubrirnos las espaldas a ambos.</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v> Centro de datos Clear Outlaw</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v> Centro de datos Clear Outlaw</v>
+        <v> Extracción de recompensa: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="243" xml:space="preserve">
+      <c r="A243" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tuvimos suerte y algunos escaneos recientes de ~mission(Location|Address) han revelado que hay una recompensa pendiente con el nombre de ~mission(TargetName) oculta allí. Se le ha autorizado a entrar en el sitio, encontrarla y resolver la recompensa. Sin embargo, además de la recompensa y sus cómplices, es probable que también haya civiles en el sitio. Si bien estamos ansiosos por eliminar a ~mission(TargetName|Last), no podemos permitirnos bajas civiles. Tenga cuidado al interactuar con los hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Gibbs ID# 91G66BW0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v> Destruir los servidores de datos de XenoThreat</v>
+        <v> Recompensa emitida para ~mission(TargetName) (LRT)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v> Destruir los servidores de datos de XenoThreat</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v> Destruir servidores de datos de Outlaw</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v> Destruir servidores de datos de Outlaw</v>
+        <v> Evaluación de recompensas para freelancers verificados</v>
+      </c>
+    </row>
+    <row r="247" xml:space="preserve">
+      <c r="A247" t="str" xml:space="preserve">
+        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personas cualificadas para colaborar en la cobranza de recompensas en la zona. Hemos evaluado que usted posee las habilidades necesarias y, por lo tanto, nos gustaría ofrecerle un contrato inicial de prueba para la captura de ~mission(TargetName), vista por última vez en ~mission(Location|Address). Al completar con éxito este contrato, se le incluirá en la lista de Freelancers Verificados de Crusader y podrá optar a futuros trabajos de cobranza de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v> Falta: ~misión(NombreObjetivo)</v>
-      </c>
-    </row>
-    <row r="249" xml:space="preserve">
-      <c r="A249" t="str" xml:space="preserve">
-        <v xml:space="preserve">Lamentablemente, uno de nuestros socios comunitarios, ~mission(TargetName), lleva desaparecido varios días. Su familia se puso en contacto con Citizens for Prosperity para pedir ayuda y les dije que haríamos lo posible. Dicho esto, con tanto tiempo transcurrido, no tengo muchas esperanzas. Sea cual sea su situación actual, buscamos a alguien que nos ayude a localizarlo. Hay muchas probabilidades de que se dirigiera a ~mission(Location|Address), una zona conocida por ser muy peligrosa. Si logra localizarlo y confirmar su paradero, de una forma u otra, me aseguraré de que reciba la compensación adecuada. Lima Endicott, Coordinadora Principal de Despacho, Citizens for Prosperity</v>
+        <v> Recompensa emitida para ~mission(TargetName) (HRT)</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v> Falta: ~misión(NombreObjetivo)</v>
-      </c>
-    </row>
-    <row r="251" xml:space="preserve">
-      <c r="A251" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de nuestros compañeros, ~mission(TargetName), debía realizar un reconocimiento preliminar en ~mission(Location|Address), pero nunca se presentó. Esperamos que simplemente haya tenido mala suerte, pero aquí, incluso el más mínimo error puede resultar fatal. Agradecería que alguien se dirigiera a la zona e intentara localizarlo. Sería estupendo encontrarlo con vida, pero si no, brindarles un cierre es lo mínimo que podemos hacer por su familia. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v> Recompensa emitida para ~mission(TargetName) (MRT)</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v> Entrega de regalos de Luminalia</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="str">
-        <v> ~misión(Contratista|DescripciónDeEntregaLocal)</v>
+        <v> Reevaluación de la recompensa para freelancers verificados</v>
+      </c>
+    </row>
+    <row r="253" xml:space="preserve">
+      <c r="A253" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Buenas noticias! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de recompensas. Esperamos que durante este tiempo hayas corregido cualquier problema de rendimiento anterior y puedas volver a ser un activo valioso. Sin embargo, primero debemos reevaluarte, por lo que nos gustaría que completaras este contrato de recompensa para ~mission(TargetName). Tras completar con éxito esta prueba, volverás a la lista de Freelancers Verificados de Crusader y podrás optar a futuros trabajos de cobro de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v> Ruta de envío local de Covalex</v>
-      </c>
-    </row>
-    <row r="255" xml:space="preserve">
-      <c r="A255" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos un envío bastante grande esperando en la misión (Recogida 1) en la dirección (Recogida 1) que está listo para ser entregado. Con esta cantidad de cajas para transportar, probablemente sería bueno contar con ayuda adicional para cargar y descargar todo de su nave. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item11|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item12|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff8|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item13|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item14|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item15|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff9|Address)&lt;/EM4&gt; Mucha suerte, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite'. Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
+        <v> Recompensa emitida para ~mission(TargetName) (ERT)</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Oportunidad para transportista de carga independiente</v>
-      </c>
-    </row>
-    <row r="257" xml:space="preserve">
-      <c r="A257" t="str" xml:space="preserve">
-        <v xml:space="preserve">Covalex, galardonada con reconocimientos como "Las 10 mejores empresas de transporte marítimo" de Imperial Finance y "El transporte más confiable de Delivery Digest" (2945), está más activa que nunca. Esto significa más carga para más destinos. Ahí es donde entras tú. Covalex busca pilotos confiables y trabajadores para unirse a nuestra creciente familia. ¿Tienes acceso a un barco con capacidad para contenedores de carga de &lt;EM4&gt;~mission(MissionMaxSCUSize)&lt;/EM4&gt;? ¿Puedes superar una verificación de antecedentes de Advocacy si se requiere? Entonces, un universo de oportunidades te espera. Simplemente completa una "Prueba de evaluación" recogiendo un envío de &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entregándolo con éxito en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Tras completar satisfactoriamente el proceso, podrá formar parte de la amplia red de especialistas en transporte independientes de Covalex Shipping*. Por cierto, recomendamos encarecidamente a los contratistas que traigan consigo un rayo tractor portátil. Covalex Shipping: «Todo lo que necesite, donde lo necesite». *Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de carga, Covalex Shipping establecerá un plazo de entrega y, una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
+        <v> Recompensa emitida para ~mission(TargetName) (VLRT)</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Reevaluación del servicio de transporte de carga de Covalex</v>
-      </c>
-    </row>
-    <row r="259" xml:space="preserve">
-      <c r="A259" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos buenas noticias para ti. Covalex ha finalizado recientemente una evaluación de nuestro grupo de contratistas y ha decidido reconsiderar tu estatus como transportista de carga. Para volver a calificar, solo necesitas completar con éxito la siguiente entrega. Recoge &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; de un montacargas en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y entrégalo en un montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Para completar este transporte de forma rápida y eficiente, necesitarás un barco que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Esperamos que todo salga bien para poder darte la bienvenida de nuevo al equipo. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Covalex Shipping 'Todo lo que necesitas, donde lo necesitas'. Covalex Shipping es una sociedad de responsabilidad limitada. Para fomentar las entregas puntuales y prevenir el fraude en el transporte de mercancías, Covalex Shipping establecerá un plazo límite de entrega. Una vez transcurrido dicho plazo, cualquier carga no entregada se considerará robada y se tratará como tal. El pago total se prorrateará según el porcentaje de carga entregada con éxito.</v>
+        <v> Recompensa emitida para ~mission(TargetName) (VHRT)</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Manipulador de paquetes Covalex</v>
+        <v> URGENTE: Retomar el puesto de seguridad de Kareah</v>
       </c>
     </row>
     <row r="261" xml:space="preserve">
       <c r="A261" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, hay un montón de paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que necesitan ser trasladados dentro de las instalaciones hasta su lugar de almacenamiento correspondiente. Sería de gran ayuda si pudieras encargarte personalmente de que todo se organice. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Realmente aprecio todo lo que haces, Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones como se describen en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29' extendida. Covalex Shipping no es responsable de ningún daño que ocurra mientras opera como contratista independiente.</v>
+        <v xml:space="preserve">El puesto de seguridad Kareah está siendo atacado por un número desconocido de asaltantes. Crusader busca contratistas que se dirijan rápidamente a la estación y eliminen a todos los intrusos en las inmediaciones antes de que nuestras fuerzas de seguridad se vean superadas. No sabemos si los atacantes buscan el contrabando en nuestro depósito de pruebas o nuestra base de datos CrimeStat, pero sea lo que sea que busquen, debemos neutralizarlos. Recibirás una bonificación de combate por cada objetivo neutralizado. Al aceptar este contrato, te comprometes a cumplir con todos los protocolos de seguridad de Crusader: si dañas a algún guardia u otro contratista autorizado mientras te encuentres en la estación, tu contrato se dará por terminado y serás marcado como objetivo. El tiempo apremia, así que asegúrate de estar bien equipado para enfrentarte a los hostiles antes de responder. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Ruta de reparto local de Covalex</v>
+        <v> Apoyar a las fuerzas de seguridad y proteger los materiales confidenciales.</v>
       </c>
     </row>
     <row r="263" xml:space="preserve">
       <c r="A263" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Hola! Acabamos de recibir una entrega local que necesitamos que se encarguen, si están disponibles. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesite, donde lo necesite.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no se hace responsable de los daños que puedan producirse mientras opera como contratista independiente.</v>
+        <v xml:space="preserve">Los informes indican que nuestro personal de seguridad en ~mission(location|address) ha sido aniquilado por un grupo de los Nueve Colas, quienes intentan robar material confidencial entregado recientemente a las instalaciones. Crusader Security necesita un contratista experimentado para expulsar a los hostiles y asegurar estas cajas. Según los informes iniciales, recomendamos encarecidamente que venga bien equipado y considere traer refuerzos. Por motivos de seguridad, el material confidencial fue transportado allí como parte de un envío con otras cajas y guardado bajo llave en una bóveda automatizada. Los códigos de acceso al material confidencial se encuentran en tabletas de datos en poder de personal de seguridad de alto rango, pero desconocemos quién las tiene ahora. Es probable que los Nueve Colas también las estén buscando. Cuando tenga todo el material confidencial, entréguelo en ~mission(dropoff1|address) para recibir el pago. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Evaluación de Covalex</v>
+        <v> Sitio de vigilancia contra hostiles</v>
       </c>
     </row>
     <row r="265" xml:space="preserve">
       <c r="A265" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Hola! Covalex está buscando nuevos contratistas de entrega. Para ver si tienes el perfil de Covalex, hemos organizado la siguiente ruta de entrega como evaluación de tus habilidades. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Completar con éxito esta ruta te certificará como contratista oficial de Covalex. Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. ~mission(Contractor|SignOff) Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una sociedad de responsabilidad limitada. Al aceptar este contrato, usted acepta todos los términos y condiciones descritos en nuestra "Guía de información complementaria para trabajadores independientes v.2948.01.29". Covalex Shipping no se responsabiliza de los daños que puedan producirse durante su actividad como contratista independiente.</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una pandilla local y estamos buscando contratar a un contratista para formar un equipo de seguridad que haga frente a cualquier ataque. Esta pandilla tiene antecedentes, pero aún son bastante novatos. Creo que será relativamente sencillo para usted y su equipo manejar la situación. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Reevaluación de Covalex</v>
+        <v> Sitio de protección contra hostiles graves</v>
       </c>
     </row>
     <row r="267" xml:space="preserve">
       <c r="A267" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, dado que Covalex ha estado experimentando un exceso de entregas y escasez de contratistas, logré convencer a la administración para que reconsiderara tu situación. Solo tienes que completar con éxito la siguiente entrega y volverás a formar parte del sistema. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por cierto, recomendamos encarecidamente a los contratistas que traigan un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Buena suerte. Sería genial tenerte de nuevo en la lista. Chase Hewitt Jr. Coordinador de Logística Covalex Shipping 'Todo lo que necesites, donde lo necesites.' Covalex Shipping es una corporación de responsabilidad limitada. Al aceptar este contrato, aceptas todos los términos y condiciones descritos en nuestra 'Guía de información complementaria para trabajadores independientes v.2948.01.29'. Covalex Shipping no es responsable de los daños que se produzcan mientras se opera como contratista independiente.</v>
+        <v xml:space="preserve"> Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes y estamos buscando contratar a un contratista para formar un equipo de seguridad que repela cualquier ataque. Sé que puede que tengas la tentación de intentar resolver esto por tu cuenta, pero necesitas formar un equipo. Créeme, no vale la pena intentarlo solo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Error de envío - Carga sensible a la calidad</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v> ~misión(Contratista|DescripciónDeEntregaSensibleCuántica)</v>
+        <v> Sitio de vigilancia contra hostiles peligrosos</v>
+      </c>
+    </row>
+    <row r="269" xml:space="preserve">
+      <c r="A269" t="str" xml:space="preserve">
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una banda criminal conocida que opera en la zona y estamos buscando contratar un equipo de seguridad experimentado para hacer frente a cualquier ataque. Asegúrese de que la persona que contrate esté debidamente cualificada. Necesitará toda la ayuda posible para lidiar con este grupo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v> Programa piloto de entrega para Covalex</v>
+        <v> Destruir las drogas ilegales</v>
       </c>
     </row>
     <row r="271" xml:space="preserve">
       <c r="A271" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, tengo una entrega que necesito gestionar. El pedido está esperando en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser llevado a &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Estoy seguro de que no tendrás problemas, pero para que lo sepas, veo varias advertencias de seguridad en esta zona. Parece que ha habido algunos ataques en esa área en los últimos días. No digo que vayas a tener ningún problema, pero probablemente sería mejor que llevaras algo de protección. Mucha suerte, Chase Hewitt Jr., Coordinador de Logística de Covalex Shipping. «Todo lo que necesites, donde lo necesites».</v>
+        <v xml:space="preserve">Hemos descubierto que un grupo está intentando montar su propio negocio de drogas en ~mission(Location|Address). Aunque parecen ser delincuentes comunes y corrientes, el producto que fabrican es tóxico y ha causado la muerte de varios civiles, así que no podemos permitir que se venda más. Estamos trabajando en una operación a gran escala para desmantelar su negocio definitivamente, pero mientras tanto, debemos detener el flujo de sus drogas. Por eso, Crusader quiere que vayas al lugar y destruyas el alijo que tienen allí. Sin duda, tendrán guardias protegiendo el alijo, pero no creo que representen una gran amenaza. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v> Efectos personales</v>
+        <v> Destruye el contrabando mortal</v>
       </c>
     </row>
     <row r="273" xml:space="preserve">
       <c r="A273" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, entenderé perfectamente si no quieres ayudarme con esto, pero si puedes, sería genial. Verás, mi novio falleció durante la tragedia de Covalex Gundo. Me dijeron que recuperaría todas las pertenencias de Scott una vez que terminara la investigación, pero hasta donde sé, ya pasó un tiempo y todavía no me han dado ninguna indicación de cuándo podré recuperarlas. Ya ha sido bastante difícil lidiar con todo esto, y saber que dentro de uno o dos meses llegará un paquete que reabrirá todas estas heridas es demasiado. Preferiría resolverlo ahora y terminar con esto. Si pudieras encontrar la manera de recoger sus efectos personales (ID de empleado n.° 104) y entregarlos en ~mission(Destino), te lo agradecería muchísimo. Gracias por tu ayuda, Anya</v>
+        <v xml:space="preserve">Un incipiente sindicato se ha instalado en ~mission(Location|Address) y está intentando introducirse en el mercado de las drogas. Desafortunadamente, su producto se ha relacionado con varias muertes en Crusader y sus alrededores. Dada la potencia de esta sustancia, representa una grave amenaza para la población. Crusader está trabajando para desmantelar la operación, pero mientras su producto siga circulando, los cadáveres se acumularán. Queremos que vayas al lugar y destruyas el alijo que tienen allí antes de que tengan la oportunidad de venderlo. Sin embargo, debes tener en cuenta que su alijo está extremadamente bien custodiado. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v> Ayúdenme a recuperar mis cosas.</v>
+        <v> Destruir narcóticos tóxicos</v>
       </c>
     </row>
     <row r="275" xml:space="preserve">
       <c r="A275" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mi hermano fue una de las personas que murió cuando explotó la estación Covalex cerca de Crusader. Peor aún, estaba usando algo mío cuando ocurrió. Ahora un burócrata de mierda me dice que tengo que esperar para recuperar mis cosas. ¡Claro que sí! Primero matan a mi hermano y ahora quieren que tenga paciencia. ¡Qué descaro el de estos imbéciles corporativos! Olvídalo. En vez de eso, pensé en contratar a alguien para que vaya a Gundo a buscar mis cosas y las lleve a ~misión(Destino) por mí. O sea, ¿qué demonios van a hacer al respecto? En fin, es lo que mi hermano hubiera querido. Será la caja marcada con el número 156. - Ed</v>
+        <v xml:space="preserve">Hemos estado investigando una reciente oleada de sobredosis y todas parecen haberse originado con un lote defectuoso de drogas fabricado en ~mission(Location|Address). Estoy trabajando con otros contratistas para dar con los responsables, pero la gente sigue muriendo mientras el producto siga circulando. Quiero que vayas al lugar y destruyas el alijo que tienen allí. Eso nos dará algo de tiempo antes de cerrarlo definitivamente. Tendrán guardias protegiendo su suministro, así que prepárate para enfrentarte a hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v> Herencia inesperada</v>
+        <v> Proporcionar respaldo</v>
       </c>
     </row>
     <row r="277" xml:space="preserve">
       <c r="A277" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, esto me resulta un poco incómodo, pero resulta que una de las personas que falleció en el desastre de la estación Covalex, Kyomi Santos, me dejó algo en su testamento. Me sorprendió mucho, pero ahora soy el orgulloso dueño de todo lo que hay en la caja n.° 173. En Covalex dicen que podré recogerlo cuando la estación vuelva a abrir, pero... aquí viene lo incómodo... lo necesito urgentemente. Normalmente esperaría, pero estoy intentando montar mi propio negocio (hago pasteles con la forma de los planetas de origen de la gente) y los créditos que gane con la venta me vendrán de maravilla. Tengo algo de dinero ahorrado que puedo usar para pagarle a alguien que me lo envíe desde Gundo hasta ~misión(Destino). Sé que todo esto es un poco raro, pero si hubiera otra manera, no estaría preguntando. Gracias por la ayuda, Thrace.</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes. Si bien contamos con personal de seguridad en el lugar, estamos buscando contratar personal adicional para repeler cualquier ataque. Como contratista, desconozco su experiencia trabajando en equipo, pero no quiero oír hablar de "fuego amigo", ya que esto podría generar problemas. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v> La súplica de una madre</v>
+        <v> Evaluación del trabajo de seguridad</v>
       </c>
     </row>
     <row r="279" xml:space="preserve">
       <c r="A279" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mi hijo Nico fue, lamentablemente, una de las víctimas del trágico accidente en la estación de Covelex en Gundo, y aún no me han devuelto todas sus pertenencias. Entiendo que deben cumplir con las normas, pero me parece inconcebible que no tengan en cuenta el dolor de la familia. Por ello, busco a alguien que pueda ir a la estación por mí. Cabe aclarar que actualmente Gundo está fuera de los límites, lo que significa que esto no sería legal, pero creo que mi situación merece una consideración especial. Mi hermana dice que la tarifa que ofrezco es la correcta para recuperar la caja con las pertenencias de Nico (n.º 964) y llevarlas a ~mission(Destination), así que espero encontrar a alguien competente que pueda resolver este asunto rápidamente. Atentamente, Gloria Theolone</v>
+        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personal cualificado para colaborar en labores de seguridad en la zona. Hemos determinado que usted posee las habilidades necesarias para ofrecerle un contrato de prueba inicial. Colaborará con Crusader Security para hacer frente a un pequeño grupo hostil que ha estado realizando amenazas contra ~mission(Location|Address). Tenga en cuenta que ya contamos con personal de seguridad en el lugar, por lo que deberá tener cuidado con el fuego amigo. Tras la finalización satisfactoria de este contrato, podrá solicitar cualquier otro puesto de seguridad que surja en el futuro. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v> Buscando un cierre</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="str">
-        <v>Me dijeron que podría encontrar a alguien aquí que fuera a Gundo por mí y recogiera una caja que pertenecía a mi esposa. Si el nombre no te suena, es la estación donde ocurrió aquel gran accidente. Mi esposa trabajaba para Covalex y sé que eso no hará que su pérdida sea más fácil, pero de verdad quiero recuperar las cosas de Claudia. Pienso en su colección de fotos o en el collar que le regalé, ahí, en esa fría y desolada estación, en una caja marcada con el número 249, y no es justo. Ella se merece algo mejor. ¿Qué te parece? ¿Estás dispuesto a ir a Gundo y llevar su caja de vuelta a ~misión(Destino)?</v>
+        <v> Reevaluación del trabajo de seguridad</v>
+      </c>
+    </row>
+    <row r="281" xml:space="preserve">
+      <c r="A281" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Felicidades! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de seguridad. Con un poco de esfuerzo y dedicación, esperamos que puedas superar cualquier problema de rendimiento anterior. Sin embargo, para reevaluar tu idoneidad, nos gustaría que ayudaras a Crusader Security a lidiar con un grupo de delincuentes que ha estado realizando amenazas contra ~mission(Location|Address). Ahora bien, dado que has tenido problemas de rendimiento en el pasado, te recuerdo que el fuego amigo no será tolerado. Una vez que completes con éxito esta prueba, se restablecerá tu elegibilidad y podrás volver a solicitar trabajo de seguridad con Crusader. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v> Las cosas de mi papá</v>
+        <v> Despejemos el nido criminal</v>
       </c>
     </row>
     <row r="283" xml:space="preserve">
       <c r="A283" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, busco a alguien que vaya a la estación Covalex Gundo cerca de Crusader y recoja algunos objetos. Sé que puede sonar a robo, pero son las cosas de mi papá. Verás, él estaba en la estación Gundo cuando ocurrió el accidente. Mi mamá dice que tenemos que esperar a que Covalex lo autorice, pero no me parece justo porque lo extraño muchísimo. Me gustaría tener algo para recordarlo y no quiero esperar más porque podría empezar a olvidar cosas. Te pagaré para que me consigas la caja 510 y la lleves a ~mission(Destination) para que pueda tenerla. Muchas gracias, Baylor Ward</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) se está utilizando actualmente como base de operaciones para numerosas actividades ilegales. Para acabar con este "nido de delincuentes", buscamos un contratista para que se dirija al lugar y elimine a todos los elementos hostiles. Por la fuerza si es necesario. Cabe mencionar que, a veces, bandas como esta reclutan civiles para que trabajen para ellas, a menudo mediante coacción. Es obvio, pero si ven a algún civil, deben protegerlo. Crusader Security no puede permitir que uno de sus contratistas ande disparando indiscriminadamente contra la gente. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v> Apoderarse de los datos</v>
+        <v> Fin de la ocupación de Nine Tails en Orison</v>
       </c>
     </row>
     <row r="285" xml:space="preserve">
       <c r="A285" t="str" xml:space="preserve">
-        <v xml:space="preserve">He estado buscando un paquete de datos específico y justo cuando tengo un respiro, la nave es atacada por esta Reclamadora de Nueve Colas modificada llamada Cometa Negra. Intenté hackear los servidores de la Cometa Negra para ver si copiaron los datos, pero no pude encontrar la manera de sortear sus protocolos de cifrado de forma remota sin la clave física. Ahí es donde entras tú. Necesito que alguien acceda a su nave, consiga su clave de descifrado y descifre el servidor para poder descargar remotamente lo que necesito. Eres lo suficientemente inteligente como para saber con quién estamos tratando, así que planifica en consecuencia. Dado que esto va a causar revuelo, no dejemos nada al azar. Destruye la Cometa Negra cuando termines para cubrirnos las espaldas a ambos.</v>
+        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención, las fuerzas de Nine Tails han tomado el control de varias plataformas comerciales cerca de Orison. Usando un Inversor de Identidad Amigo o Enemigo (IFFI), se han apoderado del espacio aéreo restringido que rodea las plataformas y solo las naves afiliadas a Nine Tails pueden acceder al área. Esto ha obstaculizado gravemente los intentos iniciales de Crusader Security para retomar las plataformas. Por lo tanto, Crusader ha solicitado a las fuerzas de CDF que ayuden a apagar el inversor y eliminar toda presencia hostil. Se anima a todos los voluntarios de CDF disponibles a brindar apoyo. Información adicional: * Mientras el inversor está activo y el espacio aéreo inaccesible, CDF ha logrado tomar el control de un sistema de transporte local y redirigirlo para acceder a la Plataforma Solanki sin el conocimiento de Nine Tails. Los voluntarios deberán dirigirse a la Sala de Exposiciones de Crusader Industries en la Plataforma Comercial y llegar a la azotea para encontrar el transporte que viajará a las plataformas ocupadas. * Se cree que el IFFI está ubicado en un contenedor de almacenamiento cerrado en una barcaza de carga atracada en el Centro de Administración central. * Los códigos de acceso para el contenedor IFFI están en posesión del líder de las fuerzas de Nine Tails, Mendo Ren. * La experiencia previa con Mendo Ren indica que es improbable que muestre su rostro y se arriesgue a ser capturado. Sin embargo, si todos sus lugartenientes son neutralizados, creemos que no tendrá más remedio que tomar el mando de las fuerzas en persona y darnos la oportunidad de recuperar los códigos. * Además del sistema de transporte, Crusader Security nos ha informado que hay varios vehículos en las plataformas disponibles para que las CDF los requisen. Estos vehículos serán la única forma de llegar al Centro Administrativo. NOTA: Si todos los vehículos dentro del espacio aéreo restringido son destruidos antes de que se pueda apagar el inversor, entonces no habrá forma de llegar a la barcaza de carga y las CDF se verán obligadas a retirarse. * Las plataformas están protegidas por armas antiaéreas controladas por Nine Tails. Tenga en cuenta que la SAIC Rowena Dulli de Advocacy es la agregada oficial de las CDF y dirigirá la operación.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v> Extracción de recompensa: ~misión(Nombre del objetivo) (MRT)</v>
+        <v>Doble toque</v>
       </c>
     </row>
     <row r="287" xml:space="preserve">
       <c r="A287" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tuvimos suerte y algunos escaneos recientes de ~mission(Location|Address) han revelado que hay una recompensa pendiente con el nombre de ~mission(TargetName) oculta allí. Se le ha autorizado a entrar en el sitio, encontrarla y resolver la recompensa. Sin embargo, además de la recompensa y sus cómplices, es probable que también haya civiles en el sitio. Si bien estamos ansiosos por eliminar a ~mission(TargetName|Last), no podemos permitirnos bajas civiles. Tenga cuidado al interactuar con los hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Gibbs ID# 91G66BW0</v>
+        <v xml:space="preserve"> Se ha puesto precio a las cabezas de ~mission(TargetName) y ~mission(TargetName2). Si bien tener que alcanzar dos objetivos no es tan extraño, el cliente quiere enviar un mensaje muy específico, así que necesitan que ambos objetivos sean alcanzados en el mismo instante. Los créditos adicionales compensarán las molestias. Y, lamentablemente, como no viajan juntos, es obvio que para lograrlo necesitarás ayuda. Asegúrate de llevar gente de confianza que pueda manejar más de una nave, ya que se sabe que los objetivos viajan con refuerzos.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (LRT)</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Dos en la cabeza</v>
+      </c>
+    </row>
+    <row r="289" xml:space="preserve">
+      <c r="A289" t="str" xml:space="preserve">
+        <v xml:space="preserve">Se trata de dos objetivos que deben ser eliminados simultáneamente. Al parecer, el cliente teme que, si no se eliminan juntos, uno de ellos se vuelva loco y busque venganza. Se les conoce como ~mission(TargetName) y ~mission(TargetName2). Reúne a tu equipo, divide y vencerás. Asegúrate de que cada miembro tenga las habilidades necesarias, porque estos dos tienen fama de ser muy hábiles en combate y, sin duda, no estarán solos. Prepárate para que te den problemas.</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v> Evaluación de recompensas para freelancers verificados</v>
+        <v> Eliminación coordinada</v>
       </c>
     </row>
     <row r="291" xml:space="preserve">
       <c r="A291" t="str" xml:space="preserve">
-        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personas cualificadas para colaborar en la cobranza de recompensas en la zona. Hemos evaluado que usted posee las habilidades necesarias y, por lo tanto, nos gustaría ofrecerle un contrato inicial de prueba para la captura de ~mission(TargetName), vista por última vez en ~mission(Location|Address). Al completar con éxito este contrato, se le incluirá en la lista de Freelancers Verificados de Crusader y podrá optar a futuros trabajos de cobranza de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v xml:space="preserve">Me ha llegado una misión interesante. Necesito eliminar a dos objetivos distintos: ~mission(TargetName) y ~mission(TargetName2). El problema es que si uno se entera de que el otro ha sido atacado, se esconderá. No puedo arriesgarme a perder a ninguno. Requerirá una coordinación considerable, pero quiero que los elimines a ambos al mismo tiempo. Y como no puedes estar en dos sitios a la vez, tendrás que encontrar a alguien de confianza que te ayude. Por suerte, mi información indica que ambos objetivos viajarán solos. Eso debería facilitarte las cosas.</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (HRT)</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Doble eliminación</v>
+      </c>
+    </row>
+    <row r="293" xml:space="preserve">
+      <c r="A293" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tengo un contrato para eliminar a dos jóvenes problemáticos que han estado causando problemas. Tiene que ser una operación limpia y simultánea, o podrían causar aún más problemas. En resumen, necesitarás ayuda. Tanto ~mission(TargetName) como ~mission(TargetName2) saben defenderse, y sus compañeros de vuelo tampoco son ninguna broma. Cada uno de ellos estará protegido por varias naves.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (MRT)</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Divide y vencerás</v>
+      </c>
+    </row>
+    <row r="295" xml:space="preserve">
+      <c r="A295" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Normalmente, enfrentarse a ~mission(TargetName) y ~mission(TargetName2) juntos sería demasiado. Ambos son excelentes en combate aéreo y sus tripulaciones son casi igual de buenas. Sin embargo, recientemente se separaron —no se sabe por qué— y por el momento vuelan por separado. Alguien cree que esta podría ser la mejor oportunidad para eliminarlos. Reúna personal de confianza y planifique un ataque simultáneo contra ambos objetivos. Es demasiado peligroso arriesgar la vida de uno de ellos tras un ataque tan directo.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v> Reevaluación de la recompensa para freelancers verificados</v>
+        <v>Combinación de uno-dos</v>
       </c>
     </row>
     <row r="297" xml:space="preserve">
       <c r="A297" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Buenas noticias! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de recompensas. Esperamos que durante este tiempo hayas corregido cualquier problema de rendimiento anterior y puedas volver a ser un activo valioso. Sin embargo, primero debemos reevaluarte, por lo que nos gustaría que completaras este contrato de recompensa para ~mission(TargetName). Tras completar con éxito esta prueba, volverás a la lista de Freelancers Verificados de Crusader y podrás optar a futuros trabajos de cobro de recompensas cuando estén disponibles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v xml:space="preserve"> Hay otro par que deben ser eliminados: ~mission(TargetName) y ~mission(TargetName2). Han estado desaparecidos durante algunos días, pero acaban de aparecer. Si no los eliminamos ahora, no estoy seguro de que tengamos otra oportunidad. Necesitas reclutar a un compañero para asegurarte de que ambos objetivos sean alcanzados al mismo tiempo. En cuanto a su resistencia, se sabe que ~mission(TargetName) trae a un amigo para que le cubra las espaldas, y sospecho que ~mission(TargetName2) hará lo mismo.</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (ERT)</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Combinación mortal</v>
+      </c>
+    </row>
+    <row r="299" xml:space="preserve">
+      <c r="A299" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Dos operadores de alto nivel que recientemente decidieron atacar a su jefe. Cada uno viaja con una pequeña armada de élite y se adentra en territorio ajeno. Tú, junto con quien reclutes para que te ayude, los eliminarás, y ambos deben hacerlo simultáneamente para que no puedan reagruparse.</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (VLRT)</v>
+        <v> Soporte al cliente bajo ataque</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v/>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v> Recompensa emitida para ~mission(TargetName) (VHRT)</v>
+        <v> Detengan el ataque contra un cliente de alto perfil.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v/>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v> URGENTE: Retomar el puesto de seguridad de Kareah</v>
-      </c>
-    </row>
-    <row r="305" xml:space="preserve">
-      <c r="A305" t="str" xml:space="preserve">
-        <v xml:space="preserve">El puesto de seguridad Kareah está siendo atacado por un número desconocido de asaltantes. Crusader busca contratistas que se dirijan rápidamente a la estación y eliminen a todos los intrusos en las inmediaciones antes de que nuestras fuerzas de seguridad se vean superadas. No sabemos si los atacantes buscan el contrabando en nuestro depósito de pruebas o nuestra base de datos CrimeStat, pero sea lo que sea que busquen, debemos neutralizarlos. Recibirás una bonificación de combate por cada objetivo neutralizado. Al aceptar este contrato, te comprometes a cumplir con todos los protocolos de seguridad de Crusader: si dañas a algún guardia u otro contratista autorizado mientras te encuentres en la estación, tu contrato se dará por terminado y serás marcado como objetivo. El tiempo apremia, así que asegúrate de estar bien equipado para enfrentarte a los hostiles antes de responder. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v>Encuentro de alto riesgo con un barco</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v/>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v> Apoyar a las fuerzas de seguridad y proteger los materiales confidenciales.</v>
-      </c>
-    </row>
-    <row r="307" xml:space="preserve">
-      <c r="A307" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los informes indican que nuestro personal de seguridad en ~mission(location|address) ha sido aniquilado por un grupo de los Nueve Colas, quienes intentan robar material confidencial entregado recientemente a las instalaciones. Crusader Security necesita un contratista experimentado para expulsar a los hostiles y asegurar estas cajas. Según los informes iniciales, recomendamos encarecidamente que venga bien equipado y considere traer refuerzos. Por motivos de seguridad, el material confidencial fue transportado allí como parte de un envío con otras cajas y guardado bajo llave en una bóveda automatizada. Los códigos de acceso al material confidencial se encuentran en tabletas de datos en poder de personal de seguridad de alto rango, pero desconocemos quién las tiene ahora. Es probable que los Nueve Colas también las estén buscando. Cuando tenga todo el material confidencial, entréguelo en ~mission(dropoff1|address) para recibir el pago. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Defensa extremadamente peligrosa</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v/>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v> Sitio de vigilancia contra hostiles</v>
-      </c>
-    </row>
-    <row r="309" xml:space="preserve">
-      <c r="A309" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una pandilla local y estamos buscando contratar a un contratista para formar un equipo de seguridad que haga frente a cualquier ataque. Esta pandilla tiene antecedentes, pero aún son bastante novatos. Creo que será relativamente sencillo para usted y su equipo manejar la situación. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Detengan el ataque mortal al barco</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v/>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v> Sitio de protección contra hostiles graves</v>
-      </c>
-    </row>
-    <row r="311" xml:space="preserve">
-      <c r="A311" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes y estamos buscando contratar a un contratista para formar un equipo de seguridad que repela cualquier ataque. Sé que puede que tengas la tentación de intentar resolver esto por tu cuenta, pero necesitas formar un equipo. Créeme, no vale la pena intentarlo solo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Guardar envío</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v/>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v> Sitio de vigilancia contra hostiles peligrosos</v>
-      </c>
-    </row>
-    <row r="313" xml:space="preserve">
-      <c r="A313" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por una banda criminal conocida que opera en la zona y estamos buscando contratar un equipo de seguridad experimentado para hacer frente a cualquier ataque. Asegúrese de que la persona que contrate esté debidamente cualificada. Necesitará toda la ayuda posible para lidiar con este grupo. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Equipo de protección ejecutiva</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v/>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v> Destruir las drogas ilegales</v>
-      </c>
-    </row>
-    <row r="315" xml:space="preserve">
-      <c r="A315" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos descubierto que un grupo está intentando montar su propio negocio de drogas en ~mission(Location|Address). Aunque parecen ser delincuentes comunes y corrientes, el producto que fabrican es tóxico y ha causado la muerte de varios civiles, así que no podemos permitir que se venda más. Estamos trabajando en una operación a gran escala para desmantelar su negocio definitivamente, pero mientras tanto, debemos detener el flujo de sus drogas. Por eso, Crusader quiere que vayas al lugar y destruyas el alijo que tienen allí. Sin duda, tendrán guardias protegiendo el alijo, pero no creo que representen una gran amenaza. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Los clientes VIP necesitan protección.</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v/>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v> Destruye el contrabando mortal</v>
-      </c>
-    </row>
-    <row r="317" xml:space="preserve">
-      <c r="A317" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un incipiente sindicato se ha instalado en ~mission(Location|Address) y está intentando introducirse en el mercado de las drogas. Desafortunadamente, su producto se ha relacionado con varias muertes en Crusader y sus alrededores. Dada la potencia de esta sustancia, representa una grave amenaza para la población. Crusader está trabajando para desmantelar la operación, pero mientras su producto siga circulando, los cadáveres se acumularán. Queremos que vayas al lugar y destruyas el alijo que tienen allí antes de que tengan la oportunidad de venderlo. Sin embargo, debes tener en cuenta que su alijo está extremadamente bien custodiado. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Se necesita personal de seguridad con experiencia.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v/>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v> Destruir narcóticos tóxicos</v>
-      </c>
-    </row>
-    <row r="319" xml:space="preserve">
-      <c r="A319" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos estado investigando una reciente oleada de sobredosis y todas parecen haberse originado con un lote defectuoso de drogas fabricado en ~mission(Location|Address). Estoy trabajando con otros contratistas para dar con los responsables, pero la gente sigue muriendo mientras el producto siga circulando. Quiero que vayas al lugar y destruyas el alijo que tienen allí. Eso nos dará algo de tiempo antes de cerrarlo definitivamente. Tendrán guardias protegiendo su suministro, así que prepárate para enfrentarte a hostiles. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Se necesita operador de primer nivel.</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v/>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v> Proporcionar respaldo</v>
-      </c>
-    </row>
-    <row r="321" xml:space="preserve">
-      <c r="A321" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) está siendo amenazada por un grupo de delincuentes. Si bien contamos con personal de seguridad en el lugar, estamos buscando contratar personal adicional para repeler cualquier ataque. Como contratista, desconozco su experiencia trabajando en equipo, pero no quiero oír hablar de "fuego amigo", ya que esto podría generar problemas. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Detalle de protección de bajo riesgo</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v/>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v> Evaluación del trabajo de seguridad</v>
-      </c>
-    </row>
-    <row r="323" xml:space="preserve">
-      <c r="A323" t="str" xml:space="preserve">
-        <v xml:space="preserve">Con el fin de aumentar la seguridad de Crusader y sus alrededores, Crusader Security busca personal cualificado para colaborar en labores de seguridad en la zona. Hemos determinado que usted posee las habilidades necesarias para ofrecerle un contrato de prueba inicial. Colaborará con Crusader Security para hacer frente a un pequeño grupo hostil que ha estado realizando amenazas contra ~mission(Location|Address). Tenga en cuenta que ya contamos con personal de seguridad en el lugar, por lo que deberá tener cuidado con el fuego amigo. Tras la finalización satisfactoria de este contrato, podrá solicitar cualquier otro puesto de seguridad que surja en el futuro. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Se requiere protección adicional. Alto riesgo.</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v/>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v> Reevaluación del trabajo de seguridad</v>
-      </c>
-    </row>
-    <row r="325" xml:space="preserve">
-      <c r="A325" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Felicidades! Crusader Security ha decidido ofrecerte otra oportunidad como contratista de seguridad. Con un poco de esfuerzo y dedicación, esperamos que puedas superar cualquier problema de rendimiento anterior. Sin embargo, para reevaluar tu idoneidad, nos gustaría que ayudaras a Crusader Security a lidiar con un grupo de delincuentes que ha estado realizando amenazas contra ~mission(Location|Address). Ahora bien, dado que has tenido problemas de rendimiento en el pasado, te recuerdo que el fuego amigo no será tolerado. Una vez que completes con éxito esta prueba, se restablecerá tu elegibilidad y podrás volver a solicitar trabajo de seguridad con Crusader. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Es hora de dar una lección</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v/>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v> Despejemos el nido criminal</v>
-      </c>
-    </row>
-    <row r="327" xml:space="preserve">
-      <c r="A327" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que ~mission(Location|Address) se está utilizando actualmente como base de operaciones para numerosas actividades ilegales. Para acabar con este "nido de delincuentes", buscamos un contratista para que se dirija al lugar y elimine a todos los elementos hostiles. Por la fuerza si es necesario. Cabe mencionar que, a veces, bandas como esta reclutan civiles para que trabajen para ellas, a menudo mediante coacción. Es obvio, pero si ven a algún civil, deben protegerlo. Crusader Security no puede permitir que uno de sus contratistas ande disparando indiscriminadamente contra la gente. CONTRATO AUTORIZADO POR: Oficial de Enlace Bautista ID# 948J030K</v>
+        <v> Emboscada engañosa</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v/>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v> Fin de la ocupación de Nine Tails en Orison</v>
-      </c>
-    </row>
-    <row r="329" xml:space="preserve">
-      <c r="A329" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención, las fuerzas de Nine Tails han tomado el control de varias plataformas comerciales cerca de Orison. Usando un Inversor de Identidad Amigo o Enemigo (IFFI), se han apoderado del espacio aéreo restringido que rodea las plataformas y solo las naves afiliadas a Nine Tails pueden acceder al área. Esto ha obstaculizado gravemente los intentos iniciales de Crusader Security para retomar las plataformas. Por lo tanto, Crusader ha solicitado a las fuerzas de CDF que ayuden a apagar el inversor y eliminar toda presencia hostil. Se anima a todos los voluntarios de CDF disponibles a brindar apoyo. Información adicional: * Mientras el inversor está activo y el espacio aéreo inaccesible, CDF ha logrado tomar el control de un sistema de transporte local y redirigirlo para acceder a la Plataforma Solanki sin el conocimiento de Nine Tails. Los voluntarios deberán dirigirse a la Sala de Exposiciones de Crusader Industries en la Plataforma Comercial y llegar a la azotea para encontrar el transporte que viajará a las plataformas ocupadas. * Se cree que el IFFI está ubicado en un contenedor de almacenamiento cerrado en una barcaza de carga atracada en el Centro de Administración central. * Los códigos de acceso para el contenedor IFFI están en posesión del líder de las fuerzas de Nine Tails, Mendo Ren. * La experiencia previa con Mendo Ren indica que es improbable que muestre su rostro y se arriesgue a ser capturado. Sin embargo, si todos sus lugartenientes son neutralizados, creemos que no tendrá más remedio que tomar el mando de las fuerzas en persona y darnos la oportunidad de recuperar los códigos. * Además del sistema de transporte, Crusader Security nos ha informado que hay varios vehículos en las plataformas disponibles para que las CDF los requisen. Estos vehículos serán la única forma de llegar al Centro Administrativo. NOTA: Si todos los vehículos dentro del espacio aéreo restringido son destruidos antes de que se pueda apagar el inversor, entonces no habrá forma de llegar a la barcaza de carga y las CDF se verán obligadas a retirarse. * Las plataformas están protegidas por armas antiaéreas controladas por Nine Tails. Tenga en cuenta que la SAIC Rowena Dulli de Advocacy es la agregada oficial de las CDF y dirigirá la operación.</v>
+        <v> Nueva oportunidad: ataque de emboscada</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v/>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Doble toque</v>
-      </c>
-    </row>
-    <row r="331" xml:space="preserve">
-      <c r="A331" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se ha puesto precio a las cabezas de ~mission(TargetName) y ~mission(TargetName2). Si bien tener que alcanzar dos objetivos no es tan extraño, el cliente quiere enviar un mensaje muy específico, así que necesitan que ambos objetivos sean alcanzados en el mismo instante. Los créditos adicionales compensarán las molestias. Y, lamentablemente, como no viajan juntos, es obvio que para lograrlo necesitarás ayuda. Asegúrate de llevar gente de confianza que pueda manejar más de una nave, ya que se sabe que los objetivos viajan con refuerzos.</v>
+        <v> Lanzar ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v/>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v> Dos en la cabeza</v>
-      </c>
-    </row>
-    <row r="333" xml:space="preserve">
-      <c r="A333" t="str" xml:space="preserve">
-        <v xml:space="preserve">Se trata de dos objetivos que deben ser eliminados simultáneamente. Al parecer, el cliente teme que, si no se eliminan juntos, uno de ellos se vuelva loco y busque venganza. Se les conoce como ~mission(TargetName) y ~mission(TargetName2). Reúne a tu equipo, divide y vencerás. Asegúrate de que cada miembro tenga las habilidades necesarias, porque estos dos tienen fama de ser muy hábiles en combate y, sin duda, no estarán solos. Prepárate para que te den problemas.</v>
+        <v> Emboscada sumamente peligrosa</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v/>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v> Eliminación coordinada</v>
-      </c>
-    </row>
-    <row r="335" xml:space="preserve">
-      <c r="A335" t="str" xml:space="preserve">
-        <v xml:space="preserve">Me ha llegado una misión interesante. Necesito eliminar a dos objetivos distintos: ~mission(TargetName) y ~mission(TargetName2). El problema es que si uno se entera de que el otro ha sido atacado, se esconderá. No puedo arriesgarme a perder a ninguno. Requerirá una coordinación considerable, pero quiero que los elimines a ambos al mismo tiempo. Y como no puedes estar en dos sitios a la vez, tendrás que encontrar a alguien de confianza que te ayude. Por suerte, mi información indica que ambos objetivos viajarán solos. Eso debería facilitarte las cosas.</v>
+        <v> Ajustar cuentas</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v/>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v> Doble eliminación</v>
-      </c>
-    </row>
-    <row r="337" xml:space="preserve">
-      <c r="A337" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tengo un contrato para eliminar a dos jóvenes problemáticos que han estado causando problemas. Tiene que ser una operación limpia y simultánea, o podrían causar aún más problemas. En resumen, necesitarás ayuda. Tanto ~mission(TargetName) como ~mission(TargetName2) saben defenderse, y sus compañeros de vuelo tampoco son ninguna broma. Cada uno de ellos estará protegido por varias naves.</v>
+        <v> Emboscada peligrosa</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v/>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v> Divide y vencerás</v>
+        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="339" xml:space="preserve">
       <c r="A339" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Normalmente, enfrentarse a ~mission(TargetName) y ~mission(TargetName2) juntos sería demasiado. Ambos son excelentes en combate aéreo y sus tripulaciones son casi igual de buenas. Sin embargo, recientemente se separaron —no se sabe por qué— y por el momento vuelan por separado. Alguien cree que esta podría ser la mejor oportunidad para eliminarlos. Reúna personal de confianza y planifique un ataque simultáneo contra ambos objetivos. Es demasiado peligroso arriesgar la vida de uno de ellos tras un ataque tan directo.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido información procesable sobre una recompensa peligrosa, que ha resultado ser extremadamente escurridiza. &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; fue visto con un contingente dedicado de asociados conocidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Estamos buscando un contratista listo y dispuesto a ejecutar esta recompensa antes de que desaparezca de nuevo. Basándonos en intentos anteriores de aprehender a este criminal, hay una buena probabilidad de que &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; intente evitar una confrontación directa y, en su lugar, envíe a sus aliados a enfrentarlo. Creemos que neutralizar estas fuerzas protectoras y destruir la red de seguridad que proporcionan es la mejor manera de obligar a &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; a enfrentarse directamente a usted. Prepárese para enfrentarse a una fuerza significativa y experimentada. Le recomendamos que planifique en consecuencia. El pago se efectuará una vez finalizado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Combinación de uno-dos</v>
+        <v>Gestionar la misión (nombre del objetivo) y las fuerzas de apoyo.</v>
       </c>
     </row>
     <row r="341" xml:space="preserve">
       <c r="A341" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hay otro par que deben ser eliminados: ~mission(TargetName) y ~mission(TargetName2). Han estado desaparecidos durante algunos días, pero acaban de aparecer. Si no los eliminamos ahora, no estoy seguro de que tengamos otra oportunidad. Necesitas reclutar a un compañero para asegurarte de que ambos objetivos sean alcanzados al mismo tiempo. En cuanto a su resistencia, se sabe que ~mission(TargetName) trae a un amigo para que le cubra las espaldas, y sospecho que ~mission(TargetName2) hará lo mismo.</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Tenemos un contrato de recompensa de alto nivel listo para ser ejecutado. &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y su equipo fueron identificados ejecutando una incursión en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Si su modus operandi es el correcto, &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; ha aparecido para dar un gran golpe y luego desaparecerá en el éter. No permitamos que eso vuelva a suceder. Se dice que las fuerzas hostiles se han dispersado por la ubicación. Eso hará que rastrear la ubicación precisa de &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; sea difícil. Además, espere que el objetivo actúe a la defensiva cuando sea atacado. En enfrentamientos anteriores, permanecieron ocultos y dirigieron sus fuerzas desde lejos. Recomendamos que se concentre primero en eliminar a sus aliados y obligue a &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; a defenderse. También le aconsejamos que lleve abundante munición e incluso algún tipo de apoyo para evitar ser superado. El pago se realizará al completar el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v> Combinación mortal</v>
-      </c>
-    </row>
-    <row r="343" xml:space="preserve">
-      <c r="A343" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Dos operadores de alto nivel que recientemente decidieron atacar a su jefe. Cada uno viaja con una pequeña armada de élite y se adentra en territorio ajeno. Tú, junto con quien reclutes para que te ayude, los eliminarás, y ambos deben hacerlo simultáneamente para que no puedan reagruparse.</v>
+        <v>Contrato de nivel amarillo: Interrupción de operaciones</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v/>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v> Solicitud de asistencia para el buque</v>
+        <v> Contrato de nivel naranja: Destruir infraestructura ilegal</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v> Solicitud de asistencia para el buque</v>
+        <v/>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Soporte al cliente bajo ataque</v>
+        <v> Contrato de nivel naranja: Retire los suministros de combustible</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v> Soporte al cliente bajo ataque</v>
+        <v/>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v> Repeler naves de cuchillas destrozadas</v>
+        <v> Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v> Repeler naves de cuchillas destrozadas</v>
+        <v/>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v> Detengan el ataque contra un cliente de alto perfil.</v>
+        <v> Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v> Detengan el ataque contra un cliente de alto perfil.</v>
+        <v/>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v> Ataque de hoja rota grave</v>
+        <v> Contrato de nivel rojo: Demolición de contenedores de combustible</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v> Ataque de hoja rota grave</v>
+        <v/>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v> Encuentro de alto riesgo con un barco</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="str">
-        <v> Encuentro de alto riesgo con un barco</v>
+        <v> Contrato de nivel amarillo: Proteger ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="355" xml:space="preserve">
+      <c r="A355" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Hay algún piloto dispuesto en la zona? Necesitamos protección alrededor de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; para un cliente. Una banda de forajidos ha estado atacando su &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;, y si no se hace nada al respecto causarán daños graves. Necesitamos a alguien que proteja la propiedad del cliente lo mejor posible y se encargue de los matones. Según la información que hemos logrado recopilar, estos matones son de poca monta, pero pueden causar problemas si no se tiene cuidado. Así que, si logras cumplir con los estándares de Foxwell, ofrecemos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v> Golpe de hoja destrozada</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="str">
-        <v> Golpe de hoja destrozada</v>
+        <v>Contrato de nivel naranja: Proteger ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="357" xml:space="preserve">
+      <c r="A357" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de nuestros clientes de alta prioridad está siendo atacado por una banda criminal que apunta a sus &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Los activos del cliente son valiosos, así que necesitamos mantenerlos seguros a toda costa, pero no voy a bromear: será un desafío enorme con estos matones decididos a causar daños reales. Si fuera yo, no dudaría en &lt;EM&gt;traer refuerzos&lt;/EM4&gt; para lidiar con ellos. No son ninguna broma, así que ofrecemos un merecido &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal que se encargue de estos tipos con éxito. Mucha suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v> Defensa extremadamente peligrosa</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="str">
-        <v> Defensa extremadamente peligrosa</v>
+        <v>Contrato de nivel naranja: Defender ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="359" xml:space="preserve">
+      <c r="A359" t="str" xml:space="preserve">
+        <v xml:space="preserve">Espero que puedas brindar servicios de protección en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Uno de nuestros clientes de alta prioridad está teniendo serios problemas con una banda de forajidos que atacan su ~mission(Objects). Necesitamos poder mantener los activos lo más seguros e intactos posible. El cliente espera el servicio por el que paga, así que no lo arruines o podríamos perder un cliente leal. Por ahora, todavía estamos un poco a oscuras con respecto a estos forajidos, pero si logras resolver esto según los estándares de Foxwell, le ofreceremos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v> Necesidades del cliente Apoyo en combate</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="str">
-        <v> Necesidades del cliente Apoyo en combate</v>
+        <v>Contrato de nivel rojo: Proteger ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="361" xml:space="preserve">
+      <c r="A361" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acaba de llegar un contrato de emergencia sobre una banda de matones violentos que están causando estragos en la infraestructura de uno de nuestros clientes VIP. Si está disponible, necesitamos que acuda rápidamente a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y defienda los valiosos &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; del cliente a toda costa. Foxwell está muy al tanto de este grupo, así que créame cuando le digo que no hay que subestimar a estos pilotos. Le recomiendo encarecidamente que organice una &lt;EM&gt;fuerza de apoyo altamente competente&lt;/EM&gt; para que vuele con usted al lugar. Si logra sobrevivir al encuentro con la propiedad del cliente intacta, añadiremos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; a cualquier contratista principal lo suficientemente valiente como para aceptar este trabajo. Manténgase a salvo y buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v> Detengan el ataque mortal al barco</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="str">
-        <v> Detengan el ataque mortal al barco</v>
+        <v>Contrato de nivel amarillo: Defender ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="363" xml:space="preserve">
+      <c r="A363" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Llamando a todos los pilotos: uno de nuestros clientes busca protección para sus &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;, ubicados en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Por lo que hemos averiguado, los atacantes son un grupo de aspirantes a delincuentes que probablemente no se han dado cuenta del valor de los bienes que intentan destruir, solo causan estragos por diversión. Aun así, la propiedad del cliente es importante, por lo que debe mantenerse lo más intacta posible. Si se encargan de ellos según los estándares de Foxwell, ofrecemos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v> Detengan el ataque de la hoja destrozada</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="str">
-        <v> Detengan el ataque de la hoja destrozada</v>
+        <v>Contrato de nivel rojo: Defender ~misión(Objetos)</v>
+      </c>
+    </row>
+    <row r="365" xml:space="preserve">
+      <c r="A365" t="str" xml:space="preserve">
+        <v xml:space="preserve">Se necesita apoyo urgente para el barco en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Una conocida organización criminal destructiva ha estado tanteando el terreno con la propiedad de uno de nuestros clientes durante meses, y ahora ha causado estragos atacando los &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; del cliente. Estos activos son muy valiosos, por lo que debemos mantenerlos a salvo a toda costa, aunque sabemos que no será tarea fácil. No puedo enfatizar lo suficiente lo peligrosos que son estos individuos, así que no dudaría en &lt;EM&gt;traer refuerzos&lt;/EM&gt; para lidiar con ellos. Si usted y los activos salen ilesos, ofrecemos un merecido &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Mucha suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v> Guardar envío</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="str">
-        <v> Guardar envío</v>
+        <v>Contrato de nivel amarillo: Defender ~mission(DefendLocationWrapperLocation)</v>
+      </c>
+    </row>
+    <row r="367" xml:space="preserve">
+      <c r="A367" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Las naves que entran y salen de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; están siendo atacadas por fuerzas hostiles. La gente de allí nos ha contratado para solucionar este problema de inmediato. Necesitamos a alguien que llegue pronto y empiece a combatir estas naves. La situación parece estar en constante evolución, así que te mantendré informado sobre dónde se te necesita más. Por el esfuerzo y la diligencia, también pagaremos una bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal por encargarse de esto. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v> Equipo de protección ejecutiva</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="str">
-        <v> Equipo de protección ejecutiva</v>
+        <v> Contrato de Nivel Naranja: Proteja los intereses de nuestros clientes.</v>
+      </c>
+    </row>
+    <row r="369" xml:space="preserve">
+      <c r="A369" t="str" xml:space="preserve">
+        <v xml:space="preserve">La gente de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; está bajo ataque y necesita nuestro apoyo. Sus naves en la zona están siendo atacadas y existe una creciente preocupación de que esto sea solo el preludio de algo más grande. La situación está evolucionando, pero estoy recibiendo actualizaciones constantes sobre lo que está sucediendo y te mantendré informado a medida que avance el contrato. ¿Estás disponible para ayudarlos? Sería inteligente reclutar a algunos amigos para que ayuden. Son clientes importantes y no podemos permitirnos fallarles. El contratista principal ganará un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; si completas el trabajo. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v> Los clientes VIP necesitan protección.</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="str">
-        <v> Los clientes VIP necesitan protección.</v>
+        <v>Contrato de nivel naranja: Se requiere protección para el buque.</v>
+      </c>
+    </row>
+    <row r="371" xml:space="preserve">
+      <c r="A371" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos clientes que reportan ataques de forajidos a barcos alrededor de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt;. Están completamente bloqueados y cualquiera que entre o salga es un objetivo. Cualquier intento de resolver el problema solo ha sido recibido con más refuerzos de forajidos. El cliente está desesperado por una solución, así que estamos contratando a un contratista para que vaya y restablezca la paz en el área. Si surge algún otro problema una vez que estés allí, te comunicaré las instrucciones sobre cómo ayudar. Realmente necesitamos a alguien rápido. Así que para hacer la oferta más atractiva, el contratista principal también recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v> Se necesita personal de seguridad con experiencia.</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="str">
-        <v> Se necesita personal de seguridad con experiencia.</v>
+        <v xml:space="preserve">Contrato de nivel rojo: Soporte a clientes VIP</v>
+      </c>
+    </row>
+    <row r="373" xml:space="preserve">
+      <c r="A373" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Buscamos un profesional consumado para manejar un trabajo de alto riesgo. Tenemos clientes VIP en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; que se enfrentan a forajidos extremadamente agresivos y motivados que atacan naves alrededor de su ubicación. Los detalles exactos del ataque aún están llegando, pero parece ser una operación amplia y multifacética. Si está disponible, le recomiendo encarecidamente que traiga naves de apoyo de combate adicionales, muchos suministros y su mejor desempeño. Si lo hace bien, recompensaremos al contratista principal con un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v> Se necesita operador de primer nivel.</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="str">
-        <v> Se necesita operador de primer nivel.</v>
+        <v>Contrato de nivel amarillo: Enfréntate a los agresores</v>
+      </c>
+    </row>
+    <row r="375" xml:space="preserve">
+      <c r="A375" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Naves no autorizadas están acosando a cualquiera que intente aterrizar o salir de las operaciones de nuestro cliente en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt;. Necesitamos a alguien que vuele hasta allí para defender el sitio y proteger las naves de nuestro cliente antes de que la situación se salga de control. Llega allí, persigue a esos agresores y te mantendré informado sobre la situación. Ayuda a solucionar esto y le pasaremos un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v> Detalle de protección de bajo riesgo</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="str">
-        <v>Detalle de protección de bajo riesgo</v>
+        <v> Contrato de nivel rojo: Salvar naves en ~mission(DefendLocationWrapperLocation)</v>
+      </c>
+    </row>
+    <row r="377" xml:space="preserve">
+      <c r="A377" t="str" xml:space="preserve">
+        <v xml:space="preserve">Se necesita apoyo naval en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; inmediatamente. Los intereses de nuestro cliente en la zona están siendo atacados ferozmente por fuerzas ilegales. Buscamos a alguien que pueda recoger su equipo, algunos barcos de apoyo de confianza y desplegarlos antes de que sea demasiado tarde. Una vez que llegues, te enviaré cualquier actualización de la situación. No lo estropees. Estos clientes están pagando y esperan protección de primer nivel. Si algo sale mal, podríamos perder este contrato. Por eso, le daremos al contratista principal un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; si todo sale a la perfección. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v> Se requiere protección adicional. Alto riesgo.</v>
+        <v>Contrato de nivel amarillo: Barco bajo ataque</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v> Se requiere protección adicional. Alto riesgo.</v>
+        <v/>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v> Es hora de dar una lección</v>
+        <v> Contrato de nivel rojo: El barco está bajo ataque.</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v> Es hora de dar una lección</v>
+        <v/>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v> Emboscada engañosa</v>
+        <v> Contrato de nivel naranja: ~misión (nave) necesita asistencia</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v> Emboscada engañosa</v>
+        <v/>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v> Nueva oportunidad: ataque de emboscada</v>
+        <v> Desmantelan una nueva operación antidrogas.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v> Nueva oportunidad: ataque de emboscada</v>
+        <v/>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v> Lanzar ataque sorpresa</v>
+        <v> Destruir drogas peligrosas</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v> Lanzar ataque sorpresa</v>
+        <v/>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v> Emboscada sumamente peligrosa</v>
+        <v> Destruir las drogas ilegales</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v> Emboscada sumamente peligrosa</v>
+        <v/>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v> Ajustar cuentas</v>
+        <v> Ayuda a proteger el sitio.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v> Ajustar cuentas</v>
+        <v/>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v> Emboscada peligrosa</v>
+        <v> Limpie cuidadosamente el sitio</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v> Emboscada peligrosa</v>
+        <v/>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v> Sitio seguro</v>
-      </c>
-    </row>
-    <row r="395" xml:space="preserve">
-      <c r="A395" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de Ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente ha interceptado comunicaciones entre miembros de pandillas y ha descubierto que están planeando un ataque en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Ahora necesitan nuestra ayuda para asegurar que el ataque no tenga éxito. Buscamos un contratista que pueda defender la ubicación de esta ofensiva. No tenemos detalles sobre los delincuentes, pero dudamos que sean muy hábiles si nuestro cliente interceptó sus comunicaciones tan fácilmente. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Contrato de nivel amarillo: Merc Work</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v/>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v> Repeler a los asaltantes</v>
-      </c>
-    </row>
-    <row r="397" xml:space="preserve">
-      <c r="A397" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Se avecina un grave problema para uno de nuestros clientes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Han sido advertidos de que un grupo de forajidos altamente capacitados tiene la mira puesta en tomar y ocupar esa ubicación. Hemos sido contratados para asegurarnos de que eso no suceda. Necesitamos un contratista para desplegarse en la ubicación de inmediato. Según la información proporcionada por el cliente, esto no será fácil. Le recomendamos encarecidamente que traiga aliados y muchos suministros para ayudar a repeler el inminente ataque. El pago se emitirá una vez completado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Contrato de nivel amarillo: Despeje de la PAF</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v/>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v> Proteger ubicación</v>
-      </c>
-    </row>
-    <row r="399" xml:space="preserve">
-      <c r="A399" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de la ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido información de que delincuentes tienen la mira puesta en atacar &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Nuestro cliente está preocupado por la inminencia del ataque y solicitó que se despliegue seguridad en el sitio de inmediato. Si está interesado y disponible, reúna todos los suministros y el apoyo que pueda necesitar y diríjase a la ubicación lo antes posible. El pago se emitirá una vez completado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Barrer y despejar la ubicación</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v/>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v> Expulsar a los forajidos</v>
-      </c>
-    </row>
-    <row r="401" xml:space="preserve">
-      <c r="A401" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Desalojo de ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente está enviando comunicaciones frenéticas indicando que una de sus ubicaciones está siendo atacada. Necesitamos un contratista que pueda dirigirse rápidamente a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y despejar la ubicación de actores hostiles. Según el personal en el sitio, los delincuentes se encuentran actualmente atrincherados cerca de &lt;EM4&gt;~mission(Location)&lt;/EM4&gt;. Acérquese con precaución y esté preparado para usar fuerza letal si los delincuentes se resisten a ser desalojados. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Ataque de precisión en ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v/>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v> Apoyo en combate: ~misión(Ubicación)</v>
+        <v> Localizar ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v> Apoyo en combate: ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v> Solicitar ayuda</v>
+        <v> Contrato de nivel rojo: Recuperar cargamento</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v> Solicitar ayuda</v>
+        <v/>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo)</v>
-      </c>
-    </row>
-    <row r="407" xml:space="preserve">
-      <c r="A407" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido información procesable sobre una recompensa peligrosa, que ha resultado ser extremadamente escurridiza. &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; fue visto con un contingente dedicado de asociados conocidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Estamos buscando un contratista listo y dispuesto a ejecutar esta recompensa antes de que desaparezca de nuevo. Basándonos en intentos anteriores de aprehender a este criminal, hay una buena probabilidad de que &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; intente evitar una confrontación directa y, en su lugar, envíe a sus aliados a enfrentarlo. Creemos que neutralizar estas fuerzas protectoras y destruir la red de seguridad que proporcionan es la mejor manera de obligar a &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; a enfrentarse directamente a usted. Prepárese para enfrentarse a una fuerza significativa y experimentada. Le recomendamos que planifique en consecuencia. El pago se efectuará una vez finalizado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v> Contrato de nivel rojo: Recuperar el cargamento robado</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v/>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Recompensa de caza: ~misión(Nombre del objetivo)</v>
-      </c>
-    </row>
-    <row r="409" xml:space="preserve">
-      <c r="A409" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Hemos recibido un aviso sobre la ubicación de una recompensa de alto perfil. Los informes de inteligencia han rastreado a &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Necesitamos un contratista que se dirija rápidamente hacia esa dirección antes de que el objetivo desaparezca. Según los últimos informes, fueron vistos por última vez cerca de &lt;EM4&gt;~mission(Location)&lt;/EM4&gt;. Venga preparado para usar fuerza letal si &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; se resiste a la detención. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v/>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v> Evaluación de contratistas de seguridad</v>
-      </c>
-    </row>
-    <row r="411" xml:space="preserve">
-      <c r="A411" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Juicio - Defensa Ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Eckhart Security está buscando profesionales de seguridad calificados para unirse a sus filas. Si cree que tiene la disposición y la experiencia para manejar una amplia variedad de contratos de seguridad, lo alentamos a demostrar su competencia ejecutando el contrato a continuación. Los delincuentes han estado molestando a uno de nuestros clientes atacando a su personal y operaciones. Basándonos en el patrón establecido por ataques anteriores, creemos que estas fuerzas hostiles atacarán &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; a continuación. Complete con éxito este contrato para recibir el pago y más oportunidades de trabajo de Eckhart Security. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> ¿Sigues buscando trabajo?</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v/>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Reevaluación de contratistas de seguridad</v>
+        <v> Contrato de nivel amarillo: Inspección de seguridad</v>
       </c>
     </row>
     <row r="413" xml:space="preserve">
       <c r="A413" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Prueba - Defender Ubicación CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Eckhart Security continúa evaluando posibles nuevos contratistas. Según nuestros registros, usted ya intentó un contrato de prueba. Entendemos lo exigente e impredecible que puede ser este trabajo y nos gustaría darle otra oportunidad de completar un contrato que califique. Si está interesado, preséntese en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; listo para defenderlo de un ataque inminente de delincuentes. Complete con éxito este contrato para recibir el pago y más oportunidades de trabajo de Eckhart Security. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Necesitas a alguien para eliminar una patrulla de seguridad. Tendrás que ir al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en tu HUD y luego escanear varios puntos de ruta designados asegurándote de que sean seguros. Los satélites en esa región han estado fallando últimamente. No estoy seguro de qué está pasando allí, pero es mejor estar preparado en caso de que haya algún problema. Completa este contrato y el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(ScripAmount) MG Scrip.&lt;/EM4&gt; Buena suerte, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v> Gestionar la misión (nombre del objetivo) y las fuerzas de apoyo.</v>
+        <v> Contrato de nivel naranja: amenaza potencial para la seguridad</v>
       </c>
     </row>
     <row r="415" xml:space="preserve">
       <c r="A415" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Recompensa CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Tenemos un contrato de recompensa de alto nivel listo para ser ejecutado. &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y su equipo fueron identificados ejecutando una incursión en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Si su modus operandi es el correcto, &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; ha aparecido para dar un gran golpe y luego desaparecerá en el éter. No permitamos que eso vuelva a suceder. Se dice que las fuerzas hostiles se han dispersado por la ubicación. Eso hará que rastrear la ubicación precisa de &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; sea difícil. Además, espere que el objetivo actúe a la defensiva cuando sea atacado. En enfrentamientos anteriores, permanecieron ocultos y dirigieron sus fuerzas desde lejos. Recomendamos que se concentre primero en eliminar a sus aliados y obligue a &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; a defenderse. También le aconsejamos que lleve abundante munición e incluso algún tipo de apoyo para evitar ser superado. El pago se realizará al completar el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Se han avistado varios barcos desconocidos en zonas frecuentadas por transportistas que entregan mercancías para nuestro cliente. Les preocupa que estos barcos estén vigilando a sus transportistas para preparar una emboscada, por lo que nos han contratado para patrullar la zona. Empiece por ir al marcador de ubicación en su HUD y escanéelo para asegurarse de que no haya peligro. Después, le enviaremos a otras zonas para que busque posibles amenazas. Le recomendamos que traiga un compañero y suficientes suministros para estar preparado para cualquier eventualidad. Tenga en cuenta también que completar con éxito este contrato le reportará al contratista principal una bonificación de ~misión(Cantidad de Scrip) MG Scrip. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Contrato de nivel amarillo: Interrupción de operaciones</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="str">
-        <v> Contrato de nivel amarillo: Interrupción de operaciones</v>
+        <v>Contrato de nivel naranja: Patrulla de seguridad</v>
+      </c>
+    </row>
+    <row r="417" xml:space="preserve">
+      <c r="A417" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Un cliente está preocupado por la actividad cerca de algunos de sus intereses. Hemos sido contratados para patrullar el área y realizar escaneos en varias ubicaciones. ¿Interesado? Si es así, diríjase al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en su HUD para comenzar el patrullaje. El cliente no especificó las amenazas, pero no cree que todo sea del todo correcto. Esperamos poder brindarle algo de tranquilidad. Además, el cliente acordó que ofrezcamos un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v> Contrato de nivel naranja: Destruir infraestructura ilegal</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="str">
-        <v> Contrato de nivel naranja: Destruir infraestructura ilegal</v>
+        <v> Contrato de Nivel Rojo: Asegurar el Espacio Amenazado</v>
+      </c>
+    </row>
+    <row r="419" xml:space="preserve">
+      <c r="A419" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesitamos un piloto experimentado para una patrulla importante. Un cliente importante está harto de que los forajidos ataquen sus naves y satélites. Nos han contratado para escanear las áreas en cuestión y lidiar con las fuerzas hostiles. La patrulla comienza en el marcador de ubicación &lt;EM4&gt; en tu HUD antes de dirigirnos a otras ubicaciones que esperamos que despejes. No sabemos con qué te encontrarás, pero según la información compartida por el cliente, frecuentemente ven grupos de cazas de cinco a siete naves patrullando la región. Algunos incluso tienen naves más grandes liderando el ataque. Eso significa que más te vale estar preparado para una dura batalla. Si puedes, intenta reclutar al menos a &lt;EM4&gt;tres amigos&lt;/EM4&gt; para la causa. Incluso un piloto experimentado necesitará toda la ayuda posible contra esta tripulación. Dado que esta va a ser una misión difícil, el contratista principal recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al final de la patrulla. Buena suerte, Kevin Walton, Despachador de Foxwell Enforcement. «Seguridad a tu medida». Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v> Contrato de nivel naranja: Retire los suministros de combustible</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="str">
-        <v> Contrato de nivel naranja: Retire los suministros de combustible</v>
+        <v>Contrato de nivel amarillo: Patrullaje de rutina</v>
+      </c>
+    </row>
+    <row r="421" xml:space="preserve">
+      <c r="A421" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Es hora de realizar una patrulla de rutina para uno de nuestros clientes de larga data. La ruta es una serie de puntos de referencia que deben visitarse y escanearse para confirmar que todo esté como se espera. Debería ser bastante simple. Si está interesado, acepte y diríjase al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en su HUD para comenzar. Si lo logra, el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(ScripAmount) MG Scrip.&lt;/EM4&gt; Buena suerte, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v> Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="str">
-        <v> Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
+        <v> Contrato de nivel rojo: Patrulla de seguridad de alto riesgo</v>
+      </c>
+    </row>
+    <row r="423" xml:space="preserve">
+      <c r="A423" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un cliente necesita nuestra ayuda. Forajidos están merodeando por ciertos sectores donde hacen negocios y atacando a cualquiera que se cruce en su camino. Nuestro cliente ya ha perdido varias naves y no puede permitirse perder más. Necesitamos a alguien que patrulle esas áreas y atraiga a cualquier fuerza hostil. El trabajo comienza con usted dirigiéndose al marcador de ubicación &lt;EM4&gt; en su HUD y escaneando. Luego compartiremos algunos otros puntos de patrulla para que los escanee. Por lo que parece, estos grupos de naves cuentan con pilotos hábiles y agresivos. Mejor prepárese para la pelea si se encuentra con alguno de ellos. Sería bueno tener al menos &lt;EM4&gt;dos pilotos de confianza&lt;/EM4&gt; a su lado para esto. Al final de una patrulla exitosa, el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Manténgase frío, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v> Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
+        <v>Contrato de nivel amarillo: Ataque sorpresa</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v> Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
+        <v/>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v> Contrato de nivel rojo: Demolición de contenedores de combustible</v>
+        <v> Contrato de nivel naranja: Devuelve el favor</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v> Contrato de nivel rojo: Demolición de contenedores de combustible</v>
+        <v/>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v> Contrato de nivel amarillo: Proteger ~misión(Objetos)</v>
-      </c>
-    </row>
-    <row r="429" xml:space="preserve">
-      <c r="A429" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Hay algún piloto dispuesto en la zona? Necesitamos protección alrededor de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; para un cliente. Una banda de forajidos ha estado atacando su &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;, y si no se hace nada al respecto causarán daños graves. Necesitamos a alguien que proteja la propiedad del cliente lo mejor posible y se encargue de los matones. Según la información que hemos logrado recopilar, estos matones son de poca monta, pero pueden causar problemas si no se tiene cuidado. Así que, si logras cumplir con los estándares de Foxwell, ofrecemos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
+        <v> Contrato de nivel naranja: Tender una trampa</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v/>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Contrato de nivel naranja: Proteger ~misión(Objetos)</v>
-      </c>
-    </row>
-    <row r="431" xml:space="preserve">
-      <c r="A431" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de nuestros clientes de alta prioridad está siendo atacado por una banda criminal que apunta a sus &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Los activos del cliente son valiosos, así que necesitamos mantenerlos seguros a toda costa, pero no voy a bromear: será un desafío enorme con estos matones decididos a causar daños reales. Si fuera yo, no dudaría en &lt;EM&gt;traer refuerzos&lt;/EM4&gt; para lidiar con ellos. No son ninguna broma, así que ofrecemos un merecido &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal que se encargue de estos tipos con éxito. Mucha suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
+        <v> Contrato de nivel rojo: Ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v/>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Contrato de nivel naranja: Defender ~misión(Objetos)</v>
-      </c>
-    </row>
-    <row r="433" xml:space="preserve">
-      <c r="A433" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espero que puedas brindar servicios de protección en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Uno de nuestros clientes de alta prioridad está teniendo serios problemas con una banda de forajidos que atacan su ~mission(Objects). Necesitamos poder mantener los activos lo más seguros e intactos posible. El cliente espera el servicio por el que paga, así que no lo arruines o podríamos perder un cliente leal. Por ahora, todavía estamos un poco a oscuras con respecto a estos forajidos, pero si logras resolver esto según los estándares de Foxwell, le ofreceremos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contratos.</v>
+        <v> Contrato de nivel amarillo: Emboscada a un aficionado</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v/>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Contrato de nivel rojo: Proteger ~misión(Objetos)</v>
-      </c>
-    </row>
-    <row r="435" xml:space="preserve">
-      <c r="A435" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acaba de llegar un contrato de emergencia sobre una banda de matones violentos que están causando estragos en la infraestructura de uno de nuestros clientes VIP. Si está disponible, necesitamos que acuda rápidamente a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y defienda los valiosos &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; del cliente a toda costa. Foxwell está muy al tanto de este grupo, así que créame cuando le digo que no hay que subestimar a estos pilotos. Le recomiendo encarecidamente que organice una &lt;EM&gt;fuerza de apoyo altamente competente&lt;/EM&gt; para que vuele con usted al lugar. Si logra sobrevivir al encuentro con la propiedad del cliente intacta, añadiremos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; a cualquier contratista principal lo suficientemente valiente como para aceptar este trabajo. Manténgase a salvo y buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
+        <v> Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v/>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Contrato de nivel amarillo: Defender ~misión(Objetos)</v>
+        <v> Contrato de nivel amarillo: Neutralizar a la banda de secuestradores de barcos</v>
       </c>
     </row>
     <row r="437" xml:space="preserve">
       <c r="A437" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Llamando a todos los pilotos: uno de nuestros clientes busca protección para sus &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;, ubicados en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Por lo que hemos averiguado, los atacantes son un grupo de aspirantes a delincuentes que probablemente no se han dado cuenta del valor de los bienes que intentan destruir, solo causan estragos por diversión. Aun así, la propiedad del cliente es importante, por lo que debe mantenerse lo más intacta posible. Si se encargan de ellos según los estándares de Foxwell, ofrecemos &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve">Bien, esto podría ser un poco complicado de hacer solo, así que si tienes algún favor que pedir, sería bueno cobrarlo ahora. Hay un grupo de forajidos atacando naves de reparto en este sector y nos han encargado eliminarlos. Cuando tu tripulación esté lista, dirígete a ~mission(Location|Address) y acaba con los enemigos de allí. Estos desgraciados son bastante listos, así que tienden a dividirse en grupos más pequeños. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Contrato de nivel rojo: Defender ~misión(Objetos)</v>
+        <v> Contrato de nivel naranja: Eliminar flota criminal</v>
       </c>
     </row>
     <row r="439" xml:space="preserve">
       <c r="A439" t="str" xml:space="preserve">
-        <v xml:space="preserve">Se necesita apoyo urgente para el barco en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Una conocida organización criminal destructiva ha estado tanteando el terreno con la propiedad de uno de nuestros clientes durante meses, y ahora ha causado estragos atacando los &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; del cliente. Estos activos son muy valiosos, por lo que debemos mantenerlos a salvo a toda costa, aunque sabemos que no será tarea fácil. No puedo enfatizar lo suficiente lo peligrosos que son estos individuos, así que no dudaría en &lt;EM&gt;traer refuerzos&lt;/EM&gt; para lidiar con ellos. Si usted y los activos salen ilesos, ofrecemos un merecido &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Mucha suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve">Parece que un par de pandillas de poca monta han decidido unir fuerzas y comenzar a realizar ataques coordinados. Por separado no eran gran cosa, pero juntas están demostrando ser una seria amenaza que hay que neutralizar. Recluta refuerzos de confianza y vuela a ~misión(Ubicación|Dirección). Una vez que ataques a los primeros miembros de la pandilla que encuentres allí, los otros grupos llegarán para apoyarlos. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada y con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Contrato de nivel amarillo: Defender ~mission(DefendLocationWrapperLocation)</v>
+        <v> Contrato de nivel naranja: Destruir la amenaza de los forajidos</v>
       </c>
     </row>
     <row r="441" xml:space="preserve">
       <c r="A441" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Las naves que entran y salen de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; están siendo atacadas por fuerzas hostiles. La gente de allí nos ha contratado para solucionar este problema de inmediato. Necesitamos a alguien que llegue pronto y empiece a combatir estas naves. La situación parece estar en constante evolución, así que te mantendré informado sobre dónde se te necesita más. Por el esfuerzo y la diligencia, también pagaremos una bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal por encargarse de esto. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
+        <v xml:space="preserve">Un grupo disidente de forajidos se ha separado de una de las principales bandas del sistema y está intentando actuar por su cuenta. Por la cantidad de problemas que han causado, es evidente que buscan hacerse un nombre cuanto antes. Dependerá de ti y de tu equipo detenerlos. Cuando tu equipo esté listo, dirígete a ~mission(Location|Address) y enfréntate a la banda. No todos estarán esperando allí. Espera refuerzos una vez que comiences el asalto. Asegúrate de quedarte hasta que te hayas encargado de todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. "Seguridad a tu manera". Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v> Contrato de Nivel Naranja: Proteja los intereses de nuestros clientes.</v>
+        <v> Contrato de nivel amarillo: Clear Shipjacking Group</v>
       </c>
     </row>
     <row r="443" xml:space="preserve">
       <c r="A443" t="str" xml:space="preserve">
-        <v xml:space="preserve">La gente de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; está bajo ataque y necesita nuestro apoyo. Sus naves en la zona están siendo atacadas y existe una creciente preocupación de que esto sea solo el preludio de algo más grande. La situación está evolucionando, pero estoy recibiendo actualizaciones constantes sobre lo que está sucediendo y te mantendré informado a medida que avance el contrato. ¿Estás disponible para ayudarlos? Sería inteligente reclutar a algunos amigos para que ayuden. Son clientes importantes y no podemos permitirnos fallarles. El contratista principal ganará un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; si completas el trabajo. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contrato.</v>
+        <v xml:space="preserve">Hay un pequeño grupo de criminales que han estado marcando su territorio, atacando a cualquier carguero que se acerque lo suficiente. Sin embargo, se volvieron un poco codiciosos, porque ahora alguien nos está pagando para que nos encarguemos de ellos. Una vez que usted y quien lo acompañe estén listos, diríjase a ~mission(Location|Address) y enfréntese a estos criminales. Como les gusta volar en grupos separados, asegúrese de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Contrato de nivel naranja: Se requiere protección para el buque.</v>
+        <v> SE NECESITA MENSAJERO DE NIVEL INICIAL EN NYX</v>
       </c>
     </row>
     <row r="445" xml:space="preserve">
       <c r="A445" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tenemos clientes que reportan ataques de forajidos a barcos alrededor de &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt;. Están completamente bloqueados y cualquiera que entre o salga es un objetivo. Cualquier intento de resolver el problema solo ha sido recibido con más refuerzos de forajidos. El cliente está desesperado por una solución, así que estamos contratando a un contratista para que vaya y restablezca la paz en el área. Si surge algún otro problema una vez que estés allí, te comunicaré las instrucciones sobre cómo ayudar. Realmente necesitamos a alguien rápido. Así que para hacer la oferta más atractiva, el contratista principal también recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve">CONTRATO FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** FTL requiere un mensajero de nivel inicial para realizar entregas en Nyx. El mensajero debe contar con su propio transporte. Se prefiere experiencia previa en levantamiento manual de cargas, con la capacidad de mover cajas de hasta 0.25 SCU de peso. Al aceptar este contrato, usted acepta asumir la responsabilidad total de la seguridad de los paquetes asignados. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v xml:space="preserve">Contrato de nivel rojo: Soporte a clientes VIP</v>
+        <v> SE NECESITA MENSAJERO DE NIVEL INICIAL EN STANTON</v>
       </c>
     </row>
     <row r="447" xml:space="preserve">
       <c r="A447" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Buscamos un profesional consumado para manejar un trabajo de alto riesgo. Tenemos clientes VIP en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; que se enfrentan a forajidos extremadamente agresivos y motivados que atacan naves alrededor de su ubicación. Los detalles exactos del ataque aún están llegando, pero parece ser una operación amplia y multifacética. Si está disponible, le recomiendo encarecidamente que traiga naves de apoyo de combate adicionales, muchos suministros y su mejor desempeño. Si lo hace bien, recompensaremos al contratista principal con un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve"> CONTRATO DE FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** Se necesita un mensajero confiable y trabajador de nivel inicial para realizar una entrega en Stanton. Usted será responsable de su propio transporte. Los contratistas interesados deben tener la capacidad de levantar cajas de hasta 0.25 SCU. Los contratistas son empleados de forma independiente y, por lo tanto, no están cubiertos por el seguro de la empresa FTL. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Contrato de nivel amarillo: Enfréntate a los agresores</v>
+        <v> SE NECESITA MENSAJERO DE NIVEL JUNIOR EN STANTON</v>
       </c>
     </row>
     <row r="449" xml:space="preserve">
       <c r="A449" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Naves no autorizadas están acosando a cualquiera que intente aterrizar o salir de las operaciones de nuestro cliente en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt;. Necesitamos a alguien que vuele hasta allí para defender el sitio y proteger las naves de nuestro cliente antes de que la situación se salga de control. Llega allí, persigue a esos agresores y te mantendré informado sobre la situación. Ayuda a solucionar esto y le pasaremos un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
+        <v xml:space="preserve">CONTRATO FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** Se necesita mensajero de nivel junior para entregas en todo el Sistema Stanton. El transporte debe ser proporcionado por el mensajero. Deberá levantar hasta 0.25 SCU de peso. Los mensajeros son responsables del manejo correcto y la seguridad de todos los paquetes a su cargo. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v> Contrato de nivel rojo: Salvar naves en ~mission(DefendLocationWrapperLocation)</v>
+        <v> Juego de guerra de Idris</v>
       </c>
     </row>
     <row r="451" xml:space="preserve">
       <c r="A451" t="str" xml:space="preserve">
-        <v xml:space="preserve">Se necesita apoyo naval en &lt;EM4&gt;~mission(DefendLocationWrapperLocation|Address)&lt;/EM4&gt; inmediatamente. Los intereses de nuestro cliente en la zona están siendo atacados ferozmente por fuerzas ilegales. Buscamos a alguien que pueda recoger su equipo, algunos barcos de apoyo de confianza y desplegarlos antes de que sea demasiado tarde. Una vez que llegues, te enviaré cualquier actualización de la situación. No lo estropees. Estos clientes están pagando y esperan protección de primer nivel. Si algo sale mal, podríamos perder este contrato. Por eso, le daremos al contratista principal un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; si todo sale a la perfección. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve"> Para poner a prueba la preparación de nuestros equipos de respuesta, solicitamos voluntarios que simulen un asalto contra un Idris de la CDF, neutralizando y tomando el control de la embarcación. Es importante aclarar que el objetivo del ejercicio no es destruir el Idris, sino abordarlo y mantener el control el mayor tiempo posible. Los voluntarios deben esperar una fuerte resistencia por parte de la tripulación altamente entrenada del Idris y se les recomienda obtener una imagen actualizada con anticipación. Las coordenadas se proporcionarán una vez confirmada su participación. Gracias y buena suerte.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Contrato de nivel amarillo: Barco bajo ataque</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="str">
-        <v> Contrato de nivel amarillo: Barco bajo ataque</v>
+        <v> Perezoso</v>
+      </c>
+    </row>
+    <row r="453" xml:space="preserve">
+      <c r="A453" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los Headhunters le prestaron créditos recientemente a ~mission(TargetName) bajo ciertas condiciones. Específicamente, páguenos o lo mataremos. Es increíble pensar que eso no fue suficiente incentivo, pero aquí estamos, después de la fecha límite de pago. Ahora, por mucho que apreciemos a ~mission(TargetName|First), necesito que cumpla nuestra promesa. ~mission(TargetName|Last) fue visto por última vez en ~mission(Location|Address). Rastrea a ese tipo, hazlo desaparecer y cobra. Es así de simple. Se esconde.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v> Contrato de nivel rojo: El barco está bajo ataque.</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="str">
-        <v> Contrato de nivel rojo: El barco está bajo ataque.</v>
+        <v> Vencido</v>
+      </c>
+    </row>
+    <row r="455" xml:space="preserve">
+      <c r="A455" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Se acabó el tiempo para la misión (Nombre del objetivo). Los Skav tienen un retraso considerable en el pago a los Cazadores de cabezas, así que necesito que los elimines. Mátalos, no los golpees, por si no queda claro. Alguien vio recientemente a la misión (Apellido del objetivo) cerca de la ubicación (Dirección), así que dirígete allí y elimínalos. Aviso importante: hemos recibido informes de que usaron parte de nuestros créditos para contratar protección adicional. Prepárate. Se esconde.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v> Contrato de nivel naranja: ~misión (nave) necesita asistencia</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="str">
-        <v> Contrato de nivel naranja: ~misión (nave) necesita asistencia</v>
+        <v> Aviso de cobro</v>
+      </c>
+    </row>
+    <row r="457" xml:space="preserve">
+      <c r="A457" t="str" xml:space="preserve">
+        <v xml:space="preserve">~mission(TargetName) tomó prestados varios créditos de los Headhunters y pensó que lo más inteligente era intentar esconderse en lugar de devolvernos el dinero, así que necesito que alguien haga un escarmiento a ~mission(TargetName|Last). Acaban de ser vistos en ~mission(Location|Address), así que recomiendo ir allí ahora antes de que se pierda el rastro. ~mission(TargetName|Last) es una persona paranoica, así que no te sorprendas si no está solo. Haz lo que quieras, siempre y cuando ~mission(TargetName|Last) sea polvo cuando termines. Se esconde.</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v> Desmantelan una nueva operación antidrogas.</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="str">
-        <v> Desmantelan una nueva operación antidrogas.</v>
+        <v> Ataque preventivo</v>
+      </c>
+    </row>
+    <row r="459" xml:space="preserve">
+      <c r="A459" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los Headhunters recibieron información de que se está preparando una operación XenoThreat dirigida contra uno de nuestros equipos. No tenemos detalles precisos sobre el plan, pero sabemos que ~mission(TargetName) lo está organizando. En lugar de quedarnos de brazos cruzados esperando a que algo suceda, hemos decidido actuar de forma proactiva. ~mission(TargetName|Last) acaba de ser visto con otros cerca de ~mission(Location|Address). No podemos movilizar a nadie lo suficientemente rápido para que lleguen allí. Quiero que vayas corriendo y lances un ataque preventivo. Stows out.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v> Destruir drogas peligrosas</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="str">
-        <v> Destruir drogas peligrosas</v>
+        <v> Venganza</v>
+      </c>
+    </row>
+    <row r="461" xml:space="preserve">
+      <c r="A461" t="str" xml:space="preserve">
+        <v xml:space="preserve">XenoThreat atacó recientemente un bastión de Headhunters. Les ahorraré los detalles, pero le hicieron algo realmente atroz a nuestro equipo. Hemos identificado al líder de la operación como ~mission(TargetName) y buscamos venganza. No nos importa lo que hagan para lograrlo. Solo que ~mission(TargetName|Last) esté muerto. Una fuente nos acaba de decir que pueden rastrear a este canalla de XenoThreat en ~mission(Location|Address). Este enfermo es un profesional y nunca viaja solo, así que no esperen que eliminarlo sea pan comido. Se esconde.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v> Destruir las drogas ilegales</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v> Destruir las drogas ilegales</v>
+        <v> Justicia exacta</v>
+      </c>
+    </row>
+    <row r="463" xml:space="preserve">
+      <c r="A463" t="str" xml:space="preserve">
+        <v xml:space="preserve">Recientemente se reveló que ~mission(TargetName) era un topo de XenoThreat. Ahora todo tiene sentido porque el skav era un verdadero cabrón. Desafortunadamente, se separaron antes de que pudiéramos encargarnos nosotros mismos. Basándonos en todo lo que aprendieron sobre nuestras operaciones, necesitamos eliminarlos cuanto antes. Si nos ven venir, simplemente volverán a huir, pero pensé que alguien como tú tiene más posibilidades de acercarse lo suficiente para un disparo mortal. Acabamos de enterarnos de que ~mission(TargetName|Last) andaba por ~mission(Location|Address). Parece que también hay otras naves protegiéndolos. ¿Crees que tienes la habilidad para librar al universo de un bastardo traidor y sus amigos bastardos? Esconderse.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v> Ayuda a proteger el sitio.</v>
+        <v> Una pequeña represalia</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v> Ayuda a proteger el sitio.</v>
+        <v/>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v> Limpie cuidadosamente el sitio</v>
+        <v> Eliminando algo de basura XenoThreat</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v> Limpie cuidadosamente el sitio</v>
+        <v/>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v> Contrato de nivel amarillo: Merc Work</v>
+        <v> Expulsando a CFP</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v> Contrato de nivel amarillo: Merc Work</v>
+        <v/>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v> Contrato de nivel amarillo: Despeje de la PAF</v>
+        <v> Limpiar y despejar algunos lugares frecuentados por CFP</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v> Contrato de nivel amarillo: Despeje de la PAF</v>
+        <v/>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v> Barrer y despejar la ubicación</v>
+        <v> Tomando el territorio de XenoThreat</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v> Barrer y despejar la ubicación</v>
+        <v/>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v> Ataque de precisión en ~misión(Nombre del objetivo)</v>
+        <v> Golpea un complejo CFP</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v> Ataque de precisión en ~misión(Nombre del objetivo)</v>
+        <v/>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v> Localizar ~misión(Nombre del objetivo)</v>
+        <v> Desmantelando un escondite de XenoThreat</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v> Localizar ~misión(Nombre del objetivo)</v>
+        <v/>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v> Contrato de nivel rojo: Recuperar cargamento</v>
+        <v> Es hora de empezar con CFP</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Contrato de nivel rojo: Recuperar cargamento</v>
+        <v/>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v> Contrato de nivel rojo: Recuperar el cargamento robado</v>
+        <v> ¡A la carga!</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v> Contrato de nivel rojo: Recuperar el cargamento robado</v>
+        <v/>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v> Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
+        <v>Golpear en el comando XenoThreat</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v> Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
+        <v/>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v> Nuevas y emocionantes oportunidades con Foxwell Enforcement</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="str">
-        <v> Nuevas y emocionantes oportunidades con Foxwell Enforcement</v>
+        <v> Eliminar a los espías</v>
+      </c>
+    </row>
+    <row r="485" xml:space="preserve">
+      <c r="A485" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Algún imbécil está intentando desenterrar trapos sucios de los Headhunters. Se desplegaron algunos centinelas orbitales en ~mission(location|address) para espiarnos. También hemos visto una nave vigilándolos. Una propuesta sencilla para ti: ve a eliminar a los centinelas y te pagaremos por ello. ¿Te interesa? En cuanto a la nave, puedes hacer lo que quieras con ella, pero si te detecta, no te sorprendas si intenta buscar refuerzos. Así son estas cosas. Se esconde.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v> ¿Sigues buscando trabajo?</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="str">
-        <v> ¿Sigues buscando trabajo?</v>
+        <v> Exterminar a los espías</v>
+      </c>
+    </row>
+    <row r="487" xml:space="preserve">
+      <c r="A487" t="str" xml:space="preserve">
+        <v xml:space="preserve">Algunos idiotas creen que pueden espiar descaradamente a los Headhunters y salirse con la suya. Han instalado varios centinelas orbitales en ~mission(location|address) y tienen algunas naves patrullando la zona. No sabemos quién está detrás de esto, pero sinceramente no nos importa. Solo necesitamos que desaparezcan. Avísanos si te apetece poner en su sitio a esos descarados. Te pagaremos bien y te daremos los créditos en cuanto termines el trabajo. Ten en cuenta que solo nos preocupan los centinelas. Las naves que tienen patrullando solo son un problema si se interponen en tu camino o si intentan llamar a algunos amigos para detenerte.</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v> Contrato de nivel amarillo: Inspección de seguridad</v>
+        <v> Borrar espía</v>
       </c>
     </row>
     <row r="489" xml:space="preserve">
       <c r="A489" t="str" xml:space="preserve">
-        <v xml:space="preserve">Necesitas a alguien para eliminar una patrulla de seguridad. Tendrás que ir al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en tu HUD y luego escanear varios puntos de ruta designados asegurándote de que sean seguros. Los satélites en esa región han estado fallando últimamente. No estoy seguro de qué está pasando allí, pero es mejor estar preparado en caso de que haya algún problema. Completa este contrato y el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(ScripAmount) MG Scrip.&lt;/EM4&gt; Buena suerte, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contrato.</v>
+        <v xml:space="preserve"> Tenemos un pequeño problema que los Headhunters deben solucionar. Hay una torreta orbital en ~mission(location|address) que algún pequeño alborotador instaló para espiar nuestras operaciones. ¿Quieres ganar algo de dinero fácil y volarla por nosotros? ¡Adelante!</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v> Contrato de nivel naranja: amenaza potencial para la seguridad</v>
+        <v> Erradicar a los espías</v>
       </c>
     </row>
     <row r="491" xml:space="preserve">
       <c r="A491" t="str" xml:space="preserve">
-        <v xml:space="preserve">Se han avistado varios barcos desconocidos en zonas frecuentadas por transportistas que entregan mercancías para nuestro cliente. Les preocupa que estos barcos estén vigilando a sus transportistas para preparar una emboscada, por lo que nos han contratado para patrullar la zona. Empiece por ir al marcador de ubicación en su HUD y escanéelo para asegurarse de que no haya peligro. Después, le enviaremos a otras zonas para que busque posibles amenazas. Le recomendamos que traiga un compañero y suficientes suministros para estar preparado para cualquier eventualidad. Tenga en cuenta también que completar con éxito este contrato le reportará al contratista principal una bonificación de ~misión(Cantidad de Scrip) MG Scrip. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve">Los Headhunters buscan un mercenario para que nos ayude con un poco de limpieza. Descubrimos que alguien está intentando espiarnos en ~mission(location|address). No podemos permitirlo. Necesitamos un operador experto para que se encargue de los centinelas orbitales que desplegaron allí y, si es necesario, de cualquier nave que se interponga en tu camino. Parece una operación bien organizada, así que conseguirla puede no ser fácil, pero seguro que será divertido. Avísanos si eres el indicado. Los créditos se transferirán una vez que nuestros escaneos confirmen que se ha ido. Se esconde.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Contrato de nivel naranja: Patrulla de seguridad</v>
-      </c>
-    </row>
-    <row r="493" xml:space="preserve">
-      <c r="A493" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Un cliente está preocupado por la actividad cerca de algunos de sus intereses. Hemos sido contratados para patrullar el área y realizar escaneos en varias ubicaciones. ¿Interesado? Si es así, diríjase al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en su HUD para comenzar el patrullaje. El cliente no especificó las amenazas, pero no cree que todo sea del todo correcto. Esperamos poder brindarle algo de tranquilidad. Además, el cliente acordó que ofrezcamos un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contrato.</v>
+        <v> Recuperemos Carvers Ridge</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v/>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v> Contrato de Nivel Rojo: Asegurar el Espacio Amenazado</v>
-      </c>
-    </row>
-    <row r="495" xml:space="preserve">
-      <c r="A495" t="str" xml:space="preserve">
-        <v xml:space="preserve">Necesitamos un piloto experimentado para una patrulla importante. Un cliente importante está harto de que los forajidos ataquen sus naves y satélites. Nos han contratado para escanear las áreas en cuestión y lidiar con las fuerzas hostiles. La patrulla comienza en el marcador de ubicación &lt;EM4&gt; en tu HUD antes de dirigirnos a otras ubicaciones que esperamos que despejes. No sabemos con qué te encontrarás, pero según la información compartida por el cliente, frecuentemente ven grupos de cazas de cinco a siete naves patrullando la región. Algunos incluso tienen naves más grandes liderando el ataque. Eso significa que más te vale estar preparado para una dura batalla. Si puedes, intenta reclutar al menos a &lt;EM4&gt;tres amigos&lt;/EM4&gt; para la causa. Incluso un piloto experimentado necesitará toda la ayuda posible contra esta tripulación. Dado que esta va a ser una misión difícil, el contratista principal recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al final de la patrulla. Buena suerte, Kevin Walton, Despachador de Foxwell Enforcement. «Seguridad a tu medida». Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
+        <v> Concentración en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v/>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Contrato de nivel amarillo: Patrullaje de rutina</v>
-      </c>
-    </row>
-    <row r="497" xml:space="preserve">
-      <c r="A497" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Es hora de realizar una patrulla de rutina para uno de nuestros clientes de larga data. La ruta es una serie de puntos de referencia que deben visitarse y escanearse para confirmar que todo esté como se espera. Debería ser bastante simple. Si está interesado, acepte y diríjase al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en su HUD para comenzar. Si lo logra, el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(ScripAmount) MG Scrip.&lt;/EM4&gt; Buena suerte, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
+        <v> El centro de la ciudad está bajo ataque.</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v/>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v> Contrato de nivel rojo: Patrulla de seguridad de alto riesgo</v>
-      </c>
-    </row>
-    <row r="499" xml:space="preserve">
-      <c r="A499" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un cliente necesita nuestra ayuda. Forajidos están merodeando por ciertos sectores donde hacen negocios y atacando a cualquiera que se cruce en su camino. Nuestro cliente ya ha perdido varias naves y no puede permitirse perder más. Necesitamos a alguien que patrulle esas áreas y atraiga a cualquier fuerza hostil. El trabajo comienza con usted dirigiéndose al marcador de ubicación &lt;EM4&gt; en su HUD y escaneando. Luego compartiremos algunos otros puntos de patrulla para que los escanee. Por lo que parece, estos grupos de naves cuentan con pilotos hábiles y agresivos. Mejor prepárese para la pelea si se encuentra con alguno de ellos. Sería bueno tener al menos &lt;EM4&gt;dos pilotos de confianza&lt;/EM4&gt; a su lado para esto. Al final de una patrulla exitosa, el contratista principal recibirá un pago de bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Manténgase frío, Kevin Walton Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
+        <v> No dejes que caiga la caída del viento</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v/>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Contrato de nivel amarillo: Ataque sorpresa</v>
+        <v> Detengamos la expansión de la amenaza alienígena</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v> Contrato de nivel amarillo: Ataque sorpresa</v>
+        <v/>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v> Contrato de nivel naranja: Devuelve el favor</v>
+        <v> Se necesitan refuerzos en el puesto de avanzada.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v> Contrato de nivel naranja: Devuelve el favor</v>
+        <v/>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v> Contrato de nivel naranja: Tender una trampa</v>
+        <v> Bloquear la expansión de XenoThreat</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v> Contrato de nivel naranja: Tender una trampa</v>
+        <v/>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v> Contrato de nivel rojo: Ataque sorpresa</v>
+        <v> Brindar protección en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v> Contrato de nivel rojo: Ataque sorpresa</v>
+        <v/>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v> Contrato de nivel amarillo: Emboscada a un aficionado</v>
+        <v> Detén el ataque rival en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v> Contrato de nivel amarillo: Emboscada a un aficionado</v>
+        <v/>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v> Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
+        <v> Asegurar la misión (ubicación) de los advenedizos</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v> Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
+        <v/>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v> Contrato de nivel amarillo: Neutralizar a la banda de secuestradores de barcos</v>
-      </c>
-    </row>
-    <row r="513" xml:space="preserve">
-      <c r="A513" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bien, esto podría ser un poco complicado de hacer solo, así que si tienes algún favor que pedir, sería bueno cobrarlo ahora. Hay un grupo de forajidos atacando naves de reparto en este sector y nos han encargado eliminarlos. Cuando tu tripulación esté lista, dirígete a ~mission(Location|Address) y acaba con los enemigos de allí. Estos desgraciados son bastante listos, así que tienden a dividirse en grupos más pequeños. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
+        <v> Guardia ~misión(Ubicación) De Rivales</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v/>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v> Contrato de nivel naranja: Eliminar flota criminal</v>
-      </c>
-    </row>
-    <row r="515" xml:space="preserve">
-      <c r="A515" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parece que un par de pandillas de poca monta han decidido unir fuerzas y comenzar a realizar ataques coordinados. Por separado no eran gran cosa, pero juntas están demostrando ser una seria amenaza que hay que neutralizar. Recluta refuerzos de confianza y vuela a ~misión(Ubicación|Dirección). Una vez que ataques a los primeros miembros de la pandilla que encuentres allí, los otros grupos llegarán para apoyarlos. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada y con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
+        <v>Mantén ~misión(ubicación) a salvo</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v/>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v> Contrato de nivel naranja: Destruir la amenaza de los forajidos</v>
-      </c>
-    </row>
-    <row r="517" xml:space="preserve">
-      <c r="A517" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un grupo disidente de forajidos se ha separado de una de las principales bandas del sistema y está intentando actuar por su cuenta. Por la cantidad de problemas que han causado, es evidente que buscan hacerse un nombre cuanto antes. Dependerá de ti y de tu equipo detenerlos. Cuando tu equipo esté listo, dirígete a ~mission(Location|Address) y enfréntate a la banda. No todos estarán esperando allí. Espera refuerzos una vez que comiences el asalto. Asegúrate de quedarte hasta que te hayas encargado de todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. "Seguridad a tu manera". Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
+        <v> Defender ~misión(Ubicación) de los mercenarios</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v/>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v> Contrato de nivel amarillo: Clear Shipjacking Group</v>
-      </c>
-    </row>
-    <row r="519" xml:space="preserve">
-      <c r="A519" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hay un pequeño grupo de criminales que han estado marcando su territorio, atacando a cualquier carguero que se acerque lo suficiente. Sin embargo, se volvieron un poco codiciosos, porque ahora alguien nos está pagando para que nos encarguemos de ellos. Una vez que usted y quien lo acompañe estén listos, diríjase a ~mission(Location|Address) y enfréntese a estos criminales. Como les gusta volar en grupos separados, asegúrese de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
+        <v> Necesitamos un bateador</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v/>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v> SE NECESITA MENSAJERO DE NIVEL INICIAL EN NYX</v>
+        <v> Una rápida represalia</v>
       </c>
     </row>
     <row r="521" xml:space="preserve">
       <c r="A521" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** FTL requiere un mensajero de nivel inicial para realizar entregas en Nyx. El mensajero debe contar con su propio transporte. Se prefiere experiencia previa en levantamiento manual de cargas, con la capacidad de mover cajas de hasta 0.25 SCU de peso. Al aceptar este contrato, usted acepta asumir la responsabilidad total de la seguridad de los paquetes asignados. ~mission(Contractor|SignOff)</v>
+        <v xml:space="preserve"> Oye, unos matones de poca monta se han atrincherado en ~mission(Location|Address). No les prestaríamos atención si no fuera porque esos arrogantes intentaron atacar un puesto de avanzada bajo nuestra protección. Los ahuyentamos sin mayores problemas, pero no podemos dejar que semejante falta de respeto quede impune. Nuestros agentes están ocupados con asuntos más importantes, así que nos gustaría que te encargaras de esto. ¡No te lo pierdas!</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v> SE NECESITA MENSAJERO DE NIVEL INICIAL EN STANTON</v>
-      </c>
-    </row>
-    <row r="523" xml:space="preserve">
-      <c r="A523" t="str" xml:space="preserve">
-        <v xml:space="preserve"> CONTRATO DE FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** Se necesita un mensajero confiable y trabajador de nivel inicial para realizar una entrega en Stanton. Usted será responsable de su propio transporte. Los contratistas interesados deben tener la capacidad de levantar cajas de hasta 0.25 SCU. Los contratistas son empleados de forma independiente y, por lo tanto, no están cubiertos por el seguro de la empresa FTL. ~mission(Contractor|SignOff)</v>
+        <v> Visitar un sitio CFP</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v/>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v> SE NECESITA MENSAJERO DE NIVEL JUNIOR EN STANTON</v>
-      </c>
-    </row>
-    <row r="525" xml:space="preserve">
-      <c r="A525" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO FTL DISPONIBLE PARA ASIGNACIÓN INMEDIATA **DETALLES DEL CONTRATO** Se necesita mensajero de nivel junior para entregas en todo el Sistema Stanton. El transporte debe ser proporcionado por el mensajero. Deberá levantar hasta 0.25 SCU de peso. Los mensajeros son responsables del manejo correcto y la seguridad de todos los paquetes a su cargo. ~mission(Contractor|SignOff)</v>
+        <v> Buscando un poco de venganza</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v/>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v> Juego de guerra de Idris</v>
-      </c>
-    </row>
-    <row r="527" xml:space="preserve">
-      <c r="A527" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Para poner a prueba la preparación de nuestros equipos de respuesta, solicitamos voluntarios que simulen un asalto contra un Idris de la CDF, neutralizando y tomando el control de la embarcación. Es importante aclarar que el objetivo del ejercicio no es destruir el Idris, sino abordarlo y mantener el control el mayor tiempo posible. Los voluntarios deben esperar una fuerte resistencia por parte de la tripulación altamente entrenada del Idris y se les recomienda obtener una imagen actualizada con anticipación. Las coordenadas se proporcionarán una vez confirmada su participación. Gracias y buena suerte.</v>
+        <v> Eliminar ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v/>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v> Perezoso</v>
+        <v> Gestión de la reputación</v>
       </c>
     </row>
     <row r="529" xml:space="preserve">
       <c r="A529" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Headhunters le prestaron créditos recientemente a ~mission(TargetName) bajo ciertas condiciones. Específicamente, páguenos o lo mataremos. Es increíble pensar que eso no fue suficiente incentivo, pero aquí estamos, después de la fecha límite de pago. Ahora, por mucho que apreciemos a ~mission(TargetName|First), necesito que cumpla nuestra promesa. ~mission(TargetName|Last) fue visto por última vez en ~mission(Location|Address). Rastrea a ese tipo, hazlo desaparecer y cobra. Es así de simple. Se esconde.</v>
+        <v xml:space="preserve">Unos cretinos se niegan a pagarnos lo que nos deben. El problema es que estos idiotas se jactan de ello. Si se hubieran callado, podríamos haber resuelto esto de forma más eficaz, pero ahora tenemos que dar un escarmiento. Estos imbéciles operan desde ~mission(Location|Address). Necesitamos que se vayan todos. ¡Que se oiga bien alto! Enviaremos el pago una vez que nos hayamos encargado de todos. - Se despide.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v> Vencido</v>
-      </c>
-    </row>
-    <row r="531" xml:space="preserve">
-      <c r="A531" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se acabó el tiempo para la misión (Nombre del objetivo). Los Skav tienen un retraso considerable en el pago a los Cazadores de cabezas, así que necesito que los elimines. Mátalos, no los golpees, por si no queda claro. Alguien vio recientemente a la misión (Apellido del objetivo) cerca de la ubicación (Dirección), así que dirígete allí y elimínalos. Aviso importante: hemos recibido informes de que usaron parte de nuestros créditos para contratar protección adicional. Prepárate. Se esconde.</v>
+        <v> Muerte y carga</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v/>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v> Aviso de cobro</v>
-      </c>
-    </row>
-    <row r="533" xml:space="preserve">
-      <c r="A533" t="str" xml:space="preserve">
-        <v xml:space="preserve">~mission(TargetName) tomó prestados varios créditos de los Headhunters y pensó que lo más inteligente era intentar esconderse en lugar de devolvernos el dinero, así que necesito que alguien haga un escarmiento a ~mission(TargetName|Last). Acaban de ser vistos en ~mission(Location|Address), así que recomiendo ir allí ahora antes de que se pierda el rastro. ~mission(TargetName|Last) es una persona paranoica, así que no te sorprendas si no está solo. Haz lo que quieras, siempre y cuando ~mission(TargetName|Last) sea polvo cuando termines. Se esconde.</v>
+        <v> Una tarea muy complicada</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v/>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v> Ataque preventivo</v>
-      </c>
-    </row>
-    <row r="535" xml:space="preserve">
-      <c r="A535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Headhunters recibieron información de que se está preparando una operación XenoThreat dirigida contra uno de nuestros equipos. No tenemos detalles precisos sobre el plan, pero sabemos que ~mission(TargetName) lo está organizando. En lugar de quedarnos de brazos cruzados esperando a que algo suceda, hemos decidido actuar de forma proactiva. ~mission(TargetName|Last) acaba de ser visto con otros cerca de ~mission(Location|Address). No podemos movilizar a nadie lo suficientemente rápido para que lleguen allí. Quiero que vayas corriendo y lances un ataque preventivo. Stows out.</v>
+        <v> Golpea a XenoThreat en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v/>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v> Venganza</v>
-      </c>
-    </row>
-    <row r="537" xml:space="preserve">
-      <c r="A537" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat atacó recientemente un bastión de Headhunters. Les ahorraré los detalles, pero le hicieron algo realmente atroz a nuestro equipo. Hemos identificado al líder de la operación como ~mission(TargetName) y buscamos venganza. No nos importa lo que hagan para lograrlo. Solo que ~mission(TargetName|Last) esté muerto. Una fuente nos acaba de decir que pueden rastrear a este canalla de XenoThreat en ~mission(Location|Address). Este enfermo es un profesional y nunca viaja solo, así que no esperen que eliminarlo sea pan comido. Se esconde.</v>
+        <v> Guerra territorial</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v/>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v> Justicia exacta</v>
-      </c>
-    </row>
-    <row r="539" xml:space="preserve">
-      <c r="A539" t="str" xml:space="preserve">
-        <v xml:space="preserve">Recientemente se reveló que ~mission(TargetName) era un topo de XenoThreat. Ahora todo tiene sentido porque el skav era un verdadero cabrón. Desafortunadamente, se separaron antes de que pudiéramos encargarnos nosotros mismos. Basándonos en todo lo que aprendieron sobre nuestras operaciones, necesitamos eliminarlos cuanto antes. Si nos ven venir, simplemente volverán a huir, pero pensé que alguien como tú tiene más posibilidades de acercarse lo suficiente para un disparo mortal. Acabamos de enterarnos de que ~mission(TargetName|Last) andaba por ~mission(Location|Address). Parece que también hay otras naves protegiéndolos. ¿Crees que tienes la habilidad para librar al universo de un bastardo traidor y sus amigos bastardos? Esconderse.</v>
+        <v> Luz verde en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v/>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v> Una pequeña represalia</v>
+        <v> Se necesita una muerte en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v> Una pequeña represalia</v>
+        <v/>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v> Eliminando algo de basura XenoThreat</v>
+        <v> Impacto en el espacio profundo</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v> Eliminando algo de basura XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v> Expulsando a CFP</v>
+        <v> Necesitas un bisturí en Carver's</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v> Expulsando a CFP</v>
+        <v/>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v> Limpiar y despejar algunos lugares frecuentados por CFP</v>
+        <v> Disparado en medio del caos</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v> Limpiar y despejar algunos lugares frecuentados por CFP</v>
+        <v/>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v> Tomando el territorio de XenoThreat</v>
+        <v> Objetivo pagado en CFP</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v> Tomando el territorio de XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v> Golpea un complejo CFP</v>
+        <v> Necesito que me quiten el CFP</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Golpea un complejo CFP</v>
+        <v/>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v> Desmantelando un escondite de XenoThreat</v>
+        <v> Tapón a un traidor</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v> Desmantelando un escondite de XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v> Es hora de empezar con CFP</v>
+        <v> Matad al rey</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v> Es hora de empezar con CFP</v>
+        <v/>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v> ¡A la carga!</v>
+        <v> Necesito que saquen a alguien.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v> ¡A la carga!</v>
+        <v/>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v> Golpear en el comando XenoThreat</v>
+        <v> Luz verde en ~misión(NombreObjetivo|Apellido)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v> Golpear en el comando XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v> Eliminar a los espías</v>
-      </c>
-    </row>
-    <row r="561" xml:space="preserve">
-      <c r="A561" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Algún imbécil está intentando desenterrar trapos sucios de los Headhunters. Se desplegaron algunos centinelas orbitales en ~mission(location|address) para espiarnos. También hemos visto una nave vigilándolos. Una propuesta sencilla para ti: ve a eliminar a los centinelas y te pagaremos por ello. ¿Te interesa? En cuanto a la nave, puedes hacer lo que quieras con ella, pero si te detecta, no te sorprendas si intenta buscar refuerzos. Así son estas cosas. Se esconde.</v>
+        <v> Necesitas un éxito en la Riviera</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v/>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v> Exterminar a los espías</v>
-      </c>
-    </row>
-    <row r="563" xml:space="preserve">
-      <c r="A563" t="str" xml:space="preserve">
-        <v xml:space="preserve">Algunos idiotas creen que pueden espiar descaradamente a los Headhunters y salirse con la suya. Han instalado varios centinelas orbitales en ~mission(location|address) y tienen algunas naves patrullando la zona. No sabemos quién está detrás de esto, pero sinceramente no nos importa. Solo necesitamos que desaparezcan. Avísanos si te apetece poner en su sitio a esos descarados. Te pagaremos bien y te daremos los créditos en cuanto termines el trabajo. Ten en cuenta que solo nos preocupan los centinelas. Las naves que tienen patrullando solo son un problema si se interponen en tu camino o si intentan llamar a algunos amigos para detenerte.</v>
+        <v> Golpe a XenoThreat en el Yard</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v/>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v> Borrar espía</v>
+        <v xml:space="preserve">Listos para la retribución</v>
       </c>
     </row>
     <row r="565" xml:space="preserve">
       <c r="A565" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Tenemos un pequeño problema que los Headhunters deben solucionar. Hay una torreta orbital en ~mission(location|address) que algún pequeño alborotador instaló para espiar nuestras operaciones. ¿Quieres ganar algo de dinero fácil y volarla por nosotros? ¡Adelante!</v>
+        <v xml:space="preserve"> Me acaba de caer información interesante. Parece que el infame líder de XenoThreat, ~mission(TargetName), está escondido en ~mission(location|address) trabajando en una gran operación para ellos. Oportunidad perfecta para acabar con ese cabrón de una vez por todas. El problema es que los Xenos están vigilando todas las operaciones de Headhunter en este momento. No hay forma de que podamos movilizar y desplegar un equipo sin que ~mission(TargetName|Last) se entere. Así que te ofrezco la oportunidad de mejorar Pyro y ganar algo de crédito al mismo tiempo. Si te interesa, te sugiero que te equipes y busques refuerzos antes de salir. Solo te pagarán si eliminas a ~mission(TargetName|Last), pero no dudes en matar a cualquier otro XenoThug que pueda estar escondido allí con ellos. ¡Que se vayan!</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v> Erradicar a los espías</v>
-      </c>
-    </row>
-    <row r="567" xml:space="preserve">
-      <c r="A567" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Headhunters buscan un mercenario para que nos ayude con un poco de limpieza. Descubrimos que alguien está intentando espiarnos en ~mission(location|address). No podemos permitirlo. Necesitamos un operador experto para que se encargue de los centinelas orbitales que desplegaron allí y, si es necesario, de cualquier nave que se interponga en tu camino. Parece una operación bien organizada, así que conseguirla puede no ser fácil, pero seguro que será divertido. Avísanos si eres el indicado. Los créditos se transferirán una vez que nuestros escaneos confirmen que se ha ido. Se esconde.</v>
+        <v> Cabeza de la serpiente</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v/>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v> Recuperemos Carvers Ridge</v>
+        <v> El teniente de XenoThreat necesita que lo maten.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v> Recuperemos Carvers Ridge</v>
+        <v/>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v> Concentración en ~misión(Ubicación)</v>
+        <v> Lanza una amenaza xeno</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v> Concentración en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v> El centro de la ciudad está bajo ataque.</v>
+        <v> Se busca: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v> El centro de la ciudad está bajo ataque.</v>
+        <v/>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v> No dejes que caiga la caída del viento</v>
+        <v> Eliminación de objetivo para una vía rápida en</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v> No dejes que caiga la caída del viento</v>
+        <v/>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v> Detengamos la expansión de la amenaza alienígena</v>
+        <v xml:space="preserve">Objetivo en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v> Detengamos la expansión de la amenaza alienígena</v>
+        <v/>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v> Se necesitan refuerzos en el puesto de avanzada.</v>
+        <v> Orden de matar</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v> Se necesitan refuerzos en el puesto de avanzada.</v>
+        <v/>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v> Bloquear la expansión de XenoThreat</v>
+        <v> Choca contra un barco de CFP</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v> Bloquear la expansión de XenoThreat</v>
+        <v/>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Brindar protección en ~misión(Ubicación)</v>
+        <v> Objetivo Primo</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v> Brindar protección en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v> Detén el ataque rival en ~misión(Ubicación)</v>
+        <v> Se busca: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v> Detén el ataque rival en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v> Asegurar la misión (ubicación) de los advenedizos</v>
+        <v> Un golpe sencillo</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v> Asegurar la misión (ubicación) de los advenedizos</v>
+        <v/>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v> Guardia ~misión(Ubicación) De Rivales</v>
+        <v> Regálate una pelea</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v> Guardia ~misión(Ubicación) De Rivales</v>
+        <v/>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v> Mantén ~misión(ubicación) a salvo</v>
+        <v> ¿Quieres ser cazatalentos?</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v> Mantén ~misión(ubicación) a salvo</v>
+        <v/>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v> Defender ~misión(Ubicación) de los mercenarios</v>
+        <v> Fantasma de XenoTrash</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v> Defender ~misión(Ubicación) de los mercenarios</v>
+        <v/>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v> Necesitamos un bateador</v>
+        <v> Choquen algunos barcos</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v> Necesitamos un bateador</v>
+        <v/>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v> Una rápida represalia</v>
+        <v> Iniciativa Overdrive: OBJETIVOS PRIORITARIOS</v>
       </c>
     </row>
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Oye, unos matones de poca monta se han atrincherado en ~mission(Location|Address). No les prestaríamos atención si no fuera porque esos arrogantes intentaron atacar un puesto de avanzada bajo nuestra protección. Los ahuyentamos sin mayores problemas, pero no podemos dejar que semejante falta de respeto quede impune. Nuestros agentes están ocupados con asuntos más importantes, así que nos gustaría que te encargaras de esto. ¡No te lo pierdas!</v>
+        <v xml:space="preserve"> Nuestros analistas han examinado la información incautada a los equipos de reconocimiento de XenoThreat, pero los datos parecen estar protegidos por un sofisticado sistema de cifrado y requieren una clave criptográfica personalizada para acceder a ellos. Hemos logrado localizar a varios tenientes de XenoThreat que operan en el sistema; su misión es encontrar e interrogar a los sospechosos para determinar si poseen una clave criptográfica que nos permita acceder a la información. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de las Fuerzas de Defensa de Canadá que lleven esta iniciativa hasta el final.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v> Visitar un sitio CFP</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="str">
-        <v> Visitar un sitio CFP</v>
+        <v> Iniciativa Overdrive: VIGILANCIA DE AMENAZAS XENOTRAS</v>
+      </c>
+    </row>
+    <row r="599" xml:space="preserve">
+      <c r="A599" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de los sospechosos capturados durante los recientes ataques reveló que XenoThreat busca acceder remotamente a varias antenas de comunicación en todo el sistema. Que XenoThreat esté interceptando las comunicaciones es extremadamente peligroso para la población local, por lo que se ha solicitado a la CDF que reinicie la antena de comunicación y la defienda de cualquier Vanguardia de XenoThreat que intente reconectarse a los servidores. Una vez derrotadas dichas Vanguardias, se eliminarán las naves hostiles restantes en la zona. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que completen esta iniciativa.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Buscando un poco de venganza</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="str">
-        <v> Buscando un poco de venganza</v>
+        <v> Iniciativa Overdrive: INTEL RAID</v>
+      </c>
+    </row>
+    <row r="601" xml:space="preserve">
+      <c r="A601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos recibido información de que XenoThreat planea lanzar otro ataque contra el sistema Stanton. La CDF ha solicitado a la organización Advocacy la creación de una nueva iniciativa, denominada Operación Overdrive, para detener este ataque antes de que se produzca. La CDF está enviando voluntarios para infiltrarse y obtener información que pueda revelar sus planes. Huelga decir que se espera una fuerte resistencia por parte de cualquier XenoThreat presente. Como incentivo adicional, las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v> Eliminar ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="str">
-        <v> Eliminar ~misión(Ubicación)</v>
+        <v> Iniciativa Overdrive: INCURSIÓN DE AMENAZA XENÓCRATA</v>
+      </c>
+    </row>
+    <row r="603" xml:space="preserve">
+      <c r="A603" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Oleadas de naves de la Amenaza Xeno han estado invadiendo el sistema Stanton y atacando a civiles al azar. No podemos determinar si se trata de un ataque aislado o una reacción a nuestras iniciativas recientes, pero debemos detenerlas. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v> Entregar un mensaje</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="str">
-        <v> Entregar un mensaje</v>
+        <v> Iniciativa Overdrive: EMERGENCIA EN KAREAH</v>
+      </c>
+    </row>
+    <row r="605" xml:space="preserve">
+      <c r="A605" t="str" xml:space="preserve">
+        <v xml:space="preserve">Atención a todos los voluntarios de CDF: hemos recibido una llamada de auxilio del Puesto de Seguridad Kareah. Resulta que XenoThreat utilizó los sistemas de comunicaciones como distracción para alejar a las fuerzas del orden y así poder lanzar un ataque contra la estación. Hemos descubierto que están intentando acceder a sus sistemas, por lo que todos los voluntarios deben desviarse inmediatamente para retomar Kareah y eliminar a todas las fuerzas de XenoThreat. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v> Gestión de la reputación</v>
+        <v> Iniciativa Overdrive: SOLICITUD DE SUMINISTRO</v>
       </c>
     </row>
     <row r="607" xml:space="preserve">
       <c r="A607" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Unos cretinos se niegan a pagarnos lo que nos deben. El problema es que estos idiotas se jactan de ello. Si se hubieran callado, podríamos haber resuelto esto de forma más eficaz, pero ahora tenemos que dar un escarmiento. Estos imbéciles operan desde ~mission(Location|Address). Necesitamos que se vayan todos. ¡Que se oiga bien alto! Enviaremos el pago una vez que nos hayamos encargado de todos. - Se despide.</v>
+        <v xml:space="preserve">Atención, voluntarios de CDF: XenoThreat ha desaparecido. Sospechamos que se han desconectado para preparar la fase final de su plan. La historia demuestra que a XenoThreat le gusta luchar, así que es lógico pensar que podría tratarse de un ataque. Por ello, solicitamos voluntarios para entregar suministros a la estación Gateway, cerca del punto de salto Stanton-Pyro, para reforzar la defensa ante un posible asalto. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v> Muéstrales quién manda.</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="str">
-        <v> Muéstrales quién manda.</v>
+        <v> Iniciativa Overdrive: Recompensa</v>
+      </c>
+    </row>
+    <row r="609" xml:space="preserve">
+      <c r="A609" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Gracias por tu dedicación a esta Iniciativa Overdrive. Como prometimos, te hemos aprobado una mejora de una F7C mk ii civil a una F7A mk ii militar, si dispones de una. Además, se te ha proporcionado un alquiler temporal de una F7A mk ii militar a la que puedes acceder en tu ASOP. _________________ Para actualizar, visita la página web de RSI para aplicar el token, luego reinicia el juego y accede a la nave.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v> Muerte y carga</v>
+        <v>Trata con los Kopions en ~mission(Location)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v> Muerte y carga</v>
+        <v/>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v> Una tarea muy complicada</v>
+        <v> Paquete de Kopion del carnicero en ~misión(Ubicación)</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v> Una tarea muy complicada</v>
+        <v/>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v> Golpea a XenoThreat en ~mission(Location)</v>
+        <v> Mata a los Kopions en ~mission(Ubicación)</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v> Golpea a XenoThreat en ~mission(Location)</v>
+        <v/>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v> Guerra territorial</v>
+        <v> Reducir la población de la estación de interruptores de Valakkar</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v> Guerra territorial</v>
+        <v/>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v> Luz verde en ~misión(Ubicación)</v>
+        <v> Expediente Jorrit: Datos actualizados sobre anomalías energéticas</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v> Luz verde en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v> Saldar una cuenta pendiente</v>
+        <v> Expediente Jorrit: Datos de seguridad actualizados</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v> Saldar una cuenta pendiente</v>
+        <v/>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Se necesita una muerte en ~misión(Ubicación)</v>
+        <v> Expediente Jorrit: Datos sísmicos actualizados</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v> Se necesita una muerte en ~misión(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v> Impacto en el espacio profundo</v>
+        <v> Expediente Jorrit: Datos actualizados sobre el consumo de energía</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v> Impacto en el espacio profundo</v>
+        <v/>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v> Necesitas un bisturí en Carver's</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="str">
-        <v> Necesitas un bisturí en Carver's</v>
+        <v> Recompensa esquiva: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="627" xml:space="preserve">
+      <c r="A627" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGOS: Objetivo de alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Esta recompensa ha resultado extremadamente escurridiza hasta ahora, pero los informes de inteligencia han rastreado al objetivo y a un grupo de sus asociados conocidos hasta ~mission(Location|Address). Sin embargo, hay una alta probabilidad de que ~mission(TargetName|Last) no se arriesgue a una confrontación a menos que se vea absolutamente obligado a ello. Recomendamos que primero neutralice a una parte significativa de los aliados del criminal para atraerlos. El informe indica que un gran grupo de estos hostiles se encuentra actualmente cerca de ~mission(Location). El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v> Disparado en medio del caos</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="str">
-        <v> Disparado en medio del caos</v>
+        <v>Recompensa atrincherada: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
+        <v xml:space="preserve"> DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensa AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: L. Paleski EVALUACIÓN DE RIESGO: Objetivo de riesgo moderado (posible apoyo armado) CONTRATO URGENTE: No Hurston Dynamics busca un contratista para completar una recompensa para ~mission(TargetName). Los informes de inteligencia han localizado el paradero actual del objetivo en ~mission(Location|Address). Si bien tiene autorización para interactuar con cualquier delincuente en el lugar como considere oportuno, se debe proteger a cualquier civil presente en el lugar. El pago se realizará únicamente después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v> Objetivo pagado en CFP</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="str">
-        <v> Objetivo pagado en CFP</v>
+        <v> Recompensa evasiva: ~misión(Nombre del objetivo) (VHRT)</v>
+      </c>
+    </row>
+    <row r="631" xml:space="preserve">
+      <c r="A631" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGO: Objetivo de muy alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Se ha informado que este objetivo y la gran fuerza hostil con la que viaja han atacado recientemente ~mission(Location|Address). Sin embargo, si su modus operandi es el correcto, ~mission(TargetName|Last) generalmente se ha mantenido oculto durante los ataques, prefiriendo dirigir sus fuerzas desde lejos. Recomendamos que se concentre primero en reducir el número de sus aliados, y una vez que sus números se hayan debilitado significativamente, ~mission(TargetName|Last) no tendrá más remedio que enfrentarlo directamente. El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v> Necesito que me quiten el CFP</v>
+        <v>Se busca: ~misión(Nombre del objetivo) (LRT)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v> Necesito que me quiten el CFP</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v> Tapón a un traidor</v>
+        <v> Se busca: ~misión(Nombre del objetivo) (HRT)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v> Tapón a un traidor</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v> Matad al rey</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="str">
-        <v> Matad al rey</v>
+        <v xml:space="preserve"> Evaluación de contratistas de cazarrecompensas</v>
+      </c>
+    </row>
+    <row r="637" xml:space="preserve">
+      <c r="A637" t="str" xml:space="preserve">
+        <v xml:space="preserve">DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Después de repetidos y continuos delitos menores, se ha emitido una recompensa por la siguiente persona: ~mission(TargetName). Para evaluar su potencial para ayudar en la captura de criminales más escurridizos, Hurston Dynamics evaluará su capacidad para localizar y aprehender a ~mission(TargetName|Last) por cualquier medio a su disposición. La información más reciente sobre el paradero actual de ~mission(TargetName|Last) indica que fue visto por última vez en ~mission(Location|Address). El pago se liberará solo después de que se haya resuelto la recompensa. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v> Necesito que saquen a alguien.</v>
+        <v>Se busca: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v> Necesito que saquen a alguien.</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v> Luz verde en ~misión(NombreObjetivo|Apellido)</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="str">
-        <v> Luz verde en ~misión(NombreObjetivo|Apellido)</v>
+        <v xml:space="preserve"> Reevaluación del contratista de cazarrecompensas</v>
+      </c>
+    </row>
+    <row r="641" xml:space="preserve">
+      <c r="A641" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Nuestro departamento realiza reevaluaciones periódicas de antiguos cazadores de recompensas y ha determinado que usted puede ser un candidato adecuado para una posible reincorporación. Como demostración de su idoneidad, capture con éxito al siguiente individuo buscado: ~mission(TargetName). La información más reciente sobre el paradero actual de ~mission(TargetName|Last) es que fue visto por última vez en ~mission(Location|Address). La reincorporación como cazador de recompensas de Hurston Dynamics y el pago se producirán tras la finalización exitosa de este contrato. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v> Fantasma ~misión(Nombre del objetivo)</v>
+        <v>Se busca: ~misión(Nombre del objetivo) (ERT)</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v> Fantasma ~misión(Nombre del objetivo)</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v> Necesitas un éxito en la Riviera</v>
+        <v> Se busca: ~misión(Nombre del objetivo) (VLRT)</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v> Necesitas un éxito en la Riviera</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v> Golpe a XenoThreat en el Yard</v>
+        <v> Se busca: ~misión(Nombre del objetivo) (VHRT)</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v> Golpe a XenoThreat en el Yard</v>
+        <v> ~misión(Contratista|Descripción de la recompensa)</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v xml:space="preserve"> Listos para la retribución</v>
+        <v> Neutralizar la incursión de forajidos</v>
       </c>
     </row>
     <row r="649" xml:space="preserve">
       <c r="A649" t="str" xml:space="preserve">
-        <v xml:space="preserve">Me acaba de caer información interesante. Parece que el infame líder de XenoThreat, ~mission(TargetName), está escondido en ~mission(location|address) trabajando en una gran operación para ellos. Oportunidad perfecta para acabar con ese cabrón de una vez por todas. El problema es que los Xenos están vigilando todas las operaciones de Headhunter en este momento. No hay forma de que podamos movilizar y desplegar un equipo sin que ~mission(TargetName|Last) se entere. Así que te ofrezco la oportunidad de mejorar Pyro y ganar algo de crédito al mismo tiempo. Si te interesa, te sugiero que te equipes y busques refuerzos antes de salir. Solo te pagarán si eliminas a ~mission(TargetName|Last), pero no dudes en matar a cualquier otro XenoThug que pueda estar escondido allí con ellos. ¡Que se vayan!</v>
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Neutralización de Fuerzas Hostiles GERENTE DE SUBCONTRATACIÓN: T. Dalik EVALUACIÓN DE RIESGO: Alto Nuestras fuerzas de seguridad han sido notificadas de una incursión de delincuentes en curso en ~mission(Ubicación|Dirección), y necesitamos un operador independiente capaz de desalojar a los actores hostiles. Según el personal en el lugar, los delincuentes se encuentran actualmente atrincherados cerca de ~mission(Ubicación). Proceda con precaución y esté preparado para usar fuerza letal si los delincuentes se resisten a ser desalojados. El pago solo se autorizará una vez que la ubicación haya sido despejada de manera efectiva. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v> Cabeza de la serpiente</v>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="str">
-        <v> Cabeza de la serpiente</v>
+        <v> Recompensa localizada: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="651" xml:space="preserve">
+      <c r="A651" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: T. Davik EVALUACIÓN DE RIESGOS: Riesgo moderado Hurston Dynamics busca un contratista para completar una recompensa por la misión ~(Nombre del objetivo). Los informes de inteligencia han rastreado al objetivo hasta ~(Ubicación|Dirección), donde fue visto por última vez cerca de ~(Ubicación). Prepárese para que oponga resistencia a la detención y para el uso de fuerza letal si fuera necesario. El pago se realizará únicamente después de que la recompensa se considere completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v> El teniente de XenoThreat necesita que lo maten.</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="str">
-        <v> El teniente de XenoThreat necesita que lo maten.</v>
+        <v> Erradicar todos los nidos</v>
+      </c>
+    </row>
+    <row r="653" xml:space="preserve">
+      <c r="A653" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar varios nidos que han impedido que los departamentos inspeccionen las cuevas pertinentes en busca de recursos. Estamos dispuestos a ofrecer una generosa remuneración por la erradicación de estas plagas. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v> Lanza una amenaza xeno</v>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="str">
-        <v> Lanza una amenaza xeno</v>
+        <v> Exterminar Nido de ~misión(Criatura)</v>
+      </c>
+    </row>
+    <row r="655" xml:space="preserve">
+      <c r="A655" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar a ~mission(Criatura) que se ha instalado en ~mission(ubicación|dirección). Se han convertido en un problema y necesitamos un profesional para resolver la situación. El pago se realizará una vez que se haya eliminado el nido. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo)</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo)</v>
+        <v xml:space="preserve"> Proteger el sitio y recuperar materiales confidenciales.</v>
+      </c>
+    </row>
+    <row r="657" xml:space="preserve">
+      <c r="A657" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Inspección de instalaciones y recuperación de paquetes AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: Sí Hurston ha sabido que los Nine Tails están atacando ~mission(Location|address). Nuestras fuerzas en el sitio han sufrido numerosas bajas y han dejado de responder a las comunicaciones. Los informes iniciales indicaron que la banda estaba intentando obtener material confidencial entregado recientemente a las instalaciones. Afortunadamente, contamos con medidas de seguridad que deberían darnos tiempo para responder. Necesitamos que un agente se dirija a las instalaciones de inmediato, recupere esas cajas y las entregue en un lugar seguro. Usted y cualquier refuerzo que elija traer están autorizados a tomar las medidas necesarias al enfrentarse a los intrusos. Se considera que los sospechosos están armados y son peligrosos. Hurston no proporcionará apoyo material ni actualizaciones sobre el estado de las fuerzas de seguridad de las instalaciones. El material confidencial se entregó discretamente junto con otras cajas en un envío y se guardó en nuestra bóveda automatizada con códigos de acceso almacenados en tabletas electrónicas custodiadas por personal de seguridad de alto nivel. Sin embargo, existe una alta probabilidad de que Nine Tails ya se haya apoderado de él. Deberá encontrar esas tabletas electrónicas e introducir los códigos en la cinta transportadora de paquetes para recuperar el material confidencial. El pago se enviará una vez que se haya entregado en ~mission(dropoff1|address). ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como cualquier acción basada en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v> Eliminación de objetivo para una vía rápida en</v>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="str">
-        <v> Eliminación de objetivo para una vía rápida en</v>
+        <v xml:space="preserve">Informe de persona desaparecida: ~misión(Nombre del objetivo)</v>
+      </c>
+    </row>
+    <row r="659" xml:space="preserve">
+      <c r="A659" t="str" xml:space="preserve">
+        <v xml:space="preserve"> CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Localización de persona desaparecida. GERENTE DE SUBCONTRATACIÓN: I. Takao. EVALUACIÓN DE RIESGO: Baja. El personal de ~mission(Ubicación|Dirección) ha presentado recientemente una denuncia por desaparición de ~mission(Nombre del objetivo). Esta persona lleva varios días desaparecida y fue vista por última vez dirigiéndose a ~mission(Ubicación). Se le contrata para realizar una búsqueda in situ de ~mission(Apellido del objetivo) e intentar determinar su paradero. El pago depende de la obtención de un registro de su ubicación actual, ya sea que se encuentre viva o fallecida. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v xml:space="preserve"> Objetivo en ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="str">
-        <v xml:space="preserve"> Objetivo en ~misión(Ubicación)</v>
+        <v> Instalación de protección contra amenazas</v>
+      </c>
+    </row>
+    <row r="661" xml:space="preserve">
+      <c r="A661" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Una pequeña banda local ha estado profiriendo amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v> Orden de matar</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="str">
-        <v> Orden de matar</v>
+        <v> Instalación de vigilancia contra hostiles</v>
+      </c>
+    </row>
+    <row r="663" xml:space="preserve">
+      <c r="A663" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Delincuentes locales han estado realizando amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v> Choca contra un barco de CFP</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="str">
-        <v> Choca contra un barco de CFP</v>
+        <v> Instalación de vigilancia contra hostiles peligrosos</v>
+      </c>
+    </row>
+    <row r="665" xml:space="preserve">
+      <c r="A665" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Muy alta CONTRATO URGENTE: No Una creciente facción delictiva ha estado realizando amenazas contra ~mission(Location|Address) y Hurston Security requiere un contratista para formar un equipo de seguridad y proteger las instalaciones contra cualquier intrusión. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v> Objetivo Primo</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="str">
-        <v> Objetivo Primo</v>
+        <v> Eliminar el alijo de contrabando</v>
+      </c>
+    </row>
+    <row r="667" xml:space="preserve">
+      <c r="A667" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Delincuentes locales han estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de contrabando. Hurston Security requiere un contratista para que acuda a las instalaciones y destruya todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo)</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo)</v>
+        <v> Eliminar el alijo de narcóticos</v>
+      </c>
+    </row>
+    <row r="669" xml:space="preserve">
+      <c r="A669" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Muy alta CONTRATO URGENTE: No Un pequeño grupo criminal ha estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de narcóticos altamente peligrosos. Hurston Security busca un contratista para que acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v> Un golpe sencillo</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="str">
-        <v> Un golpe sencillo</v>
+        <v> Eliminar el alijo de drogas</v>
+      </c>
+    </row>
+    <row r="671" xml:space="preserve">
+      <c r="A671" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Se ha identificado a delincuentes locales que utilizan ~mission(Location|Address) para fabricar grandes cantidades de contrabando ilegal. Hurston Security requiere que un contratista acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v> Regálate una pelea</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="str">
-        <v> Regálate una pelea</v>
+        <v> Ayudar en la defensa del sitio.</v>
+      </c>
+    </row>
+    <row r="673" xml:space="preserve">
+      <c r="A673" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No El personal de seguridad en ~mission(Location|Address) está siendo amenazado por un grupo criminal local y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente acceder al sitio. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v> ¿Quieres ser cazatalentos?</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="str">
-        <v> ¿Quieres ser cazatalentos?</v>
+        <v> Evaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="675" xml:space="preserve">
+      <c r="A675" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Un grupo criminal local ha estado amenazando ~mission(Location|Address) y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente entrar en las instalaciones. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en las instalaciones resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta evaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v> Fantasma de XenoTrash</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="str">
-        <v> Fantasma de XenoTrash</v>
+        <v> Reevaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="677" xml:space="preserve">
+      <c r="A677" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Nuestro departamento realiza reevaluaciones periódicas de los contratistas de seguridad anteriores y ha determinado que usted podría ser un candidato adecuado para una posible reincorporación. Para recuperar su estatus, Hurston Security busca contratistas que ayuden a eliminar un elemento criminal local que amenaza ~mission(Location|Address). Tenga en cuenta que solo está autorizado para interactuar con hostiles confirmados. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta reevaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v> Choquen algunos barcos</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="str">
-        <v> Choquen algunos barcos</v>
+        <v>Desalojar a los ocupantes ilegales</v>
+      </c>
+    </row>
+    <row r="679" xml:space="preserve">
+      <c r="A679" t="str" xml:space="preserve">
+        <v xml:space="preserve"> CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Limpieza de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: K. Restle EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Hurston busca un contratista dispuesto a desalojar a los ocupantes criminales de ~mission(Location|Address). El sitio se ha utilizado para albergar numerosas actividades ilegales, por lo que es imperativo asegurarlo. Tenga en cuenta que solo está autorizado a interactuar con hostiles confirmados. Agredir a cualquier civil en el sitio se considerará una violación de su contrato. El pago se enviará una vez que se confirme que las instalaciones están despejadas. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v> La oportunidad llama a la puerta en ~mission(Location)</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="str">
-        <v> La oportunidad llama a la puerta en ~mission(Location)</v>
+        <v> Defienda al agente de InterSec</v>
+      </c>
+    </row>
+    <row r="681" xml:space="preserve">
+      <c r="A681" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Nave de Combate Informe: Se requiere asistencia urgente para un agente de InterSec que actualmente está bajo fuego en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Un grupo de forajidos había capturado previamente a nuestro agente con la intención de extraerle información confidencial, pero milagrosamente lograron escapar. Desafortunadamente, los forajidos que lo persiguen ahora lo tienen acorralado. Debido a la cantidad de naves que lo atacan, ofrecemos una compensación adicional para compensar el peligro adicional. &lt;EM4&gt;Reclutar naves adicionales&lt;/EM4&gt; para apoyarlo en esta misión es altamente recomendable. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v> Roba algo ~misión(objeto)</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="str">
-        <v> Roba algo ~misión(objeto)</v>
+        <v>Proteja los activos vitales</v>
+      </c>
+    </row>
+    <row r="683" xml:space="preserve">
+      <c r="A683" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: Uno de nuestros pilotos está siendo atacado en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y necesita asistencia. Este operativo lleva información clave sobre un ataque coordinado a infraestructura clave de la UEE y es vital que pueda entregárnosla. Usted y cualquier &lt;EM4&gt;piloto confiable que pueda reclutar&lt;/EM4&gt; tienen la misión de protegerlo de los forajidos que lo persiguen el tiempo suficiente para que pueda escapar mediante QT. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v> Iniciativa Overdrive: OBJETIVOS PRIORITARIOS</v>
+        <v> Extracción quirúrgica</v>
       </c>
     </row>
     <row r="685" xml:space="preserve">
       <c r="A685" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nuestros analistas han examinado la información incautada a los equipos de reconocimiento de XenoThreat, pero los datos parecen estar protegidos por un sofisticado sistema de cifrado y requieren una clave criptográfica personalizada para acceder a ellos. Hemos logrado localizar a varios tenientes de XenoThreat que operan en el sistema; su misión es encontrar e interrogar a los sospechosos para determinar si poseen una clave criptográfica que nos permita acceder a la información. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de las Fuerzas de Defensa de Canadá que lleven esta iniciativa hasta el final.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: Un agente encubierto nuestro fue descubierto y ahora está siendo perseguido por la banda de forajidos en la que se había infiltrado. Por lo tanto, necesita ser extraído de inmediato en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Una vez en el sitio, interactúe con todos los hostiles para brindar cobertura y que nuestro agente pueda escapar mediante QT. &lt;EM4&gt;Traiga refuerzos adicionales&lt;/EM4&gt; y no subestime a estos forajidos. Son violentos y están motivados, por lo que es poco probable que se rindan pronto. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v> Iniciativa Overdrive: VIGILANCIA DE AMENAZAS XENOTRAS</v>
+        <v> Cómo gestionar el ataque de Vanduul a la nave</v>
       </c>
     </row>
     <row r="687" xml:space="preserve">
       <c r="A687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de los sospechosos capturados durante los recientes ataques reveló que XenoThreat busca acceder remotamente a varias antenas de comunicación en todo el sistema. Que XenoThreat esté interceptando las comunicaciones es extremadamente peligroso para la población local, por lo que se ha solicitado a la CDF que reinicie la antena de comunicación y la defienda de cualquier Vanguardia de XenoThreat que intente reconectarse a los servidores. Una vez derrotadas dichas Vanguardias, se eliminarán las naves hostiles restantes en la zona. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que completen esta iniciativa.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Nave de Combate Informe: Un operador que trabaja con InterSec está siendo atacado por naves Vanduul en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. La probabilidad de que sobrevivan por sí solos es baja, por lo que buscamos un contratista dispuesto a brindar apoyo en combate. Los contratistas que acepten esta misión deben estar bien equipados y listos para enfrentar la amenaza Vanduul de frente. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v> Iniciativa Overdrive: INTEL RAID</v>
+        <v> Piloto bajo fuego de Vanduul</v>
       </c>
     </row>
     <row r="689" xml:space="preserve">
       <c r="A689" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos recibido información de que XenoThreat planea lanzar otro ataque contra el sistema Stanton. La CDF ha solicitado a la organización Advocacy la creación de una nueva iniciativa, denominada Operación Overdrive, para detener este ataque antes de que se produzca. La CDF está enviando voluntarios para infiltrarse y obtener información que pueda revelar sus planes. Huelga decir que se espera una fuerte resistencia por parte de cualquier XenoThreat presente. Como incentivo adicional, las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: Acabamos de perder contacto con un piloto que se enfrentó a fuerzas Vanduul en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Viaje a su última ubicación conocida y, si aún está vivo, defiéndalo el tiempo suficiente para asegurar que pueda escapar. Garantizar la seguridad del operativo es crucial, al igual que eliminar cualquier amenaza Vanduul para la UEE. Probablemente necesitará un grupo de &lt;EM4&gt;naves fuertes&lt;/EM4&gt; para neutralizar con éxito a estos Vanduul. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v> Iniciativa Overdrive: INCURSIÓN DE AMENAZA XENÓCRATA</v>
+        <v> Terrorista ~misión(Nombre del objetivo) a neutralizar</v>
       </c>
     </row>
     <row r="691" xml:space="preserve">
       <c r="A691" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Oleadas de naves de la Amenaza Xeno han estado invadiendo el sistema Stanton y atacando a civiles al azar. No podemos determinar si se trata de un ataque aislado o una reacción a nuestras iniciativas recientes, pero debemos detenerlas. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de la CDF que lleven esta iniciativa hasta el final.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: InterSec ha identificado a más forajidos que planean una operación contra los intereses de la UEE desde Nyx. Su misión será neutralizar esta amenaza potencial antes de que puedan ejecutar sus planes. Viaje a &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; y envíe al líder de estos forajidos, &lt;EM4&gt;~mission(NombreObjetivo)&lt;/EM4&gt; sin dudarlo. Hemos explorado un pequeño número de naves, pero nuestro informe sugiere que son pilotos competentes; &lt;EM4&gt;se recomienda traer refuerzos.&lt;/EM4&gt; Recuerde que eliminar a estos forajidos no solo sirve a la gente de Nyx, sino también a la UEE. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v> Iniciativa Overdrive: EMERGENCIA EN KAREAH</v>
+        <v>Ataque preventivo contra ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="693" xml:space="preserve">
       <c r="A693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Atención a todos los voluntarios de CDF: hemos recibido una llamada de auxilio del Puesto de Seguridad Kareah. Resulta que XenoThreat utilizó los sistemas de comunicaciones como distracción para alejar a las fuerzas del orden y así poder lanzar un ataque contra la estación. Hemos descubierto que están intentando acceder a sus sistemas, por lo que todos los voluntarios deben desviarse inmediatamente para retomar Kareah y eliminar a todas las fuerzas de XenoThreat. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: InterSec requiere un contratista experto para eliminar a un grupo de criminales altamente peligrosos con base en Nyx que planean un ataque coordinado contra un miembro prominente de la Armada de la UEE. Hemos interceptado información crucial que sugiere que un terrorista conocido llamado &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; pretende llevar a cabo este asesinato con la ayuda de elementos criminales locales. Actualmente se encuentran en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;, lo que hace que este sea el momento ideal para nuestro ataque. Tenga cuidado, estos forajidos son asesinos experimentados; se recomienda traer un &lt;EM4&gt;grupo de aliados de confianza&lt;/EM4&gt;. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v> Iniciativa Overdrive: SOLICITUD DE SUMINISTRO</v>
+        <v>Nuevo contrato de defensa: ~misión(Nombre del objetivo) Eliminación</v>
       </c>
     </row>
     <row r="695" xml:space="preserve">
       <c r="A695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Atención, voluntarios de CDF: XenoThreat ha desaparecido. Sospechamos que se han desconectado para preparar la fase final de su plan. La historia demuestra que a XenoThreat le gusta luchar, así que es lógico pensar que podría tratarse de un ataque. Por ello, solicitamos voluntarios para entregar suministros a la estación Gateway, cerca del punto de salto Stanton-Pyro, para reforzar la defensa ante un posible asalto. Les recordamos que el ejército ha donado generosamente algunos F7A Hornet antiguos para los miembros de CDF que completen esta iniciativa.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha sido contratada para combatir el creciente número de forajidos que utilizan Nyx como base para sus operaciones, con la intención de atacar los sistemas UEE vecinos. Como medida preventiva, le solicitamos que viaje a &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y elimine al cabecilla &lt;EM4&gt;~misión(Nombre del Objetivo)&lt;/EM4&gt; para disuadir su ataque planeado contra Stanton. Él y su tripulación son altamente peligrosos y se le &lt;EM4&gt;aconseja que traiga un compañero&lt;/EM4&gt; para apoyo. Los contratistas que puedan demostrar ser confiables y competentes en la ejecución de operaciones serán elegibles para futuras misiones con InterSec. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v> Iniciativa Overdrive: Recompensa</v>
+        <v>Neutralizar la amenaza UEE: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="697" xml:space="preserve">
       <c r="A697" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Gracias por tu dedicación a esta Iniciativa Overdrive. Como prometimos, te hemos aprobado una mejora de una F7C mk ii civil a una F7A mk ii militar, si dispones de una. Además, se te ha proporcionado un alquiler temporal de una F7A mk ii militar a la que puedes acceder en tu ASOP. _________________ Para actualizar, visita la página web de RSI para aplicar el token, luego reinicia el juego y accede a la nave.</v>
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: Aparentemente insatisfechos con sus ganancias en Nyx, un grupo de forajidos liderado por &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; ha estado planeando un ataque importante contra la UEE. Esto no puede permitirse. Gracias al trabajo de nuestro equipo de Inteligencia, hemos podido localizarlos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Diríjanse allí lo antes posible y ataquen antes de que tengan la oportunidad de abandonar el sistema. Con base en nuestro análisis estratégico, recomendamos que una flota &lt;EM4&gt;bien armada y capacitada&lt;/EM4&gt; será necesaria para el éxito de esta misión. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>Trata con los Kopions en ~mission(Location)</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v> Trata con los Kopions en ~mission(Location)</v>
+        <v>Eliminar la nave Vanduul</v>
+      </c>
+    </row>
+    <row r="699" xml:space="preserve">
+      <c r="A699" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Nave de Combate Informe: InterSec requiere los servicios de un piloto experto que esté preparado para ayudar a derribar un peligroso objetivo Vanduul que ha estado involucrado en numerosos ataques. Las incursiones Vanduul han ido en aumento recientemente, lo que representa una amenaza no solo para el sistema Nyx, sino para la UEE en su conjunto. Es imperativo que estos avistamientos sean respondidos de manera rápida y eficiente. Requerimos que vuele al último avistamiento conocido de la nave Vanduul en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y los elimine de inmediato. Los pilotos Vanduul son altamente expertos y extremadamente peligrosos. Enfréntese al enemigo de inmediato y no dude; no mostrarán la misma piedad. Se otorgará una compensación proporcional al riesgo del contrato. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v> Paquete de Kopion del carnicero en ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v> Paquete de Kopion del carnicero en ~misión(Ubicación)</v>
+        <v>Neutralizar objetivo Vanduul</v>
+      </c>
+    </row>
+    <row r="701" xml:space="preserve">
+      <c r="A701" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec necesita un piloto de combate altamente capacitado que pueda localizar y neutralizar un peligroso objetivo Vanduul. Un operador nuestro ha identificado una nave Vanduul volando en las cercanías de &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Hemos recibido instrucciones estrictas de eliminar cualquier Vanduul avistado en los límites del espacio UEE, por temor a una invasión del territorio del Imperio. Traiga una &lt;EM4&gt;pequeña flota de pilotos competentes&lt;/EM4&gt; para enfrentarse y neutralizar el objetivo. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v> Mata a los Kopions en ~mission(Ubicación)</v>
+        <v>Recuperar cadáveres de Vanduul</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v> Mata a los Kopions en ~mission(Ubicación)</v>
+        <v/>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v> Control de plagas</v>
+        <v> Recuperar Vanduul Tech</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v> Control de plagas</v>
+        <v/>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v> Esfuerzo intensivo de erradicación</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v> Esfuerzo intensivo de erradicación</v>
+        <v> Patrulla en el sector peligroso</v>
+      </c>
+    </row>
+    <row r="707" xml:space="preserve">
+      <c r="A707" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha recibido información de inteligencia de que los forajidos planean lanzar un ataque contra un objetivo dentro de la UEE. En un esfuerzo por evitar que esto suceda, necesitamos un contratista para patrullar un sector que creemos que estos forajidos están usando para preparar su ataque. La actividad de los forajidos en este sector es mayor de lo normal, por lo que InterSec recomienda que &lt;EM4&gt;traiga refuerzos&lt;/EM4&gt;. Cuando esté listo, diríjase al &lt;EM4&gt;marcador de ubicación&lt;/EM4&gt; en su HUD y escanee los puntos de ruta a lo largo de la ruta. Una vez que haya confirmado que todo el sector está despejado, el contratista principal recibirá una bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v> Eliminar las criaturas invasoras</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v> Eliminar las criaturas invasoras</v>
+        <v>Patrulla el terreno de caza de Vanduul</v>
+      </c>
+    </row>
+    <row r="709" xml:space="preserve">
+      <c r="A709" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: Existe una creciente preocupación de que los grupos de caza Vanduul estén avanzando más en Nyx. La primera línea de defensa contra esta invasión es el aumento de patrullas. InterSec ha identificado un sector que ha visto un aumento en la actividad Vanduul y está buscando a alguien para patrullar la región y proporcionar una actualización al respecto. Comenzarás tu patrulla en un marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; enviado a tu HUD y luego escanearás una serie de puntos de ruta a lo largo de una ruta designada. Las naves Vanduul en este sector son altamente hábiles y agresivas, por lo que InterSec recomienda encarecidamente que &lt;EM4&gt;traigas varias naves listas para el combate como respaldo&lt;/EM4&gt;. InterSec comprende el inmenso peligro al que te enfrentarás en esta patrulla, por lo que enviaremos una bonificación especial de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal una vez que el sector esté despejado. Atentamente, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación constituye una oferta no vinculante que, una vez aceptada, podrá ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v> Reducir la superpoblación</v>
+        <v>Patrulla para prevenir un posible ataque.</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v> Reducir la superpoblación</v>
+        <v/>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v> Solicitud de eliminación de Kopion</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="str">
-        <v> Solicitud de eliminación de Kopion</v>
+        <v> Buque de la Alianza Popular Tranquility</v>
+      </c>
+    </row>
+    <row r="713" xml:space="preserve">
+      <c r="A713" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operaciones: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Listo para Combate Informe: Una nave de seguridad de la Alianza Popular clase Idris llamada Tranquility está actualmente en combate con una nave capital Vanduul cerca de una antigua estación de extracción QV y Intersec está buscando pilotos de combate para brindar apoyo. Desplácese rápidamente al AO y ataque a los cazas Vanduul para que la Tranquility pueda concentrarse en la nave capital. Buena suerte, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v> Reducir la población de la estación de interruptores de Valakkar</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="str">
-        <v> Reducir la población de la estación de interruptores de Valakkar</v>
+        <v> Bombardeo estratégico</v>
+      </c>
+    </row>
+    <row r="715" xml:space="preserve">
+      <c r="A715" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Naves de Combate con Armamento Informe: Los recursos locales han indicado que elementos de Shattered Blade están intentando reconstruir una de sus estaciones e Intersec está buscando un piloto para asegurarse de que eso no suceda. Han logrado poner en línea las defensas básicas de las torretas, pero actualmente solo tienen &lt;EM4&gt;dos relés de energía activados&lt;/EM4&gt;. Estos serán sus objetivos ya que &lt;EM4&gt;no pueden ser destruidos por armas de energía, necesitará traer armamento balístico o de artillería para ser efectivo&lt;/EM4&gt;. La reactivación de esta estación permitirá a Shattered Blade intentar recuperar una posición en este sistema y no podemos permitir que eso suceda. Buena suerte, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa UEE y la legislación del sistema aplicable.</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v> Eliminar kopiones irradiados</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="str">
-        <v> Eliminar kopiones irradiados</v>
+        <v>Se necesita un grupo de ataque táctico.</v>
+      </c>
+    </row>
+    <row r="717" xml:space="preserve">
+      <c r="A717" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Informe del Grupo de Ataque: Hemos recibido información de que una nave de seguridad de la Alianza Popular llamada Tranquility se topó con Shattered Blade escondida en una antigua estación de extracción QV. Los detalles son escasos, pero los conectaremos con recursos locales una vez en el lugar. Intersec está buscando un equipo para intervenir y proteger a la Tranquility y a su personal. Según las conversaciones con el capitán de la Tranquility, necesitarán &lt;EM4&gt;armamento balístico y municiones para romper las defensas de la estación&lt;/EM4&gt; y, en última instancia, &lt;EM4&gt;llegar a tierra para rescatar a su piloto&lt;/EM4&gt;. &lt;EM4&gt;Reclutar naves adicionales&lt;/EM4&gt; para apoyarlos en esta misión es absolutamente crítico. Necesitarán &lt;EM4&gt;una variedad de tipos de naves&lt;/EM4&gt; para equilibrar múltiples zonas de combate en el espacio y en tierra. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Ignore este mensaje si lo ha recibido por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa UEE y las leyes del sistema, según corresponda.</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v> Jorrit Dossier: Expedientes de Personal de Onyx</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="str">
-        <v> Jorrit Dossier: Expedientes de Personal de Onyx</v>
+        <v>Listo para ser aprovechado</v>
+      </c>
+    </row>
+    <row r="719" xml:space="preserve">
+      <c r="A719" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tengo buenas noticias para ti. En este preciso instante, hay una instalación automatizada que está produciendo paquete tras paquete de producto de primera calidad, prácticamente listo para ser aprovechado. Solo tienes que ir allí, lidiar con un par de matones, agarrar lo que puedas y venderlo con una gran ganancia. No debería ser ningún problema. Y hay mucha gente dispuesta a pagar bien por comprarte ese producto. Hablando de créditos, no voy a dar las coordenadas de esta instalación por pura generosidad. Creo que es justo pedir una comisión por información tan valiosa. No esperes demasiado. No sé cuánto tiempo más estará activa la página web. -Ruto</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v> Expediente Jorrit: Acceso a los archivos de ingeniería</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="str">
-        <v> Expediente Jorrit: Acceso a los archivos de ingeniería</v>
+        <v> Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="721" xml:space="preserve">
+      <c r="A721" t="str" xml:space="preserve">
+        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados Hemos podido rastrear un reciente aumento de contrabando hasta una planta de producción automatizada en ~mission(Location|Address). No podemos asegurar cuánto tiempo más estará operativa la planta, por lo que BlacJac necesita a alguien en el lugar para inspeccionar, asegurar el contrabando y transportarlo hasta ~mission(Destination|Address). Una vez allí, pueden usar la terminal administrativa de mercancías para transferirnos el contrabando y cobrar su recompensa. No hemos podido determinar qué tipo de fuerza hostil estará presente, pero sea cual sea la que encuentren, están autorizados a usar la fuerza letal si es necesario. Cuanto más contrabando logren traernos, más créditos ganarán. Gracias, Teniente Aaron Riegert, Supervisor de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v> Expediente Jorrit: Acceso a los archivos de investigación</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="str">
-        <v> Expediente Jorrit: Acceso a los archivos de investigación</v>
+        <v> Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="723" xml:space="preserve">
+      <c r="A723" t="str" xml:space="preserve">
+        <v xml:space="preserve">Crusader Security ha descubierto que una instalación de producción ilegal en ~mission(Location|Address) se está utilizando para fabricar contrabando. Buscamos un contratista para asegurar el sitio, confiscar el contrabando y entregarlo en ~mission(Destination|Address). La terminal administrativa de mercancías le permitirá entregar el contrabando a nuestro depósito de pruebas y cobrar su pago. Dado que se trata de una instalación automatizada, no está claro cuánto tiempo estarán fabricando ni cuántas personas podrían estar presentes. Para mayor seguridad, le recomendamos que vaya preparado para encontrar una fuerte resistencia. Su compensación total dependerá de la seguridad con la que se entreguen los paquetes como prueba. CONTRATO AUTORIZADO POR: Oficial de Enlace Vanzant ID# 712L921P</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v> Expediente Jorrit: Datos actualizados sobre anomalías energéticas</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="str">
-        <v>Expediente Jorrit: Datos actualizados sobre anomalías energéticas</v>
+        <v> Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="725" xml:space="preserve">
+      <c r="A725" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Confiscar contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Odington EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Hurston Security ha tenido conocimiento de una instalación de producción automatizada ilegal y activa en ~mission(Location|Address) y busca un contratista para asegurar el sitio y confiscar la mayor cantidad posible de paquetes de contrabando para su entrega a una instalación de Hurston Security en ~mission(Destination|Address) para su eliminación inmediata. La transferencia del contrabando y la atribución de su pago de recompensa deben realizarse a través de la terminal administrativa de mercancías en dicho lugar. Usted está autorizado a usar la fuerza necesaria para completar su objetivo. El pago se basará en la cantidad de contrabando incautado. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v> Expediente Jorrit: Datos de seguridad actualizados</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="str">
-        <v> Expediente Jorrit: Datos de seguridad actualizados</v>
+        <v>Confiscar contrabando</v>
+      </c>
+    </row>
+    <row r="727" xml:space="preserve">
+      <c r="A727" t="str" xml:space="preserve">
+        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional de seguridad orientado a los detalles que pueda ayudarnos a asegurar el contrabando de un sitio de producción automatizado ilegal en ~mission(Location|Address). Los paquetes luego deberán ser llevados a ~mission(Destination|Address) y transferidos a nuestra posesión para su destrucción a través de la terminal administrativa de mercancías. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Gestionar cualquier hostil encontrado dentro del sitio; usando la fuerza según sea necesario. • Asegurar el contrabando y entregarlo a las terminales de mercancías en ~mission(Destination|Address) REQUISITOS MÍNIMOS • 2 años de experiencia combinada de mercenario y/o seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v> Expediente Jorrit: Datos sísmicos actualizados</v>
+        <v> Recuperar información adicional sobre contrabandistas.</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v> Expediente Jorrit: Datos sísmicos actualizados</v>
+        <v/>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v> Expediente Jorrit: Datos actualizados sobre el consumo de energía</v>
+        <v> Oportunidad de transporte de carga con Ling Hauling</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v> Expediente Jorrit: Datos actualizados sobre el consumo de energía</v>
+        <v/>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v> Recompensa esquiva: ~misión(Nombre del objetivo) (HRT)</v>
-      </c>
-    </row>
-    <row r="733" xml:space="preserve">
-      <c r="A733" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGOS: Objetivo de alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Esta recompensa ha resultado extremadamente escurridiza hasta ahora, pero los informes de inteligencia han rastreado al objetivo y a un grupo de sus asociados conocidos hasta ~mission(Location|Address). Sin embargo, hay una alta probabilidad de que ~mission(TargetName|Last) no se arriesgue a una confrontación a menos que se vea absolutamente obligado a ello. Recomendamos que primero neutralice a una parte significativa de los aliados del criminal para atraerlos. El informe indica que un gran grupo de estos hostiles se encuentra actualmente cerca de ~mission(Location). El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v>Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v/>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>Recompensa atrincherada: ~misión(Nombre del objetivo) (MRT)</v>
-      </c>
-    </row>
-    <row r="735" xml:space="preserve">
-      <c r="A735" t="str" xml:space="preserve">
-        <v xml:space="preserve"> DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensa AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: L. Paleski EVALUACIÓN DE RIESGO: Objetivo de riesgo moderado (posible apoyo armado) CONTRATO URGENTE: No Hurston Dynamics busca un contratista para completar una recompensa para ~mission(TargetName). Los informes de inteligencia han localizado el paradero actual del objetivo en ~mission(Location|Address). Si bien tiene autorización para interactuar con cualquier delincuente en el lugar como considere oportuno, se debe proteger a cualquier civil presente en el lugar. El pago se realizará únicamente después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v/>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v> Recompensa evasiva: ~misión(Nombre del objetivo) (VHRT)</v>
+        <v> Ruta de reparto local de la familia Ling</v>
       </c>
     </row>
     <row r="737" xml:space="preserve">
       <c r="A737" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: I. Takao EVALUACIÓN DE RIESGO: Objetivo de muy alto riesgo (apoyo armado) Hurston Dynamics busca un contratista para completar una recompensa por ~mission(TargetName). Se ha informado que este objetivo y la gran fuerza hostil con la que viaja han atacado recientemente ~mission(Location|Address). Sin embargo, si su modus operandi es el correcto, ~mission(TargetName|Last) generalmente se ha mantenido oculto durante los ataques, prefiriendo dirigir sus fuerzas desde lejos. Recomendamos que se concentre primero en reducir el número de sus aliados, y una vez que sus números se hayan debilitado significativamente, ~mission(TargetName|Last) no tendrá más remedio que enfrentarlo directamente. El pago se liberará solo después de que la recompensa se haya considerado completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v xml:space="preserve"> Hola, espero que estés disponible para hacer una entrega. ~mission(Contractor|Family) PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Avísame si puedes hacerlo. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling Coordinadora de Envíos Ling Family Hauling</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo) (LRT)</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> La familia Ling busca nuevos contratistas.</v>
+      </c>
+    </row>
+    <row r="739" xml:space="preserve">
+      <c r="A739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, somos una pequeña empresa de reparto familiar que actualmente busca nuevos contratistas en la zona de Crusader. Si te interesa trabajar con nosotros, la siguiente entrega sería una excelente prueba para ver si encajas bien con la empresa. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si todo sale bien, te convertirás en el miembro más reciente de Ling Family Hauling. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo) (HRT)</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Reevaluación del contratista Ling</v>
+      </c>
+    </row>
+    <row r="741" xml:space="preserve">
+      <c r="A741" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, no me entusiasma tener que hacer esto, pero tenemos escasez de contratistas y más entregas que nunca. Estoy dispuesto a darte otra oportunidad, pero necesitas completar la siguiente entrega. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por último, probablemente sería buena idea llevar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v xml:space="preserve"> Evaluación de contratistas de cazarrecompensas</v>
+        <v>Entrega de paquetes para Ling</v>
       </c>
     </row>
     <row r="743" xml:space="preserve">
       <c r="A743" t="str" xml:space="preserve">
-        <v xml:space="preserve">DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS CONTRATO: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Después de repetidos y continuos delitos menores, se ha emitido una recompensa por la siguiente persona: ~mission(TargetName). Para evaluar su potencial para ayudar en la captura de criminales más escurridizos, Hurston Dynamics evaluará su capacidad para localizar y aprehender a ~mission(TargetName|Last) por cualquier medio a su disposición. La información más reciente sobre el paradero actual de ~mission(TargetName|Last) indica que fue visto por última vez en ~mission(Location|Address). El pago se liberará solo después de que se haya resuelto la recompensa. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v xml:space="preserve"> Hola, necesitamos que recojas un paquete en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y lo lleves a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Originalmente iba a enviar a mi hermano Ricki, pero dijo que la zona es demasiado peligrosa. Supongo que ha habido varias advertencias de seguridad por allí, pero mientras tengas cuidado y lleves armas o algo así, seguro que no tendrás problemas. Probablemente ni siquiera te topes con nada. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo) (MRT)</v>
+        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v/>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v xml:space="preserve"> Reevaluación del contratista de cazarrecompensas</v>
-      </c>
-    </row>
-    <row r="747" xml:space="preserve">
-      <c r="A747" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: ~mission(Contractor|Auth) EVALUACIÓN DE RIESGOS: ~mission(Danger) CONTRATO URGENTE: ~mission(Contractor|BountyTimed) Nuestro departamento realiza reevaluaciones periódicas de antiguos cazadores de recompensas y ha determinado que usted puede ser un candidato adecuado para una posible reincorporación. Como demostración de su idoneidad, capture con éxito al siguiente individuo buscado: ~mission(TargetName). La información más reciente sobre el paradero actual de ~mission(TargetName|Last) es que fue visto por última vez en ~mission(Location|Address). La reincorporación como cazador de recompensas de Hurston Dynamics y el pago se producirán tras la finalización exitosa de este contrato. ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto.</v>
+        <v> Oportunidades de empleo en seguridad de Eckhart</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v> ~misión(Descripción)</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>Se busca: ~misión(Nombre del objetivo) (ERT)</v>
+        <v> Supervisión de la producción</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> ~misión(Contratista|Descripción del producto farmacéutico de entrega local)</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo) (VLRT)</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Una tanda hecha desde cero</v>
+      </c>
+    </row>
+    <row r="751" xml:space="preserve">
+      <c r="A751" t="str" xml:space="preserve">
+        <v xml:space="preserve">Normalmente, me gusta cocinar todo desde cero. Me enorgullece el producto y todo eso. Pero de vez en cuando, ya sea por mucha demanda, mucho calor o lo que sea, necesito recurrir a otros laboratorios para un pedido. Sin embargo, aquí estoy muy ocupado, así que me vendría bien alguien que me ayudara a supervisar toda la línea de producción. No se me ocurre nadie mejor ni más disponible que tú. ~Misión (Itinerario) Simplemente no te distraigas ni te desvíes del camino. Sucede más a menudo de lo que crees. Si logras completar la lista, me aseguraré de que recibas una buena parte de las ganancias. -Wallace</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v> Se busca: ~misión(Nombre del objetivo) (VHRT)</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa)</v>
+        <v> Capturan al miembro de la pandilla de Arlington, Les Arlington</v>
+      </c>
+    </row>
+    <row r="753" xml:space="preserve">
+      <c r="A753" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Una comunicación anónima nos ha avisado de que Les Arlington, hijo del líder de la banda Maltrox Arlington, había sido visto recogiendo una entrega en un centro de transferencia de Covalex. Le proporcionaremos las coordenadas de donde creemos que se encuentran actualmente. Les es un piloto experimentado que lleva volando casi tanto tiempo como ellos llevan caminando y suele ser el piloto de escape de la banda. Podría ser conveniente traer naves de apoyo adicionales para frustrar cualquier intento de fuga. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v> Neutralizar la incursión de forajidos</v>
+        <v>Captura de Nicks Cantwell, miembro de la pandilla de Arlington.</v>
       </c>
     </row>
     <row r="755" xml:space="preserve">
       <c r="A755" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Neutralización de Fuerzas Hostiles GERENTE DE SUBCONTRATACIÓN: T. Dalik EVALUACIÓN DE RIESGO: Alto Nuestras fuerzas de seguridad han sido notificadas de una incursión de delincuentes en curso en ~mission(Ubicación|Dirección), y necesitamos un operador independiente capaz de desalojar a los actores hostiles. Según el personal en el lugar, los delincuentes se encuentran actualmente atrincherados cerca de ~mission(Ubicación). Proceda con precaución y esté preparado para usar fuerza letal si los delincuentes se resisten a ser desalojados. El pago solo se autorizará una vez que la ubicación haya sido despejada de manera efectiva. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de arresto grupal para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero de reparación. Si bien el robo fue detenido, los miembros del grupo se han dispersado en la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. Hemos recibido información de que Nicks Cantwell, conocido de larga data y confidente de Maltrox Arlington, fue visto intentando comprar un láser de minería de alta densidad, del tipo que se usa frecuentemente en intentos de secuestro de naves para perforar estratégicamente los cascos. Hemos proporcionado las coordenadas de la última ubicación conocida de Nicks. Nicks es un experto en municiones muy respetado en los círculos criminales y suele dejar un rastro de destrucción a su paso. Se recomienda aumentar la potencia de fuego en este encuentro. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v> Recompensa localizada: ~misión(Nombre del objetivo) (MRT)</v>
+        <v>Captura a Sam 'Weepy' Arlington, miembro de la pandilla de Arlington.</v>
       </c>
     </row>
     <row r="757" xml:space="preserve">
       <c r="A757" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Cobro de recompensas GERENTE DE SUBCONTRATACIÓN: T. Davik EVALUACIÓN DE RIESGOS: Riesgo moderado Hurston Dynamics busca un contratista para completar una recompensa por la misión ~(Nombre del objetivo). Los informes de inteligencia han rastreado al objetivo hasta ~(Ubicación|Dirección), donde fue visto por última vez cerca de ~(Ubicación). Prepárese para que oponga resistencia a la detención y para el uso de fuerza letal si fuera necesario. El pago se realizará únicamente después de que la recompensa se considere completada. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Sam 'Weepy' Arlington fue marcado por sistemas de seguridad automatizados en un R&amp;R después de estar involucrado en una pelea de borrachos. Weepy logró abandonar la estación antes de que llegaran los equipos de respuesta, pero hemos podido localizarlo en el lugar donde creemos que se encuentra escondido. Weepy es tío y principal ejecutor del líder de la pandilla, Maltrox Arlington. Sus problemas de ira, sumados a un largo historial de abuso de sustancias, lo convierten en un verdadero impredecible. Espere que oponga una resistencia considerable cuando usted y sus fuerzas lo acorralen. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v> Erradicar todos los nidos</v>
+        <v>Captura de un miembro de la pandilla de Arlington en Oslo, Arlington.</v>
       </c>
     </row>
     <row r="759" xml:space="preserve">
       <c r="A759" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar varios nidos que han impedido que los departamentos inspeccionen las cuevas pertinentes en busca de recursos. Estamos dispuestos a ofrecer una generosa remuneración por la erradicación de estas plagas. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Recientemente, se accedió ilegalmente a una terminal de seguridad utilizando una criptoclave personalizada única que había sido utilizada en un robo el año pasado por un tal Oslo Arlington, el hermano menor del líder de la banda Maltrox Arlington. Aunque no podemos confirmar con certeza si Oslo hackeó la terminal, consideramos que vale la pena investigarlo. Oslo, un estratega de renombre, sumamente inteligente y experto en tecnología, ha demostrado ser difícil de capturar en el pasado. Si esta pista conduce a su localización, un equipo de ataque táctico bien coordinado sería fundamental para el éxito de la operación. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al finalizar el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. Dicha información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v> Exterminar Nido de ~misión(Criatura)</v>
+        <v>Captura de Kass Dent, miembro de la pandilla de Arlington.</v>
       </c>
     </row>
     <row r="761" xml:space="preserve">
       <c r="A761" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Exterminación de plagas AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Hurston busca un contratista dispuesto a exterminar a ~mission(Criatura) que se ha instalado en ~mission(ubicación|dirección). Se han convertido en un problema y necesitamos un profesional para resolver la situación. El pago se realizará una vez que se haya eliminado el nido. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su revista. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado al espacio profundo. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Dos guardias de banco fueron reportados como desaparecidos la semana pasada. Hace unas horas, sus cuerpos aparecieron en un montón de basura en Magnus con sus datos biométricos robados. Afortunadamente, un puesto de dumplings cercano tenía una cámara de seguridad que captó el momento en que arrojaron los cadáveres. El reconocimiento facial permitió identificar a Kass Dent, pareja sentimental de Maltrox Arlington y padre de Les Arlington. Usando el video para reconstruir la cronología, hemos proporcionado las coordenadas del lugar donde se cree que Kass se esconde actualmente. Se sospecha que Kass es responsable de una larga lista de asesinatos, siendo estos dos los más recientes. Recomendamos traer solo a personas altamente capacitadas para intentar minimizar el número de víctimas. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v xml:space="preserve"> Proteger el sitio y recuperar materiales confidenciales.</v>
+        <v>Captura de Maltrox Arlington, líder de la pandilla de Arlington.</v>
       </c>
     </row>
     <row r="763" xml:space="preserve">
       <c r="A763" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Inspección de instalaciones y recuperación de paquetes AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: G. Livingston EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: Sí Hurston ha sabido que los Nine Tails están atacando ~mission(Location|address). Nuestras fuerzas en el sitio han sufrido numerosas bajas y han dejado de responder a las comunicaciones. Los informes iniciales indicaron que la banda estaba intentando obtener material confidencial entregado recientemente a las instalaciones. Afortunadamente, contamos con medidas de seguridad que deberían darnos tiempo para responder. Necesitamos que un agente se dirija a las instalaciones de inmediato, recupere esas cajas y las entregue en un lugar seguro. Usted y cualquier refuerzo que elija traer están autorizados a tomar las medidas necesarias al enfrentarse a los intrusos. Se considera que los sospechosos están armados y son peligrosos. Hurston no proporcionará apoyo material ni actualizaciones sobre el estado de las fuerzas de seguridad de las instalaciones. El material confidencial se entregó discretamente junto con otras cajas en un envío y se guardó en nuestra bóveda automatizada con códigos de acceso almacenados en tabletas electrónicas custodiadas por personal de seguridad de alto nivel. Sin embargo, existe una alta probabilidad de que Nine Tails ya se haya apoderado de él. Deberá encontrar esas tabletas electrónicas e introducir los códigos en la cinta transportadora de paquetes para recuperar el material confidencial. El pago se enviará una vez que se haya entregado en ~mission(dropoff1|address). ** La información transmitida puede contener material confidencial y/o privilegiado. Queda prohibida cualquier revisión, retransmisión, difusión o cualquier otro uso de esta información, así como cualquier acción basada en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado en el espacio. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Maltrox Arlington ha estado manteniendo un perfil bajo últimamente, pero creemos que ha salido de su escondite. Una patrulla estaba reabasteciendo combustible en una estación cuando una de sus naves fue potenciada. Maltrox es el sospechoso más probable. Aunque el registro de la nave estuvo desactivado temporalmente, hemos podido rastrear su firma cuántica y le hemos facilitado las coordenadas. La banda de Arlington, criminal de tercera generación, ha estado bajo el liderazgo de Maltrox durante los últimos seis años. Tenga en cuenta que se trata de un objetivo inteligente, agresivo y muy peligroso. Cuantos más recursos pueda aportar, mayores serán las probabilidades de que logremos capturar a Maltrox de una vez por todas. Está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v xml:space="preserve">Informe de persona desaparecida: ~misión(Nombre del objetivo)</v>
+        <v>Idris robado por una banda de Arlington</v>
       </c>
     </row>
     <row r="765" xml:space="preserve">
       <c r="A765" t="str" xml:space="preserve">
-        <v xml:space="preserve"> CONTRATO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Localización de persona desaparecida. GERENTE DE SUBCONTRATACIÓN: I. Takao. EVALUACIÓN DE RIESGO: Baja. El personal de ~mission(Ubicación|Dirección) ha presentado recientemente una denuncia por desaparición de ~mission(Nombre del objetivo). Esta persona lleva varios días desaparecida y fue vista por última vez dirigiéndose a ~mission(Ubicación). Se le contrata para realizar una búsqueda in situ de ~mission(Apellido del objetivo) e intentar determinar su paradero. El pago depende de la obtención de un registro de su ubicación actual, ya sea que se encuentre viva o fallecida. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO Parece que la segunda vez es la vencida para la banda de Arlington. Después de un intento fallido, la familia criminal recientemente fugada ha logrado robar un Idris de un astillero. Ahora sabemos para qué eran el láser de minería y la biometría que robaron. Dado que tuvimos tanto éxito capturándolos la primera vez, Eckhart Security ha recibido la orden de arresto de la banda. Esto requerirá una potencia de fuego considerable para derribar una nave capital de esta capacidad. Usted está autorizado a usar la fuerza que sea necesaria para rastrear el Idris y neutralizar a la banda. El pago se emitirá al completar con éxito el contrato y se ajustará según la evaluación final de su calificación de efectividad en combate y la de su equipo. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v> Instalación de protección contra amenazas</v>
+        <v>Se emite la orden de compra grupal.</v>
       </c>
     </row>
     <row r="767" xml:space="preserve">
       <c r="A767" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Una pequeña banda local ha estado profiriendo amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve"> TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO En relación con un delito cometido conjuntamente, se ha emitido una orden de arresto grupal para: ~mission(Target1) ~mission(Target2) ~mission(Target3) Actualmente se cree que ya no viajan juntos para evadir la captura y que pronto podrían huir del sistema. Debería considerar seriamente reclutar ayuda adicional para ejecutar todas las órdenes de arresto en el plazo limitado. Está autorizado a usar la fuerza que sea necesaria para neutralizar a los objetivos. El pago se emitirá al completar con éxito el contrato cuando todos los objetivos hayan sido neutralizados en el tiempo asignado. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v> Instalación de vigilancia contra hostiles</v>
+        <v> ¿Necesitas una salida?</v>
       </c>
     </row>
     <row r="769" xml:space="preserve">
       <c r="A769" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Delincuentes locales han estado realizando amenazas contra ~mission(Location|Address) y Hurston Security busca un contratista para formar un equipo de seguridad que proteja las instalaciones contra cualquier intrusión. El pago se realizará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola. Todavía no hemos tenido la oportunidad de trabajar juntos, pero estoy en un aprieto y necesito a alguien más. No gratis, por supuesto. Me gusta el intercambio. Uno de mis socios, que estuvo cumpliendo condena en Klescher, debía traerme un chip de datos, pero luego dejó de dar señales de vida. Supongo que está muerto, pero aquí está el trato: si terminas su trabajo, borro tu historial delictivo. No está mal, ¿verdad? Tu predecesor planeaba usar unos túneles viejos para escapar. Dio a entender que no eran precisamente fáciles de acceder, pero confío en que podrás resolverlo. Supongo que encontrarás su cuerpo por ahí y, si tenemos suerte, todavía tendrá el chip. Una vez que lo consigas, termina de escapar como puedas. Luego, tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me sorprendería que te los encontraras. Después de obtener los datos y validarlos, borraré tu historial delictivo. Entonces podrás disfrutar de tu recién descubierta libertad. Si lo haces bien, tal vez tenga un trabajo más lucrativo para ti en el futuro.</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v> Instalación de vigilancia contra hostiles peligrosos</v>
+        <v>ayudémonos mutuamente</v>
       </c>
     </row>
     <row r="771" xml:space="preserve">
       <c r="A771" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Muy alta CONTRATO URGENTE: No Una creciente facción delictiva ha estado realizando amenazas contra ~mission(Location|Address) y Hurston Security requiere un contratista para formar un equipo de seguridad y proteger las instalaciones contra cualquier intrusión. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola. Oí que acabaste en Klescher, lo cual es una verdadera lástima. Pero en realidad podría ser un día de suerte para ambos. En resumen, tenía a alguien sacando un chip de datos de la prisión, pero nunca volvió a contactarme. Sé con certeza que no ha salido de las instalaciones, así que creo que algo le pudo haber pasado. Aunque es trágico, el trabajo debe continuar. Si puedes conseguir el chip y terminar el trabajo, puedo borrar tu historial criminal. ¿Qué dices? Claro, no sé exactamente hasta dónde llegó, pero puedo decirte que la prisión tiene toda una red de túneles ocultos que mi tipo planeaba usar para escapar. Supongo que su cadáver se está pudriendo por ahí. Cuando encuentres el cuerpo, espero que el chip todavía esté con él. Cuando lo tengas, termina de escapar y tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Una advertencia: ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me extrañaría que te los encontraras. Cuando tenga los datos, borraré tu historial delictivo y listo, quedarás libre de toda sospecha. Lo que hagas después es decisión tuya.</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v> Eliminar el alijo de contrabando</v>
+        <v>Violación y robo</v>
       </c>
     </row>
     <row r="773" xml:space="preserve">
       <c r="A773" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGOS: Media CONTRATO URGENTE: No Delincuentes locales han estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de contrabando. Hurston Security requiere un contratista para que acuda a las instalaciones y destruya todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola. Los Nueve Colas tienen un pequeño problema. Resulta que tienen un pequeño negocio paralelo en el tráfico clandestino de órganos. Un tema que prefiero evitar, pero un trabajo es un trabajo, ¿no? Parece que una de sus carnicerías móviles a bordo del 'October Rising' fue asaltada por seguridad privada mientras trabajaba. Ahora los Nueve Colas están dispuestos a romper lazos con el barco y su tripulación (que probablemente ya estén todos muertos), pero necesitan que les extraigan una caja en particular. Supongo que era un pedido especial o algo así. En fin, suban al October Rising, consigan el paquete y salgan. La seguridad sigue por ahí, así que tengan cuidado y tal vez traigan a algunos amigos, pero recuerden, su prioridad es el paquete. Si quieren ahorrarse problemas, también podrían apagar la zona desactivando la antena de comunicaciones más cercana si quieren evitar que los arresten por, ya saben, matar a un montón de guardias de seguridad. Pero bueno, hagan lo que quieran. Cuando salgas, deja el paquete en la clínica de Grim HEX y yo me encargaré del pago. Pan comido, Ruto.</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v> Eliminar el alijo de narcóticos</v>
+        <v>consigue los productos</v>
       </c>
     </row>
     <row r="775" xml:space="preserve">
       <c r="A775" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Muy alta CONTRATO URGENTE: No Un pequeño grupo criminal ha estado utilizando ~mission(Location|Address) para fabricar grandes cantidades de narcóticos altamente peligrosos. Hurston Security busca un contratista para que acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Hola, hace poco escuché información confidencial de que ~mission(location|address) recibió material confidencial de gran interés para un conocido mío. Es tan interesante que están dispuestos a pagar para que alguien asalte las instalaciones, se apodere del material y lo entregue en ~mission(DropOff1|address). Supongo que habrá mucha seguridad, que probablemente opondrá resistencia, así que llevaría un par de armas. Se rumorea que el material confidencial se entregó en un envío junto con otras cosas y ahora se encuentra almacenado en la bóveda automatizada de las instalaciones. Los oficiales de seguridad de alto rango llevan tabletas con códigos de acceso a la bóveda. Tendrás que conseguir una tableta antes de usar la cinta transportadora para recuperar las cajas. Si necesitas un incentivo adicional, he visto el manifiesto y puedo confirmar que las otras cajas almacenadas en las instalaciones son de primera calidad. A mi cliente no le importa lo que les pase, así que puedes hacer lo que quieras con ellas. Si lo gestionas bien, esas cajas adicionales podrían suponer una buena ganancia extra, además de la tarifa de envío.</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v> Eliminar el alijo de drogas</v>
+        <v>suministro limitado</v>
       </c>
     </row>
     <row r="777" xml:space="preserve">
       <c r="A777" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Eliminación de contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: R. Russel EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Se ha identificado a delincuentes locales que utilizan ~mission(Location|Address) para fabricar grandes cantidades de contrabando ilegal. Hurston Security requiere que un contratista acuda a las instalaciones y elimine todo el contrabando almacenado allí. El pago se realizará una vez que se haya eliminado todo el contrabando. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve"> Parece que hay un nuevo advenedizo en el sector que no ha estado pagando lo que le corresponde. Para darles una lección, mi cliente quiere que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Los matones de bajo nivel que tienen allí probablemente armarán un escándalo e intentarán detenerte. Haz lo que quieras con ellos, pero lo más importante es deshacerte de la droga.</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v> Ayudar en la defensa del sitio.</v>
+        <v> liquidación de inventario</v>
       </c>
     </row>
     <row r="779" xml:space="preserve">
       <c r="A779" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No El personal de seguridad en ~mission(Location|Address) está siendo amenazado por un grupo criminal local y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente acceder al sitio. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve"> Un cliente mío está intentando negociar un acuerdo, pero no está teniendo mucha suerte. La otra parte cree tener toda la ventaja porque tiene un gran inventario a su disposición. Para facilitar las negociaciones, necesito que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Debería advertirte que el sitio está protegido por gente muy peligrosa, así que llegar al alijo va a ser complicado, pero confío en que encontrarás la manera.</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v> Evaluación de contratistas de seguridad</v>
+        <v> Agotado</v>
       </c>
     </row>
     <row r="781" xml:space="preserve">
       <c r="A781" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGO: Alto CONTRATO URGENTE: No Un grupo criminal local ha estado amenazando ~mission(Location|Address) y Hurston Security busca contratistas para reforzar sus defensas y eliminar a cualquier persona hostil que intente entrar en las instalaciones. Tenga en cuenta que solo está autorizado a interactuar con personas hostiles confirmadas. Agredir a cualquier miembro del personal de seguridad en las instalaciones resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta evaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">Uno de mis clientes se ha enfadado al enterarse de que alguien está invadiendo su territorio. Ahora, en lugar de optar por la vía tradicional de matar a algunas personas y armar un escándalo, ha decidido enviar un mensaje diferente. Vas a ir a ~misión(Ubicación|Dirección) y destruir toda la droga del lugar. Claro que, si alguien quiere pelear contigo, puedes defenderte, pero lo más importante es deshacerte de la droga.</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v> Reevaluación de contratistas de seguridad</v>
+        <v> demasiados cocineros</v>
       </c>
     </row>
     <row r="783" xml:space="preserve">
       <c r="A783" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Protección de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Spooner EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Nuestro departamento realiza reevaluaciones periódicas de los contratistas de seguridad anteriores y ha determinado que usted podría ser un candidato adecuado para una posible reincorporación. Para recuperar su estatus, Hurston Security busca contratistas que ayuden a eliminar un elemento criminal local que amenaza ~mission(Location|Address). Tenga en cuenta que solo está autorizado para interactuar con hostiles confirmados. Agredir a cualquier miembro del personal de seguridad en el sitio resultará en un incumplimiento de contrato. El pago se enviará una vez que se confirme que las instalaciones son seguras. La finalización exitosa de esta reevaluación le permitirá ser considerado para futuros trabajos como contratista de seguridad. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve"> Un cliente está siendo superado por un nuevo competidor y busca sabotear el negocio. Dirígete a ~mission(Location|Address) y elimina a todos los civiles que trabajan allí. Haz lo que quieras con los matones armados que custodian a los trabajadores, pero recuerda que no son la prioridad.</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>Desalojar a los ocupantes ilegales</v>
-      </c>
-    </row>
-    <row r="785" xml:space="preserve">
-      <c r="A785" t="str" xml:space="preserve">
-        <v xml:space="preserve"> CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Limpieza de instalaciones AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: K. Restle EVALUACIÓN DE RIESGOS: Alta CONTRATO URGENTE: No Hurston busca un contratista dispuesto a desalojar a los ocupantes criminales de ~mission(Location|Address). El sitio se ha utilizado para albergar numerosas actividades ilegales, por lo que es imperativo asegurarlo. Tenga en cuenta que solo está autorizado a interactuar con hostiles confirmados. Agredir a cualquier civil en el sitio se considerará una violación de su contrato. El pago se enviará una vez que se confirme que las instalaciones están despejadas. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o tomar medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v> Vive y deja que un contratista independiente se vengue.</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v xml:space="preserve">Todo el mundo guarda rencor, ¿no? O sea, cuando te pillan cometiendo un delito, entiendo que te moleste un poco, pero así son las cosas, ¿no?</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v> Defienda al agente de InterSec</v>
+        <v> Es difícil encontrar buena ayuda.</v>
       </c>
     </row>
     <row r="787" xml:space="preserve">
       <c r="A787" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Nave de Combate Informe: Se requiere asistencia urgente para un agente de InterSec que actualmente está bajo fuego en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Un grupo de forajidos había capturado previamente a nuestro agente con la intención de extraerle información confidencial, pero milagrosamente lograron escapar. Desafortunadamente, los forajidos que lo persiguen ahora lo tienen acorralado. Debido a la cantidad de naves que lo atacan, ofrecemos una compensación adicional para compensar el peligro adicional. &lt;EM4&gt;Reclutar naves adicionales&lt;/EM4&gt; para apoyarlo en esta misión es altamente recomendable. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve"> Conozco a alguien que quiere montar un negocio, pero le cuesta mucho contratar a los trabajadores cualificados que necesita. Resulta que encontró al equipo perfecto en ~mission(Location|Address), pero sus jefes no les dejan ir. Incluso contrataron guardias armados adicionales para asegurarse. Lo que quiero que hagas es ir allí y acabar con todos los guardias, asegurándote de que los trabajadores salgan ilesos.</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>Proteja los activos vitales</v>
+        <v> haciendo un desastre</v>
       </c>
     </row>
     <row r="789" xml:space="preserve">
       <c r="A789" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: Uno de nuestros pilotos está siendo atacado en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y necesita asistencia. Este operativo lleva información clave sobre un ataque coordinado a infraestructura clave de la UEE y es vital que pueda entregárnosla. Usted y cualquier &lt;EM4&gt;piloto confiable que pueda reclutar&lt;/EM4&gt; tienen la misión de protegerlo de los forajidos que lo persiguen el tiempo suficiente para que pueda escapar mediante QT. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve"> Esto es un poco agresivo para mi gusto, pero los créditos son créditos, ¿no? Tengo un cliente que busca a alguien muy motivado para ir a ~misión(Ubicación|Dirección) y matar a todos los que estén allí. Básicamente, empieza a disparar y no pares. Te pagarán cuando el lugar esté despejado.</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v> Extracción quirúrgica</v>
+        <v> coger y llevar</v>
       </c>
     </row>
     <row r="791" xml:space="preserve">
       <c r="A791" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: Un agente encubierto nuestro fue descubierto y ahora está siendo perseguido por la banda de forajidos en la que se había infiltrado. Por lo tanto, necesita ser extraído de inmediato en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Una vez en el sitio, interactúe con todos los hostiles para brindar cobertura y que nuestro agente pueda escapar mediante QT. &lt;EM4&gt;Traiga refuerzos adicionales&lt;/EM4&gt; y no subestime a estos forajidos. Son violentos y están motivados, por lo que es poco probable que se rindan pronto. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">Esta misión es perfecta para alguien como tú. Hay un paquete retenido en ~mission(Location|Address) y necesito que lo lleves a ~mission(Destination|Address). Hay un pequeño detalle que debes saber: habrá muchísima seguridad allí. Pero seguro que todo irá bien. :)</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v> Cómo gestionar el ataque de Vanduul a la nave</v>
+        <v> Tras el desastre</v>
       </c>
     </row>
     <row r="793" xml:space="preserve">
       <c r="A793" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Nave de Combate Informe: Un operador que trabaja con InterSec está siendo atacado por naves Vanduul en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. La probabilidad de que sobrevivan por sí solos es baja, por lo que buscamos un contratista dispuesto a brindar apoyo en combate. Los contratistas que acepten esta misión deben estar bien equipados y listos para enfrentar la amenaza Vanduul de frente. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">La fortuna nos sonríe una vez más. Acabo de enterarme de una batalla cerca de ~mission(Location) que acaba de tener lugar lejos de las miradas indiscretas de cualquier sistema de comunicaciones entrometido, y aún no se han enviado refuerzos de ninguna de las fuerzas involucradas. Esto significa que hay una oportunidad para que un alma emprendedora saquee el cementerio. Me gustaría ofrecer esta oportunidad a todos mis contactos de confianza. Cualquiera que esté interesado puede obtener la ubicación... por el precio adecuado. Las coordenadas se proporcionarán una vez que acepte el contrato y permanecerán disponibles hasta que decida rescindirlo. Por supuesto, la rapidez será esencial, ya que no solo se enfrentará a la posible competencia de otros rescatadores, sino también a la inminente posibilidad de que lleguen refuerzos para inspeccionar el campo de batalla. Si aún lo duda, recuerde: la fortuna favorece a los audaces. -cd</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v> Piloto bajo fuego de Vanduul</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
     <row r="795" xml:space="preserve">
       <c r="A795" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: Acabamos de perder contacto con un piloto que se enfrentó a fuerzas Vanduul en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Viaje a su última ubicación conocida y, si aún está vivo, defiéndalo el tiempo suficiente para asegurar que pueda escapar. Garantizar la seguridad del operativo es crucial, al igual que eliminar cualquier amenaza Vanduul para la UEE. Probablemente necesitará un grupo de &lt;EM4&gt;naves fuertes&lt;/EM4&gt; para neutralizar con éxito a estos Vanduul. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para ayudar en la detención de ~mission(TargetName) de ~mission(Location|Address). Somos conscientes de que puede haber civiles en el lugar, así que tenga cuidado con el posible fuego cruzado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. • Asegurar que no haya bajas civiles. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v> Terrorista ~misión(Nombre del objetivo) a neutralizar</v>
+        <v xml:space="preserve"> Evaluación de recompensas activas</v>
       </c>
     </row>
     <row r="797" xml:space="preserve">
       <c r="A797" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: InterSec ha identificado a más forajidos que planean una operación contra los intereses de la UEE desde Nyx. Su misión será neutralizar esta amenaza potencial antes de que puedan ejecutar sus planes. Viaje a &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; y envíe al líder de estos forajidos, &lt;EM4&gt;~mission(NombreObjetivo)&lt;/EM4&gt; sin dudarlo. Hemos explorado un pequeño número de naves, pero nuestro informe sugiere que son pilotos competentes; &lt;EM4&gt;se recomienda traer refuerzos.&lt;/EM4&gt; Recuerde que eliminar a estos forajidos no solo sirve a la gente de Nyx, sino también a la UEE. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que nos ayudara a capturar a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, su principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>Ataque preventivo contra ~misión(Nombre del objetivo)</v>
+        <v xml:space="preserve"> Reevaluación activa de recompensas</v>
       </c>
     </row>
     <row r="799" xml:space="preserve">
       <c r="A799" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: InterSec requiere un contratista experto para eliminar a un grupo de criminales altamente peligrosos con base en Nyx que planean un ataque coordinado contra un miembro prominente de la Armada de la UEE. Hemos interceptado información crucial que sugiere que un terrorista conocido llamado &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; pretende llevar a cabo este asesinato con la ayuda de elementos criminales locales. Actualmente se encuentran en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;, lo que hace que este sea el momento ideal para nuestro ataque. Tenga cuidado, estos forajidos son asesinos experimentados; se recomienda traer un &lt;EM4&gt;grupo de aliados de confianza&lt;/EM4&gt;. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO Aunque tu desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerte una oportunidad para redimirte. Para reevaluar tus habilidades, nos gustaría que detuvieras a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, tu principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar tu propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazadores de Recompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>Nuevo contrato de defensa: ~misión(Nombre del objetivo) Eliminación</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (ERT)</v>
       </c>
     </row>
     <row r="801" xml:space="preserve">
       <c r="A801" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha sido contratada para combatir el creciente número de forajidos que utilizan Nyx como base para sus operaciones, con la intención de atacar los sistemas UEE vecinos. Como medida preventiva, le solicitamos que viaje a &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y elimine al cabecilla &lt;EM4&gt;~misión(Nombre del Objetivo)&lt;/EM4&gt; para disuadir su ataque planeado contra Stanton. Él y su tripulación son altamente peligrosos y se le &lt;EM4&gt;aconseja que traiga un compañero&lt;/EM4&gt; para apoyo. Los contratistas que puedan demostrar ser confiables y competentes en la ejecución de operaciones serán elegibles para futuras misiones con InterSec. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo extremo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo extremo generalmente pilota una nave de clase subcapital, tiene varios aliados fuertemente armados y se espera que sea muy difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>Neutralizar la amenaza UEE: ~misión(Nombre del objetivo)</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (HRT)</v>
       </c>
     </row>
     <row r="803" xml:space="preserve">
       <c r="A803" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves de Combate Informe: Aparentemente insatisfechos con sus ganancias en Nyx, un grupo de forajidos liderado por &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; ha estado planeando un ataque importante contra la UEE. Esto no puede permitirse. Gracias al trabajo de nuestro equipo de Inteligencia, hemos podido localizarlos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Diríjanse allí lo antes posible y ataquen antes de que tengan la oportunidad de abandonar el sistema. Con base en nuestro análisis estratégico, recomendamos que una flota &lt;EM4&gt;bien armada y capacitada&lt;/EM4&gt; será necesaria para el éxito de esta misión. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de alto riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de alto riesgo generalmente pilota una nave grande con tripulación múltiple, tiene varios aliados conocidos y se espera que sea difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>Eliminar la nave Vanduul</v>
+        <v> Evaluación de recompensas activas</v>
       </c>
     </row>
     <row r="805" xml:space="preserve">
       <c r="A805" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Nave de Combate Informe: InterSec requiere los servicios de un piloto experto que esté preparado para ayudar a derribar un peligroso objetivo Vanduul que ha estado involucrado en numerosos ataques. Las incursiones Vanduul han ido en aumento recientemente, lo que representa una amenaza no solo para el sistema Nyx, sino para la UEE en su conjunto. Es imperativo que estos avistamientos sean respondidos de manera rápida y eficiente. Requerimos que vuele al último avistamiento conocido de la nave Vanduul en &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y los elimine de inmediato. Los pilotos Vanduul son altamente expertos y extremadamente peligrosos. Enfréntese al enemigo de inmediato y no dude; no mostrarán la misma piedad. Se otorgará una compensación proporcional al riesgo del contrato. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra lista actual. Para evaluar sus habilidades, nos gustaría que nos ayudara en la detención de ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>Neutralizar objetivo Vanduul</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (LRT)</v>
       </c>
     </row>
     <row r="807" xml:space="preserve">
       <c r="A807" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec necesita un piloto de combate altamente capacitado que pueda localizar y neutralizar un peligroso objetivo Vanduul. Un operador nuestro ha identificado una nave Vanduul volando en las cercanías de &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt;. Hemos recibido instrucciones estrictas de eliminar cualquier Vanduul avistado en los límites del espacio UEE, por temor a una invasión del territorio del Imperio. Traiga una &lt;EM4&gt;pequeña flota de pilotos competentes&lt;/EM4&gt; para enfrentarse y neutralizar el objetivo. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de bajo riesgo generalmente pilota una nave monoplaza, tiene varios aliados conocidos y debería ser fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>Recuperar cadáveres de Vanduul</v>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" t="str">
-        <v> Recuperar cadáveres de Vanduul</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+      </c>
+    </row>
+    <row r="809" xml:space="preserve">
+      <c r="A809" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo moderado ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo moderado generalmente pilota una pequeña nave multitripulación, tiene varios aliados conocidos y puede ser un poco difícil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v> Recuperar Vanduul Tech</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="str">
-        <v> Recuperar Vanduul Tech</v>
+        <v> Reevaluación de la detención de recompensas</v>
+      </c>
+    </row>
+    <row r="811" xml:space="preserve">
+      <c r="A811" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. Para reevaluar sus habilidades, nos gustaría que detuviera a ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v> Patrulla en el sector peligroso</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (VLRT)</v>
       </c>
     </row>
     <row r="813" xml:space="preserve">
       <c r="A813" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha recibido información de inteligencia de que los forajidos planean lanzar un ataque contra un objetivo dentro de la UEE. En un esfuerzo por evitar que esto suceda, necesitamos un contratista para patrullar un sector que creemos que estos forajidos están usando para preparar su ataque. La actividad de los forajidos en este sector es mayor de lo normal, por lo que InterSec recomienda que &lt;EM4&gt;traiga refuerzos&lt;/EM4&gt;. Cuando esté listo, diríjase al &lt;EM4&gt;marcador de ubicación&lt;/EM4&gt; en su HUD y escanee los puntos de ruta a lo largo de la ruta. Una vez que haya confirmado que todo el sector está despejado, el contratista principal recibirá una bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación consiste en una oferta no vinculante que, una vez aceptada, puede ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de muy bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de muy bajo riesgo generalmente pilota una nave monoplaza, tiene pocos aliados conocidos y debería ser relativamente fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>Patrulla el terreno de caza de Vanduul</v>
+        <v> Eliminar fuerza hostil</v>
       </c>
     </row>
     <row r="815" xml:space="preserve">
       <c r="A815" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Naves con calificación de combate Informe: Existe una creciente preocupación de que los grupos de caza Vanduul estén avanzando más en Nyx. La primera línea de defensa contra esta invasión es el aumento de patrullas. InterSec ha identificado un sector que ha visto un aumento en la actividad Vanduul y está buscando a alguien para patrullar la región y proporcionar una actualización al respecto. Comenzarás tu patrulla en un marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; enviado a tu HUD y luego escanearás una serie de puntos de ruta a lo largo de una ruta designada. Las naves Vanduul en este sector son altamente hábiles y agresivas, por lo que InterSec recomienda encarecidamente que &lt;EM4&gt;traigas varias naves listas para el combate como respaldo&lt;/EM4&gt;. InterSec comprende el inmenso peligro al que te enfrentarás en esta patrulla, por lo que enviaremos una bonificación especial de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal una vez que el sector esté despejado. Atentamente, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación constituye una oferta no vinculante que, una vez aceptada, podrá ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos rápida y seguramente en la eliminación completa del grupo de forajidos que ha tomado temporalmente el control de ~mission(Location) en ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los miembros de la fuerza hostil de forajidos; usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>Patrulla para prevenir un posible ataque.</v>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="str">
-        <v/>
+        <v> Capturar recompensa: ~misión(Nombre del objetivo) (HRT)</v>
+      </c>
+    </row>
+    <row r="817" xml:space="preserve">
+      <c r="A817" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa en ~mission(Location|Address), y creemos que finalmente podrían salir de su escondite si sus fuerzas que atacan ~mission(Location) se enfrentan a una resistencia lo suficientemente fuerte. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a los asociados criminales de ~mission(TargetName) cerca de ~mission(Location) para atraer al objetivo a campo abierto. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v> Buque de la Alianza Popular Tranquility</v>
+        <v> Recompensa asegurada: ~misión(Nombre del objetivo) (VHRT)</v>
       </c>
     </row>
     <row r="819" xml:space="preserve">
       <c r="A819" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operaciones: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: Listo para Combate Informe: Una nave de seguridad de la Alianza Popular clase Idris llamada Tranquility está actualmente en combate con una nave capital Vanduul cerca de una antigua estación de extracción QV y Intersec está buscando pilotos de combate para brindar apoyo. Desplácese rápidamente al AO y ataque a los cazas Vanduul para que la Tranquility pueda concentrarse en la nave capital. Buena suerte, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa que se ha extendido por todo ~mission(Location|Address). Esperamos que finalmente pueda sacarlos de su escondite si enfrenta a sus fuerzas en varios puntos de ataque diferentes. Con sus números suficientemente debilitados, ~mission(TargetName|Last) probablemente correrá el riesgo de ser expuesto y usted podrá enfrentarlos directamente. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Enfrentar a los asociados criminales de ~mission(TargetName) para hacer que el objetivo salga a la luz. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v> Bombardeo estratégico</v>
+        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
     <row r="821" xml:space="preserve">
       <c r="A821" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Naves de Combate con Armamento Informe: Los recursos locales han indicado que elementos de Shattered Blade están intentando reconstruir una de sus estaciones e Intersec está buscando un piloto para asegurarse de que eso no suceda. Han logrado poner en línea las defensas básicas de las torretas, pero actualmente solo tienen &lt;EM4&gt;dos relés de energía activados&lt;/EM4&gt;. Estos serán sus objetivos ya que &lt;EM4&gt;no pueden ser destruidos por armas de energía, necesitará traer armamento balístico o de artillería para ser efectivo&lt;/EM4&gt;. La reactivación de esta estación permitirá a Shattered Blade intentar recuperar una posición en este sistema y no podemos permitir que eso suceda. Buena suerte, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa UEE y la legislación del sistema aplicable.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName) en ~mission(Location|Address). Fueron vistos recientemente cerca de ~mission(Location) y se cree que todavía están en esa área. Si bien puede haber otros criminales activos en el sitio, su enfoque principal debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>Recuperar datos de Vanduul</v>
+        <v> Ajuste de la población de vida silvestre</v>
       </c>
     </row>
     <row r="823" xml:space="preserve">
       <c r="A823" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Vanduul Especificaciones del Equipo: N/A Informe: El Capitán Martel de la nave Tranquility de la Alianza Popular se comunicó para informarle que lo han reclutado para recuperar unidades de datos de la nave capital Vanduul destruida. Tenga cuidado al extraer dichas unidades y entréguelas a la Alianza Popular para su análisis una vez completada la misión. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para eliminar varias criaturas de diversas especies. Esta es una medida preventiva para asegurar que el tamaño de su población no aumente más allá de los parámetros aceptables. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar la especie objetivo en ~misión(Ubicación). • Usar la fuerza según sea necesario para eliminar a los animales. REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su Diario.</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v> Misión de extracción</v>
+        <v> Control de vida silvestre: ~misión(Criatura)</v>
       </c>
     </row>
     <row r="825" xml:space="preserve">
       <c r="A825" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Listo para Combate Informe: Intersec ha interceptado conversaciones de los canales de Shattered Blade que indican que han capturado a un piloto de seguridad de la Alianza Popular en una antigua estación de extracción que controlan. Necesitamos un piloto de combate experimentado para brindar asistencia en combate para que el piloto pueda escapar. El espacio aéreo fuera del hangar está repleto de hostiles, por lo que &lt;EM4&gt;necesitará despejar el espacio aéreo para que el piloto pueda despegar y realizar el QT de forma segura&lt;/EM4&gt;. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Por favor, ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo el propio riesgo personal del contratista y deben cumplir con la UEE y la ley del sistema cuando corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para reducir el número de ~mission(Creature) en estado salvaje a parámetros aceptables. Su población está aumentando demasiado rápido, y la reducción de algunos de sus números ayudará a garantizar que la situación no se salga de control. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar a ~mission(Creature) en ~mission(Location). • Usar la fuerza según sea necesario para eliminar a ~mission(Creature). REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio Para obtener más información sobre los animales en cuestión, consulte "The Guide to Stanton Wildlife" en su Diario.</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v> Se necesita un grupo de ataque táctico.</v>
+        <v> Proteger la ubicación y entregar materiales confidenciales.</v>
       </c>
     </row>
     <row r="827" xml:space="preserve">
       <c r="A827" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Informe del Grupo de Ataque: Hemos recibido información de que una nave de seguridad de la Alianza Popular llamada Tranquility se topó con Shattered Blade escondida en una antigua estación de extracción QV. Los detalles son escasos, pero los conectaremos con recursos locales una vez en el lugar. Intersec está buscando un equipo para intervenir y proteger a la Tranquility y a su personal. Según las conversaciones con el capitán de la Tranquility, necesitarán &lt;EM4&gt;armamento balístico y municiones para romper las defensas de la estación&lt;/EM4&gt; y, en última instancia, &lt;EM4&gt;llegar a tierra para rescatar a su piloto&lt;/EM4&gt;. &lt;EM4&gt;Reclutar naves adicionales&lt;/EM4&gt; para apoyarlos en esta misión es absolutamente crítico. Necesitarán &lt;EM4&gt;una variedad de tipos de naves&lt;/EM4&gt; para equilibrar múltiples zonas de combate en el espacio y en tierra. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Ignore este mensaje si lo ha recibido por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa UEE y las leyes del sistema, según corresponda.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional de seguridad para una operación de recuperación en ~mission(Location). La ubicación está actualmente bajo ataque y las fuerzas de seguridad en el sitio no responden y se presumen muertas. Creemos que los materiales confidenciales entregados recientemente a las instalaciones para custodia temporal fueron el objetivo del ataque. Su enfoque principal será recoger esas cajas y entregarlas en un lugar seguro. Por razones de seguridad, los materiales confidenciales se entregaron como parte de un envío más grande y se aseguraron en la bóveda automatizada. Los materiales tienen códigos de recuperación únicos que deben ingresarse en el teclado en la cinta transportadora de paquetes. Los protocolos exigen que solo los oficiales de seguridad de alto rango pueden llevar un datapad que contenga un código, pero dada la situación volátil, no podemos garantizar que los Nine Tails no se hayan apoderado de ellos. Una vez asegurados, entregue todos los materiales confidenciales a ~mission(dropoff1) para el pago. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|address). • Usar la fuerza según sea necesario para recoger los materiales confidenciales. • Entregar los materiales confidenciales a ~mission(dropoff1|address). REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate. • Acceso a una nave espacial con capacidad de transporte de carga. • Disponibilidad para despliegue inmediato. REQUISITOS DESEABLES • Experiencia en técnicas de desescalada rápida de hostilidades. • Experiencia en el transporte de carga importante.</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>Operación de bombardeo táctico</v>
+        <v>Proteger la ubicación contra amenazas menores</v>
       </c>
     </row>
     <row r="829" xml:space="preserve">
       <c r="A829" t="str" xml:space="preserve">
-        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Shattered Blade Especificaciones del Equipo: Naves de Combate con Armamento Informe: El análisis regional indica que existe un posible escondite de Shattered Blade en una antigua estación de extracción QV e Intersec está buscando un piloto para lanzar un ataque contra la infraestructura de energía de la estación. Este será un asalto de múltiples niveles, que requerirá que usted apunte y destruya componentes de la estación en el exterior y el interior. De operaciones anteriores, hemos aprendido que &lt;EM4&gt;ciertos componentes no pueden ser destruidos por armas de energía, por lo que se necesitarán armas balísticas o de munición&lt;/EM4&gt;. Partes de la estación históricamente han estado inundadas con &lt;EM4&gt;energía de distorsión pesada, por lo que deberá actuar con eficiencia mientras esté dentro&lt;/EM4&gt;. Todos estos ataques son un esfuerzo para permitirle &lt;EM4&gt;destruir el núcleo de energía ahora expuesto en el centro&lt;/EM4&gt;. La pérdida de esta estación impactará enormemente la capacidad de la banda para operar en el sistema y, por lo tanto, se ha considerado una alta prioridad. Buena suerte, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación contiene información confidencial destinada exclusivamente al destinatario. Si la recibe por error, ignórela y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la UEE y la legislación del sistema, según corresponda.</v>
+        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra cualquier amenaza menor. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>Listo para ser aprovechado</v>
+        <v> Proteger la ubicación contra amenazas moderadas</v>
       </c>
     </row>
     <row r="831" xml:space="preserve">
       <c r="A831" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Tengo buenas noticias para ti. En este preciso instante, hay una instalación automatizada que está produciendo paquete tras paquete de producto de primera calidad, prácticamente listo para ser aprovechado. Solo tienes que ir allí, lidiar con un par de matones, agarrar lo que puedas y venderlo con una gran ganancia. No debería ser ningún problema. Y hay mucha gente dispuesta a pagar bien por comprarte ese producto. Hablando de créditos, no voy a dar las coordenadas de esta instalación por pura generosidad. Creo que es justo pedir una comisión por información tan valiosa. No esperes demasiado. No sé cuánto tiempo más estará activa la página web. -Ruto</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v> Confiscar contrabando</v>
+        <v> Proteja la ubicación contra amenazas graves.</v>
       </c>
     </row>
     <row r="833" xml:space="preserve">
       <c r="A833" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados Hemos podido rastrear un reciente aumento de contrabando hasta una planta de producción automatizada en ~mission(Location|Address). No podemos asegurar cuánto tiempo más estará operativa la planta, por lo que BlacJac necesita a alguien en el lugar para inspeccionar, asegurar el contrabando y transportarlo hasta ~mission(Destination|Address). Una vez allí, pueden usar la terminal administrativa de mercancías para transferirnos el contrabando y cobrar su recompensa. No hemos podido determinar qué tipo de fuerza hostil estará presente, pero sea cual sea la que encuentren, están autorizados a usar la fuerza letal si es necesario. Cuanto más contrabando logren traernos, más créditos ganarán. Gracias, Teniente Aaron Riegert, Supervisor de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles graves. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v> Confiscar contrabando</v>
+        <v> Sitio libre de contrabando</v>
       </c>
     </row>
     <row r="835" xml:space="preserve">
       <c r="A835" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que una instalación de producción ilegal en ~mission(Location|Address) se está utilizando para fabricar contrabando. Buscamos un contratista para asegurar el sitio, confiscar el contrabando y entregarlo en ~mission(Destination|Address). La terminal administrativa de mercancías le permitirá entregar el contrabando a nuestro depósito de pruebas y cobrar su pago. Dado que se trata de una instalación automatizada, no está claro cuánto tiempo estarán fabricando ni cuántas personas podrían estar presentes. Para mayor seguridad, le recomendamos que vaya preparado para encontrar una fuerte resistencia. Su compensación total dependerá de la seguridad con la que se entreguen los paquetes como prueba. CONTRATO AUTORIZADO POR: Oficial de Enlace Vanzant ID# 712L921P</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir el contrabando que se almacena allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de contrabando; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v> Confiscar contrabando</v>
+        <v> Sitio libre de narcóticos</v>
       </c>
     </row>
     <row r="837" xml:space="preserve">
       <c r="A837" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO DEL DEPARTAMENTO DE SUBCONTRATACIÓN DE HURSTON DYNAMICS: Confiscar contrabando AFILIACIÓN DEL CONTRATISTA: Independiente GERENTE DE SUBCONTRATACIÓN: T. Odington EVALUACIÓN DE RIESGO: Alta CONTRATO URGENTE: No Hurston Security ha tenido conocimiento de una instalación de producción automatizada ilegal y activa en ~mission(Location|Address) y busca un contratista para asegurar el sitio y confiscar la mayor cantidad posible de paquetes de contrabando para su entrega a una instalación de Hurston Security en ~mission(Destination|Address) para su eliminación inmediata. La transferencia del contrabando y la atribución de su pago de recompensa deben realizarse a través de la terminal administrativa de mercancías en dicho lugar. Usted está autorizado a usar la fuerza necesaria para completar su objetivo. El pago se basará en la cantidad de contrabando incautado. ** La información transmitida puede contener material confidencial y/o privilegiado. Se prohíbe cualquier revisión, retransmisión, difusión u otro uso de esta información, o la adopción de medidas basadas en ella, por parte de personas o entidades distintas del destinatario previsto. **</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir los narcóticos que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de narcóticos; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>Confiscar contrabando</v>
+        <v> Sitio libre de drogas</v>
       </c>
     </row>
     <row r="839" xml:space="preserve">
       <c r="A839" t="str" xml:space="preserve">
-        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional de seguridad orientado a los detalles que pueda ayudarnos a asegurar el contrabando de un sitio de producción automatizado ilegal en ~mission(Location|Address). Los paquetes luego deberán ser llevados a ~mission(Destination|Address) y transferidos a nuestra posesión para su destrucción a través de la terminal administrativa de mercancías. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Gestionar cualquier hostil encontrado dentro del sitio; usando la fuerza según sea necesario. • Asegurar el contrabando y entregarlo a las terminales de mercancías en ~mission(Destination|Address) REQUISITOS MÍNIMOS • 2 años de experiencia combinada de mercenario y/o seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir las drogas que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de drogas; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v> Contrabandistas de tecnología Vanduul</v>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" t="str">
-        <v> Contrabandistas de tecnología Vanduul</v>
+        <v> Defender a los ocupantes</v>
+      </c>
+    </row>
+    <row r="841" xml:space="preserve">
+      <c r="A841" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudar de manera rápida y segura al equipo de seguridad estacionado en ~mission(Location|Address) a proteger el sitio contra amenazas hostiles. Tenga en cuenta que cualquier fuego amigo, accidental o de otro tipo, no será tolerado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar al equipo de seguridad local a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>Recuperar información adicional sobre contrabandistas.</v>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" t="str">
-        <v> Recuperar información adicional sobre contrabandistas.</v>
+        <v> Evaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="843" xml:space="preserve">
+      <c r="A843" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita profesionales de seguridad nuevos, calificados y orientados a los detalles para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que ayudara a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v> Oportunidad de transporte de carga con Ling Hauling</v>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" t="str">
-        <v> Oportunidad de transporte de carga con Ling Hauling</v>
+        <v> Reevaluación de contratistas de seguridad</v>
+      </c>
+    </row>
+    <row r="845" xml:space="preserve">
+      <c r="A845" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. En un esfuerzo por reevaluar sus habilidades, microTech Protection Services desea que ayude a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza según sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" t="str">
-        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+        <v> Desalojar a los ocupantes ilegales</v>
+      </c>
+    </row>
+    <row r="847" xml:space="preserve">
+      <c r="A847" t="str" xml:space="preserve">
+        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos de manera rápida y segura en la eliminación completa de ocupantes ilegales que han tomado temporalmente el control de ~mission(Location|Address). Tenga en cuenta que nuestra inteligencia muestra que hay trabajadores civiles en el sitio. Dado que su conexión con la pandilla no está clara, deben ser considerados no combatientes. No se tolerará ninguna acción hostil hacia ellos. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los ocupantes hostiles que se encuentren dentro del sitio; usando la fuerza si es necesario. • Garantizar la seguridad de cualquier civil que pueda estar en el sitio. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" t="str">
-        <v> Familia Ling ~misión(ReputationRank) Transporte de carga - ~escala de misión(CargoGradeToken)</v>
+        <v> URGENTE: Embarque en curso</v>
+      </c>
+    </row>
+    <row r="849" xml:space="preserve">
+      <c r="A849" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un cliente ejecutivo nos acaba de informar que su 890 Jump fue interceptada en ~mission(Location) y abordada por forajidos. Prefieren que el asunto se resuelva de forma privada debido a la naturaleza confidencial de los datos confidenciales almacenados a bordo. Su prioridad será eliminar a todos los forajidos lo antes posible para que se pueda enviar un equipo de recuperación y devolver la nave al propietario. Cuanto más tiempo tengan los forajidos el control de la nave, mayor será la probabilidad de que se pierda. Le recomiendo que consiga un equipo para esta misión para agilizar el proceso. Tenga en cuenta que, gracias a un pequeño contingente de personal de seguridad que permaneció a bordo, todos los miembros supervivientes de la tripulación pudieron escapar en una nave de escape. Se desconoce el estado actual del resto del personal de seguridad, pero por si acaso, esté atento a la presencia de aliados cuando se enfrente a los hostiles. En segundo lugar, si es posible, el cliente está muy interesado en evitar el robo de los datos mencionados. Si logra detener el robo de sus almacenes de datos confidenciales antes de que se transmitan, recibirá una generosa bonificación. Como es lógico, este es un cliente al que me gustaría mantener muy satisfecho. Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v> Ruta de reparto local de la familia Ling</v>
+        <v>Asignación de recompensa: ~misión(Nombre del objetivo) (HRT)</v>
       </c>
     </row>
     <row r="851" xml:space="preserve">
       <c r="A851" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, espero que estés disponible para hacer una entrega. ~mission(Contractor|Family) PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Avísame si puedes hacerlo. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling Coordinadora de Envíos Ling Family Hauling</v>
+        <v xml:space="preserve"> Hola, tengo un contrato para ti que requiere un poco más de estrategia de lo habitual. Un criminal de alto nivel llamado ~mission(TargetName) se esconde con un gran contingente de forajidos en ~mission(Location|Address). Nuestra información sugiere que las fuerzas de ~mission(TargetName|Last) probablemente actuarán como línea defensiva para proteger a su jefe. Supongo que tendrás que enfrentarte a ellos antes de poder acceder a ~mission(TargetName|Last). Dicho esto, no quiero que dispares indiscriminadamente. A veces, estos forajidos mantienen a civiles cerca y deben ser tratados como no combatientes. Mucha suerte, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v> La familia Ling busca nuevos contratistas.</v>
+        <v> Misión de recompensa por fuga: ~mission(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="853" xml:space="preserve">
       <c r="A853" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, somos una pequeña empresa de reparto familiar que actualmente busca nuevos contratistas en la zona de Crusader. Si te interesa trabajar con nosotros, la siguiente entrega sería una excelente prueba para ver si encajas bien con la empresa. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si todo sale bien, te convertirás en el miembro más reciente de Ling Family Hauling. Por último, probablemente sería buena idea traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+        <v xml:space="preserve">El delincuente convicto ~mission(TargetName) se ha fugado de un centro de rehabilitación local y Northrock ha sido contratado para devolverlo a prisión. En mi experiencia, los presos fugados no suelen rendirse pacíficamente, así que utilicen cualquier método posible para encontrarlo y someterlo. Podría ser conveniente vigilar los lugares donde podría intentar borrar sus antecedentes penales. No sería la primera vez que un preso intenta borrar su condena tras fugarse. Buena suerte en la búsqueda, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v> Reevaluación del contratista Ling</v>
+        <v> Contrato provisional de recompensa por fuga</v>
       </c>
     </row>
     <row r="855" xml:space="preserve">
       <c r="A855" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, no me entusiasma tener que hacer esto, pero tenemos escasez de contratistas y más entregas que nunca. Estoy dispuesto a darte otra oportunidad, pero necesitas completar la siguiente entrega. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Por último, probablemente sería buena idea llevar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+        <v xml:space="preserve">Hola, mi nombre es Braden Corchado y soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera en el sistema Stanton. Puede que ya te haya contactado, pero nos esforzamos por contactar a cualquier persona que cumpla con nuestros altos estándares y animarla a completar un contrato temporal. No hay mejor opción que ser contratista de Northrock. Tenemos una sólida reputación por ofrecer trabajo desafiante e interesante con una remuneración superior a la de muchos de nuestros competidores en el sistema. Para ser aprobado, deberás capturar a ~mission(TargetName). Recientemente escapó del centro de detención y tu trabajo consistirá en localizarlo antes de que desaparezca por completo. Un pequeño consejo: es probable que el objetivo intente limpiar su historial. Te recomiendo triangular tu búsqueda entre el centro de detención del que escapó y los lugares donde pueda acceder al sistema de registros. Si lo logras, veremos si podemos ofrecerte más trabajo. Espero tener noticias suyas pronto, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>Entrega de paquetes para Ling</v>
+        <v>Contrato provisional de recompensa para fugitivos (reevaluación)</v>
       </c>
     </row>
     <row r="857" xml:space="preserve">
       <c r="A857" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, necesitamos que recojas un paquete en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y lo lleves a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Originalmente iba a enviar a mi hermano Ricki, pero dijo que la zona es demasiado peligrosa. Supongo que ha habido varias advertencias de seguridad por allí, pero mientras tengas cuidado y lleves armas o algo así, seguro que no tendrás problemas. Probablemente ni siquiera te topes con nada. Gracias, Conni Ling, Coordinadora de Envíos, Ling Family Hauling</v>
+        <v xml:space="preserve"> Hola, sé que ha pasado un tiempo, pero si todavía te interesa trabajar por contrato para Northrock, convencí a la gerencia para que te hicieran una reevaluación. Si logras completar con éxito una misión de recompensa, podemos ver si podemos restituirte tu puesto. Este contrato temporal consiste en localizar al criminal fugado ~mission(TargetName). Haz todo lo posible por encontrarlo antes de que borre su registro en el punto de acceso a la base de datos, o el trabajo será mucho más difícil. Esperamos poder confiar en ti. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
+        <v> Detener sospechoso: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v> &lt;= MARCADOR DE POSICIÓN =&gt;</v>
+        <v> ~misión(Contratista|DescripciónPVPRecompensa)</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v> Oportunidades de empleo en seguridad de Eckhart</v>
-      </c>
-    </row>
-    <row r="861">
-      <c r="A861" t="str">
-        <v> ~misión(Descripción)</v>
+        <v> Detención provisional del sospechoso</v>
+      </c>
+    </row>
+    <row r="861" xml:space="preserve">
+      <c r="A861" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, espero que no le importe, pero me enteré de su pertenencia al Gremio de Cazadores de Recompensas y quería ponerme en contacto con usted para ver si estaría interesado en colaborar con Northrock Service Group, una de las empresas de seguridad privada mejor valoradas del sistema. Si es así, el primer paso sería completar una detención provisional del sospechoso. No se trata tanto de una evaluación, sino más bien de una oportunidad para asegurarnos de que podemos establecer una buena relación laboral. El sospechoso que busca se conoce como &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;. Se sabe que es particularmente escurridizo, así que puede que tenga un trabajo arduo por delante. Espero tener noticias suyas pronto. Atentamente, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v> Supervisión de la producción</v>
-      </c>
-    </row>
-    <row r="863">
-      <c r="A863" t="str">
-        <v> ~misión(Contratista|Descripción del producto farmacéutico de entrega local)</v>
+        <v> Detención provisional de sospechoso (reevaluación)</v>
+      </c>
+    </row>
+    <row r="863" xml:space="preserve">
+      <c r="A863" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola de nuevo, hace tiempo que no hablamos, espero que todo esté bien. Sé que las cosas no terminaron de la mejor manera, pero después de hablarlo con la gerencia, me gustaría ofrecerte una oportunidad para redimirte. Tenías potencial y me da mucha pena que no hayas tenido la oportunidad de demostrar de lo que eres capaz. Completa la misión &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y veremos cómo podemos restituirte en tu puesto. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v> Una tanda hecha desde cero</v>
+        <v> Operación de recuperación</v>
       </c>
     </row>
     <row r="865" xml:space="preserve">
       <c r="A865" t="str" xml:space="preserve">
-        <v xml:space="preserve">Normalmente, me gusta cocinar todo desde cero. Me enorgullece el producto y todo eso. Pero de vez en cuando, ya sea por mucha demanda, mucho calor o lo que sea, necesito recurrir a otros laboratorios para un pedido. Sin embargo, aquí estoy muy ocupado, así que me vendría bien alguien que me ayudara a supervisar toda la línea de producción. No se me ocurre nadie mejor ni más disponible que tú. ~Misión (Itinerario) Simplemente no te distraigas ni te desvíes del camino. Sucede más a menudo de lo que crees. Si logras completar la lista, me aseguraré de que recibas una buena parte de las ganancias. -Wallace</v>
+        <v xml:space="preserve">Aquí está el trato: un cliente nuestro (que debería haber gastado los créditos extra en una escolta de Northrock) sufrió un ataque a una de sus naves y ahora necesita que lideremos una operación de recuperación de un paquete importante que fue robado. Por suerte, tuvimos un golpe de suerte y pudimos localizar a los responsables en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;. Necesitamos que vayas allí y recuperes el paquete. Podrás identificarlo por su número de serie: &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt;. Supongo que los forajidos van a oponer resistencia, pero recuerda que no son la prioridad. Una vez que tengas el paquete, llévalo de vuelta al cliente en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Una última cosa, asegúrate de llevar una nave con suficiente espacio para carga. No queremos que llegues hasta allí en tu Gladius o lo que sea solo para tener que regresar. Enorgullécenos, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group *RESUMEN DE LA OPERACIÓN DE RECUPERACIÓN* * Recuperar el paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; * Entregar en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v> Capturan al miembro de la pandilla de Arlington, Les Arlington</v>
-      </c>
-    </row>
-    <row r="867" xml:space="preserve">
-      <c r="A867" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Una comunicación anónima nos ha avisado de que Les Arlington, hijo del líder de la banda Maltrox Arlington, había sido visto recogiendo una entrega en un centro de transferencia de Covalex. Le proporcionaremos las coordenadas de donde creemos que se encuentran actualmente. Les es un piloto experimentado que lleva volando casi tanto tiempo como ellos llevan caminando y suele ser el piloto de escape de la banda. Podría ser conveniente traer naves de apoyo adicionales para frustrar cualquier intento de fuga. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v>Asignación de recompensa: Orden de arresto grupal (MRT)</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>Captura de Nicks Cantwell, miembro de la pandilla de Arlington.</v>
-      </c>
-    </row>
-    <row r="869" xml:space="preserve">
-      <c r="A869" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de arresto grupal para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero de reparación. Si bien el robo fue detenido, los miembros del grupo se han dispersado en la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. Hemos recibido información de que Nicks Cantwell, conocido de larga data y confidente de Maltrox Arlington, fue visto intentando comprar un láser de minería de alta densidad, del tipo que se usa frecuentemente en intentos de secuestro de naves para perforar estratégicamente los cascos. Hemos proporcionado las coordenadas de la última ubicación conocida de Nicks. Nicks es un experto en municiones muy respetado en los círculos criminales y suele dejar un rastro de destrucción a su paso. Se recomienda aumentar la potencia de fuego en este encuentro. Usted está autorizado a usar la fuerza que sea necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Asignación de recompensa: Orden de arresto grupal (HRT)</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>Captura a Sam 'Weepy' Arlington, miembro de la pandilla de Arlington.</v>
-      </c>
-    </row>
-    <row r="871" xml:space="preserve">
-      <c r="A871" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Sam 'Weepy' Arlington fue marcado por sistemas de seguridad automatizados en un R&amp;R después de estar involucrado en una pelea de borrachos. Weepy logró abandonar la estación antes de que llegaran los equipos de respuesta, pero hemos podido localizarlo en el lugar donde creemos que se encuentra escondido. Weepy es tío y principal ejecutor del líder de la pandilla, Maltrox Arlington. Sus problemas de ira, sumados a un largo historial de abuso de sustancias, lo convierten en un verdadero impredecible. Espere que oponga una resistencia considerable cuando usted y sus fuerzas lo acorralen. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v> Asignación de recompensa: Orden de arresto grupal (VHRT)</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>Captura de un miembro de la pandilla de Arlington en Oslo, Arlington.</v>
-      </c>
-    </row>
-    <row r="873" xml:space="preserve">
-      <c r="A873" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado a la oscuridad. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Recientemente, se accedió ilegalmente a una terminal de seguridad utilizando una criptoclave personalizada única que había sido utilizada en un robo el año pasado por un tal Oslo Arlington, el hermano menor del líder de la banda Maltrox Arlington. Aunque no podemos confirmar con certeza si Oslo hackeó la terminal, consideramos que vale la pena investigarlo. Oslo, un estratega de renombre, sumamente inteligente y experto en tecnología, ha demostrado ser difícil de capturar en el pasado. Si esta pista conduce a su localización, un equipo de ataque táctico bien coordinado sería fundamental para el éxito de la operación. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al finalizar el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. Dicha información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v> Asignación de recompensa: Orden de grupo (ERT)</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="str">
+        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>Captura de Kass Dent, miembro de la pandilla de Arlington.</v>
+        <v> Contrato de garantía grupal pro tempore</v>
       </c>
     </row>
     <row r="875" xml:space="preserve">
       <c r="A875" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado al espacio profundo. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Dos guardias de banco fueron reportados como desaparecidos la semana pasada. Hace unas horas, sus cuerpos aparecieron en un montón de basura en Magnus con sus datos biométricos robados. Afortunadamente, un puesto de dumplings cercano tenía una cámara de seguridad que captó el momento en que arrojaron los cadáveres. El reconocimiento facial permitió identificar a Kass Dent, pareja sentimental de Maltrox Arlington y padre de Les Arlington. Usando el video para reconstruir la cronología, hemos proporcionado las coordenadas del lugar donde se cree que Kass se esconde actualmente. Se sospecha que Kass es responsable de una larga lista de asesinatos, siendo estos dos los más recientes. Recomendamos traer solo a personas altamente capacitadas para intentar minimizar el número de víctimas. Usted está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se realizará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Hola, espero que todo vaya bien. Puede que ya te haya contactado, pero quería asegurarme de presentarme. Soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera actualmente en el sistema Stanton, que proporciona una variedad de servicios a todos los principales organismos gubernamentales, así como a varias empresas privadas. El motivo por el que me pongo en contacto contigo es porque creemos que alguien con tus habilidades podría ser muy valioso para nuestros clientes. Además, creo que seríamos una buena opción para ti. Nuestros contratistas suelen recibir una remuneración más alta que muchos de nuestros competidores en el sistema, y muchos de ellos me comentan lo mucho que disfrutan del trabajo desafiante e interesante que les ofrecemos. Ahora bien, Northrock se rige por estándares muy altos, por lo que antes de que podamos formalizar nada, tendrás que obtener la aprobación como contratista completando un contrato provisional. Esperaba que pudieras capturar a varios miembros buscados de una banda de forajidos: ~misión(Objetivo1), ~misión(Objetivo2) y ~misión(Objetivo3). Una vez que lo hagas, veremos si podemos conseguirte más trabajo. Espero tener noticias tuyas pronto. Atentamente, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>Captura de Maltrox Arlington, líder de la pandilla de Arlington.</v>
+        <v>Orden de reevaluación del grupo provisional</v>
       </c>
     </row>
     <row r="877" xml:space="preserve">
       <c r="A877" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO ********* __Información de antecedentes__ Se ha emitido una orden de grupo para la notoria banda de secuestradores de naves Arlington después de su reciente y descarado intento de robo de un Idris de un astillero. Si bien el robo fue detenido, los miembros del grupo se han dispersado en el espacio. Eckhart Security ha recibido la recompensa por la captura inmediata de todos los miembros de alto nivel de la banda: Maltrox Arlington, Kass Dent, Nicks Cantwell, Sam 'Weepy' Arlington, Oslo Arlington y Les Arlington. ********* Maltrox Arlington ha estado manteniendo un perfil bajo últimamente, pero creemos que ha salido de su escondite. Una patrulla estaba reabasteciendo combustible en una estación cuando una de sus naves fue potenciada. Maltrox es el sospechoso más probable. Aunque el registro de la nave estuvo desactivado temporalmente, hemos podido rastrear su firma cuántica y le hemos facilitado las coordenadas. La banda de Arlington, criminal de tercera generación, ha estado bajo el liderazgo de Maltrox durante los últimos seis años. Tenga en cuenta que se trata de un objetivo inteligente, agresivo y muy peligroso. Cuantos más recursos pueda aportar, mayores serán las probabilidades de que logremos capturar a Maltrox de una vez por todas. Está autorizado a usar la fuerza necesaria para neutralizar al objetivo. El pago se efectuará al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve"> Hola, he estado reflexionando sobre todo lo sucedido y decidí hablar con la gerencia. Han accedido a darte otra oportunidad, pero solo si completas con éxito un contrato para nosotros. Podemos considerar la posibilidad de restituirte en tu puesto si logras capturar a este trío criminal: ~misión(Objetivo1) ~misión(Objetivo2) ~misión(Objetivo3). Evadieron al último asociado que los persiguió, así que si los capturas a todos, sin duda ganarás puntos. Espero que hayas enderezado tu vida desde tu último trabajo. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>Idris robado por una banda de Arlington</v>
+        <v> Ayuda al bloqueo</v>
       </c>
     </row>
     <row r="879" xml:space="preserve">
       <c r="A879" t="str" xml:space="preserve">
-        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Orden de grupo ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO Parece que la segunda vez es la vencida para la banda de Arlington. Después de un intento fallido, la familia criminal recientemente fugada ha logrado robar un Idris de un astillero. Ahora sabemos para qué eran el láser de minería y la biometría que robaron. Dado que tuvimos tanto éxito capturándolos la primera vez, Eckhart Security ha recibido la orden de arresto de la banda. Esto requerirá una potencia de fuego considerable para derribar una nave capital de esta capacidad. Usted está autorizado a usar la fuerza que sea necesaria para rastrear el Idris y neutralizar a la banda. El pago se emitirá al completar con éxito el contrato y se ajustará según la evaluación final de su calificación de efectividad en combate y la de su equipo. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Ahora que Crusader ha encontrado su flota, parece que los Nueve Colas por fin se han dado cuenta de lo útil que puede ser un poco de ayuda extra. En resumen, buscan mercenarios para mantener a raya a Crusader. Tú y todos los demás que se ofrezcan voluntarios recibiréis una recompensa por cada nave de seguridad que derribéis. Y, además, si mantenéis a Crusader ocupado el tiempo suficiente para que los Nueve Colas terminen con lo que sea que estén tramando con este bloqueo cuántico, recibiréis una generosa bonificación.</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>Se emite la orden de compra grupal.</v>
+        <v> Bloqueo ilegal: Neutralización de la Flota de Nueve Colas</v>
       </c>
     </row>
     <row r="881" xml:space="preserve">
       <c r="A881" t="str" xml:space="preserve">
-        <v xml:space="preserve"> TIPO DE CONTRATO: Orden de arresto grupal ESTADO DEL CONTRATISTA: Independiente Código de aprobación: = ~mission(Contractor|ApprovalCode) PARA PROCESAMIENTO INMEDIATO En relación con un delito cometido conjuntamente, se ha emitido una orden de arresto grupal para: ~mission(Target1) ~mission(Target2) ~mission(Target3) Actualmente se cree que ya no viajan juntos para evadir la captura y que pronto podrían huir del sistema. Debería considerar seriamente reclutar ayuda adicional para ejecutar todas las órdenes de arresto en el plazo limitado. Está autorizado a usar la fuerza que sea necesaria para neutralizar a los objetivos. El pago se emitirá al completar con éxito el contrato cuando todos los objetivos hayan sido neutralizados en el tiempo asignado. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
+        <v xml:space="preserve">Crusader Security ha confirmado la ubicación de la flota forajida de los Nueve Colas y se está movilizando para poner fin al bloqueo cuántico de ~mission(Location). Buscamos nuevamente profesionales de seguridad capacitados para unirse a nuestros esfuerzos de respuesta de emergencia y ayudar a neutralizar esta peligrosa amenaza. Antes de aceptar, tenga en cuenta que se espera que los Nueve Colas ofrezcan una resistencia considerable y que, hasta que se levante el bloqueo, no será posible realizar viajes cuánticos en el sector. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v> ¿Necesitas una salida?</v>
+        <v> Lejos de miradas indiscretas</v>
       </c>
     </row>
     <row r="883" xml:space="preserve">
       <c r="A883" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. Todavía no hemos tenido la oportunidad de trabajar juntos, pero estoy en un aprieto y necesito a alguien más. No gratis, por supuesto. Me gusta el intercambio. Uno de mis socios, que estuvo cumpliendo condena en Klescher, debía traerme un chip de datos, pero luego dejó de dar señales de vida. Supongo que está muerto, pero aquí está el trato: si terminas su trabajo, borro tu historial delictivo. No está mal, ¿verdad? Tu predecesor planeaba usar unos túneles viejos para escapar. Dio a entender que no eran precisamente fáciles de acceder, pero confío en que podrás resolverlo. Supongo que encontrarás su cuerpo por ahí y, si tenemos suerte, todavía tendrá el chip. Una vez que lo consigas, termina de escapar como puedas. Luego, tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me sorprendería que te los encontraras. Después de obtener los datos y validarlos, borraré tu historial delictivo. Entonces podrás disfrutar de tu recién descubierta libertad. Si lo haces bien, tal vez tenga un trabajo más lucrativo para ti en el futuro.</v>
+        <v xml:space="preserve">Les dije a los Nueve Colas que bloquear los viajes cuánticos para mantener toda una zona como rehén iba a atraer la atención equivocada, pero ¿me hacen caso? No. Ahora Crusader tiene docenas de naves de escaneo por ahí husmeando en cosas que prefiero mantener ocultas. Por eso estoy intentando contratar a tanta gente como pueda para que me ayude. Quiero pagarte por cada nave de escaneo de Crusader que destruyas. De hecho, incluso aumentaré tu tarifa por nave si todos alcanzan un cierto número de bajas. Llámalo incentivo por rendimiento. Y si de verdad te sientes con ganas de superarte, elimina a cualquier tonto lo suficientemente valiente como para intentar transportar carga a la estación bloqueada. Tengo algunos proveedores que agradecerán la demanda extra.</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>ayudémonos mutuamente</v>
+        <v> Bloqueo ilegal: se busca al responsable de la flota de las Nueve Colas.</v>
       </c>
     </row>
     <row r="885" xml:space="preserve">
       <c r="A885" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. Oí que acabaste en Klescher, lo cual es una verdadera lástima. Pero en realidad podría ser un día de suerte para ambos. En resumen, tenía a alguien sacando un chip de datos de la prisión, pero nunca volvió a contactarme. Sé con certeza que no ha salido de las instalaciones, así que creo que algo le pudo haber pasado. Aunque es trágico, el trabajo debe continuar. Si puedes conseguir el chip y terminar el trabajo, puedo borrar tu historial criminal. ¿Qué dices? Claro, no sé exactamente hasta dónde llegó, pero puedo decirte que la prisión tiene toda una red de túneles ocultos que mi tipo planeaba usar para escapar. Supongo que su cadáver se está pudriendo por ahí. Cuando encuentres el cuerpo, espero que el chip todavía esté con él. Cuando lo tengas, termina de escapar y tráeme los datos. Hay un lugar cerca donde puedes subir el contenido del chip. Una advertencia: ten cuidado con la Seguridad de Hurston. Últimamente han sido un fastidio, así que no me extrañaría que te los encontraras. Cuando tenga los datos, borraré tu historial delictivo y listo, quedarás libre de toda sospecha. Lo que hagas después es decisión tuya.</v>
+        <v xml:space="preserve">Crusader Security ha descubierto que la organización criminal conocida como los Nueve Colas ha establecido un bloqueo ilegal alrededor de ~mission(Location) y ha detenido todo el tráfico cuántico entrante y saliente en el sector. Es necesario localizar la flota ilegal y levantar el bloqueo. Solicitamos urgentemente a cualquier profesional de seguridad capacitado en el sistema que se una a las fuerzas de Crusader Security y proteja nuestras naves de escaneo mientras buscan la ubicación de la flota de los Nueve Colas que está causando este bloqueo. Tenga en cuenta que, con el viaje cuántico desactivado y numerosos enemigos en la zona, esta debe considerarse una operación de alto riesgo. Se recomienda encarecidamente que todos los pilotos que participen en esta operación de respuesta de emergencia cuenten con el equipo adecuado y el tanque de combustible lleno. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>Violación y robo</v>
+        <v> Bloqueo ilegal: se necesitan suministros médicos.</v>
       </c>
     </row>
     <row r="887" xml:space="preserve">
       <c r="A887" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. Los Nueve Colas tienen un pequeño problema. Resulta que tienen un pequeño negocio paralelo en el tráfico clandestino de órganos. Un tema que prefiero evitar, pero un trabajo es un trabajo, ¿no? Parece que una de sus carnicerías móviles a bordo del 'October Rising' fue asaltada por seguridad privada mientras trabajaba. Ahora los Nueve Colas están dispuestos a romper lazos con el barco y su tripulación (que probablemente ya estén todos muertos), pero necesitan que les extraigan una caja en particular. Supongo que era un pedido especial o algo así. En fin, suban al October Rising, consigan el paquete y salgan. La seguridad sigue por ahí, así que tengan cuidado y tal vez traigan a algunos amigos, pero recuerden, su prioridad es el paquete. Si quieren ahorrarse problemas, también podrían apagar la zona desactivando la antena de comunicaciones más cercana si quieren evitar que los arresten por, ya saben, matar a un montón de guardias de seguridad. Pero bueno, hagan lo que quieran. Cuando salgas, deja el paquete en la clínica de Grim HEX y yo me encargaré del pago. Pan comido, Ruto.</v>
+        <v xml:space="preserve">El bloqueo cuántico ilegal de ~mission(Location) ha interrumpido las rutas comerciales habituales y los productos esenciales escasean. Crusader Security busca comerciantes y transportistas para suministrar los suministros médicos que tanto necesita la estación. Los precios ofrecidos por la administración de la estación se ajustarán para reflejar la situación con los Nine Tails y, además, Crusader otorgará una bonificación por riesgo al entregar con éxito los suministros médicos debido al mayor riesgo. Gracias de antemano por su apoyo durante estos tiempos difíciles. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>consigue los productos</v>
-      </c>
-    </row>
-    <row r="889" xml:space="preserve">
-      <c r="A889" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, hace poco escuché información confidencial de que ~mission(location|address) recibió material confidencial de gran interés para un conocido mío. Es tan interesante que están dispuestos a pagar para que alguien asalte las instalaciones, se apodere del material y lo entregue en ~mission(DropOff1|address). Supongo que habrá mucha seguridad, que probablemente opondrá resistencia, así que llevaría un par de armas. Se rumorea que el material confidencial se entregó en un envío junto con otras cosas y ahora se encuentra almacenado en la bóveda automatizada de las instalaciones. Los oficiales de seguridad de alto rango llevan tabletas con códigos de acceso a la bóveda. Tendrás que conseguir una tableta antes de usar la cinta transportadora para recuperar las cajas. Si necesitas un incentivo adicional, he visto el manifiesto y puedo confirmar que las otras cajas almacenadas en las instalaciones son de primera calidad. A mi cliente no le importa lo que les pase, así que puedes hacer lo que quieras con ellas. Si lo gestionas bien, esas cajas adicionales podrían suponer una buena ganancia extra, además de la tarifa de envío.</v>
+        <v> Iniciativa Overdrive: Emboscada contra Xenoamenazas - Se necesita apoyo</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="str">
+        <v/>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>suministro limitado</v>
+        <v> ALERTA DE LAS FDI: Emboscada de xenoamenazas - Se necesita apoyo</v>
       </c>
     </row>
     <row r="891" xml:space="preserve">
       <c r="A891" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Parece que hay un nuevo advenedizo en el sector que no ha estado pagando lo que le corresponde. Para darles una lección, mi cliente quiere que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Los matones de bajo nivel que tienen allí probablemente armarán un escándalo e intentarán detenerte. Haz lo que quieras con ellos, pero lo más importante es deshacerte de la droga.</v>
+        <v xml:space="preserve">*PARA PUBLICACIÓN INMEDIATA EN TODO EL SISTEMA* Atención, fuerzas de XenoThreat comenzaron a emboscar a los convoyes navales que transportaban suministros vitales mientras se dirigían a la estación Jericho en el Pyro Gateway en el Sistema Stanton. La Armada ha solicitado a las fuerzas de CDF que ayuden a recuperar estos suministros de los restos y entregarlos de forma segura a Jericho. La Armada ha organizado un estipendio comunitario para gestionar la distribución del pago. Este se distribuirá entre todos los voluntarios de CDF en intervalos asignados. Aparecerá un indicador en su HUD para medir estos pagos. Tenga en cuenta que algunos de estos suministros son altamente volátiles si no se manipulan correctamente. Tenga precaución al transportar estos materiales: * Zeta-Prolanide se degrada con el tiempo hasta descomponerse por completo. * AcryliPlex Composite se vuelve explosivamente inestable si se daña. * Diluthermex libera un pulso de energía destructivo si se expone al viaje cuántico. Además, si bien no es tan volátil, la Armada aún necesita urgentemente los suministros de DynaFlex perdidos durante el ataque para completar las reparaciones del Javelin, por lo que su recuperación debe ser prioritaria. Asimismo, es posible que aún haya hostiles de XenoThreat en la zona, así que tengan cuidado. Se insta a los voluntarios de las CDF con experiencia en combate a contribuir asegurando estas áreas de las fuerzas XenoThreat que aún persistan. La SAIC Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v> liquidación de inventario</v>
+        <v>Iniciativa Overdrive: Ataque a XenoThreat</v>
       </c>
     </row>
     <row r="893" xml:space="preserve">
       <c r="A893" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Un cliente mío está intentando negociar un acuerdo, pero no está teniendo mucha suerte. La otra parte cree tener toda la ventaja porque tiene un gran inventario a su disposición. Para facilitar las negociaciones, necesito que vayas a ~mission(Location|Address) y destruyas toda la droga del lugar. Debería advertirte que el sitio está protegido por gente muy peligrosa, así que llegar al alijo va a ser complicado, pero confío en que encontrarás la manera.</v>
+        <v xml:space="preserve"> Atención, las fuerzas navales se han reagrupado para el asalto final que XenoThreat ha estado planeando. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. Esto incluye a voluntarios que no hayan participado en la Iniciativa Overdrive. La suboficial Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y dirigirá la operación. Si tiene éxito, se completará esta serie de la Iniciativa Overdrive y recibirá acceso temporal a los F7A Hornet o una actualización gratuita si actualmente posee un F7C.</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v> Agotado</v>
+        <v> ALERTA DE CDF: Ataque a XenoThreat</v>
       </c>
     </row>
     <row r="895" xml:space="preserve">
       <c r="A895" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de mis clientes se ha enfadado al enterarse de que alguien está invadiendo su territorio. Ahora, en lugar de optar por la vía tradicional de matar a algunas personas y armar un escándalo, ha decidido enviar un mensaje diferente. Vas a ir a ~misión(Ubicación|Dirección) y destruir toda la droga del lugar. Claro que, si alguien quiere pelear contigo, puedes defenderte, pero lo más importante es deshacerte de la droga.</v>
+        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención: las fuerzas navales se han reagrupado para un asalto final contra la manada de forajidos XenoThreat que ha estado asolando el Sistema Stanton. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. La suboficial Rowena Dulli, de la División de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v> demasiados cocineros</v>
-      </c>
-    </row>
-    <row r="897" xml:space="preserve">
-      <c r="A897" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Un cliente está siendo superado por un nuevo competidor y busca sabotear el negocio. Dirígete a ~mission(Location|Address) y elimina a todos los civiles que trabajan allí. Haz lo que quieras con los matones armados que custodian a los trabajadores, pero recuerda que no son la prioridad.</v>
+        <v> dinero de la nada</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="str">
+        <v> ¿Alguna vez has deseado que aparecieran créditos por arte de magia? Varias terminales de crédito antiguas de CCB están activas y simulan transacciones bancarias para desviar fondos a quien las controle. Si te interesa, te vendo las coordenadas por una pequeña comisión. Date prisa si quieres aprovechar la oportunidad. No sé cuánto tiempo seguirá funcionando.</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v> Vive y deja que un contratista independiente se vengue.</v>
+        <v> Recursos adicionales para la investigación</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v xml:space="preserve">Todo el mundo guarda rencor, ¿no? O sea, cuando te pillan cometiendo un delito, entiendo que te moleste un poco, pero así son las cosas, ¿no?</v>
+        <v/>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v> Es difícil encontrar buena ayuda.</v>
-      </c>
-    </row>
-    <row r="901" xml:space="preserve">
-      <c r="A901" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Conozco a alguien que quiere montar un negocio, pero le cuesta mucho contratar a los trabajadores cualificados que necesita. Resulta que encontró al equipo perfecto en ~mission(Location|Address), pero sus jefes no les dejan ir. Incluso contrataron guardias armados adicionales para asegurarse. Lo que quiero que hagas es ir allí y acabar con todos los guardias, asegurándote de que los trabajadores salgan ilesos.</v>
-      </c>
-    </row>
-    <row r="902">
-      <c r="A902" t="str">
-        <v> haciendo un desastre</v>
-      </c>
-    </row>
-    <row r="903" xml:space="preserve">
-      <c r="A903" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Esto es un poco agresivo para mi gusto, pero los créditos son créditos, ¿no? Tengo un cliente que busca a alguien muy motivado para ir a ~misión(Ubicación|Dirección) y matar a todos los que estén allí. Básicamente, empieza a disparar y no pares. Te pagarán cuando el lugar esté despejado.</v>
+        <v> Recursos vitales necesarios para la investigación</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="902" xml:space="preserve">
+      <c r="A902" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesito recursos para la investigación.</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="str">
+        <v/>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v> coger y llevar</v>
+        <v> Ruta de envío local de Red Wind</v>
       </c>
     </row>
     <row r="905" xml:space="preserve">
       <c r="A905" t="str" xml:space="preserve">
-        <v xml:space="preserve">Esta misión es perfecta para alguien como tú. Hay un paquete retenido en ~mission(Location|Address) y necesito que lo lleves a ~mission(Destination|Address). Hay un pequeño detalle que debes saber: habrá muchísima seguridad allí. Pero seguro que todo irá bien. :)</v>
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Recibimos una solicitud de ~mission(Pickup1|Address) indicando que tienen una buena cantidad de paquetes esperando en ~mission(Pickup1) que necesitan ser entregados. Antes de aceptar el contrato, asegúrese de tener una nave con suficiente espacio. Un rayo tractor tampoco vendría mal. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; SOMOS UNA EMPRESA QUE OFRECE IGUALDAD DE OPORTUNIDADES: Red Wind Linehaul es y siempre ha sido una empresa que ofrece igualdad de oportunidades. Si cree que puede hacer un buen trabajo para nosotros, no dude en inscribirse.</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v> Tras el desastre</v>
+        <v>Servicio de mensajería discreta Red Wind</v>
       </c>
     </row>
     <row r="907" xml:space="preserve">
       <c r="A907" t="str" xml:space="preserve">
-        <v xml:space="preserve">La fortuna nos sonríe una vez más. Acabo de enterarme de una batalla cerca de ~mission(Location) que acaba de tener lugar lejos de las miradas indiscretas de cualquier sistema de comunicaciones entrometido, y aún no se han enviado refuerzos de ninguna de las fuerzas involucradas. Esto significa que hay una oportunidad para que un alma emprendedora saquee el cementerio. Me gustaría ofrecer esta oportunidad a todos mis contactos de confianza. Cualquiera que esté interesado puede obtener la ubicación... por el precio adecuado. Las coordenadas se proporcionarán una vez que acepte el contrato y permanecerán disponibles hasta que decida rescindirlo. Por supuesto, la rapidez será esencial, ya que no solo se enfrentará a la posible competencia de otros rescatadores, sino también a la inminente posibilidad de que lleguen refuerzos para inspeccionar el campo de batalla. Si aún lo duda, recuerde: la fortuna favorece a los audaces. -cd</v>
+        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tengo otro trabajo especial para el que podrías contar contigo. Debería ser un viaje rápido. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;) LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Y por favor recuerda no molestar a los clientes ni a ninguno de sus invitados. La profesionalidad es clave aquí.</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+        <v> Viento Rojo necesita mensajeros discretos</v>
       </c>
     </row>
     <row r="909" xml:space="preserve">
       <c r="A909" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para ayudar en la detención de ~mission(TargetName) de ~mission(Location|Address). Somos conscientes de que puede haber civiles en el lugar, así que tenga cuidado con el posible fuego cruzado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. • Asegurar que no haya bajas civiles. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Sé que has hecho un buen trabajo para nosotros en el pasado, así que pensé en preguntarte si te interesaría encargarte de un viaje especial que está un poco más lejos de lo que has estado haciendo hasta ahora. En resumen, necesitamos un piloto que esté dispuesto a trabajar con discreción, concentrarse en entregar los paquetes y, lo más importante, no hacer muchas preguntas. Verás, para una empresa pequeña como la nuestra, mantenernos por delante de la competencia significa que necesitamos ofrecer a nuestros clientes algo que no pueden obtener en ningún otro lugar: discreción. En Red Wind, siempre que tengas los créditos, llevaremos lo que sea a donde sea. ¿Entendido? Si eso te parece bien, veamos cómo te va en esta carrera: PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Un último consejo: probablemente sería bueno evitar retrasos innecesarios una vez que los paquetes estén a bordo, por ejemplo, que sean registrados por las fuerzas del orden locales.</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v xml:space="preserve"> Evaluación de recompensas activas</v>
+        <v>Manipulador de paquetes de Red Wind</v>
       </c>
     </row>
     <row r="911" xml:space="preserve">
       <c r="A911" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que nos ayudara a capturar a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, su principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Parece que hubo un pequeño problema logístico en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitan a alguien que se asegure de que los paquetes extraviados terminen donde se supone que deben ir dentro de las instalaciones. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; LA CONFIANZA ES BIDIRECTA: al aceptar este contrato, usted se compromete a no estafarnos, y Red Wind Linehaul se compromete a tratarlo de la misma manera.</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v xml:space="preserve"> Reevaluación activa de recompensas</v>
+        <v>Ruta de reparto local de Red Wind</v>
       </c>
     </row>
     <row r="913" xml:space="preserve">
       <c r="A913" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO Aunque tu desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerte una oportunidad para redimirte. Para reevaluar tus habilidades, nos gustaría que detuvieras a ~mission(TargetName) en ~mission(Location|Address). Aunque habrá otros criminales en el lugar, tu principal objetivo debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar tu propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazadores de Recompensas y certificación apropiada. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Se necesita un piloto independiente disponible para una entrega local rápida. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de la &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Intente no causar problemas cuando esté fuera. Si lleva paquetes de Red Wind a bordo, se agradece cierto nivel de profesionalismo. Y no olvide empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar consigo. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (ERT)</v>
+        <v> Red Wind busca nuevos pilotos.</v>
       </c>
     </row>
     <row r="915" xml:space="preserve">
       <c r="A915" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo extremo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo extremo generalmente pilota una nave de clase subcapital, tiene varios aliados fuertemente armados y se espera que sea muy difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Buscamos contratar un piloto independiente interesado en operar una ruta local para nosotros. PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si lo logras, podemos considerar otros contratos en el futuro. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~mission(Contractor|SignOff)</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (HRT)</v>
+        <v> Otro intento de entrega de viento rojo</v>
       </c>
     </row>
     <row r="917" xml:space="preserve">
       <c r="A917" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de alto riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de alto riesgo generalmente pilota una nave grande con tripulación múltiple, tiene varios aliados conocidos y se espera que sea difícil de capturar. Puede ser útil traer personal de apoyo para ayudar a enfrentarse a este objetivo. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Aunque hace tiempo que no le contratamos, ahora mismo nos vendría bien su ayuda extra. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a la &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Si logras esta entrega, podemos ver si podemos volver a hacerla más frecuente. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~misión(Contratista|Aprobación)</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v> Evaluación de recompensas activas</v>
+        <v>SE NECESITA PILOTO DE RED WIND DELIVERY</v>
       </c>
     </row>
     <row r="919" xml:space="preserve">
       <c r="A919" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita nuevos cazarrecompensas calificados para ampliar nuestra lista actual. Para evaluar sus habilidades, nos gustaría que nos ayudara en la detención de ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tenemos un envío esperando ser transportado desde &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Sin embargo, seré sincero contigo, este lugar no tiene la mejor reputación. Dicho esto, todavía necesitan entregar paquetes y tienen créditos, así que todo está en orden. Pero si vas allí, hay una buena posibilidad de que te encuentres con algunos problemas. No aceptes el trabajo si no puedes manejar eso. A TODOS LOS VETERANOS: ¡Red Wind agradece su servicio a nuestro Imperio! ¡Sus esfuerzos significan nuestra libertad!</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (LRT)</v>
+        <v> Oportunidad de manutención para reclusos</v>
       </c>
     </row>
     <row r="921" xml:space="preserve">
       <c r="A921" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de bajo riesgo generalmente pilota una nave monoplaza, tiene varios aliados conocidos y debería ser fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">Estimados usuarios: Recientemente nos han informado de que uno de nuestros dispensadores de oxígeno ha sufrido una avería técnica. Como saben, estos dispensadores son esenciales para garantizar que dispongan de suficiente oxígeno durante su participación en nuestro Programa de Reinserción Laboral. Buscamos a algún usuario disponible que pueda reiniciar el dispensador. Esto debería reconectarlo a la red y solucionar el problema. El primer usuario que complete esta tarea no solo recibirá una recompensa, sino también la satisfacción de contribuir a un entorno de trabajo más seguro para los demás usuarios. Gracias.</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+        <v> Negociaciones fallidas</v>
       </c>
     </row>
     <row r="923" xml:space="preserve">
       <c r="A923" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de riesgo moderado ~mission(TargetName) de ~mission(Location|Address). Un objetivo de riesgo moderado generalmente pilota una pequeña nave multitripulación, tiene varios aliados conocidos y puede ser un poco difícil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">Tuve un percance con la mala suerte y espero que puedas ayudarme. Hace unos días, contraté a la tripulación del 'Orgullo de Arliss' para obtener datos importantes. Cumplieron el trabajo sin problemas, pero el capitán, ese desgraciado, me contactó exigiendo más créditos. Resulta que no era la primera vez que intentaba esta trampa, porque en medio de una "negociación" conmigo, su nave fue atacada por unos individuos muy enfadados que querían darle una lección. Nuestra comunicación se cortó cuando empezó el tiroteo y fue lo último que supe de él. Supongo que lo han borrado de mi vida, pero quiero que vayas al Orgullo de Arliss e intentes obtener mis datos del datapad personal del capitán. Una vez que los tengas, he configurado un canal de transmisión seguro en el área de descanso ARC-L1. Ve allí y, cuando estés dentro del alcance, envíame los datos a través de este contrato para que te pague. No intentes engañarme. El karma puede ser un verdadero cabrón.</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v> Reevaluación de la detención de recompensas</v>
+        <v> Doble juego</v>
       </c>
     </row>
     <row r="925" xml:space="preserve">
       <c r="A925" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. Para reevaluar sus habilidades, nos gustaría que detuviera a ~mission(TargetName) de ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">Rough &amp; Ready recientemente proporcionó servicios de repostaje a un transportista llamado ~mission(TargetName), quien accedió a entregarnos su próximo cargamento como compensación. Pues bien, acabamos de descubrir que el mentiroso vendió su último cargamento a una banda rival. Buscamos a alguien que localice y elimine a ~mission(TargetName|Last) por su traición. Un viejo amigo mío acaba de ver al traidor en ~mission(Location|Address). Parece que lleva más cargamento que no va dirigido a nosotros y viaja con escolta. Solo te pagaremos por destruir el barco, así que todo lo que encuentres a bordo es tuyo. - Smokey</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (VLRT)</v>
+        <v> Entrega fallida</v>
       </c>
     </row>
     <row r="927" xml:space="preserve">
       <c r="A927" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar al objetivo de muy bajo riesgo ~mission(TargetName) de ~mission(Location|Address). Un objetivo de muy bajo riesgo generalmente pilota una nave monoplaza, tiene pocos aliados conocidos y debería ser relativamente fácil de capturar. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Membresía del Gremio de Cazarrecompensas y certificación apropiada. • Acceso a un vehículo adecuadamente equipado para el combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">Mis socios y yo cerramos un trato con un transportista llamado ~mission(TargetName) para que nos entregara suministros. Lo curioso es que el envío nunca llegó. Afirmaron que unos piratas asaltaron su barco y se llevaron nuestros suministros, pero resulta que esa historia es una completa mentira. Mentir para cancelar nuestro trato no puede quedar impune y vas a dejarlo bien claro. ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Mientras mates a ~mission(TargetName|Last), no nos importa lo que pase con la carga que transportan. - Smokey</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v> Eliminar fuerza hostil</v>
+        <v> Activar una trampa</v>
       </c>
     </row>
     <row r="929" xml:space="preserve">
       <c r="A929" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos rápida y seguramente en la eliminación completa del grupo de forajidos que ha tomado temporalmente el control de ~mission(Location) en ~mission(Location|Address). RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los miembros de la fuerza hostil de forajidos; usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">Un imbécil con el nombre ~mission(TargetName) ha estado tramando un plan: su carguero solicita repostaje solo para emboscar a nuestros barcos al llegar. Incluso cargó la maldita nave con mercancía real para asegurarse de que pasara los escaneos. Hemos corrido la voz para que nadie en Rough &amp; Ready vuelva a caer en la trampa, pero quiero que este cretino sea castigado. Creo que ~mission(TargetName|Last) reconoce a muchos de los nuestros, así que supongo que será mejor pagarte para que te encargues. He oído que lo han visto cerca de ~mission(Location|Address). Dirígete allí ahora mismo y acaba con ese carguero y con cualquiera que lo proteja de una vez por todas. - Smokey</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v> Capturar recompensa: ~misión(Nombre del objetivo) (HRT)</v>
+        <v> Saboteador de la huelga</v>
       </c>
     </row>
     <row r="931" xml:space="preserve">
       <c r="A931" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa en ~mission(Location|Address), y creemos que finalmente podrían salir de su escondite si sus fuerzas que atacan ~mission(Location) se enfrentan a una resistencia lo suficientemente fuerte. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a los asociados criminales de ~mission(TargetName) cerca de ~mission(Location) para atraer al objetivo a campo abierto. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">¿Te interesa ir de caza? ~mission(TargetName) saboteó uno de nuestros envíos de combustible y nos costó un montón de créditos, así que busco a alguien que le haga pagar por lo que hizo. Me acaban de avisar de que ~mission(TargetName|Last) fue visto en ~mission(Location|Address). Si vas allí ahora, hay muchas posibilidades de que puedas seguirle la pista y acabar con él definitivamente. ~mission(TargetName|Last) no actuó solo, así que no te sorprendas si va acompañado. - Smokey</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v> Recompensa asegurada: ~misión(Nombre del objetivo) (VHRT)</v>
+        <v> Ya era hora.</v>
       </c>
     </row>
     <row r="933" xml:space="preserve">
       <c r="A933" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName), quien hasta ahora ha logrado evadir la captura. Están coordinando una incursión activa que se ha extendido por todo ~mission(Location|Address). Esperamos que finalmente pueda sacarlos de su escondite si enfrenta a sus fuerzas en varios puntos de ataque diferentes. Con sus números suficientemente debilitados, ~mission(TargetName|Last) probablemente correrá el riesgo de ser expuesto y usted podrá enfrentarlos directamente. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Enfrentar a los asociados criminales de ~mission(TargetName) para hacer que el objetivo salga a la luz. • Neutralizar a ~mission(TargetName); usando la fuerza si es necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">Rough &amp; Ready lleva años haciendo negocios con ~mission(TargetName), pero la relación se ha deteriorado. Durante un tiempo, les suministrábamos combustible a crédito, pero a la hora de cobrar, el cobarde se escondió. Si ~mission(TargetName|Last) no puede pagar con créditos, supongo que pagará con su vida. Un socio acaba de localizar a ~mission(TargetName|Last) en ~mission(Location|Address). Me encantaría que fueras allí ahora mismo para hacer que ese tacaño pague. Por cierto, parece que ~mission(TargetName|Last) no viaja solo, así que asegúrate de tener suficiente combustible antes de ir tras él. - Smokey</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v> Recompensa activa: ~misión(Nombre del objetivo) (MRT)</v>
+        <v> Regalo de despedida</v>
       </c>
     </row>
     <row r="935" xml:space="preserve">
       <c r="A935" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un cazarrecompensas calificado para capturar a ~mission(TargetName) en ~mission(Location|Address). Fueron vistos recientemente cerca de ~mission(Location) y se cree que todavía están en esa área. Si bien puede haber otros criminales activos en el sitio, su enfoque principal debe ser completar la recompensa. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Neutralizar a ~mission(TargetName); usando la fuerza según sea necesario. REQUISITOS MÍNIMOS • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Capacidad para manejar situaciones de alta presión.</v>
+        <v xml:space="preserve">Tengo una situación delicada que requiere atención. Tras años de ser un miembro leal de Rough &amp; Ready, ~mission(TargetName) desertó de la banda y está por ahí filtrando secretos a nuestros rivales. Necesitamos eliminar a ~mission(TargetName|Last) de inmediato. En casos como este, siempre es mejor pagarle a alguien ajeno a nosotros para que se encargue. Los escaneos detectaron a ~mission(TargetName|Last) cerca de ~mission(Location|Address) hace poco. Te pagaremos bien para que vayas allí ahora mismo y te encargues de él. ~mission(TargetName|Last) no es tonto y sabe que iremos tras él. Prepárate para una dura batalla y no esperes que esté solo. - Smokey</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v> Ajuste de la población de vida silvestre</v>
+        <v> Operación de espionaje en silencio</v>
       </c>
     </row>
     <row r="937" xml:space="preserve">
       <c r="A937" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para eliminar varias criaturas de diversas especies. Esta es una medida preventiva para asegurar que el tamaño de su población no aumente más allá de los parámetros aceptables. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar la especie objetivo en ~misión(Ubicación). • Usar la fuerza según sea necesario para eliminar a los animales. REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio. Para obtener más información sobre los animales en cuestión, consulte "La guía de la fauna silvestre de Stanton" en su Diario.</v>
+        <v xml:space="preserve">El equipo de Rough &amp; Ready busca a alguien para manejar una situación delicada. Hemos descubierto una nave y centinelas orbitales en ~mission(location|address) espiándonos. Estamos en un aprieto porque no queremos iniciar una pelea mayor con quienquiera que esté detrás de esto. Por eso buscamos ayuda a sueldo que pueda encargarse de esto rápida y discretamente. ¿Te interesa? Último consejo: una vez allí, asegúrate de vigilar la nave. Apuesto a que en cuanto empieces a destruir sus centinelas intentarán traer refuerzos para detenerte. - Smokey</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v> Control de vida silvestre: ~misión(Criatura)</v>
+        <v> Operación de espionaje de Stomp</v>
       </c>
     </row>
     <row r="939" xml:space="preserve">
       <c r="A939" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional para reducir el número de ~mission(Creature) en estado salvaje a parámetros aceptables. Su población está aumentando demasiado rápido, y la reducción de algunos de sus números ayudará a garantizar que la situación no se salga de control. RESPONSABILIDADES • Proporcionar transporte propio. • Localizar a ~mission(Creature) en ~mission(Location). • Usar la fuerza según sea necesario para eliminar a ~mission(Creature). REQUISITOS MÍNIMOS • 1 año de experiencia relevante como mercenario y/o en seguridad. • Acceso a equipo de combate. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con exterminio Para obtener más información sobre los animales en cuestión, consulte "The Guide to Stanton Wildlife" en su Diario.</v>
+        <v xml:space="preserve">El equipo de Rough &amp; Ready busca un mercenario independiente interesado en algo pesado. Hemos estado vigilando una situación que se está desarrollando en ~mission(location|address), donde varias naves custodian centinelas orbitales que espían nuestras operaciones. Puede que haya nacido de noche, pero no fue anoche. Dada la descarada forma en que están instalados, quien sea el responsable debía saber que tarde o temprano lo descubriríamos. Casi parece que están tendiéndole una trampa a R&amp;R para que ataquemos, y no quiero que caigamos en ella. En cambio, tú lo harás por nosotros y recibirás una buena cantidad de créditos por tu esfuerzo. Las naves estacionadas allí sospecharán menos de una nave no afiliada que se acerque, lo que dificultará que nos atribuyan el ataque. Asegúrate de planificar bien antes de ir. Quizás deberías llevar tus propios refuerzos por si alguna de sus naves escapa y pide ayuda. - Smokey</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v> Proteger la ubicación y entregar materiales confidenciales.</v>
+        <v xml:space="preserve"> Detengan las operaciones de espionaje</v>
       </c>
     </row>
     <row r="941" xml:space="preserve">
       <c r="A941" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita un profesional de seguridad para una operación de recuperación en ~mission(Location). La ubicación está actualmente bajo ataque y las fuerzas de seguridad en el sitio no responden y se presumen muertas. Creemos que los materiales confidenciales entregados recientemente a las instalaciones para custodia temporal fueron el objetivo del ataque. Su enfoque principal será recoger esas cajas y entregarlas en un lugar seguro. Por razones de seguridad, los materiales confidenciales se entregaron como parte de un envío más grande y se aseguraron en la bóveda automatizada. Los materiales tienen códigos de recuperación únicos que deben ingresarse en el teclado en la cinta transportadora de paquetes. Los protocolos exigen que solo los oficiales de seguridad de alto rango pueden llevar un datapad que contenga un código, pero dada la situación volátil, no podemos garantizar que los Nine Tails no se hayan apoderado de ellos. Una vez asegurados, entregue todos los materiales confidenciales a ~mission(dropoff1) para el pago. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|address). • Usar la fuerza según sea necesario para recoger los materiales confidenciales. • Entregar los materiales confidenciales a ~mission(dropoff1|address). REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate. • Acceso a una nave espacial con capacidad de transporte de carga. • Disponibilidad para despliegue inmediato. REQUISITOS DESEABLES • Experiencia en técnicas de desescalada rápida de hostilidades. • Experiencia en el transporte de carga importante.</v>
+        <v xml:space="preserve">Mis socios y yo nos encontramos en un pequeño aprieto y necesitamos ayuda. Hay un centinela orbital en ~mission(location|address) que nos está espiando. No sabemos quién lo puso ahí, pero desde luego no puede quedarse. El problema es que somos gente de negocios ante todo y nos preocupa que si lo destruimos nosotros mismos se arme un lío. Por eso es mejor que lo haga alguien como tú. Debería ser un trabajo rápido y fácil para alguien interesado en ganar algo de prestigio. - Smokey</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>Proteger la ubicación contra amenazas menores</v>
+        <v> Operación de espionaje de Squash</v>
       </c>
     </row>
     <row r="943" xml:space="preserve">
       <c r="A943" t="str" xml:space="preserve">
-        <v xml:space="preserve"> SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra cualquier amenaza menor. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+        <v xml:space="preserve">Recientemente hicimos un descubrimiento interesante: alguien instaló varios centinelas orbitales en ~mission(location|address). Supongo que intentan obtener información sobre nuestras operaciones allí. Incluso tienen algunas naves vigilando para asegurarse de que no les pase nada. Por supuesto, queremos deshacernos de estos desgraciados, pero me preocupa que hacerlo nosotros mismos sea perjudicial para el negocio. Por eso buscamos una forma de "negación plausible". Alguien ajeno a R&amp;R que elimine el problema, para que quien esté detrás no pueda vincular directamente el ataque con nosotros. Sé que no será fácil, sobre todo con esos guardias al acecho. ¿Quién sabe cuántos refuerzos tienen preparados? Pero si lo consigues, estamos dispuestos a pagarte como es debido. ¿Crees que tienes las habilidades necesarias para lograrlo? - Smokey</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v> Proteger la ubicación contra amenazas moderadas</v>
+        <v> Echar leña al fuego</v>
       </c>
     </row>
     <row r="945" xml:space="preserve">
       <c r="A945" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+        <v xml:space="preserve">Si buscas créditos fáciles, tengo una oferta para ti. Verás, corre el rumor de que ~mission(location|address) está funcionando como depósito de combustible. Parece que no se enteraron de que el comercio de combustible en Pyro pertenece a Rough &amp; Ready. Por eso tienes que ir allí y destruir sus reservas de combustible. Deberían ser fáciles de encontrar. Son los grandes tanques de almacenamiento amarillos repartidos por el puesto de avanzada. Pero ten cuidado, hay torretas defendiendo la zona, así que asegúrate de estar preparado para esquivar sus disparos o volar las armas por los aires. Tú decides cómo llevar a cabo la demolición. Las bombas serían mi primera opción, pero no me importa mucho con tal de que el trabajo se haga. - Smokey</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v> Proteja la ubicación contra amenazas graves.</v>
+        <v> Invitados no deseados</v>
       </c>
     </row>
     <row r="947" xml:space="preserve">
       <c r="A947" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda formar un equipo de seguridad para proteger ~misión(Ubicación|Dirección) contra amenazas hostiles graves. RESPONSABILIDADES • Proporcionar su propio transporte a ~misión(Ubicación|Dirección). • Proporcionar su propio equipo de seguridad para ayudar. • Proteger el sitio contra amenazas hostiles; usando la fuerza cuando sea necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia en la gestión de un equipo.</v>
+        <v xml:space="preserve">Tenemos a unos forajidos que se están quedando más tiempo del debido en una de nuestras estaciones. Intentaron engañarnos, pero ahora están atrapados en ~mission(location|address). Necesitamos que los elimines. Rough &amp; Ready no quiere que quede ninguno con vida cuando termines. No importa lo complicado que sea, con tal de que se haga, ¿entendido? - Smokey</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v> Sitio libre de contrabando</v>
+        <v> Trabajo de exterminio</v>
       </c>
     </row>
     <row r="949" xml:space="preserve">
       <c r="A949" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir el contrabando que se almacena allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de contrabando; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+        <v xml:space="preserve"> En Rough &amp; Ready tenemos un problema de ratas. Una de nuestras tripulaciones intentó amotinarse y ahora se han apoderado de ~mission(location|address). Como no puedo estar completamente seguro de que no tengan simpatizantes a bordo, quiero que te encargues de eliminar a estos traidores. Si logras solucionar este problema de plagas, recibirás una buena recompensa. Solo asegúrate de no dejar a ninguno con vida. No quiero que a nadie más se le ocurran ideas raras. - Smokey</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v> Sitio libre de narcóticos</v>
+        <v> juntos para siempre</v>
       </c>
     </row>
     <row r="951" xml:space="preserve">
       <c r="A951" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir los narcóticos que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de narcóticos; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+        <v xml:space="preserve">Aquí está el trato. ~mission(TargetName) y ~mission(TargetName2) deben morir al mismo tiempo. Desafortunadamente, no estarán en el mismo lugar. Un doble impacto puede sonar complicado, pero si contratas algunos artilleros adicionales, no debería ser tan difícil lograr dos impactos simultáneos. Asegúrate de encontrar gente con habilidades, ya que tengo información fidedigna de que cada uno volará con escoltas para "protección".</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v> Sitio libre de drogas</v>
+        <v> El doble de dolor de cabeza</v>
       </c>
     </row>
     <row r="953" xml:space="preserve">
       <c r="A953" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un mercenario o profesional de seguridad con atención al detalle para presentarse en ~mission(Location|Address) y destruir las drogas que se almacenan allí. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Limpiar el sitio de drogas; usando la fuerza si es necesario. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • No tener problemas de adicción en curso.</v>
+        <v xml:space="preserve"> Hay otro par que necesita ser asesinado simultáneamente. Parece que se está volviendo cada vez más popular como opción de asesinato. Esta vez son ~mission(TargetName) y ~mission(TargetName2). Se supone que ambos son operadores bastante hábiles y no volarán solos. Asegúrate de que quien te ayude en esta misión pueda manejar un combate.</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v> Defender a los ocupantes</v>
+        <v> lanzamiento simultáneo</v>
       </c>
     </row>
     <row r="955" xml:space="preserve">
       <c r="A955" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudar de manera rápida y segura al equipo de seguridad estacionado en ~mission(Location|Address) a proteger el sitio contra amenazas hostiles. Tenga en cuenta que cualquier fuego amigo, accidental o de otro tipo, no será tolerado. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar al equipo de seguridad local a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">¿Adivina qué tienen en común ~mission(TargetName) y ~mission(TargetName2)? ¡Vas a matarlos a ambos! Lo difícil es que necesito que los mates al mismo tiempo para que ninguno pueda escapar, o peor aún, matar a quien intenta matarlo. Así que forma un equipo para rastrear a un objetivo mientras tú te encargas del otro. ¡Divide y vencerás! Y a pesar de que armaron un lío lo suficientemente grande como para que los mataran, entiendo que son bastante débiles. No esperes mucha resistencia.</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v> Evaluación de contratistas de seguridad</v>
+        <v> amigos hasta el final</v>
       </c>
     </row>
     <row r="957" xml:space="preserve">
       <c r="A957" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services necesita profesionales de seguridad nuevos, calificados y orientados a los detalles para ampliar nuestra plantilla actual. Para evaluar sus habilidades, nos gustaría que ayudara a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar transporte propio a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza cuando sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">Espero de verdad que no seas amigo de ~mission(TargetName) ni de ~mission(TargetName2), porque necesito que los elimines a ambos... al mismo tiempo... Claro que no nos lo pondrían fácil viajando en la misma nave o algo así de obvio. No. Tendrás que formar una tripulación para poder derribar a ambos objetivos simultáneamente. En cuanto uno de ellos muera, prepárate para eliminar al otro también. No podemos arriesgarnos a que ninguno escape. Y creo que debería mencionar que no solo son buenos pilotos, sino que también viajarán con refuerzos. Seguro que puedes con esto.</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v> Reevaluación de contratistas de seguridad</v>
+        <v> doble problema</v>
       </c>
     </row>
     <row r="959" xml:space="preserve">
       <c r="A959" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO Si bien su desempeño anterior no ha estado a la altura de nuestros estándares, microTech Protection Services ha decidido ofrecerle una oportunidad para redimirse. En un esfuerzo por reevaluar sus habilidades, microTech Protection Services desea que ayude a proteger ~mission(Location|Address) contra amenazas hostiles. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Ayudar a proteger el sitio; usando la fuerza según sea necesario. • Evitar cualquier incidente de fuego amigo. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve">Si me hubieras preguntado, te habría dicho que ~mission(TargetName) y ~mission(TargetName2) acabarían matándose entre sí. Pero en cambio, tendrás el honor de eliminarlos a ambos a la vez. Eso sí, tendrás que ganártelo. Son peligrosos. Tienen un historial delictivo, están altamente entrenados y son demasiado listos para volar sin refuerzos. Reúne al mejor equipo posible. Lo necesitarás. Y no seas tacaño. No puedes gastar créditos si estás muerto.</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v> Desalojar a los ocupantes ilegales</v>
+        <v> Que la muerte nos separe</v>
       </c>
     </row>
     <row r="961" xml:space="preserve">
       <c r="A961" t="str" xml:space="preserve">
-        <v xml:space="preserve">SOBRE EL TRABAJO microTech Protection Services está buscando un profesional mercenario orientado a los detalles que pueda ayudarnos de manera rápida y segura en la eliminación completa de ocupantes ilegales que han tomado temporalmente el control de ~mission(Location|Address). Tenga en cuenta que nuestra inteligencia muestra que hay trabajadores civiles en el sitio. Dado que su conexión con la pandilla no está clara, deben ser considerados no combatientes. No se tolerará ninguna acción hostil hacia ellos. RESPONSABILIDADES • Proporcionar su propio transporte a ~mission(Location|Address). • Eliminar a todos los ocupantes hostiles que se encuentren dentro del sitio; usando la fuerza si es necesario. • Garantizar la seguridad de cualquier civil que pueda estar en el sitio. REQUISITOS MÍNIMOS • 2 años de experiencia combinada como mercenario y/o en seguridad. • Acceso a equipo de combate y medio de transporte. • Disponibilidad para despliegue inmediato. REQUISITOS PREFERIBLES • Experiencia con técnicas de desescalada rápida de hostilidades.</v>
+        <v xml:space="preserve"> Es bastante conmovedor encontrarse con una pareja dispuesta a morir el uno por el otro. Estúpido pero conmovedor. ~mission(TargetName) y ~mission(TargetName2) decidieron apoyarse mutuamente y ahora la situación los ha llevado a la muerte. Busca a un amigo y dales caza a estos dos. Asegúrate de matarlos al mismo tiempo. Llámalo justicia poética. Deberían morir fácilmente. Tal vez tengan una o dos naves con ellos, pero no creo que sea nada de qué preocuparse.</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v> URGENTE: Embarque en curso</v>
+        <v>dos por el precio de dos</v>
       </c>
     </row>
     <row r="963" xml:space="preserve">
       <c r="A963" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un cliente ejecutivo nos acaba de informar que su 890 Jump fue interceptada en ~mission(Location) y abordada por forajidos. Prefieren que el asunto se resuelva de forma privada debido a la naturaleza confidencial de los datos confidenciales almacenados a bordo. Su prioridad será eliminar a todos los forajidos lo antes posible para que se pueda enviar un equipo de recuperación y devolver la nave al propietario. Cuanto más tiempo tengan los forajidos el control de la nave, mayor será la probabilidad de que se pierda. Le recomiendo que consiga un equipo para esta misión para agilizar el proceso. Tenga en cuenta que, gracias a un pequeño contingente de personal de seguridad que permaneció a bordo, todos los miembros supervivientes de la tripulación pudieron escapar en una nave de escape. Se desconoce el estado actual del resto del personal de seguridad, pero por si acaso, esté atento a la presencia de aliados cuando se enfrente a los hostiles. En segundo lugar, si es posible, el cliente está muy interesado en evitar el robo de los datos mencionados. Si logra detener el robo de sus almacenes de datos confidenciales antes de que se transmitan, recibirá una generosa bonificación. Como es lógico, este es un cliente al que me gustaría mantener muy satisfecho. Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Creo que podrían estar emparentados, ¿o saliendo juntos? En realidad no importa, alguien quiere matarlos. He organizado todo para que puedas atacarlos cuando no estén volando juntos. Así estarás más seguro. Son objetivos serios y cuentan con un apoyo igualmente serio. Asegúrate de que tú y tu equipo coordinen bien los ataques. No quiero que ninguno quede con vida, o será un verdadero dolor de cabeza.</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>Asignación de recompensa: ~misión(Nombre del objetivo) (HRT)</v>
+        <v> Asistencia en combate</v>
       </c>
     </row>
     <row r="965" xml:space="preserve">
       <c r="A965" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, tengo un contrato para ti que requiere un poco más de estrategia de lo habitual. Un criminal de alto nivel llamado ~mission(TargetName) se esconde con un gran contingente de forajidos en ~mission(Location|Address). Nuestra información sugiere que las fuerzas de ~mission(TargetName|Last) probablemente actuarán como línea defensiva para proteger a su jefe. Supongo que tendrás que enfrentarte a ellos antes de poder acceder a ~mission(TargetName|Last). Dicho esto, no quiero que dispares indiscriminadamente. A veces, estos forajidos mantienen a civiles cerca y deben ser tratados como no combatientes. Mucha suerte, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> ~mission(InitiatorName) solicita asistencia en combate en ~mission(InitiatorLocation). Si se acepta, recibirá ~mission(PaymentAmount) aUEC al eliminar la amenaza.</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v> Asignación de recompensa provisional: ~misión(Nombre del objetivo)</v>
-      </c>
-    </row>
-    <row r="967">
-      <c r="A967" t="str">
-        <v> Asignación de recompensa provisional: ~misión(Nombre del objetivo)</v>
+        <v> Asistencia en combate - BAJO RIESGO</v>
+      </c>
+    </row>
+    <row r="967" xml:space="preserve">
+      <c r="A967" t="str" xml:space="preserve">
+        <v xml:space="preserve"> [BAJO NIVEL DE AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v> Misión de recompensa por fuga: ~mission(Nombre del objetivo)</v>
+        <v>Asistencia en combate - ALTA AMENAZA</v>
       </c>
     </row>
     <row r="969" xml:space="preserve">
       <c r="A969" t="str" xml:space="preserve">
-        <v xml:space="preserve">El delincuente convicto ~mission(TargetName) se ha fugado de un centro de rehabilitación local y Northrock ha sido contratado para devolverlo a prisión. En mi experiencia, los presos fugados no suelen rendirse pacíficamente, así que utilicen cualquier método posible para encontrarlo y someterlo. Podría ser conveniente vigilar los lugares donde podría intentar borrar sus antecedentes penales. No sería la primera vez que un preso intenta borrar su condena tras fugarse. Buena suerte en la búsqueda, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> [ALTA AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v> Contrato provisional de recompensa por fuga</v>
+        <v> Asistencia en combate - AMENAZA MODERADA</v>
       </c>
     </row>
     <row r="971" xml:space="preserve">
       <c r="A971" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, mi nombre es Braden Corchado y soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera en el sistema Stanton. Puede que ya te haya contactado, pero nos esforzamos por contactar a cualquier persona que cumpla con nuestros altos estándares y animarla a completar un contrato temporal. No hay mejor opción que ser contratista de Northrock. Tenemos una sólida reputación por ofrecer trabajo desafiante e interesante con una remuneración superior a la de muchos de nuestros competidores en el sistema. Para ser aprobado, deberás capturar a ~mission(TargetName). Recientemente escapó del centro de detención y tu trabajo consistirá en localizarlo antes de que desaparezca por completo. Un pequeño consejo: es probable que el objetivo intente limpiar su historial. Te recomiendo triangular tu búsqueda entre el centro de detención del que escapó y los lugares donde pueda acceder al sistema de registros. Si lo logras, veremos si podemos ofrecerte más trabajo. Espero tener noticias suyas pronto, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> [AMENAZA MODERADA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>Contrato provisional de recompensa para fugitivos (reevaluación)</v>
+        <v> Asistencia en combate - AMENAZA CRÍTICA</v>
       </c>
     </row>
     <row r="973" xml:space="preserve">
       <c r="A973" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, sé que ha pasado un tiempo, pero si todavía te interesa trabajar por contrato para Northrock, convencí a la gerencia para que te hicieran una reevaluación. Si logras completar con éxito una misión de recompensa, podemos ver si podemos restituirte tu puesto. Este contrato temporal consiste en localizar al criminal fugado ~mission(TargetName). Haz todo lo posible por encontrarlo antes de que borre su registro en el punto de acceso a la base de datos, o el trabajo será mucho más difícil. Esperamos poder confiar en ti. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> [AMENAZA CRÍTICA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v> Detener sospechoso: ~misión(Nombre del objetivo)</v>
-      </c>
-    </row>
-    <row r="975">
-      <c r="A975" t="str">
-        <v> ~misión(Contratista|DescripciónPVPRecompensa)</v>
+        <v> Escolta</v>
+      </c>
+    </row>
+    <row r="975" xml:space="preserve">
+      <c r="A975" t="str" xml:space="preserve">
+        <v xml:space="preserve">~mission(InitiatorName) solicita un acompañante en la ubicación: ~mission(InitiatorLocation). Si se acepta, recibirá un pago de ~mission(PaymentAmount) aUEC/minuto hasta que el iniciador lo CANCELE o el proveedor del servicio lo ABANDONE. NOTA: El contrato y el pago comenzarán una vez que se reúna con el cliente.</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v> Detención provisional del sospechoso</v>
+        <v xml:space="preserve"> Asistencia médica</v>
       </c>
     </row>
     <row r="977" xml:space="preserve">
       <c r="A977" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, espero que no le importe, pero me enteré de su pertenencia al Gremio de Cazadores de Recompensas y quería ponerme en contacto con usted para ver si estaría interesado en colaborar con Northrock Service Group, una de las empresas de seguridad privada mejor valoradas del sistema. Si es así, el primer paso sería completar una detención provisional del sospechoso. No se trata tanto de una evaluación, sino más bien de una oportunidad para asegurarnos de que podemos establecer una buena relación laboral. El sospechoso que busca se conoce como &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;. Se sabe que es particularmente escurridizo, así que puede que tenga un trabajo arduo por delante. Espero tener noticias suyas pronto. Atentamente, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> ~mission(InitiatorName) requiere asistencia médica en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v> Detención provisional de sospechoso (reevaluación)</v>
+        <v> Transporte personal</v>
       </c>
     </row>
     <row r="979" xml:space="preserve">
       <c r="A979" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola de nuevo, hace tiempo que no hablamos, espero que todo esté bien. Sé que las cosas no terminaron de la mejor manera, pero después de hablarlo con la gerencia, me gustaría ofrecerte una oportunidad para redimirte. Tenías potencial y me da mucha pena que no hayas tenido la oportunidad de demostrar de lo que eres capaz. Completa la misión &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt; y veremos cómo podemos restituirte en tu puesto. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v xml:space="preserve"> ~mission(InitiatorName) solicita transporte desde ~mission(InitiatorLocation) hasta ~mission(SelectedDestination). Al completar con éxito este servicio, recibirá ~mission(PaymentAmount) aUEC.</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v> Operación de recuperación</v>
+        <v> Rescate médico</v>
       </c>
     </row>
     <row r="981" xml:space="preserve">
       <c r="A981" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aquí está el trato: un cliente nuestro (que debería haber gastado los créditos extra en una escolta de Northrock) sufrió un ataque a una de sus naves y ahora necesita que lideremos una operación de recuperación de un paquete importante que fue robado. Por suerte, tuvimos un golpe de suerte y pudimos localizar a los responsables en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;. Necesitamos que vayas allí y recuperes el paquete. Podrás identificarlo por su número de serie: &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt;. Supongo que los forajidos van a oponer resistencia, pero recuerda que no son la prioridad. Una vez que tengas el paquete, llévalo de vuelta al cliente en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Una última cosa, asegúrate de llevar una nave con suficiente espacio para carga. No queremos que llegues hasta allí en tu Gladius o lo que sea solo para tener que regresar. Enorgullécenos, Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group *RESUMEN DE LA OPERACIÓN DE RECUPERACIÓN* * Recuperar el paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; * Entregar en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;</v>
+        <v xml:space="preserve"> ~mission(InitiatorName) requiere tratamiento médico de emergencia en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>Asignación de recompensa: Orden de arresto grupal (MRT)</v>
-      </c>
-    </row>
-    <row r="983">
-      <c r="A983" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v> Eliminar Claimjumpers</v>
+      </c>
+    </row>
+    <row r="983" xml:space="preserve">
+      <c r="A983" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Acabamos de recibir la noticia de que un contratista de Shubin fue expulsado de una de nuestras concesiones por forajidos que operan allí ilegalmente. Para complicar aún más las cosas, han instalado algunos centinelas orbitales para protegerse mientras extraen minerales. Esperamos contratar a un mercenario que pueda buscar y destruir los centinelas en ~mission(location). Si se encuentra con un minero ilegal en el sitio, tenga en cuenta que es práctica común que este tipo de personas contacten refuerzos para pedir ayuda. Podría ser mejor neutralizarlos lo más rápido posible antes de que puedan hacerlo. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v> Asignación de recompensa: Orden de arresto grupal (HRT)</v>
-      </c>
-    </row>
-    <row r="985">
-      <c r="A985" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v> Expulsar a los usurpadores de derechos</v>
+      </c>
+    </row>
+    <row r="985" xml:space="preserve">
+      <c r="A985" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) CONDICIONES*: Un equipo minero independiente local de Stanton estaba trabajando en ~mission(Location) como contratistas de Shubin Interstellar cuando una fuerza hostil atacó y tomó el sitio. Creemos que los perpetradores todavía están en la mina usando el equipo que dejaron para extraer el valioso mineral. Entre el equipo perdido había un puñado de centinelas orbitales que, desafortunadamente, aún no se habían desplegado por completo en el momento del ataque. Los escaneos de largo alcance de la mina nos han llevado a concluir que los forajidos han activado los centinelas orbitales y los están usando para proteger sus operaciones ilegales. Para recuperar el sitio, estamos buscando contratistas que vayan a ~mission(Location), destruyan los centinelas orbitales y limpien el sitio de mineros hostiles. Se recomienda encarecidamente la eficiencia, ya que existe un alto riesgo de que pidan refuerzos una vez que descubran que están siendo desalojados. Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v> Asignación de recompensa: Orden de arresto grupal (VHRT)</v>
-      </c>
-    </row>
-    <row r="987">
-      <c r="A987" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v>Eliminar a los saltadores de reclamaciones</v>
+      </c>
+    </row>
+    <row r="987" xml:space="preserve">
+      <c r="A987" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Recientemente se descubrió que un minero renegado se apropió ilegalmente de una concesión minera de Shubin. Si bien el minero ya no parece estar robando mineral del sitio, dejó un centinela orbital que nos impide recuperarlo debido a sus capacidades ofensivas. Buscamos un mercenario dispuesto a viajar a ~mission(location), dar caza al centinela y destruirlo para preparar la recuperación del sitio por parte de Shubin. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v> Asignación de recompensa: Orden de grupo (ERT)</v>
-      </c>
-    </row>
-    <row r="989">
-      <c r="A989" t="str">
-        <v> ~misión(Contratista|Descripción de la recompensa grupal)</v>
+        <v> Expulsar a los usurpadores de derechos</v>
+      </c>
+    </row>
+    <row r="989" xml:space="preserve">
+      <c r="A989" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar deseable) CONDICIONES*: Se descubrió que una concesión minera de Shubin Interstellar, recientemente adquirida y pendiente de procesamiento, había sido usurpada por una compañía minera renegada que está robando mineral del sitio. Si bien se ha notificado a las autoridades locales, existe la preocupación de que se puedan extraer activos valiosos antes de que se inicie una investigación oficial. Por lo tanto, como es nuestro derecho como titulares de la concesión, deseamos contratar una fuerza mercenaria para que se dirija a ~mission(Location) y destruya los centinelas orbitales que protegen esta operación ilegal. Se recomienda precaución, ya que aún podría haber algunos mineros ilegales en el lugar, junto con cualquier refuerzo que reúnan. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v> Contrato de garantía grupal pro tempore</v>
-      </c>
-    </row>
-    <row r="991" xml:space="preserve">
-      <c r="A991" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, espero que todo vaya bien. Puede que ya te haya contactado, pero quería asegurarme de presentarme. Soy oficial de logística de Northrock Service Group, la empresa de seguridad independiente líder que opera actualmente en el sistema Stanton, que proporciona una variedad de servicios a todos los principales organismos gubernamentales, así como a varias empresas privadas. El motivo por el que me pongo en contacto contigo es porque creemos que alguien con tus habilidades podría ser muy valioso para nuestros clientes. Además, creo que seríamos una buena opción para ti. Nuestros contratistas suelen recibir una remuneración más alta que muchos de nuestros competidores en el sistema, y muchos de ellos me comentan lo mucho que disfrutan del trabajo desafiante e interesante que les ofrecemos. Ahora bien, Northrock se rige por estándares muy altos, por lo que antes de que podamos formalizar nada, tendrás que obtener la aprobación como contratista completando un contrato provisional. Esperaba que pudieras capturar a varios miembros buscados de una banda de forajidos: ~misión(Objetivo1), ~misión(Objetivo2) y ~misión(Objetivo3). Una vez que lo hagas, veremos si podemos conseguirte más trabajo. Espero tener noticias tuyas pronto. Atentamente, Braden Corchado, Responsable de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v>Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="str">
+        <v/>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>Orden de reevaluación del grupo provisional</v>
-      </c>
-    </row>
-    <row r="993" xml:space="preserve">
-      <c r="A993" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, he estado reflexionando sobre todo lo sucedido y decidí hablar con la gerencia. Han accedido a darte otra oportunidad, pero solo si completas con éxito un contrato para nosotros. Podemos considerar la posibilidad de restituirte en tu puesto si logras capturar a este trío criminal: ~misión(Objetivo1) ~misión(Objetivo2) ~misión(Objetivo3). Evadieron al último asociado que los persiguió, así que si los capturas a todos, sin duda ganarás puntos. Espero que hayas enderezado tu vida desde tu último trabajo. Braden Corchado, Oficial de Logística - Sucursal Stanton, Northrock Service Group</v>
+        <v> Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v/>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v> Ayuda al bloqueo</v>
+        <v> Gran orden de compra: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="995" xml:space="preserve">
       <c r="A995" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ahora que Crusader ha encontrado su flota, parece que los Nueve Colas por fin se han dado cuenta de lo útil que puede ser un poco de ayuda extra. En resumen, buscan mercenarios para mantener a raya a Crusader. Tú y todos los demás que se ofrezcan voluntarios recibiréis una recompensa por cada nave de seguridad que derribéis. Y, además, si mantenéis a Crusader ocupado el tiempo suficiente para que los Nueve Colas terminen con lo que sea que estén tramando con este bloqueo cuántico, recibiréis una generosa bonificación.</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v> Bloqueo ilegal: Neutralización de la Flota de Nueve Colas</v>
+        <v> Orden de compra médica: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="997" xml:space="preserve">
       <c r="A997" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha confirmado la ubicación de la flota forajida de los Nueve Colas y se está movilizando para poner fin al bloqueo cuántico de ~mission(Location). Buscamos nuevamente profesionales de seguridad capacitados para unirse a nuestros esfuerzos de respuesta de emergencia y ayudar a neutralizar esta peligrosa amenaza. Antes de aceptar, tenga en cuenta que se espera que los Nueve Colas ofrezcan una resistencia considerable y que, hasta que se levante el bloqueo, no será posible realizar viajes cuánticos en el sector. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde extraer&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v> Lejos de miradas indiscretas</v>
+        <v> Orden de compra XL: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="999" xml:space="preserve">
       <c r="A999" t="str" xml:space="preserve">
-        <v xml:space="preserve">Les dije a los Nueve Colas que bloquear los viajes cuánticos para mantener toda una zona como rehén iba a atraer la atención equivocada, pero ¿me hacen caso? No. Ahora Crusader tiene docenas de naves de escaneo por ahí husmeando en cosas que prefiero mantener ocultas. Por eso estoy intentando contratar a tanta gente como pueda para que me ayude. Quiero pagarte por cada nave de escaneo de Crusader que destruyas. De hecho, incluso aumentaré tu tarifa por nave si todos alcanzan un cierto número de bajas. Llámalo incentivo por rendimiento. Y si de verdad te sientes con ganas de superarte, elimina a cualquier tonto lo suficientemente valiente como para intentar transportar carga a la estación bloqueada. Tengo algunos proveedores que agradecerán la demanda extra.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de materiales raros. Agradecemos su ayuda en este asunto. Solo se conocen algunas ubicaciones donde se pueden obtener estos materiales, principalmente de los sitios ahora inactivos del Grupo Hathor en &lt;EM4&gt;Daymar y Aberdeen&lt;/EM4&gt;. Nuestra sugerencia sería dirigirse a las Instalaciones de Alineación de Plataformas (PAF) e intentar reactivar su Plataforma Láser Orbital (OLP) para acceder a los materiales debajo de la superficie del planeta. Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v> Bloqueo ilegal: se busca al responsable de la flota de las Nueve Colas.</v>
+        <v>Orden de compra XL: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="1001" xml:space="preserve">
       <c r="A1001" t="str" xml:space="preserve">
-        <v xml:space="preserve">Crusader Security ha descubierto que la organización criminal conocida como los Nueve Colas ha establecido un bloqueo ilegal alrededor de ~mission(Location) y ha detenido todo el tráfico cuántico entrante y saliente en el sector. Es necesario localizar la flota ilegal y levantar el bloqueo. Solicitamos urgentemente a cualquier profesional de seguridad capacitado en el sistema que se una a las fuerzas de Crusader Security y proteja nuestras naves de escaneo mientras buscan la ubicación de la flota de los Nueve Colas que está causando este bloqueo. Tenga en cuenta que, con el viaje cuántico desactivado y numerosos enemigos en la zona, esta debe considerarse una operación de alto riesgo. Se recomienda encarecidamente que todos los pilotos que participen en esta operación de respuesta de emergencia cuenten con el equipo adecuado y el tanque de combustible lleno. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v> Bloqueo ilegal: se necesitan suministros médicos.</v>
-      </c>
-    </row>
-    <row r="1003" xml:space="preserve">
-      <c r="A1003" t="str" xml:space="preserve">
-        <v xml:space="preserve">El bloqueo cuántico ilegal de ~mission(Location) ha interrumpido las rutas comerciales habituales y los productos esenciales escasean. Crusader Security busca comerciantes y transportistas para suministrar los suministros médicos que tanto necesita la estación. Los precios ofrecidos por la administración de la estación se ajustarán para reflejar la situación con los Nine Tails y, además, Crusader otorgará una bonificación por riesgo al entregar con éxito los suministros médicos debido al mayor riesgo. Gracias de antemano por su apoyo durante estos tiempos difíciles. CONTRATO AUTORIZADO POR: Directora Sasha Rust ID# 122L964G</v>
+        <v> Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="str">
+        <v/>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v> Iniciativa Overdrive: Emboscada contra Xenoamenazas - Se necesita apoyo</v>
+        <v> Pedido pequeño: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="1005">
@@ -5429,557 +5429,557 @@
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v> ALERTA DE LAS FDI: Emboscada de xenoamenazas - Se necesita apoyo</v>
+        <v> Gran orden de compra: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="1007" xml:space="preserve">
       <c r="A1007" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA PUBLICACIÓN INMEDIATA EN TODO EL SISTEMA* Atención, fuerzas de XenoThreat comenzaron a emboscar a los convoyes navales que transportaban suministros vitales mientras se dirigían a la estación Jericho en el Pyro Gateway en el Sistema Stanton. La Armada ha solicitado a las fuerzas de CDF que ayuden a recuperar estos suministros de los restos y entregarlos de forma segura a Jericho. La Armada ha organizado un estipendio comunitario para gestionar la distribución del pago. Este se distribuirá entre todos los voluntarios de CDF en intervalos asignados. Aparecerá un indicador en su HUD para medir estos pagos. Tenga en cuenta que algunos de estos suministros son altamente volátiles si no se manipulan correctamente. Tenga precaución al transportar estos materiales: * Zeta-Prolanide se degrada con el tiempo hasta descomponerse por completo. * AcryliPlex Composite se vuelve explosivamente inestable si se daña. * Diluthermex libera un pulso de energía destructivo si se expone al viaje cuántico. Además, si bien no es tan volátil, la Armada aún necesita urgentemente los suministros de DynaFlex perdidos durante el ataque para completar las reparaciones del Javelin, por lo que su recuperación debe ser prioritaria. Asimismo, es posible que aún haya hostiles de XenoThreat en la zona, así que tengan cuidado. Se insta a los voluntarios de las CDF con experiencia en combate a contribuir asegurando estas áreas de las fuerzas XenoThreat que aún persistan. La SAIC Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>Iniciativa Overdrive: Ataque a XenoThreat</v>
+        <v> Gran orden de compra: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="1009" xml:space="preserve">
       <c r="A1009" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Atención, las fuerzas navales se han reagrupado para el asalto final que XenoThreat ha estado planeando. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. Esto incluye a voluntarios que no hayan participado en la Iniciativa Overdrive. La suboficial Rowena Dulli, de la Oficina de Defensa, es la agregada oficial de las CDF y dirigirá la operación. Si tiene éxito, se completará esta serie de la Iniciativa Overdrive y recibirá acceso temporal a los F7A Hornet o una actualización gratuita si actualmente posee un F7C.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v> ALERTA DE CDF: Ataque a XenoThreat</v>
+        <v> Orden de compra médica: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="1011" xml:space="preserve">
       <c r="A1011" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Atención: las fuerzas navales se han reagrupado para un asalto final contra la manada de forajidos XenoThreat que ha estado asolando el Sistema Stanton. La Armada ha solicitado oficialmente voluntarios de las Fuerzas de Defensa de Canadá (CDF) para brindar apoyo en combate durante este último esfuerzo por asegurar nuestro sistema. La suboficial Rowena Dulli, de la División de Defensa, es la agregada oficial de las CDF y estará a cargo de la operación.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde extraer&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v> dinero de la nada</v>
-      </c>
-    </row>
-    <row r="1013">
-      <c r="A1013" t="str">
-        <v> ¿Alguna vez has deseado que aparecieran créditos por arte de magia? Varias terminales de crédito antiguas de CCB están activas y simulan transacciones bancarias para desviar fondos a quien las controle. Si te interesa, te vendo las coordenadas por una pequeña comisión. Date prisa si quieres aprovechar la oportunidad. No sé cuánto tiempo seguirá funcionando.</v>
+        <v> Orden de compra XL: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1013" xml:space="preserve">
+      <c r="A1013" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de materiales raros. Agradecemos su ayuda en este asunto. Solo se conocen algunas ubicaciones donde se pueden obtener estos materiales, principalmente de los sitios ahora inactivos del Grupo Hathor en &lt;EM4&gt;Daymar y Aberdeen&lt;/EM4&gt;. Nuestra sugerencia sería dirigirse a las Instalaciones de Alineación de Plataformas (PAF) e intentar reactivar su Plataforma Láser Orbital (OLP) para acceder a los materiales debajo de la superficie del planeta. Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v> Recursos adicionales para la investigación</v>
-      </c>
-    </row>
-    <row r="1015">
-      <c r="A1015" t="str">
-        <v> Recursos adicionales para la investigación</v>
+        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1015" xml:space="preserve">
+      <c r="A1015" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v> Recursos vitales necesarios para la investigación</v>
-      </c>
-    </row>
-    <row r="1017">
-      <c r="A1017" t="str">
-        <v> Recursos vitales necesarios para la investigación</v>
-      </c>
-    </row>
-    <row r="1018" xml:space="preserve">
-      <c r="A1018" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Necesito recursos para la investigación.</v>
+        <v>Gran orden de compra: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1017" xml:space="preserve">
+      <c r="A1017" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v> Orden de compra médica: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1019" xml:space="preserve">
       <c r="A1019" t="str" xml:space="preserve">
-        <v xml:space="preserve">Necesito recursos para la investigación.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v> Recoge cuernos de kopión irradiados</v>
-      </c>
-    </row>
-    <row r="1021">
-      <c r="A1021" t="str">
-        <v> Recoge cuernos de kopión irradiados</v>
+        <v>Orden de compra mayor: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1021" xml:space="preserve">
+      <c r="A1021" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v> Obtén perlas Valakkar irradiadas</v>
+        <v>Orden de compra XS: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v> Obtén perlas Valakkar irradiadas</v>
+        <v/>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v> Reúne colmillos de Valakkar irradiados</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="str">
-        <v> Reúne colmillos de Valakkar irradiados</v>
+        <v> Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1025" xml:space="preserve">
+      <c r="A1025" t="str" xml:space="preserve">
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v> Recoge huevos de Valakkar irradiados.</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="str">
-        <v> Recoge huevos de Valakkar irradiados.</v>
+        <v>Orden de compra XL: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1027" xml:space="preserve">
+      <c r="A1027" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v> ¿Te interesa construir un futuro mejor?</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="str">
-        <v> ¿Te interesa construir un futuro mejor?</v>
+        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1029" xml:space="preserve">
+      <c r="A1029" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v> Ruta de envío local de Red Wind</v>
+        <v>Gran orden de compra: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1031" xml:space="preserve">
       <c r="A1031" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Recibimos una solicitud de ~mission(Pickup1|Address) indicando que tienen una buena cantidad de paquetes esperando en ~mission(Pickup1) que necesitan ser entregados. Antes de aceptar el contrato, asegúrese de tener una nave con suficiente espacio. Un rayo tractor tampoco vendría mal. PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; SOMOS UNA EMPRESA QUE OFRECE IGUALDAD DE OPORTUNIDADES: Red Wind Linehaul es y siempre ha sido una empresa que ofrece igualdad de oportunidades. Si cree que puede hacer un buen trabajo para nosotros, no dude en inscribirse.</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>Servicio de mensajería discreta Red Wind</v>
+        <v> Gran orden de compra: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1033" xml:space="preserve">
       <c r="A1033" t="str" xml:space="preserve">
-        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tengo otro trabajo especial para el que podrías contar contigo. Debería ser un viaje rápido. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt;) LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Y por favor recuerda no molestar a los clientes ni a ninguno de sus invitados. La profesionalidad es clave aquí.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v> Viento Rojo necesita mensajeros discretos</v>
+        <v> Orden de compra médica: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1035" xml:space="preserve">
       <c r="A1035" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Sé que has hecho un buen trabajo para nosotros en el pasado, así que pensé en preguntarte si te interesaría encargarte de un viaje especial que está un poco más lejos de lo que has estado haciendo hasta ahora. En resumen, necesitamos un piloto que esté dispuesto a trabajar con discreción, concentrarse en entregar los paquetes y, lo más importante, no hacer muchas preguntas. Verás, para una empresa pequeña como la nuestra, mantenernos por delante de la competencia significa que necesitamos ofrecer a nuestros clientes algo que no pueden obtener en ningún otro lugar: discreción. En Red Wind, siempre que tengas los créditos, llevaremos lo que sea a donde sea. ¿Entendido? Si eso te parece bien, veamos cómo te va en esta carrera: PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Un último consejo: probablemente sería bueno evitar retrasos innecesarios una vez que los paquetes estén a bordo, por ejemplo, que sean registrados por las fuerzas del orden locales.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>Manipulador de paquetes de Red Wind</v>
+        <v>Orden de compra mayor: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1037" xml:space="preserve">
       <c r="A1037" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Parece que hubo un pequeño problema logístico en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitan a alguien que se asegure de que los paquetes extraviados terminen donde se supone que deben ir dentro de las instalaciones. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; LA CONFIANZA ES BIDIRECTA: al aceptar este contrato, usted se compromete a no estafarnos, y Red Wind Linehaul se compromete a tratarlo de la misma manera.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>Ruta de reparto local de Red Wind</v>
+        <v>Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1039" xml:space="preserve">
       <c r="A1039" t="str" xml:space="preserve">
-        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Se necesita un piloto independiente disponible para una entrega local rápida. PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de la &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Intente no causar problemas cuando esté fuera. Si lleva paquetes de Red Wind a bordo, se agradece cierto nivel de profesionalismo. Y no olvide empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar consigo. ~mission(Contractor|SignOff)</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v> Red Wind busca nuevos pilotos.</v>
+        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1041" xml:space="preserve">
       <c r="A1041" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Buscamos contratar un piloto independiente interesado en operar una ruta local para nosotros. PAQUETES PARA RECOGER (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER ORDEN) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si lo logras, podemos considerar otros contratos en el futuro. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~mission(Contractor|SignOff)</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v> Otro intento de entrega de viento rojo</v>
+        <v>Gran orden de compra: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1043" xml:space="preserve">
       <c r="A1043" t="str" xml:space="preserve">
-        <v xml:space="preserve">RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Aunque hace tiempo que no le contratamos, ahora mismo nos vendría bien su ayuda extra. PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~misión(Dropoff2|Dirección)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~misión(Artículo3|Número de serie)&lt;/EM4&gt; a la &lt;EM4&gt;~misión(Dropoff3|Dirección)&lt;/EM4&gt; Si logras esta entrega, podemos ver si podemos volver a hacerla más frecuente. Y no olvides empacar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para llevar contigo. ~misión(Contratista|Aprobación)</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>SE NECESITA PILOTO DE RED WIND DELIVERY</v>
+        <v> Gran orden de compra: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1045" xml:space="preserve">
       <c r="A1045" t="str" xml:space="preserve">
-        <v xml:space="preserve"> RED WIND LINEHAUL 'SUS MERCANCÍAS EN BUENAS MANOS' ---------------------------- Tenemos un envío esperando ser transportado desde &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. Sin embargo, seré sincero contigo, este lugar no tiene la mejor reputación. Dicho esto, todavía necesitan entregar paquetes y tienen créditos, así que todo está en orden. Pero si vas allí, hay una buena posibilidad de que te encuentres con algunos problemas. No aceptes el trabajo si no puedes manejar eso. A TODOS LOS VETERANOS: ¡Red Wind agradece su servicio a nuestro Imperio! ¡Sus esfuerzos significan nuestra libertad!</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v> Oportunidad de manutención para reclusos</v>
+        <v>Gran orden de compra: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1047" xml:space="preserve">
       <c r="A1047" t="str" xml:space="preserve">
-        <v xml:space="preserve">Estimados usuarios: Recientemente nos han informado de que uno de nuestros dispensadores de oxígeno ha sufrido una avería técnica. Como saben, estos dispensadores son esenciales para garantizar que dispongan de suficiente oxígeno durante su participación en nuestro Programa de Reinserción Laboral. Buscamos a algún usuario disponible que pueda reiniciar el dispensador. Esto debería reconectarlo a la red y solucionar el problema. El primer usuario que complete esta tarea no solo recibirá una recompensa, sino también la satisfacción de contribuir a un entorno de trabajo más seguro para los demás usuarios. Gracias.</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v> Negociaciones fallidas</v>
+        <v> Orden de compra médica: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1049" xml:space="preserve">
       <c r="A1049" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tuve un percance con la mala suerte y espero que puedas ayudarme. Hace unos días, contraté a la tripulación del 'Orgullo de Arliss' para obtener datos importantes. Cumplieron el trabajo sin problemas, pero el capitán, ese desgraciado, me contactó exigiendo más créditos. Resulta que no era la primera vez que intentaba esta trampa, porque en medio de una "negociación" conmigo, su nave fue atacada por unos individuos muy enfadados que querían darle una lección. Nuestra comunicación se cortó cuando empezó el tiroteo y fue lo último que supe de él. Supongo que lo han borrado de mi vida, pero quiero que vayas al Orgullo de Arliss e intentes obtener mis datos del datapad personal del capitán. Una vez que los tengas, he configurado un canal de transmisión seguro en el área de descanso ARC-L1. Ve allí y, cuando estés dentro del alcance, envíame los datos a través de este contrato para que te pague. No intentes engañarme. El karma puede ser un verdadero cabrón.</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v> Doble juego</v>
+        <v>Orden de compra mayor: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1051" xml:space="preserve">
       <c r="A1051" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rough &amp; Ready recientemente proporcionó servicios de repostaje a un transportista llamado ~mission(TargetName), quien accedió a entregarnos su próximo cargamento como compensación. Pues bien, acabamos de descubrir que el mentiroso vendió su último cargamento a una banda rival. Buscamos a alguien que localice y elimine a ~mission(TargetName|Last) por su traición. Un viejo amigo mío acaba de ver al traidor en ~mission(Location|Address). Parece que lleva más cargamento que no va dirigido a nosotros y viaja con escolta. Solo te pagaremos por destruir el barco, así que todo lo que encuentres a bordo es tuyo. - Smokey</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v> Entrega fallida</v>
-      </c>
-    </row>
-    <row r="1053" xml:space="preserve">
-      <c r="A1053" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mis socios y yo cerramos un trato con un transportista llamado ~mission(TargetName) para que nos entregara suministros. Lo curioso es que el envío nunca llegó. Afirmaron que unos piratas asaltaron su barco y se llevaron nuestros suministros, pero resulta que esa historia es una completa mentira. Mentir para cancelar nuestro trato no puede quedar impune y vas a dejarlo bien claro. ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Mientras mates a ~mission(TargetName|Last), no nos importa lo que pase con la carga que transportan. - Smokey</v>
+        <v>Orden de compra XS: Envío de mineral extraído</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v/>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v> Activar una trampa</v>
+        <v> Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1055" xml:space="preserve">
       <c r="A1055" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un imbécil con el nombre ~mission(TargetName) ha estado tramando un plan: su carguero solicita repostaje solo para emboscar a nuestros barcos al llegar. Incluso cargó la maldita nave con mercancía real para asegurarse de que pasara los escaneos. Hemos corrido la voz para que nadie en Rough &amp; Ready vuelva a caer en la trampa, pero quiero que este cretino sea castigado. Creo que ~mission(TargetName|Last) reconoce a muchos de los nuestros, así que supongo que será mejor pagarte para que te encargues. He oído que lo han visto cerca de ~mission(Location|Address). Dirígete allí ahora mismo y acaba con ese carguero y con cualquiera que lo proteja de una vez por todas. - Smokey</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v> Saboteador de la huelga</v>
+        <v>Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1057" xml:space="preserve">
       <c r="A1057" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Te interesa ir de caza? ~mission(TargetName) saboteó uno de nuestros envíos de combustible y nos costó un montón de créditos, así que busco a alguien que le haga pagar por lo que hizo. Me acaban de avisar de que ~mission(TargetName|Last) fue visto en ~mission(Location|Address). Si vas allí ahora, hay muchas posibilidades de que puedas seguirle la pista y acabar con él definitivamente. ~mission(TargetName|Last) no actuó solo, así que no te sorprendas si va acompañado. - Smokey</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v> Ya era hora.</v>
+        <v>Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1059" xml:space="preserve">
       <c r="A1059" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rough &amp; Ready lleva años haciendo negocios con ~mission(TargetName), pero la relación se ha deteriorado. Durante un tiempo, les suministrábamos combustible a crédito, pero a la hora de cobrar, el cobarde se escondió. Si ~mission(TargetName|Last) no puede pagar con créditos, supongo que pagará con su vida. Un socio acaba de localizar a ~mission(TargetName|Last) en ~mission(Location|Address). Me encantaría que fueras allí ahora mismo para hacer que ese tacaño pague. Por cierto, parece que ~mission(TargetName|Last) no viaja solo, así que asegúrate de tener suficiente combustible antes de ir tras él. - Smokey</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v> Regalo de despedida</v>
+        <v>Orden de compra especial: Materiales extraídos</v>
       </c>
     </row>
     <row r="1061" xml:space="preserve">
       <c r="A1061" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tengo una situación delicada que requiere atención. Tras años de ser un miembro leal de Rough &amp; Ready, ~mission(TargetName) desertó de la banda y está por ahí filtrando secretos a nuestros rivales. Necesitamos eliminar a ~mission(TargetName|Last) de inmediato. En casos como este, siempre es mejor pagarle a alguien ajeno a nosotros para que se encargue. Los escaneos detectaron a ~mission(TargetName|Last) cerca de ~mission(Location|Address) hace poco. Te pagaremos bien para que vayas allí ahora mismo y te encargues de él. ~mission(TargetName|Last) no es tonto y sabe que iremos tras él. Prepárate para una dura batalla y no esperes que esté solo. - Smokey</v>
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Esta orden de compra es más compleja de lo habitual, ya que requiere múltiples métodos de minería, pero dado que has demostrado tu habilidad hasta ahora, creemos que tú y tu equipo están listos para el desafío. Recordatorio: los &lt;EM4&gt;materiales deben estar refinados antes de la entrega&lt;/EM4&gt;, y dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v> Operación de espionaje en silencio</v>
-      </c>
-    </row>
-    <row r="1063" xml:space="preserve">
-      <c r="A1063" t="str" xml:space="preserve">
-        <v xml:space="preserve">El equipo de Rough &amp; Ready busca a alguien para manejar una situación delicada. Hemos descubierto una nave y centinelas orbitales en ~mission(location|address) espiándonos. Estamos en un aprieto porque no queremos iniciar una pelea mayor con quienquiera que esté detrás de esto. Por eso buscamos ayuda a sueldo que pueda encargarse de esto rápida y discretamente. ¿Te interesa? Último consejo: una vez allí, asegúrate de vigilar la nave. Apuesto a que en cuanto empieces a destruir sus centinelas intentarán traer refuerzos para detenerte. - Smokey</v>
+        <v>Derechos mineros de la estación trituradora QV (compartidos)</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v/>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v> Operación de espionaje de Stomp</v>
-      </c>
-    </row>
-    <row r="1065" xml:space="preserve">
-      <c r="A1065" t="str" xml:space="preserve">
-        <v xml:space="preserve">El equipo de Rough &amp; Ready busca un mercenario independiente interesado en algo pesado. Hemos estado vigilando una situación que se está desarrollando en ~mission(location|address), donde varias naves custodian centinelas orbitales que espían nuestras operaciones. Puede que haya nacido de noche, pero no fue anoche. Dada la descarada forma en que están instalados, quien sea el responsable debía saber que tarde o temprano lo descubriríamos. Casi parece que están tendiéndole una trampa a R&amp;R para que ataquemos, y no quiero que caigamos en ella. En cambio, tú lo harás por nosotros y recibirás una buena cantidad de créditos por tu esfuerzo. Las naves estacionadas allí sospecharán menos de una nave no afiliada que se acerque, lo que dificultará que nos atribuyan el ataque. Asegúrate de planificar bien antes de ir. Quizás deberías llevar tus propios refuerzos por si alguna de sus naves escapa y pide ayuda. - Smokey</v>
+        <v> Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v/>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v xml:space="preserve"> Detengan las operaciones de espionaje</v>
-      </c>
-    </row>
-    <row r="1067" xml:space="preserve">
-      <c r="A1067" t="str" xml:space="preserve">
-        <v xml:space="preserve">Mis socios y yo nos encontramos en un pequeño aprieto y necesitamos ayuda. Hay un centinela orbital en ~mission(location|address) que nos está espiando. No sabemos quién lo puso ahí, pero desde luego no puede quedarse. El problema es que somos gente de negocios ante todo y nos preocupa que si lo destruimos nosotros mismos se arme un lío. Por eso es mejor que lo haga alguien como tú. Debería ser un trabajo rápido y fácil para alguien interesado en ganar algo de prestigio. - Smokey</v>
+        <v> Desguace ~misión(NombreObjetivo)</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v> No tengo tiempo que perder, así que iré directo al grano: ~mission(TargetName) tiene que morir y quiero que lo hagas tú. Puedes encontrarlo cerca de ~mission(Location) en ~mission(Location|address). No estará solo, pero no te distraigas con esos otros inútiles. Solo te pagan por eliminar a ~mission(TargetName|Last).</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v> Operación de espionaje de Squash</v>
+        <v> Misión de demolición</v>
       </c>
     </row>
     <row r="1069" xml:space="preserve">
       <c r="A1069" t="str" xml:space="preserve">
-        <v xml:space="preserve">Recientemente hicimos un descubrimiento interesante: alguien instaló varios centinelas orbitales en ~mission(location|address). Supongo que intentan obtener información sobre nuestras operaciones allí. Incluso tienen algunas naves vigilando para asegurarse de que no les pase nada. Por supuesto, queremos deshacernos de estos desgraciados, pero me preocupa que hacerlo nosotros mismos sea perjudicial para el negocio. Por eso buscamos una forma de "negación plausible". Alguien ajeno a R&amp;R que elimine el problema, para que quien esté detrás no pueda vincular directamente el ataque con nosotros. Sé que no será fácil, sobre todo con esos guardias al acecho. ¿Quién sabe cuántos refuerzos tienen preparados? Pero si lo consigues, estamos dispuestos a pagarte como es debido. ¿Crees que tienes las habilidades necesarias para lograrlo? - Smokey</v>
+        <v xml:space="preserve"> Quiero enviar un mensaje contundente al equipo de ~mission(Location|Address) y sé la manera perfecta de hacerlo: causando daños materiales. Solo tienen que ir, destrozar algunas cosas y dejarles bien clara la importancia de respetar a los superiores. Si lo hacen, me sentiré muy feliz. Y generoso. ¿Les interesa?</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v> Echar leña al fuego</v>
+        <v> Toma peligrosa</v>
       </c>
     </row>
     <row r="1071" xml:space="preserve">
       <c r="A1071" t="str" xml:space="preserve">
-        <v xml:space="preserve">Si buscas créditos fáciles, tengo una oferta para ti. Verás, corre el rumor de que ~mission(location|address) está funcionando como depósito de combustible. Parece que no se enteraron de que el comercio de combustible en Pyro pertenece a Rough &amp; Ready. Por eso tienes que ir allí y destruir sus reservas de combustible. Deberían ser fáciles de encontrar. Son los grandes tanques de almacenamiento amarillos repartidos por el puesto de avanzada. Pero ten cuidado, hay torretas defendiendo la zona, así que asegúrate de estar preparado para esquivar sus disparos o volar las armas por los aires. Tú decides cómo llevar a cabo la demolición. Las bombas serían mi primera opción, pero no me importa mucho con tal de que el trabajo se haga. - Smokey</v>
+        <v xml:space="preserve">Tenía la esperanza de que te interesara hacer un pequeño trabajo para nosotros. Hay algunas cosas en ~mission(Location|Address) que están listas para ser tomadas. El único problema es, y es uno grande, que los desgraciados que dirigen el lugar tienen toda la zona sembrada de minas de proximidad. Tendrás que encontrar la manera de pasar, o si no te apetece, la manera de activarlas. En cualquier caso, intenta no volarte por los aires. Luego solo tienes que coger las cosas y llevarlas a ~mission(Destination|Address). No será fácil, pero si lo consigues, te prometo que merecerá la pena.</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v> Invitados no deseados</v>
-      </c>
-    </row>
-    <row r="1073" xml:space="preserve">
-      <c r="A1073" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tenemos a unos forajidos que se están quedando más tiempo del debido en una de nuestras estaciones. Intentaron engañarnos, pero ahora están atrapados en ~mission(location|address). Necesitamos que los elimines. Rough &amp; Ready no quiere que quede ninguno con vida cuando termines. No importa lo complicado que sea, con tal de que se haga, ¿entendido? - Smokey</v>
+        <v> Venganza 01 (En desarrollo)</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v> Descripción de la misión (en desarrollo)</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v> Trabajo de exterminio</v>
-      </c>
-    </row>
-    <row r="1075" xml:space="preserve">
-      <c r="A1075" t="str" xml:space="preserve">
-        <v xml:space="preserve"> En Rough &amp; Ready tenemos un problema de ratas. Una de nuestras tripulaciones intentó amotinarse y ahora se han apoderado de ~mission(location|address). Como no puedo estar completamente seguro de que no tengan simpatizantes a bordo, quiero que te encargues de eliminar a estos traidores. Si logras solucionar este problema de plagas, recibirás una buena recompensa. Solo asegúrate de no dejar a ninguno con vida. No quiero que a nadie más se le ocurran ideas raras. - Smokey</v>
+        <v> Lobo Extra Especial</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v> Wikelo está muy emocionado. Tiene una idea para un nuevo material. Pero fabricarlo es muy complicado. Necesito ayuda para fabricar una muestra de prueba. Te doy el plano, lo fabricas, me lo traes y te lo cambio. Te doy un L-22 Wolf extra especial. Muy potente, muy lobo.</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v> juntos para siempre</v>
-      </c>
-    </row>
-    <row r="1077" xml:space="preserve">
-      <c r="A1077" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aquí está el trato. ~mission(TargetName) y ~mission(TargetName2) deben morir al mismo tiempo. Desafortunadamente, no estarán en el mismo lugar. Un doble impacto puede sonar complicado, pero si contratas algunos artilleros adicionales, no debería ser tan difícil lograr dos impactos simultáneos. Asegúrate de encontrar gente con habilidades, ya que tengo información fidedigna de que cada uno volará con escoltas para "protección".</v>
+        <v xml:space="preserve"> Tu mejor oportunidad</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v>Este rifle dispara muy bien, pero podría tener un diseño más bonito. Arreglo de Wikelo. Ahora se ve muy bien. Te lo doy a cambio. Tráeme cosas y te doy el rifle. Incluso te doy el plano si lo necesitas.</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v> El doble de dolor de cabeza</v>
-      </c>
-    </row>
-    <row r="1079" xml:space="preserve">
-      <c r="A1079" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hay otro par que necesita ser asesinado simultáneamente. Parece que se está volviendo cada vez más popular como opción de asesinato. Esta vez son ~mission(TargetName) y ~mission(TargetName2). Se supone que ambos son operadores bastante hábiles y no volarán solos. Asegúrate de que quien te ayude en esta misión pueda manejar un combate.</v>
+        <v> ¡Prepárate y despega!</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v xml:space="preserve"> Las naves tienen ventanas grandes. Todos pueden verte volar. Debes lucir impecable. Wikelo tiene un traje de vuelo excelente para ti. Intercambia conmigo lo que necesito y Wikelo te dará el traje. Si no tienes el plano, tráemelo también.</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v> lanzamiento simultáneo</v>
+        <v> Tutorial - Tus primeros pasos</v>
       </c>
     </row>
     <row r="1081" xml:space="preserve">
       <c r="A1081" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Adivina qué tienen en común ~mission(TargetName) y ~mission(TargetName2)? ¡Vas a matarlos a ambos! Lo difícil es que necesito que los mates al mismo tiempo para que ninguno pueda escapar, o peor aún, matar a quien intenta matarlo. Así que forma un equipo para rastrear a un objetivo mientras tú te encargas del otro. ¡Divide y vencerás! Y a pesar de que armaron un lío lo suficientemente grande como para que los mataran, entiendo que son bastante débiles. No esperes mucha resistencia.</v>
+        <v xml:space="preserve"> ¡Enhorabuena por tus primeros pasos en el universo! A lo largo de este tutorial, aprenderás a moverte tanto a pie como en el espacio. Para empezar, te familiarizarás con los controles básicos de movimiento y el uso de tu mobiGlas dentro de tu hábitat. Sigue los objetivos y las indicaciones de tu HUD (pantalla de visualización frontal) para completar esta misión.</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v> amigos hasta el final</v>
+        <v> Tutorial - Tu primera salida</v>
       </c>
     </row>
     <row r="1083" xml:space="preserve">
       <c r="A1083" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espero de verdad que no seas amigo de ~mission(TargetName) ni de ~mission(TargetName2), porque necesito que los elimines a ambos... al mismo tiempo... Claro que no nos lo pondrían fácil viajando en la misma nave o algo así de obvio. No. Tendrás que formar una tripulación para poder derribar a ambos objetivos simultáneamente. En cuanto uno de ellos muera, prepárate para eliminar al otro también. No podemos arriesgarnos a que ninguno escape. Y creo que debería mencionar que no solo son buenos pilotos, sino que también viajarán con refuerzos. Seguro que puedes con esto.</v>
+        <v xml:space="preserve">¡Bien hecho! Con la primera parte completada, ya deberías tener cierta familiaridad con los controles de movimiento, la gestión de tu hambre y sed, y algunas de las funciones principales de tu mobiGlas, concretamente el Gestor de Contratos y tu Diario. Esta siguiente sección te ayudará a familiarizarte con ~mission(Location|Name) y te llevará a visitar ~mission(StoreName), una tienda de armas aquí en ~mission(Location|Name). Puedes comprar allí, y en otras tiendas similares, usando Créditos de la Tierra Unida (UEC). Durante la fase alfa del desarrollo de Star Citizen, utilizaremos una moneda llamada aUEC (Créditos de la Tierra Unida Alfa). Esta es una moneda temporal diseñada específicamente para probar la economía y el equilibrio del juego.</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v> doble problema</v>
+        <v> Tutorial - Tu primer vuelo</v>
       </c>
     </row>
     <row r="1085" xml:space="preserve">
       <c r="A1085" t="str" xml:space="preserve">
-        <v xml:space="preserve">Si me hubieras preguntado, te habría dicho que ~mission(TargetName) y ~mission(TargetName2) acabarían matándose entre sí. Pero en cambio, tendrás el honor de eliminarlos a ambos a la vez. Eso sí, tendrás que ganártelo. Son peligrosos. Tienen un historial delictivo, están altamente entrenados y son demasiado listos para volar sin refuerzos. Reúne al mejor equipo posible. Lo necesitarás. Y no seas tacaño. No puedes gastar créditos si estás muerto.</v>
+        <v xml:space="preserve">Ya casi terminas el tutorial. ¡Solo queda despegar! Con tu misión en ~mission(Location|Name) terminada, es hora de abandonar la ciudad y, finalmente, el planeta. Dirígete a las lanzaderas de tránsito de ~mission(TransitNameShort). Estas lanzaderas te pueden llevar por toda ~mission(Location|Name), pero tu destino es el puerto espacial, donde te han proporcionado temporalmente una Anvil C8 Pisces. Esta nave de exploración es una excelente nave de iniciación, perfecta para pilotos novatos que buscan obtener sus alas.</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v> Que la muerte nos separe</v>
+        <v> Ruta de envío local de UDM</v>
       </c>
     </row>
     <row r="1087" xml:space="preserve">
       <c r="A1087" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Es bastante conmovedor encontrarse con una pareja dispuesta a morir el uno por el otro. Estúpido pero conmovedor. ~mission(TargetName) y ~mission(TargetName2) decidieron apoyarse mutuamente y ahora la situación los ha llevado a la muerte. Busca a un amigo y dales caza a estos dos. Asegúrate de matarlos al mismo tiempo. Llámalo justicia poética. Deberían morir fácilmente. Tal vez tengan una o dos naves con ellos, pero no creo que sea nada de qué preocuparse.</v>
+        <v xml:space="preserve">¡Saludos, socio de envíos calificado! Hoy es el día perfecto para adquirir experiencia práctica en envíos. Si dispone de un barco con suficiente espacio de almacenamiento, hay una buena cantidad de paquetes en ~mission(Pickup1) en ~mission(Pickup1|Address) listos para ser entregados. ¡Una excelente oportunidad para el crecimiento profesional! PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>dos por el precio de dos</v>
+        <v>Controlador de paquetes UDM</v>
       </c>
     </row>
     <row r="1089" xml:space="preserve">
       <c r="A1089" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~misión(NombreObjetivo) y ~misión(NombreObjetivo2). Creo que podrían estar emparentados, ¿o saliendo juntos? En realidad no importa, alguien quiere matarlos. He organizado todo para que puedas atacarlos cuando no estén volando juntos. Así estarás más seguro. Son objetivos serios y cuentan con un apoyo igualmente serio. Asegúrate de que tú y tu equipo coordinen bien los ataques. No quiero que ninguno quede con vida, o será un verdadero dolor de cabeza.</v>
+        <v xml:space="preserve">¡Saludos, experto en manipulación de paquetes! Aunque no tengan que ir muy lejos, los siguientes paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; requieren un manejo experto. ¿Eres el experto que buscamos? PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Solo tienes que aceptar el contrato y listo. Esperamos trabajar contigo, Unified Distribution Management -Ofreciendo el paquete completo-</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v> Asistencia en combate</v>
+        <v xml:space="preserve">Ruta de entrega local de UDM</v>
       </c>
     </row>
     <row r="1091" xml:space="preserve">
       <c r="A1091" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) solicita asistencia en combate en ~mission(InitiatorLocation). Si se acepta, recibirá ~mission(PaymentAmount) aUEC al eliminar la amenaza.</v>
+        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! ¿Busca una excusa para surcar los cielos con su nave de carga? Gane créditos y explore la zona con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si ser su propio supervisor y que le paguen por pilotar su propia nave le parece el trabajo perfecto, este contrato es justo lo que estaba buscando. Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v> Asistencia en combate - BAJO RIESGO</v>
+        <v> Evaluación de la entrega local de UDM</v>
       </c>
     </row>
     <row r="1093" xml:space="preserve">
       <c r="A1093" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [BAJO NIVEL DE AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve">¡Saludos, potencial socio de envío cualificado! ¿Listo para contribuir a nuestra creciente red de entregas? ¿Tienes una nave a tu disposición que pueda transportar varios paquetes y volar entre cuerpos celestes y satélites? ¡Unified Distribution Management busca un piloto como tú! Nos encantaría evaluar tu potencial de contratación con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si esto te interesa, ¡acepta esta oferta de inmediato! Solo asegúrate de traer tu propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar contigo, Unified Distribution Management -Entregando el paquete completo-</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>Asistencia en combate - ALTA AMENAZA</v>
+        <v> Reevaluación de la entrega local de UDM</v>
       </c>
     </row>
     <row r="1095" xml:space="preserve">
       <c r="A1095" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [ALTA AMENAZA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve">¡Saludos, antiguo socio naviero cualificado! ¿Estás listo para otra oportunidad de usar tu buque listo para el transporte de carga y ganar créditos? Unified Distribution Management ha elegido el siguiente itinerario cuidadosamente seleccionado como la manera perfecta de reevaluar sus habilidades: PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos volver a trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v> Asistencia en combate - AMENAZA MODERADA</v>
+        <v>Recogida de paquetes UDM</v>
       </c>
     </row>
     <row r="1097" xml:space="preserve">
       <c r="A1097" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [AMENAZA MODERADA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! Si buscas trabajo como repartidor, ¡tenemos la oportunidad perfecta para ti! Un paquete te espera en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser entregado en &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. ¿Suena interesante, verdad? Advertencia: se han registrado varias alertas de seguridad en la zona. Asegúrate de llevar contigo medidas de protección para mantenerte a salvo. Si esto te interesa, ¡acepta esta oferta de inmediato! Esperamos trabajar contigo. Unified Distribution Management -Entregando el paquete completo-</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v> Asistencia en combate - AMENAZA CRÍTICA</v>
-      </c>
-    </row>
-    <row r="1099" xml:space="preserve">
-      <c r="A1099" t="str" xml:space="preserve">
-        <v xml:space="preserve"> [AMENAZA CRÍTICA] ~serviceBeacon(InitiatorName) solicita asistencia de combate en el espacio profundo. Si se acepta, recibirá ~serviceBeacon(PaymentAmount) aUEC al eliminar la amenaza. Distancia a ~serviceBeacon(InitiatorName): ~serviceBeacon(DistToInitiator)</v>
+        <v> SOLICITUD DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="str">
+        <v/>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v> Escolta</v>
-      </c>
-    </row>
-    <row r="1101" xml:space="preserve">
-      <c r="A1101" t="str" xml:space="preserve">
-        <v xml:space="preserve">~mission(InitiatorName) solicita un acompañante en la ubicación: ~mission(InitiatorLocation). Si se acepta, recibirá un pago de ~mission(PaymentAmount) aUEC/minuto hasta que el iniciador lo CANCELE o el proveedor del servicio lo ABANDONE. NOTA: El contrato y el pago comenzarán una vez que se reúna con el cliente.</v>
+        <v xml:space="preserve"> SOLICITUD DE REPOSTAJE CRÍTICA: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="str">
+        <v/>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v xml:space="preserve"> Asistencia médica</v>
-      </c>
-    </row>
-    <row r="1103" xml:space="preserve">
-      <c r="A1103" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) requiere asistencia médica en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
+        <v> SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="str">
+        <v/>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v> Transporte personal</v>
-      </c>
-    </row>
-    <row r="1105" xml:space="preserve">
-      <c r="A1105" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) solicita transporte desde ~mission(InitiatorLocation) hasta ~mission(SelectedDestination). Al completar con éxito este servicio, recibirá ~mission(PaymentAmount) aUEC.</v>
+        <v> REPOSTAJE URGENTE DE LA FLOTA</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="str">
+        <v/>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v> Rescate médico</v>
+        <v> Todas las cosas llegan a su fin.</v>
       </c>
     </row>
     <row r="1107" xml:space="preserve">
       <c r="A1107" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ~mission(InitiatorName) requiere tratamiento médico de emergencia en ~mission(InitiatorLocation). El pago será de ~mission(PaymentAmount) aUEC.</v>
+        <v xml:space="preserve">No sé si conoces ~mission(Location|Address), pero ~mission(TargetName) es quien manda allí. Necesito eliminarlos. Me temo que es más fácil decirlo que hacerlo. Son conocidos por su renuencia a ocuparse personalmente de los asuntos, prefiriendo que sus subordinados se encarguen del trabajo sucio. Dicho esto, si eliminas a suficientes subordinados, no les quedará más remedio que enfrentarse a ti directamente. Atentamente, Vaughn</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v> Eliminar Claimjumpers</v>
+        <v> Se les echará de menos.</v>
       </c>
     </row>
     <row r="1109" xml:space="preserve">
       <c r="A1109" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Acabamos de recibir la noticia de que un contratista de Shubin fue expulsado de una de nuestras concesiones por forajidos que operan allí ilegalmente. Para complicar aún más las cosas, han instalado algunos centinelas orbitales para protegerse mientras extraen minerales. Esperamos contratar a un mercenario que pueda buscar y destruir los centinelas en ~mission(location). Si se encuentra con un minero ilegal en el sitio, tenga en cuenta que es práctica común que este tipo de personas contacten refuerzos para pedir ayuda. Podría ser mejor neutralizarlos lo más rápido posible antes de que puedan hacerlo. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">Un alto funcionario de seguridad llamado ~mission(TargetName) ha sido marcado para su eliminación. Aunque se encuentra en ~mission(Location|Address), no será fácil llegar hasta él. Me temo que será necesario un esfuerzo considerable para atraerlo. Normalmente, recomendaría eliminar a suficientes subordinados como para que se vea obligado a enfrentarse a usted personalmente. Sin embargo, en este caso se requiere un enfoque más delicado. Si bien puede eliminar a todas las fuerzas de seguridad presentes, debe garantizar la seguridad de todos los trabajadores civiles. Sin duda, es una tarea ardua, pero necesaria. Atentamente, Vaughn</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v> Expulsar a los usurpadores de derechos</v>
+        <v> Una oportunidad para impresionar</v>
       </c>
     </row>
     <row r="1111" xml:space="preserve">
       <c r="A1111" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) CONDICIONES*: Un equipo minero independiente local de Stanton estaba trabajando en ~mission(Location) como contratistas de Shubin Interstellar cuando una fuerza hostil atacó y tomó el sitio. Creemos que los perpetradores todavía están en la mina usando el equipo que dejaron para extraer el valioso mineral. Entre el equipo perdido había un puñado de centinelas orbitales que, desafortunadamente, aún no se habían desplegado por completo en el momento del ataque. Los escaneos de largo alcance de la mina nos han llevado a concluir que los forajidos han activado los centinelas orbitales y los están usando para proteger sus operaciones ilegales. Para recuperar el sitio, estamos buscando contratistas que vayan a ~mission(Location), destruyan los centinelas orbitales y limpien el sitio de mineros hostiles. Se recomienda encarecidamente la eficiencia, ya que existe un alto riesgo de que pidan refuerzos una vez que descubran que están siendo desalojados. Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+        <v xml:space="preserve">En primer lugar, permítame presentarme. Para decirlo de forma un tanto dramática, me dedico a la vida. La gente me contrata cuando hay que eliminar a alguien, y yo, a cambio, empleo a la persona perfecta para hacerlo. Esto proporciona seguridad a todas las partes involucradas, ya que nadie conoce la identidad de la otra. Una situación ideal en estos casos. Recientemente me enteré de que usted podría poseer habilidades que me serían útiles y decidí que valdría la pena investigar esta afirmación. Si le interesa establecer una relación laboral, necesitaré una demostración de dichas habilidades. Busque y elimine discretamente a ~mission(TargetName) en ~mission(Location|Address). Si lo logra, será recompensado. Además, habrá demostrado ser digno de ser considerado para futuras contrataciones. Atentamente, Vaughn</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>Eliminar a los saltadores de reclamaciones</v>
+        <v> Otra oportunidad para impresionar</v>
       </c>
     </row>
     <row r="1113" xml:space="preserve">
       <c r="A1113" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar es un plus) TÉRMINOS*: Recientemente se descubrió que un minero renegado se apropió ilegalmente de una concesión minera de Shubin. Si bien el minero ya no parece estar robando mineral del sitio, dejó un centinela orbital que nos impide recuperarlo debido a sus capacidades ofensivas. Buscamos un mercenario dispuesto a viajar a ~mission(location), dar caza al centinela y destruirlo para preparar la recuperación del sitio por parte de Shubin. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
+        <v xml:space="preserve">No es frecuente en la vida tener una segunda oportunidad para causar una buena primera impresión, pero te la voy a brindar. Decir que me decepcionó cómo se desarrollaron las cosas en tu último intento de asesinato sería quedarse corto. Sin embargo, esta es tu oportunidad para demostrar que eres capaz de más. Elimina a ~mission(TargetName) en ~mission(Location|Address) y consideraré que has borrado el pasado. Atentamente, Vaughn</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v> Expulsar a los usurpadores de derechos</v>
-      </c>
-    </row>
-    <row r="1115" xml:space="preserve">
-      <c r="A1115" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUESTO: Seguridad / Mercenario UBICACIÓN: ~mission(LagrangeLocation) EXPERIENCIA LABORAL: Piloto de combate (Experiencia militar deseable) CONDICIONES*: Se descubrió que una concesión minera de Shubin Interstellar, recientemente adquirida y pendiente de procesamiento, había sido usurpada por una compañía minera renegada que está robando mineral del sitio. Si bien se ha notificado a las autoridades locales, existe la preocupación de que se puedan extraer activos valiosos antes de que se inicie una investigación oficial. Por lo tanto, como es nuestro derecho como titulares de la concesión, deseamos contratar una fuerza mercenaria para que se dirija a ~mission(Location) y destruya los centinelas orbitales que protegen esta operación ilegal. Se recomienda precaución, ya que aún podría haber algunos mineros ilegales en el lugar, junto con cualquier refuerzo que reúnan. *Shubin Interstellar es un contratista que ofrece igualdad de oportunidades. Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que se produzca durante la vigencia del contrato.</v>
+        <v> Fin de una salamandra</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="str">
+        <v/>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>Pedido pequeño: Materiales extraídos a mano</v>
+        <v> Un merecido descanso</v>
       </c>
     </row>
     <row r="1117">
@@ -5989,1937 +5989,177 @@
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v> Orden minera pequeña: Sadaryx</v>
-      </c>
-    </row>
-    <row r="1119" xml:space="preserve">
-      <c r="A1119" t="str" xml:space="preserve">
-        <v xml:space="preserve">CONTRATO: Orden de Minería UBICACIÓN: Nyx DETALLES: Uno de nuestros equipos de prospección confirmó recientemente que los asteroides que albergan las Estaciones de Intercambio QV en todo el Cinturón Keeger de Nyx contienen un tipo de mineral raro, Sadaryx. Sin embargo, debido a la dificultad de acceso a estas estaciones y los riesgos inherentes, estamos buscando equipos de minería externos para encargarse de la extracción. No tenemos una ubicación confirmada de dónde se encuentran los depósitos de Sadaryx dentro de la estación, pero recomendamos comenzar con las secciones de cuevas donde los minerales se forman naturalmente. Si tienen mucha suerte, incluso podrían encontrar algunos cristales almacenados que fueron extraídos por los antiguos equipos de trabajo de QV. &lt;EM4&gt;TÉRMINOS*:&lt;/EM4&gt; Su equipo deberá obtener acceso a una &lt;EM4&gt;Estación de Intercambio QV&lt;/EM4&gt;, recolectar el &lt;EM4&gt;mineral Sadaryx&lt;/EM4&gt; requerido y entregarlo al montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Esto requerirá una multiherramienta con accesorio de minería y conocimientos básicos de minería manual. Nuestros equipos de prospección han informado que estas estaciones podrían haber sido infiltradas por forajidos. Se recomienda precaución. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+        <v> Un contrato desafiante</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="str">
+        <v/>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>Pedido pequeño: Materiales extraídos a mano</v>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" t="str">
-        <v/>
+        <v> Localizar a un miembro de la pandilla</v>
+      </c>
+    </row>
+    <row r="1121" xml:space="preserve">
+      <c r="A1121" t="str" xml:space="preserve">
+        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de nivel Clips de la banda Headhunters, ~mission(TargetName|Last) ha liderado operaciones dirigidas contra operativos, misiones e infraestructura de XenoThreat. Por estas transgresiones, XenoThreat pagará a cualquiera que logre localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto cerca de ~mission(Location|Address) hace poco. Si decide aceptar este contrato, diríjase a las coordenadas de inmediato. ~mission(TargetName|Last) sabe que lo estamos buscando y ha estado viajando con un escolta recientemente. No se sorprenda si no está solo. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v> Gran orden de compra: Materiales extraídos a mano</v>
+        <v> Localiza al traidor</v>
       </c>
     </row>
     <row r="1123" xml:space="preserve">
       <c r="A1123" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). ~mission(TargetName|Last), un conocido miembro de la banda Headhunters, ha traicionado a la humanidad al ser un aliado alienígena conocido con quien mantiene relaciones tanto personales como comerciales. XenoThreat exige que estas relaciones traidoras cesen de inmediato antes de que traigan más influencia alienígena a Pyro. Recompensaremos a quien logre localizar y asesinar a ~mission(TargetName|Last) por estos crímenes contra la humanidad. ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v> Orden de compra médica: Materiales extraídos a mano</v>
+        <v> Rastrear al espía</v>
       </c>
     </row>
     <row r="1125" xml:space="preserve">
       <c r="A1125" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde extraer&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de la banda Headhunters, ~mission(TargetName|Last) hackeó los sistemas de XenoThreat para robar información sobre nuestras operaciones y personal. El daño causado solo puede repararse asegurándonos de que ~mission(TargetName|Last) jamás vuelva a hacer algo así. Por eso, XenoThreat pagará a cualquiera que pueda localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: Escaneos recientes identificaron a ~mission(TargetName|Last) viajando con otras naves cerca de ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v> Orden de compra XL: Materiales extraídos a mano</v>
+        <v> Centinelas del silencio</v>
       </c>
     </row>
     <row r="1127" xml:space="preserve">
       <c r="A1127" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de materiales raros. Agradecemos su ayuda en este asunto. Solo se conocen algunas ubicaciones donde se pueden obtener estos materiales, principalmente de los sitios ahora inactivos del Grupo Hathor en &lt;EM4&gt;Daymar y Aberdeen&lt;/EM4&gt;. Nuestra sugerencia sería dirigirse a las Instalaciones de Alineación de Plataformas (PAF) e intentar reactivar su Plataforma Láser Orbital (OLP) para acceder a los materiales debajo de la superficie del planeta. Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+        <v xml:space="preserve">Nuestro movimiento de resistencia crece día a día, pero esto conlleva cierta atención no deseada. Escaneos recientes descubrieron centinelas orbitales en ~mission(location|address) y una nave patrullando. Creemos que esto forma parte de una campaña de espionaje contra XenoThreat, probablemente financiada por la UEE. Buscamos un mercenario experimentado dispuesto a destruir los centinelas cuanto antes. Dado que ya nos tienen vigilados, enviar a alguien ajeno a la organización llamaría menos la atención. Si aceptas el trabajo, recibirás tu pago inmediatamente una vez destruidos los centinelas. Ahora bien, aunque la nave patrulla no es el objetivo principal, sospechamos que si escapa podría tener refuerzos en reserva. Sería prudente neutralizarla cuanto antes. Si decides ayudarnos, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>Orden de compra XL: Materiales extraídos a mano</v>
+        <v> Aniquilar centinelas</v>
       </c>
     </row>
     <row r="1129" xml:space="preserve">
       <c r="A1129" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">Escaneos recientes descubrieron varios centinelas orbitales y naves en ~mission(location|address). Creemos que forman parte de una campaña de espionaje contra XenoThreat, en respuesta a nuestras acciones recientes en el sistema Stanton. Parece que XenoThreat está haciendo algo bien, si están espiando de esta manera. Buscamos un mercenario experimentado y altamente capacitado dispuesto a eliminar esta operación. Si no quieres que Pyro se convierta en un sistema de vigilancia, esta es tu oportunidad para impedirlo. Los centinelas probablemente no representen un gran problema, pero ten cuidado con las naves de patrulla. Si logran escapar, tendrás muchos más problemas pisándote los talones. Te estaremos agradecidos y te pagaremos generosamente una vez que completes el trabajo. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v> Pedido pequeño: Materiales extraídos a mano</v>
-      </c>
-    </row>
-    <row r="1131">
-      <c r="A1131" t="str">
-        <v/>
+        <v> Finalización de la vigilancia</v>
+      </c>
+    </row>
+    <row r="1131" xml:space="preserve">
+      <c r="A1131" t="str" xml:space="preserve">
+        <v xml:space="preserve">Parece que nuestra lucha por liberar a la humanidad tiene nerviosos a los lacayos del gobierno en la Tierra. Escaneos recientes descubrieron un centinela orbital en ~mission(location|address) que creemos forma parte de una campaña de espionaje de la UEE. Según nuestros informes, están entregando los datos directamente a los propios slinks. Solo se ha detectado un centinela hasta ahora, pero quién sabe hasta dónde llegará la operación si no se desactiva. No debería ser demasiado problema para un mercenario habilidoso. Si te identificas con esto, recibirás el pago inmediatamente después de destruir el centinela. Además, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v> Pedido pequeño: Materiales extraídos a mano</v>
-      </c>
-    </row>
-    <row r="1133">
-      <c r="A1133" t="str">
-        <v/>
+        <v> Erradicar centinelas</v>
+      </c>
+    </row>
+    <row r="1133" xml:space="preserve">
+      <c r="A1133" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Valoras la libertad de la humanidad? Si es así, te ofrezco la oportunidad de demostrarlo. Escaneos recientes han detectado centinelas orbitales y naves patrullando en ~mission(location|address). Creemos que forman parte de una campaña de espionaje de la UEE contra XenoThreat. Es crucial detener su labor de recopilación de inteligencia antes de lanzar nuestra próxima misión. Buscamos un mercenario experimentado dispuesto a eliminar estas fuerzas de inmediato. Los centinelas son la prioridad, pero las naves podrían representar un problema mayor si logran escapar. Deberás evaluar la situación con más detalle una vez que estés en el lugar. Podríamos encargarnos nosotros mismos, pero preferimos enviar a un contratista para que los responsables no sepan quién los atacó. El pago se realizará puntualmente al finalizar la misión. Además, tendrás la satisfacción de saber que estás ayudando a una buena causa. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v> Gran orden de compra: Materiales extraídos a mano</v>
+        <v> Borrado total del servidor</v>
       </c>
     </row>
     <row r="1135" xml:space="preserve">
       <c r="A1135" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">Uno de nuestros agentes de datos desapareció mientras transportaba información operativa vital. Hace unas horas, determinamos que fue atacado por un grupo de asalto de Headhunters y que el contenido de los almacenes de datos de la nave fue transferido a sus servidores en ~mission(location|address). Si bien tenemos motivos para creer que nuestro cifrado resistirá, no podemos arriesgarnos a que el contenido de esos archivos quede expuesto. Se le ordena dirigirse allí y garantizar la privacidad de nuestros datos destruyendo los servidores de Headhunters. Le recomiendo encarecidamente que actúe con la máxima minuciosidad. Destruya todo y a todos los que pueda. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v> Gran orden de compra: Materiales extraídos a mano</v>
+        <v> Sabotaje de la línea de suministro</v>
       </c>
     </row>
     <row r="1137" xml:space="preserve">
       <c r="A1137" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">Los supuestos “activistas” de salón de Ciudadanos por la Prosperidad siguen intentando extender su influencia por todo el sistema. Con tu ayuda, existe la oportunidad de desmantelar sus operaciones de raíz. El grupo utiliza ~mission(location|address) para distribuir suministros a independientes dispersos por todo el planeta. Si destruimos la ~mission(ship) ubicada allí, su red colapsará. Un bombardeo enviaría un mensaje claro, pero te dejo a ti la decisión sobre el método de destrucción. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v> Orden de compra médica: Materiales extraídos a mano</v>
+        <v> Orden de eliminación: "Ciudadanos" en ~mission(location)</v>
       </c>
     </row>
     <row r="1139" xml:space="preserve">
       <c r="A1139" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde extraer&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+        <v xml:space="preserve">El grupo de instigadores que se autodenomina «Ciudadanos por la Prosperidad» ya no puede seguir difundiendo sus mentiras y propaganda impunemente. Como un claro recordatorio de quién controla realmente a Pyro, hemos emitido una orden de eliminación para erradicar toda presencia de «Ciudadanos» en ~misión(ubicación|dirección). Es probable que haya resistencia, pero esperamos que la resuelvan sin mayores dificultades. Sigan las instrucciones y recibirán una buena recompensa por su trabajo. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v> Orden de compra XL: Materiales extraídos a mano</v>
+        <v> Lucha por un Pyro gratis</v>
       </c>
     </row>
     <row r="1141" xml:space="preserve">
       <c r="A1141" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de materiales raros. Agradecemos su ayuda en este asunto. Solo se conocen algunas ubicaciones donde se pueden obtener estos materiales, principalmente de los sitios ahora inactivos del Grupo Hathor en &lt;EM4&gt;Daymar y Aberdeen&lt;/EM4&gt;. Nuestra sugerencia sería dirigirse a las Instalaciones de Alineación de Plataformas (PAF) e intentar reactivar su Plataforma Láser Orbital (OLP) para acceder a los materiales debajo de la superficie del planeta. Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+        <v xml:space="preserve">Los esfuerzos de XenoThreat por evitar que influencias externas infecten este sistema están siendo puestos a prueba por un grupo que se atreve a llamarse Ciudadanos por la Prosperidad. Un miembro destacado del grupo, ~mission(TargetName), ha establecido operaciones en ~mission(Location|Address) y ya está trabajando arduamente difundiendo sus mentiras y propaganda a cualquiera que quiera escuchar. Si queremos que Pyro permanezca independiente de la UEE y de la influencia alienígena, entonces debemos hacer algo al respecto ahora. Por eso XenoThreat está emitiendo una orden de eliminación para ~mission(TargetName|Last). Y sabiendo lo importantes que son para las operaciones de Ciudadanos por la Prosperidad, no me sorprendería que tuvieras que abrirte paso luchando contra un grupo de sus seguidores más fanáticos antes de siquiera tener la oportunidad de dispararles. Pero recuerda que ~mission(TargetName|Last) es tu objetivo, y el pago depende únicamente de que te asegures de eliminarlo. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
+        <v> Búsqueda de talentos</v>
       </c>
     </row>
     <row r="1143" xml:space="preserve">
       <c r="A1143" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
+        <v xml:space="preserve">Los Cazadores de Cabezas han reunido un equipo de ataque especial cuyo único propósito es atacar, interrumpir y sabotear nuestras operaciones. Aunque me cueste admitirlo, han tenido algunos éxitos menores y se están convirtiendo rápidamente en una preocupación. XenoThreat sabe que la mejor manera de matar a una serpiente es cortándole la cabeza, así que emitimos una orden de eliminación para el comandante del equipo de ataque, ~mission(TargetName), quien, según nuestras fuentes de inteligencia, se ha estado escondiendo en ~mission(Location|Address) durante algunos días. Preveo una fuerte resistencia por parte de las fuerzas de los Cazadores de Cabezas allí. Por lo que hemos oído, ~mission(TargetName|Last) recibió este mando en parte debido a la feroz lealtad que inspira en los demás. Reunir a tu propio equipo para abordar esto sería una sólida estrategia operativa. Feliz caza de cabezas, Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>Gran orden de compra: Envío de mineral extraído</v>
+        <v> Robar subsidios</v>
       </c>
     </row>
     <row r="1145" xml:space="preserve">
       <c r="A1145" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve">Típico de la UEE mentirosa, decir que no está involucrada en las operaciones de Ciudadanos por la Prosperidad simplemente porque "donan" suministros a una organización de ayuda terciaria que luego se los entrega inmediatamente. Acabamos de enterarnos de que uno de estos envíos de ayuda gubernamental fue entregado en un puesto avanzado alineado con Ciudadanos por la Prosperidad. Por eso te pagaremos para que asaltes ~mission(Pickup1|Address) y reclames el ~mission(item) para la causa. Una vez que entregues todo en ~mission(Dropoff1|Address), podremos redistribuir el envío para ayudar en nuestra lucha. No hay nada mejor que usar los recursos del enemigo en su contra. Pero no creas que te lo van a entregar así como así. Aunque se supone que Ciudadanos por la Prosperidad está aquí para traer la paz, será mejor que estés preparado para enfrentarte a ellos. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v> Orden de compra médica: Envío de mineral extraído</v>
+        <v> Suministros para la recuperación de bienes</v>
       </c>
     </row>
     <row r="1147" xml:space="preserve">
       <c r="A1147" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
+        <v xml:space="preserve">Por mucho que XenoThreat se haya esforzado por hacer de Pyro un refugio seguro para los humanos, no todos comparten nuestros objetivos. Entre ellos destacan los Cazadores de Cabezas, que se han degradado al contratar a un transportista alienígena para que les entregue suministros. Perdimos la oportunidad de interceptar ese cargamento, pero aun así queremos dejar claro que no se tolerará la colaboración con alienígenas bajo ninguna circunstancia en este sistema. El cargamento fue entregado en ~mission(Pickup1|Address). Queremos que alguien ataque el puesto de avanzada, reclame el ~mission(item) y lo lleve a ~mission(Dropoff1|Address) para que podamos deshacernos de él adecuadamente. ¿Te animas a mantener Pyro libre de la influencia alienígena? Comm. Spec. Engler</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>Orden de compra mayor: Envío de mineral extraído</v>
+        <v> Agente del Caos</v>
       </c>
     </row>
     <row r="1149" xml:space="preserve">
       <c r="A1149" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
+        <v xml:space="preserve">Ciudadanos por la Prosperidad se han atrincherado en ~mission(Pickup1|Address). Para evitar que se acomoden demasiado en esa estación, queremos mostrarles cómo es realmente la vida en nuestro sistema. Te pagaremos para que vayas a la estación, recojas el ~mission(item) y mates a cualquiera que se interponga en tu camino. El pago depende de que entregues esos suministros en ~mission(Dropoff1|Address). Cualquiera que mates será una ventaja. Especialista en Comunicaciones Engler</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>Orden de compra XS: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1151">
-      <c r="A1151" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1152">
-      <c r="A1152" t="str">
-        <v> Orden de compra XL: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1153" xml:space="preserve">
-      <c r="A1153" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1154">
-      <c r="A1154" t="str">
-        <v>Orden de compra XL: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1155" xml:space="preserve">
-      <c r="A1155" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1156">
-      <c r="A1156" t="str">
-        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1157" xml:space="preserve">
-      <c r="A1157" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
-      </c>
-    </row>
-    <row r="1158">
-      <c r="A1158" t="str">
-        <v>Gran orden de compra: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1159" xml:space="preserve">
-      <c r="A1159" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1160">
-      <c r="A1160" t="str">
-        <v> Gran orden de compra: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1161" xml:space="preserve">
-      <c r="A1161" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1162">
-      <c r="A1162" t="str">
-        <v> Orden de compra médica: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1163" xml:space="preserve">
-      <c r="A1163" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
-      </c>
-    </row>
-    <row r="1164">
-      <c r="A1164" t="str">
-        <v>Orden de compra mayor: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1165" xml:space="preserve">
-      <c r="A1165" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1166">
-      <c r="A1166" t="str">
-        <v>Orden de compra XL: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1167" xml:space="preserve">
-      <c r="A1167" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1168">
-      <c r="A1168" t="str">
-        <v>Orden de compra especial: Materiales extraídos</v>
-      </c>
-    </row>
-    <row r="1169" xml:space="preserve">
-      <c r="A1169" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Esta orden de compra es más compleja de lo habitual, ya que requiere múltiples métodos de minería, pero dado que has demostrado tu habilidad hasta ahora, creemos que tú y tu equipo están listos para el desafío. Recordatorio: los &lt;EM4&gt;materiales deben estar refinados antes de la entrega&lt;/EM4&gt;, y dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1170">
-      <c r="A1170" t="str">
-        <v>Pedido de compra pequeño: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1171" xml:space="preserve">
-      <c r="A1171" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Debido a cambios en nuestra cadena de suministro, Shubin Interstellar está buscando actualmente comprar una variedad de materiales refinados de mineros independientes que operan en el área. Si bien vender en un centro comercial puede generar un precio más competitivo que cumplir con nuestro pedido, muchos mineros consideran que fortalecer sus vínculos con Shubin es una sabia inversión a largo plazo para su carrera. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Mientras esté allí, no dude en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si desea un repaso sobre cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben ser refinados antes de su entrega&lt;/EM4&gt;. Esto puede hacerse en cualquier refinería, cuyas ubicaciones se encuentran en su Mapa Estelar. Cuando esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
-      </c>
-    </row>
-    <row r="1172">
-      <c r="A1172" t="str">
-        <v>Gran orden de compra: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1173" xml:space="preserve">
-      <c r="A1173" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1174">
-      <c r="A1174" t="str">
-        <v> Gran orden de compra: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1175" xml:space="preserve">
-      <c r="A1175" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1176">
-      <c r="A1176" t="str">
-        <v>Gran orden de compra: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1177" xml:space="preserve">
-      <c r="A1177" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1178">
-      <c r="A1178" t="str">
-        <v> Orden de compra médica: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1179" xml:space="preserve">
-      <c r="A1179" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulte &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en su Diario mobiGlas. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Tenga en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se pueden encontrar en su Mapa estelar. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
-      </c>
-    </row>
-    <row r="1180">
-      <c r="A1180" t="str">
-        <v>Orden de compra mayor: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1181" xml:space="preserve">
-      <c r="A1181" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="str">
-        <v>Orden de compra XS: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1183">
-      <c r="A1183" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1184">
-      <c r="A1184" t="str">
-        <v> Orden de compra XL: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1185" xml:space="preserve">
-      <c r="A1185" t="str" xml:space="preserve">
-        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1186">
-      <c r="A1186" t="str">
-        <v>Orden de compra XL: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1187" xml:space="preserve">
-      <c r="A1187" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1188">
-      <c r="A1188" t="str">
-        <v>Orden de compra XL: Envío de mineral extraído</v>
-      </c>
-    </row>
-    <row r="1189" xml:space="preserve">
-      <c r="A1189" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Muchos de estos minerales son extremadamente raros y difíciles de encontrar, detectables solo cuando una roca se ha abierto. Recordatorio, todos los &lt;EM4&gt;materiales deben ser refinados antes de la entrega&lt;/EM4&gt;, y dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales refinados requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ninguna manera por los daños acumulados durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1190">
-      <c r="A1190" t="str">
-        <v>Orden de compra especial: Materiales extraídos</v>
-      </c>
-    </row>
-    <row r="1191" xml:space="preserve">
-      <c r="A1191" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra de una variedad de materiales refinados. Esta orden de compra es más compleja de lo habitual, ya que requiere múltiples métodos de minería, pero dado que has demostrado tu habilidad hasta ahora, creemos que tú y tu equipo están listos para el desafío. Recordatorio: los &lt;EM4&gt;materiales deben estar refinados antes de la entrega&lt;/EM4&gt;, y dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable de ningún daño acumulado durante la duración del contrato.</v>
-      </c>
-    </row>
-    <row r="1192">
-      <c r="A1192" t="str">
-        <v>Pedido de suministro: Lentes Sadaryx Focus</v>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1194">
-      <c r="A1194" t="str">
-        <v> Derechos mineros de la estación trituradora QV (compartidos)</v>
-      </c>
-    </row>
-    <row r="1195">
-      <c r="A1195" t="str">
-        <v> Derechos mineros de la estación trituradora QV (compartidos)</v>
-      </c>
-    </row>
-    <row r="1196">
-      <c r="A1196" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-320</v>
-      </c>
-    </row>
-    <row r="1197">
-      <c r="A1197" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-320</v>
-      </c>
-    </row>
-    <row r="1198">
-      <c r="A1198" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-546</v>
-      </c>
-    </row>
-    <row r="1199">
-      <c r="A1199" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-546</v>
-      </c>
-    </row>
-    <row r="1200">
-      <c r="A1200" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-127</v>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-127</v>
-      </c>
-    </row>
-    <row r="1202">
-      <c r="A1202" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-425</v>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-425</v>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-608</v>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-608</v>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-267</v>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-267</v>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-235</v>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-235</v>
-      </c>
-    </row>
-    <row r="1210">
-      <c r="A1210" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-304</v>
-      </c>
-    </row>
-    <row r="1211">
-      <c r="A1211" t="str">
-        <v>Derechos mineros (compartidos) de la estación trituradora QV BRK-304</v>
-      </c>
-    </row>
-    <row r="1212">
-      <c r="A1212" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-521</v>
-      </c>
-    </row>
-    <row r="1213">
-      <c r="A1213" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-521</v>
-      </c>
-    </row>
-    <row r="1214">
-      <c r="A1214" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-985</v>
-      </c>
-    </row>
-    <row r="1215">
-      <c r="A1215" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-985</v>
-      </c>
-    </row>
-    <row r="1216">
-      <c r="A1216" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-542</v>
-      </c>
-    </row>
-    <row r="1217">
-      <c r="A1217" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-542</v>
-      </c>
-    </row>
-    <row r="1218">
-      <c r="A1218" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-184</v>
-      </c>
-    </row>
-    <row r="1219">
-      <c r="A1219" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-184</v>
-      </c>
-    </row>
-    <row r="1220">
-      <c r="A1220" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-970</v>
-      </c>
-    </row>
-    <row r="1221">
-      <c r="A1221" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-970</v>
-      </c>
-    </row>
-    <row r="1222">
-      <c r="A1222" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-879</v>
-      </c>
-    </row>
-    <row r="1223">
-      <c r="A1223" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-879</v>
-      </c>
-    </row>
-    <row r="1224">
-      <c r="A1224" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-563</v>
-      </c>
-    </row>
-    <row r="1225">
-      <c r="A1225" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-563</v>
-      </c>
-    </row>
-    <row r="1226">
-      <c r="A1226" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-782</v>
-      </c>
-    </row>
-    <row r="1227">
-      <c r="A1227" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-782</v>
-      </c>
-    </row>
-    <row r="1228">
-      <c r="A1228" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-711</v>
-      </c>
-    </row>
-    <row r="1229">
-      <c r="A1229" t="str">
-        <v>Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-711</v>
-      </c>
-    </row>
-    <row r="1230">
-      <c r="A1230" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-284</v>
-      </c>
-    </row>
-    <row r="1231">
-      <c r="A1231" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-284</v>
-      </c>
-    </row>
-    <row r="1232">
-      <c r="A1232" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-437</v>
-      </c>
-    </row>
-    <row r="1233">
-      <c r="A1233" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-437</v>
-      </c>
-    </row>
-    <row r="1234">
-      <c r="A1234" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-630</v>
-      </c>
-    </row>
-    <row r="1235">
-      <c r="A1235" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-630</v>
-      </c>
-    </row>
-    <row r="1236">
-      <c r="A1236" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-892</v>
-      </c>
-    </row>
-    <row r="1237">
-      <c r="A1237" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-892</v>
-      </c>
-    </row>
-    <row r="1238">
-      <c r="A1238" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-597</v>
-      </c>
-    </row>
-    <row r="1239">
-      <c r="A1239" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-597</v>
-      </c>
-    </row>
-    <row r="1240">
-      <c r="A1240" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-110</v>
-      </c>
-    </row>
-    <row r="1241">
-      <c r="A1241" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-110</v>
-      </c>
-    </row>
-    <row r="1242">
-      <c r="A1242" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-913</v>
-      </c>
-    </row>
-    <row r="1243">
-      <c r="A1243" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-913</v>
-      </c>
-    </row>
-    <row r="1244">
-      <c r="A1244" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-864</v>
-      </c>
-    </row>
-    <row r="1245">
-      <c r="A1245" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-864</v>
-      </c>
-    </row>
-    <row r="1246">
-      <c r="A1246" t="str">
-        <v> Derechos mineros (compartidos) de la estación trituradora QV BRK-529</v>
-      </c>
-    </row>
-    <row r="1247">
-      <c r="A1247" t="str">
-        <v>Derechos mineros (compartidos) de la estación trituradora QV BRK-529</v>
-      </c>
-    </row>
-    <row r="1248">
-      <c r="A1248" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-709</v>
-      </c>
-    </row>
-    <row r="1249">
-      <c r="A1249" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-709</v>
-      </c>
-    </row>
-    <row r="1250">
-      <c r="A1250" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-766</v>
-      </c>
-    </row>
-    <row r="1251">
-      <c r="A1251" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-766</v>
-      </c>
-    </row>
-    <row r="1252">
-      <c r="A1252" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-223</v>
-      </c>
-    </row>
-    <row r="1253">
-      <c r="A1253" t="str">
-        <v> Derechos de explotación minera (compartidos) de la planta trituradora QV BRK-223</v>
-      </c>
-    </row>
-    <row r="1254">
-      <c r="A1254" t="str">
-        <v> Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
-      </c>
-    </row>
-    <row r="1255">
-      <c r="A1255" t="str">
-        <v> Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
-      </c>
-    </row>
-    <row r="1256">
-      <c r="A1256" t="str">
-        <v> Desguace ~misión(NombreObjetivo)</v>
-      </c>
-    </row>
-    <row r="1257">
-      <c r="A1257" t="str">
-        <v> No tengo tiempo que perder, así que iré directo al grano: ~mission(TargetName) tiene que morir y quiero que lo hagas tú. Puedes encontrarlo cerca de ~mission(Location) en ~mission(Location|address). No estará solo, pero no te distraigas con esos otros inútiles. Solo te pagan por eliminar a ~mission(TargetName|Last).</v>
-      </c>
-    </row>
-    <row r="1258">
-      <c r="A1258" t="str">
-        <v> Misión de demolición</v>
-      </c>
-    </row>
-    <row r="1259" xml:space="preserve">
-      <c r="A1259" t="str" xml:space="preserve">
-        <v xml:space="preserve">Quiero enviar un mensaje contundente al equipo de ~mission(Location|Address) y sé la manera perfecta de hacerlo: causando daños materiales. Solo tienen que ir, destrozar algunas cosas y dejarles bien clara la importancia de respetar a los superiores. Si lo hacen, me sentiré muy feliz. Y generoso. ¿Les interesa?</v>
-      </c>
-    </row>
-    <row r="1260">
-      <c r="A1260" t="str">
-        <v> Toma peligrosa</v>
-      </c>
-    </row>
-    <row r="1261" xml:space="preserve">
-      <c r="A1261" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Tenía la esperanza de que te interesara hacer un pequeño trabajo para nosotros. Hay algunas cosas en ~mission(Location|Address) que están listas para ser tomadas. El único problema es, y es uno grande, que los desgraciados que dirigen el lugar tienen toda la zona sembrada de minas de proximidad. Tendrás que encontrar la manera de pasar, o si no te apetece, la manera de activarlas. En cualquier caso, intenta no volarte por los aires. Luego solo tienes que coger las cosas y llevarlas a ~mission(Destination|Address). No será fácil, pero si lo consigues, te prometo que merecerá la pena.</v>
-      </c>
-    </row>
-    <row r="1262">
-      <c r="A1262" t="str">
-        <v> Venganza 01 (En desarrollo)</v>
-      </c>
-    </row>
-    <row r="1263">
-      <c r="A1263" t="str">
-        <v>Descripción de la misión (en desarrollo)</v>
-      </c>
-    </row>
-    <row r="1264">
-      <c r="A1264" t="str">
-        <v> Cambiar las cosas a favor</v>
-      </c>
-    </row>
-    <row r="1265">
-      <c r="A1265" t="str">
-        <v> Cambiar las cosas a favor</v>
-      </c>
-    </row>
-    <row r="1266">
-      <c r="A1266" t="str">
-        <v> ¿Intercambiar cupones de mercaderes por favores?</v>
-      </c>
-    </row>
-    <row r="1267" xml:space="preserve">
-      <c r="A1267" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Wikelo tiene otra forma de conseguir favores si te interesa. Tu alma mercenaria tiene metales de "scriptos", que se usan como favores, pero están hechos de un metal muy interesante que Wikelo necesita para un nuevo proyecto. Si llevas los scrips a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, los cambiaremos por favores. Adiós.</v>
-      </c>
-    </row>
-    <row r="1268">
-      <c r="A1268" t="str">
-        <v> ¿El Consejo Comercial ofrece vales a cambio de favores?</v>
-      </c>
-    </row>
-    <row r="1269" xml:space="preserve">
-      <c r="A1269" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Si buscas otra forma de obtener favores de Wikelo, tengo algo para ti. Wikelo necesita vales que le entrega el grupo del Consejo. Wikelo no forma parte de la banda de ladrones, pero tiene negocios de vez en cuando. Si llevas vales a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, los intercambiarás por favores. Adiós.</v>
-      </c>
-    </row>
-    <row r="1270">
-      <c r="A1270" t="str">
-        <v> ¿Intercambiar partes de gusanos por favores?</v>
-      </c>
-    </row>
-    <row r="1271" xml:space="preserve">
-      <c r="A1271" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hay una nueva forma de obtener favores de Wikelo. Se habla mucho de gusanos en tormentas de radiación. Está compuesto de muchas piezas interesantes que Wikelo utiliza. Si llevas piezas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, las intercambiarás por favores. Adiós.</v>
-      </c>
-    </row>
-    <row r="1272">
-      <c r="A1272" t="str">
-        <v> ¿Quieres Polaris? Necesitas algo especial.</v>
-      </c>
-    </row>
-    <row r="1273">
-      <c r="A1273" t="str">
-        <v> ¿Quieres Polaris? Necesitas algo especial.</v>
-      </c>
-    </row>
-    <row r="1274">
-      <c r="A1274" t="str">
-        <v> Wikelo llega al sistema</v>
-      </c>
-    </row>
-    <row r="1275">
-      <c r="A1275" t="str">
-        <v> Wikelo llega al sistema</v>
-      </c>
-    </row>
-    <row r="1276">
-      <c r="A1276" t="str">
-        <v> Tengo mucha hambre</v>
-      </c>
-    </row>
-    <row r="1277">
-      <c r="A1277" t="str">
-        <v> Tengo mucha hambre</v>
-      </c>
-    </row>
-    <row r="1278">
-      <c r="A1278" t="str">
-        <v> Mira el desierto pero no te ve.</v>
-      </c>
-    </row>
-    <row r="1279" xml:space="preserve">
-      <c r="A1279" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Estás en el desierto caliente haciendo cosas. Necesitas ser sigiloso. No quieres que te vean. Entiende. Wikelo te dará una armadura que te hará sigiloso en la arena. Trae las cosas a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y lo haré. Fácil. Adiós.</v>
-      </c>
-    </row>
-    <row r="1280">
-      <c r="A1280" t="str">
-        <v> Hacer un arma Sandy</v>
-      </c>
-    </row>
-    <row r="1281" xml:space="preserve">
-      <c r="A1281" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Wikelo puede hacer que la nueva pistola VOLT parezca un montón de arena. Es muy sigilosa en el desierto. Lleva las cosas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y Wikelo se encargará. Adiós.</v>
-      </c>
-    </row>
-    <row r="1282">
-      <c r="A1282" t="str">
-        <v> ¿Quieres que tu armadura parezca un árbol?</v>
-      </c>
-    </row>
-    <row r="1283" xml:space="preserve">
-      <c r="A1283" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola. ¿Te gusta pasear por el bosque pero no quieres que nadie lo sepa? Wikelo tiene una armadura para ti. Si la traes a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;, podrás conseguirla. ¿Te interesa?</v>
-      </c>
-    </row>
-    <row r="1284">
-      <c r="A1284" t="str">
-        <v> Pistola Zappy más parecida a la madera</v>
-      </c>
-    </row>
-    <row r="1285" xml:space="preserve">
-      <c r="A1285" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Wikelo se enteró de un nuevo tipo de arma de energía de VOLT souli. Golpeó muy fuerte. Si quieres, Wikelo puede hacer que el arma se vea aún mejor. Se encontró en la tormenta, dispara tormenta, pero Wikelo la hizo parecer más leñosa. ¿Cayó en el bosque? Desapareció. Trae las cosas a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y Wikelo lo hará. Adiós.</v>
-      </c>
-    </row>
-    <row r="1286">
-      <c r="A1286" t="str">
-        <v> Fabricar armadura naval espacial</v>
-      </c>
-    </row>
-    <row r="1287" xml:space="preserve">
-      <c r="A1287" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Sé que a los humanos les gusta la armada. Wikelo lo entiende. Barcos muy grandes. Y poderosos también. Wikelo puede darte un conjunto de armadura que parezca de color azul marino. Es muy fácil de hacer. Mira lo que Wikelo necesita, consíguelo y tráelo a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y será tuyo. Wikelo</v>
-      </c>
-    </row>
-    <row r="1288">
-      <c r="A1288" t="str">
-        <v> El arma Volt es más parecida a la de la Marina.</v>
-      </c>
-    </row>
-    <row r="1289" xml:space="preserve">
-      <c r="A1289" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wikelo se enteró de la nueva arma de energía de VOLT Souli. Si quieres, Wikelo puede mejorar el aspecto del arma. Se encuentra en Storm, dispara Storm, pero Wikelo la mejorará para quienes prefieren Human Navy. Trae las cosas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y Wikelo lo hará. Adiós.</v>
-      </c>
-    </row>
-    <row r="1290">
-      <c r="A1290" t="str">
-        <v> Ahora fabrica Polaris. Oferta por tiempo limitado.</v>
-      </c>
-    </row>
-    <row r="1291" xml:space="preserve">
-      <c r="A1291" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Wikelo ha conseguido recientemente muchos planos a cambio de un humano no muy inteligente. Ahora puede construir naves muy grandes. No son baratas y requieren muchas piezas, pero se construirán. Si quieres, date prisa, esto le cuesta mucho a Wikelo, así que no podrá hacerlo por mucho tiempo, pero me gusta el nuevo sistema humano, así que quiero agradeceros a todos la bienvenida. Llévalo a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; si quieres. Adiós.</v>
-      </c>
-    </row>
-    <row r="1292">
-      <c r="A1292" t="str">
-        <v> Apolo de la Lucha Roja</v>
-      </c>
-    </row>
-    <row r="1293">
-      <c r="A1293" t="str">
-        <v> Apollo es una nave muy buena. Sería mucho mejor si fuera roja. Wikelo hace que todo sea posible. Intercambia lo que yo quiero y cerramos el trato.</v>
-      </c>
-    </row>
-    <row r="1294">
-      <c r="A1294" t="str">
-        <v> Haz que el ATLS se ponga nervioso.</v>
-      </c>
-    </row>
-    <row r="1295" xml:space="preserve">
-      <c r="A1295" t="str" xml:space="preserve">
-        <v xml:space="preserve">Encuentra una pieza muy divertida para añadir a un traje humano grande que te permita saltar muy alto. Ahora dispara y salta. ¡Emocionante! Si quieres, tráeme esto a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt;. Lo haré. Wikelo</v>
-      </c>
-    </row>
-    <row r="1296">
-      <c r="A1296" t="str">
-        <v> Haz que ATLS dispare</v>
-      </c>
-    </row>
-    <row r="1297" xml:space="preserve">
-      <c r="A1297" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola. Sé que a ti, humano, te gustan los trajes metálicos extraños. ¿Qué te parece un traje metálico con ikti? Lo siento, ikti es una palabra Banu, tú la llamas 'pistola'. Si quieres, trae lo que te diga y te la haré. La pistola disparará. Causará mucho daño. Adiós.</v>
-      </c>
-    </row>
-    <row r="1298">
-      <c r="A1298" t="str">
-        <v> Prueba de armadura</v>
-      </c>
-    </row>
-    <row r="1299">
-      <c r="A1299" t="str">
-        <v> Tráeme armadura y otras cosas y te daré una armadura de prueba especial. Primera versión. Muy especial. Tráela y te la daré. Adiós.</v>
-      </c>
-    </row>
-    <row r="1300">
-      <c r="A1300" t="str">
-        <v> Arma curiosa</v>
-      </c>
-    </row>
-    <row r="1301" xml:space="preserve">
-      <c r="A1301" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Wikelo encontró un arma muy extraña pero funcional mientras exploraba tus sistemas. Es muy simple pero muy efectiva. Si me traes algo, te mostraré lo que hago con ello. Muy divertido.</v>
-      </c>
-    </row>
-    <row r="1302">
-      <c r="A1302" t="str">
-        <v> ¿Quieres ver mejor?</v>
-      </c>
-    </row>
-    <row r="1303">
-      <c r="A1303" t="str">
-        <v> Wikelo tiene los mejores ojos para ver a lo lejos. Te doy si me das.</v>
-      </c>
-    </row>
-    <row r="1304">
-      <c r="A1304" t="str">
-        <v> El F55 se ve mejor</v>
-      </c>
-    </row>
-    <row r="1305">
-      <c r="A1305" t="str">
-        <v> veces disparas a la gente, pero si eres lo último que ven antes de morir, el arma debería verse increíble, ¿verdad? Wikelo hará que tu arma se vea mucho mejor. Tráeme lo que necesito y luego te doy el arma. Adiós.</v>
-      </c>
-    </row>
-    <row r="1306">
-      <c r="A1306" t="str">
-        <v> Escopeta de combate roja</v>
-      </c>
-    </row>
-    <row r="1307">
-      <c r="A1307" t="str">
-        <v> Disparar puede ser un desastre. Sangre humana roja por todas partes. Con esta escopeta no hay problema. ¡Las salpicaduras se camuflan perfectamente! Te la doy si me das todo lo que pido en la lista. Buen trato.</v>
-      </c>
-    </row>
-    <row r="1308">
-      <c r="A1308" t="str">
-        <v> Traje de constructor brillante</v>
-      </c>
-    </row>
-    <row r="1309">
-      <c r="A1309" t="str">
-        <v> Necesitas un traje de trabajo. Ideal para el trabajo. Si quieres, Wikelo puede hacerlo más brillante. Quedará genial. Consulta con Wikelo qué necesitas y tráelo.</v>
-      </c>
-    </row>
-    <row r="1310">
-      <c r="A1310" t="str">
-        <v> Traje de nieve oculto</v>
-      </c>
-    </row>
-    <row r="1311" xml:space="preserve">
-      <c r="A1311" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Quieres estar escondido. Wikelo lo entiende. No preguntes por qué. ¿Pero qué haces cuando estás en la nieve? Wikelo tiene un traje para eso. Bienvenido.</v>
-      </c>
-    </row>
-    <row r="1312">
-      <c r="A1312" t="str">
-        <v> Crea armaduras brillantes</v>
-      </c>
-    </row>
-    <row r="1313" xml:space="preserve">
-      <c r="A1313" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wikelo tuvo una idea genial durante un breve descanso. Estaba pensando en las pequeñas luciérnagas de Pyro y vio cómo la armadura se modificaba para parecerse a ellas. Si me consigues las piezas, tráelas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y te las haré para que tú también puedas brillar. Adiós.</v>
-      </c>
-    </row>
-    <row r="1314">
-      <c r="A1314" t="str">
-        <v> Pistola de calavera Fun Kopion</v>
-      </c>
-    </row>
-    <row r="1315" xml:space="preserve">
-      <c r="A1315" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola. Puedo hacerle modificaciones divertidas al arma si quieres. Usa la skin de Kopion para el patrón y el pequeño colgante de calavera. Es muy efectiva. Dispara mucho mejor. Solo tienes que traerme las piezas a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y la haré. Adiós.</v>
-      </c>
-    </row>
-    <row r="1316">
-      <c r="A1316" t="str">
-        <v> Pistola de dientes Fun Kopion</v>
-      </c>
-    </row>
-    <row r="1317" xml:space="preserve">
-      <c r="A1317" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola. Puedo hacerle modificaciones divertidas al arma si quieres. Si no te gusta decir que no es una calavera de bebé, tienes otra opción. Usa la piel de kopion para el patrón, pero usa un diente en lugar de un colgante. Sigue siendo efectivo y dispara mejor. Trae las piezas a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y las fabricaré. Adiós.</v>
-      </c>
-    </row>
-    <row r="1318">
-      <c r="A1318" t="str">
-        <v> Lobo Extra Especial</v>
-      </c>
-    </row>
-    <row r="1319">
-      <c r="A1319" t="str">
-        <v>Wikelo está muy emocionado. Tiene una idea para un nuevo material. Pero fabricarlo es muy complicado. Necesito ayuda para fabricar una muestra de prueba. Te doy el plano, lo fabricas, me lo traes y te lo cambio. Te doy un L-22 Wolf extra especial. Muy potente, muy lobo.</v>
-      </c>
-    </row>
-    <row r="1320">
-      <c r="A1320" t="str">
-        <v> Zapper VOLT pesado</v>
-      </c>
-    </row>
-    <row r="1321" xml:space="preserve">
-      <c r="A1321" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Necesitas un arma útil. Sí, sí, lo entiendo. Wikelo también hace que las armas útiles sean más bonitas. Ves cosas que necesito. ¿Las traes? Sí. Adiós.</v>
-      </c>
-    </row>
-    <row r="1322">
-      <c r="A1322" t="str">
-        <v> Pistola con calavera militar divertida</v>
-      </c>
-    </row>
-    <row r="1323" xml:space="preserve">
-      <c r="A1323" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola. Puedo hacer una versión del arma si quieres un soldado. Haz un material como el camuflaje del soldado pero con una calavera muerta en el frente. El arma también dispara mejor. Si quieres, trae la pieza a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y la haré.</v>
-      </c>
-    </row>
-    <row r="1324">
-      <c r="A1324" t="str">
-        <v> Pistola militar divertida con forma de diente</v>
-      </c>
-    </row>
-    <row r="1325" xml:space="preserve">
-      <c r="A1325" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Aquí Wikelo con otra forma de jugar con este tipo de arma. Haz que se parezca más a tu arma de soldado, pero con un diente de kopion colgando. Realmente desagradable. Si quieres, trae la pieza a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y la haré. Adiós.</v>
-      </c>
-    </row>
-    <row r="1326">
-      <c r="A1326" t="str">
-        <v> Traje de lava</v>
-      </c>
-    </row>
-    <row r="1327">
-      <c r="A1327" t="str">
-        <v>Si tienes armadura, Wikelo puede hacer que se vea cálida. Buen aspecto para una armadura útil. Tráeme cosas y lo haré.</v>
-      </c>
-    </row>
-    <row r="1328">
-      <c r="A1328" t="str">
-        <v xml:space="preserve"> Tu mejor oportunidad</v>
-      </c>
-    </row>
-    <row r="1329">
-      <c r="A1329" t="str">
-        <v> Este rifle dispara muy bien, pero podría tener un diseño más bonito. Arreglo de Wikelo. Ahora se ve muy bien. Te lo doy a cambio. Tráeme cosas y te doy el rifle. Incluso te doy el plano si lo necesitas.</v>
-      </c>
-    </row>
-    <row r="1330">
-      <c r="A1330" t="str">
-        <v> Hot Shot</v>
-      </c>
-    </row>
-    <row r="1331" xml:space="preserve">
-      <c r="A1331" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Necesitas una buena arma, ¿verdad? Aquí tienes una. Pequeña pero potente. Como un chile balalu extra picante. Wikelo también hace que esta pistola parezca extra picante. Tú traes lo que necesito y yo hago un intercambio. Adiós.</v>
-      </c>
-    </row>
-    <row r="1332">
-      <c r="A1332" t="str">
-        <v> Armadura de combate roja</v>
-      </c>
-    </row>
-    <row r="1333">
-      <c r="A1333" t="str">
-        <v> Wikelo oyó que los humanos piensan que el rojo es el color de la pasión y la ira. Esta armadura es buena para ambas. Dame los objetos de la lista y esta armadura roja será tuya.</v>
-      </c>
-    </row>
-    <row r="1334">
-      <c r="A1334" t="str">
-        <v> Armadura con cuerno y cuerda</v>
-      </c>
-    </row>
-    <row r="1335" xml:space="preserve">
-      <c r="A1335" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, sé que muchos humanos quieren saldynium para problemas de regeneración. Los créditos son buenos, sí, pero Wikelo puede usar eso, cuerno de kopion y otras cosas para hacer una armadura especial. Una vez hecha, serás muy duro. Da mucho miedo. Verás los objetos necesarios. Tráelos a &lt;EM4&gt;~mission(destino|ListAll)&lt;/EM4&gt; y los haré por ti. Adiós.</v>
-      </c>
-    </row>
-    <row r="1336">
-      <c r="A1336" t="str">
-        <v> Cañón Yormandi</v>
-      </c>
-    </row>
-    <row r="1337">
-      <c r="A1337" t="str">
-        <v> Esta pistola tiene la imagen de una criatura asombrosa en un costado. Úsala y te hará grande y fuerte como Yormandi. Escupe rayos. Tráeme mis objetos y entonces la obtendrás. Adiós.</v>
-      </c>
-    </row>
-    <row r="1338">
-      <c r="A1338" t="str">
-        <v> Armadura con Vanduul</v>
-      </c>
-    </row>
-    <row r="1339" xml:space="preserve">
-      <c r="A1339" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Vanduul tiene costumbres extrañas. Nunca hablo con ellos, el viejo souli sí, pero Wikelo no. De todos modos, aunque no son amigables, hacen cosas interesantes. Si quieres, Wikelo puede hacer que te parezcas más a ellos. Trae cosas. Lo haré. Adiós.</v>
-      </c>
-    </row>
-    <row r="1340">
-      <c r="A1340" t="str">
-        <v> ¡Prepárate y despega!</v>
-      </c>
-    </row>
-    <row r="1341">
-      <c r="A1341" t="str">
-        <v xml:space="preserve"> Las naves tienen ventanas grandes. Todos pueden verte volar. Debes lucir impecable. Wikelo tiene un traje de vuelo excelente para ti. Intercambia conmigo lo que necesito y Wikelo te dará el traje. Si no tienes el plano, tráemelo también.</v>
-      </c>
-    </row>
-    <row r="1342">
-      <c r="A1342" t="str">
-        <v>Haz que la escopeta VOLT se enfurezca más.</v>
-      </c>
-    </row>
-    <row r="1343" xml:space="preserve">
-      <c r="A1343" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¿Sientes que el arma no es lo suficientemente agresiva? ¿La escopeta VOLT es muy potente, muy peligrosa, pero no da miedo? Tráela. Puede hacer que te dé mucho miedo y te enfade. Entonces te respetarán. Tráela a &lt;EM4&gt;~mission(destination|ListAll)&lt;/EM4&gt; y lo haremos. Adiós.</v>
-      </c>
-    </row>
-    <row r="1344">
-      <c r="A1344" t="str">
-        <v> agachadiza de nieve</v>
-      </c>
-    </row>
-    <row r="1345" xml:space="preserve">
-      <c r="A1345" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¿Quieres disparar desde lejos y esconderte? ¿Pero está nevando? Wikelo tiene un arma para ti. Trae tus cosas. Te las doy. Adiós.</v>
-      </c>
-    </row>
-    <row r="1346">
-      <c r="A1346" t="str">
-        <v> Mod de lucha de Asgard</v>
-      </c>
-    </row>
-    <row r="1347">
-      <c r="A1347" t="str">
-        <v> Mod de lucha de Asgard</v>
-      </c>
-    </row>
-    <row r="1348">
-      <c r="A1348" t="str">
-        <v xml:space="preserve"> ¿Listos para RAFT?</v>
-      </c>
-    </row>
-    <row r="1349">
-      <c r="A1349" t="str">
-        <v xml:space="preserve"> ¿Listos para RAFT?</v>
-      </c>
-    </row>
-    <row r="1350">
-      <c r="A1350" t="str">
-        <v> Quiero un barco Tauro</v>
-      </c>
-    </row>
-    <row r="1351">
-      <c r="A1351" t="str">
-        <v> Quiero un barco Tauro</v>
-      </c>
-    </row>
-    <row r="1352">
-      <c r="A1352" t="str">
-        <v> Mod de guerra Starlifter A2</v>
-      </c>
-    </row>
-    <row r="1353">
-      <c r="A1353" t="str">
-        <v> Mod de guerra Starlifter A2</v>
-      </c>
-    </row>
-    <row r="1354">
-      <c r="A1354" t="str">
-        <v> Golem Rocas</v>
-      </c>
-    </row>
-    <row r="1355">
-      <c r="A1355" t="str">
-        <v> Golem Rocas</v>
-      </c>
-    </row>
-    <row r="1356">
-      <c r="A1356" t="str">
-        <v> Wikelo Navy F7</v>
-      </c>
-    </row>
-    <row r="1357">
-      <c r="A1357" t="str">
-        <v> Wikelo Navy F7</v>
-      </c>
-    </row>
-    <row r="1358">
-      <c r="A1358" t="str">
-        <v> Mod de guerra F8</v>
-      </c>
-    </row>
-    <row r="1359">
-      <c r="A1359" t="str">
-        <v> Mod de guerra F8</v>
-      </c>
-    </row>
-    <row r="1360">
-      <c r="A1360" t="str">
-        <v> Apuñalador sigiloso</v>
-      </c>
-    </row>
-    <row r="1361">
-      <c r="A1361" t="str">
-        <v> Apuñalador sigiloso</v>
-      </c>
-    </row>
-    <row r="1362">
-      <c r="A1362" t="str">
-        <v> Mod de Firebird</v>
-      </c>
-    </row>
-    <row r="1363">
-      <c r="A1363" t="str">
-        <v> Mod de Firebird</v>
-      </c>
-    </row>
-    <row r="1364">
-      <c r="A1364" t="str">
-        <v> Barco de la fortuna para ti</v>
-      </c>
-    </row>
-    <row r="1365">
-      <c r="A1365" t="str">
-        <v> Barco de la fortuna para ti</v>
-      </c>
-    </row>
-    <row r="1366">
-      <c r="A1366" t="str">
-        <v> Mod de lucha del guardián</v>
-      </c>
-    </row>
-    <row r="1367">
-      <c r="A1367" t="str">
-        <v> Mod de lucha del guardián</v>
-      </c>
-    </row>
-    <row r="1368">
-      <c r="A1368" t="str">
-        <v> Guardian WiK-X</v>
-      </c>
-    </row>
-    <row r="1369">
-      <c r="A1369" t="str">
-        <v> Guardian WiK-X</v>
-      </c>
-    </row>
-    <row r="1370">
-      <c r="A1370" t="str">
-        <v> El guardián derriba el barco</v>
-      </c>
-    </row>
-    <row r="1371">
-      <c r="A1371" t="str">
-        <v> El guardián derriba el barco</v>
-      </c>
-    </row>
-    <row r="1372">
-      <c r="A1372" t="str">
-        <v>Idris especial por matar</v>
-      </c>
-    </row>
-    <row r="1373">
-      <c r="A1373" t="str">
-        <v> Idris especial por matar</v>
-      </c>
-    </row>
-    <row r="1374">
-      <c r="A1374" t="str">
-        <v> Actualizar Intrepid</v>
-      </c>
-    </row>
-    <row r="1375">
-      <c r="A1375" t="str">
-        <v> Actualizar Intrepid</v>
-      </c>
-    </row>
-    <row r="1376">
-      <c r="A1376" t="str">
-        <v> ¿Dónde está Wolf? Aquí Wolf</v>
-      </c>
-    </row>
-    <row r="1377">
-      <c r="A1377" t="str">
-        <v> ¿Dónde está Wolf? Aquí Wolf</v>
-      </c>
-    </row>
-    <row r="1378">
-      <c r="A1378" t="str">
-        <v> Mod de meteorito RSI</v>
-      </c>
-    </row>
-    <row r="1379">
-      <c r="A1379" t="str">
-        <v> Mod de meteorito RSI</v>
-      </c>
-    </row>
-    <row r="1380">
-      <c r="A1380" t="str">
-        <v> Las perspectivas son buenas.</v>
-      </c>
-    </row>
-    <row r="1381">
-      <c r="A1381" t="str">
-        <v> Las perspectivas son buenas.</v>
-      </c>
-    </row>
-    <row r="1382">
-      <c r="A1382" t="str">
-        <v> Mod Noxy</v>
-      </c>
-    </row>
-    <row r="1383">
-      <c r="A1383" t="str">
-        <v> Mod Noxy</v>
-      </c>
-    </row>
-    <row r="1384">
-      <c r="A1384" t="str">
-        <v> Peregrino Wikelo Mod</v>
-      </c>
-    </row>
-    <row r="1385">
-      <c r="A1385" t="str">
-        <v> Peregrino Wikelo Mod</v>
-      </c>
-    </row>
-    <row r="1386">
-      <c r="A1386" t="str">
-        <v> Prowler Más utilidad</v>
-      </c>
-    </row>
-    <row r="1387">
-      <c r="A1387" t="str">
-        <v> Prowler Más utilidad</v>
-      </c>
-    </row>
-    <row r="1388">
-      <c r="A1388" t="str">
-        <v> Pulse Plus</v>
-      </c>
-    </row>
-    <row r="1389">
-      <c r="A1389" t="str">
-        <v> Pulse Plus</v>
-      </c>
-    </row>
-    <row r="1390">
-      <c r="A1390" t="str">
-        <v> Construye un Mod Scorpius</v>
-      </c>
-    </row>
-    <row r="1391">
-      <c r="A1391" t="str">
-        <v> Construye un Mod Scorpius</v>
-      </c>
-    </row>
-    <row r="1392">
-      <c r="A1392" t="str">
-        <v> Mod Spirit Cargo</v>
-      </c>
-    </row>
-    <row r="1393">
-      <c r="A1393" t="str">
-        <v> Mod Spirit Cargo</v>
-      </c>
-    </row>
-    <row r="1394">
-      <c r="A1394" t="str">
-        <v> Starfighter Inferno Especial</v>
-      </c>
-    </row>
-    <row r="1395">
-      <c r="A1395" t="str">
-        <v> Starfighter Inferno Especial</v>
-      </c>
-    </row>
-    <row r="1396">
-      <c r="A1396" t="str">
-        <v> Ion, el astuto caza estelar</v>
-      </c>
-    </row>
-    <row r="1397">
-      <c r="A1397" t="str">
-        <v> Ion, el astuto caza estelar</v>
-      </c>
-    </row>
-    <row r="1398">
-      <c r="A1398" t="str">
-        <v> Nueva nave espacial Big Starlancer</v>
-      </c>
-    </row>
-    <row r="1399">
-      <c r="A1399" t="str">
-        <v> Nueva nave espacial Big Starlancer</v>
-      </c>
-    </row>
-    <row r="1400">
-      <c r="A1400" t="str">
-        <v> Más que un máximo</v>
-      </c>
-    </row>
-    <row r="1401">
-      <c r="A1401" t="str">
-        <v> Más que un máximo</v>
-      </c>
-    </row>
-    <row r="1402">
-      <c r="A1402" t="str">
-        <v> ¿Qué es Terrapin?</v>
-      </c>
-    </row>
-    <row r="1403">
-      <c r="A1403" t="str">
-        <v> ¿Qué es Terrapin?</v>
-      </c>
-    </row>
-    <row r="1404">
-      <c r="A1404" t="str">
-        <v> Crea un mod para Ursa</v>
-      </c>
-    </row>
-    <row r="1405">
-      <c r="A1405" t="str">
-        <v> Crea un mod para Ursa</v>
-      </c>
-    </row>
-    <row r="1406">
-      <c r="A1406" t="str">
-        <v> Lobo más especial</v>
-      </c>
-    </row>
-    <row r="1407">
-      <c r="A1407" t="str">
-        <v> Lobo más especial</v>
-      </c>
-    </row>
-    <row r="1408">
-      <c r="A1408" t="str">
-        <v> Zeus Cargo Especial</v>
-      </c>
-    </row>
-    <row r="1409">
-      <c r="A1409" t="str">
-        <v> Zeus Cargo Especial</v>
-      </c>
-    </row>
-    <row r="1410">
-      <c r="A1410" t="str">
-        <v> Especial de Zeus</v>
-      </c>
-    </row>
-    <row r="1411">
-      <c r="A1411" t="str">
-        <v> Especial de Zeus</v>
-      </c>
-    </row>
-    <row r="1412">
-      <c r="A1412" t="str">
-        <v> Reparar la pistola Coda</v>
-      </c>
-    </row>
-    <row r="1413">
-      <c r="A1413" t="str">
-        <v>Reparar la pistola Coda</v>
-      </c>
-    </row>
-    <row r="1414">
-      <c r="A1414" t="str">
-        <v> Camina en peligro. Luce bien.</v>
-      </c>
-    </row>
-    <row r="1415">
-      <c r="A1415" t="str">
-        <v> Camina en peligro. Luce bien.</v>
-      </c>
-    </row>
-    <row r="1416">
-      <c r="A1416" t="str">
-        <v> Embellecer Karna Gun</v>
-      </c>
-    </row>
-    <row r="1417">
-      <c r="A1417" t="str">
-        <v> Embellecer Karna Gun</v>
-      </c>
-    </row>
-    <row r="1418">
-      <c r="A1418" t="str">
-        <v> Construido sobre el rifle S71</v>
-      </c>
-    </row>
-    <row r="1419">
-      <c r="A1419" t="str">
-        <v> Construido sobre el rifle S71</v>
-      </c>
-    </row>
-    <row r="1420">
-      <c r="A1420" t="str">
-        <v> Una aventura de una vida</v>
-      </c>
-    </row>
-    <row r="1421">
-      <c r="A1421" t="str">
-        <v> Una aventura de una vida</v>
-      </c>
-    </row>
-    <row r="1422">
-      <c r="A1422" t="str">
-        <v> Traje Xi'an Xanthule mejorado</v>
-      </c>
-    </row>
-    <row r="1423">
-      <c r="A1423" t="str">
-        <v> Traje Xi'an Xanthule mejorado</v>
-      </c>
-    </row>
-    <row r="1424">
-      <c r="A1424" t="str">
-        <v> Tutorial - Tus primeros pasos</v>
-      </c>
-    </row>
-    <row r="1425" xml:space="preserve">
-      <c r="A1425" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Enhorabuena por tus primeros pasos en el universo! A lo largo de este tutorial, aprenderás a moverte tanto a pie como en el espacio. Para empezar, te familiarizarás con los controles básicos de movimiento y el uso de tu mobiGlas dentro de tu hábitat. Sigue los objetivos y las indicaciones de tu HUD (pantalla de visualización frontal) para completar esta misión.</v>
-      </c>
-    </row>
-    <row r="1426">
-      <c r="A1426" t="str">
-        <v> Tutorial - Tu primera salida</v>
-      </c>
-    </row>
-    <row r="1427" xml:space="preserve">
-      <c r="A1427" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Bien hecho! Con la primera parte completada, ya deberías tener cierta familiaridad con los controles de movimiento, la gestión de tu hambre y sed, y algunas de las funciones principales de tu mobiGlas, concretamente el Gestor de Contratos y tu Diario. Esta siguiente sección te ayudará a familiarizarte con ~mission(Location|Name) y te llevará a visitar ~mission(StoreName), una tienda de armas aquí en ~mission(Location|Name). Puedes comprar allí, y en otras tiendas similares, usando Créditos de la Tierra Unida (UEC). Durante la fase alfa del desarrollo de Star Citizen, utilizaremos una moneda llamada aUEC (Créditos de la Tierra Unida Alfa). Esta es una moneda temporal diseñada específicamente para probar la economía y el equilibrio del juego.</v>
-      </c>
-    </row>
-    <row r="1428">
-      <c r="A1428" t="str">
-        <v> Tutorial - Tu primer vuelo</v>
-      </c>
-    </row>
-    <row r="1429" xml:space="preserve">
-      <c r="A1429" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ya casi terminas el tutorial. ¡Solo queda despegar! Con tu misión en ~mission(Location|Name) terminada, es hora de abandonar la ciudad y, finalmente, el planeta. Dirígete a las lanzaderas de tránsito de ~mission(TransitNameShort). Estas lanzaderas te pueden llevar por toda ~mission(Location|Name), pero tu destino es el puerto espacial, donde te han proporcionado temporalmente una Anvil C8 Pisces. Esta nave de exploración es una excelente nave de iniciación, perfecta para pilotos novatos que buscan obtener sus alas.</v>
-      </c>
-    </row>
-    <row r="1430">
-      <c r="A1430" t="str">
-        <v> Ruta de envío local de UDM</v>
-      </c>
-    </row>
-    <row r="1431" xml:space="preserve">
-      <c r="A1431" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, socio de envíos calificado! Hoy es el día perfecto para adquirir experiencia práctica en envíos. Si dispone de un barco con suficiente espacio de almacenamiento, hay una buena cantidad de paquetes en ~mission(Pickup1) en ~mission(Pickup1|Address) listos para ser entregados. ¡Una excelente oportunidad para el crecimiento profesional! PAQUETES PARA RECOGER · Todos los paquetes en &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff4|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff5|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item7|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item8|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff6|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item9|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item10|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff7|Address)&lt;/EM4&gt; Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
-      </c>
-    </row>
-    <row r="1432">
-      <c r="A1432" t="str">
-        <v>Controlador de paquetes UDM</v>
-      </c>
-    </row>
-    <row r="1433" xml:space="preserve">
-      <c r="A1433" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, experto en manipulación de paquetes! Aunque no tengan que ir muy lejos, los siguientes paquetes en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; requieren un manejo experto. ¿Eres el experto que buscamos? PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; de &lt;EM4&gt;~mission(Pickup6)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff1)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff2)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff3)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item4|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff4)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item5|SerialNumber)&lt;/EM4&gt; al &lt;EM4&gt;~mission(Dropoff5)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item6|SerialNumber)&lt;/EM4&gt; a la &lt;EM4&gt;~mission(Dropoff6)&lt;/EM4&gt; Solo tienes que aceptar el contrato y listo. Esperamos trabajar contigo, Unified Distribution Management -Ofreciendo el paquete completo-</v>
-      </c>
-    </row>
-    <row r="1434">
-      <c r="A1434" t="str">
-        <v xml:space="preserve">Ruta de entrega local de UDM</v>
-      </c>
-    </row>
-    <row r="1435" xml:space="preserve">
-      <c r="A1435" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! ¿Busca una excusa para surcar los cielos con su nave de carga? Gane créditos y explore la zona con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si ser su propio supervisor y que le paguen por pilotar su propia nave le parece el trabajo perfecto, este contrato es justo lo que estaba buscando. Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
-      </c>
-    </row>
-    <row r="1436">
-      <c r="A1436" t="str">
-        <v> Evaluación de la entrega local de UDM</v>
-      </c>
-    </row>
-    <row r="1437" xml:space="preserve">
-      <c r="A1437" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, potencial socio de envío cualificado! ¿Listo para contribuir a nuestra creciente red de entregas? ¿Tienes una nave a tu disposición que pueda transportar varios paquetes y volar entre cuerpos celestes y satélites? ¡Unified Distribution Management busca un piloto como tú! Nos encantaría evaluar tu potencial de contratación con este itinerario cuidadosamente seleccionado: PAQUETE PARA RECOGER · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; LUGAR DE ENTREGA · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; hasta &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; Si esto te interesa, ¡acepta esta oferta de inmediato! Solo asegúrate de traer tu propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos trabajar contigo, Unified Distribution Management -Entregando el paquete completo-</v>
-      </c>
-    </row>
-    <row r="1438">
-      <c r="A1438" t="str">
-        <v> Reevaluación de la entrega local de UDM</v>
-      </c>
-    </row>
-    <row r="1439" xml:space="preserve">
-      <c r="A1439" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Saludos, antiguo socio naviero cualificado! ¿Estás listo para otra oportunidad de usar tu buque listo para el transporte de carga y ganar créditos? Unified Distribution Management ha elegido el siguiente itinerario cuidadosamente seleccionado como la manera perfecta de reevaluar sus habilidades: PAQUETES PARA RECOGER (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; desde &lt;EM4&gt;~mission(Pickup3|Address)&lt;/EM4&gt; LUGARES DE ENTREGA (CUALQUIER PEDIDO) · Paquete &lt;EM4&gt;#~mission(Item1|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item2|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt; · Paquete &lt;EM4&gt;#~mission(Item3|SerialNumber)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff3|Address)&lt;/EM4&gt; Asegúrese de traer su propio &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para una máxima eficiencia. Esperamos volver a trabajar con usted, Unified Distribution Management -Entregando el paquete completo-</v>
-      </c>
-    </row>
-    <row r="1440">
-      <c r="A1440" t="str">
-        <v>Recogida de paquetes UDM</v>
-      </c>
-    </row>
-    <row r="1441" xml:space="preserve">
-      <c r="A1441" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ¡Saludos, socio de envíos calificado! Si buscas trabajo como repartidor, ¡tenemos la oportunidad perfecta para ti! Un paquete te espera en &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; para ser entregado en &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. ¿Suena interesante, verdad? Advertencia: se han registrado varias alertas de seguridad en la zona. Asegúrate de llevar contigo medidas de protección para mantenerte a salvo. Si esto te interesa, ¡acepta esta oferta de inmediato! Esperamos trabajar contigo. Unified Distribution Management -Entregando el paquete completo-</v>
-      </c>
-    </row>
-    <row r="1442">
-      <c r="A1442" t="str">
-        <v> SOLICITUD DE REPOSTAJE: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1443">
-      <c r="A1443" t="str">
-        <v> SOLICITUD DE REPOSTAJE: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1444">
-      <c r="A1444" t="str">
-        <v xml:space="preserve"> SOLICITUD DE REPOSTAJE CRÍTICA: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1445">
-      <c r="A1445" t="str">
-        <v xml:space="preserve"> SOLICITUD DE REPOSTAJE CRÍTICA: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1446">
-      <c r="A1446" t="str">
-        <v> UWC CONTRATA PERSONAL PARA REPOSTEAR COMBUSTIBLES</v>
-      </c>
-    </row>
-    <row r="1447">
-      <c r="A1447" t="str">
-        <v> UWC CONTRATA PERSONAL PARA REPOSTEAR COMBUSTIBLES</v>
-      </c>
-    </row>
-    <row r="1448">
-      <c r="A1448" t="str">
-        <v> SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1449">
-      <c r="A1449" t="str">
-        <v> SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1450">
-      <c r="A1450" t="str">
-        <v> REPOSTAJE URGENTE DE LA FLOTA</v>
-      </c>
-    </row>
-    <row r="1451">
-      <c r="A1451" t="str">
-        <v>REPOSTAJE URGENTE DE LA FLOTA</v>
-      </c>
-    </row>
-    <row r="1452">
-      <c r="A1452" t="str">
-        <v> Todas las cosas llegan a su fin.</v>
-      </c>
-    </row>
-    <row r="1453" xml:space="preserve">
-      <c r="A1453" t="str" xml:space="preserve">
-        <v xml:space="preserve"> No sé si conoces ~mission(Location|Address), pero ~mission(TargetName) es quien manda allí. Necesito eliminarlos. Me temo que es más fácil decirlo que hacerlo. Son conocidos por su renuencia a ocuparse personalmente de los asuntos, prefiriendo que sus subordinados se encarguen del trabajo sucio. Dicho esto, si eliminas a suficientes subordinados, no les quedará más remedio que enfrentarse a ti directamente. Atentamente, Vaughn</v>
-      </c>
-    </row>
-    <row r="1454">
-      <c r="A1454" t="str">
-        <v> Se les echará de menos.</v>
-      </c>
-    </row>
-    <row r="1455" xml:space="preserve">
-      <c r="A1455" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un alto funcionario de seguridad llamado ~mission(TargetName) ha sido marcado para su eliminación. Aunque se encuentra en ~mission(Location|Address), no será fácil llegar hasta él. Me temo que será necesario un esfuerzo considerable para atraerlo. Normalmente, recomendaría eliminar a suficientes subordinados como para que se vea obligado a enfrentarse a usted personalmente. Sin embargo, en este caso se requiere un enfoque más delicado. Si bien puede eliminar a todas las fuerzas de seguridad presentes, debe garantizar la seguridad de todos los trabajadores civiles. Sin duda, es una tarea ardua, pero necesaria. Atentamente, Vaughn</v>
-      </c>
-    </row>
-    <row r="1456">
-      <c r="A1456" t="str">
-        <v> Una oportunidad para impresionar</v>
-      </c>
-    </row>
-    <row r="1457" xml:space="preserve">
-      <c r="A1457" t="str" xml:space="preserve">
-        <v xml:space="preserve">En primer lugar, permítame presentarme. Para decirlo de forma un tanto dramática, me dedico a la vida. La gente me contrata cuando hay que eliminar a alguien, y yo, a cambio, empleo a la persona perfecta para hacerlo. Esto proporciona seguridad a todas las partes involucradas, ya que nadie conoce la identidad de la otra. Una situación ideal en estos casos. Recientemente me enteré de que usted podría poseer habilidades que me serían útiles y decidí que valdría la pena investigar esta afirmación. Si le interesa establecer una relación laboral, necesitaré una demostración de dichas habilidades. Busque y elimine discretamente a ~mission(TargetName) en ~mission(Location|Address). Si lo logra, será recompensado. Además, habrá demostrado ser digno de ser considerado para futuras contrataciones. Atentamente, Vaughn</v>
-      </c>
-    </row>
-    <row r="1458">
-      <c r="A1458" t="str">
-        <v> Otra oportunidad para impresionar</v>
-      </c>
-    </row>
-    <row r="1459" xml:space="preserve">
-      <c r="A1459" t="str" xml:space="preserve">
-        <v xml:space="preserve">No es frecuente en la vida tener una segunda oportunidad para causar una buena primera impresión, pero te la voy a brindar. Decir que me decepcionó cómo se desarrollaron las cosas en tu último intento de asesinato sería quedarse corto. Sin embargo, esta es tu oportunidad para demostrar que eres capaz de más. Elimina a ~mission(TargetName) en ~mission(Location|Address) y consideraré que has borrado el pasado. Atentamente, Vaughn</v>
-      </c>
-    </row>
-    <row r="1460">
-      <c r="A1460" t="str">
-        <v> Fin de una salamandra</v>
-      </c>
-    </row>
-    <row r="1461">
-      <c r="A1461" t="str">
-        <v> Fin de una salamandra</v>
-      </c>
-    </row>
-    <row r="1462">
-      <c r="A1462" t="str">
-        <v> Un merecido descanso</v>
-      </c>
-    </row>
-    <row r="1463">
-      <c r="A1463" t="str">
-        <v> Un merecido descanso</v>
-      </c>
-    </row>
-    <row r="1464">
-      <c r="A1464" t="str">
-        <v> Un contrato desafiante</v>
-      </c>
-    </row>
-    <row r="1465">
-      <c r="A1465" t="str">
-        <v> Un contrato desafiante</v>
-      </c>
-    </row>
-    <row r="1466">
-      <c r="A1466" t="str">
-        <v> Otro desafío que debe ser eliminado</v>
-      </c>
-    </row>
-    <row r="1467">
-      <c r="A1467" t="str">
-        <v> Otro desafío que debe ser eliminado</v>
-      </c>
-    </row>
-    <row r="1468">
-      <c r="A1468" t="str">
-        <v> Matar a un fantasma</v>
-      </c>
-    </row>
-    <row r="1469">
-      <c r="A1469" t="str">
-        <v> Matar a un fantasma</v>
-      </c>
-    </row>
-    <row r="1470">
-      <c r="A1470" t="str">
-        <v> Contrato de Pyro</v>
-      </c>
-    </row>
-    <row r="1471">
-      <c r="A1471" t="str">
-        <v> Contrato de Pyro</v>
-      </c>
-    </row>
-    <row r="1472">
-      <c r="A1472" t="str">
-        <v> Localizar a un miembro de la pandilla</v>
-      </c>
-    </row>
-    <row r="1473" xml:space="preserve">
-      <c r="A1473" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de nivel Clips de la banda Headhunters, ~mission(TargetName|Last) ha liderado operaciones dirigidas contra operativos, misiones e infraestructura de XenoThreat. Por estas transgresiones, XenoThreat pagará a cualquiera que logre localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto cerca de ~mission(Location|Address) hace poco. Si decide aceptar este contrato, diríjase a las coordenadas de inmediato. ~mission(TargetName|Last) sabe que lo estamos buscando y ha estado viajando con un escolta recientemente. No se sorprenda si no está solo. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1474">
-      <c r="A1474" t="str">
-        <v> Localiza al traidor</v>
-      </c>
-    </row>
-    <row r="1475" xml:space="preserve">
-      <c r="A1475" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). ~mission(TargetName|Last), un conocido miembro de la banda Headhunters, ha traicionado a la humanidad al ser un aliado alienígena conocido con quien mantiene relaciones tanto personales como comerciales. XenoThreat exige que estas relaciones traidoras cesen de inmediato antes de que traigan más influencia alienígena a Pyro. Recompensaremos a quien logre localizar y asesinar a ~mission(TargetName|Last) por estos crímenes contra la humanidad. ACTUALIZACIÓN DE UBICACIÓN: ~mission(TargetName|Last) fue visto recientemente con una escolta en ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1476">
-      <c r="A1476" t="str">
-        <v> Rastrear al espía</v>
-      </c>
-    </row>
-    <row r="1477" xml:space="preserve">
-      <c r="A1477" t="str" xml:space="preserve">
-        <v xml:space="preserve">XenoThreat ha emitido una orden de asesinato contra ~mission(TargetName). Como miembro de la banda Headhunters, ~mission(TargetName|Last) hackeó los sistemas de XenoThreat para robar información sobre nuestras operaciones y personal. El daño causado solo puede repararse asegurándonos de que ~mission(TargetName|Last) jamás vuelva a hacer algo así. Por eso, XenoThreat pagará a cualquiera que pueda localizar y asesinar a ~mission(TargetName|Last). ACTUALIZACIÓN DE UBICACIÓN: Escaneos recientes identificaron a ~mission(TargetName|Last) viajando con otras naves cerca de ~mission(Location|Address). Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1478">
-      <c r="A1478" t="str">
-        <v> Centinelas del silencio</v>
-      </c>
-    </row>
-    <row r="1479" xml:space="preserve">
-      <c r="A1479" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nuestro movimiento de resistencia crece día a día, pero esto conlleva cierta atención no deseada. Escaneos recientes descubrieron centinelas orbitales en ~mission(location|address) y una nave patrullando. Creemos que esto forma parte de una campaña de espionaje contra XenoThreat, probablemente financiada por la UEE. Buscamos un mercenario experimentado dispuesto a destruir los centinelas cuanto antes. Dado que ya nos tienen vigilados, enviar a alguien ajeno a la organización llamaría menos la atención. Si aceptas el trabajo, recibirás tu pago inmediatamente una vez destruidos los centinelas. Ahora bien, aunque la nave patrulla no es el objetivo principal, sospechamos que si escapa podría tener refuerzos en reserva. Sería prudente neutralizarla cuanto antes. Si decides ayudarnos, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1480">
-      <c r="A1480" t="str">
-        <v> Aniquilar centinelas</v>
-      </c>
-    </row>
-    <row r="1481" xml:space="preserve">
-      <c r="A1481" t="str" xml:space="preserve">
-        <v xml:space="preserve">Escaneos recientes descubrieron varios centinelas orbitales y naves en ~mission(location|address). Creemos que forman parte de una campaña de espionaje contra XenoThreat, en respuesta a nuestras acciones recientes en el sistema Stanton. Parece que XenoThreat está haciendo algo bien, si están espiando de esta manera. Buscamos un mercenario experimentado y altamente capacitado dispuesto a eliminar esta operación. Si no quieres que Pyro se convierta en un sistema de vigilancia, esta es tu oportunidad para impedirlo. Los centinelas probablemente no representen un gran problema, pero ten cuidado con las naves de patrulla. Si logran escapar, tendrás muchos más problemas pisándote los talones. Te estaremos agradecidos y te pagaremos generosamente una vez que completes el trabajo. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1482">
-      <c r="A1482" t="str">
-        <v> Finalización de la vigilancia</v>
-      </c>
-    </row>
-    <row r="1483" xml:space="preserve">
-      <c r="A1483" t="str" xml:space="preserve">
-        <v xml:space="preserve">Parece que nuestra lucha por liberar a la humanidad tiene nerviosos a los lacayos del gobierno en la Tierra. Escaneos recientes descubrieron un centinela orbital en ~mission(location|address) que creemos forma parte de una campaña de espionaje de la UEE. Según nuestros informes, están entregando los datos directamente a los propios slinks. Solo se ha detectado un centinela hasta ahora, pero quién sabe hasta dónde llegará la operación si no se desactiva. No debería ser demasiado problema para un mercenario habilidoso. Si te identificas con esto, recibirás el pago inmediatamente después de destruir el centinela. Además, XenoThreat recordará que eres alguien dispuesto a luchar por la justicia. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1484">
-      <c r="A1484" t="str">
-        <v> Erradicar centinelas</v>
-      </c>
-    </row>
-    <row r="1485" xml:space="preserve">
-      <c r="A1485" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Valoras la libertad de la humanidad? Si es así, te ofrezco la oportunidad de demostrarlo. Escaneos recientes han detectado centinelas orbitales y naves patrullando en ~mission(location|address). Creemos que forman parte de una campaña de espionaje de la UEE contra XenoThreat. Es crucial detener su labor de recopilación de inteligencia antes de lanzar nuestra próxima misión. Buscamos un mercenario experimentado dispuesto a eliminar estas fuerzas de inmediato. Los centinelas son la prioridad, pero las naves podrían representar un problema mayor si logran escapar. Deberás evaluar la situación con más detalle una vez que estés en el lugar. Podríamos encargarnos nosotros mismos, pero preferimos enviar a un contratista para que los responsables no sepan quién los atacó. El pago se realizará puntualmente al finalizar la misión. Además, tendrás la satisfacción de saber que estás ayudando a una buena causa. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1486">
-      <c r="A1486" t="str">
-        <v> Borrado total del servidor</v>
-      </c>
-    </row>
-    <row r="1487" xml:space="preserve">
-      <c r="A1487" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de nuestros agentes de datos desapareció mientras transportaba información operativa vital. Hace unas horas, determinamos que fue atacado por un grupo de asalto de Headhunters y que el contenido de los almacenes de datos de la nave fue transferido a sus servidores en ~mission(location|address). Si bien tenemos motivos para creer que nuestro cifrado resistirá, no podemos arriesgarnos a que el contenido de esos archivos quede expuesto. Se le ordena dirigirse allí y garantizar la privacidad de nuestros datos destruyendo los servidores de Headhunters. Le recomiendo encarecidamente que actúe con la máxima minuciosidad. Destruya todo y a todos los que pueda. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1488">
-      <c r="A1488" t="str">
-        <v> Sabotaje de la línea de suministro</v>
-      </c>
-    </row>
-    <row r="1489" xml:space="preserve">
-      <c r="A1489" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los supuestos “activistas” de salón de Ciudadanos por la Prosperidad siguen intentando extender su influencia por todo el sistema. Con tu ayuda, existe la oportunidad de desmantelar sus operaciones de raíz. El grupo utiliza ~mission(location|address) para distribuir suministros a independientes dispersos por todo el planeta. Si destruimos la ~mission(ship) ubicada allí, su red colapsará. Un bombardeo enviaría un mensaje claro, pero te dejo a ti la decisión sobre el método de destrucción. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1490">
-      <c r="A1490" t="str">
-        <v> Orden de eliminación: "Ciudadanos" en ~mission(location)</v>
-      </c>
-    </row>
-    <row r="1491" xml:space="preserve">
-      <c r="A1491" t="str" xml:space="preserve">
-        <v xml:space="preserve">El grupo de instigadores que se autodenomina «Ciudadanos por la Prosperidad» ya no puede seguir difundiendo sus mentiras y propaganda impunemente. Como un claro recordatorio de quién controla realmente a Pyro, hemos emitido una orden de eliminación para erradicar toda presencia de «Ciudadanos» en ~misión(ubicación|dirección). Es probable que haya resistencia, pero esperamos que la resuelvan sin mayores dificultades. Sigan las instrucciones y recibirán una buena recompensa por su trabajo. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1492">
-      <c r="A1492" t="str">
-        <v> Lucha por un Pyro gratis</v>
-      </c>
-    </row>
-    <row r="1493" xml:space="preserve">
-      <c r="A1493" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los esfuerzos de XenoThreat por evitar que influencias externas infecten este sistema están siendo puestos a prueba por un grupo que se atreve a llamarse Ciudadanos por la Prosperidad. Un miembro destacado del grupo, ~mission(TargetName), ha establecido operaciones en ~mission(Location|Address) y ya está trabajando arduamente difundiendo sus mentiras y propaganda a cualquiera que quiera escuchar. Si queremos que Pyro permanezca independiente de la UEE y de la influencia alienígena, entonces debemos hacer algo al respecto ahora. Por eso XenoThreat está emitiendo una orden de eliminación para ~mission(TargetName|Last). Y sabiendo lo importantes que son para las operaciones de Ciudadanos por la Prosperidad, no me sorprendería que tuvieras que abrirte paso luchando contra un grupo de sus seguidores más fanáticos antes de siquiera tener la oportunidad de dispararles. Pero recuerda que ~mission(TargetName|Last) es tu objetivo, y el pago depende únicamente de que te asegures de eliminarlo. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1494">
-      <c r="A1494" t="str">
-        <v> Búsqueda de talentos</v>
-      </c>
-    </row>
-    <row r="1495" xml:space="preserve">
-      <c r="A1495" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Cazadores de Cabezas han reunido un equipo de ataque especial cuyo único propósito es atacar, interrumpir y sabotear nuestras operaciones. Aunque me cueste admitirlo, han tenido algunos éxitos menores y se están convirtiendo rápidamente en una preocupación. XenoThreat sabe que la mejor manera de matar a una serpiente es cortándole la cabeza, así que emitimos una orden de eliminación para el comandante del equipo de ataque, ~mission(TargetName), quien, según nuestras fuentes de inteligencia, se ha estado escondiendo en ~mission(Location|Address) durante algunos días. Preveo una fuerte resistencia por parte de las fuerzas de los Cazadores de Cabezas allí. Por lo que hemos oído, ~mission(TargetName|Last) recibió este mando en parte debido a la feroz lealtad que inspira en los demás. Reunir a tu propio equipo para abordar esto sería una sólida estrategia operativa. Feliz caza de cabezas, Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1496">
-      <c r="A1496" t="str">
-        <v> Robar subsidios</v>
-      </c>
-    </row>
-    <row r="1497" xml:space="preserve">
-      <c r="A1497" t="str" xml:space="preserve">
-        <v xml:space="preserve">Típico de la UEE mentirosa, decir que no está involucrada en las operaciones de Ciudadanos por la Prosperidad simplemente porque "donan" suministros a una organización de ayuda terciaria que luego se los entrega inmediatamente. Acabamos de enterarnos de que uno de estos envíos de ayuda gubernamental fue entregado en un puesto avanzado alineado con Ciudadanos por la Prosperidad. Por eso te pagaremos para que asaltes ~mission(Pickup1|Address) y reclames el ~mission(item) para la causa. Una vez que entregues todo en ~mission(Dropoff1|Address), podremos redistribuir el envío para ayudar en nuestra lucha. No hay nada mejor que usar los recursos del enemigo en su contra. Pero no creas que te lo van a entregar así como así. Aunque se supone que Ciudadanos por la Prosperidad está aquí para traer la paz, será mejor que estés preparado para enfrentarte a ellos. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1498">
-      <c r="A1498" t="str">
-        <v> Suministros para la recuperación de bienes</v>
-      </c>
-    </row>
-    <row r="1499" xml:space="preserve">
-      <c r="A1499" t="str" xml:space="preserve">
-        <v xml:space="preserve">Por mucho que XenoThreat se haya esforzado por hacer de Pyro un refugio seguro para los humanos, no todos comparten nuestros objetivos. Entre ellos destacan los Cazadores de Cabezas, que se han degradado al contratar a un transportista alienígena para que les entregue suministros. Perdimos la oportunidad de interceptar ese cargamento, pero aun así queremos dejar claro que no se tolerará la colaboración con alienígenas bajo ninguna circunstancia en este sistema. El cargamento fue entregado en ~mission(Pickup1|Address). Queremos que alguien ataque el puesto de avanzada, reclame el ~mission(item) y lo lleve a ~mission(Dropoff1|Address) para que podamos deshacernos de él adecuadamente. ¿Te animas a mantener Pyro libre de la influencia alienígena? Comm. Spec. Engler</v>
-      </c>
-    </row>
-    <row r="1500">
-      <c r="A1500" t="str">
-        <v> Agente del Caos</v>
-      </c>
-    </row>
-    <row r="1501" xml:space="preserve">
-      <c r="A1501" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ciudadanos por la Prosperidad se han atrincherado en ~mission(Pickup1|Address). Para evitar que se acomoden demasiado en esa estación, queremos mostrarles cómo es realmente la vida en nuestro sistema. Te pagaremos para que vayas a la estación, recojas el ~mission(item) y mates a cualquiera que se interponga en tu camino. El pago depende de que entregues esos suministros en ~mission(Dropoff1|Address). Cualquiera que mates será una ventaja. Especialista en Comunicaciones Engler</v>
-      </c>
-    </row>
-    <row r="1502">
-      <c r="A1502" t="str">
         <v> Precio de los negocios</v>
       </c>
     </row>
-    <row r="1503" xml:space="preserve">
-      <c r="A1503" t="str" xml:space="preserve">
+    <row r="1151" xml:space="preserve">
+      <c r="A1151" t="str" xml:space="preserve">
         <v xml:space="preserve">No sé si has tenido el placer de tratar con los Rough &amp; Ready, pero la banda está totalmente centrada en acaparar el mercado del combustible en Pyro. Es una jugada inteligente, pero no podemos permitir que suceda sin que nos den algunas concesiones. Como no están interesados en negociar, nos vemos obligados a mostrarles lo que les pasa a quienes se oponen a nosotros. Hemos identificado ~mission(Pickup1|Address) como un objetivo principal para dicho ataque. También sabemos que recientemente recibieron suministros que deberían ser un precio justo por su obstinación. Una vez dentro de la estación, haz lo que sea necesario para confiscar el ~mission(item). Enviaremos el pago una vez que lo hayas entregado en ~mission(Dropoff1|Address). Especialista en Comunicaciones Engler</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A1503"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A1151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/work/from_google/missions.xlsx
+++ b/work/from_google/missions.xlsx
@@ -412,59 +412,59 @@
         <v> Se necesita recuperador (escasa cantidad de RMC)</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Adagio Holdings Un orgulloso empleador de igualdad de oportunidades &gt; Acerca del trabajo &lt; Para ayudar a satisfacer un pedido reciente a pequeña escala, estamos buscando contratistas para ayudar a obtener Compuesto de Material Reciclado (RMC) desmantelando barcos abandonados. Recomendamos buscar restos en puntos de Lagrange o puede comprar un reclamo de salvamento de nosotros en su Administrador de Contratos. Una vez adquiridos, entregue los materiales al montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas. &gt; Requisitos &lt; - Cualquier clase/tamaño de barco de salvamento &gt; Descargo de responsabilidad &lt; Los contratistas son responsables de asegurarse de que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE correspondientes. Adagio Holdings no es responsable de ninguna manera por ningún delito o falta cometida por los contratistas y no ofrecerá compensación o reparación a ninguna persona afectada por estas acciones.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v> Adagio Holdings necesita rescatadores.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
+        <v>Adagio Holdings necesita rescatadores.</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Adagio Holdings Un orgulloso empleador de igualdad de oportunidades &gt; Acerca de nosotros &lt; Como principal comprador y distribuidor de derechos de salvamento, Adagio Holdings ahora busca expandirse en la adquisición y distribución de materiales recuperables a empresas tanto pequeñas como grandes. &gt; Acerca del trabajo &lt; Como parte de esta iniciativa, necesitamos contratistas con buen ojo capaces de identificar materiales recuperables, desmantelarlos de manera eficiente y entregarnos el Compuesto de Material Reciclado (RMC) y los componentes recuperados. Este contrato introductorio requerirá que se dirija a &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; y desmantele un barco abandonado aprobado para salvamento. Una vez que haya reunido el RMC, lo entregará al montacargas ubicado en &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. &gt; Requisitos &lt; - Cualquier clase/tamaño de barco de salvamento Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas. &gt; Descargo de responsabilidad &lt; Los contratistas son responsables de asegurarse de que están recolectando materiales de vehículos que se consideran salvamento lícito según las leyes UEE vigentes. Adagio Holdings no se hace responsable de ningún delito o falta cometida por los contratistas y no ofrecerá compensación ni reparación a ninguna persona afectada por estas acciones.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve"> Se necesita recuperador (suministro médico de RMC)</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
+        <v xml:space="preserve">Se necesita recuperador (suministro médico de RMC)</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Adagio Holdings Un orgulloso empleador de igualdad de oportunidades &gt; Acerca del trabajo &lt; Para ayudar a satisfacer un pedido reciente de tamaño medio, estamos buscando contratistas para ayudar a obtener Compuesto de Material Reciclado (RMC) desmantelando barcos abandonados. Recomendamos buscar restos en puntos de Lagrange o puede comprar un reclamo de salvamento de nosotros en su Administrador de Contratos. Una vez adquiridos, entregue los materiales al montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas. &gt; Requisitos &lt; - Cualquier clase/tamaño de barco de salvamento &gt; Descargo de responsabilidad &lt; Los contratistas son responsables de asegurarse de que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE vigentes. Adagio Holdings no es responsable de ninguna manera por ningún delito o falta cometida por los contratistas y no ofrecerá compensación o reparación a ninguna persona afectada por estas acciones.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
+        <v>Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str" xml:space="preserve">
+        <v xml:space="preserve">-------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(Nombre del objetivo) SISTEMA: Stanton EVALUACIÓN DE RIESGO: Medio ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: &lt;Ninguna&gt; NOTAS: Hemos rastreado a este objetivo de recompensa hasta el &lt;EM4&gt;ala de ingeniería&lt;/EM4&gt; de una instalación de investigación abandonada de Associated Science and Development. Aunque está cerrada, se sabe que varios carroñeros y otros tipos indeseables frecuentan la zona. La propia instalación también podría suponer un riesgo, ya que se desconoce la naturaleza de la investigación que se lleva a cabo allí. Esté atento a posibles peligros ambientales mientras persigue al objetivo. GREMIO DE CAZARRECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v> Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
+        <v>Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str" xml:space="preserve">
+        <v xml:space="preserve">-------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(NombreDelObjetivo) SISTEMA: Stanton EVALUACIÓN DE RIESGO: Medio ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: &lt;Ninguna&gt; NOTAS: Hemos rastreado a este objetivo de recompensa hasta el &lt;EM4&gt;Ala de Investigación&lt;/EM4&gt; de una instalación abandonada de Associated Science and Development. Aunque cerrada, se sabe que varios carroñeros y otros tipos indeseables frecuentan la zona. La propia instalación también podría suponer un riesgo, ya que se desconoce la naturaleza de la investigación que se lleva a cabo allí. Esté atento a posibles peligros ambientales mientras persigue al objetivo. GREMIO DE CAZARRECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v> Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
+        <v>Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str" xml:space="preserve">
+        <v xml:space="preserve"> -------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(Nombre del Objetivo) SISTEMA: ~mission(Sistema) EVALUACIÓN DE RIESGO: ~mission(Peligro) ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: &lt;Ninguna&gt; NOTAS: Tienen varios asociados conocidos con antecedentes penales, por lo que podrían no estar solos, así que ármense y tengan precaución al enfrentarse a ellos. GREMIO DE CAZADORES DE RECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="14">
@@ -489,7 +489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v> Certificación de Permiso de Iniciación para Rastreadores</v>
+        <v>Certificación de Permiso de Iniciación para Rastreadores</v>
       </c>
     </row>
     <row r="19">
@@ -562,19 +562,19 @@
         <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v/>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str" xml:space="preserve">
+        <v xml:space="preserve">-------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(NombreDelObjetivo) SISTEMA: Nyx EVALUACIÓN DE RIESGO: Alto ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: Salamandras Garra NOTAS: Debido a que estas estaciones de ruptura QV abandonadas no son completamente funcionales, hay una buena probabilidad de que tengas que realizar algunas reparaciones antes de poder acceder a la ubicación del objetivo. También puedes tener que lidiar con otros peligros como fauna peligrosa. Además, la información recopilada sobre ~mission(NombreDelObjetivo) lo tiene como un miembro de alto rango de las Salamandras Garra, uno que no aparecerá a menos que sea convenientemente sacado de su escondite. Enfréntate a suficientes asociados de menor rango y se verán obligados a venir a tratar contigo ellos mismos. GREMIO DE CAZARRECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v> En llamas</v>
+        <v>En llamas</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
       <c r="A35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
+        <v xml:space="preserve"> Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
       </c>
     </row>
     <row r="36">
@@ -902,9 +902,9 @@
         <v> Eliminar las estaciones de servicio</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v/>
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos estado teniendo problemas cada vez mayores con los forajidos en ~mission(Location|Address) y ya no podemos quedarnos de brazos cruzados mientras sus acciones agresivas perjudican a nuestra comunidad. Somos cautelosos a la hora de lanzar un ataque a gran escala, pero creemos que si se agotan sus reservas de combustible, se disuadirán de realizar más acciones hostiles. Si le es posible, le agradecería que se encargara personalmente de la destrucción del combustible. Un barco capaz de lanzar misiles probablemente sería lo más lógico, pero la decisión final es suya. Gracias, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="102">
@@ -912,9 +912,9 @@
         <v> Reducir la preparación operativa de Outlaw</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v/>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str" xml:space="preserve">
+        <v xml:space="preserve">En ~mission(Location|Address) hay un grupo de forajidos que se han vuelto cada vez más osados en sus ataques contra los activos de Citizens for Prosperity en el sistema. Para minimizar las pérdidas de vidas, primero intentaremos convencerlos de que se trasladen a otro lugar desactivando sus generadores y destruyendo sus reservas de combustible. Con suerte, eso será suficiente para que busquen un lugar más seguro. Gracias, Lima Endicott, Despachadora Principal de Citizens for Prosperity.</v>
       </c>
     </row>
     <row r="104">
@@ -922,9 +922,9 @@
         <v> Alerta: ~misión(Ubicación) bajo ataque</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v/>
+    <row r="105" xml:space="preserve">
+      <c r="A105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesitamos que todo el personal de seguridad disponible se presente en ~mission(Location|Address). Un grupo de individuos armados ha atacado uno de nuestros puestos de avanzada y necesitamos ayuda urgentemente. Aunque el grupo parece no estar afiliado a ninguna de las bandas conocidas, hemos recibido información de que su líder es ~mission(TargetName), un forajido local con una reputación temible. Por favor, diríjanse lo antes posible y aseguren la zona eliminando a los forajidos y a ~mission(TargetName|Last). Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="106">
@@ -932,9 +932,9 @@
         <v> Recuperando terreno de los cazatalentos</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v/>
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Actualmente buscamos agentes de seguridad cualificados y disponibles para dirigirse a ~mission(Location|Address) y recuperar una instalación de CFP que ha sido tomada por Headhunters. El grupo que actualmente ocupa el puesto de avanzada está liderado por ~mission(TargetName), un Headhunter de renombre con un historial de agresiones contra la población local y los voluntarios de CFP. Necesitamos asegurar a todos los Headhunters y eliminar a ~mission(TargetName|Last). Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="108">
@@ -942,19 +942,19 @@
         <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v/>
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Acabamos de recibir una comunicación urgente de ~mission(Location|Address) y buscamos especialistas en combate disponibles para ayudar a repeler un ataque de Headhunters. Todavía hay hostiles en el lugar y se han reportado varias bajas, por lo que necesitamos que esto se resuelva rápidamente. Proporcionaré todos los datos relevantes una vez que acepten mi solicitud. Gracias por su ayuda. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ataque de forajidos en ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v/>
+        <v> Ataque de forajidos en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Varios grupos de CFP cerca de ~mission(Location|Address) acaban de ser atacados por un grupo de forajidos liderado por ~mission(TargetName). Buscamos especialistas en combate disponibles para ayudar a recuperar los puestos de avanzada. Puedo proporcionar las ubicaciones una vez que acepten la solicitud, pero necesitamos despejar el puesto de avanzada principal y las instalaciones satélite de todas las fuerzas hostiles y eliminar a ~mission(TargetName|Last), ya que es poco probable que no cesen sus hostilidades si escapan. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="112">
@@ -962,9 +962,9 @@
         <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v/>
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ciudadanos por la Prosperidad busca agentes de seguridad disponibles para recuperar varias antiguas instalaciones de CFP cerca de ~mission(Location|Address) del control de Headhunter. Estos centros nos fueron arrebatados violentamente por ~mission(TargetName), lo que provocó la muerte de muchos voluntarios. Recuperar el control de estos puestos avanzados contribuirá a la estabilidad del sistema. Los informes indican que ~mission(TargetName|Last) suele esconderse entre sus filas, por lo que probablemente aparecerán una vez que hayas eliminado a la mayoría de los enemigos. Los XenoThreat están entrenados y motivados, por lo que no se rendirán fácilmente. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="114">
@@ -972,9 +972,9 @@
         <v> Recuperando puestos avanzados de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v/>
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str" xml:space="preserve">
+        <v xml:space="preserve">Buscamos personal de seguridad disponible para recuperar varios clústeres perdidos a manos de agresores XenoThreat. Ubicados cerca de ~mission(Location|Address), fueron tomados en brutales ataques liderados por ~mission(TargetName), un notorio teniente de XenoThreat. Queremos recuperar estos clústeres para restablecer las operaciones y continuar con nuestro trabajo. Deberás eliminar a todos los enemigos que aún se encuentren en el lugar, así como a ~mission(TargetName|Last). Recuerda que los XenoThreat están altamente entrenados y son rápidos en el combate, así que prepárate. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="116">
@@ -982,9 +982,9 @@
         <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v/>
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str" xml:space="preserve">
+        <v xml:space="preserve">La presencia de delincuentes en esta zona se ha vuelto mucho más audaz últimamente y muchas personas están resultando heridas. Recientemente hemos perdido varios grupos de delincuentes alrededor de ~mission(Location|Address). Si bien no nos gusta tener que recurrir a la violencia, la junta ha reconocido que estas ubicaciones son cruciales para establecer la estabilidad en el sistema y ha autorizado el uso de un dispositivo de seguridad para recuperarlas. También sabemos que los delincuentes infiltrados están liderados por ~mission(TargetName), quien tiene un historial de ataques contra intereses de CFP. La junta desea que se tomen medidas contra ~mission(TargetName|Last) para prevenir futuros ataques. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="118">
@@ -992,9 +992,9 @@
         <v> Recuperando clústeres de las manos de los cazatalentos</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v/>
+    <row r="119" xml:space="preserve">
+      <c r="A119" t="str" xml:space="preserve">
+        <v xml:space="preserve">La junta directiva de Ciudadanos por la Prosperidad acaba de autorizar fondos para contratar personal de seguridad con el fin de recuperar varios grupos cerca de ~mission(Location|Address) que han caído en manos de los Cazadores de Cabezas. Aunque intentamos aceptar la pérdida, se ha hecho evidente que son cruciales para nuestras operaciones en el sistema. Deberás despejar cada una de las ubicaciones que se te proporcionarán, pero, lo que es más importante, también deberás eliminar a ~mission(TargetName), quien está a cargo de los hostiles en el lugar. Estos Cazadores de Cabezas están fuertemente infiltrados y tienen un historial de violencia, así que prepárate en consecuencia. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="120">
@@ -1002,9 +1002,9 @@
         <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v/>
+    <row r="121" xml:space="preserve">
+      <c r="A121" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aunque Ciudadanos por la Prosperidad está comprometido con el cambio por medios no violentos, se ha hecho evidente que podrían ser necesarias excepciones. Las zonas seguras de CFP cerca de ~mission(Location|Address) fueron tomadas recientemente y de forma violenta por fuerzas XenoThreat bajo el mando de ~mission(TargetName). Buscamos operativos de combate disponibles para ayudar a recuperar estos puestos avanzados. Sin duda, será una tarea difícil, ya que las fuerzas XenoThreat están altamente entrenadas y ansiosas por luchar, así que prepárense en consecuencia. Además de eliminar cada grupo de fuerzas XenoThreat, deberán eliminar a ~mission(TargetName|Last), cuya pérdida sin duda hará que el sistema sea más seguro. Buena suerte, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="122">
@@ -1012,9 +1012,9 @@
         <v> Se necesita ayuda en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v/>
+    <row r="123" xml:space="preserve">
+      <c r="A123" t="str" xml:space="preserve">
+        <v xml:space="preserve">Recibimos una llamada de auxilio de ~mission(Location|Address) indicando que están siendo asaltados por un pequeño grupo de forajidos. ~mission(Location|CaveSize) Aunque remoto, este puesto de avanzada es una pieza crucial de la infraestructura de CFP en la zona, por lo que debemos recuperarlo. Lima Endicott, Despachadora principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="124">
@@ -1022,9 +1022,9 @@
         <v> Ataque de Headhunter en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v/>
+    <row r="125" xml:space="preserve">
+      <c r="A125" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Acabamos de recibir una llamada de auxilio desde ~mission(Location|Address) informando que una gran fuerza de Headhunters ha atacado nuestro puesto de avanzada. Se han registrado varios muertos y heridos entre quienes lograron huir. Buscamos personal de seguridad disponible para que se dirija al lugar y retome el control del puesto. Testigos han identificado a los atacantes como miembros de élite de los Headhunters, así que tengan cuidado y, si pueden, envíen refuerzos. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="126">
@@ -1032,9 +1032,9 @@
         <v> Solicitar ayuda: ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v/>
+    <row r="127" xml:space="preserve">
+      <c r="A127" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos recibido una llamada de auxilio desde ~mission(Location|Address). Un grupo de asaltantes desconocidos ha lanzado un ataque. Se han reportado varias muertes y necesitamos recuperar el puesto de avanzada. Sé que esto está lejos de su posición actual, pero estamos desesperados por asegurar la zona y que el puesto de avanzada vuelva a estar operativo. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="128">
@@ -1042,9 +1042,9 @@
         <v> Defiende ~misión(Ubicación) de los forajidos</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v/>
+    <row r="129" xml:space="preserve">
+      <c r="A129" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Nos enteramos de que ~mission(Location|Address) está bajo amenaza de ataque por parte de forajidos y ha solicitado ayuda. Necesitamos a alguien que los proteja y ahuyente a los forajidos. Asegúrate de permanecer cerca después del ataque inicial. Con demasiada frecuencia, los forajidos ganan las peleas simplemente enviando más enemigos de los que nadie puede defender razonablemente, así que asegúrate de repeler cualquier refuerzo antes de abandonar la zona. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="130">
@@ -1052,9 +1052,9 @@
         <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v/>
+    <row r="131" xml:space="preserve">
+      <c r="A131" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos descubierto que XenoThreat está a punto de lanzar un ataque contra ~mission(Location|Address). Si tienen éxito, se espera un alto número de bajas. Espero que con tu ayuda para defenderlos podamos evitarlo. Sabemos por encuentros anteriores que XenoThreat envía varios grupos de asalto para llevar a cabo sus ataques, así que asegúrate de no abandonar el puesto de avanzada hasta que hayas repelido a todos los refuerzos. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="132">
@@ -1062,9 +1062,9 @@
         <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v/>
+    <row r="133" xml:space="preserve">
+      <c r="A133" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Urgente! XenoThreat está atacando ~mission(Location|Address) para enviar un mensaje a otros colonos sobre las consecuencias de aceptar nuestro apoyo. Si logras repeler a los atacantes, seguramente enviarán refuerzos, así que tendrás que prepararte para múltiples asaltos. Dado que XenoThreat cuenta con muchos recursos, deberías considerar reclutar a otros para que te ayuden a mantener a todos a salvo. Contamos contigo. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="134">
@@ -1072,9 +1072,9 @@
         <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v/>
+    <row r="135" xml:space="preserve">
+      <c r="A135" t="str" xml:space="preserve">
+        <v xml:space="preserve">¡Urgente! XenoThreat se está movilizando para una incursión masiva con el objetivo de eliminar ~mission(Location|Address) del mapa. Eres su única esperanza para resistir este ataque y protegerlos de la crueldad de XenoThreat. Sé que te pido que te pongas en peligro, pero este sistema no cambiará a menos que personas como tú sean lo suficientemente valientes para afrontar estos peligros. Ninguna cantidad de créditos podría compensar el bien que harías al intervenir. Si estás dispuesto y eres capaz de asumir esta misión, asegúrate de llevar algunos aliados contigo. XenoThreat sin duda enviará refuerzos más fuertes una vez que se den cuenta de que están sufriendo bajas. Creemos en ti. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="136">
@@ -1082,9 +1082,9 @@
         <v> Piloto busca apoyo en combate</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v/>
+    <row r="137" xml:space="preserve">
+      <c r="A137" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de nuestros pilotos acababa de recoger un cargamento de suministros cerca de ~mission(Location|Address) cuando fue atacado por unos despiadados secuestradores de naves. Acabamos de recibir su señal de socorro y espero que puedan ir a brindarles apoyo en combate. Cualquier ayuda que puedan ofrecer sería crucial. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="138">
@@ -1092,9 +1092,9 @@
         <v> El barco necesita asistencia de emergencia</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v/>
+    <row r="139" xml:space="preserve">
+      <c r="A139" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Una nave afiliada a Ciudadanos por la Prosperidad intentaba entregar suministros en ~mission(Location|Address) cuando fue atacada por los destinatarios, quienes se negaron a pagar y optaron por la violencia. Daré instrucciones a nuestros comerciantes para que tengan más cuidado con quién hacen negocios en el futuro, pero por ahora, les agradecería mucho su ayuda para repeler a estos atacantes. Atentamente, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="140">
@@ -1102,9 +1102,9 @@
         <v> Convoy atrapado en un brutal ataque.</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v/>
+    <row r="141" xml:space="preserve">
+      <c r="A141" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acabamos de recibir la noticia de que un convoy de naves afiliadas a Ciudadanos por la Prosperidad ha sido atacado por forajidos y que nuestra gente necesita ayuda urgentemente. Si está disponible, necesitamos pilotos listos para el combate en ~mission(Location|Address) para defender a nuestra gente. Tenga en cuenta que en este momento crítico, no podemos permitirnos perder ni una sola nave y esperamos que, con su ayuda, todos nuestros miembros sobrevivan. Buena suerte, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="142">
@@ -1112,9 +1112,9 @@
         <v> Acudan en auxilio del convoy</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v/>
+    <row r="143" xml:space="preserve">
+      <c r="A143" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Estoy recibiendo informes de que un convoy de Ciudadanos por la Prosperidad que transporta suministros vitales está siendo atacado en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Perder esa carga sería un duro golpe para nuestras operaciones. Si tienes las habilidades de combate necesarias para enfrentarte a enemigos altamente agresivos, estamos más que dispuestos a pagar por tu ayuda. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="144">
@@ -1122,9 +1122,9 @@
         <v> Responder a la baliza de socorro</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v/>
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un convoy de Ciudadanos por la Prosperidad, en una misión de reabastecimiento, lanzó una baliza de socorro cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. No responden a las comunicaciones, así que supongo que la situación es grave. Ese convoy cuenta con pilotos experimentados, así que si no responden, sin duda necesitan ayuda. Le compensaremos por brindar apoyo a ese convoy. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="146">
@@ -1132,9 +1132,9 @@
         <v> Piloto en apuros</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v/>
+    <row r="147" xml:space="preserve">
+      <c r="A147" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Parece que una de las rutas que considerábamos relativamente seguras ha resultado ser lo contrario. Unos forajidos han atacado a uno de nuestros pilotos en ~mission(Location|Address) y no durará mucho sin ayuda. Les agradecería que volaran hasta allí lo antes posible para ayudarles a enfrentarse a estos atacantes. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="148">
@@ -1142,19 +1142,19 @@
         <v> Se necesita ayuda contra XenoThreat Raid</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v/>
+    <row r="149" xml:space="preserve">
+      <c r="A149" t="str" xml:space="preserve">
+        <v xml:space="preserve">La XenoThreat ha atacado sin piedad a nuestra gente y ahora necesitan urgentemente apoyo de combate y suministros médicos. Si estás disponible, deberás recoger los suministros en ~mission(Location|Address) antes de dirigirte a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Una vez allí, es importante que neutralices a todos los enemigos antes de completar la entrega de los suministros. Además, para ayudar a prevenir que un incidente como este vuelva a ocurrir, creemos que destruir los servidores de la XenoThreat en &lt;EM4&gt;~mission(Location1|Address)&lt;/EM4&gt; sería una medida disuasoria adicional. Gracias, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Entrega para ~misión(Destino) Lista</v>
+        <v> Entrega para ~misión(Destino) Lista</v>
       </c>
     </row>
     <row r="151" xml:space="preserve">
       <c r="A151" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve">Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="152">
@@ -1182,9 +1182,9 @@
         <v> Ataque a un puesto de avanzada de la CFP</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v/>
+    <row r="157" xml:space="preserve">
+      <c r="A157" t="str" xml:space="preserve">
+        <v xml:space="preserve">Citizens for Prosperity busca operadores de combate disponibles para la misión en ~(Ubicación|Dirección). Un grupo de delincuentes ha lanzado un ataque no provocado y nuestro personal de seguridad necesita refuerzos con urgencia. Por favor, envíense a ~(Ubicación) con la mayor brevedad posible. ¡Buena suerte! Lima Endicott, Coordinadora de Despacho, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="158">
@@ -1192,9 +1192,9 @@
         <v> Se necesitan defensores contra los cazadores de cabezas</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v/>
+    <row r="159" xml:space="preserve">
+      <c r="A159" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hemos recibido una comunicación de emergencia de ~mission(Location|Address) informando que están siendo atacados por un grupo de Headhunters. Sabemos que nuestra presencia en el sistema ha molestado a los Headhunters, pero eso no justifica este ataque no provocado. Si es posible, por favor, reúnan su equipo y salgan. Tengan en cuenta que los Headhunters son combatientes experimentados y no se rendirán fácilmente. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="160">
@@ -1202,9 +1202,9 @@
         <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v/>
+    <row r="161" xml:space="preserve">
+      <c r="A161" t="str" xml:space="preserve">
+        <v xml:space="preserve">Fuerzas de XenoThreat lanzaron un ataque no provocado cerca de ~mission(Location|Address). Buscamos operadores de combate disponibles para brindar apoyo. Si no los has enfrentado antes, es importante saber que XenoThreat son combatientes entrenados, por lo que no será una batalla fácil, pero es necesaria. Buena suerte, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="162">
@@ -1212,9 +1212,9 @@
         <v> Recuperar el puesto de avanzada de los cazadores de cabezas</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v/>
+    <row r="163" xml:space="preserve">
+      <c r="A163" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Citizens for Prosperity busca personal de seguridad para hacerse cargo de un antiguo puesto de avanzada de CFP que actualmente sirve de escondite para que los Headhunters lancen ataques por todo el sistema. Ubicado cerca de ~mission(Location|Address), recuperar este puesto permitirá a CFP brindar mayor apoyo a los esfuerzos locales para lograr la estabilidad. Lima Endicott, Despachadora principal, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="164">
@@ -1222,19 +1222,19 @@
         <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v/>
+    <row r="165" xml:space="preserve">
+      <c r="A165" t="str" xml:space="preserve">
+        <v xml:space="preserve"> pesar de nuestros esfuerzos por promover la no violencia, grupos delictivos locales siguen atacando a nuestra organización. Recientemente, XenoThreat atacó ~mission(Location|Address) y expulsó a nuestros voluntarios que trabajaban allí. Buscamos reclutar personal de combate para retomar el puesto de avanzada. Idealmente, podríamos llegar a un acuerdo para que se marchen, pero XenoThreat recurre rápidamente a la violencia para resolver todos sus problemas, así que sin duda habrá una pelea. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Intercepción de la carrera de suministros</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v/>
+        <v> Intercepción de la carrera de suministros</v>
+      </c>
+    </row>
+    <row r="167" xml:space="preserve">
+      <c r="A167" t="str" xml:space="preserve">
+        <v xml:space="preserve">La vida en la frontera es dura, y cada entrega a nuestros colonos es importante. No podemos permitirnos perder más este año. Uno de nuestros proveedores clave ha sido atacado por un grupo de forajidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y ha dejado de comunicarse con nosotros. Temo lo peor, pero si aún podemos recuperar los suministros que transportaban, podría marcar una gran diferencia. Es probable que los forajidos que los atacaron sigan merodeando por allí, así que manténganse alerta. Una vez que se hayan encargado de ellos, tomen la carga y llévenla al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Asegúrense de pilotar una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y lleven también un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;. Vuelen con seguridad, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="168">
@@ -1242,19 +1242,19 @@
         <v> Es necesario recuperar suministros esenciales.</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v/>
+    <row r="169" xml:space="preserve">
+      <c r="A169" t="str" xml:space="preserve">
+        <v xml:space="preserve">Estábamos en el proceso de entregar un envío urgente a la gente de &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; cuando nuestro piloto se topó con un grupo de forajidos. Intentaron huir, pero ya era demasiado tarde. Sin embargo, hay un lado positivo. Los rastreadores muestran que la carga sigue intacta, ubicada en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Hay muchas probabilidades de que los forajidos la estén custodiando mientras localizan una nave lo suficientemente grande para transportar todo. Aunque no quiero arriesgarme a perder a otro piloto, la necesidad de la carga a bordo es tan apremiante que justifica la decisión de enviar a alguien a recuperarla. Esto no será fácil, estos forajidos no tuvieron piedad con nuestro piloto. Tendrás que eliminarlos primero antes de recuperar la carga. Trae una nave que pueda almacenar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt; para el traslado. Entrégalo en el montacargas en &lt;EM4&gt;~misión(Destino)&lt;/EM4&gt; y solucionemos esto. Vuela seguro, Lima Endicott, Despachadora principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v> Recuperación de suministros valiosos</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v/>
+        <v>Recuperación de suministros valiosos</v>
+      </c>
+    </row>
+    <row r="171" xml:space="preserve">
+      <c r="A171" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Una nave de Ciudadanos por la Prosperidad ha sido emboscada por un grupo de forajidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitamos un piloto experto para ayudarlos. Perdimos el contacto con ellos durante la comunicación, pero parecía que estaban bajo fuego intenso. Puede que sea demasiado tarde para ellos, pero los suministros vitales que transportaban aún podrían ser útiles. Vuela hasta allí, elimina a los enemigos y recupera el cargamento. Necesitarás una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt; para transportar los suministros a tu nave. Llévalos al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; y te garantizo que se les dará un buen uso. Ten cuidado ahí fuera, Lima Endicott, Despachadora Principal de Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="172">
@@ -1262,29 +1262,29 @@
         <v> Operación especial de recuperación</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v/>
+    <row r="173" xml:space="preserve">
+      <c r="A173" t="str" xml:space="preserve">
+        <v xml:space="preserve">Normalmente no le pediría a nadie que hiciera algo tan arriesgado, pero estas son circunstancias excepcionales. Nuestro piloto transportaba una carga vital cuando fue atacado por un grupo de forajidos. Bajo ninguna circunstancia podemos permitir que se apoderen de la carga. Dado el tamaño de la fuerza hostil que atacó, no podrás hacerlo solo; necesitarás traer una tripulación experta a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; para eliminar a estos forajidos y recuperar la carga. Asegúrate de que al menos uno de ustedes tenga una nave con capacidad para almacenar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;. Si por algún milagro logras recuperar la carga, llévala al montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Es mucho pedir, pero si lo consigues, tendrás mi agradecimiento y el de toda la organización. Mucha suerte, Lima Endicott, Despachadora Principal de Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v> El envío de carga debe completarse.</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v/>
+        <v>El envío de carga debe completarse.</v>
+      </c>
+    </row>
+    <row r="175" xml:space="preserve">
+      <c r="A175" t="str" xml:space="preserve">
+        <v xml:space="preserve">Cada vez más naves de la CFP están siendo atacadas últimamente, y a pesar de nuestros mejores esfuerzos por mantener nuestras rutas comerciales tranquilas, seguimos perdiendo transportistas en ataques de forajidos. Nuestro piloto en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; es la última víctima. Me duele pensar en todo lo que hemos perdido, pero mientras haya gente que necesite nuestra ayuda, tenemos que seguir luchando. Si tienes una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta potencia&lt;/EM4&gt;, necesitamos que te dirijas a la ubicación mencionada y recuperes esa carga. Esto no será fácil, el piloto era uno de los mejores y no se rendiría sin luchar. No subestimemos a estos forajidos, traigan una tripulación de confianza y cuídense las espaldas. Una vez que tengas la carga, entrégala en el montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; y yo me encargaré de procesarla. Buena suerte y cuídate, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v> Suministros robados</v>
+        <v>Suministros robados</v>
       </c>
     </row>
     <row r="177" xml:space="preserve">
       <c r="A177" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v xml:space="preserve"> Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="178">
@@ -1302,19 +1302,19 @@
         <v> Operación de detención de narcóticos</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v/>
+    <row r="181" xml:space="preserve">
+      <c r="A181" t="str" xml:space="preserve">
+        <v xml:space="preserve">Citizens for Prosperity ha estado trabajando arduamente para mejorar la vida de las personas en todo el sistema, pero una tarea que ya es difícil se vuelve casi imposible cuando las drogas entran en juego. Recientemente hemos visto a un traficante que se dirige específicamente a nuestros miembros más vulnerables y hemos experimentado contratiempos en todos los ámbitos. Esto tiene que parar. Nos gustaría que se dirigieran a ~mission(Location|Address) y pusieran fin de forma definitiva a su red de producción. Si lo hacen, esperamos poder ayudar a nuestra gente a retomar el buen camino. Lima Endicott, Coordinadora Principal de Citizens for Prosperity</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Desactiva Headhunter Stronghold</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v/>
+        <v> Desactiva Headhunter Stronghold</v>
+      </c>
+    </row>
+    <row r="183" xml:space="preserve">
+      <c r="A183" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ante la reciente agresión perpetrada por los Cazadores de Cabezas contra nuestra gente, Ciudadanos por la Prosperidad ha estado organizando una operación a gran escala que, esperamos, les aseste un duro golpe. Sin embargo, antes de que esto suceda, necesitamos ganar algo más de tiempo para finalizar nuestros preparativos. Si pudieras destruir los generadores de energía en ~mission(Location|Address), lograrías retrasar a los Cazadores de Cabezas el tiempo suficiente para que podamos preparar nuestro contraataque. Tu ayuda será crucial para nuestro éxito. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="184">
@@ -1322,9 +1322,9 @@
         <v> Limitar la capacidad operativa de los forajidos</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v/>
+    <row r="185" xml:space="preserve">
+      <c r="A185" t="str" xml:space="preserve">
+        <v xml:space="preserve">En ~mission(Location|Address) hay una banda de forajidos que se ha convertido en un problema cada vez mayor para los asentamientos de Ciudadanos por la Prosperidad en el sector. Si bien la violencia directa contra los perpetradores podría ser efectiva, no se ajusta al espíritu de nuestra misión. En cambio, les pedimos que desconecten los generadores cerca de su fortaleza. Esto debería limitar su capacidad operativa y, con suerte, preservar vidas. Me gusta pensar que los forajidos de hoy son los miembros productivos de la sociedad del mañana. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="186">
@@ -1332,9 +1332,9 @@
         <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v/>
+    <row r="187" xml:space="preserve">
+      <c r="A187" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos recibido información de que los forajidos de ~mission(Location|Address) han comenzado a reclutar con la intención de lanzar un ataque contra Ciudadanos por la Prosperidad. Para evitar que la situación se descontrole, les pedimos que desactiven sus generadores de energía y detengan su expansión. Si lo logran, podrían salvar muchas vidas. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="188">
@@ -1342,9 +1342,9 @@
         <v> Desactivar Fortaleza de Forajidos en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v/>
+    <row r="189" xml:space="preserve">
+      <c r="A189" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tras una serie de incursiones contra asentamientos aliados de Ciudadanos por la Prosperidad, creemos haber localizado a los responsables en ~mission(Location|Address). Atacarlos directamente supondría un riesgo demasiado grande y probablemente provocaría represalias agresivas. En cambio, creemos que si se desactivaran sus generadores de energía, podrían verse obligados a asentarse en otro lugar. ¿Crees que podrías encargarte de ello? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="190">
@@ -1352,9 +1352,9 @@
         <v> Eliminar todo rastro de datos de reclutadores</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v/>
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str" xml:space="preserve">
+        <v xml:space="preserve">Estamos reconstruyendo la situación, pero hasta ahora sabemos que un Headhunter llamado ~mission(TargetName) robó recientemente datos confidenciales que, de ser expuestos, perjudicarían la causa de Ciudadanos por la Prosperidad. Debemos asegurarnos de eliminar todo rastro de los datos robados. Esto implica desactivar todos los servidores de Headhunter en ~mission(Location|Address) y localizar a ~mission(TargetName|Last) para impedir que siga difundiendo la información. Agradecemos mucho su ayuda. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="192">
@@ -1362,9 +1362,9 @@
         <v> Borrar los servidores de datos de Headhunter</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v/>
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str" xml:space="preserve">
+        <v xml:space="preserve">Con creciente frecuencia, miembros de la banda Headhunters atacan los asentamientos de Citizens for Prosperity cuando nuestras patrullas están demasiado lejos para brindar asistencia. Para ello, utilizan información recopilada sobre nosotros y almacenada en ~mission(Location|Address). Al destruir estos servidores y la información que contienen, podremos dificultar significativamente la capacidad de los Headhunters para actuar contra nosotros. Gracias por su ayuda. Lima Endicott, Despachadora Principal de Citizens for Prosperity.</v>
       </c>
     </row>
     <row r="194">
@@ -1372,9 +1372,9 @@
         <v> Destruir datos logísticos de XenoThreat</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v/>
+    <row r="195" xml:space="preserve">
+      <c r="A195" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos un pequeño problema que espero que puedas resolver. Uno de nuestros informantes ha revelado que XenoThreat ha estado recopilando datos sobre las operaciones de Ciudadanos por la Prosperidad en todo el sistema. Esta información, si se usa correctamente, podría poner a nuestra gente en grave riesgo. La mejor solución es que destruyas por completo los servidores donde se almacenan los datos en ~mission(Location|Address). Al eliminar su enorme cantidad de información, nuestra gente tendrá una oportunidad de defenderse. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="196">
@@ -1382,9 +1382,9 @@
         <v> Destruye los datos robados de Headhunter</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v/>
+    <row r="197" xml:space="preserve">
+      <c r="A197" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los Headhunters atacaron recientemente uno de nuestros transportes y, lamentablemente, lograron acceder a datos confidenciales. Aunque el cifrado es robusto, es solo cuestión de tiempo antes de que puedan acceder a ellos. Antes de que eso suceda, necesitamos que vayas a ~mission(Location|Address) y destruyas todo rastro de la información de sus servidores. Si logras esto, serías de gran ayuda para Citizens for Prosperity. Lima Endicott, Despachadora Principal, Citizens for Prosperity</v>
       </c>
     </row>
     <row r="198">
@@ -1392,19 +1392,19 @@
         <v> Centro de datos Clear Outlaw</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v/>
+    <row r="199" xml:space="preserve">
+      <c r="A199" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tras varios intentos de convencer a los forajidos de ~mission(Location|Address) de que detuvieran sus ataques contra los asentamientos aliados de Ciudadanos por la Prosperidad, hemos decidido un nuevo plan de acción. Queremos que borren todos los registros que almacenan en sus servidores. Este revés debería obligarlos a reconsiderar sus acciones o, al menos, darnos tiempo para evaluar otras opciones. Gracias, Lima Endicott, Despachadora Principal de Ciudadanos por la Prosperidad.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v> Destruir los servidores de datos de XenoThreat</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v/>
+        <v>Destruir los servidores de datos de XenoThreat</v>
+      </c>
+    </row>
+    <row r="201" xml:space="preserve">
+      <c r="A201" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Uno de los miembros de Ciudadanos por la Prosperidad que ha estado actuando como informante de XenoThreat nos ha informado que los servidores de datos ubicados en ~mission(Location|Address) albergan una gran cantidad de información vital para las operaciones de la banda. Si pudieras destruir estos servidores en nuestro nombre, sería un gran logro para la seguridad de todo el sistema. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="202">
@@ -1412,9 +1412,9 @@
         <v> Destruir servidores de datos de Outlaw</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v/>
+    <row r="203" xml:space="preserve">
+      <c r="A203" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ciudadanos por la Prosperidad hemos estado monitoreando a un grupo de forajidos muy peligroso en ~mission(Location|Address) y creemos que están planeando un ataque importante que podría desestabilizar todo el sistema. Para proteger el progreso que hemos logrado, les pedimos que asalten su base y destruyan todos los servidores que albergan sus planes. Esto debería darles tiempo suficiente para que reconsideren su ofensiva. Gracias, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="204">
@@ -1902,9 +1902,9 @@
         <v> Soporte al cliente bajo ataque</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="str">
-        <v/>
+    <row r="301" xml:space="preserve">
+      <c r="A301" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de buque CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Uno de nuestros clientes tuvo la brillante idea de poner a prueba sus habilidades de combate aéreo en un escenario del mundo real. No parece que vaya bien, porque nos contactaron pidiendo ayuda. Dirígete a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y ayúdanos a limpiar el desastre que crearon. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="302">
@@ -1912,19 +1912,19 @@
         <v> Detengan el ataque contra un cliente de alto perfil.</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="str">
-        <v/>
+    <row r="303" xml:space="preserve">
+      <c r="A303" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de nave CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente de alto perfil decidió recorrer el sistema Nyx pero fue atacado por naves hostiles cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Parece que están abrumados. ¿Hay alguna posibilidad de que se dirija a su ubicación y brinde apoyo? El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Encuentro de alto riesgo con un barco</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="str">
-        <v/>
+        <v> Encuentro de alto riesgo con un barco</v>
+      </c>
+    </row>
+    <row r="305" xml:space="preserve">
+      <c r="A305" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de nave CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Recientemente, recomendamos a un cliente que utilizara una ruta específica para cruzar Nyx de forma segura. Resulta que no era tan segura como suponíamos, porque un grupo emboscó la nave de nuestro cliente. Necesitamos solucionar esto lo antes posible. ¿Está disponible para ayudar? La información del cliente indica un ataque bien organizado, así que más vale que esté preparado para lidiar con hostiles experimentados en esta misión. Apúrese a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;, ayúdelos a sobrevivir y le pagaremos bien por su ayuda. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="306">
@@ -1932,9 +1932,9 @@
         <v> Defensa extremadamente peligrosa</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="str">
-        <v/>
+    <row r="307" xml:space="preserve">
+      <c r="A307" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de buque CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Tenemos un cliente actualmente bajo ataque en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Tenemos una larga trayectoria con este cliente y sabemos que es un experto en combate aéreo. Si está luchando por sobrevivir, entonces esta situación debe ser crítica. Buscamos un experto en combate aéreo de primer nivel para que se dirija allí y brinde apoyo. Si está disponible, este cliente realmente podría necesitar su ayuda. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="308">
@@ -1942,9 +1942,9 @@
         <v> Detengan el ataque mortal al barco</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="str">
-        <v/>
+    <row r="309" xml:space="preserve">
+      <c r="A309" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de buque CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO A pesar de nuestras advertencias, un cliente decidió volar a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Como era de esperar, acaban de dejar caer una baliza de rescate en la zona, por lo que estamos buscando un contratista para que vaya al lugar, evalúe la situación y, con suerte, rescate al cliente. Les advertimos que forajidos extremadamente peligrosos y bien equipados suelen atacar buques allí. Eso es exactamente lo que supongo que sucedió aquí, así que asegúrese de planificar en consecuencia. El pago se emitirá una vez completado el contrato con éxito. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="310">
@@ -1952,9 +1952,9 @@
         <v> Guardar envío</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="str">
-        <v/>
+    <row r="311" xml:space="preserve">
+      <c r="A311" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Defensa de buque CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente está reportando problemas cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Según sus comunicaciones, no parece ser un ataque organizado y profesional. Aun así, se nos paga para brindar protección y se ha solicitado. Necesitamos un contratista para volar allí y asegurar la situación. El pago se emitirá al completar con éxito el contrato. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="312">
@@ -1962,9 +1962,9 @@
         <v> Equipo de protección ejecutiva</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="str">
-        <v/>
+    <row r="313" xml:space="preserve">
+      <c r="A313" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Buque de escolta Código de aprobación: = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un grupo de buques ubicados en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; solicitan una escolta. Si acepta, diríjase a la ubicación de inmediato y espere instrucciones. El cliente afirma que esta escolta es una medida de precaución, pero eso no significa que deba bajar la guardia. Espere encontrar fuerzas hostiles y actúe en consecuencia. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="314">
@@ -1972,9 +1972,9 @@
         <v> Los clientes VIP necesitan protección.</v>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="str">
-        <v/>
+    <row r="315" xml:space="preserve">
+      <c r="A315" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Buque de escolta Código de aprobación: = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Se necesita un contratista que pueda presentarse ahora. Un cliente se encuentra en apuros en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesita protección para escapar de una base de asteroides. Han reportado múltiples naves hostiles bien armadas, lo que significa que necesitará una tripulación propia para lidiar con ellas. Según el relato del cliente, estos atacantes parecen muy motivados, por lo que probablemente no retrocederán fácilmente. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="316">
@@ -1982,9 +1982,9 @@
         <v> Se necesita personal de seguridad con experiencia.</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="str">
-        <v/>
+    <row r="317" xml:space="preserve">
+      <c r="A317" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Buque de escolta Código de aprobación: = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Uno de mis clientes necesita una escolta inmediata a través de un espacio peligroso. Reúnase en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y se reunirán con usted después del lanzamiento. Los informes indican un aumento de la actividad delictiva en la zona, así que no baje la guardia. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="318">
@@ -1992,9 +1992,9 @@
         <v> Se necesita operador de primer nivel.</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="str">
-        <v/>
+    <row r="319" xml:space="preserve">
+      <c r="A319" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Buque de escolta Código de aprobación: = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Este contrato solo debe ser considerado por los pilotos más capaces. Un cliente de gran valor está siendo atacado en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y requiere extracción inmediata. Se encuentran en el hangar listos para partir, pero no pueden moverse hasta que las naves hostiles en el área hayan sido neutralizadas. No veo que los forajidos se detengan pronto y nuestro cliente informa que están llevando armamento de alta gama en sus naves. Esto pondrá a prueba tanto su habilidad como su resistencia. Reúna a quien necesite y diríjase allí de inmediato para ayudarlos. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="320">
@@ -2002,9 +2002,9 @@
         <v> Detalle de protección de bajo riesgo</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="str">
-        <v/>
+    <row r="321" xml:space="preserve">
+      <c r="A321" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Escolta de naves Código de aprobación: = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente ha solicitado un contratista con disponibilidad inmediata para brindar apoyo adicional a varias naves que salen de una base de asteroides ubicada en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;). Una vez que haya aceptado, reúnase allí y espere más instrucciones. En este caso, su trabajo es brindar apoyo para su paso seguro. Puede haber hostiles presentes, pero no deberían ser demasiado difíciles de manejar. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="322">
@@ -2012,9 +2012,9 @@
         <v> Se requiere protección adicional. Alto riesgo.</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="str">
-        <v/>
+    <row r="323" xml:space="preserve">
+      <c r="A323" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Buque de escolta Código de aprobación: = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Necesito un piloto altamente competente que pueda reunir una tripulación de pilotos igualmente capaces para una misión de escolta. La base minera en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; está siendo atacada por un grupo de forajidos y la tripulación no puede salir sin ayuda. Nuestros exploradores han informado que los atacantes están armados con armamento y naves excepcionales. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="324">
@@ -2022,74 +2022,74 @@
         <v> Es hora de dar una lección</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="str">
-        <v/>
+    <row r="325" xml:space="preserve">
+      <c r="A325" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada de nave CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente nuestro ha estado recibiendo amenazas anónimas en un intento de chantaje, y después de un poco de trabajo de campo de nuestra parte, hemos logrado rastrearlo hasta un individuo que pilota una &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; en particular. El cliente quiere que nos encarguemos de este chantajista antes de que tenga la oportunidad de cumplir su amenaza. Según nuestra evaluación, el objetivo no debería ser demasiado difícil de manejar. Vuela regularmente por &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que tiene una &lt;EM4&gt;nube de emisión&lt;/EM4&gt; que es un lugar ideal para apagar su nave y esperar. A veces el objetivo está solo, pero a menudo viaja con otras naves monoplaza como protección. Será mejor ser estratégico al lanzar la emboscada o el &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; podría tener la oportunidad de escapar. No queremos perder esta. Alertaremos a otros contratistas en el área de la emboscada para que puedan venir a ayudar una vez que comience. El pago se emitirá al completar con éxito el contrato. El cliente también ha añadido un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; para el contratista principal. Este contrato no es negociable. Este mensaje puede contener información confidencial, propietaria, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v> Emboscada engañosa</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="str">
-        <v/>
+        <v>Emboscada engañosa</v>
+      </c>
+    </row>
+    <row r="327" xml:space="preserve">
+      <c r="A327" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada a barco CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Buscamos un contratista competente que pueda reclutar un compañero para ayudar a ejecutar una emboscada. El objetivo es un &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; que ha estado involucrado en varias operaciones contra uno de nuestros clientes más importantes. Al neutralizarlo de una vez por todas, le facilitará mucho la vida a nuestro cliente. Si bien el ~mission(AmbushTarget) es nuestro objetivo principal, normalmente no vuelan a ningún lugar sin una escolta considerable, incluyendo aeronaves grandes. Nos han informado de que este grupo pasará pronto por &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. ¿Hay alguna posibilidad de que se dé prisa y llegue antes que ellos? Ese lugar tiene una nube de emisión &lt;EM4&gt; que puedes apagar tu nave y esconderte. Así, cuando pasen, tendrás ventaja. El pago se realizará al completar el contrato con éxito. El cliente sabe que será difícil, así que incluyó un pago adicional de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip&lt;/EM4&gt; que irá al contratista principal. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v> Nueva oportunidad: ataque de emboscada</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="str">
-        <v/>
+        <v>Nueva oportunidad: ataque de emboscada</v>
+      </c>
+    </row>
+    <row r="329" xml:space="preserve">
+      <c r="A329" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada a nave CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Buscamos contratistas con experiencia en combate que estén dispuestos a ensuciarse las manos, por así decirlo. Un cliente nuestro fue traicionado por un &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; y hemos estado esperando una oportunidad para abordar el problema. Después de rastrearlos durante varias semanas, hemos identificado &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; como el lugar ideal para interceptarlos. Cuenta con una &lt;EM4&gt;nube de emisión&lt;/EM4&gt; donde puede esconderse y apagar su nave mientras espera al &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;. La inteligencia sugiere que pueden viajar con una escolta. Si lo hacen, también tendrá que lidiar con ellos. Dado que este es su primer contrato, contaremos con otros contratistas en la zona que podrán ayudarle una vez que lo firme. El pago se realizará al finalizar el contrato con éxito. También se incluye una bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; para el contratista principal. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v> Lanzar ataque sorpresa</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="str">
-        <v/>
+        <v>Lanzar ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="331" xml:space="preserve">
+      <c r="A331" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada a barco CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Necesitamos a alguien que elimine un &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; y se encargue de los barcos de escolta que lo protegen. Ya han interferido con varias de nuestras operaciones en curso y se han convertido en un verdadero problema en varios casos de Eckhart Security. No estamos seguros de cuál es su objetivo final, pero no importará una vez que se encargue de ellos. Hemos dejado entrever que estaremos trabajando en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que debería servir como cebo para atraerlos. El lugar es ideal para una emboscada debido a la &lt;EM4&gt;nube de emisión&lt;/EM4&gt; que es un lugar perfecto para apagar la energía y esconderse hasta que esté listo para atacar. Si está disponible, la misión &lt;EM4&gt;~(ObjetivoEmboscada)&lt;/EM4&gt; y sus escoltas deberían pasar pronto. El pago se realizará al finalizar el contrato con éxito. El contratista principal también recibirá una bonificación de &lt;EM4&gt;~misión(MontoCertificado) MG Scrip&lt;/EM4&gt;. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v> Emboscada sumamente peligrosa</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="str">
-        <v/>
+        <v>Emboscada sumamente peligrosa</v>
+      </c>
+    </row>
+    <row r="333" xml:space="preserve">
+      <c r="A333" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada de nave CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Recientemente, enviamos a un contratista tras un &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;, que lideraba un equipo que tenía como objetivo las operaciones de un cliente extremadamente importante. Desafortunadamente, fue una trampa y perdimos a algunas personas valiosas. No podemos permitir que el objetivo escape de nuevo, así que hemos decidido que el mejor curso de acción es darles una dosis de su propia medicina. Emboscar a este objetivo parece el curso de acción más seguro, y hemos identificado un buen lugar para tal ataque. Hay una &lt;EM4&gt;nube de emisión&lt;/EM4&gt; cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; por donde el objetivo y su equipo vuelan frecuentemente. Puedes apagar tu nave y esconderte allí hasta que estés listo para atacar. Este equipo es despiadado y extremadamente hábil. No cometas el mismo error que el contratista anterior y lo hagas solo. Lo mejor sería que trajeras a algunos amigos de confianza para que te ayuden con este equipo. El pago se realizará al finalizar el contrato con éxito. Además, le daremos una bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; al contratista principal por encargarse de esto. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v> Ajustar cuentas</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="str">
-        <v/>
+        <v>Ajustar cuentas</v>
+      </c>
+    </row>
+    <row r="335" xml:space="preserve">
+      <c r="A335" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada de nave CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Uno de nuestros clientes ha sido víctima de acoso constante, por lo que ha llegado el momento de enviar un claro mensaje de cese y desistimiento eliminando su preciado &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;. El individuo en cuestión sigue una rutina bastante predecible, lo que lo hace susceptible a una emboscada. Hemos identificado &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; como el lugar ideal. Cuenta con una &lt;EM4&gt;nube de emisión&lt;/EM4&gt; donde puede esconderse y apagar su nave mientras espera. Por cierto, el &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; suele volar solo, pero a veces se le une un amigo en una nave monoplaza. Ninguno de los dos debería causarle demasiados problemas, pero tenemos otros contratistas en la zona que pueden echarle una mano una vez que ataque. El pago se efectuará una vez finalizado el contrato con éxito. El contratista principal también recibirá una bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada al uso exclusivo de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v> Emboscada peligrosa</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="str">
-        <v/>
+        <v>Emboscada peligrosa</v>
+      </c>
+    </row>
+    <row r="337" xml:space="preserve">
+      <c r="A337" t="str" xml:space="preserve">
+        <v xml:space="preserve">ECKHART SECURITY, LLC. CONTRATOS Y DESPACHO TIPO DE CONTRATO: Emboscada a barco CÓDIGO DE APROBACIÓN = ~mission(ApprovalCode) PARA PROCESAMIENTO INMEDIATO Un cliente de alto perfil perdió recientemente un envío importante cuando un piloto lo traicionó y se llevó su producto. Después de semanas de búsqueda, hemos descubierto que estaban conectados con una banda de forajidos, por lo que el cliente busca que disuadamos que surjan problemas similares en el futuro. El objetivo final es el piloto de un &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;, quien lidera la tripulación responsable. Esto no será fácil. No van a ninguna parte sin cazas de escolta y naves subcapitales. Por eso recomendamos encarecidamente que encuentre uno o dos amigos de confianza que puedan manejar esto con usted. La inteligencia recopilada por nuestros analistas indica que frecuentemente vuelan cerca de una &lt;EM4&gt;nube de emisión&lt;/EM4&gt; cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que proporcionaría un área excelente para realizar un ataque sorpresa. El pago se efectuará una vez finalizado el contrato con éxito. Además, se añadirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; que se entregará al contratista principal. Este contrato no es negociable. Este mensaje puede contener información confidencial, de propiedad exclusiva, privilegiada y/o privada. La información está destinada únicamente al uso de la persona o entidad designada anteriormente.</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo)</v>
+        <v>Recompensa de alto riesgo: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
     <row r="339" xml:space="preserve">
@@ -2112,59 +2112,59 @@
         <v>Contrato de nivel amarillo: Interrupción de operaciones</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="str">
-        <v/>
+    <row r="343" xml:space="preserve">
+      <c r="A343" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Acabamos de recibir la ubicación de un puesto de avanzada de forajidos donde se han estado escondiendo algunos criminales emergentes. Nuestro cliente dice que no hay razón para enfrentarse directamente a ellos. En cambio, su objetivo serán sus líneas de suministro. Vuele a &lt;EM4&gt;~misión(Ubicación|Dirección)&lt;/EM4&gt; y destruya sus depósitos de combustible mientras lidia con cualquier resistencia mínima que puedan oponer. Usted decide cuánto se enfrenta a las fuerzas hostiles, pero no olvide que su objetivo principal es asegurarse de que esos tanques de combustible queden fuera de servicio. Este es un contrato de nivel amarillo, por lo que la paga será proporcional. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v> Contrato de nivel naranja: Destruir infraestructura ilegal</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="str">
-        <v/>
+        <v>Contrato de nivel naranja: Destruir infraestructura ilegal</v>
+      </c>
+    </row>
+    <row r="345" xml:space="preserve">
+      <c r="A345" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Se le ha presentado una oportunidad a un cliente para tomar medidas contra un grupo de criminales que han estado acosando su negocio. Según los informes, este grupo de forajidos se encuentra actualmente escondido en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. El cliente cree que este es un buen momento para sorprenderlos y llevarlos ante la justicia. El trabajo es destruir sus tanques de combustible y poner fin a sus operaciones de contrabando de una vez por todas. No subestime a esta gente. Será mejor que traiga refuerzos y vuele bajo para evitar las torretas. La prioridad, como siempre, son los tanques de combustible. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v> Contrato de nivel naranja: Retire los suministros de combustible</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="str">
-        <v/>
+        <v>Contrato de nivel naranja: Retire los suministros de combustible</v>
+      </c>
+    </row>
+    <row r="347" xml:space="preserve">
+      <c r="A347" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesitamos un contratista astuto para una operación de ataque y fuga. El cliente dice que algunos matones locales se han estado reuniendo en cantidades preocupantes y nos han encargado interrumpir su base de operaciones. Dirígete a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y destruye sus tanques de combustible. Si tienes éxito, podemos retrasar los planes de esta gente por un tiempo y, lo más importante, sin tener que lidiar con ellos directamente. Los informes muestran que hay un par de naves sobrevolando la zona y algunas torretas de defensa. Solo concéntrate en los tanques de combustible y todo debería salir bien. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v> Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="str">
-        <v/>
+        <v>Contrato de nivel rojo: Destruir la infraestructura de los forajidos</v>
+      </c>
+    </row>
+    <row r="349" xml:space="preserve">
+      <c r="A349" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Buscamos un equipo de mercenarios altamente competente para ayudar en una demolición compleja para un cliente VIP. Los forajidos que operan en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; han sido identificados como una amenaza creciente en la zona y, para ayudar a lidiar con esta situación, su equipo tiene la tarea de destruir los tanques de combustible en la ubicación. Sin embargo, no será tan fácil como entrar y salir sin ser detectados: prepárense para enfrentarse a múltiples enemigos y torretas que los estarán esperando. Cuanto más fuerte sea su equipo, mayores serán sus posibilidades de completar esta operación con éxito. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera'. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v> Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="str">
-        <v/>
+        <v>Contrato de nivel amarillo: Limitación de amenazas potenciales</v>
+      </c>
+    </row>
+    <row r="351" xml:space="preserve">
+      <c r="A351" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Un grupo de forajidos ha estado acosando a nuestro cliente y recientemente las cosas han empeorado. Se han apoderado de su propiedad y hemos agotado todas las demás opciones. Necesitamos un piloto competente que se dirija a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y destruya sus tanques de combustible. Si logra cortarles el suministro, podrá allanar el camino para que el cliente recupere su propiedad. Esto no debería ser difícil. Puede que se encuentre con una o dos naves y tal vez algunas torretas, pero está autorizado a usar fuerza letal. Todo lo que necesitamos que haga es entrar, conseguir los tanques de combustible y salir. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v> Contrato de nivel rojo: Demolición de contenedores de combustible</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="str">
-        <v/>
+        <v>Contrato de nivel rojo: Demolición de contenedores de combustible</v>
+      </c>
+    </row>
+    <row r="353" xml:space="preserve">
+      <c r="A353" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Foxwell ha sido contratado por un cliente para participar en una operación de varias etapas en una base de forajidos conocida en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesita un piloto fuerte para desempeñar su papel en esto. Usted, y cualquier nave de apoyo adicional que organice, tendrá la tarea de destruir los tanques de combustible ubicados allí para preparar el terreno para el resto de la operación. Desafortunadamente, este lugar está repleto de naves y torretas antiaéreas. Así que asegúrese de que usted y su gente estén listos, y recuerde, los tanques de combustible son su prioridad. No es necesario ser un héroe. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="354">
@@ -2292,9 +2292,9 @@
         <v>Contrato de nivel amarillo: Barco bajo ataque</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="str">
-        <v/>
+    <row r="379" xml:space="preserve">
+      <c r="A379" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Foxwell busca un piloto de combate disponible para brindar asistencia inmediata a una misión (nave) bajo ataque por parte de una misión (ubicación/dirección). No hemos identificado a los perpetradores del ataque, pero nos han asegurado que se trata de una fuerza pequeña. Por favor, envíenlo rápidamente y eliminen a todos los hostiles. Necesitamos que el cliente supere esto, ya que aún no nos ha pagado. Buena suerte, Marcus Clenn Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="380">
@@ -2302,9 +2302,9 @@
         <v> Contrato de nivel rojo: El barco está bajo ataque.</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="str">
-        <v/>
+    <row r="381" xml:space="preserve">
+      <c r="A381" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acaba de llegar un contrato de emergencia sobre una pelea cerca de ~mission(Location|Address). Aparentemente, un grupo de naves fue emboscado por forajidos liderados por ~mission(TargetName), buscado en múltiples planetas por asesinato y robo de naves. Foxwell busca pilotos de combate de élite para proteger a los clientes. Este contrato está marcado como de nivel rojo, por lo que es muy peligroso. Si conoces gente que puedas traer, deberías hacerlo. Si lo haces, también deberías informarles sobre las políticas de contratación de Foxwell. Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="382">
@@ -2312,9 +2312,9 @@
         <v> Contrato de nivel naranja: ~misión (nave) necesita asistencia</v>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="str">
-        <v/>
+    <row r="383" xml:space="preserve">
+      <c r="A383" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos un contrato de nivel naranja para cualquier piloto de combate disponible. Una ~misión(Nave) está siendo atacada cerca de ~misión(Ubicación|Dirección) y necesita ayuda desesperadamente. No estamos seguros de cuántos perpetradores hay, pero parecen motivados y peligrosos, así que tenga cuidado. Una vez en el lugar, ataque y destruya a cualquier hostil que encuentre y proteja al cliente. Una vez que hayan transferido los créditos, le enviaremos su pago. Marcus Clenn Foxwell Enforcement 'Seguridad, a su manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="384">
@@ -2322,39 +2322,39 @@
         <v> Desmantelan una nueva operación antidrogas.</v>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="str">
-        <v/>
+    <row r="385" xml:space="preserve">
+      <c r="A385" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hay gente que haría cualquier cosa por unos cuantos créditos. Hay un grupo de forajidos recién llegados en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; que han decidido empezar a fabricar drogas. Resulta que no son muy buenos en ello, o quizás demasiado buenos. La porquería que producen es más fuerte que la normal y un verdadero peligro para cualquiera que la consuma. Nos han contratado para desmantelar su operación y destruir cualquier alijo de drogas que haya en el lugar. Guardias armados protegen el lugar, pero no parecen muy hábiles. Nuestros equipos de vigilancia observaron a uno de ellos casi dispararse en el pie. No podemos asegurarlo, pero lo más probable es que no le den muchos problemas a un profesional como usted. Marcus Clenn Foxwell Enforcement 'Seguridad a su manera' Foxwell Enforcement es una empresa de seguridad especializada y con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v> Destruir drogas peligrosas</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="str">
-        <v/>
+        <v>Destruir drogas peligrosas</v>
+      </c>
+    </row>
+    <row r="387" xml:space="preserve">
+      <c r="A387" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Los informes sobre un aumento repentino de sobredosis de drogas en los alrededores de Stanton tienen a los servicios de seguridad preocupados. Parece que una banda de poca monta está aumentando sus ganancias adulterando sus drogas con sustancias químicas tóxicas. Desmantelar esta banda y detener la distribución de sus drogas se ha convertido en una prioridad. Un informante de Foxwell ha revelado que parte de esta banda se ha instalado en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Contratarán a un contratista para que se dirija rápidamente al lugar y destruya las drogas que tengan almacenadas antes de que se distribuyan por todo el sistema. Sin embargo, mejor tener cuidado, se rumorea que esta banda está armada hasta los dientes y decidida a lucrarse con ese veneno a cualquier precio. Marcus Clenn Foxwell Enforcement 'Seguridad a tu medida' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v> Destruir las drogas ilegales</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="str">
-        <v/>
+        <v>Destruir las drogas ilegales</v>
+      </c>
+    </row>
+    <row r="389" xml:space="preserve">
+      <c r="A389" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nos han contratado para solucionar un problema en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Ha habido un aumento reciente de actividad en la zona relacionada con el narcotráfico. Parece ser una operación bien organizada y existe una creciente preocupación de que se expanda si no se detiene. ¿Hay alguna posibilidad de que estés disponible para asegurarte de que eso no suceda? El trabajo es bastante sencillo. Dirígete al lugar y destruye su alijo de drogas. De esa manera, no tendrán la credibilidad para expandir sus operaciones. Sin embargo, no esperes que te lo pongan fácil. Se ven guardias armados con regularidad alrededor de las instalaciones, así que asegúrate de tener el equipo suficiente para enfrentarte a ellos también. Marcus Clenn Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v> Ayuda a proteger el sitio.</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="str">
-        <v/>
+        <v>Ayuda a proteger el sitio.</v>
+      </c>
+    </row>
+    <row r="391" xml:space="preserve">
+      <c r="A391" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Nos enteramos de que unos delincuentes están intentando tomar &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Hay fuerzas de seguridad locales allí, pero están teniendo dificultades para detener el ataque. Necesitamos un contratista que se desplace rápidamente y ayude a neutralizar a los agresores. Traiga suficiente equipo y tenga cuidado al enfrentarse a los objetivos. No queremos que ningún miembro del equipo de seguridad quede atrapado en el fuego cruzado. Marcus Clenn Foxwell Enforcement 'Seguridad a su medida' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="392">
@@ -2362,9 +2362,9 @@
         <v> Limpie cuidadosamente el sitio</v>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="str">
-        <v/>
+    <row r="393" xml:space="preserve">
+      <c r="A393" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nos han contratado para encargarnos de una situación delicada. Una banda se ha instalado en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitamos desalojarla. El único problema es que todavía hay civiles allí. Buscamos a alguien con las habilidades y buen instinto para disparar para deshacerse de esos forajidos sin dañar a ninguna persona inocente. Si eres tú, toma tu equipo y ven para allá. Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="394">
@@ -2372,9 +2372,9 @@
         <v> Contrato de nivel amarillo: Merc Work</v>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="str">
-        <v/>
+    <row r="395" xml:space="preserve">
+      <c r="A395" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos estado siguiendo a un grupo de forajidos en nombre de un cliente, y parece que se han establecido permanentemente en una antigua plataforma orbital. Buscamos un contratista que pueda dirigirse a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y neutralizar a los objetivos. La plataforma está plagada de matones armados y peligrosos, por lo que hemos clasificado este contrato como de nivel amarillo. Marcus Clenn Foxwell Enforcement 'Seguridad a tu medida' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="396">
@@ -2382,9 +2382,9 @@
         <v> Contrato de nivel amarillo: Despeje de la PAF</v>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="str">
-        <v/>
+    <row r="397" xml:space="preserve">
+      <c r="A397" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos estado siguiendo a un grupo de delincuentes que han estado causando problemas a uno de nuestros clientes. Parece que se han instalado en una antigua instalación de Hathor. No sabemos cuáles son sus planes con esa antigua instalación, pero nuestro cliente está ansioso por que se encarguen de ellos. Buscamos a alguien que vaya a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y neutralice a estos objetivos. Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="398">
@@ -2392,9 +2392,9 @@
         <v> Barrer y despejar la ubicación</v>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="str">
-        <v/>
+    <row r="399" xml:space="preserve">
+      <c r="A399" t="str" xml:space="preserve">
+        <v xml:space="preserve">Buscando a alguien dispuesto a sacar la basura en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Parece que una pandilla se ha instalado sin el permiso de los dueños. Así que nos han contratado para echarlos como mejor nos parezca. Yo traería mucha munición, si fuera tú. Dudo que quieran irse voluntariamente. Marcus Clenn Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="400">
@@ -2402,9 +2402,9 @@
         <v> Ataque de precisión en ~misión(Nombre del objetivo)</v>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="str">
-        <v/>
+    <row r="401" xml:space="preserve">
+      <c r="A401" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tengo una pista sobre una recompensa llamada &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;. Alguien los vio junto con cómplices criminales conocidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Necesito que llegues allí antes de que se vayan. &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt; tiene fama de solo dejarse ver en lugares con civiles. Realmente necesito que elimines esta recompensa sin que haya daños colaterales civiles. Foxwell no puede permitirse verse envuelto en la tormenta de mierda que estallaría por la pérdida de vidas inocentes. Marcus Clenn Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, por favor contacta a uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="402">
@@ -2412,9 +2412,9 @@
         <v> Localizar ~misión(Nombre del objetivo)</v>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="str">
-        <v/>
+    <row r="403" xml:space="preserve">
+      <c r="A403" t="str" xml:space="preserve">
+        <v xml:space="preserve">Buscamos ejecutar una recompensa por &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;. Nos hemos enterado de que actualmente se esconden con algunos cómplices en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Estaría preparado para lidiar con los maleantes que andan por &lt;EM4&gt;~mission(TargetName|Last)&lt;/EM4&gt;, pero nuestra única preocupación real es que captures al objetivo. Marcus Clenn Foxwell Enforcement 'Seguridad a tu manera' Foxwell Enforcement es una empresa de seguridad especializada y con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="404">
@@ -2422,39 +2422,39 @@
         <v> Contrato de nivel rojo: Recuperar cargamento</v>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="str">
-        <v/>
+    <row r="405" xml:space="preserve">
+      <c r="A405" t="str" xml:space="preserve">
+        <v xml:space="preserve">Buscamos un contratista con las habilidades y la nave adecuadas para una misión importante. Unos forajidos emboscaron un Hull C que transportaba una carga de &lt;EM4&gt;~mission(CargoGradeToken)&lt;/EM4&gt; y la llevaron a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Nos han contratado para recuperarla. La carga está almacenada en algún lugar de una instalación Hathor abandonada. El lugar es grande y está plagado de forajidos. Necesitamos a alguien que recoja la mercancía del montacargas y la lleve de vuelta al &lt;EM4&gt;montacargas en ~mission(Destination|Address)&lt;/EM4&gt;. No creas que esto será un paseo por el parque. Trae mucha munición y una nave que pueda manejar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Tampoco estaría de más traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Marcus Clenn Foxwell Enforcement: Seguridad a tu medida. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Buscamos constantemente nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v> Contrato de nivel rojo: Recuperar el cargamento robado</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="str">
-        <v/>
+        <v>Contrato de nivel rojo: Recuperar el cargamento robado</v>
+      </c>
+    </row>
+    <row r="407" xml:space="preserve">
+      <c r="A407" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un grupo asaltó recientemente un centro de distribución y se llevó &lt;EM4&gt;~mission(CargoGradeToken) carga de mercancía&lt;/EM4&gt;. Foxwell ha sido contratado para recuperar toda esa mercancía. Estamos recibiendo informes de que estos forajidos utilizan antiguas instalaciones de Hathor como escondites y creemos que los artículos robados se encuentran actualmente en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Si le interesa, necesitará una nave que pueda manejar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Dudo que pueda entrar y salir de esa PAF sin ser detectado, así que mejor prepárese para despejar la zona. Una vez a salvo, tome la mercancía del montacargas y entréguela en el &lt;EM4&gt;montacargas en ~mission(Destination|Address)&lt;/EM4&gt;. Tampoco estaría de más llevar un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. Marcus Clenn Foxwell Enforcement: Seguridad a tu medida. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Buscamos constantemente nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v> Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="str">
-        <v/>
+        <v>Contrato de nivel rojo: Eliminar PAF, recuperar la carga y entregarla a OLP.</v>
+      </c>
+    </row>
+    <row r="409" xml:space="preserve">
+      <c r="A409" t="str" xml:space="preserve">
+        <v xml:space="preserve">Algo extraño está sucediendo en las antiguas instalaciones mineras de Hathor. Tanto las plataformas de alineación como las plataformas láser orbitales han estado abandonadas y acumulando polvo durante décadas, pero unos forajidos han comenzado a usarlas como base de operaciones. Nos ha contratado una persona preocupada que recientemente perdió una gran cantidad de cargamento importante a manos de una de estas bandas. Actualmente, su mercancía está escondida en &lt;EM4&gt;~mission(Location1|Address)&lt;/EM4&gt; y &lt;EM4&gt;~mission(Location2|Address)&lt;/EM4&gt;, pero existe un temor creciente de que la banda pueda estar descargando su mercancía pronto. Por eso nos han contratado para atacar ambas instalaciones de Hathor, recuperar la carga de los montacargas y llevarla al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Aquí están los detalles sobre qué recoger de cada ubicación. No importa el orden en que lo hagas, siempre y cuando todo se recoja y se entregue. Asegúrate de traer una nave que pueda manejar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;. Tampoco estaría de más traer un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ~mission(MultiToSingleToken) Foxwell no ha podido explorar estas ubicaciones, pero si yo fuera tú, esperaría enfrentar una seria resistencia armada. Mejor trae un montón de equipo y algunos amigos. Marcus Clenn Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contrato.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v> ¿Sigues buscando trabajo?</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v/>
+        <v>¿Sigues buscando trabajo?</v>
+      </c>
+    </row>
+    <row r="411" xml:space="preserve">
+      <c r="A411" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Debido a una reestructuración corporativa, Foxwell tiene algunas vacantes que deben cubrirse de inmediato. Sabemos que usted ha expresado interés en este tipo de trabajo y nos preguntamos si le gustaría intentarlo nuevamente con un contrato. Uno de nuestros clientes necesita apoyo en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;, donde sus fuerzas de seguridad están teniendo dificultades para controlar una incursión de delincuentes. Diríjase allí y ayude a las fuerzas locales a resolver el problema antes de que sea demasiado tarde. Si completa este contrato con éxito, Foxwell estará encantado de enviarle más trabajo. Marcus Clenn Foxwell Enforcement 'Seguridad a su medida' Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="412">
@@ -2522,69 +2522,69 @@
         <v>Contrato de nivel amarillo: Ataque sorpresa</v>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="str">
-        <v/>
+    <row r="425" xml:space="preserve">
+      <c r="A425" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un forajido que ha estado huyendo finalmente ha regresado al sistema. Parece que esperaba que desapareciendo por un tiempo nos hiciera olvidarnos de él. Ni siquiera intenta ocultar su identidad ni variar su rutina, lo que significa que sabemos exactamente dónde va a estar. La información más reciente indica que está volando una &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; y pasará por &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; pronto. Ya he localizado una nube de emisión que es un lugar perfecto para que te cubras, apagues tu nave y esperes. La única incógnita es si estará solo o no. Hemos oído que a veces vuela con amigos que pilotan monoplazas. Lograr ese primer ataque sorpresa será importante, ya que esta tripulación está curtida en combate, pero tendremos refuerzos listos para brindar apoyo si los necesitas. Si lo haces, le daremos al contratista principal un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera'. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, comunícate con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v> Contrato de nivel naranja: Devuelve el favor</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="str">
-        <v/>
+        <v>Contrato de nivel naranja: Devuelve el favor</v>
+      </c>
+    </row>
+    <row r="427" xml:space="preserve">
+      <c r="A427" t="str" xml:space="preserve">
+        <v xml:space="preserve">Recientemente, una misión de emboscada atrajo a las fuerzas de Foxwell con una falsa baliza de rescate. Para cuando nuestras fuerzas se dieron cuenta de lo que estaba sucediendo, un escuadrón de naves lanzó un ataque devastador y solo un contratista de Foxwell sobrevivió. Sus registros de escaneo identificaron la nave señuelo, y desde entonces hemos tenido exploradores vigilándolos. Nuestra vigilancia ha revelado que el escuadrón tiene un patrón de vuelo regular que creemos que podemos aprovechar. Hay una nube de emisión considerable en la ubicación de la misión, lo que la convierte en un lugar ideal para posicionarse. ¿Crees que tienes lo que se necesita para encargarte de esto? Serás tú contra la misión de emboscada, otras naves grandes y una escolta considerable. Ojalá pudiera ser más específico, pero esta tripulación rota regularmente las naves dentro y fuera del escuadrón. Sería inteligente traer apoyo para que no te veas abrumado por su número. Completa el trabajo y le daremos al contratista principal un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en todo el UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v> Contrato de nivel naranja: Tender una trampa</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="str">
-        <v/>
+        <v>Contrato de nivel naranja: Tender una trampa</v>
+      </c>
+    </row>
+    <row r="429" xml:space="preserve">
+      <c r="A429" t="str" xml:space="preserve">
+        <v xml:space="preserve">Foxwell ha estado rastreando una &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; utilizada por forajidos y ha descubierto un patrón en sus movimientos. La nave debería pasar pronto por &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Buscamos un contratista dispuesto a ir rápidamente hasta allí, esconderse en la nube de emisión y luego activar la trampa cuando sea el momento adecuado. Normalmente hay naves de escolta con la &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;. Cuidado de no precipitarse y revelar su identidad. El elemento sorpresa es crucial por lo que he leído. Si lo consigues, le daremos al contratista principal un pago extra de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, póngase en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v> Contrato de nivel rojo: Ataque sorpresa</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="str">
-        <v/>
+        <v>Contrato de nivel rojo: Ataque sorpresa</v>
+      </c>
+    </row>
+    <row r="431" xml:space="preserve">
+      <c r="A431" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos recibido varias comunicaciones sobre ataques recientes llevados a cabo por una &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt; y sus naves de escolta. Tras abrir un archivo, comenzamos a rastrear los movimientos de la nave y notamos que frecuentemente pasa por una nube de emisión cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Queremos aprovechar esto para lanzar un ataque sorpresa. Una vez en el lugar, debes esconderte en la nube de emisión para camuflar tu firma lo suficiente como para poder realizar el primer ataque. Desafortunadamente, Foxwell no puede proporcionar refuerzos adicionales para esta operación, por lo que serás responsable de traer las fuerzas de apoyo. Puede que tú también necesites ayuda. La tripulación de la ~mission(AmbushTarget) es agresiva y está curtida en combate. Si te encargas de esto por nosotros, el contratista principal recibirá un pago adicional de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador de Foxwell Enforcement. «Seguridad a tu medida». Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre buscamos nuevos operadores para unirse a nuestro equipo. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratación.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v> Contrato de nivel amarillo: Emboscada a un aficionado</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="str">
-        <v/>
+        <v>Contrato de nivel amarillo: Emboscada a un aficionado</v>
+      </c>
+    </row>
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str" xml:space="preserve">
+        <v xml:space="preserve">¿Te gustaría ayudarnos a eliminar a un tipo malo? Nos han contratado para dar caza a un forajido que vuela una &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;. No debería ser muy difícil, ya que siguen la misma ruta de vuelo todos los días. Eso los convierte en un objetivo perfecto para una emboscada. He analizado la ruta y he determinado que &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; es el lugar ideal para atacar. Hay una nube de emisión allí que será perfecta para ocultar la firma de tu nave mientras esperas. El trabajo es sencillo si te interesa. Dirígete a la ubicación, escóndete, apaga la energía y luego espera a que pasen volando. A veces vuelan solos, pero a menudo vienen acompañados de otras naves monoplaza. No debería ser demasiado difícil para un profesional. Además, todavía tendremos refuerzos cerca y listos para desplegarse cuando comience la emboscada. Si lo logras, le daremos al contratista principal un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt;. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad a tu manera'. Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v> Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="str">
-        <v/>
+        <v>Contrato de nivel rojo: Escuadrón de ataque de emboscada</v>
+      </c>
+    </row>
+    <row r="435" xml:space="preserve">
+      <c r="A435" t="str" xml:space="preserve">
+        <v xml:space="preserve">Foxwell recibió información de un cliente importante de que unos forajidos han formado un escuadrón que ha estado acechando el sistema con naves subcapitales y cazas de escolta. Nuestro cliente está preocupado de que, si no se les detiene, los forajidos creen más escuadrones de ataque y desestabilicen la seguridad del sistema. Nos han contratado para eliminar a este grupo antes de que eso suceda. Necesitamos un contratista seguro y capacitado para esta tarea. La buena noticia es que tenemos un plan. Una de las naves utilizadas por este escuadrón, una &lt;EM4&gt;~mission(AmbushTarget)&lt;/EM4&gt;, fue robada a nuestro cliente, quien aún puede rastrear sus movimientos. Nos han compartido los datos de ubicación y hemos descubierto que este escuadrón suele usar la &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Hemos explorado la zona y descubierto que una gran nube de emisión es un lugar ideal para una emboscada. No voy a mentir, esto no va a ser fácil. No tenemos fuerzas adicionales disponibles para desplegar, así que sería bueno que trajeras tu propio apoyo. Si logras esto, he organizado un pago de bonificación de &lt;EM4&gt;~mission(ScripAmount) MG Scrip&lt;/EM4&gt; para el contratista principal. Buena suerte, Kevin Walton, Despachador, Foxwell Enforcement 'Seguridad, a tu manera' Foxwell Enforcement es un especialista en seguridad con fianza y licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si usted o alguien que conoce está interesado, comuníquese con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v> Contrato de nivel amarillo: Neutralizar a la banda de secuestradores de barcos</v>
+        <v>Contrato de nivel amarillo: Neutralizar a la banda de secuestradores de barcos</v>
       </c>
     </row>
     <row r="437" xml:space="preserve">
       <c r="A437" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bien, esto podría ser un poco complicado de hacer solo, así que si tienes algún favor que pedir, sería bueno cobrarlo ahora. Hay un grupo de forajidos atacando naves de reparto en este sector y nos han encargado eliminarlos. Cuando tu tripulación esté lista, dirígete a ~mission(Location|Address) y acaba con los enemigos de allí. Estos desgraciados son bastante listos, así que tienden a dividirse en grupos más pequeños. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
+        <v xml:space="preserve"> Bien, esto podría ser un poco complicado de hacer solo, así que si tienes algún favor que pedir, sería bueno cobrarlo ahora. Hay un grupo de forajidos atacando naves de reparto en este sector y nos han encargado eliminarlos. Cuando tu tripulación esté lista, dirígete a ~mission(Location|Address) y acaba con los enemigos de allí. Estos desgraciados son bastante listos, así que tienden a dividirse en grupos más pequeños. Asegúrate de esperar para eliminarlos a todos. Buena suerte, Marcus Clenn, Foxwell Enforcement. Foxwell Enforcement es una empresa de seguridad especializada, con licencia para operar en toda la UEE. Siempre estamos buscando nuevos operadores para unirse a nuestra familia. Si tú o alguien que conoces está interesado, ponte en contacto con uno de nuestros representantes de contratos.</v>
       </c>
     </row>
     <row r="438">
@@ -2722,9 +2722,9 @@
         <v> Una pequeña represalia</v>
       </c>
     </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v/>
+    <row r="465" xml:space="preserve">
+      <c r="A465" t="str" xml:space="preserve">
+        <v xml:space="preserve">Me han llegado rumores de que la seguridad de CFP se ha vuelto un poco más agresiva y ha empezado a desalojar a la gente de las casas que construyeron con los restos del sistema. Quieren venganza, así que vinieron a nosotros. Dirígete a ~mission(Location|Address) y acaba con la CFP de allí. Debería ser bastante fácil y te saldrá bien. ¡Que te escondan!</v>
       </c>
     </row>
     <row r="466">
@@ -2732,9 +2732,9 @@
         <v> Eliminando algo de basura XenoThreat</v>
       </c>
     </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v/>
+    <row r="467" xml:space="preserve">
+      <c r="A467" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Acabo de recibir autorización de mi Juez para contraatacar a XenoThreat. He estado observando algunos puntos bajo su control cerca de ~mission(Location|Address). Te daré los objetivos, tú eliminas a todos los que encuentres. ¡Diablos, me encantaría ir yo mismo, suena divertido! -Stows</v>
       </c>
     </row>
     <row r="468">
@@ -2742,9 +2742,9 @@
         <v> Expulsando a CFP</v>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" t="str">
-        <v/>
+    <row r="469" xml:space="preserve">
+      <c r="A469" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hemos intentado llevarnos bien con esta gente de Ciudadanos por la Prosperidad, pero han dejado bien claro que no tenemos cabida en su "sistema seguro". Su uso de mercenarios para la seguridad ha provocado todo tipo de violencia injustificada, como cuando este imbécil ~mission(TargetName) abrió fuego contra un grupo de colonos para ahuyentarlos de un puesto de avanzada que habían estado vigilando. Así que ahora se acabaron los guantes. Necesito gente trabajadora que vaya a ~mission(Location|Address) y elimine a ~mission(TargetName|Last). Lo más probable es que se queden escondidos hasta que demuestres que eres una amenaza suficiente, así que asegúrate de causarles daño. Se esconde.</v>
       </c>
     </row>
     <row r="470">
@@ -2752,9 +2752,9 @@
         <v> Limpiar y despejar algunos lugares frecuentados por CFP</v>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" t="str">
-        <v/>
+    <row r="471" xml:space="preserve">
+      <c r="A471" t="str" xml:space="preserve">
+        <v xml:space="preserve">Recibí noticias de mi Juez de que tenemos que recuperar algunos de los puestos avanzados que CFP ha tomado. Están un poco cabreados porque CFP está afianzándose tanto en el sistema y creen que está haciendo que los Headhunters parezcan débiles. Encontré un par de candidatos cerca de ~mission(Location|Address) que podrían necesitar una revisión. La guinda del pastel es que el jefe de seguridad allí es ~mission(TargetName). No sé si has oído hablar de ellos, pero dispararon a un puñado de Clips el mes pasado, así que es una situación en la que todos ganan. Recuperamos algo de territorio y le damos una paliza a alguien que realmente se lo merece. Se esconde.</v>
       </c>
     </row>
     <row r="472">
@@ -2762,9 +2762,9 @@
         <v> Tomando el territorio de XenoThreat</v>
       </c>
     </row>
-    <row r="473">
-      <c r="A473" t="str">
-        <v/>
+    <row r="473" xml:space="preserve">
+      <c r="A473" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesitamos soldados valientes con gusto por la violencia para atacar algunos escondites de XenoThreat ubicados cerca de ~mission(Location|Address). Te daré los detalles si te interesa, pero tendrás que eliminar dos grupos de escondites distintos. También nos han informado que ~mission(TargetName) está merodeando por ahí. Si eliminas a suficientes XenoThreat, asomarán la cabeza. Cuando lo hagan, dispárales. Se esconden.</v>
       </c>
     </row>
     <row r="474">
@@ -2772,9 +2772,9 @@
         <v> Golpea un complejo CFP</v>
       </c>
     </row>
-    <row r="475">
-      <c r="A475" t="str">
-        <v/>
+    <row r="475" xml:space="preserve">
+      <c r="A475" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tenemos una misión importante. Necesitamos un equipo que se dirija a ~mission(Location|Address). Se rumorea que la CFP está atrincherada en tres grupos distintos de la zona. Nuestro juez quiere que los eliminen a todos. Parece que uno de sus mercenarios, un tipo muy peligroso llamado ~mission(TargetName), está escondido en uno de ellos. Queremos que vayas allí, los elimines a todos y acabes con ~mission(TargetName|Last). De paso, te llevarás una buena paga. ¡Hasta luego!</v>
       </c>
     </row>
     <row r="476">
@@ -2782,9 +2782,9 @@
         <v> Desmantelando un escondite de XenoThreat</v>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="str">
-        <v/>
+    <row r="477" xml:space="preserve">
+      <c r="A477" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos una jugosa misión para cualquier ejecutor importante que quiera un buen botín. En ~mission(Location|Address) tenemos territorio de XenoThreat controlado por un verdadero bastardo llamado ~mission(TargetName). Si llevas el tiempo suficiente en el sistema, probablemente hayas oído hablar de ~mission(TargetName|Last) o al menos hayas visto su trabajo. Skag tiene la costumbre de dejar cadáveres por dondequiera que va. En fin, Judge quiere que limpien esta zona, lo que significa que tienes que atacar los tres grupos y matar a toda la escoria XenoThreat que encuentres. Mata a suficientes y ~mission(TargetName|Last) no podrá esconderse. Acaba con todos y tómate uno por nuestra cuenta. Se esconde.</v>
       </c>
     </row>
     <row r="478">
@@ -2792,9 +2792,9 @@
         <v> Es hora de empezar con CFP</v>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="str">
-        <v/>
+    <row r="479" xml:space="preserve">
+      <c r="A479" t="str" xml:space="preserve">
+        <v xml:space="preserve">Buscamos a alguien con ganas de atacar. Queremos atacar una base en ~mission(Location|Address) y tomarla para nosotros. Pero hay que jugar con inteligencia. Hay varios puestos satélite alrededor del principal y todos tienen seguridad, así que hay que eliminarlos todos antes de tomar la base principal. Pero bueno, si quieres lanzarte de cabeza y repeler todos los refuerzos, allá tú. Lo importante es que lo consigas. ¡Hasta luego!</v>
       </c>
     </row>
     <row r="480">
@@ -2802,19 +2802,19 @@
         <v> ¡A la carga!</v>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="str">
-        <v/>
+    <row r="481" xml:space="preserve">
+      <c r="A481" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Buscamos sicarios para darles una buena paliza a unos imbéciles locales que se han estado aprovechando del sistema para atacar a los Headhunters. Intentamos explicarles su error, pero mataron a nuestro mensajero, así que ahora optamos por la opción B. Los encontrarás escondidos cerca de ~mission(Location|Address). Ve allí y pinta las paredes con su sangre. ¡Que te diviertas! Stows se despide.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Golpear en el comando XenoThreat</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="str">
-        <v/>
+        <v> Golpear en el comando XenoThreat</v>
+      </c>
+    </row>
+    <row r="483" xml:space="preserve">
+      <c r="A483" t="str" xml:space="preserve">
+        <v xml:space="preserve">Estos cabrones de XenoThreat son como aloprats. Cada vez que crees que los has eliminado, vuelven a aparecer. Parece que han vuelto a las andadas y están tramando algo grande. Ni idea de qué, pero nos han dado permiso para detenerlo antes de que empiece. Se supone que un grupo de XenoThreat se reúne en ~mission(Location|Address) para planear, desahogarse o lo que sea que hagan, pero vamos a acabar con ellos. O tú. Ve allí y acaba con todos los que encuentres. Seguro que los grandes se unirán a la pelea. Siempre lo hacen. Esto va a ser duro. Por mucho que odie a XenoThreat, son buenísimos en combate, así que ten cuidado y trae ayuda si puedes. Stows se despide.</v>
       </c>
     </row>
     <row r="484">
@@ -2824,7 +2824,7 @@
     </row>
     <row r="485" xml:space="preserve">
       <c r="A485" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Algún imbécil está intentando desenterrar trapos sucios de los Headhunters. Se desplegaron algunos centinelas orbitales en ~mission(location|address) para espiarnos. También hemos visto una nave vigilándolos. Una propuesta sencilla para ti: ve a eliminar a los centinelas y te pagaremos por ello. ¿Te interesa? En cuanto a la nave, puedes hacer lo que quieras con ella, pero si te detecta, no te sorprendas si intenta buscar refuerzos. Así son estas cosas. Se esconde.</v>
+        <v xml:space="preserve">Algún imbécil está intentando desenterrar trapos sucios de los Headhunters. Se desplegaron algunos centinelas orbitales en ~mission(location|address) para espiarnos. También hemos visto una nave vigilándolos. Una propuesta sencilla para ti: ve a eliminar a los centinelas y te pagaremos por ello. ¿Te interesa? En cuanto a la nave, puedes hacer lo que quieras con ella, pero si te detecta, no te sorprendas si intenta buscar refuerzos. Así son estas cosas. Se esconde.</v>
       </c>
     </row>
     <row r="486">
@@ -2862,9 +2862,9 @@
         <v> Recuperemos Carvers Ridge</v>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="str">
-        <v/>
+    <row r="493" xml:space="preserve">
+      <c r="A493" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Juro que todos los maleantes locales se han vuelto mucho más osados desde que Ciudadanos por la Prosperidad se instaló aquí. Ahora tenemos un grupo atacando ~misión(Ubicación|Dirección), así que necesito que alguien la recupere y les recuerde que los Cazadores de Cabezas siguen teniendo el poder en el sistema. Si los eliminas, no tengo que averiguar quiénes son, así que ponte manos a la obra. Me despido.</v>
       </c>
     </row>
     <row r="494">
@@ -2872,9 +2872,9 @@
         <v> Concentración en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="str">
-        <v/>
+    <row r="495" xml:space="preserve">
+      <c r="A495" t="str" xml:space="preserve">
+        <v xml:space="preserve">Se busca a cualquiera con ganas de armar un poco de revuelo. Unos idiotas creyeron que podían derribar ~mission(Location|Address) y que no nos quedaríamos callados. ¡Vayan y demuéstrenles lo equivocados que estaban! ¡A la carga!</v>
       </c>
     </row>
     <row r="496">
@@ -2882,9 +2882,9 @@
         <v> El centro de la ciudad está bajo ataque.</v>
       </c>
     </row>
-    <row r="497">
-      <c r="A497" t="str">
-        <v/>
+    <row r="497" xml:space="preserve">
+      <c r="A497" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Avisadnos. Tenemos un puesto de avanzada de los Headhunters cerca de ~misión(Ubicación|Dirección) bajo ataque y necesitamos refuerzos. Todavía no sabemos quién ataca, pero no nos importa. Si os acercáis a los Headhunters, preparaos para recibir una paliza. Id allí cuanto antes y acabad con ellos. ¡Fuera!</v>
       </c>
     </row>
     <row r="498">
@@ -2892,9 +2892,9 @@
         <v> No dejes que caiga la caída del viento</v>
       </c>
     </row>
-    <row r="499">
-      <c r="A499" t="str">
-        <v/>
+    <row r="499" xml:space="preserve">
+      <c r="A499" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesitamos algunos detonantes para llegar a ~misión(Ubicación|Dirección) y defender uno de nuestros lugares que está siendo atacado. No estoy seguro de quién busca una muerte rápida, pero podemos averiguarlo cuando estén fríos e inmóviles. Trae a alguien si quieres, solo asegúrate de que lo recuperemos. Se esconde.</v>
       </c>
     </row>
     <row r="500">
@@ -2902,9 +2902,9 @@
         <v> Detengamos la expansión de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" t="str">
-        <v/>
+    <row r="501" xml:space="preserve">
+      <c r="A501" t="str" xml:space="preserve">
+        <v xml:space="preserve">No sé qué tan familiarizado estés con lo que está pasando en Pyro, pero actualmente estamos en una guerra territorial infernal con XenoThreat. Últimamente ha sido bastante brutal, y acabo de enterarme de que XenoThreat está a punto de atacar ~mission(Location|Address). El problema es que no puedo reunir suficientes Clips para llegar a tiempo para defenderlo, así que necesito que lo hagas por nosotros. Toma tu equipo, reúne a algunos amigos y llega a la ubicación lo más rápido que puedas. A los Xenos les gusta escalonar la llegada de sus tropas, así que no gastes toda tu munición durante la defensa inicial porque hay muchas posibilidades de que lleguen más. Evita que tomen el control del sitio y te pagaré por las molestias. -Stows fuera</v>
       </c>
     </row>
     <row r="502">
@@ -2912,9 +2912,9 @@
         <v> Se necesitan refuerzos en el puesto de avanzada.</v>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="str">
-        <v/>
+    <row r="503" xml:space="preserve">
+      <c r="A503" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Esos matones de XenoThreat lanzaron un ataque contra ~mission(Location|Address), así que buscamos gente para repelerlos. Salgan y eliminen a todos los XenoThreat que vean. ¡Que se callen!</v>
       </c>
     </row>
     <row r="504">
@@ -2922,9 +2922,9 @@
         <v> Bloquear la expansión de XenoThreat</v>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" t="str">
-        <v/>
+    <row r="505" xml:space="preserve">
+      <c r="A505" t="str" xml:space="preserve">
+        <v xml:space="preserve">XenoThreat está en pie de guerra ahora mismo. Han lanzado ataques simultáneos contra varios emplazamientos de Headhunters y han agotado nuestras fuerzas. Me han dicho que planean asaltar ~mission(Location|Address) próximamente, y no podemos enviar a nadie para defenderlo. Busco a alguien que reúna un equipo, consiga suministros y organice una defensa sólida. Para serte sincero, esto se perfila como una batalla épica. Los xenos están enviando a algunas de sus fuerzas más experimentadas. No puedo decirte mucho más, salvo que probablemente escalonarán la llegada de sus fuerzas, las aniquilarán y te pagarán generosamente. ¿Crees que puedes estar a la altura? -Stows</v>
       </c>
     </row>
     <row r="506">
@@ -2932,9 +2932,9 @@
         <v> Brindar protección en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="str">
-        <v/>
+    <row r="507" xml:space="preserve">
+      <c r="A507" t="str" xml:space="preserve">
+        <v xml:space="preserve">Estaba teniendo un día de mierda, y solo empeoró. Nuestros intereses en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; me avisaron de que sus &lt;EM&gt;~mission(Objects)&lt;/EM4&gt; están siendo atacados por unos matones sin nombre que buscan hacerse con el control. Irás allí por mí y protegerás el lugar, incluyendo cualquier &lt;EM4&gt;nave amiga&lt;/EM4&gt; que tenga la mala suerte de quedar atrapada en el fuego cruzado. No creo que poner a estos aspirantes a ser nada del otro mundo sea demasiado difícil para alguien como tú. Además, te daré un incentivo extra: &lt;EM4&gt;~mission(ScripAmount) Council Scrip&lt;/EM4&gt; al contratista principal para mostrarle mi agradecimiento. Se escondo.</v>
       </c>
     </row>
     <row r="508">
@@ -2942,9 +2942,9 @@
         <v> Detén el ataque rival en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="str">
-        <v/>
+    <row r="509" xml:space="preserve">
+      <c r="A509" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hay una pequeña banda que sigue siendo una espina clavada en nuestro costado, y esos desgraciados acaban de emboscar a unos amigos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Parece que están haciendo todo lo posible por destruir los &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; que hay allí. Necesito que tú y cualquier &lt;EM4&gt;tripulación que puedas reunir&lt;/EM4&gt; estén allí para detener a estos desgraciados antes de que lo hagan volar todo por los aires y proteger cualquier &lt;EM4&gt;nave amiga&lt;/EM4&gt; que necesite ayuda. Si lo solucionas bien, le daré al contratista principal &lt;EM4&gt;~mission(ScripAmount) Council Scrip&lt;/EM4&gt;. - Stows</v>
       </c>
     </row>
     <row r="510">
@@ -2952,9 +2952,9 @@
         <v> Asegurar la misión (ubicación) de los advenedizos</v>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="str">
-        <v/>
+    <row r="511" xml:space="preserve">
+      <c r="A511" t="str" xml:space="preserve">
+        <v xml:space="preserve">Una nueva banda que está resultando ser una verdadera molestia para los Headhunters acaba de subir la apuesta atacando &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt; en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Nunca es buena señal, ya que nos interesa el bienestar de la gente de allí, pero aún más porque si causan demasiado daño, podrían arruinar por completo una operación próxima. Dirígete allí tan pronto como puedas y detén el ataque antes de que causen daños permanentes. Y si alguna &lt;EM4&gt;nave amiga&lt;/EM4&gt; necesita ayuda, también quiero que estés pendiente de ella. No esperes que esta banda sea fácil de vencer, pero deberías poder lidiar con ellos si mantienes la cabeza fría. Si necesitas motivación adicional, estoy añadiendo &lt;EM4&gt;~mission(ScripAmount) Council Scrip&lt;/EM4&gt; para el contratista principal. - Stows</v>
       </c>
     </row>
     <row r="512">
@@ -2962,19 +2962,19 @@
         <v> Guardia ~misión(Ubicación) De Rivales</v>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="str">
-        <v/>
+    <row r="513" xml:space="preserve">
+      <c r="A513" t="str" xml:space="preserve">
+        <v xml:space="preserve">El mantenimiento y el funcionamiento fiable de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; son de vital importancia para los Headhunters, pero esta tripulación rival parece decidida a eliminarlo. Ya están en el lugar, apuntando a &lt;EM4&gt;~mission(Objects)&lt;/EM4&gt;. Proteger el sitio y cualquier &lt;EM4&gt;nave amiga&lt;/EM4&gt; en la zona es tan importante que quiero que traigas refuerzos &lt;EM4&gt;confiables&lt;/EM4&gt; cuando vayas a eliminar a estos cerebros nulos. Para demostrar lo en serio que nos tomamos esto, el contratista principal ganará &lt;EM4&gt;~mission(ScripAmount) Scrip del Consejo&lt;/EM4&gt; por asegurarse de que no haya absolutamente ningún problema. - Stow</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Mantén ~misión(ubicación) a salvo</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="str">
-        <v/>
+        <v> Mantén ~misión(ubicación) a salvo</v>
+      </c>
+    </row>
+    <row r="515" xml:space="preserve">
+      <c r="A515" t="str" xml:space="preserve">
+        <v xml:space="preserve">No te aburriré con los detalles, pero créeme cuando te digo que &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; es importante para los Headhunters. Así que imagina lo cabreado que estoy al enterarme de que están siendo acosados por unos advenedizos agresivos empeñados en acabar con sus &lt;EM&gt;~mission(Objects)&lt;/EM4&gt;. No lo voy a permitir. Llega allí y proporciona protección antes de que todo sea destruido, incluyendo &lt;EM4&gt;naves amigas&lt;/EM4&gt; en la zona. Esperemos que esos cerebros nulos no supongan un gran desafío para una estrella en ascenso como tú. Acaba con todos. Le daré &lt;EM4&gt;~mission(ScripAmount) Council Scrip&lt;/EM4&gt; a quien acepte este trabajo. - Stows</v>
       </c>
     </row>
     <row r="516">
@@ -2982,9 +2982,9 @@
         <v> Defender ~misión(Ubicación) de los mercenarios</v>
       </c>
     </row>
-    <row r="517">
-      <c r="A517" t="str">
-        <v/>
+    <row r="517" xml:space="preserve">
+      <c r="A517" t="str" xml:space="preserve">
+        <v xml:space="preserve">Así que pensé que habíamos hecho un buen trabajo manteniendo las cosas en secreto, pero parece que se ha filtrado que &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; tiene vínculos con los Headhunters. Ahora hay algunos operadores pesados causando grandes problemas allí, apuntando a &lt;EM&gt;~mission(Objects)&lt;/EM4&gt; y, en general, causándome un gran dolor de cabeza. Con la cantidad de potencia de fuego que tienen estos intrusos, vas a necesitar traer una &lt;EM4&gt;tripulación propia&lt;/EM4&gt; para lograr esto. Especialmente porque necesito que protejas cualquier &lt;EM4&gt;nave amiga&lt;/EM4&gt; que necesite ayuda. Esta operación tiene que salir sin problemas, así que le ofrezco al contratista principal &lt;EM4&gt;~mission(ScripAmount) Council Scrip&lt;/EM4&gt; por un trabajo bien hecho. Se guarda.</v>
       </c>
     </row>
     <row r="518">
@@ -2992,9 +2992,9 @@
         <v> Necesitamos un bateador</v>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" t="str">
-        <v/>
+    <row r="519" xml:space="preserve">
+      <c r="A519" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bueno, aquí está el trato: tenemos a unos tipos insignificantes que se creen la gran cosa, huyendo de una base cerca de ~mission(Location|Address). No sé qué porquería tóxica se beben, pero pensaron que sería buena idea enfrentarse a unos Headhunter Clips. Maté a uno e hirí a tres más. Así que busco a alguien que vaya allí para volarles la ambición de raíz. Ve y encárgate. Te darán un buen subidón de créditos. - Stows</v>
       </c>
     </row>
     <row r="520">
@@ -3012,9 +3012,9 @@
         <v> Visitar un sitio CFP</v>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" t="str">
-        <v/>
+    <row r="523" xml:space="preserve">
+      <c r="A523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesito a alguien que haga una limpieza en ~misión(Ubicación|Dirección). Las fuerzas de seguridad de CFP se apoderaron del puesto de avanzada de un grupo de lugareños que llevaban años allí. Por lo que oí, les dieron una paliza, así que vinieron a Headhunters pidiendo venganza. Necesito que se haga rápido y sin problemas. Se esconde.</v>
       </c>
     </row>
     <row r="524">
@@ -3022,9 +3022,9 @@
         <v> Buscando un poco de venganza</v>
       </c>
     </row>
-    <row r="525">
-      <c r="A525" t="str">
-        <v/>
+    <row r="525" xml:space="preserve">
+      <c r="A525" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Aquí está el trato. Algunos de esos mercenarios que CFP contrató como seguridad dispararon contra unos Headhunters que simplemente estaban de paso por el sistema. Ni siquiera estaban haciendo nada, solo volando. En fin, los rastreamos hasta ~mission(Location|Address) y queremos vengarnos. Prepara tu equipo y conviértete en nuestra arma, te lo haremos merecer. - Stows</v>
       </c>
     </row>
     <row r="526">
@@ -3032,9 +3032,9 @@
         <v> Eliminar ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="str">
-        <v/>
+    <row r="527" xml:space="preserve">
+      <c r="A527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nos enteramos de que un grupo de secuestradores de naves se esconde cerca de ~mission(Location|Address). Se llevaron un par de naves Headhunter hace unos meses tras arrojar a la tripulación por la esclusa, así que los hemos estado vigilando desde entonces. Queremos que vayas allí y les muestres la misma misericordia que ellos mostraron a nuestra gente. ¿Entendido? Me escondo.</v>
       </c>
     </row>
     <row r="528">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="529" xml:space="preserve">
       <c r="A529" t="str" xml:space="preserve">
-        <v xml:space="preserve">Unos cretinos se niegan a pagarnos lo que nos deben. El problema es que estos idiotas se jactan de ello. Si se hubieran callado, podríamos haber resuelto esto de forma más eficaz, pero ahora tenemos que dar un escarmiento. Estos imbéciles operan desde ~mission(Location|Address). Necesitamos que se vayan todos. ¡Que se oiga bien alto! Enviaremos el pago una vez que nos hayamos encargado de todos. - Se despide.</v>
+        <v xml:space="preserve"> Unos cretinos se niegan a pagarnos lo que nos deben. El problema es que estos idiotas se jactan de ello. Si se hubieran callado, podríamos haber resuelto esto de forma más eficaz, pero ahora tenemos que dar un escarmiento. Estos imbéciles operan desde ~mission(Location|Address). Necesitamos que se vayan todos. ¡Que se oiga bien alto! Enviaremos el pago una vez que nos hayamos encargado de todos. - Se despide.</v>
       </c>
     </row>
     <row r="530">
@@ -3052,9 +3052,9 @@
         <v> Muerte y carga</v>
       </c>
     </row>
-    <row r="531">
-      <c r="A531" t="str">
-        <v/>
+    <row r="531" xml:space="preserve">
+      <c r="A531" t="str" xml:space="preserve">
+        <v xml:space="preserve">Una banda local decidió atacar uno de nuestros convoyes y robarnos nuestras cosas. Se escaparon, pero no vamos a dejar que celebren por mucho tiempo. Quiero que vayas a ~mission(Location|Address), donde tienen una base, los hagas volar por los aires y recuperes nuestras cosas. Una vez que tengas la carga, llévala a ~mission(Destination|Address) y podremos olvidarnos de que estos imbéciles alguna vez existieron. ¡No te metas!</v>
       </c>
     </row>
     <row r="532">
@@ -3062,9 +3062,9 @@
         <v> Una tarea muy complicada</v>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" t="str">
-        <v/>
+    <row r="533" xml:space="preserve">
+      <c r="A533" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de los jueces locales ha estado intentando obtener información sobre algunas de las nuevas bandas de la zona. Ya sabes, ver si alguien tiene información sobre lo que tenemos. Ese tipo de cosas. En fin, enviamos a ~mission(TargetName) de incógnito para intentar averiguar si alguien está pensando en actuar. En fin, ~mission(TargetName|First) se dirigía a ~mission(Location|Address) para hacer un trato con unos matones locales o algo así, pero no hemos tenido noticias suyas. El juez teme que ~mission(TargetName|Last) haya sido descubierto y asesinado, así que queremos que vayas allí y veas qué pasa. Ve a averiguar qué le pasó a ~mission(TargetName|Last) y recupera nuestra carga. Lo más probable es que tengas que acabar con cualquiera que te encuentres porque si ~mission(TargetName|Last) está muerto, esos cabrones mataron a un Headhunter. Una vez que tengas la carga, déjala en ~mission(Destination|Address) y obtén una buena paga. Se esconde.</v>
       </c>
     </row>
     <row r="534">
@@ -3072,9 +3072,9 @@
         <v> Golpea a XenoThreat en ~mission(Location)</v>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="str">
-        <v/>
+    <row r="535" xml:space="preserve">
+      <c r="A535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de los nuestros se topó con un grupo de XenoThreat escondido cerca de ~mission(Location|Address). No sabemos si están atrincherados o de paso, pero queremos atacarlos antes de que se muevan. Si tienes gente, trae a alguien, porque los XenoThreat no suelen ser fáciles de derrotar. Llega allí y recuérdales quién manda en este sistema. ¡Que se vayan!</v>
       </c>
     </row>
     <row r="536">
@@ -3082,9 +3082,9 @@
         <v> Guerra territorial</v>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="str">
-        <v/>
+    <row r="537" xml:space="preserve">
+      <c r="A537" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Uno de nuestros jueces se enteró de que XenoThreat está intentando invadir nuestro territorio. Parece que están intentando tomar el control de ~mission(Location|Address). No queremos que esos psicópatas se afiancen más en el sistema de lo que ya lo hacen, así que estamos poniendo en juego algunos créditos para que se retiren. Queremos que actúes con contundencia contra ellos. No ceses hasta que todo el lugar sea un cementerio. Te enviaremos el pago cuando los cuerpos estén listos para ser enterrados. - Se despide.</v>
       </c>
     </row>
     <row r="538">
@@ -3092,9 +3092,9 @@
         <v> Luz verde en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="str">
-        <v/>
+    <row r="539" xml:space="preserve">
+      <c r="A539" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lamentablemente, perdimos uno de nuestros puestos avanzados a manos de XenoThreat. Es terrible, la verdad, pero por eso buscamos a alguien con el tiempo y la munición necesarios para recuperarlo. Si eres tú, dirígete a ~mission(Location|Address) y recupéralo. ¡No te lo pierdas!</v>
       </c>
     </row>
     <row r="540">
@@ -3102,9 +3102,9 @@
         <v> Se necesita una muerte en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="str">
-        <v/>
+    <row r="541" xml:space="preserve">
+      <c r="A541" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesito que alguien se encargue de ellos. Están escondidos cerca de ~mission(Location|Address). No sé si te importa quiénes son, pero se llaman ~mission(TargetName). No hay mucho que contar, un matón local que mató a alguien que estaba relacionado con ellos. Han estado huyendo, así que estarán nerviosos. Yo me acercaría con precaución. Se esconden.</v>
       </c>
     </row>
     <row r="542">
@@ -3112,9 +3112,9 @@
         <v> Impacto en el espacio profundo</v>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="str">
-        <v/>
+    <row r="543" xml:space="preserve">
+      <c r="A543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nos enteramos de que hay una banda que ha estado haciendo trabajos y ganándose una reputación. Como han dicho que no quieren tener nada que ver con Headhunters, queremos desmantelarlos antes de que se conviertan en un problema. Su líder es un mocoso llamado ~mission(TargetName) y creemos que si les disparan, el resto se dispersará. Nos han dicho que puedes encontrar a ~mission(TargetName|Last) cerca de ~mission(Location|Address). Ve allí y encárgate de ellos. No deberían suponer un gran problema para un profesional como tú. Se esconde.</v>
       </c>
     </row>
     <row r="544">
@@ -3122,9 +3122,9 @@
         <v> Necesitas un bisturí en Carver's</v>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="str">
-        <v/>
+    <row r="545" xml:space="preserve">
+      <c r="A545" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hay gente en ~mission(Location|Address) resistiendo el ataque de una amenaza alienígena. Es una faena, claro, pero resulta que es una oportunidad para vengarse. Esos imbéciles alienígenas están liderados por ~mission(TargetName), que lleva semanas en la lista negra de mi jefe. Te necesito para que vayas allí y acabes con ellos. ¡Hasta luego!</v>
       </c>
     </row>
     <row r="546">
@@ -3132,9 +3132,9 @@
         <v> Disparado en medio del caos</v>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="str">
-        <v/>
+    <row r="547" xml:space="preserve">
+      <c r="A547" t="str" xml:space="preserve">
+        <v xml:space="preserve">Mi jefe busca un sicario disponible. Los cazarrecompensas quieren retomar ~mission(Location|Address). Los mercenarios de la CFP se han atrincherado allí para una larga batalla. Mira, no queremos matar a nadie que no sea necesario, así que estamos considerando otras opciones. La seguridad está a cargo de ~mission(TargetName) y mi juez cree que si los eliminan, el resto se dispersará. Un poco de sangre es mejor que mucha, ¿no? -Stows</v>
       </c>
     </row>
     <row r="548">
@@ -3142,9 +3142,9 @@
         <v> Objetivo pagado en CFP</v>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="str">
-        <v/>
+    <row r="549" xml:space="preserve">
+      <c r="A549" t="str" xml:space="preserve">
+        <v xml:space="preserve">Los Headhunters están lanzando un ataque cerca de ~mission(Location|Address). Este imbécil exmarine llamado ~mission(TargetName) ha estado enviando a sus mercenarios a desalojar los campamentos cercanos si no entregan sus armas. Si bien toda la seguridad ha recibido luz verde, ~mission(TargetName|Last) ha sido el objetivo. En su último ataque, mataron a golpes a un okupa por responderles. Resulta que ese okupa era primo de uno de nuestros Clips, así que están pagando extra para asegurarse de que se haga justicia. Pero ten cuidado, ~mission(TargetName|Last) puede ser un canalla que se lo merece; sigue siendo un exmilitar, así que no será fácil acabar con él. -Stows</v>
       </c>
     </row>
     <row r="550">
@@ -3152,9 +3152,9 @@
         <v> Necesito que me quiten el CFP</v>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="str">
-        <v/>
+    <row r="551" xml:space="preserve">
+      <c r="A551" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesitas un detonante disponible para eliminar a un objetivo en un puesto avanzado de CFP. Es un tipo realmente peligroso llamado ~mission(NombreDelObjetivo). Un mercenario de la vieja escuela, cruel y despiadado. He oído que está en ~mission(Ubicación|Dirección). Pásate y elimínalo. Intenta no causarle demasiado daño. Él es el objetivo, nadie más. Se esconde.</v>
       </c>
     </row>
     <row r="552">
@@ -3162,9 +3162,9 @@
         <v> Tapón a un traidor</v>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="str">
-        <v/>
+    <row r="553" xml:space="preserve">
+      <c r="A553" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Esta mierda me entristece. No sé si alguna vez te has cruzado con ~mission(TargetName) en tus tratos con nosotros. Pensé que era uno muy bueno. Lleva años con los Headhunters, pero algo debió pasar porque corrió a CFP en busca de protección. Vendió a algunos de nuestros hermanos y hermanas en el camino. Todos los Jueces están furiosos y quieren sangre. Ahí es donde entras tú. Ve a ~mission(Location|Address), encuentra a ~mission(TargetName|Last) y mátalo. No tiene que ser nada sofisticado. Solo quiero el resultado. Maldita sea. Esconderse.</v>
       </c>
     </row>
     <row r="554">
@@ -3172,9 +3172,9 @@
         <v> Matad al rey</v>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="str">
-        <v/>
+    <row r="555" xml:space="preserve">
+      <c r="A555" t="str" xml:space="preserve">
+        <v xml:space="preserve">Buscamos sicarios disponibles para un trabajo rápido. En ~mission(Location|Address), están siendo atacados por unos genios liderados por ~mission(TargetName). Ya nos hemos enfrentado a ~mission(TargetName|Last) en el pasado, así que no es de extrañar que no hayan aprendido la lección. Queremos que vayas allí y los elimines. Mata a quien quieras, pero ~mission(TargetName|Last) debe ser tu objetivo. ¡Que se vayan!</v>
       </c>
     </row>
     <row r="556">
@@ -3182,9 +3182,9 @@
         <v> Necesito que saquen a alguien.</v>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="str">
-        <v/>
+    <row r="557" xml:space="preserve">
+      <c r="A557" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tenemos un grupo que últimamente ha estado atacando naves de Headhunters. Su líder es un tipo muy peligroso llamado ~mission(TargetName). Los hemos localizado en ~mission(Location|Address), así que buscamos a alguien que los elimine de una vez por todas. A este grupo le gusta pelear, pero no debería ser un problema para alguien como tú. Ve allí y encárgate. ¡No te metas!</v>
       </c>
     </row>
     <row r="558">
@@ -3192,9 +3192,9 @@
         <v> Luz verde en ~misión(NombreObjetivo|Apellido)</v>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="str">
-        <v/>
+    <row r="559" xml:space="preserve">
+      <c r="A559" t="str" xml:space="preserve">
+        <v xml:space="preserve">Me han llegado noticias de mis jefes de que estamos saldando viejas cuentas. Tengo una línea directa con un sicario veterano llamado ~mission(TargetName), que tiene una larga lista de víctimas. Nos enteramos de que se escondía con unos tipos en ~mission(Location|Address), que no son precisamente nuestros favoritos, así que probablemente no te reciban con los brazos abiertos. ~mission(TargetName|Last) es el objetivo, pero puede que tengas que enfrentarte a ellos. Repito, cada vez que hemos intentado eliminar a ~mission(TargetName|Last), han matado a su asesino. Creo que te irá mejor, pero si tienes refuerzos, tráelos contigo. Buena suerte. -Stows</v>
       </c>
     </row>
     <row r="560">
@@ -3202,9 +3202,9 @@
         <v> Necesitas un éxito en la Riviera</v>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="str">
-        <v/>
+    <row r="561" xml:space="preserve">
+      <c r="A561" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos una situación en ~mission(Location|Address). Uno de nuestros puestos avanzados está siendo atacado por XenoThreat. Aunque es una lástima, nos brinda una oportunidad interesante. El ataque está siendo liderado por ~mission(TargetName), quien lleva tiempo en la lista negra de los Headhunters. Queremos que vayas allí y lo elimines. Puedes matar a cualquier otro XenoThreat que quieras, pero ~mission(TargetName|Last) es el objetivo. Mucha gente lo ha intentado antes, así que definitivamente no será fácil. Incluso te recomiendo que traigas a algunos amigos, lo que sea necesario para acabar finalmente con ~mission(TargetName|Last). Stows out.</v>
       </c>
     </row>
     <row r="562">
@@ -3212,19 +3212,19 @@
         <v> Golpe a XenoThreat en el Yard</v>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="str">
-        <v/>
+    <row r="563" xml:space="preserve">
+      <c r="A563" t="str" xml:space="preserve">
+        <v xml:space="preserve">No sé si lo sabías, pero ~mission(Location|Address) está siendo atacada por XenoThreat. La situación es grave, pero está bajo control. El problema es que los atacantes están liderados por un tipo despreciable llamado ~mission(TargetName). Ya nos hemos enfrentado a ~mission(TargetName|Last) antes y siempre se escapan antes de que podamos eliminarlos. Eso va a cambiar. Queremos que vayas allí y elimines a ~mission(TargetName|Last) antes de que se escapen de esta trampa. ¡Que se vayan!</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v xml:space="preserve">Listos para la retribución</v>
+        <v xml:space="preserve"> Listos para la retribución</v>
       </c>
     </row>
     <row r="565" xml:space="preserve">
       <c r="A565" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Me acaba de caer información interesante. Parece que el infame líder de XenoThreat, ~mission(TargetName), está escondido en ~mission(location|address) trabajando en una gran operación para ellos. Oportunidad perfecta para acabar con ese cabrón de una vez por todas. El problema es que los Xenos están vigilando todas las operaciones de Headhunter en este momento. No hay forma de que podamos movilizar y desplegar un equipo sin que ~mission(TargetName|Last) se entere. Así que te ofrezco la oportunidad de mejorar Pyro y ganar algo de crédito al mismo tiempo. Si te interesa, te sugiero que te equipes y busques refuerzos antes de salir. Solo te pagarán si eliminas a ~mission(TargetName|Last), pero no dudes en matar a cualquier otro XenoThug que pueda estar escondido allí con ellos. ¡Que se vayan!</v>
+        <v xml:space="preserve">Me acaba de caer información interesante. Parece que el infame líder de XenoThreat, ~mission(TargetName), está escondido en ~mission(location|address) trabajando en una gran operación para ellos. Oportunidad perfecta para acabar con ese cabrón de una vez por todas. El problema es que los Xenos están vigilando todas las operaciones de Headhunter en este momento. No hay forma de que podamos movilizar y desplegar un equipo sin que ~mission(TargetName|Last) se entere. Así que te ofrezco la oportunidad de mejorar Pyro y ganar algo de crédito al mismo tiempo. Si te interesa, te sugiero que te equipes y busques refuerzos antes de salir. Solo te pagarán si eliminas a ~mission(TargetName|Last), pero no dudes en matar a cualquier otro XenoThug que pueda estar escondido allí con ellos. ¡Que se vayan!</v>
       </c>
     </row>
     <row r="566">
@@ -3232,9 +3232,9 @@
         <v> Cabeza de la serpiente</v>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="str">
-        <v/>
+    <row r="567" xml:space="preserve">
+      <c r="A567" t="str" xml:space="preserve">
+        <v xml:space="preserve">Me enfrenté a unos canallas de XenoThreat en ~mission(Location|Address) y descubrí que ~mission(TargetName) los está liderando. Se lo comenté a mi Jueza y se emocionó al pensar en la oportunidad de acabar con este imbécil, así que queremos que vayas allí y te asegures de que no escapen de este ataque. Se esconde.</v>
       </c>
     </row>
     <row r="568">
@@ -3242,9 +3242,9 @@
         <v> El teniente de XenoThreat necesita que lo maten.</v>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="str">
-        <v/>
+    <row r="569" xml:space="preserve">
+      <c r="A569" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Los Headhunters acaban de reunir un equipo para atacar ~mission(Location|Address) y eliminar a la XenoThreat que hay allí, pero quiero asegurarme aún más. Hay un pez gordo llamado ~mission(TargetName) que está en la cúpula de la XenoThreat y queremos eliminarlo. Cualquier otro que mates es un extra, pero él es tu objetivo principal. -Stows</v>
       </c>
     </row>
     <row r="570">
@@ -3252,9 +3252,9 @@
         <v> Lanza una amenaza xeno</v>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="str">
-        <v/>
+    <row r="571" xml:space="preserve">
+      <c r="A571" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos información sobre una amenaza alienígena que nos está dando muchos problemas. No sé si has oído hablar de ella, pero ~mission(TargetName) es un canalla incluso para los estándares de las amenazas alienígenas. Cruel, sádico y un cretino. Queremos que alguien acabe con él. ¿Te apuntas? La última noticia es que estaba cerca de ~mission(Location|Address). Ve allí y elimínalo. Bastante sencillo. Se esconde.</v>
       </c>
     </row>
     <row r="572">
@@ -3262,9 +3262,9 @@
         <v> Se busca: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="str">
-        <v/>
+    <row r="573" xml:space="preserve">
+      <c r="A573" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Aquí está el trato: acabamos de recibir noticias de que un jugador poderoso de XenoThreat llamado ~mission(TargetName) salió de su escondite y fue visto en ~mission(Location|Address). Los Headhunters han estado ansiosos por acabar con este imbécil durante meses, así que lanzamos un asalto contra el puesto avanzado, pero el Juez quiere asegurarse de que ~mission(TargetName|Last) no se escape, así que quieren usarte como garantía. Será una eliminación difícil en medio de una zona de guerra, pero pagaremos si lo logras. ¡Adiós!</v>
       </c>
     </row>
     <row r="574">
@@ -3272,19 +3272,19 @@
         <v> Eliminación de objetivo para una vía rápida en</v>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="str">
-        <v/>
+    <row r="575" xml:space="preserve">
+      <c r="A575" t="str" xml:space="preserve">
+        <v xml:space="preserve">Así que aquí está el trato, los Cazadores de Cabezas buscan ampliar su grupo de talentos y tienen algunas vacantes para cualquiera que tenga agallas. Hay un tipo realmente problemático llamado ~mission(TargetName) que se cree muy listo robando carga de los transportistas que se mueven por el sistema. Solicitamos una parte de sus ganancias como impuesto de licencia para continuar operando. Cuando ~mission(TargetName|Last) respondió, fue muy irrespetuoso. Hemos rastreado su nave hasta ~mission(Location|Address) y necesitamos eliminarlo. Debes saber que está siendo astuto y se mantiene cerca de algunos aliados para no estar solo. Haz esto y te consideraremos para futuros trabajos de Cazador de Cabezas. Se esconde.</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v xml:space="preserve">Objetivo en ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="str">
-        <v/>
+        <v xml:space="preserve"> Objetivo en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="577" xml:space="preserve">
+      <c r="A577" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hay un nido que hay que eliminar cerca de ~mission(Location|Address) que ha sido ocupado por unos intrusos. No nos importan la mayoría, pero nos ha llegado información de que están dando refugio a ~mission(TargetName), que tiene un largo historial de robar el botín de Headhunter. Ha llegado el momento de eliminarlos. Se rumorea que ~mission(TargetName|Last) está en una nave, pero puede que confíe en las defensas de la base para protegerse, así que ten cuidado. Si los matas, te pagan. Ya sabes, lo de siempre. Se esconde.</v>
       </c>
     </row>
     <row r="578">
@@ -3292,9 +3292,9 @@
         <v> Orden de matar</v>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="str">
-        <v/>
+    <row r="579" xml:space="preserve">
+      <c r="A579" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Necesitamos que eliminen otra nave de Ciudadanos por la Prosperidad. Pertenece a ~mission(TargetName), quien ha estado expulsando a los lugareños de sus hogares si no aceptan la ayuda de Ciudadanos por la Prosperidad. Son unos verdaderos sinvergüenzas y nos han dado luz verde para acabar con ellos. Su nave fue avistada cerca de ~mission(Location|Address), así que diríjanse allí y háganlo. Se esconde.</v>
       </c>
     </row>
     <row r="580">
@@ -3302,9 +3302,9 @@
         <v> Choca contra un barco de CFP</v>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="str">
-        <v/>
+    <row r="581" xml:space="preserve">
+      <c r="A581" t="str" xml:space="preserve">
+        <v xml:space="preserve">Las fuerzas de seguridad de CFP han estado atacando a los residentes locales y buscamos restablecer el equilibrio. Nos enteramos de uno en particular llamado ~mission(Nombre del objetivo|Apellido) que ha estado causando daños y necesitamos eliminarlo. Puedes encontrarlo volando por ~mission(Ubicación|Dirección). Preséntate. Se esconde.</v>
       </c>
     </row>
     <row r="582">
@@ -3312,9 +3312,9 @@
         <v> Objetivo Primo</v>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="str">
-        <v/>
+    <row r="583" xml:space="preserve">
+      <c r="A583" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tenemos un objetivo platino que hay que eliminar. ~mission(TargetName) es un pez gordo que es uno de los que se encargan de la seguridad de Ciudadanos por la Prosperidad. Aunque ~mission(TargetName|Last) puede que lo haya olvidado, los Cazadores de Cabezas recuerdan su trabajo con una compañía de mercenarios hace unos años que provocó la muerte de cinco hermanos y hermanas. Queremos sangre por sangre. Se les ha visto merodeando por ~mission(Location|Address), así que deberías poder encontrarlos allí. Son unos cabrones despiadados, así que trae a algunos amigos, pero asegúrate de que acaben muertos. Se esconden.</v>
       </c>
     </row>
     <row r="584">
@@ -3322,9 +3322,9 @@
         <v> Se busca: ~misión(Nombre del objetivo)</v>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="str">
-        <v/>
+    <row r="585" xml:space="preserve">
+      <c r="A585" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tenemos luz verde para eliminar finalmente a ~mission(TargetName). Nos han dado muchos quebraderos de cabeza desde que llegaron al sistema hace unos años y por fin es hora de acabar con ellos de una vez por todas. Nos han informado de que ~mission(TargetName|Last) fue avistado volando cerca de ~mission(Location|Address) y el Juez quiere que esto se resuelva ya. Elimínenlos. - Se esconde.</v>
       </c>
     </row>
     <row r="586">
@@ -3332,9 +3332,9 @@
         <v> Un golpe sencillo</v>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="str">
-        <v/>
+    <row r="587" xml:space="preserve">
+      <c r="A587" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Tenemos otro canalla que necesita su merecido. ~mission(TargetName) es solo un matón de poca monta que parece no aprender. Le advertimos que se una a nosotros o que cambie de sistema, pero no parece hacer caso, así que se nos acabó la paciencia. Dirígete a ~mission(Location|Address) y deberías encontrar a ~mission(TargetName|Last) volando por ahí. Se esconde.</v>
       </c>
     </row>
     <row r="588">
@@ -3342,9 +3342,9 @@
         <v> Regálate una pelea</v>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="str">
-        <v/>
+    <row r="589" xml:space="preserve">
+      <c r="A589" t="str" xml:space="preserve">
+        <v xml:space="preserve">Otra banda intentó atacar y hacerse con territorio. Fracasaron, pero los Cazadores de Cabezas no olvidan. Hemos eliminado a la mayoría, pero uno de los últimos miembros, llamado ~mission(TargetName), ha sido visto volando por ~mission(Location|Address). Probablemente estén desesperados, así que no los subestimes en la lucha. Recibirás tu recompensa cuando termine. Se esconde.</v>
       </c>
     </row>
     <row r="590">
@@ -3352,9 +3352,9 @@
         <v> ¿Quieres ser cazatalentos?</v>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="str">
-        <v/>
+    <row r="591" xml:space="preserve">
+      <c r="A591" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ya nos conoces. Ya sabes lo que hacemos. El sistema se está llenando un poco, así que buscamos buenos soldados para ayudarnos a mantener nuestro lugar aquí. Si estás dispuesto y no te importa ensuciarte las manos, tenemos algo para demostrar que tienes lo que buscamos. ~mission(TargetName) era un antiguo miembro que nos vendió a XenoThreat y provocó la muerte de algunos de sus hermanos y hermanas. Ahora creen que pueden vivir su vida sin consecuencias. Si los eliminas, te ascenderán. Parece un trato justo. Han sido vistos cerca de ~mission(Location|Address), así que ve allí y encárgate de ello. Se esconde.</v>
       </c>
     </row>
     <row r="592">
@@ -3362,9 +3362,9 @@
         <v> Fantasma de XenoTrash</v>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="str">
-        <v/>
+    <row r="593" xml:space="preserve">
+      <c r="A593" t="str" xml:space="preserve">
+        <v xml:space="preserve">Necesito que te muevas rápido en esto. Hay un teniente de XenoThreat llamado ~mission(TargetName) que ha aparecido para tomar aire. Judge cree que esta es una gran oportunidad para interferir con el mando de XenoThreat eliminándolos. Escuché que ~mission(TargetName|Last) fue visto volando cerca de ~mission(Location|Address), así que ve rápido antes de que desaparezca de nuevo. Yo traería refuerzos, dudo que caigan sin luchar. Se esconde.</v>
       </c>
     </row>
     <row r="594">
@@ -3372,9 +3372,9 @@
         <v> Choquen algunos barcos</v>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="str">
-        <v/>
+    <row r="595" xml:space="preserve">
+      <c r="A595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Muchos aspirantes a pandillas se han acercado a los Headhunters a lo largo de los años pensando que podrían entrar por la fuerza en el sistema. Nosotros seguimos aquí. Ellos no. Pero parece que los supervivientes de estos grupos han decidido unirse e intentarlo de nuevo. Supongo que hay gente que nunca aprende. El último grupo atacó a un par de nuestros convoyes mientras realizaban misiones de suministro. No debería sorprender que el Juez quiera acabar con ellos rápidamente. Hemos descubierto que están cerca de ~misión(Ubicación|Dirección) y probablemente se estén rearmando para otro ataque. Queremos que vayas allí y les hagas desear haber muerto con su antigua pandilla.</v>
       </c>
     </row>
     <row r="596">
@@ -3384,7 +3384,7 @@
     </row>
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Nuestros analistas han examinado la información incautada a los equipos de reconocimiento de XenoThreat, pero los datos parecen estar protegidos por un sofisticado sistema de cifrado y requieren una clave criptográfica personalizada para acceder a ellos. Hemos logrado localizar a varios tenientes de XenoThreat que operan en el sistema; su misión es encontrar e interrogar a los sospechosos para determinar si poseen una clave criptográfica que nos permita acceder a la información. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de las Fuerzas de Defensa de Canadá que lleven esta iniciativa hasta el final.</v>
+        <v xml:space="preserve">Nuestros analistas han examinado la información incautada a los equipos de reconocimiento de XenoThreat, pero los datos parecen estar protegidos por un sofisticado sistema de cifrado y requieren una clave criptográfica personalizada para acceder a ellos. Hemos logrado localizar a varios tenientes de XenoThreat que operan en el sistema; su misión es encontrar e interrogar a los sospechosos para determinar si poseen una clave criptográfica que nos permita acceder a la información. Cabe recordar que las fuerzas armadas han donado generosamente algunos F7A Hornet antiguos para los miembros de las Fuerzas de Defensa de Canadá que lleven esta iniciativa hasta el final.</v>
       </c>
     </row>
     <row r="598">
@@ -3452,9 +3452,9 @@
         <v>Trata con los Kopions en ~mission(Location)</v>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="str">
-        <v/>
+    <row r="611" xml:space="preserve">
+      <c r="A611" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Los Headhunters necesitan a alguien que elimine a una manada de kopions que les han estado dando problemas a nuestros chicos. Los vimos por última vez en ~mission(Location|Address). Si terminas el trabajo, te daremos algunos créditos. Se esconde.</v>
       </c>
     </row>
     <row r="612">
@@ -3462,9 +3462,9 @@
         <v> Paquete de Kopion del carnicero en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="str">
-        <v/>
+    <row r="613" xml:space="preserve">
+      <c r="A613" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Un enjambre enorme de kopions atacó uno de nuestros Clips el otro día. Nunca encontramos el cuerpo. Dicen que se comieron al pobre desgraciado. Necesitamos a alguien que vaya a ~mission(Location|Address) y dispare a todos los kopions que vea. No pares hasta que todos esos cabrones estén muertos. Ten cuidado al entrar. Si no lo adivinas, estos desgraciados son malos. Si te matan, es tu responsabilidad. Esconderse.</v>
       </c>
     </row>
     <row r="614">
@@ -3472,9 +3472,9 @@
         <v> Mata a los Kopions en ~mission(Ubicación)</v>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="str">
-        <v/>
+    <row r="615" xml:space="preserve">
+      <c r="A615" t="str" xml:space="preserve">
+        <v xml:space="preserve">Un grupo de kopions se ha instalado en territorio de Headhunter. Son unos tipos duros. Tener que ahuyentar animales salvajes cada pocas horas dificulta el negocio. Si te deshaces de ellos, te pagamos. Hazlo como quieras, siempre y cuando acaben muertos. Puedes encontrarlos en ~mission(Location|Address). -Stows</v>
       </c>
     </row>
     <row r="616">
@@ -3482,9 +3482,9 @@
         <v> Reducir la población de la estación de interruptores de Valakkar</v>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="str">
-        <v/>
+    <row r="617" xml:space="preserve">
+      <c r="A617" t="str" xml:space="preserve">
+        <v xml:space="preserve">Si tiene algún trabajo que le lleve a una de las antiguas estaciones de procesamiento QV en Keeger Belt, tenemos otra oportunidad para que nos ayude durante su estancia. Recientemente, la Alianza Popular se puso en contacto con nosotros para colaborar en una iniciativa que busca preparar estas estaciones abandonadas para su reparación. Desafortunadamente, una plaga de Valakkar está causando graves problemas no solo a la infraestructura de las estaciones, sino también a las posibilidades de que vuelvan a estar operativas algún día. Debido a que el Valakkar es una especie invasora, hemos decidido que su erradicación es la única opción viable. Si reduce la población de Valakkar en cualquiera de las antiguas estaciones de procesamiento QV, le ofreceremos una compensación económica. Atentamente, Wanda Werkheiser, Gerente de Contratos, Highpoint Wilderness Specialists</v>
       </c>
     </row>
     <row r="618">
@@ -3492,9 +3492,9 @@
         <v> Expediente Jorrit: Datos actualizados sobre anomalías energéticas</v>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="str">
-        <v/>
+    <row r="619" xml:space="preserve">
+      <c r="A619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Expediente de la Agencia Hockrow n.° JD10285 Investigador principal: Arken Mallor Actualización del caso: Sería útil contar con los datos más recientes de anomalías energéticas para poder compararlos con los que entregaste la última vez. Cualquier diferencia entre los dos conjuntos de datos podría resultar útil. Acciones del investigador contratado: Explorar el ala de &lt;EM4&gt;Ingeniería&lt;/EM4&gt; y &lt;EM4&gt;recuperar los datos de anomalías energéticas&lt;/EM4&gt; y entregarlos a &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Notas adicionales: Ten cuidado con las posibles fuerzas hostiles en el lugar. Viaja a Onyx en un vehículo que pueda almacenarse en un hangar grande. Una vez que entregues estos datos, te enviaré una &lt;EM4&gt;Unidad segura ASD&lt;/EM4&gt; que podrás recoger en tu domicilio.</v>
       </c>
     </row>
     <row r="620">
@@ -3502,9 +3502,9 @@
         <v> Expediente Jorrit: Datos de seguridad actualizados</v>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="str">
-        <v/>
+    <row r="621" xml:space="preserve">
+      <c r="A621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hockrow Agency Case File #JD10285 Investigador principal: Arken Mallor Actualización del caso: Por precaución, sería bueno comprobar si los sistemas de seguridad han detectado algo nuevo desde el último lote de datos que entregaste. De esa forma, podemos asegurarnos de estar al día de lo que ha estado sucediendo allí abajo. Acciones del investigador contratado: Explora el ala &lt;EM4&gt;Investigación&lt;/EM4&gt; y &lt;EM4&gt;recupera los datos de seguridad&lt;/EM4&gt; y entrégalos en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Notas adicionales: Ten cuidado con posibles fuerzas hostiles en el lugar. Viaja a Onyx en un vehículo que pueda guardarse en un hangar grande. Una vez que entregues estos datos, te enviaré una &lt;EM4&gt;Unidad segura ASD&lt;/EM4&gt; que podrás recoger en tu domicilio.</v>
       </c>
     </row>
     <row r="622">
@@ -3512,9 +3512,9 @@
         <v> Expediente Jorrit: Datos sísmicos actualizados</v>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="str">
-        <v/>
+    <row r="623" xml:space="preserve">
+      <c r="A623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Expediente de la Agencia Hockrow n.° JD10285 Investigador principal: Arken Mallor Actualización del caso: Uno de los mayores problemas en las investigaciones en curso es que la información se vuelve obsoleta. Para ayudar a aliviar eso, te pediré que regreses a Onyx y obtengas los datos más recientes del sensor sísmico. Sería bueno ver qué dicen las últimas lecturas. Acciones del investigador contratado: Explora el ala &lt;EM4&gt;Investigación&lt;/EM4&gt; y &lt;EM4&gt;recupera los datos sísmicos&lt;/EM4&gt; y entrégalos a &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Notas adicionales: Ten cuidado con las posibles fuerzas hostiles en el sitio. Viaja a Onyx en un vehículo que pueda almacenarse en un hangar grande. Una vez que entregues estos datos, te enviaré una &lt;EM4&gt;Unidad segura ASD&lt;/EM4&gt; que puedes recoger en tu ubicación de origen.</v>
       </c>
     </row>
     <row r="624">
@@ -3522,9 +3522,9 @@
         <v> Expediente Jorrit: Datos actualizados sobre el consumo de energía</v>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="str">
-        <v/>
+    <row r="625" xml:space="preserve">
+      <c r="A625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Expediente de la Agencia Hockrow n.° JD10285 Investigador principal: Arken Mallor Actualización del caso: Todavía estoy tratando de recopilar una imagen completa de todo lo que ha estado sucediendo en Onyx y creo que sería útil tener los datos de consumo de energía más recientes. Acciones del investigador contratado: Explora el ala de &lt;EM4&gt;Ingeniería&lt;/EM4&gt; y &lt;EM4&gt;carga los datos de consumo de energía&lt;/EM4&gt;. Si la terminal aún no funciona, es posible que tengas que extraer los datos y entregarlos de nuevo. Notas adicionales: Ten cuidado con posibles fuerzas hostiles en el sitio. Viaja a Onyx en un vehículo que pueda almacenarse en un hangar grande. Una vez que entregues estos datos, te enviaré una &lt;EM4&gt;Unidad segura ASD&lt;/EM4&gt; que puedes recoger en tu ubicación de origen.</v>
       </c>
     </row>
     <row r="626">
@@ -3912,24 +3912,24 @@
         <v>Recuperar cadáveres de Vanduul</v>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v/>
+    <row r="703" xml:space="preserve">
+      <c r="A703" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos presentes y armados Especificaciones del Equipo: &lt;EM4&gt;Nave con Capacidad de Carga&lt;/EM4&gt;, Armas Personales, &lt;EM4&gt;Rayo Tractor de Alta Resistencia&lt;/EM4&gt; Informe: Nuestra última inteligencia muestra que la Hoja Fragmentada ha repuesto su stock de cadáveres Vanduul y pronto los transferirá desde la antigua &lt;EM4&gt;estación logística QV&lt;/EM4&gt; desde la que operan a un comprador interesado. La UEE no puede tener otro incidente como el que ocurrió con ASD, así que están ansiosos por que &lt;EM4&gt;recuperemos las cápsulas criogénicas&lt;/EM4&gt; y las entreguemos en &lt;EM4&gt;el montacargas en ~misión(Destino|Dirección)&lt;/EM4&gt;. Si bien los miembros de la Hoja Fragmentada presentes en el sitio podrían ofrecer resistencia, no son el objetivo de su misión. Ocúpese de ellos según sea necesario y obtenga las cápsulas criogénicas. Atentamente, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación contiene información confidencial destinada exclusivamente al destinatario. Si la recibe por error, ignórela y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la UEE y la normativa del sistema, según corresponda.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v> Recuperar Vanduul Tech</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v/>
+        <v>Recuperar Vanduul Tech</v>
+      </c>
+    </row>
+    <row r="705" xml:space="preserve">
+      <c r="A705" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos presentes y armados Especificaciones del Equipo: Nave de Combate, Armas Personales Informe: Para evitar que la Hoja Fragmentada inunde el mercado negro con contrabando xeno, la UEE ha encargado a InterSec la recuperación de un alijo de Placas y Metal Vanduul de la antigua estación logística QV que la banda ha estado ocupando. Una vez que tenga los materiales en su poder, entréguelos en el montacargas en la dirección ~misión(Destino|Dirección). Según su experiencia previa, no sería sorprendente que la Hoja Fragmentada ofrezca resistencia, pero asegúrese de concentrarse en recuperar los materiales. Atentamente, Deacon Tobin Gerente de Operaciones InterSec Defense Solutions Esta comunicación contiene información confidencial destinada únicamente al destinatario. Ignórela si la recibe por error y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad personal del contratista y deben cumplir con la normativa UEE y la legislación del sistema aplicable.</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v> Patrulla en el sector peligroso</v>
+        <v>Patrulla en el sector peligroso</v>
       </c>
     </row>
     <row r="707" xml:space="preserve">
@@ -3952,14 +3952,14 @@
         <v>Patrulla para prevenir un posible ataque.</v>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v/>
+    <row r="711" xml:space="preserve">
+      <c r="A711" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos Especificaciones del Equipo: Naves con calificación de combate Informe: InterSec ha estado rastreando una mayor actividad de forajidos en ciertos sectores del sistema. Esta actividad, junto con otra inteligencia, nos lleva a creer que los forajidos están planeando un ataque contra elementos que viajan desde la UEE. Nuestro objetivo es patrullar estos sectores e interrumpir cualquier plan antes de que puedan ponerse en marcha. Actualmente, necesitamos a alguien que pueda ayudar a patrullar un sector altamente peligroso. Una vez que hayas aceptado la misión, puedes dirigirte al marcador de ubicación &lt;EM4&gt;&lt;/EM4&gt; en tu HUD. Desde allí, te enviaremos por una ruta específica con puntos de ruta adicionales para escanear. Completa la patrulla y enviaremos al contratista principal una bonificación de &lt;EM4&gt;~misión(Cantidad de Scrip) MG Scrip.&lt;/EM4&gt; Debido a la alta probabilidad de ataque y al nivel general de amenaza de los forajidos locales, recomendamos &lt;EM4&gt;reclutar compañeros de ala de confianza&lt;/EM4&gt; para brindar apoyo en combate. Atentamente, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación constituye una oferta no vinculante que, una vez aceptada, podrá ser rescindida inmediatamente por cualquiera de las partes sin previo aviso. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la normativa vigente, cuando corresponda.</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v> Buque de la Alianza Popular Tranquility</v>
+        <v>Buque de la Alianza Popular Tranquility</v>
       </c>
     </row>
     <row r="713" xml:space="preserve">
@@ -4042,19 +4042,19 @@
         <v> Recuperar información adicional sobre contrabandistas.</v>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="str">
-        <v/>
+    <row r="729" xml:space="preserve">
+      <c r="A729" t="str" xml:space="preserve">
+        <v xml:space="preserve">ESPECIFICACIONES DE LA MISIÓN Área de Operación: Sistema Nyx Fuerzas Hostiles: Forajidos presentes y armados Especificaciones del Equipo: Nave de combate, Armas Personales Informe: InterSec necesita sus servicios una vez más. La información que recopiló anteriormente ha sido invaluable para identificar a varios compradores importantes de las piezas Vanduul obtenidas ilegalmente. Sin embargo, desde entonces, la Hoja Fragmentada ha continuado sus operaciones y la UEE solicita que &lt;EM4&gt;actualicemos nuestra información.&lt;/EM4&gt; Creemos que se puede recuperar más información de las instalaciones de almacenamiento ubicadas en la antigua estación logística &lt;EM4&gt;QV.&lt;/EM4&gt; Los parámetros de la operación no han cambiado desde su última misión: encuentre los &lt;EM4&gt;datos encriptados&lt;/EM4&gt; y use la &lt;EM4&gt;clave de descifrado&lt;/EM4&gt; para descifrar y enviarnos la lista. La Hoja Fragmentada habrá reforzado el área desde la última vez, así que espere resistencia. Buena suerte. Nos pondremos en contacto. Atentamente, Deacon Tobin, Gerente de Operaciones de InterSec Defense Solutions. Esta comunicación contiene información confidencial destinada exclusivamente al destinatario. Si la recibe por error, ignórela y notifique al remitente. Todas las operaciones se realizan bajo la responsabilidad del contratista y deben cumplir con la UEE y la normativa del sistema, según corresponda.</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v> Oportunidad de transporte de carga con Ling Hauling</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="str">
-        <v/>
+        <v>Oportunidad de transporte de carga con Ling Hauling</v>
+      </c>
+    </row>
+    <row r="731" xml:space="preserve">
+      <c r="A731" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, soy Petra Ling y me enorgullece ofrecerles una nueva y emocionante oportunidad para asociarse con Ling Family Hauling. Cuando mis padres fundaron esta empresa, su objetivo era brindar entregas de mensajería rápidas y confiables en el área metropolitana de Crusader. Rápidamente se convirtió en un éxito, y a medida que nuestra reputación crecía, también lo hacían nuestras operaciones. Ahora, bajo mi dirección, Ling Family Hauling está dando el siguiente gran paso: el transporte de carga. La demanda de este nuevo servicio está creciendo más rápido de lo que esperaba, y eso es una gran noticia para ambos. Si alguna vez has querido ser transportista, puedo hacer tus sueños realidad. La mejor manera de aprender algo es haciéndolo, y tengo un envío de &lt;EM4&gt;~mission(Item)&lt;/EM4&gt; que necesita ir de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. No se requiere experiencia previa, pero aquí hay algunas cosas que debes tener en cuenta. Todas las recogidas y entregas deben hacerse en un montacargas o cargarse automáticamente. Necesitará un barco que pueda contener &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt;, y un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; para moverlos. Al completar con éxito esta entrega, ascenderá a la categoría de "contratista de confianza" y tendrá acceso a más transportes. Atentamente, Petra Ling Directora General de Operaciones de Carga Ling Family Hauling Ling Family Hauling sabe que es un universo peligroso e impredecible y ha establecido varios protocolos para proteger tanto a usted como la carga de nuestro cliente. Para garantizar que no sea penalizado por circunstancias ajenas a su control, el pago total se prorrateará según el porcentaje de carga entregada con éxito. Se establecerá un temporizador de entrega para cada transporte. Cualquier carga que permanezca sin entregar al expirar el plazo se marcará como robada y se tratará como tal. Todas las recogidas y entregas deben cargarse automáticamente o hacerse en un montacargas.</v>
       </c>
     </row>
     <row r="732">
@@ -4892,9 +4892,9 @@
         <v> Recursos adicionales para la investigación</v>
       </c>
     </row>
-    <row r="899">
-      <c r="A899" t="str">
-        <v/>
+    <row r="899" xml:space="preserve">
+      <c r="A899" t="str" xml:space="preserve">
+        <v xml:space="preserve"> todos los contratistas disponibles: los científicos de Rayari están trabajando arduamente para resolver los problemas con la tecnología de regeneración defectuosa. Actualmente, sus esfuerzos se ven obstaculizados por la falta de materiales que consideran esenciales para sus experimentos. En particular, nuestros científicos en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; han tenido que suspender su trabajo tras agotar dichos recursos. Dado que no será posible obtener un reabastecimiento de nuestro proveedor habitual durante meses debido a la escasez, pagaremos una prima a quien pueda ayudarnos a reabastecer los materiales. Para obtener más información sobre los animales en cuestión, consulte la "Guía del explorador para animales cosechables" en su Diario. Juntos podemos mejorar el universo para todos. Narina Lerrem, Gerente Sénior de Subcontratación de Investigación Clínica.</v>
       </c>
     </row>
     <row r="900">
@@ -4902,24 +4902,24 @@
         <v> Recursos vitales necesarios para la investigación</v>
       </c>
     </row>
-    <row r="901">
-      <c r="A901" t="str">
-        <v/>
+    <row r="901" xml:space="preserve">
+      <c r="A901" t="str" xml:space="preserve">
+        <v xml:space="preserve"> todos los contratistas disponibles: los científicos de Rayari están trabajando arduamente para resolver los problemas con la tecnología de regeneración defectuosa. Actualmente, sus esfuerzos se ven obstaculizados por la falta de tres recursos esenciales para sus experimentos: &lt;EM4&gt;saldynium, jaclium y carinite&lt;/EM4&gt;. En particular, nuestros científicos en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; han tenido que suspender su trabajo tras agotar estos recursos. Dado que no será posible obtener un reabastecimiento de nuestro proveedor habitual durante meses debido a la escasez, pagaremos una prima a quien pueda ayudarnos a reabastecer los materiales. Aunque no hemos podido realizar escaneos exhaustivos, nuestros equipos creen firmemente que las Plataformas Láser Orbitales (OLP) inactivas de Hathor se construyeron sobre áreas con una alta concentración de estos recursos. Reactivar estas OLP podría ser su mejor opción para obtener lo que necesitamos. Juntos podemos mejorar el universo para todos. Narina Lerrem, Gerente Sénior de Subcontratación de Investigación Clínica.</v>
       </c>
     </row>
     <row r="902" xml:space="preserve">
       <c r="A902" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Necesito recursos para la investigación.</v>
-      </c>
-    </row>
-    <row r="903">
-      <c r="A903" t="str">
-        <v/>
+        <v xml:space="preserve">Necesito recursos para la investigación.</v>
+      </c>
+    </row>
+    <row r="903" xml:space="preserve">
+      <c r="A903" t="str" xml:space="preserve">
+        <v xml:space="preserve"> todos los contratistas disponibles: Nuestro equipo de investigación en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; está trabajando incansablemente para resolver la actual "Crisis de Regeneración" y abordar el problema de las improntas inestables. Su trabajo ha producido resultados prometedores, pero la falta de un recurso clave está impidiendo que realicen más experimentos. Nuestro proveedor nos ha informado de que el aumento de la demanda, combinado con menores rendimientos de minería, significa que no recibiremos nuestro envío programado hasta dentro de unos meses. Nuestro equipo de investigación no puede esperar tanto y esperamos que puedan ayudarnos. El recurso es difícil de conseguir, pero tenemos información fidedigna de que las antiguas instalaciones mineras de Hathor se construyeron en zonas con una alta concentración del mineral. Dado que Hathor cesó sus operaciones poco después de establecerse en el sistema, existe una buena posibilidad de que la activación de uno de estos láseres de minería pueda proporcionarles lo que necesitamos. Juntos podemos mejorar el universo para todos. Narina Lerrem, Gerente Sénior de Subcontratación de Investigación Clínica.</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v> Ruta de envío local de Red Wind</v>
+        <v>Ruta de envío local de Red Wind</v>
       </c>
     </row>
     <row r="905" xml:space="preserve">
@@ -5352,24 +5352,24 @@
         <v>Pedido pequeño: Materiales extraídos a mano</v>
       </c>
     </row>
-    <row r="991">
-      <c r="A991" t="str">
-        <v/>
+    <row r="991" xml:space="preserve">
+      <c r="A991" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; PRUEBA DE VISTA PREVIA TÉCNICA: Completa esta misión para obtener planos para armas Volt. Para esta prueba, estos planos tienen algunas ranuras que aceptan diferentes materiales para ajustes de estadísticas variables. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulta &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en tu diario mobiGlas. Mientras estés allí, no dudes en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si quieres un repaso sobre cómo obtener los materiales. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Cuando estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable en ningún caso por los daños que se produzcan durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v> Pedido pequeño: Materiales extraídos a mano</v>
-      </c>
-    </row>
-    <row r="993">
-      <c r="A993" t="str">
-        <v/>
+        <v>Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="993" xml:space="preserve">
+      <c r="A993" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; PRUEBA DE VISTA PREVIA TÉCNICA: Completa esta misión para obtener planos para armas Volt. Para esta prueba, estos planos tienen algunas ranuras que aceptan diferentes materiales para ajustes de estadísticas variables. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulta &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en tu diario mobiGlas. Mientras estés allí, no dudes en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si quieres un repaso sobre cómo obtener los materiales. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Cuando estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v> Gran orden de compra: Materiales extraídos a mano</v>
+        <v>Gran orden de compra: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="995" xml:space="preserve">
@@ -5412,29 +5412,29 @@
         <v> Pedido pequeño: Materiales extraídos a mano</v>
       </c>
     </row>
-    <row r="1003">
-      <c r="A1003" t="str">
-        <v/>
+    <row r="1003" xml:space="preserve">
+      <c r="A1003" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; PRUEBA DE VISTA PREVIA TÉCNICA: Completa esta misión para obtener planos para armas Volt. Para esta prueba, estos planos tienen algunas ranuras que aceptan diferentes materiales para ajustes de estadísticas variables. ~mission(Hint_Location) Se han reportado avistamientos de kopion dentro del área, por lo que se recomienda precaución. Para obtener una lista completa de dónde encontrar estos minerales, consulta &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en tu diario mobiGlas. Mientras estés allí, no dudes en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si quieres un repaso sobre cómo obtener los materiales. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Cuando esté listo para vendernos los materiales necesarios, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no será responsable en ningún caso por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v> Pedido pequeño: Materiales extraídos a mano</v>
-      </c>
-    </row>
-    <row r="1005">
-      <c r="A1005" t="str">
-        <v/>
+        <v>Pedido pequeño: Materiales extraídos a mano</v>
+      </c>
+    </row>
+    <row r="1005" xml:space="preserve">
+      <c r="A1005" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; PRUEBA DE VISTA PREVIA TÉCNICA: Completa esta misión para obtener planos para armas Volt. Para esta prueba, estos planos tienen algunas ranuras que aceptan diferentes materiales para ajustes de estadísticas variables. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulta &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en tu diario mobiGlas. Mientras estés allí, no dudes en leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si quieres un repaso sobre cómo obtener los materiales. Dado que esta es una orden de compra y no un contrato de minería, se espera que proporciones tu propio equipo, como un &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Cuando estés listo para vendernos los materiales requeridos, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no podrá ser considerado responsable en modo alguno por los daños ocasionados durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v> Gran orden de compra: Materiales extraídos a mano</v>
+        <v>Gran orden de compra: Materiales extraídos a mano</v>
       </c>
     </row>
     <row r="1007" xml:space="preserve">
       <c r="A1007" t="str" xml:space="preserve">
-        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
+        <v xml:space="preserve"> PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; TÉRMINOS*: Shubin Interstellar está buscando cumplir otra orden de compra para una variedad de materiales. Agradecemos su ayuda en este asunto. ~mission(Hint_Location) Recordatorio, dado que esta es una orden de compra y no un contrato de minería, se espera que proporcione su propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Una vez que esté listo para vendernos los materiales requeridos, deposítelos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, usted asume todos y cada uno de los riesgos asociados con el trabajo descrito en el presente y Shubin Interstellar no puede ser considerado responsable de ningún daño acumulado durante la duración del contrato.</v>
       </c>
     </row>
     <row r="1008">
@@ -5512,14 +5512,14 @@
         <v>Orden de compra XS: Envío de mineral extraído</v>
       </c>
     </row>
-    <row r="1023">
-      <c r="A1023" t="str">
-        <v/>
+    <row r="1023" xml:space="preserve">
+      <c r="A1023" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; PRUEBA DE VISTA PREVIA TÉCNICA: Completa esta misión para obtener planos para un conjunto de armadura pesada Antium. Para esta prueba, estos planos tienen algunas ranuras que aceptan diferentes materiales para ajustes de estadísticas variables. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulta &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en tu diario mobiGlas. Mientras estés allí, puedes leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si quieres repasar cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Ten en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se encuentran en tu Mapa Estelar. Cuando estés listo para vendernos los materiales refinados necesarios, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v> Orden de compra XL: Envío de mineral extraído</v>
+        <v>Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1025" xml:space="preserve">
@@ -5529,7 +5529,7 @@
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>Orden de compra XL: Envío de mineral extraído</v>
+        <v> Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1027" xml:space="preserve">
@@ -5662,14 +5662,14 @@
         <v>Orden de compra XS: Envío de mineral extraído</v>
       </c>
     </row>
-    <row r="1053">
-      <c r="A1053" t="str">
-        <v/>
+    <row r="1053" xml:space="preserve">
+      <c r="A1053" t="str" xml:space="preserve">
+        <v xml:space="preserve">PUBLICACIÓN: Orden de compra UBICACIÓN: &lt;EM4&gt;~mission(System) &lt;/EM4&gt; PRUEBA DE VISTA PREVIA TÉCNICA: Completa esta misión para obtener planos para un conjunto de armadura pesada Antium. Para esta prueba, estos planos tienen algunas ranuras que aceptan diferentes materiales para ajustes de estadísticas variables. ~mission(Hint_Location) Para obtener una lista completa de dónde encontrar estos minerales, consulta &lt;EM4&gt;Fundamentos de minería n.° 2: Dónde minar&lt;/EM4&gt; en tu diario mobiGlas. Mientras estés allí, puedes leer la primera parte &lt;EM4&gt;Fundamentos de minería n.° 1: Descripción general básica&lt;/EM4&gt; si quieres repasar cómo obtener los materiales. Dado que se trata de una orden de compra y no de un contrato de minería, se espera que proporciones tu propio equipo, como una &lt;EM4&gt;~mission(Hint_Tool)&lt;/EM4&gt;. Ten en cuenta que, para agilizar el uso futuro de estos materiales, &lt;EM4&gt;deben refinarse antes de la entrega&lt;/EM4&gt;. Esto se puede hacer en cualquier refinería, cuyas ubicaciones se encuentran en tu Mapa Estelar. Cuando estés listo para vendernos los materiales refinados necesarios, deposítalos en el montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. *Al aceptar este contrato, asumes todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v> Orden de compra XL: Envío de mineral extraído</v>
+        <v>Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1055" xml:space="preserve">
@@ -5679,7 +5679,7 @@
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>Orden de compra XL: Envío de mineral extraído</v>
+        <v> Orden de compra XL: Envío de mineral extraído</v>
       </c>
     </row>
     <row r="1057" xml:space="preserve">
@@ -5712,24 +5712,24 @@
         <v>Derechos mineros de la estación trituradora QV (compartidos)</v>
       </c>
     </row>
-    <row r="1063">
-      <c r="A1063" t="str">
-        <v/>
+    <row r="1063" xml:space="preserve">
+      <c r="A1063" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO: Transferencia de Derechos Mineros UBICACIÓN: Nyx DETALLES: Exploradores interestelares de Shubin han descubierto recientemente la ubicación de una estación de trituración de QV Planetary Service abandonada cerca del cinturón de Keeger. Estas estaciones fueron utilizadas originalmente por la compañía extinta para extraer valiosos recursos del interior de asteroides, pero el conocimiento de su ubicación exacta se ha perdido con el paso de los años. Si bien esta estación en particular está fuera de servicio, nuestro equipo de exploración cree que podría volver a funcionar con las reparaciones necesarias. Además, si se volviera a poner en línea, ya hay un asteroide rico en recursos listo para ser fracturado por el láser minero de la estación. Desafortunadamente, con todos los desafíos que conlleva operar en Nyx, Shubin actualmente no tiene el ancho de banda disponible para realizar las reparaciones mencionadas por sí mismo. Sin embargo, esto ha creado una oportunidad para una operación minera independiente interesada como la suya. &lt;EM4&gt;TÉRMINOS*:&lt;/EM4&gt; Ponemos a su disposición los &lt;EM4&gt;derechos mineros compartidos&lt;/EM4&gt; de esta estación de trituración de QV. Tras la compra, le proporcionaremos las coordenadas de la estación a usted y a su tripulación. (Recuerde que cualquier otra parte interesada que adquiera los derechos mineros también tendrá acceso a la estación). Su tripulación podrá entonces dirigirse allí con una nave minera, restaurar el láser minero de la estación, fracturar el asteroide y extraer los recursos de su interior. Tenga en cuenta que, al tratarse de un contrato compartido, podemos ofrecer estos derechos mineros a precios reducidos, pero los recursos del asteroide estarán disponibles por orden de llegada para cualquier otra tripulación minera en el sitio. Asimismo, existe la posibilidad de que otras partes interesadas, como forajidos, descubran la ubicación de la estación por su cuenta. Se recomienda precaución. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de los daños que puedan producirse durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v> Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="str">
-        <v/>
+        <v>Derechos de explotación minera de la estación trituradora QV (exclusivos)</v>
+      </c>
+    </row>
+    <row r="1065" xml:space="preserve">
+      <c r="A1065" t="str" xml:space="preserve">
+        <v xml:space="preserve">CONTRATO: Transferencia de Derechos Mineros UBICACIÓN: Nyx DETALLES: Exploradores interestelares de Shubin han descubierto recientemente la ubicación de una estación de trituración de QV Planetary Service abandonada cerca del cinturón de Keeger. Estas estaciones fueron utilizadas originalmente por la compañía extinta para extraer valiosos recursos del interior de asteroides, pero el conocimiento de su ubicación exacta se ha perdido con el paso de los años. Si bien esta estación en particular está fuera de servicio, nuestro equipo de exploración cree que podría volver a funcionar con las reparaciones necesarias. Además, si se volviera a poner en línea, ya hay un asteroide rico en recursos listo para ser fracturado por el láser minero de la estación. Desafortunadamente, con todos los desafíos que conlleva operar en Nyx, Shubin actualmente no tiene el ancho de banda disponible para manejar las reparaciones mencionadas por sí mismo. Sin embargo, esto ha creado una oportunidad para una operación minera independiente interesada como la suya. &lt;EM4&gt;TÉRMINOS*: &lt;/EM4&gt; Ponemos a su disposición los &lt;EM4&gt;derechos mineros exclusivos&lt;/EM4&gt; de esta estación de trituración de QV. Tras la compra, proporcionaremos las coordenadas de la estación únicamente a usted y a su tripulación. Su equipo podrá entonces dirigirse allí con una nave minera, restaurar el láser minero de la estación, fracturar el asteroide y extraer los recursos que contiene. Tenga en cuenta que, si bien garantizamos que estas coordenadas serán exclusivas para usted, no podemos asegurar que otras partes interesadas, como delincuentes, no descubran la ubicación de la estación por su cuenta. Se recomienda precaución. *Al aceptar este contrato, usted asume todos los riesgos asociados con el trabajo aquí descrito y Shubin Interstellar no se hace responsable de ningún daño que pueda ocurrir durante la vigencia del contrato.</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v> Desguace ~misión(NombreObjetivo)</v>
+        <v>Desguace ~misión(NombreObjetivo)</v>
       </c>
     </row>
     <row r="1067">
@@ -5892,9 +5892,9 @@
         <v> SOLICITUD DE REPOSTAJE: ~misión(Nave)</v>
       </c>
     </row>
-    <row r="1099">
-      <c r="A1099" t="str">
-        <v/>
+    <row r="1099" xml:space="preserve">
+      <c r="A1099" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, si tienes experiencia en repostaje, esto te puede interesar. Una baliza acaba de activarse en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;, de un cliente cuyo &lt;EM4&gt;~mission(Ship)&lt;/EM4&gt; se está quedando sin combustible, así que asegúrate de que tus depósitos estén llenos. La nave cliente te pagará a una tasa de &lt;EM4&gt;~mission(FuelRate) aUEC por SCU de hidrógeno&lt;/EM4&gt; y &lt;EM4&gt;~mission(QTFuelRate) aUEC por SCU de Quantum&lt;/EM4&gt;, y como contratista del United Wayfarers Club, también podrás optar a la tarifa de servicio del UWC mencionada anteriormente al finalizar. Parece un trabajo sencillo y sin complicaciones, pero nunca está de más mantener los escáneres activos. Avísame si te interesa y pongamos a estas personas en marcha. Espero tu respuesta, Dina Deloit Dispatch Hub United Wayfarers Club "Te respaldamos"</v>
       </c>
     </row>
     <row r="1100">
@@ -5902,29 +5902,29 @@
         <v xml:space="preserve"> SOLICITUD DE REPOSTAJE CRÍTICA: ~misión(Nave)</v>
       </c>
     </row>
-    <row r="1101">
-      <c r="A1101" t="str">
-        <v/>
+    <row r="1101" xml:space="preserve">
+      <c r="A1101" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hola, otro día, otra señal. Hay un &lt;EM4&gt;~mission(Ship)&lt;/EM4&gt; con un tanque vacío en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. El buque cliente te pagará a la tasa de &lt;EM4&gt;~mission(FuelRate) aUEC por SCU de hidrógeno&lt;/EM4&gt; y &lt;EM4&gt;~mission(QTFuelRate) aUEC por SCU de Quantum&lt;/EM4&gt;, y como contratista del United Wayfarers Club, también calificarás para la tarifa de servicio de UWC mencionada anteriormente al completar. No puedo mentir: es un lugar horrible para quedarse atascado y peor aún para ser tomado por sorpresa. Hemos perdido gente buena allí, incluso los que tuvieron suerte regresaron a casa con partes faltantes. Si decides aceptar el trabajo, hazme un favor y mantente alerta. Si tienes un amigo con tiempo libre, tal vez podrías contactarlo para que te ayude. Quizás estoy siendo paranoica, pero eso no significa que no estén conspirando contra ti, como solía decir Mamá Deloit. En realidad, nunca dijo eso, pero estoy bastante segura de que lo diría si se dedicara a esto. Simplemente haz tu trabajo y llega a casa sana y salva, ¿de acuerdo? Dina Deloit Dispatch Hub United Wayfarers Club "Te respaldamos"</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v> SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" t="str">
-        <v/>
+        <v>SOLICITUD URGENTE DE REPOSTAJE: ~misión(Nave)</v>
+      </c>
+    </row>
+    <row r="1103" xml:space="preserve">
+      <c r="A1103" t="str" xml:space="preserve">
+        <v xml:space="preserve"> ¡Oye! Tengo una baliza en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Dicen que sus tanques están vacíos y que necesitan un repostaje completo. Si te interesa, creo que estarán encantados de verte. La nave cliente te pagará a una tasa de &lt;EM4&gt;~mission(FuelRate) aUEC por SCU de hidrógeno&lt;/EM4&gt; y &lt;EM4&gt;~mission(QTFuelRate) aUEC por SCU de Quantum&lt;/EM4&gt;, y como contratista del United Wayfarers Club, también podrás optar a la tarifa de servicio del UWC mencionada anteriormente al finalizar el trabajo. Están atrapados en una zona con mala reputación, aunque últimamente las cosas han estado un poco más tranquilas. Aun así, creo que conviene mantenerse alerta, por si acaso sigue habiendo problemas por ahí. En cualquier caso, cuanto antes todos puedan volver a volar, y eso te incluye a ti, mejor. ¡Que tengas un buen viaje, Dina! Centro de Despacho de Deloit, Club United Wayfarers. "Te respaldamos".</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v> REPOSTAJE URGENTE DE LA FLOTA</v>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="str">
-        <v/>
+        <v>REPOSTAJE URGENTE DE LA FLOTA</v>
+      </c>
+    </row>
+    <row r="1105" xml:space="preserve">
+      <c r="A1105" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Hola de nuevo, tengo una baliza en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y esta es una grande. Toda una pequeña flota de naves se quedó sin combustible al mismo tiempo. Impresionante coordinación y falta de planificación al mismo tiempo. La nave cliente te pagará a una tasa de &lt;EM4&gt;~mission(FuelRate) aUEC por SCU de hidrógeno&lt;/EM4&gt; y &lt;EM4&gt;~mission(QTFuelRate) aUEC por SCU de Quantum&lt;/EM4&gt;, y como contratista del United Wayfarers Club, también calificarás para la tarifa de servicio del UWC mencionada anteriormente al finalizar. Con suerte, como la zona en la que se encuentran es bastante segura, no debería haber demasiados problemas al acecho, pero en estos tiempos nunca se sabe. No estaría de más que volvieran a volar lo antes posible. Que tengas un buen viaje, Dina Deloit Dispatch Hub United Wayfarers Club "Te respaldamos"</v>
       </c>
     </row>
     <row r="1106">
@@ -5972,9 +5972,9 @@
         <v> Fin de una salamandra</v>
       </c>
     </row>
-    <row r="1115">
-      <c r="A1115" t="str">
-        <v/>
+    <row r="1115" xml:space="preserve">
+      <c r="A1115" t="str" xml:space="preserve">
+        <v xml:space="preserve">Uno de los líderes de la misteriosa banda de los Salamandras Garra, un ~mission(TargetName), se ha vuelto insoportable y ahora es nuestro problema. No es de extrañar, ya que nadie, excepto sus amigos, puede entender lo que dicen. Por desgracia, no será tan fácil como ir a ~mission(Location|Address) y enfrentarte a ellos directamente. No solo tendrás que asegurarte de que la estación esté operativa para llegar hasta ellos, sino que parece que también tendrás que sacarlos de su escondite eliminando primero a varios de sus compañeros. No es una tarea sencilla, pero estoy seguro de que estarás a la altura. Un saludo, Vaughn</v>
       </c>
     </row>
     <row r="1116">
@@ -5992,9 +5992,9 @@
         <v> Un contrato desafiante</v>
       </c>
     </row>
-    <row r="1119">
-      <c r="A1119" t="str">
-        <v/>
+    <row r="1119" xml:space="preserve">
+      <c r="A1119" t="str" xml:space="preserve">
+        <v xml:space="preserve">Me han reclutado para dispararle a un cliente muy motivado. El objetivo es &lt;EM4&gt;~mission(TargetName)&lt;/EM4&gt;, un personaje despreciable según todos los indicios, que parece disfrutar de la autoridad temporal que le otorga su posición de mercenario. Cree que su sadismo es justo y mi cliente quiere recordarle lo contrario. Recientemente ha sido contratado por ASD como parte de un equipo de mercenarios en &lt;EM4&gt;~mission(Location)&lt;/EM4&gt;, así que no será fácil, ya que sin duda habrá otros individuos armados. Espero que reacciones como corresponde, pero ~mission(TargetName|Last) es tu objetivo. Recibirás tu pago al completar la misión. Saludos, Vaughn</v>
       </c>
     </row>
     <row r="1120">

--- a/work/from_google/missions.xlsx
+++ b/work/from_google/missions.xlsx
@@ -412,9 +412,9 @@
         <v> Se necesita recuperador (escasa cantidad de RMC)</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Adagio Holdings Un orgulloso empleador de igualdad de oportunidades &gt; Acerca del trabajo &lt; Para ayudar a satisfacer un pedido reciente a pequeña escala, estamos buscando contratistas para ayudar a obtener Compuesto de Material Reciclado (RMC) desmantelando barcos abandonados. Recomendamos buscar restos en puntos de Lagrange o puede comprar un reclamo de salvamento de nosotros en su Administrador de Contratos. Una vez adquiridos, entregue los materiales al montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas. &gt; Requisitos &lt; - Cualquier clase/tamaño de barco de salvamento &gt; Descargo de responsabilidad &lt; Los contratistas son responsables de asegurarse de que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE correspondientes. Adagio Holdings no es responsable de ninguna manera por ningún delito o falta cometida por los contratistas y no ofrecerá compensación o reparación a ninguna persona afectada por estas acciones.</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Adagio Holdings[NL]Un orgulloso empleador que ofrece igualdad de oportunidades[NL][NL]&gt; Acerca del trabajo &lt;[NL]Para ayudar a satisfacer un pedido reciente a pequeña escala, estamos buscando contratistas para ayudar a obtener Compuesto de Material Reciclado (RMC) desmantelando barcos abandonados. Recomendamos buscar restos en puntos de Lagrange o puede comprar un reclamo de salvamento de nosotros en su Administrador de Contratos.[NL][NL]Una vez adquiridos, entregue los materiales al elevador de carga ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;.[NL][NL]Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas.[NL][NL]&gt; Requisitos &lt;[NL] - Cualquier clase/tamaño de barco de salvamento[NL][NL]&gt; Descargo de responsabilidad &lt;[NL]Los contratistas son responsables de garantizar que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE correspondientes. Adagio Holdings no se responsabiliza en modo alguno de los delitos o faltas cometidos por los contratistas y no ofrecerá compensación ni reparación alguna a las personas afectadas por estas acciones.</v>
       </c>
     </row>
     <row r="4">
@@ -422,9 +422,9 @@
         <v>Adagio Holdings necesita rescatadores.</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Adagio Holdings Un orgulloso empleador de igualdad de oportunidades &gt; Acerca de nosotros &lt; Como principal comprador y distribuidor de derechos de salvamento, Adagio Holdings ahora busca expandirse en la adquisición y distribución de materiales recuperables a empresas tanto pequeñas como grandes. &gt; Acerca del trabajo &lt; Como parte de esta iniciativa, necesitamos contratistas con buen ojo capaces de identificar materiales recuperables, desmantelarlos de manera eficiente y entregarnos el Compuesto de Material Reciclado (RMC) y los componentes recuperados. Este contrato introductorio requerirá que se dirija a &lt;EM4&gt;~mission(Ubicación|Dirección)&lt;/EM4&gt; y desmantele un barco abandonado aprobado para salvamento. Una vez que haya reunido el RMC, lo entregará al montacargas ubicado en &lt;EM4&gt;~mission(Destino|Dirección)&lt;/EM4&gt;. &gt; Requisitos &lt; - Cualquier clase/tamaño de barco de salvamento Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas. &gt; Descargo de responsabilidad &lt; Los contratistas son responsables de asegurarse de que están recolectando materiales de vehículos que se consideran salvamento lícito según las leyes UEE vigentes. Adagio Holdings no se hace responsable de ningún delito o falta cometida por los contratistas y no ofrecerá compensación ni reparación a ninguna persona afectada por estas acciones.</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Adagio Holdings[NL]Un orgulloso empleador que ofrece igualdad de oportunidades[NL][NL]&gt; Sobre nosotros &lt;[NL]Como principal comprador y distribuidor de derechos de salvamento, Adagio Holdings ahora busca expandirse en la adquisición y distribución de materiales recuperables a empresas tanto pequeñas como grandes.[NL][NL]&gt; Sobre el trabajo &lt;[NL]Como parte de esta iniciativa, necesitamos contratistas con buen ojo capaces de identificar materiales recuperables, desmantelarlos de manera eficiente y entregarnos el compuesto de material reciclado (RMC) y los componentes recuperados.[NL][NL]Este contrato introductorio requerirá que se dirija a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y desmantele un barco abandonado aprobado para salvamento.[NL][NL]Una vez que haya reunido el RMC, lo entregará al montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;.[NL][NL]&gt; Requisitos &lt;[NL] - Cualquier clase/tamaño de salvamento ship[NL][NL]Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvamento para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas.[NL][NL]&gt; Descargo de responsabilidad &lt;[NL]Los contratistas son responsables de garantizar que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE correspondientes. Adagio Holdings no es responsable de ningún delito o falta cometida por los contratistas y no ofrecerá ninguna compensación o reparación a ninguna persona afectada por estas acciones.</v>
       </c>
     </row>
     <row r="6">
@@ -432,9 +432,9 @@
         <v xml:space="preserve">Se necesita recuperador (suministro médico de RMC)</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Adagio Holdings Un orgulloso empleador de igualdad de oportunidades &gt; Acerca del trabajo &lt; Para ayudar a satisfacer un pedido reciente de tamaño medio, estamos buscando contratistas para ayudar a obtener Compuesto de Material Reciclado (RMC) desmantelando barcos abandonados. Recomendamos buscar restos en puntos de Lagrange o puede comprar un reclamo de salvamento de nosotros en su Administrador de Contratos. Una vez adquiridos, entregue los materiales al montacargas ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;. Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas. &gt; Requisitos &lt; - Cualquier clase/tamaño de barco de salvamento &gt; Descargo de responsabilidad &lt; Los contratistas son responsables de asegurarse de que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE vigentes. Adagio Holdings no es responsable de ninguna manera por ningún delito o falta cometida por los contratistas y no ofrecerá compensación o reparación a ninguna persona afectada por estas acciones.</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Adagio Holdings[NL]Un orgulloso empleador que ofrece igualdad de oportunidades[NL][NL]&gt; Acerca del trabajo &lt;[NL]Para ayudar a satisfacer un pedido reciente de tamaño medio, estamos buscando contratistas para ayudar a obtener Compuesto de Material Reciclado (RMC) desmantelando barcos abandonados. Recomendamos buscar restos en los puntos de Lagrange o puede comprar un reclamo de salvamento de nosotros en su Administrador de Contratos.[NL][NL]Una vez adquiridos, entregue los materiales al elevador de carga ubicado en &lt;EM4&gt;~misión(Destino|Dirección)&lt;/EM4&gt;.[NL][NL]Para obtener consejos sobre salvamento, consulte &lt;EM4&gt;Guía del salvador para la recolección de materiales&lt;/EM4&gt; en su diario mobiGlas.[NL][NL]&gt; Requisitos &lt;[NL] - Cualquier clase/tamaño de barco de salvamento[NL][NL]&gt; Descargo de responsabilidad &lt;[NL]Los contratistas son responsables de garantizar que están recolectando materiales de vehículos que se consideran salvamento justo según las leyes UEE correspondientes. Adagio Holdings no se responsabiliza en modo alguno de los delitos o faltas cometidos por los contratistas y no ofrecerá compensación ni reparación alguna a las personas afectadas por estas acciones.</v>
       </c>
     </row>
     <row r="8">
@@ -442,9 +442,9 @@
         <v>Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str" xml:space="preserve">
-        <v xml:space="preserve">-------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(Nombre del objetivo) SISTEMA: Stanton EVALUACIÓN DE RIESGO: Medio ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: &lt;Ninguna&gt; NOTAS: Hemos rastreado a este objetivo de recompensa hasta el &lt;EM4&gt;ala de ingeniería&lt;/EM4&gt; de una instalación de investigación abandonada de Associated Science and Development. Aunque está cerrada, se sabe que varios carroñeros y otros tipos indeseables frecuentan la zona. La propia instalación también podría suponer un riesgo, ya que se desconoce la naturaleza de la investigación que se lleva a cabo allí. Esté atento a posibles peligros ambientales mientras persigue al objetivo. GREMIO DE CAZARRECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>--------------------------------------------------------[NL]----------------- CONTRATO DE RECOMPENSA -----------------[NL]--------------------------------------------------------[NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]PROCESAMIENTO Y DISTRIBUCIÓN[NL][NL]El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial.[NL][NL]NOMBRE: ~mission(Nombre del objetivo) [NL]SISTEMA: Stanton[NL]EVALUACIÓN DE RIESGO: Medio[NL]ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección)[NL]AFILIACIONES CONOCIDAS: &lt;Ninguna&gt;[NL]NOTAS: Hemos rastreado a este objetivo de recompensa hasta el &lt;EM4&gt;ala de ingeniería&lt;/EM4&gt; de una instalación de investigación abandonada de Associated Science and Development. Aunque cerrada, se sabe que varios carroñeros y otros tipos indeseables frecuentan la zona.[NL][NL]La propia instalación también podría suponer un riesgo, ya que se desconoce la naturaleza de la investigación que se lleva a cabo allí. Esté atento a posibles peligros ambientales mientras persigue al objetivo.[NL][NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]En busca de la justicia[NL][NL]El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="10">
@@ -452,9 +452,9 @@
         <v>Recompensa verificada: ~mission(TargetName) en ~mission(Location)</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str" xml:space="preserve">
-        <v xml:space="preserve">-------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(NombreDelObjetivo) SISTEMA: Stanton EVALUACIÓN DE RIESGO: Medio ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: &lt;Ninguna&gt; NOTAS: Hemos rastreado a este objetivo de recompensa hasta el &lt;EM4&gt;Ala de Investigación&lt;/EM4&gt; de una instalación abandonada de Associated Science and Development. Aunque cerrada, se sabe que varios carroñeros y otros tipos indeseables frecuentan la zona. La propia instalación también podría suponer un riesgo, ya que se desconoce la naturaleza de la investigación que se lleva a cabo allí. Esté atento a posibles peligros ambientales mientras persigue al objetivo. GREMIO DE CAZARRECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>--------------------------------------------------------[NL]----------------- CONTRATO DE RECOMPENSA -----------------[NL]--------------------------------------------------------[NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]PROCESAMIENTO Y DISTRIBUCIÓN[NL][NL]El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial.[NL][NL]NOMBRE: ~mission(Nombre del objetivo) [NL]SISTEMA: Stanton[NL]EVALUACIÓN DE RIESGO: Medio[NL]ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección)[NL]AFILIACIONES CONOCIDAS: &lt;Ninguna&gt;[NL]NOTAS: Hemos rastreado a este objetivo de recompensa hasta el &lt;EM4&gt;Ala de investigación&lt;/EM4&gt; de una instalación abandonada de Associated Science and Development. Aunque cerrada, se sabe que varios carroñeros y otros tipos indeseables frecuentan la zona.[NL][NL]La propia instalación también podría suponer un riesgo, ya que se desconoce la naturaleza de la investigación que se lleva a cabo allí. Esté atento a posibles peligros ambientales mientras persigue al objetivo.[NL][NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]En busca de la justicia[NL][NL]El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="12">
@@ -462,9 +462,9 @@
         <v>Recompensa verificada: ~misión(Nombre del objetivo) | ~misión(Peligro)</v>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str" xml:space="preserve">
-        <v xml:space="preserve"> -------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(Nombre del Objetivo) SISTEMA: ~mission(Sistema) EVALUACIÓN DE RIESGO: ~mission(Peligro) ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: &lt;Ninguna&gt; NOTAS: Tienen varios asociados conocidos con antecedentes penales, por lo que podrían no estar solos, así que ármense y tengan precaución al enfrentarse a ellos. GREMIO DE CAZADORES DE RECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v> --------------------------------------------------------[NL]----------------- CONTRATO DE RECOMPENSA -----------------[NL]--------------------------------------------------------[NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]PROCESAMIENTO Y DISTRIBUCIÓN[NL][NL]El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial.[NL][NL]NOMBRE: ~mission(Nombre del objetivo) [NL]SISTEMA: ~mission(Sistema)[NL]EVALUACIÓN DE RIESGO: ~mission(Peligro)[NL]ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección)[NL]AFILIACIONES CONOCIDAS: &lt;Ninguna&gt;[NL]NOTAS: Tienen varios asociados conocidos con antecedentes penales, por lo que podrían no estar solos; así que ármense y tengan precaución al enfrentarse a ellos.[NL][NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]En busca de la justicia[NL][NL]El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá. de conformidad con las leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="14">
@@ -479,7 +479,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve"> Certificación de Detención de Sospechosos</v>
+        <v xml:space="preserve">Certificación de Detención de Sospechosos</v>
       </c>
     </row>
     <row r="17">
@@ -489,7 +489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Certificación de Permiso de Iniciación para Rastreadores</v>
+        <v> Certificación de Permiso de Iniciación para Rastreadores</v>
       </c>
     </row>
     <row r="19">
@@ -562,9 +562,9 @@
         <v> Recompensa de alto riesgo: ~misión(Nombre del objetivo) en la estación QV Breaker</v>
       </c>
     </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str" xml:space="preserve">
-        <v xml:space="preserve">-------------------------------------------------------- ----------------- CONTRATO DE RECOMPENSA ----------------- -------------------------------------------------------- PROCESAMIENTO Y DISTRIBUCIÓN DEL GREMIO DE CAZADORES DE RECOMPENSAS El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial. NOMBRE: ~mission(NombreDelObjetivo) SISTEMA: Nyx EVALUACIÓN DE RIESGO: Alto ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección) AFILIACIONES CONOCIDAS: Salamandras Garra NOTAS: Debido a que estas estaciones de ruptura QV abandonadas no son completamente funcionales, hay una buena probabilidad de que tengas que realizar algunas reparaciones antes de poder acceder a la ubicación del objetivo. También puedes tener que lidiar con otros peligros como fauna peligrosa. Además, la información recopilada sobre ~mission(NombreDelObjetivo) lo tiene como un miembro de alto rango de las Salamandras Garra, uno que no aparecerá a menos que sea convenientemente sacado de su escondite. Enfréntate a suficientes asociados de menor rango y se verán obligados a venir a tratar contigo ellos mismos. GREMIO DE CAZARRECOMPENSAS En busca de la justicia El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>--------------------------------------------------------[NL]----------------- CONTRATO DE RECOMPENSA -----------------[NL]--------------------------------------------------------[NL][NL]GREMIO DE CAZADORES DE RECOMPENSAS[NL]PROCESAMIENTO Y DISTRIBUCIÓN[NL][NL]El Gremio de Cazadores de Recompensas ha autorizado una recompensa oficial.[NL][NL]NOMBRE: ~mission(Nombre del objetivo) [NL]SISTEMA: Nyx[NL]EVALUACIÓN DE RIESGO: Alto[NL]ÚLTIMA UBICACIÓN CONOCIDA: ~mission(Ubicación|Dirección)[NL]AFILIACIONES CONOCIDAS: Salamandras Garra[NL]NOTAS: Debido a que estas estaciones de ruptura QV abandonadas no son completamente funcionales, hay una buena probabilidad de que tenga que realizar algunas reparaciones antes de poder acceder a la ubicación del objetivo. También puede que tengas que lidiar con otros peligros como fauna peligrosa.[NL][NL]Además, la información recopilada en ~misión(Nombre del objetivo) los tiene como un miembro de alto rango de las Salamandras Garra, uno que no aparecerá a menos que sea convenientemente sacado de su escondite. Interactúa con suficientes asociados de menor rango y se verán obligados a venir a tratar contigo ellos mismos.[NL][NL][NL]GREMIO DE CAZARRECOMPENSAS[NL]En busca de la justicia[NL][NL]El Gremio de Cazadores de Recompensas es un servicio de seguridad sancionado por el Gremio de Mercenarios y autorizado para operar tanto en la UEE como más allá de acuerdo con las Leyes de la Autoridad de Xenotrade.</v>
       </c>
     </row>
     <row r="34">
@@ -572,9 +572,9 @@
         <v>En llamas</v>
       </c>
     </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hemos estado intentando acceder a datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y digo activarla de verdad. Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos. Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda. -Bit Zeros</v>
+    <row r="35">
+      <c r="A35" t="str">
+        <v> Hemos estado intentando acceder a algunos datos confidenciales en ~mission(Location|Address), pero parece que solo hay una puerta trasera que podemos usar. El problema es que necesitamos a alguien allí para activarla. Y realmente digo activarla.[NL][NL]Si puedes ir allí y destruir parte de su infraestructura, los sistemas de respaldo de emergencia se activarán y deberíamos poder acceder a todo lo que queramos.[NL][NL]Ojalá pudiera ver la cara de sorpresa de los gentuza que dirigen el lugar cuando suceda.[NL][NL]-Bit Zeros[NL]</v>
       </c>
     </row>
     <row r="36">
@@ -582,9 +582,9 @@
         <v> Mal funcionamiento grave</v>
       </c>
     </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37" t="str" xml:space="preserve">
-        <v xml:space="preserve"> No voy a entrar en detalles sobre el porqué, pero hay algunas partes de ~mission(Location|Address) que necesitamos destruir. Lo importante es que quiero pagarte una buena cantidad de créditos por hacerlo. Casi siento que deberías pagarnos tú por esto, porque va a ser muy divertido. No me importa cómo lo hagas. Granadas, lanzacohetes, Torpedo Burrito del día anterior, nos da igual. -Bit Zeros</v>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>No voy a entrar en la larga y aburrida historia del por qué, pero hay algunas partes de ~mission(Location|Address) que necesitamos destruir. Lo importante es que quiero pagarte una buena cantidad de créditos por hacerlo. Casi siento que deberías pagarnos por esto por lo divertido que va a ser. [NL][NL]No me importa cómo lo hagas. Granadas, lanzacohetes, burrito torpedo del día anterior, nos da igual. [NL][NL]-Bit Zeros [NL]</v>
       </c>
     </row>
     <row r="38">
@@ -592,9 +592,9 @@
         <v> Servidor no encontrado</v>
       </c>
     </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, tenemos un problema en el que podríamos necesitar tu ayuda. Uno de nuestros exreclutas hizo un trabajo pésimo en un hackeo y dejó una huella digital tan desastrosa que casi podría considerarse una confesión. Un borrado remoto no será suficiente, así que quiero que vayas a ~mission(Location|Address) y te asegures de que sus servidores de datos sean eliminados por completo. Como si esto no fuera ya un lío mayor, los códigos de acceso a la puerta cerrada de la sala de servidores solo se almacenan físicamente allí. Eso significa que primero tendrás que conseguir un datapad con el código antes de poder siquiera acercarte a ellos. Pero no te preocupes, me aseguraré de que las credenciales valgan la pena. - Bit Zeros</v>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Hola, [NL][NL]Tenemos un problema en el que podríamos necesitar tu ayuda. Uno de nuestros antiguos reclutas hizo un trabajo pésimo en un hackeo y terminó dejando una huella digital tan desordenada que bien podría ser una confesión completa. [NL][NL]Una eliminación remota no será suficiente, así que quiero que vayas a ~mission(Location|Address) y te asegures de que sus servidores de datos sean borrados por completo. [NL][NL]Como si esto no fuera ya un desastre, los códigos de acceso a la puerta cerrada de la sala de servidores solo se almacenan físicamente en el sitio. Eso significa que primero tendrás que liberar una tableta de datos con el código antes de poder siquiera acercarte a ellos. [NL][NL]Pero no te preocupes. Me aseguraré de que las credenciales valgan la pena todo el problema. [NL][NL]- Bit Zeros[NL]</v>
       </c>
     </row>
     <row r="40">
@@ -602,9 +602,9 @@
         <v> Golpéalos donde más les duele</v>
       </c>
     </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los cretinos de ~mission(Location|Address) decidieron que sería buena idea interferir en nuestros asuntos, y ahora debemos dejarles bien claro que se equivocaron. Tras investigar un poco sus datos, descubrimos dónde guardan su mercancía. Ahora solo tienes que ir allí y destruirlo todo. Creo que con eso les quedará claro. - Bit Zeros</v>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Los cretinos de ~mission(Location|Address) decidieron que sería una buena idea interferir en nuestro negocio, y ahora debemos dejarles claro que se equivocaron. [NL][NL]Un poco de investigación en sus datos y pudimos averiguar dónde guardan su alijo esos idiotas. Ahora solo necesitas ir allí y destruir hasta el último pedazo. [NL][NL]Creo que con eso debería quedar claro.[NL][NL]- Bit Zeros[NL]</v>
       </c>
     </row>
     <row r="42">
@@ -612,9 +612,9 @@
         <v> Eliminar permanentemente</v>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Esos cretinos repugnantes de ~mission(Location|Address) nos han estado vendiendo datos basura mientras intentaban engañarnos. No podemos permitirlo. Queremos que les des una última lección y elimines a todos los cobardes que encuentres. La última vez que supe de ellos, estaban escondidos cerca de ~mission(Location). Si los derribas, te llenaremos la cartera. -Bit Zeros</v>
+    <row r="43">
+      <c r="A43" t="str">
+        <v> Los pequeños cretinos viscosos de ~mission(Location|Address) nos han estado vendiendo datos basura mientras intentaban engañarnos. No podemos permitirlo.[NL][NL]Queremos que vayas a darles una última lección y elimines a todos los cobardes que encuentres. Lo último que supe es que estaban escondidos cerca de ~mission(Location).[NL][NL]Derrama su sangre y te llenaremos la cartera.[NL][NL]-Bit Zeros[NL]</v>
       </c>
     </row>
     <row r="44">
@@ -622,9 +622,9 @@
         <v> Reasignación de propiedad</v>
       </c>
     </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Muy bien, en ~mission(Location|Address) tienen algunas cosas que necesitan ser recuperadas. Claro que puede que tengas que lidiar con algunos guardias o personas preocupadas, pero en general es una transacción bastante sencilla: toma las cosas de ~mission(Location) y tráelas a ~mission(Destination|Address). A veces, lo simple es lo mejor. -Bit Zeros</v>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Muy bien,[NL][NL]En ~mission(Location|Address) tienen algunas cosas en su poder que necesitan ser liberadas. Claro, puede que tengas que lidiar con algunos guardias o personas preocupadas, pero en general es una transacción bastante sencilla: toma las cosas de ~mission(Location) y tráelas a ~mission(Destination|Address). [NL][NL]A veces, lo simple es lo mejor.[NL][NL]-Bit Zeros [NL]</v>
       </c>
     </row>
     <row r="46">
@@ -632,9 +632,9 @@
         <v> Tratos delicados</v>
       </c>
     </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espero de verdad que aceptes hacer esto, ya que no parece haber mucha gente dispuesta a encargarse de un montón de minas de proximidad. Verás, hemos encontrado un botín en ~mission(Location|Address), pero la seguridad física está resultando más difícil de lo esperado. Si encuentras la manera de sortear las minas o, posiblemente, de activarlas a distancia, debería ser relativamente fácil recoger el botín y escapar. Déjalo en ~mission(Destination|Address) y recibirás una buena parte de los créditos por correr el riesgo. -Bit Zeros</v>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Realmente espero que aceptes hacer esto, ya que no parece haber mucha gente dispuesta a enfrentarse a un montón de minas de proximidad. Verás, hay un botín que hemos conseguido en ~mission(Location|Address), pero la seguridad física está resultando más difícil de lo esperado. [NL][NL]Si puedes encontrar una manera de atravesar las minas o posiblemente una manera de activarlas de forma remota, debería ser relativamente fácil coger la mercancía y salir de allí. Déjala en ~mission(Destination|Address) y recibirás más de lo que te corresponde de los créditos por correr el riesgo.[NL][NL]-Bit Zeros[NL]</v>
       </c>
     </row>
     <row r="48">
@@ -642,9 +642,9 @@
         <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (?RT)</v>
       </c>
     </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan capturar a una persona con el nombre ~mission(TargetName) en ~mission(Location|Address). Si bien puede haber otros cómplices criminales en el lugar, les pido que tengan cuidado con los civiles o trabajadores que puedan estar allí. Ya tengo suficientes problemas, así que no necesito explicar por qué un contratista disparó a varios civiles. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>ATENCIÓN: Cazarrecompensas[NL][NL]Necesito que capturen a una persona con la recompensa ~mission(TargetName) en ~mission(Location|Address). Aunque puede haber otros cómplices criminales en el lugar, quiero que tengan cuidado con los civiles o trabajadores que puedan estar allí.[NL][NL]Ya tengo suficientes problemas, así que no necesito explicar por qué un contratista disparó a varios civiles.[NL][NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección garantizada"</v>
       </c>
     </row>
     <row r="50">
@@ -652,9 +652,9 @@
         <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
-    <row r="51" xml:space="preserve">
-      <c r="A51" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Actualmente tengo más recompensas que cazarrecompensas, así que busco ampliar nuestra plantilla. Si hacen un buen trabajo en esta primera misión, habrá más contratos. Veamos cómo les va con la recompensa en ~mission(TargetName). Se cree que se esconden en ~mission(Location|Address). Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>ATENCIÓN: Cazarrecompensas[NL][NL]Actualmente tengo más recompensas que cazarrecompensas, así que busco ampliar nuestra lista. [NL][NL]Si hacen un buen trabajo en esta primera misión, habrá más contratos. [NL][NL]Veamos cómo les va con la recompensa en ~mission(TargetName). Se cree que se esconden en ~mission(Location|Address). [NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección garantizada"</v>
       </c>
     </row>
     <row r="52">
@@ -662,9 +662,9 @@
         <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Excazador de recompensas de BlacJac. Sé que BlacJac dejó de ofrecer contratos de recompensa, pero los tiempos cambian y aquí estamos para darle otra oportunidad. Si logra completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reactivar su cuenta. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="53">
+      <c r="A53" t="str">
+        <v> ATENCIÓN: Ex cazarrecompensas de BlacJac[NL][NL]Sé que BlacJac dejó de darte contratos de recompensa, pero los tiempos cambian y aquí estamos dándote otra oportunidad.[NL][NL]Si puedes completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reincorporarte.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección proporcionada"</v>
       </c>
     </row>
     <row r="54">
@@ -672,9 +672,9 @@
         <v> Buscado por ArcCorp: ~misión(NombreObjetivo) (ERT)</v>
       </c>
     </row>
-    <row r="55" xml:space="preserve">
-      <c r="A55" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Quizás hayan oído hablar de ~mission(TargetName). Son un objetivo de alto riesgo y han estado en las noticias últimamente. Esperamos que puedan formar un equipo de respuesta y ayudar a BlacJac a neutralizarlos definitivamente. Según nuestra información más reciente, su nave subcapital y escoltas fuertemente armadas sobrevuelan ~mission(Location|Address). Les recomiendo asegurarse de tener una identificación actualizada antes de partir. Por si acaso. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, Seguridad BlacJac, "Protección garantizada".</v>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>ATENCIÓN: Cazarrecompensas[NL][NL]Es posible que hayan oído hablar de ~mission(TargetName). Son un objetivo de riesgo extremo y han estado en los titulares últimamente. Esperamos que puedan formar un equipo de respuesta y ayudar a BlacJac a acabar con ellos definitivamente. Nuestra información más reciente indica que su nave subcapital y sus escoltas fuertemente armadas sobrevuelan ~mission(Location|Address).[NL] [NL]Les recomiendo que se aseguren de tener una huella digital actualizada antes de partir. Por si acaso. [NL][NL]Buena suerte,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="56">
@@ -682,9 +682,9 @@
         <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (HRT)</v>
       </c>
     </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Su próximo objetivo, ~mission(TargetName), es sin duda un objetivo de alto riesgo, y con razón. Se sabe que viaja con armamento pesado y cuenta con suficiente protección como para que cualquiera se lo piense dos veces antes de enfrentarse a él. Según fuentes, ~mission(TargetName|Last) se esconde en ~mission(Location|Address). Cuando salgan a buscarlo, asegúrense de estar preparados. Quizás incluso deberían llevar refuerzos. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>ATENCIÓN: Cazadores de recompensas[NL][NL]Su próxima recompensa, ~mission(TargetName), es definitivamente considerada un objetivo de alto riesgo por una buena razón. Se sabe que viaja con una potencia de fuego considerable y está escoltado por suficiente protección como para que cualquiera lo piense dos veces antes de enfrentarse a él.[NL][NL]Las fuentes indican que ~mission(TargetName|Last) se esconde en ~mission(Location|Address). Cuando salgan a rastrearlo, asegúrense de estar preparados. Incluso podrían considerar llevar algún refuerzo. [NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de contratos privados[NL]BlacJac Security, "Protección proporcionada"[NL]</v>
       </c>
     </row>
     <row r="58">
@@ -692,9 +692,9 @@
         <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazadores de recompensas. No sé si les interesa, pero BlacJac busca ampliar su equipo de cazarrecompensas. Tenemos más trabajos de los que nuestros contratistas actuales pueden cubrir, así que espero que puedan ayudarnos a cubrir parte de la carga de trabajo. Sus cualificaciones se ven bien en papel, pero antes de formalizar nada, BlacJac necesita ver su desempeño en el campo. Incluso tenemos un caso de prueba preparado: queremos que resuelvan la misión ~(Nombre del objetivo). Fueron vistos por última vez en ~misión(Ubicación|Dirección). Debería ser una recompensa bastante sencilla, sin demasiada resistencia. Una oportunidad perfecta para que se pongan a prueba. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>ATENCIÓN: Cazadores de recompensas[NL][NL]No sé si les interesa, pero BlacJac busca ampliar su lista de cazarrecompensas. Tenemos más trabajos de los que nuestros contratistas actuales pueden manejar, así que espero que puedan ayudarnos a cubrir parte del trabajo. [NL][NL]Sus calificaciones se ven bien en el papel, pero antes de hacer nada oficial, BlacJac necesita ver cómo se desempeñan en el campo de primera mano. Incluso tenemos un caso de prueba listo: queremos que resuelvan ~mission(TargetName). Fueron vistos por última vez en ~mission(Location|Address). Debería ser una recompensa bastante sencilla sin demasiada resistencia. Algo perfecto para afilar sus habilidades.[NL][NL]Buena suerte,[NL]Gloria Mesa[NL][NL]Supervisora de contratos privados[NL]BlacJac Security, "Protección proporcionada"[NL]</v>
       </c>
     </row>
     <row r="60">
@@ -702,9 +702,9 @@
         <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (LRT)</v>
       </c>
     </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Se ha ofrecido una recompensa por un objetivo de bajo riesgo llamado ~mission(TargetName). El objetivo en sí no es muy peligroso, pero parece que suelen volar en grupo, así que hay muchas probabilidades de que vengan acompañados cuando los localicen. Por cierto, les recomiendo comenzar la búsqueda en ~mission(Location|Address), ya que tenemos informes de que los han visto en la zona. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>ATENCIÓN: Cazadores de recompensas[NL][NL]Se ha puesto precio a una recompensa por un objetivo de bajo riesgo llamado ~mission(TargetName). El objetivo en sí no es de mucha preocupación, pero parece que suelen volar en grupo, así que hay muchas posibilidades de que vengan acompañados cuando los localicen.[NL][NL]Hablando de eso, yo empezaría la caza en ~mission(Location|Address), ya que tenemos informes de que los han visto en la zona.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de contratos privados[NL]BlacJac Security, "Protección proporcionada"[NL]</v>
       </c>
     </row>
     <row r="62">
@@ -712,9 +712,9 @@
         <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (MRT)</v>
       </c>
     </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas. Necesitan que se encarguen de ~mission(TargetName), una recompensa de riesgo moderado vista por última vez en ~mission(Location|Address) pilotando una pequeña nave con tripulación múltiple. No pudimos obtener detalles sobre la nave que pilotaban, pero parece que tenían otras naves con ellos. Prepárense para una fuerte resistencia cuando lleguen. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ATENCIÓN: Cazarrecompensas[NL][NL]Necesitamos que resuelvan el caso de ~mission(TargetName), una recompensa de riesgo moderado vista por última vez en ~mission(Location|Address) pilotando una pequeña nave con tripulación múltiple.[NL][NL]No pudimos obtener detalles sobre qué nave pilotaban exactamente, pero parece que tenían otras naves con ellos. Prepárense para una buena resistencia cuando lleguen.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="64">
@@ -722,19 +722,19 @@
         <v> Contrato de prueba de recompensa de BlacJac</v>
       </c>
     </row>
-    <row r="65" xml:space="preserve">
-      <c r="A65" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Excazador de recompensas de BlacJac. Sé que tu última misión para BlacJac no salió bien, pero el aumento de casos significa que tienes la suerte de tener otra oportunidad. Si logras completar la misión en ~mission(TargetName) en ~mission(Location|Address), podemos ver si podemos reincorporarte. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="65">
+      <c r="A65" t="str">
+        <v> ATENCIÓN: Ex cazarrecompensas de BlacJac[NL][NL]Sé que tu última misión de cazarrecompensas para BlacJac no salió bien, pero un aumento en la carga de trabajo significa que tienes la suerte de tener otra oportunidad.[NL][NL]Si puedes completar la recompensa en ~mission(TargetName) en ~mission(Location|Address), podemos ver cómo podemos reincorporarte.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VHRT)</v>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Cazarrecompensas BlacJac acaba de recibir información de que un objetivo de altísimo riesgo, ~mission(TargetName), fue avistado en las rutas aéreas de ~mission(Location|Address) pilotando una formidable nave con una fuerte escolta. Queremos eliminar esta recompensa antes de que cometa más delitos. Reúnan los recursos y el apoyo que necesiten y salgan cuanto antes. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+        <v>Buscado por ArcCorp: ~misión(Nombre del objetivo) (VHRT)</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v> ATENCIÓN: Cazadores de recompensas[NL][NL]BlacJac acaba de recibir información de que un objetivo de muy alto riesgo, ~mission(TargetName), fue avistado moviéndose por las rutas aéreas en ~mission(Location|Address) pilotando una formidable nave con una fuerte escolta.[NL][NL]Queremos que se resuelva esta recompensa antes de que cometa más crímenes. Reúna los recursos o el apoyo que necesite y salga lo antes posible.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de contratos privados[NL]BlacJac Security, "Protección proporcionada"[NL]</v>
       </c>
     </row>
     <row r="68">
@@ -742,19 +742,19 @@
         <v> Buscado por ArcCorp: ~misión(Nombre del objetivo) (VLRT)</v>
       </c>
     </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Cazarrecompensas. Tengo un objetivo de muy bajo riesgo del que debo encargarme: ~mission(NombreDelObjetivo). Su última ubicación conocida fue ~mission(Ubicación|Dirección). Se trata de una recompensa de bajo riesgo, así que espero que puedan resolverla rápidamente. Suelen pilotar una nave pequeña y no tienen muchos conocidos. Es una misión sencilla. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security, "Protección garantizada".</v>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>ATENCIÓN: Cazarrecompensas[NL][NL]Tengo un objetivo de muy bajo riesgo del que necesito que se encarguen: ~mission(NombreDelObjetivo).[NL][NL]Su última ubicación conocida fue ~mission(Ubicación|Dirección).[NL][NL]Esta es una recompensa de baja amenaza, así que espero que puedan resolverla bastante rápido. Por lo general, vuelan una nave pequeña y no tienen muchos conocidos. No puede ser más sencillo que eso.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Proteger el sitio y obtener materiales confidenciales.</v>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Mercenarios con experiencia en manejo de carga. Nine Tails está atacando una de nuestras instalaciones en ~mission(Location|address). Dado que acaban de recibir un envío de material confidencial, no creemos que sea una coincidencia. BlacJac necesita que alguien se dirija rápidamente al lugar y asegure estas cajas importantes antes de que lo haga Nine Tails. Están autorizados a usar fuerza letal contra cualquiera que intente detenerlos. Como parte de nuestro protocolo de seguridad estándar, el material confidencial se integró en otro envío y se guardó en la bóveda automatizada. Deberán encontrar los códigos de recuperación correspondientes para el material confidencial e introducirlos en la cinta transportadora de paquetes para recuperar las cajas. Los códigos de recuperación se almacenan localmente en tabletas de datos y solo se entregan al personal de alto rango. Esperemos que estén vivos para ayudarlos, pero considerando el apagón total de comunicaciones, tememos que no sea así. Existe la posibilidad de que Nine Tails ya se haya apoderado de las tabletas de datos. Una vez que haya reunido todo el material confidencial, deberá entregarlo en ~mission(dropoff1|address). El pago está condicionado a su entrega. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+        <v> Proteger el sitio y obtener materiales confidenciales.</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>ATENCIÓN: Mercenarios con experiencia en manejo de carga[NL][NL]Nueve Colas están atacando una de nuestras instalaciones en ~misión(Ubicación|dirección). Como acaban de recibir un envío de material confidencial, no creemos que sea una coincidencia. BlacJac necesita que alguien se apresure al lugar y asegure estas cajas importantes antes de que lo hagan los Nueve Colas. Están autorizados a usar fuerza letal contra cualquiera que intente detenerlos. [NL][NL]Como parte de nuestro protocolo de seguridad estándar, el material confidencial se integró en otro envío y se guardó en la bóveda automatizada. Deberán encontrar los códigos de recuperación correspondientes para el material confidencial e ingresarlos en la cinta transportadora de paquetes para recuperar las cajas. Los códigos de recuperación se almacenan localmente en tabletas de datos y solo se entregan al personal de alto rango. Esperemos que estén vivos para ayudarlos, pero considerando el apagón total de comunicaciones, tememos que no sea el caso. Existe la posibilidad de que Nueve Colas ya se hayan apoderado de las tabletas de datos. [NL][NL]Una vez que haya reunido todos los materiales confidenciales, deberá entregarlos en ~mission(dropoff1|address). El pago está condicionado a su entrega.[NL][NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección garantizada"</v>
       </c>
     </row>
     <row r="72">
@@ -762,9 +762,9 @@
         <v>Proteger el sitio de amenazas menores</v>
       </c>
     </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73" t="str" xml:space="preserve">
-        <v xml:space="preserve"> ATENCIÓN: Operadores Mercenarios Verificados. Uno de los sitios bajo la supervisión de BlacJac ha tenido enfrentamientos con algunos delincuentes locales. Les pedimos que se dirijan a ~mission(Ubicación|Dirección) y aseguren el sitio de estas amenazas. Según los primeros informes, esto será bastante sencillo, pero si lo desean, pueden reclutar un equipo para que les brinde apoyo adicional. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="73">
+      <c r="A73" t="str">
+        <v> ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Uno de los sitios bajo la jurisdicción de BlacJac ha estado teniendo enfrentamientos con algunos forajidos locales. Nos gustaría que se dirigieran a ~mission(Ubicación|Dirección) y aseguraran el sitio de estas amenazas hostiles.[NL][NL]Según los primeros informes, espero que esto sea un asunto bastante sencillo, pero si les hace sentir más seguros, no duden en reclutar un equipo para que les brinde apoyo adicional.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="74">
@@ -772,9 +772,9 @@
         <v> Proteja el sitio de amenazas</v>
       </c>
     </row>
-    <row r="75" xml:space="preserve">
-      <c r="A75" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que algunos matones locales han estado haciendo amenazas contra ~mission(Location|Address). BlacJac busca que formen un equipo para proteger el sitio de estas amenazas. Y aunque a todos nos encantan los créditos, no recomiendo intentar hacerlo solos. Contratar un equipo sería beneficioso para su sustento. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Nos han informado que algunos matones locales han estado haciendo amenazas contra ~mission(Location|Address). BlacJac busca que formen un equipo para proteger el sitio de estas amenazas hostiles.[NL][NL]Y aunque a todos nos encantan los créditos, no recomiendo intentar hacer esto solos. Contratar un equipo sería beneficioso para su sustento.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"</v>
       </c>
     </row>
     <row r="76">
@@ -782,9 +782,9 @@
         <v> Proteja el sitio de amenazas peligrosas.</v>
       </c>
     </row>
-    <row r="77" xml:space="preserve">
-      <c r="A77" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. He recibido un informe de que algunos operadores planean un ataque contra ~mission(Location|Address). BlacJac les pide que formen un equipo para defender el sitio de esta peligrosa amenaza. Se recomienda encarecidamente no intentar completar este contrato en solitario. Contratar un equipo de mercenarios experimentados para que les brinden apoyo sería la opción más inteligente. Gracias, Gloria Mesa, Supervisora de Contratos Privados de BlacJac Security. "Protección garantizada".</v>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]He recibido un informe de que algunos operadores planean atacar ~mission(Location|Address). BlacJac quiere que formen un equipo y defiendan el sitio de esta peligrosa amenaza.[NL][NL]Se recomienda encarecidamente que no intenten realizar este contrato solos. Contratar un equipo de mercenarios expertos para que les brinden apoyo sería la opción más inteligente.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="78">
@@ -792,9 +792,9 @@
         <v> Eliminar el alijo de drogas</v>
       </c>
     </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Parece que hay un nuevo operador intentando fabricar drogas en ~mission(Location|Address), pero el producto que está produciendo es extremadamente tóxico. Estamos analizando cómo proceder con los arrestos, pero lo importante es evitar que se distribuya más de su mercancía. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. Es muy probable que la instalación no esté abandonada, así que podrían encontrarse con estos delincuentes al llegar. Prepárense para una pelea. Pero si su habilidad con las armas es similar a su química, probablemente no será muy dura. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Parece que hay un nuevo operador intentando fabricar drogas en ~mission(Location|Address), pero el producto que está produciendo es extremadamente tóxico.[NL][NL]Estamos analizando cómo manejar los arrestos, pero lo importante es evitar que se distribuya más de su suministro. Necesito que vayas allí y destruyas las drogas que están almacenando en el lugar.[NL][NL]Hay muchas posibilidades de que la instalación no esté abandonada, así que podrías encontrarte con estos matones cuando vayas allí, así que prepárate para una pelea. Pero si sus habilidades con las armas son como su química, probablemente no será una pelea muy dura.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="80">
@@ -802,9 +802,9 @@
         <v> Destruir drogas peligrosas</v>
       </c>
     </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Unos químicos emprendedores han creado un nuevo producto que es el doble de potente y letal que el original. Hemos podido rastrear algunas muestras hasta la fuente en ~mission(Location|Address). BlacJac quiere que vayas cuanto antes para destruir todo el lote antes de que pueda perjudicar a más personas. Ya nos ocuparemos de los arrestos después. Por lo que sabemos de este grupo, debes esperar una fuerte resistencia al intentar eliminar el alijo. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Algunos químicos emprendedores han creado un nuevo producto que es el doble de potente y el doble de letal que el producto normal. Pudimos rastrear algunas muestras hasta la fuente en ~mission(Location|Address). [NL][NL]BlacJac quiere que vayas lo antes posible para destruir todo el lote antes de que pueda dañar a más personas. Podemos preocuparnos por hacer arrestos después.[NL][NL]Por todo lo que sabemos sobre este grupo, debes esperar encontrar una fuerte resistencia al intentar eliminar el alijo.[NL][NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="82">
@@ -812,9 +812,9 @@
         <v> Eliminar las drogas</v>
       </c>
     </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos enteramos de que un sindicato adulteró un paquete de drogas de un rival y está causando caos en las calles. Los forenses han identificado la fuente: una planta de producción ubicada en ~mission(Location|Address). Se rumorea que los fabricantes de drogas ni siquiera saben que tienen droga envenenada. Estamos analizando cómo proceder con los arrestos, pero lo importante es sacar esta porquería de las calles ahora. Necesito que vayan allí y destruyan las drogas que almacenan en el lugar. No les hará ninguna gracia, así que probablemente tendrán que enfrentarse a una pelea, pero lo importante es eliminar el producto. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección Proporcionada".</v>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Nos enteramos de que un sindicato adulteró un paquete de drogas de un rival y está causando caos en las calles. Los forenses han identificado la fuente, una instalación de producción en ~mission(Location|Address). Se rumorea que los fabricantes de drogas ni siquiera saben que tienen una cosecha envenenada.[NL][NL]Estamos analizando cómo manejar los arrestos, pero lo importante es sacar esta porquería de las calles ahora. Necesito que vayas allí y destruyas las drogas que están almacenando en el lugar.[NL][NL]No estarán contentos con esto, así que probablemente tendrás que enfrentarte a una pelea, pero lo importante es eliminar el producto.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"</v>
       </c>
     </row>
     <row r="84">
@@ -822,9 +822,9 @@
         <v> Proteger el sitio</v>
       </c>
     </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. El equipo de seguridad de ~mission(Location|Address) nos ha informado de que algunos delincuentes locales han estado realizando ataques. BlacJac busca que acudan al lugar para ayudar a protegerlo de amenazas hostiles. Asegúrense de controlar el fuego allí abajo. No quiero oír hablar de ningún incidente entre fuerzas propias. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Hemos recibido información del equipo de seguridad en ~mission(Location|Address) de que algunos delincuentes locales han estado lanzando ataques. BlacJac busca que vayas al sitio y ayudes a protegerlo de amenazas hostiles.[NL][NL]Asegúrate de controlar el fuego allí abajo. No quiero oír hablar de ningún incidente entre compañeros.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"</v>
       </c>
     </row>
     <row r="86">
@@ -832,9 +832,9 @@
         <v> Contrato de prueba del sitio de protección</v>
       </c>
     </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. BlacJac busca ampliar su equipo de profesionales de seguridad. Para evaluar si usted encaja en el perfil, le solicitamos que preste apoyo en ~mission(Location|Address), ya que han tenido problemas con personas hostiles en la zona. Si puede ayudar a proteger el sitio y eliminar la amenaza, podremos ofrecerle más trabajo de seguridad. Tenga en cuenta que no se tolerarán incidentes de fuego amigo. Buena suerte, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]BlacJac busca ampliar su lista de profesionales de seguridad. Para evaluar si usted encaja bien, nos gustaría que brindara apoyo en ~mission(Ubicación|Dirección), ya que han tenido problemas con algunos hostiles en el área.[NL][NL]Si puede ayudar a proteger el sitio y eliminar la amenaza, podremos ofrecerle más trabajo de seguridad.[NL][NL]Tenga en cuenta que los incidentes de fuego amigo no serán tolerados.[NL][NL]Buena suerte,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="88">
@@ -842,9 +842,9 @@
         <v> Contrato de prueba del sitio de protección</v>
       </c>
     </row>
-    <row r="89" xml:space="preserve">
-      <c r="A89" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Exoperador Mercenario. Sé que BlacJac dejó de ofrecer servicios de seguridad, pero debido a cambios en el personal, se decidió ofrecerle otra oportunidad. Nos han informado que ~mission(Location|Address) necesita ayuda para lidiar con una banda local de forajidos. BlacJac busca que usted acuda al lugar y ayude a eliminar esta amenaza. Y dado que su situación ya es delicada, no quiero oír que haya estado involucrado en ningún incidente de fuego amigo. Si logra llevar a cabo esta operación con éxito, podemos considerar su reincorporación. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>ATENCIÓN: Exoperador Mercenario[NL][NL]Sé que BlacJac dejó de ofrecer servicios de seguridad, pero debido a cambios en el personal, se decidió ofrecerle otra oportunidad.[NL][NL]Nos enteramos de que ~misión(Ubicación|Dirección) necesita ayuda para lidiar con una banda local de forajidos. BlacJac busca que usted vaya al lugar y ayude a eliminar esta amenaza.[NL][NL]Y como ya está en una situación delicada, no quiero oír que estuvo involucrado en ningún incidente de fuego amigo.[NL][NL]Si puede llevar a cabo esta operación, podemos ver si podemos reincorporarlo.[NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"[NL]</v>
       </c>
     </row>
     <row r="90">
@@ -852,9 +852,9 @@
         <v> Despejar el sitio</v>
       </c>
     </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91" t="str" xml:space="preserve">
-        <v xml:space="preserve">ATENCIÓN: Operadores Mercenarios Verificados. Nos han informado que ~mission(Location|Address) está siendo utilizada por delincuentes locales como base de operaciones. BlacJac busca que ustedes realicen una inspección del sitio y eliminen a cualquier persona hostil. Nuestros primeros informes indican que es muy probable que la banda tenga civiles trabajando para ellos en el lugar. No buscamos ser noticia, así que recuerden que solo están autorizados a interactuar con personas hostiles confirmadas. Gracias, Gloria Mesa, Supervisora de Contratos Privados, BlacJac Security, "Protección garantizada".</v>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>ATENCIÓN: Operadores Mercenarios Verificados[NL][NL]Nos han informado que ~mission(Location|Address) está siendo utilizada por algunos criminales locales como base de operaciones. BlacJac busca que usted inspeccione el sitio y elimine a cualquier persona hostil. [NL][NL]Nuestros primeros informes indican que hay una alta probabilidad de que la banda tenga civiles trabajando para ellos en el lugar. No buscamos ser noticia, así que recuerde que solo está autorizado a interactuar con personas hostiles confirmadas. [NL][NL]Gracias,[NL]Gloria Mesa[NL][NL]Supervisora de Contratos Privados[NL]BlacJac Security, "Protección Proporcionada"</v>
       </c>
     </row>
     <row r="92">
@@ -862,9 +862,9 @@
         <v> Buscando Zeta-Prolanide</v>
       </c>
     </row>
-    <row r="93" xml:space="preserve">
-      <c r="A93" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Se rumorea que han robado una gran cantidad de Zeta-Prolanida en ~mission(Location|address). Si encuentras alguna, tráela a ~mission(DropOffLocation|address) y te aseguraremos un buen precio. Si no, puedes rechazar esta oferta sin problema.</v>
+    <row r="93">
+      <c r="A93" t="str">
+        <v> Se rumorea que se ha robado mucho Zeta-Prolanide de ~mission(Location|address).[NL][NL]Si encuentras algo, tráelo a ~mission(DropOffLocation|address) y nos aseguraremos de que obtengas un buen precio.[NL][NL]Y si no, puedes abandonar esta oferta, sin resentimientos.</v>
       </c>
     </row>
     <row r="94">
@@ -872,9 +872,9 @@
         <v> ALERTA DE CDF: ~misión(Ubicación) Se necesitan agentes para bloquear el acceso</v>
       </c>
     </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95" t="str" xml:space="preserve">
-        <v xml:space="preserve">*PARA DIFUSIÓN INMEDIATA EN TODO EL SISTEMA* Una flota hostil de naves equipadas con inhibidores cuánticos ha creado un bloqueo alrededor de ~mission(Location|address), ha desactivado las torretas defensivas de la estación y ha robado una gran cantidad de Zeta-Prolanida. En respuesta, la CDF ha recibido autorización para activar su fuerza de voluntarios. Aunque la situación general es crítica, el robo de la Zeta-Prolanida es nuestra prioridad. Sin una acción directa, la pérdida de las reservas de Zeta-Prolanida del sector podría tener efectos devastadores en la economía de todo el sistema. Mientras las fuerzas de seguridad locales investigan la incursión, han rastreado el inventario robado hasta varias ubicaciones. Los voluntarios de la CDF tienen la misión de dirigirse a estas ubicaciones, recuperar la Zeta-Prolanida robada y transportarla de vuelta a la estación antes de que el material se degrade por completo y deje de ser viable. Tengan cuidado, la información sugiere que los cúmulos más grandes de Zeta-Prolanida tienen una mayor presencia de delincuentes. Dado que el tiempo apremia, se recomienda encarecidamente contar con un rayo tractor para facilitar el traslado de la carga. Como incentivo adicional, los voluntarios recibirán bonificaciones periódicas por su colaboración.</v>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>*PARA PUBLICACIÓN INMEDIATA EN TODO EL SISTEMA*[NL][NL]Una flota hostil de naves equipadas con inhibidores cuánticos ha creado un bloqueo alrededor de ~mission(Location|address), ha desactivado las torretas defensivas de la estación y ha robado una gran cantidad de Zeta-Prolanida. En respuesta, la CDF ha recibido autorización para activar su fuerza de voluntarios. [NL][NL]Aunque la situación general es crítica, el robo de la Zeta-Prolanida es nuestra prioridad. Sin una acción directa, la pérdida de las reservas de Zeta-Prolanida del sector podría tener efectos devastadores en la economía general de todo el sistema. [NL][NL]Mientras las fuerzas de seguridad locales investigan la incursión, han rastreado el inventario robado hasta varias ubicaciones. Los voluntarios de la CDF tienen la tarea de dirigirse a estas ubicaciones, recuperar la Zeta-Prolanida robada y transferirla de vuelta a la estación antes de que el material se degrade por completo y deje de ser viable. Solo ten cuidado, la inteligencia sugiere que los grupos más grandes de Zeta-Prolanide tienen una mayor presencia de forajidos.[NL][NL]Como el tiempo es esencial, se recomienda encarecidamente tener un rayo tractor para ayudar a mover la carga.[NL][NL]Como incentivo adicional, los voluntarios recibirán pagos de bonificación regulares por sus esfuerzos combinados.</v>
       </c>
     </row>
     <row r="96">
@@ -892,9 +892,9 @@
         <v> Superando el desafío</v>
       </c>
     </row>
-    <row r="99" xml:space="preserve">
-      <c r="A99" t="str" xml:space="preserve">
-        <v xml:space="preserve"> La CDF se ha asociado con Anvil Aerospace para encontrar a los operativos más capaces del sistema. Si encuentras una de estas certificaciones Platino, puedes canjear el boleto en un quiosco de naves en New Deal, Astro Armada o Crusader Showroom por un F8C gratis. La condición es que tu identidad y ubicación se han compartido con los participantes de todo el sistema. Para los demás, si logras detener al poseedor del boleto antes de que llegue al quiosco, puedes reclamarlo para ti. Quien lo consiga no solo recibirá este caza de superioridad de última generación, sino que también demostrará que tiene lo necesario para las misiones más difíciles de la CDF. ¡Buena suerte!</v>
+    <row r="99">
+      <c r="A99" t="str">
+        <v> La CDF se ha asociado con Anvil Aerospace para encontrar a los operativos más capaces del sistema. [NL][NL]Si encuentras una de estas certificaciones Platino, puedes canjear el boleto en un quiosco de naves en New Deal, Astro Armada o Crusader Showroom por un F8C gratis. [NL][NL]La condición es que tu identidad y ubicación se han compartido con los participantes de todo el sistema. Para todos los demás, si puedes detener al poseedor del boleto antes de que llegue al quiosco, puedes reclamar el boleto para ti. [NL][NL]Quien lo logre no solo recibirá este caza de superioridad de próxima generación, sino que también demostrará que tiene lo que se necesita para las misiones más difíciles de la CDF. [NL][NL]Buena suerte.</v>
       </c>
     </row>
     <row r="100">
@@ -902,9 +902,9 @@
         <v> Eliminar las estaciones de servicio</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos estado teniendo problemas cada vez mayores con los forajidos en ~mission(Location|Address) y ya no podemos quedarnos de brazos cruzados mientras sus acciones agresivas perjudican a nuestra comunidad. Somos cautelosos a la hora de lanzar un ataque a gran escala, pero creemos que si se agotan sus reservas de combustible, se disuadirán de realizar más acciones hostiles. Si le es posible, le agradecería que se encargara personalmente de la destrucción del combustible. Un barco capaz de lanzar misiles probablemente sería lo más lógico, pero la decisión final es suya. Gracias, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Hemos estado teniendo problemas cada vez mayores con los forajidos en ~mission(Location|Address) y ya no podemos quedarnos de brazos cruzados mientras sus acciones agresivas perjudican a nuestra comunidad. [NL][NL]Somos cautelosos a la hora de lanzar un ataque a gran escala, pero creemos que si se agotan sus reservas de combustible, se disuadirán de realizar más acciones hostiles. [NL][NL]Si te es posible, te agradecería que te encargaras personalmente de la destrucción del combustible. Un barco capaz de lanzar misiles probablemente sería lo más sensato, pero te lo dejo a ti.[NL][NL]Gracias,[NL] [NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="102">
@@ -912,9 +912,9 @@
         <v> Reducir la preparación operativa de Outlaw</v>
       </c>
     </row>
-    <row r="103" xml:space="preserve">
-      <c r="A103" t="str" xml:space="preserve">
-        <v xml:space="preserve">En ~mission(Location|Address) hay un grupo de forajidos que se han vuelto cada vez más osados en sus ataques contra los activos de Citizens for Prosperity en el sistema. Para minimizar las pérdidas de vidas, primero intentaremos convencerlos de que se trasladen a otro lugar desactivando sus generadores y destruyendo sus reservas de combustible. Con suerte, eso será suficiente para que busquen un lugar más seguro. Gracias, Lima Endicott, Despachadora Principal de Citizens for Prosperity.</v>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Hay un grupo de forajidos en ~mission(Location|Address) que se han vuelto cada vez más audaces en sus ataques contra los activos de Citizens for Prosperity en el sistema. [NL][NL]Para minimizar la pérdida de vidas, primero queremos intentar convencerlos de que se trasladen a otro lugar desactivando sus generadores y destruyendo sus reservas de combustible. [NL][NL]Con suerte, eso debería ser suficiente para convencerlos de que se vayan a otro lugar.[NL][NL]Gracias,[NL] [NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="104">
@@ -922,9 +922,9 @@
         <v> Alerta: ~misión(Ubicación) bajo ataque</v>
       </c>
     </row>
-    <row r="105" xml:space="preserve">
-      <c r="A105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Necesitamos que todo el personal de seguridad disponible se presente en ~mission(Location|Address). Un grupo de individuos armados ha atacado uno de nuestros puestos de avanzada y necesitamos ayuda urgentemente. Aunque el grupo parece no estar afiliado a ninguna de las bandas conocidas, hemos recibido información de que su líder es ~mission(TargetName), un forajido local con una reputación temible. Por favor, diríjanse lo antes posible y aseguren la zona eliminando a los forajidos y a ~mission(TargetName|Last). Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Necesitamos que todo el personal de seguridad disponible se presente en ~mission(Location|Address). Un grupo de individuos armados ha atacado uno de nuestros puestos de avanzada y necesitamos ayuda urgentemente. Aunque el grupo parece no estar afiliado a ninguna de las bandas conocidas, hemos recibido información de que su líder es ~mission(TargetName), un forajido local con una reputación temible.[NL][NL]Por favor, diríjanse lo antes posible y aseguren la zona eliminando a los forajidos y a ~mission(TargetName|Last).[NL][NL]Lima Endicott[NL]Operadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="106">
@@ -932,9 +932,9 @@
         <v> Recuperando terreno de los cazatalentos</v>
       </c>
     </row>
-    <row r="107" xml:space="preserve">
-      <c r="A107" t="str" xml:space="preserve">
-        <v xml:space="preserve">Actualmente buscamos agentes de seguridad cualificados y disponibles para dirigirse a ~mission(Location|Address) y recuperar una instalación de CFP que ha sido tomada por Headhunters. El grupo que actualmente ocupa el puesto de avanzada está liderado por ~mission(TargetName), un Headhunter de renombre con un historial de agresiones contra la población local y los voluntarios de CFP. Necesitamos asegurar a todos los Headhunters y eliminar a ~mission(TargetName|Last). Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Actualmente buscamos agentes de seguridad cualificados y disponibles para dirigirse a ~mission(Location|Address) y recuperar una instalación de CFP que ha sido tomada por Headhunters. [NL][NL]El grupo que actualmente ocupa el puesto avanzado está liderado por ~mission(TargetName), un Headhunter de cierta importancia con un historial de agresiones contra los lugareños y los voluntarios de CFP.[NL][NL]Necesitamos asegurar a todos los Headhunters y eliminar a ~mission(TargetName|Last).[NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="108">
@@ -942,19 +942,19 @@
         <v> Ayuda a defender ~misión(Ubicación) de los Cazadores de Cabezas</v>
       </c>
     </row>
-    <row r="109" xml:space="preserve">
-      <c r="A109" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Acabamos de recibir una comunicación urgente de ~mission(Location|Address) y buscamos especialistas en combate disponibles para ayudar a repeler un ataque de Headhunters. Todavía hay hostiles en el lugar y se han reportado varias bajas, por lo que necesitamos que esto se resuelva rápidamente. Proporcionaré todos los datos relevantes una vez que acepten mi solicitud. Gracias por su ayuda. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="109">
+      <c r="A109" t="str">
+        <v> Acabamos de recibir una comunicación urgente de ~mission(Location|Address) y buscamos especialistas en combate disponibles para ayudar a repeler un ataque de Headhunters. Todavía hay hostiles en el lugar y se reportan varias bajas, por lo que necesitamos que esto se resuelva rápidamente. [NL][NL]Proporcionaré todos los datos relevantes una vez aceptada su solicitud. Gracias por su ayuda.[NL][NL]Lima Endicott[NL]Operadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v> Ataque de forajidos en ~misión(Ubicación)</v>
-      </c>
-    </row>
-    <row r="111" xml:space="preserve">
-      <c r="A111" t="str" xml:space="preserve">
-        <v xml:space="preserve">Varios grupos de CFP cerca de ~mission(Location|Address) acaban de ser atacados por un grupo de forajidos liderado por ~mission(TargetName). Buscamos especialistas en combate disponibles para ayudar a recuperar los puestos de avanzada. Puedo proporcionar las ubicaciones una vez que acepten la solicitud, pero necesitamos despejar el puesto de avanzada principal y las instalaciones satélite de todas las fuerzas hostiles y eliminar a ~mission(TargetName|Last), ya que es poco probable que no cesen sus hostilidades si escapan. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+        <v>Ataque de forajidos en ~misión(Ubicación)</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v> Varios grupos de CFP cerca de ~mission(Location|Address) acaban de ser atacados por un grupo de forajidos liderado por ~mission(TargetName). Buscamos especialistas en combate disponibles para ayudar a retomar los puestos de avanzada.[NL][NL]Puedo proporcionar las ubicaciones una vez aceptada la solicitud, pero necesitamos despejar el puesto de avanzada principal y las instalaciones satélite de todas las fuerzas hostiles y eliminar a ~mission(TargetName|Last), ya que es poco probable que no cesen sus hostilidades si escapan.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="112">
@@ -962,9 +962,9 @@
         <v> Recuperando puestos avanzados de manos de los cazadores de cabezas</v>
       </c>
     </row>
-    <row r="113" xml:space="preserve">
-      <c r="A113" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ciudadanos por la Prosperidad busca agentes de seguridad disponibles para recuperar varias antiguas instalaciones de CFP cerca de ~mission(Location|Address) del control de Headhunter. Estos centros nos fueron arrebatados violentamente por ~mission(TargetName), lo que provocó la muerte de muchos voluntarios. Recuperar el control de estos puestos avanzados contribuirá a la estabilidad del sistema. Los informes indican que ~mission(TargetName|Last) suele esconderse entre sus filas, por lo que probablemente aparecerán una vez que hayas eliminado a la mayoría de los enemigos. Los XenoThreat están entrenados y motivados, por lo que no se rendirán fácilmente. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Ciudadanos por la Prosperidad busca agentes de seguridad disponibles para recuperar varias antiguas instalaciones de CFP cerca de ~mission(Location|Address) del control de Headhunter. Estos grupos nos fueron arrebatados violentamente por ~mission(TargetName), lo que resultó en la muerte de muchos voluntarios.[NL][NL]Recuperar el control de estos puestos avanzados contribuirá a la estabilidad del sistema. Los informes indican que ~mission(TargetName|Last) tiende a esconderse entre sus filas, por lo que probablemente aparecerán una vez que hayas eliminado a la mayoría de los hostiles.[NL][NL]XenoThreat está entrenado y motivado, por lo que no se rendirá fácilmente.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="114">
@@ -972,9 +972,9 @@
         <v> Recuperando puestos avanzados de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="115" xml:space="preserve">
-      <c r="A115" t="str" xml:space="preserve">
-        <v xml:space="preserve">Buscamos personal de seguridad disponible para recuperar varios clústeres perdidos a manos de agresores XenoThreat. Ubicados cerca de ~mission(Location|Address), fueron tomados en brutales ataques liderados por ~mission(TargetName), un notorio teniente de XenoThreat. Queremos recuperar estos clústeres para restablecer las operaciones y continuar con nuestro trabajo. Deberás eliminar a todos los enemigos que aún se encuentren en el lugar, así como a ~mission(TargetName|Last). Recuerda que los XenoThreat están altamente entrenados y son rápidos en el combate, así que prepárate. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Buscamos personal de seguridad disponible para recuperar varios clústeres perdidos previamente a manos de agresores XenoThreat. Ubicados cerca de ~mission(Location|Address), fueron tomados en brutales ataques liderados por ~mission(TargetName), un notorio teniente de XenoThreat.[NL][NL]Buscamos recuperar estos clústeres para restablecer las operaciones y continuar con nuestro buen trabajo. Deberás eliminar a todos los hostiles que aún se encuentren en el sitio, así como a ~mission(TargetName|Last).[NL][NL]Solo un recordatorio: los XenoThreat están altamente entrenados y son rápidos para luchar, así que prepárate en consecuencia.[NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="116">
@@ -982,9 +982,9 @@
         <v> Es necesario retomar varios puestos avanzados de la CFP.</v>
       </c>
     </row>
-    <row r="117" xml:space="preserve">
-      <c r="A117" t="str" xml:space="preserve">
-        <v xml:space="preserve">La presencia de delincuentes en esta zona se ha vuelto mucho más audaz últimamente y muchas personas están resultando heridas. Recientemente hemos perdido varios grupos de delincuentes alrededor de ~mission(Location|Address). Si bien no nos gusta tener que recurrir a la violencia, la junta ha reconocido que estas ubicaciones son cruciales para establecer la estabilidad en el sistema y ha autorizado el uso de un dispositivo de seguridad para recuperarlas. También sabemos que los delincuentes infiltrados están liderados por ~mission(TargetName), quien tiene un historial de ataques contra intereses de CFP. La junta desea que se tomen medidas contra ~mission(TargetName|Last) para prevenir futuros ataques. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>La presencia de delincuentes en esta zona se ha vuelto mucho más audaz últimamente y muchas personas están resultando heridas. Recientemente hemos perdido varios grupos alrededor de ~mission(Location|Address). Si bien no nos gusta tener que recurrir a la violencia, la junta ha reconocido que estas ubicaciones son cruciales para establecer la estabilidad en el sistema y ha autorizado el uso de un equipo de seguridad para recuperarlas.[NL][NL]También sabemos que los hostiles infiltrados están siendo liderados por ~mission(TargetName), quien tiene un historial de ataques contra intereses de CFP. La junta desea que se tomen medidas contra ~mission(TargetName|Last) para prevenir futuros ataques.[NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="118">
@@ -992,9 +992,9 @@
         <v> Recuperando clústeres de las manos de los cazatalentos</v>
       </c>
     </row>
-    <row r="119" xml:space="preserve">
-      <c r="A119" t="str" xml:space="preserve">
-        <v xml:space="preserve">La junta directiva de Ciudadanos por la Prosperidad acaba de autorizar fondos para contratar personal de seguridad con el fin de recuperar varios grupos cerca de ~mission(Location|Address) que han caído en manos de los Cazadores de Cabezas. Aunque intentamos aceptar la pérdida, se ha hecho evidente que son cruciales para nuestras operaciones en el sistema. Deberás despejar cada una de las ubicaciones que se te proporcionarán, pero, lo que es más importante, también deberás eliminar a ~mission(TargetName), quien está a cargo de los hostiles en el lugar. Estos Cazadores de Cabezas están fuertemente infiltrados y tienen un historial de violencia, así que prepárate en consecuencia. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>La junta directiva de Ciudadanos por la Prosperidad acaba de autorizar fondos para contratar personal de seguridad para recuperar varios grupos cerca de ~mission(Location|Address) que han caído en manos de los Cazadores de Cabezas. Aunque intentamos aceptar la pérdida, se ha hecho evidente que son cruciales para nuestras operaciones en el sistema.[NL][NL]Deberás despejar cada una de las ubicaciones que se te proporcionarán, pero, más importante aún, también deberás eliminar a ~mission(TargetName), quien está a cargo de los hostiles en el lugar.[NL][NL]Estos Cazadores de Cabezas están fuertemente infiltrados y tienen un historial de violencia, así que debes prepararte en consecuencia. [NL][NL]Lima Endicott[NL]Despachadora principal[NL]Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="120">
@@ -1002,9 +1002,9 @@
         <v xml:space="preserve"> Campaña para recuperar los puestos avanzados de XenoThreat</v>
       </c>
     </row>
-    <row r="121" xml:space="preserve">
-      <c r="A121" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aunque Ciudadanos por la Prosperidad está comprometido con el cambio por medios no violentos, se ha hecho evidente que podrían ser necesarias excepciones. Las zonas seguras de CFP cerca de ~mission(Location|Address) fueron tomadas recientemente y de forma violenta por fuerzas XenoThreat bajo el mando de ~mission(TargetName). Buscamos operativos de combate disponibles para ayudar a recuperar estos puestos avanzados. Sin duda, será una tarea difícil, ya que las fuerzas XenoThreat están altamente entrenadas y ansiosas por luchar, así que prepárense en consecuencia. Además de eliminar cada grupo de fuerzas XenoThreat, deberán eliminar a ~mission(TargetName|Last), cuya pérdida sin duda hará que el sistema sea más seguro. Buena suerte, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Aunque Ciudadanos por la Prosperidad está comprometido con el cambio por medios no violentos, se ha hecho evidente que podrían ser necesarias excepciones. Las zonas seguras de CFP cerca de ~mission(Location|Address) fueron tomadas recientemente y violentamente por fuerzas XenoThreat bajo el mando de ~mission(TargetName).[NL][NL]Buscamos operativos de combate disponibles para ayudar a recuperar estos puestos avanzados. Sin duda, será una tarea difícil, ya que XenoThreat está altamente entrenado y ansioso por luchar, así que prepárense en consecuencia.[NL][NL]Además de eliminar cada grupo de fuerzas XenoThreat, deberán eliminar a ~mission(TargetName|Last), cuya pérdida sin duda hará que el sistema sea más seguro.[NL][NL]Buena suerte,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="122">
@@ -1012,9 +1012,9 @@
         <v> Se necesita ayuda en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="123" xml:space="preserve">
-      <c r="A123" t="str" xml:space="preserve">
-        <v xml:space="preserve">Recibimos una llamada de auxilio de ~mission(Location|Address) indicando que están siendo asaltados por un pequeño grupo de forajidos. ~mission(Location|CaveSize) Aunque remoto, este puesto de avanzada es una pieza crucial de la infraestructura de CFP en la zona, por lo que debemos recuperarlo. Lima Endicott, Despachadora principal, Ciudadanos por la Prosperidad</v>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Recibimos una llamada de auxilio de ~mission(Location|Address) indicando que están siendo asaltados por un pequeño grupo de forajidos. ~mission(Location|CaveSize) Aunque remoto, este puesto de avanzada es una pieza crucial de la infraestructura de CFP en la zona, así que debemos recuperarlo.[NL][NL]Lima Endicott[NL]Operadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="124">
@@ -1022,9 +1022,9 @@
         <v> Ataque de Headhunter en ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="125" xml:space="preserve">
-      <c r="A125" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Acabamos de recibir una llamada de auxilio desde ~mission(Location|Address) informando que una gran fuerza de Headhunters ha atacado nuestro puesto de avanzada. Se han registrado varios muertos y heridos entre quienes lograron huir. Buscamos personal de seguridad disponible para que se dirija al lugar y retome el control del puesto. Testigos han identificado a los atacantes como miembros de élite de los Headhunters, así que tengan cuidado y, si pueden, envíen refuerzos. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="125">
+      <c r="A125" t="str">
+        <v> Acabamos de recibir una llamada de auxilio desde ~mission(Location|Address) informando que una gran fuerza de Headhunters ha atacado nuestro puesto de avanzada. Se han registrado varios muertos y heridos entre quienes lograron huir. Buscamos personal de seguridad disponible para que se dirija al lugar y retome el puesto. Los testigos identificaron a los atacantes como miembros de élite de los Headhunters, así que tengan cuidado y, si pueden, traigan ayuda. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="126">
@@ -1032,9 +1032,9 @@
         <v> Solicitar ayuda: ~misión(Ubicación)</v>
       </c>
     </row>
-    <row r="127" xml:space="preserve">
-      <c r="A127" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos recibido una llamada de auxilio desde ~mission(Location|Address). Un grupo de asaltantes desconocidos ha lanzado un ataque. Se han reportado varias muertes y necesitamos recuperar el puesto de avanzada. Sé que esto está lejos de su posición actual, pero estamos desesperados por asegurar la zona y que el puesto de avanzada vuelva a estar operativo. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Hemos recibido una llamada de auxilio de ~mission(Location|Address). Un grupo de asaltantes desconocidos ha lanzado un ataque. Se han reportado varias muertes y necesitamos recuperar el puesto de avanzada.[NL][NL]Sé que esto está lejos de tu posición actual, pero estamos desesperados por asegurar la zona y que el puesto de avanzada vuelva a estar operativo.[NL][NL]Lima Endicott[NL]Operadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="128">
@@ -1042,9 +1042,9 @@
         <v> Defiende ~misión(Ubicación) de los forajidos</v>
       </c>
     </row>
-    <row r="129" xml:space="preserve">
-      <c r="A129" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Nos enteramos de que ~mission(Location|Address) está bajo amenaza de ataque por parte de forajidos y ha solicitado ayuda. Necesitamos a alguien que los proteja y ahuyente a los forajidos. Asegúrate de permanecer cerca después del ataque inicial. Con demasiada frecuencia, los forajidos ganan las peleas simplemente enviando más enemigos de los que nadie puede defender razonablemente, así que asegúrate de repeler cualquier refuerzo antes de abandonar la zona. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="129">
+      <c r="A129" t="str">
+        <v> Nos enteramos de que ~mission(Location|Address) está bajo amenaza de ataque por parte de forajidos y ha solicitado ayuda. Necesitamos a alguien que los proteja y ahuyente a los forajidos. [NL][NL]Asegúrate de permanecer cerca después de su ataque inicial. Con demasiada frecuencia, los forajidos ganan las peleas simplemente enviando más enemigos de los que nadie puede defender razonablemente, así que asegúrate de repeler cualquier refuerzo antes de abandonar la zona. [NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="130">
@@ -1052,9 +1052,9 @@
         <v> Proteger ~misión(Ubicación) del ataque de XenoThreat</v>
       </c>
     </row>
-    <row r="131" xml:space="preserve">
-      <c r="A131" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos descubierto que XenoThreat está a punto de lanzar un ataque contra ~mission(Location|Address). Si tienen éxito, se espera un alto número de bajas. Espero que con tu ayuda para defenderlos podamos evitarlo. Sabemos por encuentros anteriores que XenoThreat envía varios grupos de asalto para llevar a cabo sus ataques, así que asegúrate de no abandonar el puesto de avanzada hasta que hayas repelido a todos los refuerzos. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Hemos descubierto que XenoThreat está a punto de lanzar un ataque en ~mission(Location|Address). Si tienen éxito, se espera un alto número de bajas. Espero que con tu ayuda para defenderlos podamos evitar que eso suceda. Sabemos por encuentros anteriores que XenoThreat envía varios grupos de asalto para llevar a cabo sus ataques, así que asegúrate de no abandonar el puesto de avanzada hasta que hayas repelido a todos los refuerzos. Lima Endicott, Despachadora principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="132">
@@ -1062,9 +1062,9 @@
         <v> Proteger ~misión(Ubicación) de la incursión de XenoThreat</v>
       </c>
     </row>
-    <row r="133" xml:space="preserve">
-      <c r="A133" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Urgente! XenoThreat está atacando ~mission(Location|Address) para enviar un mensaje a otros colonos sobre las consecuencias de aceptar nuestro apoyo. Si logras repeler a los atacantes, seguramente enviarán refuerzos, así que tendrás que prepararte para múltiples asaltos. Dado que XenoThreat cuenta con muchos recursos, deberías considerar reclutar a otros para que te ayuden a mantener a todos a salvo. Contamos contigo. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>¡Urgente! [NL][NL]XenoThreat está atacando ~mission(Location|Address) para enviar un mensaje a otros colonos sobre lo que sucederá si aceptan nuestro apoyo. [NL][NL]Si logras repeler a los atacantes, seguramente enviarán fuerzas adicionales, así que tendrás que prepararte para múltiples asaltos. Dado que XenoThreat tiene muchos recursos a su disposición, deberías considerar reclutar a otros para que te ayuden a mantener a todos a salvo. [NL][NL]Todos contamos contigo. [NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="134">
@@ -1072,9 +1072,9 @@
         <v> Proteger ~misión(Ubicación) de la incursión de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="135" xml:space="preserve">
-      <c r="A135" t="str" xml:space="preserve">
-        <v xml:space="preserve">¡Urgente! XenoThreat se está movilizando para una incursión masiva con el objetivo de eliminar ~mission(Location|Address) del mapa. Eres su única esperanza para resistir este ataque y protegerlos de la crueldad de XenoThreat. Sé que te pido que te pongas en peligro, pero este sistema no cambiará a menos que personas como tú sean lo suficientemente valientes para afrontar estos peligros. Ninguna cantidad de créditos podría compensar el bien que harías al intervenir. Si estás dispuesto y eres capaz de asumir esta misión, asegúrate de llevar algunos aliados contigo. XenoThreat sin duda enviará refuerzos más fuertes una vez que se den cuenta de que están sufriendo bajas. Creemos en ti. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>¡Urgente![NL][NL]XenoThreat se está movilizando para una incursión masiva con el objetivo de eliminar ~mission(Location|Address) del mapa. Eres su única esperanza para resistir este ataque y protegerlos de la crueldad de XenoThreat.[NL][NL]Sé que te estoy pidiendo que te pongas en la línea de fuego, pero este sistema no cambiará a menos que personas como tú sean lo suficientemente valientes como para afrontar estos peligros. Ninguna cantidad de créditos podría compensar el bien que harías al intervenir.[NL][NL]Si estás dispuesto y eres capaz de asumir esta misión, asegúrate de llevar algunos aliados contigo. XenoThreat sin duda enviará refuerzos más fuertes una vez que se den cuenta de que están sufriendo bajas.[NL][NL]Creemos en ti.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="136">
@@ -1082,9 +1082,9 @@
         <v> Piloto busca apoyo en combate</v>
       </c>
     </row>
-    <row r="137" xml:space="preserve">
-      <c r="A137" t="str" xml:space="preserve">
-        <v xml:space="preserve">Uno de nuestros pilotos acababa de recoger un cargamento de suministros cerca de ~mission(Location|Address) cuando fue atacado por unos despiadados secuestradores de naves. Acabamos de recibir su señal de socorro y espero que puedan ir a brindarles apoyo en combate. Cualquier ayuda que puedan ofrecer sería crucial. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Uno de nuestros pilotos acababa de recoger un cargamento de suministros cerca de ~mission(Location|Address) cuando fueron atacados por unos despiadados secuestradores de naves. [NL][NL]Acabamos de recibir su señal de socorro y espero que puedan ir a brindarles apoyo en combate.[NL][NL]Cualquier ayuda que puedan brindar sería crucial.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="138">
@@ -1092,9 +1092,9 @@
         <v> El barco necesita asistencia de emergencia</v>
       </c>
     </row>
-    <row r="139" xml:space="preserve">
-      <c r="A139" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Una nave afiliada a Ciudadanos por la Prosperidad intentaba entregar suministros en ~mission(Location|Address) cuando fue atacada por los destinatarios, quienes se negaron a pagar y optaron por la violencia. Daré instrucciones a nuestros comerciantes para que tengan más cuidado con quién hacen negocios en el futuro, pero por ahora, les agradecería mucho su ayuda para repeler a estos atacantes. Atentamente, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
+    <row r="139">
+      <c r="A139" t="str">
+        <v> Una nave afiliada a Ciudadanos por la Prosperidad intentaba entregar suministros a ~mission(Location|Address) cuando fue atacada por los destinatarios, quienes no quisieron pagar su compra y optaron por la violencia. [NL][NL]Instruiré a nuestros comerciantes para que tengan más cuidado con quién tratan en el futuro, pero por ahora, les agradecería mucho que les echaran una mano para repeler a estos atacantes. [NL][NL]Gracias, [NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="140">
@@ -1102,9 +1102,9 @@
         <v> Convoy atrapado en un brutal ataque.</v>
       </c>
     </row>
-    <row r="141" xml:space="preserve">
-      <c r="A141" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acabamos de recibir la noticia de que un convoy de naves afiliadas a Ciudadanos por la Prosperidad ha sido atacado por forajidos y que nuestra gente necesita ayuda urgentemente. Si está disponible, necesitamos pilotos listos para el combate en ~mission(Location|Address) para defender a nuestra gente. Tenga en cuenta que en este momento crítico, no podemos permitirnos perder ni una sola nave y esperamos que, con su ayuda, todos nuestros miembros sobrevivan. Buena suerte, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Acabamos de recibir la noticia de que un convoy de naves afiliadas a Ciudadanos por la Prosperidad ha sido atacado por forajidos y que nuestra gente necesita ayuda urgentemente. [NL][NL]Si está disponible, necesitamos pilotos listos para el combate en ~mission(Location|Address) para defender a nuestra gente. Tenga en cuenta que en este momento crítico, no podemos permitirnos perder ni una sola nave y esperamos que con su ayuda todos nuestros ciudadanos sobrevivan.[NL][NL]Buena suerte,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="142">
@@ -1112,9 +1112,9 @@
         <v> Acudan en auxilio del convoy</v>
       </c>
     </row>
-    <row r="143" xml:space="preserve">
-      <c r="A143" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Estoy recibiendo informes de que un convoy de Ciudadanos por la Prosperidad que transporta suministros vitales está siendo atacado en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Perder esa carga sería un duro golpe para nuestras operaciones. Si tienes las habilidades de combate necesarias para enfrentarte a enemigos altamente agresivos, estamos más que dispuestos a pagar por tu ayuda. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="143">
+      <c r="A143" t="str">
+        <v> Estoy recibiendo informes de que un convoy de Ciudadanos por la Prosperidad que transporta suministros vitales está siendo atacado en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Perder esa carga sería un duro golpe para nuestras operaciones. [NL][NL]Si tienes las habilidades de combate necesarias para enfrentarte a enemigos muy agresivos, estamos más que dispuestos a pagar por tu ayuda. [NL][NL]Lima Endicott[NL]Despachadora principal[NL]Ciudadanos por la Prosperidad[NL]</v>
       </c>
     </row>
     <row r="144">
@@ -1122,9 +1122,9 @@
         <v> Responder a la baliza de socorro</v>
       </c>
     </row>
-    <row r="145" xml:space="preserve">
-      <c r="A145" t="str" xml:space="preserve">
-        <v xml:space="preserve">Un convoy de Ciudadanos por la Prosperidad, en una misión de reabastecimiento, lanzó una baliza de socorro cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. No responden a las comunicaciones, así que supongo que la situación es grave. Ese convoy cuenta con pilotos experimentados, así que si no responden, sin duda necesitan ayuda. Le compensaremos por brindar apoyo a ese convoy. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Un convoy de Ciudadanos por la Prosperidad en una misión de reabastecimiento lanzó una baliza de socorro cerca de &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. No responden a las comunicaciones, así que supongo que la situación es grave. Ese convoy tiene pilotos experimentados, así que si no responden, definitivamente necesitan ayuda.[NL][NL]Te compensaremos por apoyar a ese convoy. [NL][NL]Lima Endicott[NL]Operadora principal[NL]Ciudadanos por la Prosperidad[NL]</v>
       </c>
     </row>
     <row r="146">
@@ -1132,9 +1132,9 @@
         <v> Piloto en apuros</v>
       </c>
     </row>
-    <row r="147" xml:space="preserve">
-      <c r="A147" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Parece que una de las rutas que considerábamos relativamente seguras ha resultado ser lo contrario. Unos forajidos han atacado a uno de nuestros pilotos en ~mission(Location|Address) y no durará mucho sin ayuda. Les agradecería que volaran hasta allí lo antes posible para ayudarles a enfrentarse a estos atacantes. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="147">
+      <c r="A147" t="str">
+        <v> Parece que una de las rutas que considerábamos relativamente seguras ha resultado ser lo contrario. Unos forajidos han atacado a uno de nuestros pilotos en ~mission(Location|Address) y no durará mucho sin ayuda. [NL][NL]Agradecería que volaras hasta allí lo antes posible y les ayudaras a lidiar con estos atacantes.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="148">
@@ -1142,9 +1142,9 @@
         <v> Se necesita ayuda contra XenoThreat Raid</v>
       </c>
     </row>
-    <row r="149" xml:space="preserve">
-      <c r="A149" t="str" xml:space="preserve">
-        <v xml:space="preserve">La XenoThreat ha atacado sin piedad a nuestra gente y ahora necesitan urgentemente apoyo de combate y suministros médicos. Si estás disponible, deberás recoger los suministros en ~mission(Location|Address) antes de dirigirte a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Una vez allí, es importante que neutralices a todos los enemigos antes de completar la entrega de los suministros. Además, para ayudar a prevenir que un incidente como este vuelva a ocurrir, creemos que destruir los servidores de la XenoThreat en &lt;EM4&gt;~mission(Location1|Address)&lt;/EM4&gt; sería una medida disuasoria adicional. Gracias, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>La XenoThreat ha atacado sin piedad a nuestra gente y ahora necesitan desesperadamente apoyo de combate y suministros médicos.[NL][NL]Si estás disponible, primero debes recoger los suministros en ~mission(Location|Address) antes de dirigirte a &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Una vez allí, es importante que neutralices a todos los enemigos antes de completar la entrega de los suministros.[NL][NL]Además, para ayudar a prevenir que un incidente como este vuelva a ocurrir, creemos que si destruyes los servidores de la XenoThreat en &lt;EM4&gt;~mission(Location1|Address)&lt;/EM4&gt; actuaría como un elemento disuasorio adicional.[NL][NL]Gracias,[NL] [NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="150">
@@ -1152,9 +1152,9 @@
         <v> Entrega para ~misión(Destino) Lista</v>
       </c>
     </row>
-    <row r="151" xml:space="preserve">
-      <c r="A151" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¿Estás disponible para el viaje? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Hola, [NL][NL]Nos enteramos de que hay gente esperando un envío importante que no ha llegado. Resulta que, por error, lo llevaron al lugar equivocado. Mientras investigamos cómo ocurrió el error, necesitamos que alguien vaya a &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; para recoger el paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; y entregarlo en la ubicación correcta en &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;. [NL][NL]Además, para facilitarte las cosas, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. [NL][NL]¿Estás disponible para el viaje?[NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="152">
@@ -1162,9 +1162,9 @@
         <v> Múltiples entregas listas</v>
       </c>
     </row>
-    <row r="153" xml:space="preserve">
-      <c r="A153" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, necesito que me entreguen dos paquetes. El paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; debe recogerse en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; y llevarse a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;, y el paquete &lt;EM4&gt;#~mission(item2|serialnumber)&lt;/EM4&gt; va de &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt;. Debería ser una forma fácil de ganar algunos créditos. Además, para facilitarte la vida, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. ¡Buen viaje! Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Hola, [NL][NL]Necesito que me entreguen dos paquetes. El paquete &lt;EM4&gt;#~mission(item1|serialnumber)&lt;/EM4&gt; debe recogerse en &lt;EM4&gt;~mission(Pickup1|Address)&lt;/EM4&gt; y llevarse a &lt;EM4&gt;~mission(Dropoff1|Address)&lt;/EM4&gt;, y el paquete &lt;EM4&gt;#~mission(item2|serialnumber)&lt;/EM4&gt; va de &lt;EM4&gt;~mission(Pickup2|Address)&lt;/EM4&gt; a &lt;EM4&gt;~mission(Dropoff2|Address)&lt;/EM4&gt;. Debería ser una forma fácil de ganar algunos créditos. [NL][NL]Además, para facilitarte la vida, asegúrate de tener un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt; contigo. [NL][NL]Vuela seguro, [NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="154">
@@ -1172,9 +1172,9 @@
         <v> Eliminar la amenaza Xeno Idris</v>
       </c>
     </row>
-    <row r="155" xml:space="preserve">
-      <c r="A155" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hola, los rumores son ciertos. XenoThreat ha desplegado un Idris para acechar y atacar las operaciones de Ciudadanos por la Prosperidad, en una escalada dramática de su hostilidad hacia nosotros. Acabamos de recibir la noticia de que la nave, bajo el mando de ~mission(TargetName), avanza hacia ~mission(location|address). No podemos enviar nuestras fuerzas allí lo suficientemente rápido para combatirlos y necesitamos ayuda urgentemente. Buscamos a alguien lo suficientemente valiente como para enfrentarse a estos bastardos. No basta con ahuyentarlos, necesitamos garantizar que no puedan volver a atacarnos. No sé si te has enfrentado a un Idris antes, pero es una tarea titánica para alguien que lo haga solo. Recomiendo encarecidamente reclutar a otros para la causa. Saludos, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Hola, [NL][NL]Los rumores son ciertos. XenoThreat ha desplegado un Idris para acechar y atacar las operaciones de Ciudadanos por la Prosperidad en una escalada dramática de su hostilidad hacia nosotros. Acabamos de recibir la noticia de que la nave, bajo el mando de ~mission(TargetName), avanza hacia ~mission(location|address). No podemos enviar nuestras fuerzas allí lo suficientemente rápido para combatirlos y necesitamos ayuda desesperadamente. [NL][NL]Buscamos contratar a alguien lo suficientemente valiente como para enfrentarse a estos bastardos. No basta con asustarlos, necesitamos garantizar que no puedan volver a atacarnos. [NL][NL]No sé si te has enfrentado a un Idris antes, pero es una tarea difícil para alguien que lo haga solo. Recomiendo encarecidamente reclutar a otros para la causa. [NL][NL]Saludos,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Ciudadanos por la Prosperidad[NL]</v>
       </c>
     </row>
     <row r="156">
@@ -1182,9 +1182,9 @@
         <v> Ataque a un puesto de avanzada de la CFP</v>
       </c>
     </row>
-    <row r="157" xml:space="preserve">
-      <c r="A157" t="str" xml:space="preserve">
-        <v xml:space="preserve">Citizens for Prosperity busca operadores de combate disponibles para la misión en ~(Ubicación|Dirección). Un grupo de delincuentes ha lanzado un ataque no provocado y nuestro personal de seguridad necesita refuerzos con urgencia. Por favor, envíense a ~(Ubicación) con la mayor brevedad posible. ¡Buena suerte! Lima Endicott, Coordinadora de Despacho, Citizens for Prosperity</v>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Ciudadanos por la Prosperidad busca operadores de combate disponibles para la misión ~(Ubicación|Dirección). Un grupo de delincuentes ha lanzado un ataque no provocado y nuestro personal de seguridad necesita apoyo urgentemente. [NL][NL]Por favor, envíense a la misión ~(Ubicación) con la mayor urgencia y buena suerte. [NL][NL]Lima Endicott[NL]Operadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="158">
@@ -1192,9 +1192,9 @@
         <v> Se necesitan defensores contra los cazadores de cabezas</v>
       </c>
     </row>
-    <row r="159" xml:space="preserve">
-      <c r="A159" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hemos recibido una comunicación de emergencia de ~mission(Location|Address) informando que están siendo atacados por un grupo de Headhunters. Sabemos que nuestra presencia en el sistema ha molestado a los Headhunters, pero eso no justifica este ataque no provocado. Si es posible, por favor, reúnan su equipo y salgan. Tengan en cuenta que los Headhunters son combatientes experimentados y no se rendirán fácilmente. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="159">
+      <c r="A159" t="str">
+        <v> Hemos recibido una comunicación de emergencia de ~mission(Location|Address) informando que están siendo atacados por un grupo de Headhunters. Sabemos que nuestra presencia en el sistema ha molestado a los Headhunters, pero eso no justifica este ataque no provocado.[NL][NL]Si es posible, por favor, reúnan su equipo y salgan. Tengan en cuenta que los Headhunters son combatientes experimentados y no se rendirán fácilmente.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="160">
@@ -1202,9 +1202,9 @@
         <v> Protegiendo el puesto avanzado de la amenaza alienígena</v>
       </c>
     </row>
-    <row r="161" xml:space="preserve">
-      <c r="A161" t="str" xml:space="preserve">
-        <v xml:space="preserve">Fuerzas de XenoThreat lanzaron un ataque no provocado cerca de ~mission(Location|Address). Buscamos operadores de combate disponibles para brindar apoyo. Si no los has enfrentado antes, es importante saber que XenoThreat son combatientes entrenados, por lo que no será una batalla fácil, pero es necesaria. Buena suerte, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>Fuerzas de XenoThreat lanzaron un ataque no provocado cerca de ~mission(Location|Address). Buscamos operadores de combate disponibles para brindar apoyo. [NL][NL]Si no los has enfrentado antes, es importante saber que XenoThreat son combatientes entrenados, por lo que esta no será una lucha fácil, pero es necesaria.[NL][NL]Buena suerte,[NL][NL]Lima Endicott[NL]Operadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="162">
@@ -1212,9 +1212,9 @@
         <v> Recuperar el puesto de avanzada de los cazadores de cabezas</v>
       </c>
     </row>
-    <row r="163" xml:space="preserve">
-      <c r="A163" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Citizens for Prosperity busca personal de seguridad para hacerse cargo de un antiguo puesto de avanzada de CFP que actualmente sirve de escondite para que los Headhunters lancen ataques por todo el sistema. Ubicado cerca de ~mission(Location|Address), recuperar este puesto permitirá a CFP brindar mayor apoyo a los esfuerzos locales para lograr la estabilidad. Lima Endicott, Despachadora principal, Citizens for Prosperity</v>
+    <row r="163">
+      <c r="A163" t="str">
+        <v> Ciudadanos por la Prosperidad busca personal de seguridad para hacerse cargo de un antiguo puesto de avanzada de CFP que actualmente sirve de escondite para que los Cazadores de Cabezas lancen ataques por todo el sistema. [NL][NL]Ubicado cerca de ~mission(Location|Address), recuperar este puesto de avanzada permitirá a CFP brindar mayor apoyo a los esfuerzos locales para construir estabilidad.[NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="164">
@@ -1222,9 +1222,9 @@
         <v> Recuperen el puesto de avanzada de la amenaza xeno</v>
       </c>
     </row>
-    <row r="165" xml:space="preserve">
-      <c r="A165" t="str" xml:space="preserve">
-        <v xml:space="preserve"> pesar de nuestros esfuerzos por promover la no violencia, grupos delictivos locales siguen atacando a nuestra organización. Recientemente, XenoThreat atacó ~mission(Location|Address) y expulsó a nuestros voluntarios que trabajaban allí. Buscamos reclutar personal de combate para retomar el puesto de avanzada. Idealmente, podríamos llegar a un acuerdo para que se marchen, pero XenoThreat recurre rápidamente a la violencia para resolver todos sus problemas, así que sin duda habrá una pelea. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="165">
+      <c r="A165" t="str">
+        <v> pesar de nuestros esfuerzos por promover la no violencia, grupos locales delictivos siguen atacando a nuestra organización. XenoThreat atacó recientemente ~mission(Location|Address) y expulsó a nuestros voluntarios que trabajaban allí.[NL][NL]Buscamos reclutar personal de combate para retomar el puesto de avanzada. Idealmente, podríamos llegar a un acuerdo para que se marchen, pero XenoThreat recurre rápidamente a la violencia para resolver todos sus problemas, así que sin duda habrá una pelea.[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="166">
@@ -1232,9 +1232,9 @@
         <v> Intercepción de la carrera de suministros</v>
       </c>
     </row>
-    <row r="167" xml:space="preserve">
-      <c r="A167" t="str" xml:space="preserve">
-        <v xml:space="preserve">La vida en la frontera es dura, y cada entrega a nuestros colonos es importante. No podemos permitirnos perder más este año. Uno de nuestros proveedores clave ha sido atacado por un grupo de forajidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y ha dejado de comunicarse con nosotros. Temo lo peor, pero si aún podemos recuperar los suministros que transportaban, podría marcar una gran diferencia. Es probable que los forajidos que los atacaron sigan merodeando por allí, así que manténganse alerta. Una vez que se hayan encargado de ellos, tomen la carga y llévenla al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Asegúrense de pilotar una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y lleven también un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;. Vuelen con seguridad, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>La vida es dura en la frontera, y cada entrega a nuestros colonos es importante. Realmente no podemos permitirnos perder más este año.[NL][NL]Uno de nuestros proveedores clave ha sido atacado por un grupo de forajidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y ha dejado de comunicarse con nosotros. Temo lo peor, pero si aún podemos recuperar los suministros que transportaban, podría marcar una gran diferencia.[NL][NL]Es probable que los forajidos que los atacaron todavía estén merodeando por allí, así que mantente alerta. Una vez que te hayas encargado de ellos, toma la carga y llévala al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Asegúrate de pilotar una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y lleva también un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;.[NL][NL]Vuela seguro ahí fuera,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="168">
@@ -1242,9 +1242,9 @@
         <v> Es necesario recuperar suministros esenciales.</v>
       </c>
     </row>
-    <row r="169" xml:space="preserve">
-      <c r="A169" t="str" xml:space="preserve">
-        <v xml:space="preserve">Estábamos en el proceso de entregar un envío urgente a la gente de &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; cuando nuestro piloto se topó con un grupo de forajidos. Intentaron huir, pero ya era demasiado tarde. Sin embargo, hay un lado positivo. Los rastreadores muestran que la carga sigue intacta, ubicada en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Hay muchas probabilidades de que los forajidos la estén custodiando mientras localizan una nave lo suficientemente grande para transportar todo. Aunque no quiero arriesgarme a perder a otro piloto, la necesidad de la carga a bordo es tan apremiante que justifica la decisión de enviar a alguien a recuperarla. Esto no será fácil, estos forajidos no tuvieron piedad con nuestro piloto. Tendrás que eliminarlos primero antes de recuperar la carga. Trae una nave que pueda almacenar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt; para el traslado. Entrégalo en el montacargas en &lt;EM4&gt;~misión(Destino)&lt;/EM4&gt; y solucionemos esto. Vuela seguro, Lima Endicott, Despachadora principal, Ciudadanos por la Prosperidad</v>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>Estábamos en el proceso de entregar un envío urgente a la gente de &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; cuando nuestro piloto se topó con un grupo de forajidos. Intentaron huir, pero ya era demasiado tarde.[NL][NL]Sin embargo, hay un lado positivo. Los rastreadores muestran que la carga sigue intacta, ubicada en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt;. Hay muchas posibilidades de que los forajidos la estén custodiando mientras localizan una nave lo suficientemente grande como para transportar todo. Aunque no quiero arriesgarme a perder a otro piloto, la necesidad de la carga a bordo es tan desesperada que justifica la decisión de enviar a alguien a recuperarla.[NL][NL]Esto no será fácil, estos forajidos no tuvieron piedad con nuestro piloto. Tendrás que eliminarlos primero antes de recuperar la carga. Trae una nave que pueda almacenar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt; para el traslado. Entrégalo en el montacargas en &lt;EM4&gt;~misión(Destino)&lt;/EM4&gt; y solucionemos esto.[NL][NL]Vuela seguro,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="170">
@@ -1252,9 +1252,9 @@
         <v>Recuperación de suministros valiosos</v>
       </c>
     </row>
-    <row r="171" xml:space="preserve">
-      <c r="A171" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Una nave de Ciudadanos por la Prosperidad ha sido emboscada por un grupo de forajidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitamos un piloto experto para ayudarlos. Perdimos el contacto con ellos durante la comunicación, pero parecía que estaban bajo fuego intenso. Puede que sea demasiado tarde para ellos, pero los suministros vitales que transportaban aún podrían ser útiles. Vuela hasta allí, elimina a los enemigos y recupera el cargamento. Necesitarás una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt; para transportar los suministros a tu nave. Llévalos al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; y te garantizo que se les dará un buen uso. Ten cuidado ahí fuera, Lima Endicott, Despachadora Principal de Ciudadanos por la Prosperidad.</v>
+    <row r="171">
+      <c r="A171" t="str">
+        <v> Una nave de Ciudadanos por la Prosperidad ha sido emboscada por un grupo de forajidos en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; y necesitamos un piloto experto para ayudarlos.[NL][NL]Perdimos el contacto con ellos durante las comunicaciones, pero parecía que estaban bajo fuego intenso. Puede que sea demasiado tarde para ellos, pero los suministros vitales que transportaban aún podrían ser útiles. Vuela hasta allí, elimina a los enemigos y recupera el cargamento. Necesitarás una nave que pueda soportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt; para transportar los suministros a tu nave.[NL][NL]Llévalos al montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; y te garantizo que se les dará un buen uso.[NL][NL]Ten cuidado ahí fuera,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="172">
@@ -1262,9 +1262,9 @@
         <v> Operación especial de recuperación</v>
       </c>
     </row>
-    <row r="173" xml:space="preserve">
-      <c r="A173" t="str" xml:space="preserve">
-        <v xml:space="preserve">Normalmente no le pediría a nadie que hiciera algo tan arriesgado, pero estas son circunstancias excepcionales. Nuestro piloto transportaba una carga vital cuando fue atacado por un grupo de forajidos. Bajo ninguna circunstancia podemos permitir que se apoderen de la carga. Dado el tamaño de la fuerza hostil que atacó, no podrás hacerlo solo; necesitarás traer una tripulación experta a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; para eliminar a estos forajidos y recuperar la carga. Asegúrate de que al menos uno de ustedes tenga una nave con capacidad para almacenar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;. Si por algún milagro logras recuperar la carga, llévala al montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;. Es mucho pedir, pero si lo consigues, tendrás mi agradecimiento y el de toda la organización. Mucha suerte, Lima Endicott, Despachadora Principal de Ciudadanos por la Prosperidad.</v>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>Normalmente no le pediría a alguien que hiciera algo tan arriesgado, pero estas son circunstancias excepcionales.[NL][NL]Nuestro piloto transportaba una carga vital cuando fue atacado por un grupo de forajidos. Bajo ninguna circunstancia podemos permitir que se apoderen de la carga.[NL][NL]Con el tamaño de la fuerza hostil que atacó, no podrás hacerlo solo, necesitarás traer una tripulación experta contigo a &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; para eliminar a estos forajidos y recuperar la carga. Asegúrense de que al menos uno de ustedes tenga una nave que pueda almacenar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;.[NL][NL]Si por algún milagro logran recuperar esa carga, llévenla al montacargas ubicado en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt;.[NL][NL]Es mucho pedir, pero si lo logran, contarán con mi agradecimiento y el de toda la organización.[NL][NL]Mucha suerte,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="174">
@@ -1272,9 +1272,9 @@
         <v>El envío de carga debe completarse.</v>
       </c>
     </row>
-    <row r="175" xml:space="preserve">
-      <c r="A175" t="str" xml:space="preserve">
-        <v xml:space="preserve">Cada vez más naves de la CFP están siendo atacadas últimamente, y a pesar de nuestros mejores esfuerzos por mantener nuestras rutas comerciales tranquilas, seguimos perdiendo transportistas en ataques de forajidos. Nuestro piloto en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; es la última víctima. Me duele pensar en todo lo que hemos perdido, pero mientras haya gente que necesite nuestra ayuda, tenemos que seguir luchando. Si tienes una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta potencia&lt;/EM4&gt;, necesitamos que te dirijas a la ubicación mencionada y recuperes esa carga. Esto no será fácil, el piloto era uno de los mejores y no se rendiría sin luchar. No subestimemos a estos forajidos, traigan una tripulación de confianza y cuídense las espaldas. Una vez que tengas la carga, entrégala en el montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; y yo me encargaré de procesarla. Buena suerte y cuídate, Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>Cada vez más naves de la CFP están siendo atacadas últimamente, y a pesar de nuestros mejores esfuerzos por mantener nuestras rutas comerciales tranquilas, seguimos perdiendo transportistas en ataques de forajidos.[NL][NL]Nuestro piloto en &lt;EM4&gt;~mission(Location|Address)&lt;/EM4&gt; es la última víctima. Me duele pensar en todo lo que hemos perdido, pero mientras haya gente que necesite nuestra ayuda, tenemos que seguir luchando.[NL][NL]Si tienes una nave que pueda transportar &lt;EM4&gt;~mission(MissionMaxSCUSize) contenedores de carga&lt;/EM4&gt; y un &lt;EM4&gt;rayo tractor de alta resistencia&lt;/EM4&gt;, necesitamos que te dirijas a la ubicación mencionada y recuperes esa carga.[NL][NL]Esto no será fácil, el piloto era uno de los mejores y no se rendiría sin luchar. No subestimemos a estos forajidos, traigan una tripulación de confianza y cuídense las espaldas.[NL][NL]Una vez que tengan la carga, entréguenla en el montacargas en &lt;EM4&gt;~mission(Destination|Address)&lt;/EM4&gt; y yo me encargaré de procesarla.[NL][NL]Buena suerte y cuídense,[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="176">
@@ -1282,9 +1282,9 @@
         <v>Suministros robados</v>
       </c>
     </row>
-    <row r="177" xml:space="preserve">
-      <c r="A177" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Hola, necesitamos tu ayuda. Una colaboradora local estaba realizando una entrega, pero lamentablemente se topó con unos forajidos y tuvo que entregar su mercancía. Lo bueno es que los forajidos no se percataron de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron el botín a la dirección indicada. Nos gustaría que recuperaras los paquetes y los entregaras en la dirección indicada. No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia. Además, para facilitarte la tarea, te sugiero que lleves contigo un rayo tractor portátil. ¿Qué te parece? Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="177">
+      <c r="A177" t="str">
+        <v> Hola, [NL][NL]Necesitamos tu ayuda.[NL][NL]Una colaboradora local estaba realizando una entrega para nosotros, pero desafortunadamente se topó con unos forajidos y tuvo que entregar su ~misión(Artículo). Lo bueno es que los forajidos no se dieron cuenta de los rastreadores que colocamos en la carga y ahora sabemos que se llevaron su botín a ~misión(Ubicación|Dirección). [NL][NL]Nos gustaría que recuperaras los paquetes y los entregaras en ~misión(Destino|Dirección). No creo que los forajidos los entreguen voluntariamente, pero no te pediría que te pusieras en peligro si estos suministros no fueran de vital importancia.[NL][NL]Además, para facilitarte la vida, te sugiero que lleves contigo un &lt;EM4&gt;rayo tractor portátil&lt;/EM4&gt;. [NL][NL]¿Qué te parece?[NL][NL]Lima Endicott[NL]Despachadora principal[NL]Citizens for Prosperity</v>
       </c>
     </row>
     <row r="178">
@@ -1292,19 +1292,19 @@
         <v> Material confidencial robado</v>
       </c>
     </row>
-    <row r="179" xml:space="preserve">
-      <c r="A179" t="str" xml:space="preserve">
-        <v xml:space="preserve">¿Estás disponible para un trabajo? Uno de nuestros centros de seguridad fue asaltado y robaron material altamente confidencial. Como puedes imaginar, Citizens for Prosperity necesita recuperarlo cuanto antes. Gracias a un contacto local, pudimos rastrear a los delincuentes hasta ~mission(Location|Address), donde almacenan el material confidencial en una bóveda automatizada de alta seguridad. Para acceder a ella, primero debes encontrar el código de recuperación e introducirlo en la cinta transportadora de la bóveda. Creemos que uno de los líderes de los delincuentes llevará el código consigo, por lo que es muy probable que tengas que hablar directamente con él para obtenerlo. Una vez que tengas el material confidencial en tu poder, te pedimos que lo entregues en ~mission(Dropoff1|Address). Si lo consigues, ayudarás mucho a muchas personas. Gracias de antemano, Lima Endicott, Despachadora Principal, Citizens for Prosperity</v>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>¿Estás disponible para un trabajo? Uno de nuestros lugares seguros fue atacado por delincuentes y robaron material altamente confidencial. Como puedes imaginar, Citizens for Prosperity está ansioso por recuperarlo lo antes posible.[NL][NL]Gracias a un contacto local, pudimos rastrear a los delincuentes hasta ~mission(Location|Address), donde almacenan el material confidencial dentro de una bóveda automatizada segura. Para acceder a ella, primero deberás encontrar el código de recuperación correspondiente e ingresarlo en la cinta transportadora de paquetes de la bóveda. Nuestra mejor suposición es que uno de los líderes forajidos llevará el código consigo, por lo que hay una alta probabilidad de que tengas que interactuar directamente con ellos para obtenerlo.[NL] [NL]Una vez que tengas en tu poder el material confidencial, queremos que lo entregues en ~mission(Dropoff1|Address).[NL][NL]Harás una gran diferencia para mucha gente si logras esto.[NL][NL]Gracias de antemano,[NL][NL]Lima Endicott[NL]Despachador principal[NL]Citizens for Prosperity[NL]</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v> Operación de detención de narcóticos</v>
-      </c>
-    </row>
-    <row r="181" xml:space="preserve">
-      <c r="A181" t="str" xml:space="preserve">
-        <v xml:space="preserve">Citizens for Prosperity ha estado trabajando arduamente para mejorar la vida de las personas en todo el sistema, pero una tarea que ya es difícil se vuelve casi imposible cuando las drogas entran en juego. Recientemente hemos visto a un traficante que se dirige específicamente a nuestros miembros más vulnerables y hemos experimentado contratiempos en todos los ámbitos. Esto tiene que parar. Nos gustaría que se dirigieran a ~mission(Location|Address) y pusieran fin de forma definitiva a su red de producción. Si lo hacen, esperamos poder ayudar a nuestra gente a retomar el buen camino. Lima Endicott, Coordinadora Principal de Citizens for Prosperity</v>
+        <v>Operación de detención de narcóticos</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v> Ciudadanos por la Prosperidad ha estado trabajando arduamente para mejorar la vida de las personas en todo el sistema, pero una tarea que ya es difícil se vuelve casi imposible cuando las drogas entran en juego. Recientemente hemos visto a un traficante que se dirige específicamente a nuestros más vulnerables y hemos experimentado contratiempos en todos los ámbitos. Esto tiene que parar. Nos gustaría que fueran a ~mission(Location|Address) y pusieran fin de forma permanente a su línea de producción. Si hacen esto, esperamos poder ayudar a nuestra gente a retomar el buen camino. Lima Endicott, Coordinadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="182">
@@ -1312,9 +1312,9 @@
         <v> Desactiva Headhunter Stronghold</v>
       </c>
     </row>
-    <row r="183" xml:space="preserve">
-      <c r="A183" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ante la reciente agresión perpetrada por los Cazadores de Cabezas contra nuestra gente, Ciudadanos por la Prosperidad ha estado organizando una operación a gran escala que, esperamos, les aseste un duro golpe. Sin embargo, antes de que esto suceda, necesitamos ganar algo más de tiempo para finalizar nuestros preparativos. Si pudieras destruir los generadores de energía en ~mission(Location|Address), lograrías retrasar a los Cazadores de Cabezas el tiempo suficiente para que podamos preparar nuestro contraataque. Tu ayuda será crucial para nuestro éxito. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad.</v>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Ante la reciente agresión perpetrada por los Cazadores de Cabezas contra nuestra gente, Ciudadanos por la Prosperidad ha estado organizando una operación a gran escala que, con suerte, les asestará un golpe significativo. Sin embargo, antes de que eso suceda, necesitamos ganar algo más de tiempo para finalizar nuestros preparativos. Si pudieras destruir los generadores de energía en ~mission(Location|Address), deberías retrasar a los Cazadores de Cabezas el tiempo suficiente para que preparemos nuestro contraataque. Tu ayuda será crucial para nuestro éxito. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="184">
@@ -1322,9 +1322,9 @@
         <v> Limitar la capacidad operativa de los forajidos</v>
       </c>
     </row>
-    <row r="185" xml:space="preserve">
-      <c r="A185" t="str" xml:space="preserve">
-        <v xml:space="preserve">En ~mission(Location|Address) hay una banda de forajidos que se ha convertido en un problema cada vez mayor para los asentamientos de Ciudadanos por la Prosperidad en el sector. Si bien la violencia directa contra los perpetradores podría ser efectiva, no se ajusta al espíritu de nuestra misión. En cambio, les pedimos que desconecten los generadores cerca de su fortaleza. Esto debería limitar su capacidad operativa y, con suerte, preservar vidas. Me gusta pensar que los forajidos de hoy son los miembros productivos de la sociedad del mañana. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Hay una banda de forajidos en ~mission(Location|Address) que se ha convertido en un problema cada vez mayor para los asentamientos de Ciudadanos por la Prosperidad en el sector.[NL][NL]Si bien la violencia directa contra los perpetradores podría ser efectiva, no está en consonancia con el espíritu de nuestra misión aquí. En cambio, nos gustaría que desconectaran los generadores cerca de su fortaleza. Esto debería limitar su capacidad operativa y, con suerte, preservar vidas. [NL][NL]Me gusta pensar que los forajidos de hoy son los miembros productivos de la sociedad del mañana.[NL] [NL]Lima Endicott[NL]Despachadora principal[NL]Ciudadanos por la Prosperidad</v>
       </c>
     </row>
     <row r="186">
@@ -1332,9 +1332,9 @@
         <v> Captura a los forajidos en ~mission(Ubicación) Sin conexión</v>
       </c>
     </row>
-    <row r="187" xml:space="preserve">
-      <c r="A187" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hemos recibido información de que los forajidos de ~mission(Location|Address) han comenzado a reclutar con la intención de lanzar un ataque contra Ciudadanos por la Prosperidad. Para evitar que la situación se descontrole, les pedimos que desactiven sus generadores de energía y detengan su expansión. Si lo logran, podrían salvar muchas vidas. Lima Endicott, Despachadora Principal, Ciudadanos por la Prosperidad</v>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Hemos recibido información de que los forajidos de ~mission(Location|Address) han comenzado a reclutar con la intención de lanzar un ataque contra Ciudadanos por la Prosperidad. [NL][NL]Para calmar la situación antes de que se salga de control, les pedimos que desactiven sus generadores de energía y detengan su expansión. [NL][NL]Si lo logran, podrían salvar muchas vidas.[NL] [NL]Lima Endicott[NL]Operadora principal[NL]Ciudadanos por la Prosperidad</v>
       </c